--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B42B12-FEE0-4949-9E90-981FC1549EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B35CE4-177C-494E-BC1D-DD12E803203A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DEZEMBRO" sheetId="1" r:id="rId1"/>
@@ -417,6 +417,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -424,12 +430,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -2416,14 +2416,14 @@
     </row>
     <row r="35" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
     </row>
     <row r="36" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -2801,15 +2801,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="36"/>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="36"/>
-      <c r="I70" s="36"/>
+      <c r="A70" s="38"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -2834,15 +2834,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="37"/>
-      <c r="B75" s="37"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
+      <c r="A75" s="39"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -2878,15 +2878,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="38"/>
-      <c r="B79" s="38"/>
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="38"/>
+      <c r="A79" s="40"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="40"/>
+      <c r="I79" s="40"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -2922,15 +2922,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="37"/>
-      <c r="B87" s="37"/>
-      <c r="C87" s="37"/>
-      <c r="D87" s="37"/>
-      <c r="E87" s="37"/>
-      <c r="F87" s="37"/>
-      <c r="G87" s="37"/>
-      <c r="H87" s="37"/>
-      <c r="I87" s="37"/>
+      <c r="A87" s="39"/>
+      <c r="B87" s="39"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="39"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="39"/>
+      <c r="G87" s="39"/>
+      <c r="H87" s="39"/>
+      <c r="I87" s="39"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -3033,15 +3033,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="36"/>
-      <c r="B100" s="36"/>
-      <c r="C100" s="36"/>
-      <c r="D100" s="36"/>
-      <c r="E100" s="36"/>
-      <c r="F100" s="36"/>
-      <c r="G100" s="36"/>
-      <c r="H100" s="36"/>
-      <c r="I100" s="36"/>
+      <c r="A100" s="38"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="38"/>
+      <c r="G100" s="38"/>
+      <c r="H100" s="38"/>
+      <c r="I100" s="38"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -3230,11 +3230,11 @@
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
       <c r="V2" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W2" s="11">
         <f t="array" ref="W2">_xlfn.IFS(V2="Verde",0,V2="Amarela",1.885,V2="Vermelha P1",4.463,V2="Vermelha P2",7.877)</f>
-        <v>4.4630000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
@@ -5330,14 +5330,14 @@
     <row r="34" spans="1:20" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -5714,15 +5714,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="36"/>
-      <c r="B71" s="36"/>
-      <c r="C71" s="36"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="36"/>
-      <c r="F71" s="36"/>
-      <c r="G71" s="36"/>
-      <c r="H71" s="36"/>
-      <c r="I71" s="36"/>
+      <c r="A71" s="38"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -5747,15 +5747,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="37"/>
-      <c r="B76" s="37"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="37"/>
-      <c r="I76" s="37"/>
+      <c r="A76" s="39"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -5791,15 +5791,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="38"/>
-      <c r="B80" s="38"/>
-      <c r="C80" s="38"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="38"/>
-      <c r="I80" s="38"/>
+      <c r="A80" s="40"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40"/>
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -5835,15 +5835,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="37"/>
-      <c r="B88" s="37"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="37"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
-      <c r="G88" s="37"/>
-      <c r="H88" s="37"/>
-      <c r="I88" s="37"/>
+      <c r="A88" s="39"/>
+      <c r="B88" s="39"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="39"/>
+      <c r="G88" s="39"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="39"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -5946,15 +5946,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="36"/>
-      <c r="B101" s="36"/>
-      <c r="C101" s="36"/>
-      <c r="D101" s="36"/>
-      <c r="E101" s="36"/>
-      <c r="F101" s="36"/>
-      <c r="G101" s="36"/>
-      <c r="H101" s="36"/>
-      <c r="I101" s="36"/>
+      <c r="A101" s="38"/>
+      <c r="B101" s="38"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="38"/>
+      <c r="G101" s="38"/>
+      <c r="H101" s="38"/>
+      <c r="I101" s="38"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -6143,11 +6143,11 @@
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
       <c r="V2" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W2" s="11">
         <f t="array" ref="W2">_xlfn.IFS(V2="Verde",0,V2="Amarela",1.885,V2="Vermelha P1",4.463,V2="Vermelha P2",7.877)</f>
-        <v>4.4630000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
@@ -7668,14 +7668,14 @@
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
-      <c r="B33" s="36"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
@@ -8052,15 +8052,15 @@
       <c r="I67" s="1"/>
     </row>
     <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A68" s="36"/>
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="36"/>
-      <c r="F68" s="36"/>
-      <c r="G68" s="36"/>
-      <c r="H68" s="36"/>
-      <c r="I68" s="36"/>
+      <c r="A68" s="38"/>
+      <c r="B68" s="38"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="38"/>
+      <c r="G68" s="38"/>
+      <c r="H68" s="38"/>
+      <c r="I68" s="38"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
@@ -8085,15 +8085,15 @@
       <c r="I70" s="23"/>
     </row>
     <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A73" s="37"/>
-      <c r="B73" s="37"/>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
+      <c r="A73" s="39"/>
+      <c r="B73" s="39"/>
+      <c r="C73" s="39"/>
+      <c r="D73" s="39"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="39"/>
+      <c r="G73" s="39"/>
+      <c r="H73" s="39"/>
+      <c r="I73" s="39"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
@@ -8129,15 +8129,15 @@
       <c r="I76" s="25"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A77" s="38"/>
-      <c r="B77" s="38"/>
-      <c r="C77" s="38"/>
-      <c r="D77" s="38"/>
-      <c r="E77" s="38"/>
-      <c r="F77" s="38"/>
-      <c r="G77" s="38"/>
-      <c r="H77" s="38"/>
-      <c r="I77" s="38"/>
+      <c r="A77" s="40"/>
+      <c r="B77" s="40"/>
+      <c r="C77" s="40"/>
+      <c r="D77" s="40"/>
+      <c r="E77" s="40"/>
+      <c r="F77" s="40"/>
+      <c r="G77" s="40"/>
+      <c r="H77" s="40"/>
+      <c r="I77" s="40"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
@@ -8173,15 +8173,15 @@
       <c r="B83" s="23"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A85" s="37"/>
-      <c r="B85" s="37"/>
-      <c r="C85" s="37"/>
-      <c r="D85" s="37"/>
-      <c r="E85" s="37"/>
-      <c r="F85" s="37"/>
-      <c r="G85" s="37"/>
-      <c r="H85" s="37"/>
-      <c r="I85" s="37"/>
+      <c r="A85" s="39"/>
+      <c r="B85" s="39"/>
+      <c r="C85" s="39"/>
+      <c r="D85" s="39"/>
+      <c r="E85" s="39"/>
+      <c r="F85" s="39"/>
+      <c r="G85" s="39"/>
+      <c r="H85" s="39"/>
+      <c r="I85" s="39"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
@@ -8284,15 +8284,15 @@
       <c r="B96" s="26"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A98" s="36"/>
-      <c r="B98" s="36"/>
-      <c r="C98" s="36"/>
-      <c r="D98" s="36"/>
-      <c r="E98" s="36"/>
-      <c r="F98" s="36"/>
-      <c r="G98" s="36"/>
-      <c r="H98" s="36"/>
-      <c r="I98" s="36"/>
+      <c r="A98" s="38"/>
+      <c r="B98" s="38"/>
+      <c r="C98" s="38"/>
+      <c r="D98" s="38"/>
+      <c r="E98" s="38"/>
+      <c r="F98" s="38"/>
+      <c r="G98" s="38"/>
+      <c r="H98" s="38"/>
+      <c r="I98" s="38"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
@@ -8481,11 +8481,11 @@
       <c r="S2" s="9"/>
       <c r="T2" s="9"/>
       <c r="V2" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W2" s="11">
         <f t="array" ref="W2">_xlfn.IFS(V2="Verde",0,V2="Amarela",1.885,V2="Vermelha P1",4.463,V2="Vermelha P2",7.877)</f>
-        <v>4.4630000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
@@ -10133,14 +10133,14 @@
     <row r="34" spans="1:20" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -10517,15 +10517,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="36"/>
-      <c r="B71" s="36"/>
-      <c r="C71" s="36"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="36"/>
-      <c r="F71" s="36"/>
-      <c r="G71" s="36"/>
-      <c r="H71" s="36"/>
-      <c r="I71" s="36"/>
+      <c r="A71" s="38"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -10550,15 +10550,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="37"/>
-      <c r="B76" s="37"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="37"/>
-      <c r="I76" s="37"/>
+      <c r="A76" s="39"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -10594,15 +10594,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="38"/>
-      <c r="B80" s="38"/>
-      <c r="C80" s="38"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="38"/>
-      <c r="I80" s="38"/>
+      <c r="A80" s="40"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40"/>
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -10638,15 +10638,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="37"/>
-      <c r="B88" s="37"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="37"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
-      <c r="G88" s="37"/>
-      <c r="H88" s="37"/>
-      <c r="I88" s="37"/>
+      <c r="A88" s="39"/>
+      <c r="B88" s="39"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="39"/>
+      <c r="G88" s="39"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="39"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -10749,15 +10749,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="36"/>
-      <c r="B101" s="36"/>
-      <c r="C101" s="36"/>
-      <c r="D101" s="36"/>
-      <c r="E101" s="36"/>
-      <c r="F101" s="36"/>
-      <c r="G101" s="36"/>
-      <c r="H101" s="36"/>
-      <c r="I101" s="36"/>
+      <c r="A101" s="38"/>
+      <c r="B101" s="38"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="38"/>
+      <c r="G101" s="38"/>
+      <c r="H101" s="38"/>
+      <c r="I101" s="38"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -12538,14 +12538,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -12923,15 +12923,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="36"/>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="36"/>
-      <c r="I70" s="36"/>
+      <c r="A70" s="38"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -12956,15 +12956,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="37"/>
-      <c r="B75" s="37"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
+      <c r="A75" s="39"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -13000,15 +13000,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="38"/>
-      <c r="B79" s="38"/>
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="38"/>
+      <c r="A79" s="40"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="40"/>
+      <c r="I79" s="40"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -13044,15 +13044,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="37"/>
-      <c r="B87" s="37"/>
-      <c r="C87" s="37"/>
-      <c r="D87" s="37"/>
-      <c r="E87" s="37"/>
-      <c r="F87" s="37"/>
-      <c r="G87" s="37"/>
-      <c r="H87" s="37"/>
-      <c r="I87" s="37"/>
+      <c r="A87" s="39"/>
+      <c r="B87" s="39"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="39"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="39"/>
+      <c r="G87" s="39"/>
+      <c r="H87" s="39"/>
+      <c r="I87" s="39"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -13155,15 +13155,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="36"/>
-      <c r="B100" s="36"/>
-      <c r="C100" s="36"/>
-      <c r="D100" s="36"/>
-      <c r="E100" s="36"/>
-      <c r="F100" s="36"/>
-      <c r="G100" s="36"/>
-      <c r="H100" s="36"/>
-      <c r="I100" s="36"/>
+      <c r="A100" s="38"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="38"/>
+      <c r="G100" s="38"/>
+      <c r="H100" s="38"/>
+      <c r="I100" s="38"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -14949,14 +14949,14 @@
     <row r="34" spans="1:20" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -15334,15 +15334,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="36"/>
-      <c r="B71" s="36"/>
-      <c r="C71" s="36"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="36"/>
-      <c r="F71" s="36"/>
-      <c r="G71" s="36"/>
-      <c r="H71" s="36"/>
-      <c r="I71" s="36"/>
+      <c r="A71" s="38"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -15367,15 +15367,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="37"/>
-      <c r="B76" s="37"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="37"/>
-      <c r="I76" s="37"/>
+      <c r="A76" s="39"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -15411,15 +15411,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="38"/>
-      <c r="B80" s="38"/>
-      <c r="C80" s="38"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="38"/>
-      <c r="I80" s="38"/>
+      <c r="A80" s="40"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40"/>
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -15455,15 +15455,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="37"/>
-      <c r="B88" s="37"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="37"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
-      <c r="G88" s="37"/>
-      <c r="H88" s="37"/>
-      <c r="I88" s="37"/>
+      <c r="A88" s="39"/>
+      <c r="B88" s="39"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="39"/>
+      <c r="G88" s="39"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="39"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -15566,15 +15566,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="36"/>
-      <c r="B101" s="36"/>
-      <c r="C101" s="36"/>
-      <c r="D101" s="36"/>
-      <c r="E101" s="36"/>
-      <c r="F101" s="36"/>
-      <c r="G101" s="36"/>
-      <c r="H101" s="36"/>
-      <c r="I101" s="36"/>
+      <c r="A101" s="38"/>
+      <c r="B101" s="38"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="38"/>
+      <c r="G101" s="38"/>
+      <c r="H101" s="38"/>
+      <c r="I101" s="38"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -17300,14 +17300,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -17685,15 +17685,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="36"/>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="36"/>
-      <c r="I70" s="36"/>
+      <c r="A70" s="38"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -17718,15 +17718,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="37"/>
-      <c r="B75" s="37"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
+      <c r="A75" s="39"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -17762,15 +17762,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="38"/>
-      <c r="B79" s="38"/>
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="38"/>
+      <c r="A79" s="40"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="40"/>
+      <c r="I79" s="40"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -17806,15 +17806,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="37"/>
-      <c r="B87" s="37"/>
-      <c r="C87" s="37"/>
-      <c r="D87" s="37"/>
-      <c r="E87" s="37"/>
-      <c r="F87" s="37"/>
-      <c r="G87" s="37"/>
-      <c r="H87" s="37"/>
-      <c r="I87" s="37"/>
+      <c r="A87" s="39"/>
+      <c r="B87" s="39"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="39"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="39"/>
+      <c r="G87" s="39"/>
+      <c r="H87" s="39"/>
+      <c r="I87" s="39"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -17917,15 +17917,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="36"/>
-      <c r="B100" s="36"/>
-      <c r="C100" s="36"/>
-      <c r="D100" s="36"/>
-      <c r="E100" s="36"/>
-      <c r="F100" s="36"/>
-      <c r="G100" s="36"/>
-      <c r="H100" s="36"/>
-      <c r="I100" s="36"/>
+      <c r="A100" s="38"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="38"/>
+      <c r="G100" s="38"/>
+      <c r="H100" s="38"/>
+      <c r="I100" s="38"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -19710,14 +19710,14 @@
     </row>
     <row r="35" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
     </row>
     <row r="36" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -20095,15 +20095,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="36"/>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="36"/>
-      <c r="I70" s="36"/>
+      <c r="A70" s="38"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -20128,15 +20128,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="37"/>
-      <c r="B75" s="37"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
+      <c r="A75" s="39"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -20172,15 +20172,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="38"/>
-      <c r="B79" s="38"/>
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="38"/>
+      <c r="A79" s="40"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="40"/>
+      <c r="I79" s="40"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -20216,15 +20216,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="37"/>
-      <c r="B87" s="37"/>
-      <c r="C87" s="37"/>
-      <c r="D87" s="37"/>
-      <c r="E87" s="37"/>
-      <c r="F87" s="37"/>
-      <c r="G87" s="37"/>
-      <c r="H87" s="37"/>
-      <c r="I87" s="37"/>
+      <c r="A87" s="39"/>
+      <c r="B87" s="39"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="39"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="39"/>
+      <c r="G87" s="39"/>
+      <c r="H87" s="39"/>
+      <c r="I87" s="39"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -20327,15 +20327,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="36"/>
-      <c r="B100" s="36"/>
-      <c r="C100" s="36"/>
-      <c r="D100" s="36"/>
-      <c r="E100" s="36"/>
-      <c r="F100" s="36"/>
-      <c r="G100" s="36"/>
-      <c r="H100" s="36"/>
-      <c r="I100" s="36"/>
+      <c r="A100" s="38"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="38"/>
+      <c r="G100" s="38"/>
+      <c r="H100" s="38"/>
+      <c r="I100" s="38"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -21358,14 +21358,14 @@
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="39"/>
-      <c r="R18" s="39"/>
-      <c r="S18" s="39"/>
-      <c r="T18" s="39"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
+      <c r="S18" s="36"/>
+      <c r="T18" s="36"/>
     </row>
     <row r="19" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="17">
@@ -21410,14 +21410,14 @@
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="40"/>
-      <c r="R19" s="40"/>
-      <c r="S19" s="40"/>
-      <c r="T19" s="40"/>
+      <c r="M19" s="37"/>
+      <c r="N19" s="37"/>
+      <c r="O19" s="37"/>
+      <c r="P19" s="37"/>
+      <c r="Q19" s="37"/>
+      <c r="R19" s="37"/>
+      <c r="S19" s="37"/>
+      <c r="T19" s="37"/>
     </row>
     <row r="20" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="17">
@@ -21566,14 +21566,14 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="M22" s="40"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="40"/>
-      <c r="P22" s="40"/>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="40"/>
-      <c r="S22" s="40"/>
-      <c r="T22" s="40"/>
+      <c r="M22" s="37"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="37"/>
+      <c r="P22" s="37"/>
+      <c r="Q22" s="37"/>
+      <c r="R22" s="37"/>
+      <c r="S22" s="37"/>
+      <c r="T22" s="37"/>
     </row>
     <row r="23" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="17">
@@ -22120,14 +22120,14 @@
     </row>
     <row r="36" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -22505,15 +22505,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="36"/>
-      <c r="B71" s="36"/>
-      <c r="C71" s="36"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="36"/>
-      <c r="F71" s="36"/>
-      <c r="G71" s="36"/>
-      <c r="H71" s="36"/>
-      <c r="I71" s="36"/>
+      <c r="A71" s="38"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -22538,15 +22538,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="37"/>
-      <c r="B76" s="37"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="37"/>
-      <c r="I76" s="37"/>
+      <c r="A76" s="39"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -22582,15 +22582,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="38"/>
-      <c r="B80" s="38"/>
-      <c r="C80" s="38"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="38"/>
-      <c r="I80" s="38"/>
+      <c r="A80" s="40"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40"/>
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -22626,15 +22626,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="37"/>
-      <c r="B88" s="37"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="37"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
-      <c r="G88" s="37"/>
-      <c r="H88" s="37"/>
-      <c r="I88" s="37"/>
+      <c r="A88" s="39"/>
+      <c r="B88" s="39"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="39"/>
+      <c r="G88" s="39"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="39"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -22737,15 +22737,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="36"/>
-      <c r="B101" s="36"/>
-      <c r="C101" s="36"/>
-      <c r="D101" s="36"/>
-      <c r="E101" s="36"/>
-      <c r="F101" s="36"/>
-      <c r="G101" s="36"/>
-      <c r="H101" s="36"/>
-      <c r="I101" s="36"/>
+      <c r="A101" s="38"/>
+      <c r="B101" s="38"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="38"/>
+      <c r="G101" s="38"/>
+      <c r="H101" s="38"/>
+      <c r="I101" s="38"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -23913,7 +23913,7 @@
         <v>9318</v>
       </c>
       <c r="P16" s="16">
-        <v>11812</v>
+        <v>10812</v>
       </c>
       <c r="Q16" s="16">
         <v>1275</v>
@@ -23962,7 +23962,7 @@
       </c>
       <c r="I17" s="7">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17" s="7">
         <f t="shared" si="16"/>
@@ -23982,7 +23982,7 @@
         <v>9322</v>
       </c>
       <c r="P17" s="16">
-        <v>11813</v>
+        <v>10813</v>
       </c>
       <c r="Q17" s="16">
         <v>1275</v>
@@ -24051,7 +24051,7 @@
         <v>9323</v>
       </c>
       <c r="P18" s="16">
-        <v>11813</v>
+        <v>10813</v>
       </c>
       <c r="Q18" s="16">
         <v>1275</v>
@@ -24059,8 +24059,8 @@
       <c r="R18" s="16">
         <v>3755</v>
       </c>
-      <c r="S18" s="16">
-        <v>379</v>
+      <c r="S18" s="37">
+        <v>377</v>
       </c>
       <c r="T18" s="16">
         <v>3379</v>
@@ -24076,15 +24076,15 @@
       </c>
       <c r="C19" s="7">
         <f t="shared" si="10"/>
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="11"/>
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="E19" s="7">
         <f t="shared" si="12"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F19" s="7">
         <f t="shared" si="17"/>
@@ -24096,7 +24096,7 @@
       </c>
       <c r="H19" s="7">
         <f t="shared" si="14"/>
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I19" s="7">
         <f t="shared" si="15"/>
@@ -24104,35 +24104,35 @@
       </c>
       <c r="J19" s="7">
         <f t="shared" si="16"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K19" s="18"/>
       <c r="L19" s="17">
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="M19" s="40">
+      <c r="M19" s="37">
         <v>7192</v>
       </c>
-      <c r="N19" s="40">
+      <c r="N19" s="37">
         <v>9010</v>
       </c>
-      <c r="O19" s="40">
+      <c r="O19" s="37">
         <v>9328</v>
       </c>
-      <c r="P19" s="40">
-        <v>11815</v>
-      </c>
-      <c r="Q19" s="40">
+      <c r="P19" s="37">
+        <v>10815</v>
+      </c>
+      <c r="Q19" s="37">
         <v>1275</v>
       </c>
-      <c r="R19" s="40">
+      <c r="R19" s="37">
         <v>3757</v>
       </c>
-      <c r="S19" s="40">
-        <v>379</v>
-      </c>
-      <c r="T19" s="40">
+      <c r="S19" s="37">
+        <v>377</v>
+      </c>
+      <c r="T19" s="37">
         <v>3381</v>
       </c>
     </row>
@@ -24146,19 +24146,19 @@
       </c>
       <c r="C20" s="7">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D20" s="7">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E20" s="7">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F20" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G20" s="7">
         <f t="shared" si="13"/>
@@ -24166,43 +24166,43 @@
       </c>
       <c r="H20" s="7">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" s="7">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="17">
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="M20" s="40">
-        <v>7326</v>
-      </c>
-      <c r="N20" s="40">
-        <v>9120</v>
-      </c>
-      <c r="O20" s="40">
-        <v>9339</v>
-      </c>
-      <c r="P20" s="40">
-        <v>11815</v>
-      </c>
-      <c r="Q20" s="40">
+      <c r="M20" s="37">
+        <v>7267</v>
+      </c>
+      <c r="N20" s="37">
+        <v>9065</v>
+      </c>
+      <c r="O20" s="37">
+        <v>9328</v>
+      </c>
+      <c r="P20" s="37">
+        <v>10815</v>
+      </c>
+      <c r="Q20" s="37">
         <v>1275</v>
       </c>
-      <c r="R20" s="40">
-        <v>3771</v>
-      </c>
-      <c r="S20" s="40">
-        <v>379</v>
-      </c>
-      <c r="T20" s="40">
-        <v>3393</v>
+      <c r="R20" s="37">
+        <v>3762</v>
+      </c>
+      <c r="S20" s="37">
+        <v>377</v>
+      </c>
+      <c r="T20" s="37">
+        <v>3385</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
@@ -24215,19 +24215,19 @@
       </c>
       <c r="C21" s="7">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D21" s="7">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E21" s="7">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F21" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="7">
         <f t="shared" si="13"/>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="H21" s="7">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I21" s="7">
         <f t="shared" si="15"/>
@@ -24243,35 +24243,35 @@
       </c>
       <c r="J21" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L21" s="17">
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="M21" s="40">
-        <v>7326</v>
-      </c>
-      <c r="N21" s="40">
-        <v>9120</v>
-      </c>
-      <c r="O21" s="40">
-        <v>9339</v>
-      </c>
-      <c r="P21" s="40">
-        <v>11815</v>
-      </c>
-      <c r="Q21" s="40">
+      <c r="M21" s="37">
+        <v>7302</v>
+      </c>
+      <c r="N21" s="37">
+        <v>9109</v>
+      </c>
+      <c r="O21" s="37">
+        <v>9335</v>
+      </c>
+      <c r="P21" s="37">
+        <v>10814</v>
+      </c>
+      <c r="Q21" s="37">
         <v>1275</v>
       </c>
-      <c r="R21" s="40">
-        <v>3771</v>
-      </c>
-      <c r="S21" s="40">
+      <c r="R21" s="37">
+        <v>3764</v>
+      </c>
+      <c r="S21" s="37">
         <v>379</v>
       </c>
-      <c r="T21" s="40">
-        <v>3393</v>
+      <c r="T21" s="37">
+        <v>3386</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
@@ -24284,62 +24284,62 @@
       </c>
       <c r="C22" s="7">
         <f t="shared" si="10"/>
-        <v>-7326</v>
+        <v>20</v>
       </c>
       <c r="D22" s="7">
         <f t="shared" si="11"/>
-        <v>-9120</v>
+        <v>29</v>
       </c>
       <c r="E22" s="7">
         <f t="shared" si="12"/>
-        <v>-9339</v>
+        <v>3</v>
       </c>
       <c r="F22" s="7">
         <f t="shared" si="17"/>
-        <v>-11815</v>
+        <v>1</v>
       </c>
       <c r="G22" s="7">
         <f t="shared" si="13"/>
-        <v>-1275</v>
+        <v>0</v>
       </c>
       <c r="H22" s="7">
         <f t="shared" si="14"/>
-        <v>-3771</v>
+        <v>5</v>
       </c>
       <c r="I22" s="7">
         <f t="shared" si="15"/>
-        <v>-379</v>
+        <v>0</v>
       </c>
       <c r="J22" s="7">
         <f t="shared" si="16"/>
-        <v>-3393</v>
+        <v>4</v>
       </c>
       <c r="L22" s="17">
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="M22" s="40">
+      <c r="M22" s="37">
         <v>7326</v>
       </c>
-      <c r="N22" s="40">
+      <c r="N22" s="37">
         <v>9120</v>
       </c>
-      <c r="O22" s="40">
+      <c r="O22" s="37">
         <v>9339</v>
       </c>
-      <c r="P22" s="40">
-        <v>11815</v>
-      </c>
-      <c r="Q22" s="40">
+      <c r="P22" s="37">
+        <v>10815</v>
+      </c>
+      <c r="Q22" s="37">
         <v>1275</v>
       </c>
-      <c r="R22" s="40">
+      <c r="R22" s="37">
         <v>3771</v>
       </c>
-      <c r="S22" s="40">
+      <c r="S22" s="37">
         <v>379</v>
       </c>
-      <c r="T22" s="40">
+      <c r="T22" s="37">
         <v>3393</v>
       </c>
     </row>
@@ -24353,15 +24353,15 @@
       </c>
       <c r="C23" s="7">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D23" s="7">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E23" s="7">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F23" s="7">
         <f t="shared" si="17"/>
@@ -24373,7 +24373,7 @@
       </c>
       <c r="H23" s="7">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I23" s="7">
         <f t="shared" si="15"/>
@@ -24381,20 +24381,36 @@
       </c>
       <c r="J23" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L23" s="17">
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
-      <c r="T23" s="15"/>
+      <c r="M23" s="15">
+        <v>7346</v>
+      </c>
+      <c r="N23" s="15">
+        <v>9149</v>
+      </c>
+      <c r="O23" s="15">
+        <v>9342</v>
+      </c>
+      <c r="P23" s="15">
+        <v>10816</v>
+      </c>
+      <c r="Q23" s="15">
+        <v>1275</v>
+      </c>
+      <c r="R23" s="15">
+        <v>3776</v>
+      </c>
+      <c r="S23" s="15">
+        <v>379</v>
+      </c>
+      <c r="T23" s="15">
+        <v>3397</v>
+      </c>
     </row>
     <row r="24" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="17">
@@ -24406,19 +24422,19 @@
       </c>
       <c r="C24" s="7">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D24" s="7">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E24" s="7">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F24" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="7">
         <f t="shared" si="13"/>
@@ -24426,7 +24442,7 @@
       </c>
       <c r="H24" s="7">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I24" s="7">
         <f t="shared" si="15"/>
@@ -24434,20 +24450,36 @@
       </c>
       <c r="J24" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L24" s="17">
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="15"/>
-      <c r="S24" s="15"/>
-      <c r="T24" s="15"/>
+      <c r="M24" s="15">
+        <v>7374</v>
+      </c>
+      <c r="N24" s="15">
+        <v>9204</v>
+      </c>
+      <c r="O24" s="15">
+        <v>9345</v>
+      </c>
+      <c r="P24" s="15">
+        <v>10816</v>
+      </c>
+      <c r="Q24" s="15">
+        <v>1275</v>
+      </c>
+      <c r="R24" s="15">
+        <v>3780</v>
+      </c>
+      <c r="S24" s="15">
+        <v>379</v>
+      </c>
+      <c r="T24" s="15">
+        <v>3401</v>
+      </c>
     </row>
     <row r="25" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="20">
@@ -24459,48 +24491,64 @@
       </c>
       <c r="C25" s="7">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-7408</v>
       </c>
       <c r="D25" s="7">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-9260</v>
       </c>
       <c r="E25" s="7">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>-9349</v>
       </c>
       <c r="F25" s="7">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-10817</v>
       </c>
       <c r="G25" s="7">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-1275</v>
       </c>
       <c r="H25" s="7">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-3785</v>
       </c>
       <c r="I25" s="7">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>-379</v>
       </c>
       <c r="J25" s="7">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>-3406</v>
       </c>
       <c r="L25" s="17">
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
+      <c r="M25" s="15">
+        <v>7408</v>
+      </c>
+      <c r="N25" s="15">
+        <v>9260</v>
+      </c>
+      <c r="O25" s="15">
+        <v>9349</v>
+      </c>
+      <c r="P25" s="15">
+        <v>10817</v>
+      </c>
+      <c r="Q25" s="15">
+        <v>1275</v>
+      </c>
+      <c r="R25" s="15">
+        <v>3785</v>
+      </c>
+      <c r="S25" s="15">
+        <v>379</v>
+      </c>
+      <c r="T25" s="15">
+        <v>3406</v>
+      </c>
     </row>
     <row r="26" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="17">
@@ -24841,14 +24889,14 @@
     <row r="35" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="38"/>
       <c r="K35"/>
     </row>
     <row r="36" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
@@ -25261,16 +25309,16 @@
       <c r="J69" s="1"/>
     </row>
     <row r="70" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="36"/>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="36"/>
-      <c r="I70" s="36"/>
-      <c r="J70" s="36"/>
+      <c r="A70" s="38"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
+      <c r="J70" s="38"/>
     </row>
     <row r="71" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -25297,16 +25345,16 @@
       <c r="J72" s="23"/>
     </row>
     <row r="75" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="37"/>
-      <c r="B75" s="37"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
-      <c r="J75" s="37"/>
+      <c r="A75" s="39"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
+      <c r="J75" s="39"/>
     </row>
     <row r="76" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -25345,16 +25393,16 @@
       <c r="J78" s="25"/>
     </row>
     <row r="79" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="38"/>
-      <c r="B79" s="38"/>
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="38"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="38"/>
-      <c r="J79" s="38"/>
+      <c r="A79" s="40"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="40"/>
+      <c r="I79" s="40"/>
+      <c r="J79" s="40"/>
     </row>
     <row r="80" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -25395,16 +25443,16 @@
       <c r="C85" s="23"/>
     </row>
     <row r="87" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="37"/>
-      <c r="B87" s="37"/>
-      <c r="C87" s="37"/>
-      <c r="D87" s="37"/>
-      <c r="E87" s="37"/>
-      <c r="F87" s="37"/>
-      <c r="G87" s="37"/>
-      <c r="H87" s="37"/>
-      <c r="I87" s="37"/>
-      <c r="J87" s="37"/>
+      <c r="A87" s="39"/>
+      <c r="B87" s="39"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="39"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="39"/>
+      <c r="G87" s="39"/>
+      <c r="H87" s="39"/>
+      <c r="I87" s="39"/>
+      <c r="J87" s="39"/>
     </row>
     <row r="88" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -25518,16 +25566,16 @@
       <c r="C98" s="26"/>
     </row>
     <row r="100" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="36"/>
-      <c r="B100" s="36"/>
-      <c r="C100" s="36"/>
-      <c r="D100" s="36"/>
-      <c r="E100" s="36"/>
-      <c r="F100" s="36"/>
-      <c r="G100" s="36"/>
-      <c r="H100" s="36"/>
-      <c r="I100" s="36"/>
-      <c r="J100" s="36"/>
+      <c r="A100" s="38"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="38"/>
+      <c r="G100" s="38"/>
+      <c r="H100" s="38"/>
+      <c r="I100" s="38"/>
+      <c r="J100" s="38"/>
     </row>
     <row r="101" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -25569,7 +25617,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -25742,11 +25790,11 @@
         <v>3203</v>
       </c>
       <c r="V2" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="W2" s="11">
         <f t="array" ref="W2">_xlfn.IFS(V2="Verde",0,V2="Amarela",1.885,V2="Vermelha P1",4.463,V2="Vermelha P2",7.877)</f>
-        <v>4.4630000000000001</v>
+        <v>1.885</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
@@ -27890,14 +27938,14 @@
     <row r="34" spans="1:20" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -28275,15 +28323,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="36"/>
-      <c r="B71" s="36"/>
-      <c r="C71" s="36"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="36"/>
-      <c r="F71" s="36"/>
-      <c r="G71" s="36"/>
-      <c r="H71" s="36"/>
-      <c r="I71" s="36"/>
+      <c r="A71" s="38"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -28308,15 +28356,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="37"/>
-      <c r="B76" s="37"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="37"/>
-      <c r="I76" s="37"/>
+      <c r="A76" s="39"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -28352,15 +28400,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="38"/>
-      <c r="B80" s="38"/>
-      <c r="C80" s="38"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="38"/>
-      <c r="I80" s="38"/>
+      <c r="A80" s="40"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40"/>
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -28396,15 +28444,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="37"/>
-      <c r="B88" s="37"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="37"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
-      <c r="G88" s="37"/>
-      <c r="H88" s="37"/>
-      <c r="I88" s="37"/>
+      <c r="A88" s="39"/>
+      <c r="B88" s="39"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="39"/>
+      <c r="G88" s="39"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="39"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -28507,15 +28555,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="36"/>
-      <c r="B101" s="36"/>
-      <c r="C101" s="36"/>
-      <c r="D101" s="36"/>
-      <c r="E101" s="36"/>
-      <c r="F101" s="36"/>
-      <c r="G101" s="36"/>
-      <c r="H101" s="36"/>
-      <c r="I101" s="36"/>
+      <c r="A101" s="38"/>
+      <c r="B101" s="38"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="38"/>
+      <c r="G101" s="38"/>
+      <c r="H101" s="38"/>
+      <c r="I101" s="38"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -28733,11 +28781,11 @@
         <v>3069</v>
       </c>
       <c r="V2" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W2" s="11">
         <f t="array" ref="W2">_xlfn.IFS(V2="Verde",0,V2="Amarela",1.885,V2="Vermelha P1",4.463,V2="Vermelha P2",7.877)</f>
-        <v>4.4630000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="12.75" x14ac:dyDescent="0.2">
@@ -30872,15 +30920,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="36"/>
-      <c r="B69" s="36"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="36"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="36"/>
-      <c r="G69" s="36"/>
-      <c r="H69" s="36"/>
-      <c r="I69" s="36"/>
+      <c r="A69" s="38"/>
+      <c r="B69" s="38"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="38"/>
+      <c r="G69" s="38"/>
+      <c r="H69" s="38"/>
+      <c r="I69" s="38"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -30905,15 +30953,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="37"/>
-      <c r="B74" s="37"/>
-      <c r="C74" s="37"/>
-      <c r="D74" s="37"/>
-      <c r="E74" s="37"/>
-      <c r="F74" s="37"/>
-      <c r="G74" s="37"/>
-      <c r="H74" s="37"/>
-      <c r="I74" s="37"/>
+      <c r="A74" s="39"/>
+      <c r="B74" s="39"/>
+      <c r="C74" s="39"/>
+      <c r="D74" s="39"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="39"/>
+      <c r="G74" s="39"/>
+      <c r="H74" s="39"/>
+      <c r="I74" s="39"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -30949,15 +30997,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="38"/>
-      <c r="B78" s="38"/>
-      <c r="C78" s="38"/>
-      <c r="D78" s="38"/>
-      <c r="E78" s="38"/>
-      <c r="F78" s="38"/>
-      <c r="G78" s="38"/>
-      <c r="H78" s="38"/>
-      <c r="I78" s="38"/>
+      <c r="A78" s="40"/>
+      <c r="B78" s="40"/>
+      <c r="C78" s="40"/>
+      <c r="D78" s="40"/>
+      <c r="E78" s="40"/>
+      <c r="F78" s="40"/>
+      <c r="G78" s="40"/>
+      <c r="H78" s="40"/>
+      <c r="I78" s="40"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -30993,15 +31041,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="37"/>
-      <c r="B86" s="37"/>
-      <c r="C86" s="37"/>
-      <c r="D86" s="37"/>
-      <c r="E86" s="37"/>
-      <c r="F86" s="37"/>
-      <c r="G86" s="37"/>
-      <c r="H86" s="37"/>
-      <c r="I86" s="37"/>
+      <c r="A86" s="39"/>
+      <c r="B86" s="39"/>
+      <c r="C86" s="39"/>
+      <c r="D86" s="39"/>
+      <c r="E86" s="39"/>
+      <c r="F86" s="39"/>
+      <c r="G86" s="39"/>
+      <c r="H86" s="39"/>
+      <c r="I86" s="39"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -31104,15 +31152,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="36"/>
-      <c r="B99" s="36"/>
-      <c r="C99" s="36"/>
-      <c r="D99" s="36"/>
-      <c r="E99" s="36"/>
-      <c r="F99" s="36"/>
-      <c r="G99" s="36"/>
-      <c r="H99" s="36"/>
-      <c r="I99" s="36"/>
+      <c r="A99" s="38"/>
+      <c r="B99" s="38"/>
+      <c r="C99" s="38"/>
+      <c r="D99" s="38"/>
+      <c r="E99" s="38"/>
+      <c r="F99" s="38"/>
+      <c r="G99" s="38"/>
+      <c r="H99" s="38"/>
+      <c r="I99" s="38"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC02BD70-98DC-4951-9D9D-6946BF8C6E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DC499F-3250-4EB9-BD89-2E1073A6FC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DEZEMBRO" sheetId="1" r:id="rId1"/>
@@ -259,7 +259,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -353,17 +353,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -467,13 +456,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -483,10 +465,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3366,14 +3355,14 @@
     </row>
     <row r="35" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
     </row>
     <row r="36" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -3751,15 +3740,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="34"/>
-      <c r="B70" s="34"/>
-      <c r="C70" s="34"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="34"/>
-      <c r="G70" s="34"/>
-      <c r="H70" s="34"/>
-      <c r="I70" s="34"/>
+      <c r="A70" s="38"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -3784,15 +3773,15 @@
       <c r="I72" s="21"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="35"/>
-      <c r="B75" s="35"/>
-      <c r="C75" s="35"/>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
+      <c r="A75" s="39"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -3828,15 +3817,15 @@
       <c r="I78" s="23"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="36"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-      <c r="G79" s="36"/>
-      <c r="H79" s="36"/>
-      <c r="I79" s="36"/>
+      <c r="A79" s="40"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="40"/>
+      <c r="I79" s="40"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -3872,15 +3861,15 @@
       <c r="B85" s="21"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="35"/>
-      <c r="B87" s="35"/>
-      <c r="C87" s="35"/>
-      <c r="D87" s="35"/>
-      <c r="E87" s="35"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="35"/>
+      <c r="A87" s="39"/>
+      <c r="B87" s="39"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="39"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="39"/>
+      <c r="G87" s="39"/>
+      <c r="H87" s="39"/>
+      <c r="I87" s="39"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -3983,15 +3972,15 @@
       <c r="B98" s="24"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="34"/>
-      <c r="B100" s="34"/>
-      <c r="C100" s="34"/>
-      <c r="D100" s="34"/>
-      <c r="E100" s="34"/>
-      <c r="F100" s="34"/>
-      <c r="G100" s="34"/>
-      <c r="H100" s="34"/>
-      <c r="I100" s="34"/>
+      <c r="A100" s="38"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="38"/>
+      <c r="G100" s="38"/>
+      <c r="H100" s="38"/>
+      <c r="I100" s="38"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -4224,28 +4213,28 @@
       <c r="U2" s="7">
         <v>0</v>
       </c>
-      <c r="V2" s="37">
+      <c r="V2" s="34">
         <v>594</v>
       </c>
-      <c r="W2" s="37">
+      <c r="W2" s="34">
         <v>1193</v>
       </c>
-      <c r="X2" s="37">
+      <c r="X2" s="34">
         <v>8925</v>
       </c>
-      <c r="Y2" s="37">
+      <c r="Y2" s="34">
         <v>10736</v>
       </c>
-      <c r="Z2" s="37">
+      <c r="Z2" s="34">
         <v>1256</v>
       </c>
-      <c r="AA2" s="37">
+      <c r="AA2" s="34">
         <v>3235</v>
       </c>
-      <c r="AB2" s="37">
+      <c r="AB2" s="34">
         <v>321</v>
       </c>
-      <c r="AC2" s="37">
+      <c r="AC2" s="34">
         <v>2913</v>
       </c>
       <c r="AE2" s="9" t="s">
@@ -4326,28 +4315,28 @@
       <c r="U3" s="15">
         <v>1</v>
       </c>
-      <c r="V3" s="37">
+      <c r="V3" s="34">
         <v>594</v>
       </c>
-      <c r="W3" s="37">
+      <c r="W3" s="34">
         <v>1193</v>
       </c>
-      <c r="X3" s="37">
+      <c r="X3" s="34">
         <v>8925</v>
       </c>
-      <c r="Y3" s="37">
+      <c r="Y3" s="34">
         <v>10736</v>
       </c>
-      <c r="Z3" s="37">
+      <c r="Z3" s="34">
         <v>1256</v>
       </c>
-      <c r="AA3" s="37">
+      <c r="AA3" s="34">
         <v>3235</v>
       </c>
-      <c r="AB3" s="37">
+      <c r="AB3" s="34">
         <v>321</v>
       </c>
-      <c r="AC3" s="37">
+      <c r="AC3" s="34">
         <v>2913</v>
       </c>
     </row>
@@ -4422,28 +4411,28 @@
         <f t="shared" ref="U4:U33" si="8">U3+1</f>
         <v>2</v>
       </c>
-      <c r="V4" s="37">
+      <c r="V4" s="34">
         <v>671</v>
       </c>
-      <c r="W4" s="37">
+      <c r="W4" s="34">
         <v>1289</v>
       </c>
-      <c r="X4" s="37">
+      <c r="X4" s="34">
         <v>8928</v>
       </c>
-      <c r="Y4" s="37">
+      <c r="Y4" s="34">
         <v>10736</v>
       </c>
-      <c r="Z4" s="37">
+      <c r="Z4" s="34">
         <v>1256</v>
       </c>
-      <c r="AA4" s="37">
+      <c r="AA4" s="34">
         <v>3238</v>
       </c>
-      <c r="AB4" s="37">
+      <c r="AB4" s="34">
         <v>321</v>
       </c>
-      <c r="AC4" s="37">
+      <c r="AC4" s="34">
         <v>2917</v>
       </c>
     </row>
@@ -4518,28 +4507,28 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="V5" s="37">
+      <c r="V5" s="34">
         <v>692</v>
       </c>
-      <c r="W5" s="37">
+      <c r="W5" s="34">
         <v>1453</v>
       </c>
-      <c r="X5" s="37">
+      <c r="X5" s="34">
         <v>8931</v>
       </c>
-      <c r="Y5" s="37">
+      <c r="Y5" s="34">
         <v>10736</v>
       </c>
-      <c r="Z5" s="37">
+      <c r="Z5" s="34">
         <v>1256</v>
       </c>
-      <c r="AA5" s="37">
+      <c r="AA5" s="34">
         <v>3243</v>
       </c>
-      <c r="AB5" s="37">
+      <c r="AB5" s="34">
         <v>321</v>
       </c>
-      <c r="AC5" s="37">
+      <c r="AC5" s="34">
         <v>2922</v>
       </c>
     </row>
@@ -4614,28 +4603,28 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="V6" s="37">
+      <c r="V6" s="34">
         <v>728</v>
       </c>
-      <c r="W6" s="37">
+      <c r="W6" s="34">
         <v>1501</v>
       </c>
-      <c r="X6" s="37">
+      <c r="X6" s="34">
         <v>8935</v>
       </c>
-      <c r="Y6" s="37">
+      <c r="Y6" s="34">
         <v>10738</v>
       </c>
-      <c r="Z6" s="37">
+      <c r="Z6" s="34">
         <v>1256</v>
       </c>
-      <c r="AA6" s="37">
+      <c r="AA6" s="34">
         <v>3251</v>
       </c>
-      <c r="AB6" s="37">
+      <c r="AB6" s="34">
         <v>322</v>
       </c>
-      <c r="AC6" s="37">
+      <c r="AC6" s="34">
         <v>2928</v>
       </c>
     </row>
@@ -4710,28 +4699,28 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="V7" s="37">
+      <c r="V7" s="34">
         <v>728</v>
       </c>
-      <c r="W7" s="37">
+      <c r="W7" s="34">
         <v>1501</v>
       </c>
-      <c r="X7" s="37">
+      <c r="X7" s="34">
         <v>8935</v>
       </c>
-      <c r="Y7" s="37">
+      <c r="Y7" s="34">
         <v>10738</v>
       </c>
-      <c r="Z7" s="37">
+      <c r="Z7" s="34">
         <v>1256</v>
       </c>
-      <c r="AA7" s="37">
+      <c r="AA7" s="34">
         <v>3251</v>
       </c>
-      <c r="AB7" s="37">
+      <c r="AB7" s="34">
         <v>322</v>
       </c>
-      <c r="AC7" s="37">
+      <c r="AC7" s="34">
         <v>2928</v>
       </c>
     </row>
@@ -4806,28 +4795,28 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="V8" s="37">
+      <c r="V8" s="34">
         <v>882</v>
       </c>
-      <c r="W8" s="37">
+      <c r="W8" s="34">
         <v>1705</v>
       </c>
-      <c r="X8" s="37">
+      <c r="X8" s="34">
         <v>8946</v>
       </c>
-      <c r="Y8" s="37">
+      <c r="Y8" s="34">
         <v>10739</v>
       </c>
-      <c r="Z8" s="37">
+      <c r="Z8" s="34">
         <v>1256</v>
       </c>
-      <c r="AA8" s="37">
+      <c r="AA8" s="34">
         <v>3263</v>
       </c>
-      <c r="AB8" s="37">
+      <c r="AB8" s="34">
         <v>322</v>
       </c>
-      <c r="AC8" s="37">
+      <c r="AC8" s="34">
         <v>2928</v>
       </c>
     </row>
@@ -4902,28 +4891,28 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="V9" s="37">
+      <c r="V9" s="34">
         <v>882</v>
       </c>
-      <c r="W9" s="37">
+      <c r="W9" s="34">
         <v>1705</v>
       </c>
-      <c r="X9" s="37">
+      <c r="X9" s="34">
         <v>8946</v>
       </c>
-      <c r="Y9" s="37">
+      <c r="Y9" s="34">
         <v>10739</v>
       </c>
-      <c r="Z9" s="37">
+      <c r="Z9" s="34">
         <v>1256</v>
       </c>
-      <c r="AA9" s="37">
+      <c r="AA9" s="34">
         <v>3263</v>
       </c>
-      <c r="AB9" s="37">
+      <c r="AB9" s="34">
         <v>322</v>
       </c>
-      <c r="AC9" s="37">
+      <c r="AC9" s="34">
         <v>2928</v>
       </c>
     </row>
@@ -4998,28 +4987,28 @@
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="V10" s="37">
+      <c r="V10" s="34">
         <v>1058</v>
       </c>
-      <c r="W10" s="37">
+      <c r="W10" s="34">
         <v>1995</v>
       </c>
-      <c r="X10" s="37">
+      <c r="X10" s="34">
         <v>8952</v>
       </c>
-      <c r="Y10" s="37">
+      <c r="Y10" s="34">
         <v>10741</v>
       </c>
-      <c r="Z10" s="37">
+      <c r="Z10" s="34">
         <v>1257</v>
       </c>
-      <c r="AA10" s="37">
+      <c r="AA10" s="34">
         <v>3274</v>
       </c>
-      <c r="AB10" s="37">
+      <c r="AB10" s="34">
         <v>325</v>
       </c>
-      <c r="AC10" s="37">
+      <c r="AC10" s="34">
         <v>2948</v>
       </c>
     </row>
@@ -5094,28 +5083,28 @@
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="V11" s="37">
+      <c r="V11" s="34">
         <v>1080</v>
       </c>
-      <c r="W11" s="37">
+      <c r="W11" s="34">
         <v>2125</v>
       </c>
-      <c r="X11" s="37">
+      <c r="X11" s="34">
         <v>8952</v>
       </c>
-      <c r="Y11" s="37">
+      <c r="Y11" s="34">
         <v>10741</v>
       </c>
-      <c r="Z11" s="37">
+      <c r="Z11" s="34">
         <v>1257</v>
       </c>
-      <c r="AA11" s="37">
+      <c r="AA11" s="34">
         <v>3280</v>
       </c>
-      <c r="AB11" s="37">
+      <c r="AB11" s="34">
         <v>325</v>
       </c>
-      <c r="AC11" s="37">
+      <c r="AC11" s="34">
         <v>2955</v>
       </c>
     </row>
@@ -5190,28 +5179,28 @@
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="V12" s="37">
+      <c r="V12" s="34">
         <v>1135</v>
       </c>
-      <c r="W12" s="37">
+      <c r="W12" s="34">
         <v>2301</v>
       </c>
-      <c r="X12" s="37">
+      <c r="X12" s="34">
         <v>8960</v>
       </c>
-      <c r="Y12" s="37">
+      <c r="Y12" s="34">
         <v>10742</v>
       </c>
-      <c r="Z12" s="37">
+      <c r="Z12" s="34">
         <v>1257</v>
       </c>
-      <c r="AA12" s="37">
+      <c r="AA12" s="34">
         <v>3287</v>
       </c>
-      <c r="AB12" s="37">
+      <c r="AB12" s="34">
         <v>325</v>
       </c>
-      <c r="AC12" s="37">
+      <c r="AC12" s="34">
         <v>2962</v>
       </c>
     </row>
@@ -5286,28 +5275,28 @@
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="V13" s="37">
+      <c r="V13" s="34">
         <v>1230</v>
       </c>
-      <c r="W13" s="37">
+      <c r="W13" s="34">
         <v>2418</v>
       </c>
-      <c r="X13" s="37">
+      <c r="X13" s="34">
         <v>8964</v>
       </c>
-      <c r="Y13" s="37">
+      <c r="Y13" s="34">
         <v>10743</v>
       </c>
-      <c r="Z13" s="37">
+      <c r="Z13" s="34">
         <v>1257</v>
       </c>
-      <c r="AA13" s="37">
+      <c r="AA13" s="34">
         <v>3287</v>
       </c>
-      <c r="AB13" s="37">
+      <c r="AB13" s="34">
         <v>325</v>
       </c>
-      <c r="AC13" s="37">
+      <c r="AC13" s="34">
         <v>2962</v>
       </c>
     </row>
@@ -5382,28 +5371,28 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="V14" s="37">
+      <c r="V14" s="34">
         <v>1347</v>
       </c>
-      <c r="W14" s="37">
+      <c r="W14" s="34">
         <v>2611</v>
       </c>
-      <c r="X14" s="37">
+      <c r="X14" s="34">
         <v>8967</v>
       </c>
-      <c r="Y14" s="37">
+      <c r="Y14" s="34">
         <v>10744</v>
       </c>
-      <c r="Z14" s="37">
+      <c r="Z14" s="34">
         <v>1257</v>
       </c>
-      <c r="AA14" s="37">
+      <c r="AA14" s="34">
         <v>3300</v>
       </c>
-      <c r="AB14" s="37">
+      <c r="AB14" s="34">
         <v>327</v>
       </c>
-      <c r="AC14" s="37">
+      <c r="AC14" s="34">
         <v>2973</v>
       </c>
     </row>
@@ -5477,28 +5466,28 @@
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="V15" s="37">
+      <c r="V15" s="34">
         <v>1470</v>
       </c>
-      <c r="W15" s="37">
+      <c r="W15" s="34">
         <v>2681</v>
       </c>
-      <c r="X15" s="37">
+      <c r="X15" s="34">
         <v>8971</v>
       </c>
-      <c r="Y15" s="37">
+      <c r="Y15" s="34">
         <v>10744</v>
       </c>
-      <c r="Z15" s="37">
+      <c r="Z15" s="34">
         <v>1258</v>
       </c>
-      <c r="AA15" s="37">
+      <c r="AA15" s="34">
         <v>3306</v>
       </c>
-      <c r="AB15" s="37">
+      <c r="AB15" s="34">
         <v>328</v>
       </c>
-      <c r="AC15" s="37">
+      <c r="AC15" s="34">
         <v>2977</v>
       </c>
     </row>
@@ -5573,28 +5562,28 @@
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="V16" s="37">
+      <c r="V16" s="34">
         <v>1470</v>
       </c>
-      <c r="W16" s="37">
+      <c r="W16" s="34">
         <v>2681</v>
       </c>
-      <c r="X16" s="37">
+      <c r="X16" s="34">
         <v>8971</v>
       </c>
-      <c r="Y16" s="37">
+      <c r="Y16" s="34">
         <v>10744</v>
       </c>
-      <c r="Z16" s="37">
+      <c r="Z16" s="34">
         <v>1258</v>
       </c>
-      <c r="AA16" s="37">
+      <c r="AA16" s="34">
         <v>3306</v>
       </c>
-      <c r="AB16" s="37">
+      <c r="AB16" s="34">
         <v>328</v>
       </c>
-      <c r="AC16" s="37">
+      <c r="AC16" s="34">
         <v>2977</v>
       </c>
     </row>
@@ -5669,28 +5658,28 @@
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="V17" s="37">
+      <c r="V17" s="34">
         <v>1674</v>
       </c>
-      <c r="W17" s="37">
+      <c r="W17" s="34">
         <v>2914</v>
       </c>
-      <c r="X17" s="37">
+      <c r="X17" s="34">
         <v>8979</v>
       </c>
-      <c r="Y17" s="37">
+      <c r="Y17" s="34">
         <v>10745</v>
       </c>
-      <c r="Z17" s="37">
+      <c r="Z17" s="34">
         <v>1258</v>
       </c>
-      <c r="AA17" s="37">
+      <c r="AA17" s="34">
         <v>3317</v>
       </c>
-      <c r="AB17" s="37">
+      <c r="AB17" s="34">
         <v>329</v>
       </c>
-      <c r="AC17" s="37">
+      <c r="AC17" s="34">
         <v>2988</v>
       </c>
     </row>
@@ -5765,28 +5754,28 @@
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="V18" s="37">
+      <c r="V18" s="34">
         <v>1690</v>
       </c>
-      <c r="W18" s="37">
+      <c r="W18" s="34">
         <v>2986</v>
       </c>
-      <c r="X18" s="37">
+      <c r="X18" s="34">
         <v>8979</v>
       </c>
-      <c r="Y18" s="37">
+      <c r="Y18" s="34">
         <v>10747</v>
       </c>
-      <c r="Z18" s="37">
+      <c r="Z18" s="34">
         <v>1258</v>
       </c>
-      <c r="AA18" s="37">
+      <c r="AA18" s="34">
         <v>3324</v>
       </c>
-      <c r="AB18" s="37">
+      <c r="AB18" s="34">
         <v>329</v>
       </c>
-      <c r="AC18" s="37">
+      <c r="AC18" s="34">
         <v>2994</v>
       </c>
     </row>
@@ -5861,28 +5850,28 @@
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="V19" s="37">
+      <c r="V19" s="34">
         <v>1733</v>
       </c>
-      <c r="W19" s="37">
+      <c r="W19" s="34">
         <v>3061</v>
       </c>
-      <c r="X19" s="37">
+      <c r="X19" s="34">
         <v>8985</v>
       </c>
-      <c r="Y19" s="37">
+      <c r="Y19" s="34">
         <v>10747</v>
       </c>
-      <c r="Z19" s="37">
+      <c r="Z19" s="34">
         <v>1258</v>
       </c>
-      <c r="AA19" s="37">
+      <c r="AA19" s="34">
         <v>3330</v>
       </c>
-      <c r="AB19" s="37">
+      <c r="AB19" s="34">
         <v>329</v>
       </c>
-      <c r="AC19" s="37">
+      <c r="AC19" s="34">
         <v>3000</v>
       </c>
     </row>
@@ -5957,28 +5946,28 @@
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="V20" s="37">
+      <c r="V20" s="34">
         <v>1859</v>
       </c>
-      <c r="W20" s="37">
+      <c r="W20" s="34">
         <v>3301</v>
       </c>
-      <c r="X20" s="37">
+      <c r="X20" s="34">
         <v>8988</v>
       </c>
-      <c r="Y20" s="37">
+      <c r="Y20" s="34">
         <v>10748</v>
       </c>
-      <c r="Z20" s="37">
+      <c r="Z20" s="34">
         <v>1258</v>
       </c>
-      <c r="AA20" s="37">
+      <c r="AA20" s="34">
         <v>3336</v>
       </c>
-      <c r="AB20" s="37">
+      <c r="AB20" s="34">
         <v>330</v>
       </c>
-      <c r="AC20" s="37">
+      <c r="AC20" s="34">
         <v>3005</v>
       </c>
     </row>
@@ -6053,28 +6042,28 @@
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="V21" s="37">
+      <c r="V21" s="34">
         <v>1951</v>
       </c>
-      <c r="W21" s="37">
+      <c r="W21" s="34">
         <v>3368</v>
       </c>
-      <c r="X21" s="37">
+      <c r="X21" s="34">
         <v>8992</v>
       </c>
-      <c r="Y21" s="37">
+      <c r="Y21" s="34">
         <v>10749</v>
       </c>
-      <c r="Z21" s="37">
+      <c r="Z21" s="34">
         <v>1258</v>
       </c>
-      <c r="AA21" s="37">
+      <c r="AA21" s="34">
         <v>3342</v>
       </c>
-      <c r="AB21" s="37">
+      <c r="AB21" s="34">
         <v>331</v>
       </c>
-      <c r="AC21" s="37">
+      <c r="AC21" s="34">
         <v>3010</v>
       </c>
     </row>
@@ -6149,28 +6138,28 @@
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="V22" s="37">
+      <c r="V22" s="34">
         <v>2048</v>
       </c>
-      <c r="W22" s="37">
+      <c r="W22" s="34">
         <v>3506</v>
       </c>
-      <c r="X22" s="37">
+      <c r="X22" s="34">
         <v>8995</v>
       </c>
-      <c r="Y22" s="37">
+      <c r="Y22" s="34">
         <v>10749</v>
       </c>
-      <c r="Z22" s="37">
+      <c r="Z22" s="34">
         <v>1258</v>
       </c>
-      <c r="AA22" s="37">
+      <c r="AA22" s="34">
         <v>3347</v>
       </c>
-      <c r="AB22" s="37">
+      <c r="AB22" s="34">
         <v>332</v>
       </c>
-      <c r="AC22" s="37">
+      <c r="AC22" s="34">
         <v>3015</v>
       </c>
     </row>
@@ -6245,28 +6234,28 @@
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="V23" s="37">
+      <c r="V23" s="34">
         <v>2170</v>
       </c>
-      <c r="W23" s="37">
+      <c r="W23" s="34">
         <v>3628</v>
       </c>
-      <c r="X23" s="37">
+      <c r="X23" s="34">
         <v>8985</v>
       </c>
-      <c r="Y23" s="37">
+      <c r="Y23" s="34">
         <v>10749</v>
       </c>
-      <c r="Z23" s="37">
+      <c r="Z23" s="34">
         <v>1258</v>
       </c>
-      <c r="AA23" s="37">
+      <c r="AA23" s="34">
         <v>3350</v>
       </c>
-      <c r="AB23" s="37">
+      <c r="AB23" s="34">
         <v>333</v>
       </c>
-      <c r="AC23" s="37">
+      <c r="AC23" s="34">
         <v>3017</v>
       </c>
     </row>
@@ -6341,28 +6330,28 @@
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="V24" s="37">
+      <c r="V24" s="34">
         <v>2199</v>
       </c>
-      <c r="W24" s="37">
+      <c r="W24" s="34">
         <v>3713</v>
       </c>
-      <c r="X24" s="37">
+      <c r="X24" s="34">
         <v>8999</v>
       </c>
-      <c r="Y24" s="37">
+      <c r="Y24" s="34">
         <v>10752</v>
       </c>
-      <c r="Z24" s="37">
+      <c r="Z24" s="34">
         <v>1259</v>
       </c>
-      <c r="AA24" s="37">
+      <c r="AA24" s="34">
         <v>3356</v>
       </c>
-      <c r="AB24" s="37">
+      <c r="AB24" s="34">
         <v>334</v>
       </c>
-      <c r="AC24" s="37">
+      <c r="AC24" s="34">
         <v>3021</v>
       </c>
     </row>
@@ -6437,28 +6426,28 @@
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="V25" s="37">
+      <c r="V25" s="34">
         <v>2248</v>
       </c>
-      <c r="W25" s="37">
+      <c r="W25" s="34">
         <v>3790</v>
       </c>
-      <c r="X25" s="37">
+      <c r="X25" s="34">
         <v>9004</v>
       </c>
-      <c r="Y25" s="37">
+      <c r="Y25" s="34">
         <v>10752</v>
       </c>
-      <c r="Z25" s="37">
+      <c r="Z25" s="34">
         <v>1259</v>
       </c>
-      <c r="AA25" s="37">
+      <c r="AA25" s="34">
         <v>3364</v>
       </c>
-      <c r="AB25" s="37">
+      <c r="AB25" s="34">
         <v>334</v>
       </c>
-      <c r="AC25" s="37">
+      <c r="AC25" s="34">
         <v>3023</v>
       </c>
     </row>
@@ -6533,28 +6522,28 @@
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="V26" s="37">
+      <c r="V26" s="34">
         <v>2286</v>
       </c>
-      <c r="W26" s="37">
+      <c r="W26" s="34">
         <v>3790</v>
       </c>
-      <c r="X26" s="37">
+      <c r="X26" s="34">
         <v>9009</v>
       </c>
-      <c r="Y26" s="37">
+      <c r="Y26" s="34">
         <v>10753</v>
       </c>
-      <c r="Z26" s="37">
+      <c r="Z26" s="34">
         <v>1259</v>
       </c>
-      <c r="AA26" s="37">
+      <c r="AA26" s="34">
         <v>3369</v>
       </c>
-      <c r="AB26" s="37">
+      <c r="AB26" s="34">
         <v>334</v>
       </c>
-      <c r="AC26" s="37">
+      <c r="AC26" s="34">
         <v>3035</v>
       </c>
     </row>
@@ -6629,28 +6618,28 @@
         <f t="shared" si="8"/>
         <v>25</v>
       </c>
-      <c r="V27" s="37">
+      <c r="V27" s="34">
         <v>2384</v>
       </c>
-      <c r="W27" s="37">
+      <c r="W27" s="34">
         <v>3934</v>
       </c>
-      <c r="X27" s="37">
+      <c r="X27" s="34">
         <v>9011</v>
       </c>
-      <c r="Y27" s="37">
+      <c r="Y27" s="34">
         <v>10753</v>
       </c>
-      <c r="Z27" s="37">
+      <c r="Z27" s="34">
         <v>1259</v>
       </c>
-      <c r="AA27" s="37">
+      <c r="AA27" s="34">
         <v>3371</v>
       </c>
-      <c r="AB27" s="37">
+      <c r="AB27" s="34">
         <v>334</v>
       </c>
-      <c r="AC27" s="37">
+      <c r="AC27" s="34">
         <v>3036</v>
       </c>
     </row>
@@ -6725,28 +6714,28 @@
         <f t="shared" si="8"/>
         <v>26</v>
       </c>
-      <c r="V28" s="37">
+      <c r="V28" s="34">
         <v>2452</v>
       </c>
-      <c r="W28" s="37">
+      <c r="W28" s="34">
         <v>4054</v>
       </c>
-      <c r="X28" s="37">
+      <c r="X28" s="34">
         <v>9015</v>
       </c>
-      <c r="Y28" s="37">
+      <c r="Y28" s="34">
         <v>10755</v>
       </c>
-      <c r="Z28" s="37">
+      <c r="Z28" s="34">
         <v>1259</v>
       </c>
-      <c r="AA28" s="37">
+      <c r="AA28" s="34">
         <v>3379</v>
       </c>
-      <c r="AB28" s="37">
+      <c r="AB28" s="34">
         <v>336</v>
       </c>
-      <c r="AC28" s="37">
+      <c r="AC28" s="34">
         <v>3043</v>
       </c>
     </row>
@@ -6821,28 +6810,28 @@
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
-      <c r="V29" s="37">
+      <c r="V29" s="34">
         <v>2601</v>
       </c>
-      <c r="W29" s="37">
+      <c r="W29" s="34">
         <v>4174</v>
       </c>
-      <c r="X29" s="37">
+      <c r="X29" s="34">
         <v>9017</v>
       </c>
-      <c r="Y29" s="37">
+      <c r="Y29" s="34">
         <v>10755</v>
       </c>
-      <c r="Z29" s="37">
+      <c r="Z29" s="34">
         <v>1259</v>
       </c>
-      <c r="AA29" s="37">
+      <c r="AA29" s="34">
         <v>3384</v>
       </c>
-      <c r="AB29" s="37">
+      <c r="AB29" s="34">
         <v>336</v>
       </c>
-      <c r="AC29" s="37">
+      <c r="AC29" s="34">
         <v>3048</v>
       </c>
     </row>
@@ -6917,28 +6906,28 @@
         <f t="shared" si="8"/>
         <v>28</v>
       </c>
-      <c r="V30" s="37">
+      <c r="V30" s="34">
         <v>2674</v>
       </c>
-      <c r="W30" s="37">
+      <c r="W30" s="34">
         <v>4247</v>
       </c>
-      <c r="X30" s="37">
+      <c r="X30" s="34">
         <v>9020</v>
       </c>
-      <c r="Y30" s="37">
+      <c r="Y30" s="34">
         <v>10756</v>
       </c>
-      <c r="Z30" s="37">
+      <c r="Z30" s="34">
         <v>1260</v>
       </c>
-      <c r="AA30" s="37">
+      <c r="AA30" s="34">
         <v>3390</v>
       </c>
-      <c r="AB30" s="37">
+      <c r="AB30" s="34">
         <v>337</v>
       </c>
-      <c r="AC30" s="37">
+      <c r="AC30" s="34">
         <v>3052</v>
       </c>
     </row>
@@ -7013,28 +7002,28 @@
         <f t="shared" si="8"/>
         <v>29</v>
       </c>
-      <c r="V31" s="37">
+      <c r="V31" s="34">
         <v>2742</v>
       </c>
-      <c r="W31" s="37">
+      <c r="W31" s="34">
         <v>4306</v>
       </c>
-      <c r="X31" s="37">
+      <c r="X31" s="34">
         <v>9020</v>
       </c>
-      <c r="Y31" s="37">
+      <c r="Y31" s="34">
         <v>10757</v>
       </c>
-      <c r="Z31" s="37">
+      <c r="Z31" s="34">
         <v>1260</v>
       </c>
-      <c r="AA31" s="37">
+      <c r="AA31" s="34">
         <v>3395</v>
       </c>
-      <c r="AB31" s="37">
+      <c r="AB31" s="34">
         <v>338</v>
       </c>
-      <c r="AC31" s="37">
+      <c r="AC31" s="34">
         <v>3057</v>
       </c>
     </row>
@@ -7109,28 +7098,28 @@
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-      <c r="V32" s="37">
+      <c r="V32" s="34">
         <v>2801</v>
       </c>
-      <c r="W32" s="37">
+      <c r="W32" s="34">
         <v>4403</v>
       </c>
-      <c r="X32" s="37">
+      <c r="X32" s="34">
         <v>9034</v>
       </c>
-      <c r="Y32" s="37">
+      <c r="Y32" s="34">
         <v>10757</v>
       </c>
-      <c r="Z32" s="37">
+      <c r="Z32" s="34">
         <v>1260</v>
       </c>
-      <c r="AA32" s="37">
+      <c r="AA32" s="34">
         <v>3402</v>
       </c>
-      <c r="AB32" s="37">
+      <c r="AB32" s="34">
         <v>338</v>
       </c>
-      <c r="AC32" s="37">
+      <c r="AC32" s="34">
         <v>3063</v>
       </c>
     </row>
@@ -7157,42 +7146,42 @@
         <f t="shared" si="8"/>
         <v>31</v>
       </c>
-      <c r="V33" s="37">
+      <c r="V33" s="34">
         <v>2812</v>
       </c>
-      <c r="W33" s="37">
+      <c r="W33" s="34">
         <v>4489</v>
       </c>
-      <c r="X33" s="37">
+      <c r="X33" s="34">
         <v>9036</v>
       </c>
-      <c r="Y33" s="37">
+      <c r="Y33" s="34">
         <v>10758</v>
       </c>
-      <c r="Z33" s="37">
+      <c r="Z33" s="34">
         <v>1260</v>
       </c>
-      <c r="AA33" s="37">
+      <c r="AA33" s="34">
         <v>3408</v>
       </c>
-      <c r="AB33" s="37">
+      <c r="AB33" s="34">
         <v>338</v>
       </c>
-      <c r="AC33" s="37">
+      <c r="AC33" s="34">
         <v>3069</v>
       </c>
     </row>
     <row r="34" spans="1:29" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -7569,15 +7558,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="34"/>
-      <c r="B71" s="34"/>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-      <c r="H71" s="34"/>
-      <c r="I71" s="34"/>
+      <c r="A71" s="38"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -7602,15 +7591,15 @@
       <c r="I73" s="21"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="35"/>
-      <c r="B76" s="35"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="A76" s="39"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -7646,15 +7635,15 @@
       <c r="I79" s="23"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="36"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="36"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
+      <c r="A80" s="40"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40"/>
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -7690,15 +7679,15 @@
       <c r="B86" s="21"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="35"/>
-      <c r="B88" s="35"/>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
+      <c r="A88" s="39"/>
+      <c r="B88" s="39"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="39"/>
+      <c r="G88" s="39"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="39"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -7801,15 +7790,15 @@
       <c r="B99" s="24"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="34"/>
-      <c r="B101" s="34"/>
-      <c r="C101" s="34"/>
-      <c r="D101" s="34"/>
-      <c r="E101" s="34"/>
-      <c r="F101" s="34"/>
-      <c r="G101" s="34"/>
-      <c r="H101" s="34"/>
-      <c r="I101" s="34"/>
+      <c r="A101" s="38"/>
+      <c r="B101" s="38"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="38"/>
+      <c r="G101" s="38"/>
+      <c r="H101" s="38"/>
+      <c r="I101" s="38"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -10286,14 +10275,14 @@
     </row>
     <row r="32" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
@@ -10670,15 +10659,15 @@
       <c r="I66" s="1"/>
     </row>
     <row r="67" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="34"/>
-      <c r="B67" s="34"/>
-      <c r="C67" s="34"/>
-      <c r="D67" s="34"/>
-      <c r="E67" s="34"/>
-      <c r="F67" s="34"/>
-      <c r="G67" s="34"/>
-      <c r="H67" s="34"/>
-      <c r="I67" s="34"/>
+      <c r="A67" s="38"/>
+      <c r="B67" s="38"/>
+      <c r="C67" s="38"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="38"/>
+      <c r="F67" s="38"/>
+      <c r="G67" s="38"/>
+      <c r="H67" s="38"/>
+      <c r="I67" s="38"/>
     </row>
     <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
@@ -10703,15 +10692,15 @@
       <c r="I69" s="21"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="35"/>
-      <c r="B72" s="35"/>
-      <c r="C72" s="35"/>
-      <c r="D72" s="35"/>
-      <c r="E72" s="35"/>
-      <c r="F72" s="35"/>
-      <c r="G72" s="35"/>
-      <c r="H72" s="35"/>
-      <c r="I72" s="35"/>
+      <c r="A72" s="39"/>
+      <c r="B72" s="39"/>
+      <c r="C72" s="39"/>
+      <c r="D72" s="39"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="39"/>
+      <c r="G72" s="39"/>
+      <c r="H72" s="39"/>
+      <c r="I72" s="39"/>
     </row>
     <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
@@ -10747,15 +10736,15 @@
       <c r="I75" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="36"/>
-      <c r="B76" s="36"/>
-      <c r="C76" s="36"/>
-      <c r="D76" s="36"/>
-      <c r="E76" s="36"/>
-      <c r="F76" s="36"/>
-      <c r="G76" s="36"/>
-      <c r="H76" s="36"/>
-      <c r="I76" s="36"/>
+      <c r="A76" s="40"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="40"/>
+      <c r="H76" s="40"/>
+      <c r="I76" s="40"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -10791,15 +10780,15 @@
       <c r="B82" s="21"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="35"/>
-      <c r="B84" s="35"/>
-      <c r="C84" s="35"/>
-      <c r="D84" s="35"/>
-      <c r="E84" s="35"/>
-      <c r="F84" s="35"/>
-      <c r="G84" s="35"/>
-      <c r="H84" s="35"/>
-      <c r="I84" s="35"/>
+      <c r="A84" s="39"/>
+      <c r="B84" s="39"/>
+      <c r="C84" s="39"/>
+      <c r="D84" s="39"/>
+      <c r="E84" s="39"/>
+      <c r="F84" s="39"/>
+      <c r="G84" s="39"/>
+      <c r="H84" s="39"/>
+      <c r="I84" s="39"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
@@ -10902,15 +10891,15 @@
       <c r="B95" s="24"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="34"/>
-      <c r="B97" s="34"/>
-      <c r="C97" s="34"/>
-      <c r="D97" s="34"/>
-      <c r="E97" s="34"/>
-      <c r="F97" s="34"/>
-      <c r="G97" s="34"/>
-      <c r="H97" s="34"/>
-      <c r="I97" s="34"/>
+      <c r="A97" s="38"/>
+      <c r="B97" s="38"/>
+      <c r="C97" s="38"/>
+      <c r="D97" s="38"/>
+      <c r="E97" s="38"/>
+      <c r="F97" s="38"/>
+      <c r="G97" s="38"/>
+      <c r="H97" s="38"/>
+      <c r="I97" s="38"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
@@ -13580,14 +13569,14 @@
     <row r="34" spans="1:20" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -13964,15 +13953,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="34"/>
-      <c r="B71" s="34"/>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-      <c r="H71" s="34"/>
-      <c r="I71" s="34"/>
+      <c r="A71" s="38"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -13997,15 +13986,15 @@
       <c r="I73" s="21"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="35"/>
-      <c r="B76" s="35"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="A76" s="39"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -14041,15 +14030,15 @@
       <c r="I79" s="23"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="36"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="36"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
+      <c r="A80" s="40"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40"/>
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -14085,15 +14074,15 @@
       <c r="B86" s="21"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="35"/>
-      <c r="B88" s="35"/>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
+      <c r="A88" s="39"/>
+      <c r="B88" s="39"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="39"/>
+      <c r="G88" s="39"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="39"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -14196,15 +14185,15 @@
       <c r="B99" s="24"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="34"/>
-      <c r="B101" s="34"/>
-      <c r="C101" s="34"/>
-      <c r="D101" s="34"/>
-      <c r="E101" s="34"/>
-      <c r="F101" s="34"/>
-      <c r="G101" s="34"/>
-      <c r="H101" s="34"/>
-      <c r="I101" s="34"/>
+      <c r="A101" s="38"/>
+      <c r="B101" s="38"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="38"/>
+      <c r="G101" s="38"/>
+      <c r="H101" s="38"/>
+      <c r="I101" s="38"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -16881,14 +16870,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -17266,15 +17255,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="34"/>
-      <c r="B70" s="34"/>
-      <c r="C70" s="34"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="34"/>
-      <c r="G70" s="34"/>
-      <c r="H70" s="34"/>
-      <c r="I70" s="34"/>
+      <c r="A70" s="38"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -17299,15 +17288,15 @@
       <c r="I72" s="21"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="35"/>
-      <c r="B75" s="35"/>
-      <c r="C75" s="35"/>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
+      <c r="A75" s="39"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -17343,15 +17332,15 @@
       <c r="I78" s="23"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="36"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-      <c r="G79" s="36"/>
-      <c r="H79" s="36"/>
-      <c r="I79" s="36"/>
+      <c r="A79" s="40"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="40"/>
+      <c r="I79" s="40"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -17387,15 +17376,15 @@
       <c r="B85" s="21"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="35"/>
-      <c r="B87" s="35"/>
-      <c r="C87" s="35"/>
-      <c r="D87" s="35"/>
-      <c r="E87" s="35"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="35"/>
+      <c r="A87" s="39"/>
+      <c r="B87" s="39"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="39"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="39"/>
+      <c r="G87" s="39"/>
+      <c r="H87" s="39"/>
+      <c r="I87" s="39"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -17498,15 +17487,15 @@
       <c r="B98" s="24"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="34"/>
-      <c r="B100" s="34"/>
-      <c r="C100" s="34"/>
-      <c r="D100" s="34"/>
-      <c r="E100" s="34"/>
-      <c r="F100" s="34"/>
-      <c r="G100" s="34"/>
-      <c r="H100" s="34"/>
-      <c r="I100" s="34"/>
+      <c r="A100" s="38"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="38"/>
+      <c r="G100" s="38"/>
+      <c r="H100" s="38"/>
+      <c r="I100" s="38"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -20205,14 +20194,14 @@
     <row r="34" spans="1:29" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -20590,15 +20579,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="34"/>
-      <c r="B71" s="34"/>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-      <c r="H71" s="34"/>
-      <c r="I71" s="34"/>
+      <c r="A71" s="38"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -20623,15 +20612,15 @@
       <c r="I73" s="21"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="35"/>
-      <c r="B76" s="35"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="A76" s="39"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -20667,15 +20656,15 @@
       <c r="I79" s="23"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="36"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="36"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
+      <c r="A80" s="40"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40"/>
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -20711,15 +20700,15 @@
       <c r="B86" s="21"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="35"/>
-      <c r="B88" s="35"/>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
+      <c r="A88" s="39"/>
+      <c r="B88" s="39"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="39"/>
+      <c r="G88" s="39"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="39"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -20822,15 +20811,15 @@
       <c r="B99" s="24"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="34"/>
-      <c r="B101" s="34"/>
-      <c r="C101" s="34"/>
-      <c r="D101" s="34"/>
-      <c r="E101" s="34"/>
-      <c r="F101" s="34"/>
-      <c r="G101" s="34"/>
-      <c r="H101" s="34"/>
-      <c r="I101" s="34"/>
+      <c r="A101" s="38"/>
+      <c r="B101" s="38"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="38"/>
+      <c r="G101" s="38"/>
+      <c r="H101" s="38"/>
+      <c r="I101" s="38"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -23461,14 +23450,14 @@
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
@@ -23846,15 +23835,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="34"/>
-      <c r="B69" s="34"/>
-      <c r="C69" s="34"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="34"/>
-      <c r="G69" s="34"/>
-      <c r="H69" s="34"/>
-      <c r="I69" s="34"/>
+      <c r="A69" s="38"/>
+      <c r="B69" s="38"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="38"/>
+      <c r="G69" s="38"/>
+      <c r="H69" s="38"/>
+      <c r="I69" s="38"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -23879,15 +23868,15 @@
       <c r="I71" s="21"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="35"/>
-      <c r="B74" s="35"/>
-      <c r="C74" s="35"/>
-      <c r="D74" s="35"/>
-      <c r="E74" s="35"/>
-      <c r="F74" s="35"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="35"/>
-      <c r="I74" s="35"/>
+      <c r="A74" s="39"/>
+      <c r="B74" s="39"/>
+      <c r="C74" s="39"/>
+      <c r="D74" s="39"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="39"/>
+      <c r="G74" s="39"/>
+      <c r="H74" s="39"/>
+      <c r="I74" s="39"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -23923,15 +23912,15 @@
       <c r="I77" s="23"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="36"/>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-      <c r="G78" s="36"/>
-      <c r="H78" s="36"/>
-      <c r="I78" s="36"/>
+      <c r="A78" s="40"/>
+      <c r="B78" s="40"/>
+      <c r="C78" s="40"/>
+      <c r="D78" s="40"/>
+      <c r="E78" s="40"/>
+      <c r="F78" s="40"/>
+      <c r="G78" s="40"/>
+      <c r="H78" s="40"/>
+      <c r="I78" s="40"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -23967,15 +23956,15 @@
       <c r="B84" s="21"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="35"/>
-      <c r="B86" s="35"/>
-      <c r="C86" s="35"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="35"/>
-      <c r="F86" s="35"/>
-      <c r="G86" s="35"/>
-      <c r="H86" s="35"/>
-      <c r="I86" s="35"/>
+      <c r="A86" s="39"/>
+      <c r="B86" s="39"/>
+      <c r="C86" s="39"/>
+      <c r="D86" s="39"/>
+      <c r="E86" s="39"/>
+      <c r="F86" s="39"/>
+      <c r="G86" s="39"/>
+      <c r="H86" s="39"/>
+      <c r="I86" s="39"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -24078,15 +24067,15 @@
       <c r="B97" s="24"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="34"/>
-      <c r="B99" s="34"/>
-      <c r="C99" s="34"/>
-      <c r="D99" s="34"/>
-      <c r="E99" s="34"/>
-      <c r="F99" s="34"/>
-      <c r="G99" s="34"/>
-      <c r="H99" s="34"/>
-      <c r="I99" s="34"/>
+      <c r="A99" s="38"/>
+      <c r="B99" s="38"/>
+      <c r="C99" s="38"/>
+      <c r="D99" s="38"/>
+      <c r="E99" s="38"/>
+      <c r="F99" s="38"/>
+      <c r="G99" s="38"/>
+      <c r="H99" s="38"/>
+      <c r="I99" s="38"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -26784,14 +26773,14 @@
     </row>
     <row r="35" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
     </row>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -27169,15 +27158,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="34"/>
-      <c r="B70" s="34"/>
-      <c r="C70" s="34"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="34"/>
-      <c r="G70" s="34"/>
-      <c r="H70" s="34"/>
-      <c r="I70" s="34"/>
+      <c r="A70" s="38"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -27202,15 +27191,15 @@
       <c r="I72" s="21"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="35"/>
-      <c r="B75" s="35"/>
-      <c r="C75" s="35"/>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
+      <c r="A75" s="39"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -27246,15 +27235,15 @@
       <c r="I78" s="23"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="36"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-      <c r="G79" s="36"/>
-      <c r="H79" s="36"/>
-      <c r="I79" s="36"/>
+      <c r="A79" s="40"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="40"/>
+      <c r="I79" s="40"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -27290,15 +27279,15 @@
       <c r="B85" s="21"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="35"/>
-      <c r="B87" s="35"/>
-      <c r="C87" s="35"/>
-      <c r="D87" s="35"/>
-      <c r="E87" s="35"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="35"/>
+      <c r="A87" s="39"/>
+      <c r="B87" s="39"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="39"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="39"/>
+      <c r="G87" s="39"/>
+      <c r="H87" s="39"/>
+      <c r="I87" s="39"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -27401,15 +27390,15 @@
       <c r="B98" s="24"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="34"/>
-      <c r="B100" s="34"/>
-      <c r="C100" s="34"/>
-      <c r="D100" s="34"/>
-      <c r="E100" s="34"/>
-      <c r="F100" s="34"/>
-      <c r="G100" s="34"/>
-      <c r="H100" s="34"/>
-      <c r="I100" s="34"/>
+      <c r="A100" s="38"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="38"/>
+      <c r="G100" s="38"/>
+      <c r="H100" s="38"/>
+      <c r="I100" s="38"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -30107,14 +30096,14 @@
     </row>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -30492,15 +30481,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="34"/>
-      <c r="B71" s="34"/>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-      <c r="H71" s="34"/>
-      <c r="I71" s="34"/>
+      <c r="A71" s="38"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -30525,15 +30514,15 @@
       <c r="I73" s="21"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="35"/>
-      <c r="B76" s="35"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="A76" s="39"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -30569,15 +30558,15 @@
       <c r="I79" s="23"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="36"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="36"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
+      <c r="A80" s="40"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40"/>
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -30613,15 +30602,15 @@
       <c r="B86" s="21"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="35"/>
-      <c r="B88" s="35"/>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
+      <c r="A88" s="39"/>
+      <c r="B88" s="39"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="39"/>
+      <c r="G88" s="39"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="39"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -30724,15 +30713,15 @@
       <c r="B99" s="24"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="34"/>
-      <c r="B101" s="34"/>
-      <c r="C101" s="34"/>
-      <c r="D101" s="34"/>
-      <c r="E101" s="34"/>
-      <c r="F101" s="34"/>
-      <c r="G101" s="34"/>
-      <c r="H101" s="34"/>
-      <c r="I101" s="34"/>
+      <c r="A101" s="38"/>
+      <c r="B101" s="38"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="38"/>
+      <c r="G101" s="38"/>
+      <c r="H101" s="38"/>
+      <c r="I101" s="38"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -30973,28 +30962,28 @@
       <c r="U2" s="7">
         <v>0</v>
       </c>
-      <c r="V2" s="39">
+      <c r="V2" s="36">
         <v>6375</v>
       </c>
-      <c r="W2" s="39">
+      <c r="W2" s="36">
         <v>8136</v>
       </c>
-      <c r="X2" s="39">
+      <c r="X2" s="36">
         <v>9263</v>
       </c>
-      <c r="Y2" s="39">
+      <c r="Y2" s="36">
         <v>10802</v>
       </c>
-      <c r="Z2" s="39">
+      <c r="Z2" s="36">
         <v>1270</v>
       </c>
-      <c r="AA2" s="39">
+      <c r="AA2" s="36">
         <v>3687</v>
       </c>
-      <c r="AB2" s="39">
+      <c r="AB2" s="36">
         <v>368</v>
       </c>
-      <c r="AC2" s="39">
+      <c r="AC2" s="36">
         <v>3318</v>
       </c>
       <c r="AE2" s="9" t="s">
@@ -31075,28 +31064,28 @@
       <c r="U3" s="5">
         <v>1</v>
       </c>
-      <c r="V3" s="37">
+      <c r="V3" s="34">
         <v>6429</v>
       </c>
-      <c r="W3" s="37">
+      <c r="W3" s="34">
         <v>8198</v>
       </c>
-      <c r="X3" s="37">
+      <c r="X3" s="34">
         <v>9269</v>
       </c>
-      <c r="Y3" s="37">
+      <c r="Y3" s="34">
         <v>10803</v>
       </c>
-      <c r="Z3" s="37">
+      <c r="Z3" s="34">
         <v>1271</v>
       </c>
-      <c r="AA3" s="37">
+      <c r="AA3" s="34">
         <v>3694</v>
       </c>
-      <c r="AB3" s="37">
+      <c r="AB3" s="34">
         <v>369</v>
       </c>
-      <c r="AC3" s="37">
+      <c r="AC3" s="34">
         <v>3325</v>
       </c>
     </row>
@@ -31171,28 +31160,28 @@
         <f t="shared" ref="U4:U32" si="9">U3+1</f>
         <v>2</v>
       </c>
-      <c r="V4" s="37">
+      <c r="V4" s="34">
         <v>6461</v>
       </c>
-      <c r="W4" s="37">
+      <c r="W4" s="34">
         <v>8283</v>
       </c>
-      <c r="X4" s="37">
+      <c r="X4" s="34">
         <v>9272</v>
       </c>
-      <c r="Y4" s="37">
+      <c r="Y4" s="34">
         <v>10804</v>
       </c>
-      <c r="Z4" s="37">
+      <c r="Z4" s="34">
         <v>1271</v>
       </c>
-      <c r="AA4" s="37">
+      <c r="AA4" s="34">
         <v>3697</v>
       </c>
-      <c r="AB4" s="37">
+      <c r="AB4" s="34">
         <v>369</v>
       </c>
-      <c r="AC4" s="37">
+      <c r="AC4" s="34">
         <v>3328</v>
       </c>
     </row>
@@ -31267,28 +31256,28 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="V5" s="37">
+      <c r="V5" s="34">
         <v>6524</v>
       </c>
-      <c r="W5" s="37">
+      <c r="W5" s="34">
         <v>8298</v>
       </c>
-      <c r="X5" s="37">
+      <c r="X5" s="34">
         <v>9275</v>
       </c>
-      <c r="Y5" s="37">
+      <c r="Y5" s="34">
         <v>10804</v>
       </c>
-      <c r="Z5" s="37">
+      <c r="Z5" s="34">
         <v>1271</v>
       </c>
-      <c r="AA5" s="37">
+      <c r="AA5" s="34">
         <v>3702</v>
       </c>
-      <c r="AB5" s="37">
+      <c r="AB5" s="34">
         <v>369</v>
       </c>
-      <c r="AC5" s="37">
+      <c r="AC5" s="34">
         <v>3333</v>
       </c>
     </row>
@@ -31363,28 +31352,28 @@
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="V6" s="37">
+      <c r="V6" s="34">
         <v>6619</v>
       </c>
-      <c r="W6" s="37">
+      <c r="W6" s="34">
         <v>8371</v>
       </c>
-      <c r="X6" s="37">
+      <c r="X6" s="34">
         <v>9279</v>
       </c>
-      <c r="Y6" s="37">
+      <c r="Y6" s="34">
         <v>10805</v>
       </c>
-      <c r="Z6" s="37">
+      <c r="Z6" s="34">
         <v>1271</v>
       </c>
-      <c r="AA6" s="37">
+      <c r="AA6" s="34">
         <v>3707</v>
       </c>
-      <c r="AB6" s="37">
+      <c r="AB6" s="34">
         <v>370</v>
       </c>
-      <c r="AC6" s="37">
+      <c r="AC6" s="34">
         <v>3336</v>
       </c>
     </row>
@@ -31459,28 +31448,28 @@
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="V7" s="37">
+      <c r="V7" s="34">
         <v>6676</v>
       </c>
-      <c r="W7" s="37">
+      <c r="W7" s="34">
         <v>8399</v>
       </c>
-      <c r="X7" s="37">
+      <c r="X7" s="34">
         <v>9281</v>
       </c>
-      <c r="Y7" s="37">
+      <c r="Y7" s="34">
         <v>10806</v>
       </c>
-      <c r="Z7" s="37">
+      <c r="Z7" s="34">
         <v>1271</v>
       </c>
-      <c r="AA7" s="37">
+      <c r="AA7" s="34">
         <v>3711</v>
       </c>
-      <c r="AB7" s="37">
+      <c r="AB7" s="34">
         <v>371</v>
       </c>
-      <c r="AC7" s="37">
+      <c r="AC7" s="34">
         <v>3340</v>
       </c>
     </row>
@@ -31555,28 +31544,28 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="V8" s="37">
+      <c r="V8" s="34">
         <v>6759</v>
       </c>
-      <c r="W8" s="37">
+      <c r="W8" s="34">
         <v>8479</v>
       </c>
-      <c r="X8" s="37">
+      <c r="X8" s="34">
         <v>9287</v>
       </c>
-      <c r="Y8" s="37">
+      <c r="Y8" s="34">
         <v>10807</v>
       </c>
-      <c r="Z8" s="37">
+      <c r="Z8" s="34">
         <v>1272</v>
       </c>
-      <c r="AA8" s="37">
+      <c r="AA8" s="34">
         <v>3712</v>
       </c>
-      <c r="AB8" s="37">
+      <c r="AB8" s="34">
         <v>371</v>
       </c>
-      <c r="AC8" s="37">
+      <c r="AC8" s="34">
         <v>3343</v>
       </c>
     </row>
@@ -31651,28 +31640,28 @@
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="V9" s="37">
+      <c r="V9" s="34">
         <v>6793</v>
       </c>
-      <c r="W9" s="37">
+      <c r="W9" s="34">
         <v>8509</v>
       </c>
-      <c r="X9" s="37">
+      <c r="X9" s="34">
         <v>9291</v>
       </c>
-      <c r="Y9" s="37">
+      <c r="Y9" s="34">
         <v>10808</v>
       </c>
-      <c r="Z9" s="37">
+      <c r="Z9" s="34">
         <v>1273</v>
       </c>
-      <c r="AA9" s="37">
+      <c r="AA9" s="34">
         <v>3719</v>
       </c>
-      <c r="AB9" s="37">
+      <c r="AB9" s="34">
         <v>372</v>
       </c>
-      <c r="AC9" s="37">
+      <c r="AC9" s="34">
         <v>3347</v>
       </c>
     </row>
@@ -31747,28 +31736,28 @@
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="V10" s="37">
+      <c r="V10" s="34">
         <v>6840</v>
       </c>
-      <c r="W10" s="37">
+      <c r="W10" s="34">
         <v>8572</v>
       </c>
-      <c r="X10" s="37">
+      <c r="X10" s="34">
         <v>9291</v>
       </c>
-      <c r="Y10" s="37">
+      <c r="Y10" s="34">
         <v>10808</v>
       </c>
-      <c r="Z10" s="37">
+      <c r="Z10" s="34">
         <v>1273</v>
       </c>
-      <c r="AA10" s="37">
+      <c r="AA10" s="34">
         <v>3723</v>
       </c>
-      <c r="AB10" s="37">
+      <c r="AB10" s="34">
         <v>372</v>
       </c>
-      <c r="AC10" s="37">
+      <c r="AC10" s="34">
         <v>3351</v>
       </c>
     </row>
@@ -31843,28 +31832,28 @@
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="V11" s="37">
+      <c r="V11" s="34">
         <v>6845</v>
       </c>
-      <c r="W11" s="37">
+      <c r="W11" s="34">
         <v>8607</v>
       </c>
-      <c r="X11" s="37">
+      <c r="X11" s="34">
         <v>9299</v>
       </c>
-      <c r="Y11" s="37">
+      <c r="Y11" s="34">
         <v>10809</v>
       </c>
-      <c r="Z11" s="37">
+      <c r="Z11" s="34">
         <v>1273</v>
       </c>
-      <c r="AA11" s="37">
+      <c r="AA11" s="34">
         <v>3726</v>
       </c>
-      <c r="AB11" s="37">
+      <c r="AB11" s="34">
         <v>373</v>
       </c>
-      <c r="AC11" s="37">
+      <c r="AC11" s="34">
         <v>3351</v>
       </c>
     </row>
@@ -31939,28 +31928,28 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="V12" s="37">
+      <c r="V12" s="34">
         <v>6902</v>
       </c>
-      <c r="W12" s="37">
+      <c r="W12" s="34">
         <v>8690</v>
       </c>
-      <c r="X12" s="37">
+      <c r="X12" s="34">
         <v>9302</v>
       </c>
-      <c r="Y12" s="37">
+      <c r="Y12" s="34">
         <v>10810</v>
       </c>
-      <c r="Z12" s="37">
+      <c r="Z12" s="34">
         <v>1273</v>
       </c>
-      <c r="AA12" s="37">
+      <c r="AA12" s="34">
         <v>3733</v>
       </c>
-      <c r="AB12" s="37">
+      <c r="AB12" s="34">
         <v>373</v>
       </c>
-      <c r="AC12" s="37">
+      <c r="AC12" s="34">
         <v>3359</v>
       </c>
     </row>
@@ -32035,28 +32024,28 @@
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
-      <c r="V13" s="37">
+      <c r="V13" s="34">
         <v>6917</v>
       </c>
-      <c r="W13" s="37">
+      <c r="W13" s="34">
         <v>8710</v>
       </c>
-      <c r="X13" s="37">
+      <c r="X13" s="34">
         <v>9309</v>
       </c>
-      <c r="Y13" s="37">
+      <c r="Y13" s="34">
         <v>10811</v>
       </c>
-      <c r="Z13" s="37">
+      <c r="Z13" s="34">
         <v>1274</v>
       </c>
-      <c r="AA13" s="37">
+      <c r="AA13" s="34">
         <v>3734</v>
       </c>
-      <c r="AB13" s="37">
+      <c r="AB13" s="34">
         <v>373</v>
       </c>
-      <c r="AC13" s="37">
+      <c r="AC13" s="34">
         <v>3360</v>
       </c>
     </row>
@@ -32131,28 +32120,28 @@
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="V14" s="37">
+      <c r="V14" s="34">
         <v>7029</v>
       </c>
-      <c r="W14" s="37">
+      <c r="W14" s="34">
         <v>8819</v>
       </c>
-      <c r="X14" s="37">
+      <c r="X14" s="34">
         <v>9312</v>
       </c>
-      <c r="Y14" s="37">
+      <c r="Y14" s="34">
         <v>10811</v>
       </c>
-      <c r="Z14" s="37">
+      <c r="Z14" s="34">
         <v>1274</v>
       </c>
-      <c r="AA14" s="37">
+      <c r="AA14" s="34">
         <v>3738</v>
       </c>
-      <c r="AB14" s="37">
+      <c r="AB14" s="34">
         <v>374</v>
       </c>
-      <c r="AC14" s="37">
+      <c r="AC14" s="34">
         <v>3364</v>
       </c>
     </row>
@@ -32226,28 +32215,28 @@
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
-      <c r="V15" s="37">
+      <c r="V15" s="34">
         <v>7094</v>
       </c>
-      <c r="W15" s="37">
+      <c r="W15" s="34">
         <v>8914</v>
       </c>
-      <c r="X15" s="37">
+      <c r="X15" s="34">
         <v>9318</v>
       </c>
-      <c r="Y15" s="37">
+      <c r="Y15" s="34">
         <v>10812</v>
       </c>
-      <c r="Z15" s="37">
+      <c r="Z15" s="34">
         <v>1275</v>
       </c>
-      <c r="AA15" s="37">
+      <c r="AA15" s="34">
         <v>3747</v>
       </c>
-      <c r="AB15" s="37">
+      <c r="AB15" s="34">
         <v>376</v>
       </c>
-      <c r="AC15" s="37">
+      <c r="AC15" s="34">
         <v>3371</v>
       </c>
     </row>
@@ -32322,28 +32311,28 @@
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="V16" s="37">
+      <c r="V16" s="34">
         <v>7094</v>
       </c>
-      <c r="W16" s="37">
+      <c r="W16" s="34">
         <v>8914</v>
       </c>
-      <c r="X16" s="37">
+      <c r="X16" s="34">
         <v>9318</v>
       </c>
-      <c r="Y16" s="37">
+      <c r="Y16" s="34">
         <v>10812</v>
       </c>
-      <c r="Z16" s="37">
+      <c r="Z16" s="34">
         <v>1275</v>
       </c>
-      <c r="AA16" s="37">
+      <c r="AA16" s="34">
         <v>3747</v>
       </c>
-      <c r="AB16" s="37">
+      <c r="AB16" s="34">
         <v>376</v>
       </c>
-      <c r="AC16" s="37">
+      <c r="AC16" s="34">
         <v>3371</v>
       </c>
     </row>
@@ -32418,28 +32407,28 @@
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="V17" s="37">
+      <c r="V17" s="34">
         <v>7137</v>
       </c>
-      <c r="W17" s="37">
+      <c r="W17" s="34">
         <v>8958</v>
       </c>
-      <c r="X17" s="37">
+      <c r="X17" s="34">
         <v>9322</v>
       </c>
-      <c r="Y17" s="37">
+      <c r="Y17" s="34">
         <v>10813</v>
       </c>
-      <c r="Z17" s="37">
+      <c r="Z17" s="34">
         <v>1275</v>
       </c>
-      <c r="AA17" s="37">
+      <c r="AA17" s="34">
         <v>3751</v>
       </c>
-      <c r="AB17" s="37">
+      <c r="AB17" s="34">
         <v>376</v>
       </c>
-      <c r="AC17" s="37">
+      <c r="AC17" s="34">
         <v>3375</v>
       </c>
     </row>
@@ -32514,28 +32503,28 @@
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="V18" s="37">
+      <c r="V18" s="34">
         <v>7142</v>
       </c>
-      <c r="W18" s="37">
+      <c r="W18" s="34">
         <v>8978</v>
       </c>
-      <c r="X18" s="37">
+      <c r="X18" s="34">
         <v>9323</v>
       </c>
-      <c r="Y18" s="37">
+      <c r="Y18" s="34">
         <v>10813</v>
       </c>
-      <c r="Z18" s="37">
+      <c r="Z18" s="34">
         <v>1275</v>
       </c>
-      <c r="AA18" s="37">
+      <c r="AA18" s="34">
         <v>3755</v>
       </c>
-      <c r="AB18" s="37">
+      <c r="AB18" s="34">
         <v>379</v>
       </c>
-      <c r="AC18" s="37">
+      <c r="AC18" s="34">
         <v>3379</v>
       </c>
     </row>
@@ -32611,28 +32600,28 @@
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="V19" s="37">
+      <c r="V19" s="34">
         <v>7192</v>
       </c>
-      <c r="W19" s="37">
+      <c r="W19" s="34">
         <v>9010</v>
       </c>
-      <c r="X19" s="37">
+      <c r="X19" s="34">
         <v>9328</v>
       </c>
-      <c r="Y19" s="37">
+      <c r="Y19" s="34">
         <v>10815</v>
       </c>
-      <c r="Z19" s="37">
+      <c r="Z19" s="34">
         <v>1275</v>
       </c>
-      <c r="AA19" s="37">
+      <c r="AA19" s="34">
         <v>3757</v>
       </c>
-      <c r="AB19" s="37">
+      <c r="AB19" s="34">
         <v>379</v>
       </c>
-      <c r="AC19" s="37">
+      <c r="AC19" s="34">
         <v>3381</v>
       </c>
     </row>
@@ -32707,28 +32696,28 @@
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="V20" s="37">
+      <c r="V20" s="34">
         <v>7326</v>
       </c>
-      <c r="W20" s="37">
+      <c r="W20" s="34">
         <v>9120</v>
       </c>
-      <c r="X20" s="37">
+      <c r="X20" s="34">
         <v>9339</v>
       </c>
-      <c r="Y20" s="37">
+      <c r="Y20" s="34">
         <v>10815</v>
       </c>
-      <c r="Z20" s="37">
+      <c r="Z20" s="34">
         <v>1275</v>
       </c>
-      <c r="AA20" s="37">
+      <c r="AA20" s="34">
         <v>3771</v>
       </c>
-      <c r="AB20" s="37">
+      <c r="AB20" s="34">
         <v>379</v>
       </c>
-      <c r="AC20" s="37">
+      <c r="AC20" s="34">
         <v>3393</v>
       </c>
     </row>
@@ -32803,28 +32792,28 @@
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="V21" s="37">
+      <c r="V21" s="34">
         <v>7326</v>
       </c>
-      <c r="W21" s="37">
+      <c r="W21" s="34">
         <v>9120</v>
       </c>
-      <c r="X21" s="37">
+      <c r="X21" s="34">
         <v>9339</v>
       </c>
-      <c r="Y21" s="37">
+      <c r="Y21" s="34">
         <v>10815</v>
       </c>
-      <c r="Z21" s="37">
+      <c r="Z21" s="34">
         <v>1275</v>
       </c>
-      <c r="AA21" s="37">
+      <c r="AA21" s="34">
         <v>3771</v>
       </c>
-      <c r="AB21" s="37">
+      <c r="AB21" s="34">
         <v>379</v>
       </c>
-      <c r="AC21" s="37">
+      <c r="AC21" s="34">
         <v>3393</v>
       </c>
     </row>
@@ -32899,28 +32888,28 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="V22" s="37">
+      <c r="V22" s="34">
         <v>7326</v>
       </c>
-      <c r="W22" s="37">
+      <c r="W22" s="34">
         <v>9120</v>
       </c>
-      <c r="X22" s="37">
+      <c r="X22" s="34">
         <v>9339</v>
       </c>
-      <c r="Y22" s="37">
+      <c r="Y22" s="34">
         <v>10815</v>
       </c>
-      <c r="Z22" s="37">
+      <c r="Z22" s="34">
         <v>1275</v>
       </c>
-      <c r="AA22" s="37">
+      <c r="AA22" s="34">
         <v>3771</v>
       </c>
-      <c r="AB22" s="37">
+      <c r="AB22" s="34">
         <v>379</v>
       </c>
-      <c r="AC22" s="37">
+      <c r="AC22" s="34">
         <v>3393</v>
       </c>
     </row>
@@ -32995,28 +32984,28 @@
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="V23" s="41">
+      <c r="V23" s="37">
         <v>7346</v>
       </c>
-      <c r="W23" s="41">
+      <c r="W23" s="37">
         <v>9149</v>
       </c>
-      <c r="X23" s="41">
+      <c r="X23" s="37">
         <v>9342</v>
       </c>
-      <c r="Y23" s="41">
+      <c r="Y23" s="37">
         <v>10816</v>
       </c>
-      <c r="Z23" s="41">
+      <c r="Z23" s="37">
         <v>1275</v>
       </c>
-      <c r="AA23" s="41">
+      <c r="AA23" s="37">
         <v>3776</v>
       </c>
-      <c r="AB23" s="41">
+      <c r="AB23" s="37">
         <v>379</v>
       </c>
-      <c r="AC23" s="41">
+      <c r="AC23" s="37">
         <v>3397</v>
       </c>
     </row>
@@ -33091,28 +33080,28 @@
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="V24" s="41">
+      <c r="V24" s="37">
         <v>7374</v>
       </c>
-      <c r="W24" s="41">
+      <c r="W24" s="37">
         <v>9204</v>
       </c>
-      <c r="X24" s="41">
+      <c r="X24" s="37">
         <v>9345</v>
       </c>
-      <c r="Y24" s="41">
+      <c r="Y24" s="37">
         <v>10816</v>
       </c>
-      <c r="Z24" s="41">
+      <c r="Z24" s="37">
         <v>1275</v>
       </c>
-      <c r="AA24" s="41">
+      <c r="AA24" s="37">
         <v>3780</v>
       </c>
-      <c r="AB24" s="41">
+      <c r="AB24" s="37">
         <v>379</v>
       </c>
-      <c r="AC24" s="41">
+      <c r="AC24" s="37">
         <v>3401</v>
       </c>
     </row>
@@ -33129,49 +33118,49 @@
       </c>
       <c r="D25" s="6">
         <f t="shared" si="10"/>
-        <v>-7408</v>
+        <v>57</v>
       </c>
       <c r="E25" s="12">
         <v>0</v>
       </c>
       <c r="F25" s="6">
         <f t="shared" si="11"/>
-        <v>-9260</v>
+        <v>67</v>
       </c>
       <c r="G25" s="12">
         <v>0</v>
       </c>
       <c r="H25" s="6">
         <f t="shared" si="12"/>
-        <v>-9349</v>
+        <v>2</v>
       </c>
       <c r="I25" s="12">
         <v>0</v>
       </c>
       <c r="J25" s="6">
         <f t="shared" si="17"/>
-        <v>-10817</v>
+        <v>1</v>
       </c>
       <c r="K25" s="12">
         <v>0</v>
       </c>
       <c r="L25" s="6">
         <f t="shared" si="13"/>
-        <v>-1275</v>
+        <v>0</v>
       </c>
       <c r="M25" s="12">
         <v>0</v>
       </c>
       <c r="N25" s="6">
         <f t="shared" si="14"/>
-        <v>-3785</v>
+        <v>4</v>
       </c>
       <c r="O25" s="12">
         <v>0</v>
       </c>
       <c r="P25" s="6">
         <f t="shared" si="15"/>
-        <v>-379</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="12">
         <v>0</v>
@@ -33181,7 +33170,7 @@
       </c>
       <c r="S25" s="6">
         <f t="shared" si="16"/>
-        <v>-3406</v>
+        <v>3</v>
       </c>
       <c r="U25" s="11">
         <f t="shared" si="9"/>
@@ -33225,21 +33214,21 @@
       </c>
       <c r="D26" s="6">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="E26" s="12">
         <v>0</v>
       </c>
       <c r="F26" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G26" s="12">
         <v>0</v>
       </c>
       <c r="H26" s="6">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I26" s="12">
         <v>0</v>
@@ -33260,14 +33249,14 @@
       </c>
       <c r="N26" s="6">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O26" s="12">
         <v>0</v>
       </c>
       <c r="P26" s="6">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="Q26" s="12">
         <v>0</v>
@@ -33279,18 +33268,34 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="U26" s="18">
+      <c r="U26" s="35">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="V26" s="40"/>
-      <c r="W26" s="40"/>
-      <c r="X26" s="40"/>
-      <c r="Y26" s="40"/>
-      <c r="Z26" s="40"/>
-      <c r="AA26" s="40"/>
-      <c r="AB26" s="40"/>
-      <c r="AC26" s="40"/>
+      <c r="V26" s="34">
+        <v>7465</v>
+      </c>
+      <c r="W26" s="34">
+        <v>9327</v>
+      </c>
+      <c r="X26" s="34">
+        <v>9351</v>
+      </c>
+      <c r="Y26" s="34">
+        <v>10818</v>
+      </c>
+      <c r="Z26" s="34">
+        <v>1275</v>
+      </c>
+      <c r="AA26" s="34">
+        <v>3789</v>
+      </c>
+      <c r="AB26" s="34">
+        <v>379</v>
+      </c>
+      <c r="AC26" s="34">
+        <v>3409</v>
+      </c>
     </row>
     <row r="27" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="15">
@@ -33305,49 +33310,49 @@
       </c>
       <c r="D27" s="6">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-7528</v>
       </c>
       <c r="E27" s="12">
         <v>0</v>
       </c>
       <c r="F27" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>-9397</v>
       </c>
       <c r="G27" s="12">
         <v>0</v>
       </c>
       <c r="H27" s="6">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>-9355</v>
       </c>
       <c r="I27" s="12">
         <v>0</v>
       </c>
       <c r="J27" s="6">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>-10818</v>
       </c>
       <c r="K27" s="12">
         <v>0</v>
       </c>
       <c r="L27" s="6">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>-1275</v>
       </c>
       <c r="M27" s="12">
         <v>0</v>
       </c>
       <c r="N27" s="6">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>-3793</v>
       </c>
       <c r="O27" s="12">
         <v>0</v>
       </c>
       <c r="P27" s="6">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>-438</v>
       </c>
       <c r="Q27" s="12">
         <v>0</v>
@@ -33357,20 +33362,36 @@
       </c>
       <c r="S27" s="6">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="15">
+        <v>-3409</v>
+      </c>
+      <c r="U27" s="11">
         <f t="shared" si="9"/>
         <v>25</v>
       </c>
-      <c r="V27" s="13"/>
-      <c r="W27" s="13"/>
-      <c r="X27" s="13"/>
-      <c r="Y27" s="13"/>
-      <c r="Z27" s="13"/>
-      <c r="AA27" s="13"/>
-      <c r="AB27" s="13"/>
-      <c r="AC27" s="13"/>
+      <c r="V27" s="34">
+        <v>7528</v>
+      </c>
+      <c r="W27" s="34">
+        <v>9397</v>
+      </c>
+      <c r="X27" s="34">
+        <v>9355</v>
+      </c>
+      <c r="Y27" s="34">
+        <v>10818</v>
+      </c>
+      <c r="Z27" s="34">
+        <v>1275</v>
+      </c>
+      <c r="AA27" s="34">
+        <v>3793</v>
+      </c>
+      <c r="AB27" s="34">
+        <v>438</v>
+      </c>
+      <c r="AC27" s="34">
+        <v>3409</v>
+      </c>
     </row>
     <row r="28" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="15">
@@ -33443,14 +33464,14 @@
         <f t="shared" si="9"/>
         <v>26</v>
       </c>
-      <c r="V28" s="13"/>
-      <c r="W28" s="13"/>
-      <c r="X28" s="13"/>
-      <c r="Y28" s="13"/>
-      <c r="Z28" s="13"/>
-      <c r="AA28" s="13"/>
-      <c r="AB28" s="13"/>
-      <c r="AC28" s="13"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="17"/>
+      <c r="AA28" s="17"/>
+      <c r="AB28" s="17"/>
+      <c r="AC28" s="17"/>
     </row>
     <row r="29" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="15">
@@ -33723,22 +33744,22 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="34"/>
-      <c r="S35" s="34"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="38"/>
+      <c r="P35" s="38"/>
+      <c r="Q35" s="38"/>
+      <c r="R35" s="38"/>
+      <c r="S35" s="38"/>
       <c r="T35"/>
     </row>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
@@ -34457,25 +34478,25 @@
       <c r="S69" s="1"/>
     </row>
     <row r="70" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="34"/>
-      <c r="B70" s="34"/>
-      <c r="C70" s="34"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="34"/>
-      <c r="G70" s="34"/>
-      <c r="H70" s="34"/>
-      <c r="I70" s="34"/>
-      <c r="J70" s="34"/>
-      <c r="K70" s="34"/>
-      <c r="L70" s="34"/>
-      <c r="M70" s="34"/>
-      <c r="N70" s="34"/>
-      <c r="O70" s="34"/>
-      <c r="P70" s="34"/>
-      <c r="Q70" s="34"/>
-      <c r="R70" s="34"/>
-      <c r="S70" s="34"/>
+      <c r="A70" s="38"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
+      <c r="J70" s="38"/>
+      <c r="K70" s="38"/>
+      <c r="L70" s="38"/>
+      <c r="M70" s="38"/>
+      <c r="N70" s="38"/>
+      <c r="O70" s="38"/>
+      <c r="P70" s="38"/>
+      <c r="Q70" s="38"/>
+      <c r="R70" s="38"/>
+      <c r="S70" s="38"/>
     </row>
     <row r="71" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -34520,25 +34541,25 @@
       <c r="S72" s="21"/>
     </row>
     <row r="75" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="35"/>
-      <c r="B75" s="35"/>
-      <c r="C75" s="35"/>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
-      <c r="J75" s="35"/>
-      <c r="K75" s="35"/>
-      <c r="L75" s="35"/>
-      <c r="M75" s="35"/>
-      <c r="N75" s="35"/>
-      <c r="O75" s="35"/>
-      <c r="P75" s="35"/>
-      <c r="Q75" s="35"/>
-      <c r="R75" s="35"/>
-      <c r="S75" s="35"/>
+      <c r="A75" s="39"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
+      <c r="H75" s="39"/>
+      <c r="I75" s="39"/>
+      <c r="J75" s="39"/>
+      <c r="K75" s="39"/>
+      <c r="L75" s="39"/>
+      <c r="M75" s="39"/>
+      <c r="N75" s="39"/>
+      <c r="O75" s="39"/>
+      <c r="P75" s="39"/>
+      <c r="Q75" s="39"/>
+      <c r="R75" s="39"/>
+      <c r="S75" s="39"/>
     </row>
     <row r="76" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -34604,25 +34625,25 @@
       <c r="S78" s="23"/>
     </row>
     <row r="79" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="36"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-      <c r="G79" s="36"/>
-      <c r="H79" s="36"/>
-      <c r="I79" s="36"/>
-      <c r="J79" s="36"/>
-      <c r="K79" s="36"/>
-      <c r="L79" s="36"/>
-      <c r="M79" s="36"/>
-      <c r="N79" s="36"/>
-      <c r="O79" s="36"/>
-      <c r="P79" s="36"/>
-      <c r="Q79" s="36"/>
-      <c r="R79" s="36"/>
-      <c r="S79" s="36"/>
+      <c r="A79" s="40"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="40"/>
+      <c r="I79" s="40"/>
+      <c r="J79" s="40"/>
+      <c r="K79" s="40"/>
+      <c r="L79" s="40"/>
+      <c r="M79" s="40"/>
+      <c r="N79" s="40"/>
+      <c r="O79" s="40"/>
+      <c r="P79" s="40"/>
+      <c r="Q79" s="40"/>
+      <c r="R79" s="40"/>
+      <c r="S79" s="40"/>
     </row>
     <row r="80" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -34686,25 +34707,25 @@
       <c r="E85" s="21"/>
     </row>
     <row r="87" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="35"/>
-      <c r="B87" s="35"/>
-      <c r="C87" s="35"/>
-      <c r="D87" s="35"/>
-      <c r="E87" s="35"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="35"/>
-      <c r="J87" s="35"/>
-      <c r="K87" s="35"/>
-      <c r="L87" s="35"/>
-      <c r="M87" s="35"/>
-      <c r="N87" s="35"/>
-      <c r="O87" s="35"/>
-      <c r="P87" s="35"/>
-      <c r="Q87" s="35"/>
-      <c r="R87" s="35"/>
-      <c r="S87" s="35"/>
+      <c r="A87" s="39"/>
+      <c r="B87" s="39"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="39"/>
+      <c r="E87" s="39"/>
+      <c r="F87" s="39"/>
+      <c r="G87" s="39"/>
+      <c r="H87" s="39"/>
+      <c r="I87" s="39"/>
+      <c r="J87" s="39"/>
+      <c r="K87" s="39"/>
+      <c r="L87" s="39"/>
+      <c r="M87" s="39"/>
+      <c r="N87" s="39"/>
+      <c r="O87" s="39"/>
+      <c r="P87" s="39"/>
+      <c r="Q87" s="39"/>
+      <c r="R87" s="39"/>
+      <c r="S87" s="39"/>
     </row>
     <row r="88" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -34896,25 +34917,25 @@
       <c r="E98" s="24"/>
     </row>
     <row r="100" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="34"/>
-      <c r="B100" s="34"/>
-      <c r="C100" s="34"/>
-      <c r="D100" s="34"/>
-      <c r="E100" s="34"/>
-      <c r="F100" s="34"/>
-      <c r="G100" s="34"/>
-      <c r="H100" s="34"/>
-      <c r="I100" s="34"/>
-      <c r="J100" s="34"/>
-      <c r="K100" s="34"/>
-      <c r="L100" s="34"/>
-      <c r="M100" s="34"/>
-      <c r="N100" s="34"/>
-      <c r="O100" s="34"/>
-      <c r="P100" s="34"/>
-      <c r="Q100" s="34"/>
-      <c r="R100" s="34"/>
-      <c r="S100" s="34"/>
+      <c r="A100" s="38"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="38"/>
+      <c r="G100" s="38"/>
+      <c r="H100" s="38"/>
+      <c r="I100" s="38"/>
+      <c r="J100" s="38"/>
+      <c r="K100" s="38"/>
+      <c r="L100" s="38"/>
+      <c r="M100" s="38"/>
+      <c r="N100" s="38"/>
+      <c r="O100" s="38"/>
+      <c r="P100" s="38"/>
+      <c r="Q100" s="38"/>
+      <c r="R100" s="38"/>
+      <c r="S100" s="38"/>
     </row>
     <row r="101" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -35175,28 +35196,28 @@
       <c r="U2" s="7">
         <v>0</v>
       </c>
-      <c r="V2" s="39">
+      <c r="V2" s="36">
         <v>4765</v>
       </c>
-      <c r="W2" s="39">
+      <c r="W2" s="36">
         <v>6659</v>
       </c>
-      <c r="X2" s="39">
+      <c r="X2" s="36">
         <v>9140</v>
       </c>
-      <c r="Y2" s="39">
+      <c r="Y2" s="36">
         <v>10780</v>
       </c>
-      <c r="Z2" s="39">
+      <c r="Z2" s="36">
         <v>1266</v>
       </c>
-      <c r="AA2" s="39">
+      <c r="AA2" s="36">
         <v>3556</v>
       </c>
-      <c r="AB2" s="39">
+      <c r="AB2" s="36">
         <v>353</v>
       </c>
-      <c r="AC2" s="39">
+      <c r="AC2" s="36">
         <v>3203</v>
       </c>
       <c r="AE2" s="9" t="s">
@@ -35277,28 +35298,28 @@
       <c r="U3" s="5">
         <v>1</v>
       </c>
-      <c r="V3" s="37">
+      <c r="V3" s="34">
         <v>4909</v>
       </c>
-      <c r="W3" s="37">
+      <c r="W3" s="34">
         <v>6810</v>
       </c>
-      <c r="X3" s="37">
+      <c r="X3" s="34">
         <v>9145</v>
       </c>
-      <c r="Y3" s="37">
+      <c r="Y3" s="34">
         <v>10783</v>
       </c>
-      <c r="Z3" s="37">
+      <c r="Z3" s="34">
         <v>1266</v>
       </c>
-      <c r="AA3" s="37">
+      <c r="AA3" s="34">
         <v>3565</v>
       </c>
-      <c r="AB3" s="37">
+      <c r="AB3" s="34">
         <v>354</v>
       </c>
-      <c r="AC3" s="37">
+      <c r="AC3" s="34">
         <v>3210</v>
       </c>
     </row>
@@ -35373,28 +35394,28 @@
         <f t="shared" ref="U4:U33" si="8">U3+1</f>
         <v>2</v>
       </c>
-      <c r="V4" s="37">
+      <c r="V4" s="34">
         <v>4909</v>
       </c>
-      <c r="W4" s="37">
+      <c r="W4" s="34">
         <v>6810</v>
       </c>
-      <c r="X4" s="37">
+      <c r="X4" s="34">
         <v>9145</v>
       </c>
-      <c r="Y4" s="37">
+      <c r="Y4" s="34">
         <v>10783</v>
       </c>
-      <c r="Z4" s="37">
+      <c r="Z4" s="34">
         <v>1266</v>
       </c>
-      <c r="AA4" s="37">
+      <c r="AA4" s="34">
         <v>3565</v>
       </c>
-      <c r="AB4" s="37">
+      <c r="AB4" s="34">
         <v>354</v>
       </c>
-      <c r="AC4" s="37">
+      <c r="AC4" s="34">
         <v>3210</v>
       </c>
     </row>
@@ -35469,28 +35490,28 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="V5" s="37">
+      <c r="V5" s="34">
         <v>5009</v>
       </c>
-      <c r="W5" s="37">
+      <c r="W5" s="34">
         <v>6932</v>
       </c>
-      <c r="X5" s="37">
+      <c r="X5" s="34">
         <v>9157</v>
       </c>
-      <c r="Y5" s="37">
+      <c r="Y5" s="34">
         <v>10784</v>
       </c>
-      <c r="Z5" s="37">
+      <c r="Z5" s="34">
         <v>1267</v>
       </c>
-      <c r="AA5" s="37">
+      <c r="AA5" s="34">
         <v>3574</v>
       </c>
-      <c r="AB5" s="37">
+      <c r="AB5" s="34">
         <v>355</v>
       </c>
-      <c r="AC5" s="37">
+      <c r="AC5" s="34">
         <v>3218</v>
       </c>
     </row>
@@ -35565,28 +35586,28 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="V6" s="37">
+      <c r="V6" s="34">
         <v>5025</v>
       </c>
-      <c r="W6" s="37">
+      <c r="W6" s="34">
         <v>6932</v>
       </c>
-      <c r="X6" s="37">
+      <c r="X6" s="34">
         <v>9158</v>
       </c>
-      <c r="Y6" s="37">
+      <c r="Y6" s="34">
         <v>10784</v>
       </c>
-      <c r="Z6" s="37">
+      <c r="Z6" s="34">
         <v>1267</v>
       </c>
-      <c r="AA6" s="37">
+      <c r="AA6" s="34">
         <v>3578</v>
       </c>
-      <c r="AB6" s="37">
+      <c r="AB6" s="34">
         <v>355</v>
       </c>
-      <c r="AC6" s="37">
+      <c r="AC6" s="34">
         <v>3223</v>
       </c>
     </row>
@@ -35661,28 +35682,28 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="V7" s="37">
+      <c r="V7" s="34">
         <v>5069</v>
       </c>
-      <c r="W7" s="37">
+      <c r="W7" s="34">
         <v>6997</v>
       </c>
-      <c r="X7" s="37">
+      <c r="X7" s="34">
         <v>9168</v>
       </c>
-      <c r="Y7" s="37">
+      <c r="Y7" s="34">
         <v>10784</v>
       </c>
-      <c r="Z7" s="37">
+      <c r="Z7" s="34">
         <v>1267</v>
       </c>
-      <c r="AA7" s="37">
+      <c r="AA7" s="34">
         <v>3583</v>
       </c>
-      <c r="AB7" s="37">
+      <c r="AB7" s="34">
         <v>355</v>
       </c>
-      <c r="AC7" s="37">
+      <c r="AC7" s="34">
         <v>3227</v>
       </c>
     </row>
@@ -35757,28 +35778,28 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="V8" s="37">
+      <c r="V8" s="34">
         <v>5127</v>
       </c>
-      <c r="W8" s="37">
+      <c r="W8" s="34">
         <v>7107</v>
       </c>
-      <c r="X8" s="37">
+      <c r="X8" s="34">
         <v>9172</v>
       </c>
-      <c r="Y8" s="37">
+      <c r="Y8" s="34">
         <v>10785</v>
       </c>
-      <c r="Z8" s="37">
+      <c r="Z8" s="34">
         <v>1267</v>
       </c>
-      <c r="AA8" s="37">
+      <c r="AA8" s="34">
         <v>3584</v>
       </c>
-      <c r="AB8" s="37">
+      <c r="AB8" s="34">
         <v>355</v>
       </c>
-      <c r="AC8" s="37">
+      <c r="AC8" s="34">
         <v>3228</v>
       </c>
     </row>
@@ -35853,28 +35874,28 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="V9" s="37">
+      <c r="V9" s="34">
         <v>5130</v>
       </c>
-      <c r="W9" s="37">
+      <c r="W9" s="34">
         <v>7110</v>
       </c>
-      <c r="X9" s="37">
+      <c r="X9" s="34">
         <v>9176</v>
       </c>
-      <c r="Y9" s="37">
+      <c r="Y9" s="34">
         <v>10787</v>
       </c>
-      <c r="Z9" s="37">
+      <c r="Z9" s="34">
         <v>1268</v>
       </c>
-      <c r="AA9" s="37">
+      <c r="AA9" s="34">
         <v>3590</v>
       </c>
-      <c r="AB9" s="37">
+      <c r="AB9" s="34">
         <v>356</v>
       </c>
-      <c r="AC9" s="37">
+      <c r="AC9" s="34">
         <v>3233</v>
       </c>
     </row>
@@ -35949,28 +35970,28 @@
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="V10" s="37">
+      <c r="V10" s="34">
         <v>5130</v>
       </c>
-      <c r="W10" s="37">
+      <c r="W10" s="34">
         <v>7110</v>
       </c>
-      <c r="X10" s="37">
+      <c r="X10" s="34">
         <v>9176</v>
       </c>
-      <c r="Y10" s="37">
+      <c r="Y10" s="34">
         <v>10787</v>
       </c>
-      <c r="Z10" s="37">
+      <c r="Z10" s="34">
         <v>1268</v>
       </c>
-      <c r="AA10" s="37">
+      <c r="AA10" s="34">
         <v>3590</v>
       </c>
-      <c r="AB10" s="37">
+      <c r="AB10" s="34">
         <v>356</v>
       </c>
-      <c r="AC10" s="37">
+      <c r="AC10" s="34">
         <v>3233</v>
       </c>
     </row>
@@ -36045,28 +36066,28 @@
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="V11" s="37">
+      <c r="V11" s="34">
         <v>5130</v>
       </c>
-      <c r="W11" s="37">
+      <c r="W11" s="34">
         <v>7110</v>
       </c>
-      <c r="X11" s="37">
+      <c r="X11" s="34">
         <v>9176</v>
       </c>
-      <c r="Y11" s="37">
+      <c r="Y11" s="34">
         <v>10787</v>
       </c>
-      <c r="Z11" s="37">
+      <c r="Z11" s="34">
         <v>1268</v>
       </c>
-      <c r="AA11" s="37">
+      <c r="AA11" s="34">
         <v>3590</v>
       </c>
-      <c r="AB11" s="37">
+      <c r="AB11" s="34">
         <v>356</v>
       </c>
-      <c r="AC11" s="37">
+      <c r="AC11" s="34">
         <v>3233</v>
       </c>
     </row>
@@ -36141,28 +36162,28 @@
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="V12" s="37">
+      <c r="V12" s="34">
         <v>5416</v>
       </c>
-      <c r="W12" s="37">
+      <c r="W12" s="34">
         <v>7409</v>
       </c>
-      <c r="X12" s="37">
+      <c r="X12" s="34">
         <v>9192</v>
       </c>
-      <c r="Y12" s="37">
+      <c r="Y12" s="34">
         <v>10787</v>
       </c>
-      <c r="Z12" s="37">
+      <c r="Z12" s="34">
         <v>1269</v>
       </c>
-      <c r="AA12" s="37">
+      <c r="AA12" s="34">
         <v>3604</v>
       </c>
-      <c r="AB12" s="37">
+      <c r="AB12" s="34">
         <v>358</v>
       </c>
-      <c r="AC12" s="37">
+      <c r="AC12" s="34">
         <v>3245</v>
       </c>
     </row>
@@ -36237,28 +36258,28 @@
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="V13" s="37">
+      <c r="V13" s="34">
         <v>5429</v>
       </c>
-      <c r="W13" s="37">
+      <c r="W13" s="34">
         <v>7435</v>
       </c>
-      <c r="X13" s="37">
+      <c r="X13" s="34">
         <v>9195</v>
       </c>
-      <c r="Y13" s="37">
+      <c r="Y13" s="34">
         <v>10788</v>
       </c>
-      <c r="Z13" s="37">
+      <c r="Z13" s="34">
         <v>1269</v>
       </c>
-      <c r="AA13" s="37">
+      <c r="AA13" s="34">
         <v>3609</v>
       </c>
-      <c r="AB13" s="37">
+      <c r="AB13" s="34">
         <v>358</v>
       </c>
-      <c r="AC13" s="37">
+      <c r="AC13" s="34">
         <v>3250</v>
       </c>
     </row>
@@ -36333,28 +36354,28 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="V14" s="37">
+      <c r="V14" s="34">
         <v>5458</v>
       </c>
-      <c r="W14" s="37">
+      <c r="W14" s="34">
         <v>7553</v>
       </c>
-      <c r="X14" s="37">
+      <c r="X14" s="34">
         <v>9200</v>
       </c>
-      <c r="Y14" s="37">
+      <c r="Y14" s="34">
         <v>10789</v>
       </c>
-      <c r="Z14" s="37">
+      <c r="Z14" s="34">
         <v>1269</v>
       </c>
-      <c r="AA14" s="37">
+      <c r="AA14" s="34">
         <v>3614</v>
       </c>
-      <c r="AB14" s="37">
+      <c r="AB14" s="34">
         <v>358</v>
       </c>
-      <c r="AC14" s="37">
+      <c r="AC14" s="34">
         <v>3255</v>
       </c>
     </row>
@@ -36428,28 +36449,28 @@
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="V15" s="37">
+      <c r="V15" s="34">
         <v>5458</v>
       </c>
-      <c r="W15" s="37">
+      <c r="W15" s="34">
         <v>7553</v>
       </c>
-      <c r="X15" s="37">
+      <c r="X15" s="34">
         <v>9200</v>
       </c>
-      <c r="Y15" s="37">
+      <c r="Y15" s="34">
         <v>10789</v>
       </c>
-      <c r="Z15" s="37">
+      <c r="Z15" s="34">
         <v>1269</v>
       </c>
-      <c r="AA15" s="37">
+      <c r="AA15" s="34">
         <v>3614</v>
       </c>
-      <c r="AB15" s="37">
+      <c r="AB15" s="34">
         <v>358</v>
       </c>
-      <c r="AC15" s="37">
+      <c r="AC15" s="34">
         <v>3255</v>
       </c>
     </row>
@@ -36524,28 +36545,28 @@
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="V16" s="37">
+      <c r="V16" s="34">
         <v>5458</v>
       </c>
-      <c r="W16" s="37">
+      <c r="W16" s="34">
         <v>7553</v>
       </c>
-      <c r="X16" s="37">
+      <c r="X16" s="34">
         <v>9200</v>
       </c>
-      <c r="Y16" s="37">
+      <c r="Y16" s="34">
         <v>10789</v>
       </c>
-      <c r="Z16" s="37">
+      <c r="Z16" s="34">
         <v>1269</v>
       </c>
-      <c r="AA16" s="37">
+      <c r="AA16" s="34">
         <v>3614</v>
       </c>
-      <c r="AB16" s="37">
+      <c r="AB16" s="34">
         <v>358</v>
       </c>
-      <c r="AC16" s="37">
+      <c r="AC16" s="34">
         <v>3255</v>
       </c>
     </row>
@@ -36620,28 +36641,28 @@
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="V17" s="37">
+      <c r="V17" s="34">
         <v>5695</v>
       </c>
-      <c r="W17" s="37">
+      <c r="W17" s="34">
         <v>7647</v>
       </c>
-      <c r="X17" s="37">
+      <c r="X17" s="34">
         <v>9209</v>
       </c>
-      <c r="Y17" s="37">
+      <c r="Y17" s="34">
         <v>10791</v>
       </c>
-      <c r="Z17" s="37">
+      <c r="Z17" s="34">
         <v>1269</v>
       </c>
-      <c r="AA17" s="37">
+      <c r="AA17" s="34">
         <v>3627</v>
       </c>
-      <c r="AB17" s="37">
+      <c r="AB17" s="34">
         <v>360</v>
       </c>
-      <c r="AC17" s="37">
+      <c r="AC17" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -36716,28 +36737,28 @@
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="V18" s="37">
+      <c r="V18" s="34">
         <v>5695</v>
       </c>
-      <c r="W18" s="37">
+      <c r="W18" s="34">
         <v>7647</v>
       </c>
-      <c r="X18" s="37">
+      <c r="X18" s="34">
         <v>9209</v>
       </c>
-      <c r="Y18" s="37">
+      <c r="Y18" s="34">
         <v>10791</v>
       </c>
-      <c r="Z18" s="37">
+      <c r="Z18" s="34">
         <v>1269</v>
       </c>
-      <c r="AA18" s="37">
+      <c r="AA18" s="34">
         <v>3627</v>
       </c>
-      <c r="AB18" s="37">
+      <c r="AB18" s="34">
         <v>360</v>
       </c>
-      <c r="AC18" s="37">
+      <c r="AC18" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -36812,28 +36833,28 @@
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="V19" s="37">
+      <c r="V19" s="34">
         <v>5695</v>
       </c>
-      <c r="W19" s="37">
+      <c r="W19" s="34">
         <v>7647</v>
       </c>
-      <c r="X19" s="37">
+      <c r="X19" s="34">
         <v>9209</v>
       </c>
-      <c r="Y19" s="37">
+      <c r="Y19" s="34">
         <v>10791</v>
       </c>
-      <c r="Z19" s="37">
+      <c r="Z19" s="34">
         <v>1269</v>
       </c>
-      <c r="AA19" s="37">
+      <c r="AA19" s="34">
         <v>3627</v>
       </c>
-      <c r="AB19" s="37">
+      <c r="AB19" s="34">
         <v>360</v>
       </c>
-      <c r="AC19" s="37">
+      <c r="AC19" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -36908,28 +36929,28 @@
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="V20" s="37">
+      <c r="V20" s="34">
         <v>5695</v>
       </c>
-      <c r="W20" s="37">
+      <c r="W20" s="34">
         <v>7647</v>
       </c>
-      <c r="X20" s="37">
+      <c r="X20" s="34">
         <v>9209</v>
       </c>
-      <c r="Y20" s="37">
+      <c r="Y20" s="34">
         <v>10791</v>
       </c>
-      <c r="Z20" s="37">
+      <c r="Z20" s="34">
         <v>1269</v>
       </c>
-      <c r="AA20" s="37">
+      <c r="AA20" s="34">
         <v>3627</v>
       </c>
-      <c r="AB20" s="37">
+      <c r="AB20" s="34">
         <v>360</v>
       </c>
-      <c r="AC20" s="37">
+      <c r="AC20" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37004,28 +37025,28 @@
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="V21" s="37">
+      <c r="V21" s="34">
         <v>5695</v>
       </c>
-      <c r="W21" s="37">
+      <c r="W21" s="34">
         <v>7647</v>
       </c>
-      <c r="X21" s="37">
+      <c r="X21" s="34">
         <v>9209</v>
       </c>
-      <c r="Y21" s="37">
+      <c r="Y21" s="34">
         <v>10791</v>
       </c>
-      <c r="Z21" s="37">
+      <c r="Z21" s="34">
         <v>1269</v>
       </c>
-      <c r="AA21" s="37">
+      <c r="AA21" s="34">
         <v>3627</v>
       </c>
-      <c r="AB21" s="37">
+      <c r="AB21" s="34">
         <v>360</v>
       </c>
-      <c r="AC21" s="37">
+      <c r="AC21" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37100,28 +37121,28 @@
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="V22" s="37">
+      <c r="V22" s="34">
         <v>5695</v>
       </c>
-      <c r="W22" s="37">
+      <c r="W22" s="34">
         <v>7647</v>
       </c>
-      <c r="X22" s="37">
+      <c r="X22" s="34">
         <v>9209</v>
       </c>
-      <c r="Y22" s="37">
+      <c r="Y22" s="34">
         <v>10791</v>
       </c>
-      <c r="Z22" s="37">
+      <c r="Z22" s="34">
         <v>1269</v>
       </c>
-      <c r="AA22" s="37">
+      <c r="AA22" s="34">
         <v>3627</v>
       </c>
-      <c r="AB22" s="37">
+      <c r="AB22" s="34">
         <v>360</v>
       </c>
-      <c r="AC22" s="37">
+      <c r="AC22" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37196,28 +37217,28 @@
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="V23" s="37">
+      <c r="V23" s="34">
         <v>5695</v>
       </c>
-      <c r="W23" s="37">
+      <c r="W23" s="34">
         <v>7647</v>
       </c>
-      <c r="X23" s="37">
+      <c r="X23" s="34">
         <v>9209</v>
       </c>
-      <c r="Y23" s="37">
+      <c r="Y23" s="34">
         <v>10791</v>
       </c>
-      <c r="Z23" s="37">
+      <c r="Z23" s="34">
         <v>1269</v>
       </c>
-      <c r="AA23" s="37">
+      <c r="AA23" s="34">
         <v>3627</v>
       </c>
-      <c r="AB23" s="37">
+      <c r="AB23" s="34">
         <v>360</v>
       </c>
-      <c r="AC23" s="37">
+      <c r="AC23" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37292,28 +37313,28 @@
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="V24" s="37">
+      <c r="V24" s="34">
         <v>5695</v>
       </c>
-      <c r="W24" s="37">
+      <c r="W24" s="34">
         <v>7647</v>
       </c>
-      <c r="X24" s="37">
+      <c r="X24" s="34">
         <v>9209</v>
       </c>
-      <c r="Y24" s="37">
+      <c r="Y24" s="34">
         <v>10791</v>
       </c>
-      <c r="Z24" s="37">
+      <c r="Z24" s="34">
         <v>1269</v>
       </c>
-      <c r="AA24" s="37">
+      <c r="AA24" s="34">
         <v>3627</v>
       </c>
-      <c r="AB24" s="37">
+      <c r="AB24" s="34">
         <v>360</v>
       </c>
-      <c r="AC24" s="37">
+      <c r="AC24" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37388,28 +37409,28 @@
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="V25" s="37">
+      <c r="V25" s="34">
         <v>5695</v>
       </c>
-      <c r="W25" s="37">
+      <c r="W25" s="34">
         <v>7647</v>
       </c>
-      <c r="X25" s="37">
+      <c r="X25" s="34">
         <v>9209</v>
       </c>
-      <c r="Y25" s="37">
+      <c r="Y25" s="34">
         <v>10791</v>
       </c>
-      <c r="Z25" s="37">
+      <c r="Z25" s="34">
         <v>1269</v>
       </c>
-      <c r="AA25" s="37">
+      <c r="AA25" s="34">
         <v>3627</v>
       </c>
-      <c r="AB25" s="37">
+      <c r="AB25" s="34">
         <v>360</v>
       </c>
-      <c r="AC25" s="37">
+      <c r="AC25" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37480,32 +37501,32 @@
         <v>0</v>
       </c>
       <c r="T26" s="4"/>
-      <c r="U26" s="38">
+      <c r="U26" s="35">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="V26" s="37">
+      <c r="V26" s="34">
         <v>5695</v>
       </c>
-      <c r="W26" s="37">
+      <c r="W26" s="34">
         <v>7647</v>
       </c>
-      <c r="X26" s="37">
+      <c r="X26" s="34">
         <v>9209</v>
       </c>
-      <c r="Y26" s="37">
+      <c r="Y26" s="34">
         <v>10791</v>
       </c>
-      <c r="Z26" s="37">
+      <c r="Z26" s="34">
         <v>1269</v>
       </c>
-      <c r="AA26" s="37">
+      <c r="AA26" s="34">
         <v>3627</v>
       </c>
-      <c r="AB26" s="37">
+      <c r="AB26" s="34">
         <v>360</v>
       </c>
-      <c r="AC26" s="37">
+      <c r="AC26" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37580,28 +37601,28 @@
         <f t="shared" si="8"/>
         <v>25</v>
       </c>
-      <c r="V27" s="37">
+      <c r="V27" s="34">
         <v>5695</v>
       </c>
-      <c r="W27" s="37">
+      <c r="W27" s="34">
         <v>7647</v>
       </c>
-      <c r="X27" s="37">
+      <c r="X27" s="34">
         <v>9209</v>
       </c>
-      <c r="Y27" s="37">
+      <c r="Y27" s="34">
         <v>10791</v>
       </c>
-      <c r="Z27" s="37">
+      <c r="Z27" s="34">
         <v>1269</v>
       </c>
-      <c r="AA27" s="37">
+      <c r="AA27" s="34">
         <v>3627</v>
       </c>
-      <c r="AB27" s="37">
+      <c r="AB27" s="34">
         <v>360</v>
       </c>
-      <c r="AC27" s="37">
+      <c r="AC27" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37676,28 +37697,28 @@
         <f t="shared" si="8"/>
         <v>26</v>
       </c>
-      <c r="V28" s="37">
+      <c r="V28" s="34">
         <v>5695</v>
       </c>
-      <c r="W28" s="37">
+      <c r="W28" s="34">
         <v>7647</v>
       </c>
-      <c r="X28" s="37">
+      <c r="X28" s="34">
         <v>9209</v>
       </c>
-      <c r="Y28" s="37">
+      <c r="Y28" s="34">
         <v>10791</v>
       </c>
-      <c r="Z28" s="37">
+      <c r="Z28" s="34">
         <v>1269</v>
       </c>
-      <c r="AA28" s="37">
+      <c r="AA28" s="34">
         <v>3627</v>
       </c>
-      <c r="AB28" s="37">
+      <c r="AB28" s="34">
         <v>360</v>
       </c>
-      <c r="AC28" s="37">
+      <c r="AC28" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37772,28 +37793,28 @@
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
-      <c r="V29" s="37">
+      <c r="V29" s="34">
         <v>5695</v>
       </c>
-      <c r="W29" s="37">
+      <c r="W29" s="34">
         <v>7647</v>
       </c>
-      <c r="X29" s="37">
+      <c r="X29" s="34">
         <v>9209</v>
       </c>
-      <c r="Y29" s="37">
+      <c r="Y29" s="34">
         <v>10791</v>
       </c>
-      <c r="Z29" s="37">
+      <c r="Z29" s="34">
         <v>1269</v>
       </c>
-      <c r="AA29" s="37">
+      <c r="AA29" s="34">
         <v>3627</v>
       </c>
-      <c r="AB29" s="37">
+      <c r="AB29" s="34">
         <v>360</v>
       </c>
-      <c r="AC29" s="37">
+      <c r="AC29" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37868,28 +37889,28 @@
         <f t="shared" si="8"/>
         <v>28</v>
       </c>
-      <c r="V30" s="37">
+      <c r="V30" s="34">
         <v>5695</v>
       </c>
-      <c r="W30" s="37">
+      <c r="W30" s="34">
         <v>7647</v>
       </c>
-      <c r="X30" s="37">
+      <c r="X30" s="34">
         <v>9209</v>
       </c>
-      <c r="Y30" s="37">
+      <c r="Y30" s="34">
         <v>10791</v>
       </c>
-      <c r="Z30" s="37">
+      <c r="Z30" s="34">
         <v>1269</v>
       </c>
-      <c r="AA30" s="37">
+      <c r="AA30" s="34">
         <v>3627</v>
       </c>
-      <c r="AB30" s="37">
+      <c r="AB30" s="34">
         <v>360</v>
       </c>
-      <c r="AC30" s="37">
+      <c r="AC30" s="34">
         <v>3266</v>
       </c>
     </row>
@@ -37964,28 +37985,28 @@
         <f t="shared" si="8"/>
         <v>29</v>
       </c>
-      <c r="V31" s="37">
+      <c r="V31" s="34">
         <v>6351</v>
       </c>
-      <c r="W31" s="37">
+      <c r="W31" s="34">
         <v>8113</v>
       </c>
-      <c r="X31" s="37">
+      <c r="X31" s="34">
         <v>9260</v>
       </c>
-      <c r="Y31" s="37">
+      <c r="Y31" s="34">
         <v>11801</v>
       </c>
-      <c r="Z31" s="37">
+      <c r="Z31" s="34">
         <v>1270</v>
       </c>
-      <c r="AA31" s="37">
+      <c r="AA31" s="34">
         <v>3684</v>
       </c>
-      <c r="AB31" s="37">
+      <c r="AB31" s="34">
         <v>367</v>
       </c>
-      <c r="AC31" s="37">
+      <c r="AC31" s="34">
         <v>3316</v>
       </c>
     </row>
@@ -38060,28 +38081,28 @@
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-      <c r="V32" s="37">
+      <c r="V32" s="34">
         <v>6375</v>
       </c>
-      <c r="W32" s="37">
+      <c r="W32" s="34">
         <v>8136</v>
       </c>
-      <c r="X32" s="37">
+      <c r="X32" s="34">
         <v>9263</v>
       </c>
-      <c r="Y32" s="37">
+      <c r="Y32" s="34">
         <v>11802</v>
       </c>
-      <c r="Z32" s="37">
+      <c r="Z32" s="34">
         <v>1270</v>
       </c>
-      <c r="AA32" s="37">
+      <c r="AA32" s="34">
         <v>3687</v>
       </c>
-      <c r="AB32" s="37">
+      <c r="AB32" s="34">
         <v>368</v>
       </c>
-      <c r="AC32" s="37">
+      <c r="AC32" s="34">
         <v>3318</v>
       </c>
     </row>
@@ -38091,42 +38112,42 @@
         <f t="shared" si="8"/>
         <v>31</v>
       </c>
-      <c r="V33" s="37">
+      <c r="V33" s="34">
         <v>6375</v>
       </c>
-      <c r="W33" s="37">
+      <c r="W33" s="34">
         <v>8136</v>
       </c>
-      <c r="X33" s="37">
+      <c r="X33" s="34">
         <v>9263</v>
       </c>
-      <c r="Y33" s="37">
+      <c r="Y33" s="34">
         <v>11802</v>
       </c>
-      <c r="Z33" s="37">
+      <c r="Z33" s="34">
         <v>1270</v>
       </c>
-      <c r="AA33" s="37">
+      <c r="AA33" s="34">
         <v>3687</v>
       </c>
-      <c r="AB33" s="37">
+      <c r="AB33" s="34">
         <v>368</v>
       </c>
-      <c r="AC33" s="37">
+      <c r="AC33" s="34">
         <v>3318</v>
       </c>
     </row>
     <row r="34" spans="1:29" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -38504,15 +38525,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="34"/>
-      <c r="B71" s="34"/>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-      <c r="H71" s="34"/>
-      <c r="I71" s="34"/>
+      <c r="A71" s="38"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -38537,15 +38558,15 @@
       <c r="I73" s="21"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="35"/>
-      <c r="B76" s="35"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="A76" s="39"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39"/>
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -38581,15 +38602,15 @@
       <c r="I79" s="23"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="36"/>
-      <c r="B80" s="36"/>
-      <c r="C80" s="36"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="36"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
+      <c r="A80" s="40"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40"/>
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -38625,15 +38646,15 @@
       <c r="B86" s="21"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="35"/>
-      <c r="B88" s="35"/>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
+      <c r="A88" s="39"/>
+      <c r="B88" s="39"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="39"/>
+      <c r="G88" s="39"/>
+      <c r="H88" s="39"/>
+      <c r="I88" s="39"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -38736,15 +38757,15 @@
       <c r="B99" s="24"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="34"/>
-      <c r="B101" s="34"/>
-      <c r="C101" s="34"/>
-      <c r="D101" s="34"/>
-      <c r="E101" s="34"/>
-      <c r="F101" s="34"/>
-      <c r="G101" s="34"/>
-      <c r="H101" s="34"/>
-      <c r="I101" s="34"/>
+      <c r="A101" s="38"/>
+      <c r="B101" s="38"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="38"/>
+      <c r="F101" s="38"/>
+      <c r="G101" s="38"/>
+      <c r="H101" s="38"/>
+      <c r="I101" s="38"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -38990,28 +39011,28 @@
       <c r="U2" s="7">
         <v>0</v>
       </c>
-      <c r="V2" s="39">
+      <c r="V2" s="36">
         <v>2812</v>
       </c>
-      <c r="W2" s="39">
+      <c r="W2" s="36">
         <v>4489</v>
       </c>
-      <c r="X2" s="39">
+      <c r="X2" s="36">
         <v>9036</v>
       </c>
-      <c r="Y2" s="39">
+      <c r="Y2" s="36">
         <v>10758</v>
       </c>
-      <c r="Z2" s="39">
+      <c r="Z2" s="36">
         <v>1260</v>
       </c>
-      <c r="AA2" s="39">
+      <c r="AA2" s="36">
         <v>3408</v>
       </c>
-      <c r="AB2" s="39">
+      <c r="AB2" s="36">
         <v>338</v>
       </c>
-      <c r="AC2" s="39">
+      <c r="AC2" s="36">
         <v>3069</v>
       </c>
       <c r="AE2" s="9" t="s">
@@ -39092,28 +39113,28 @@
       <c r="U3" s="5">
         <v>1</v>
       </c>
-      <c r="V3" s="37">
+      <c r="V3" s="34">
         <v>2930</v>
       </c>
-      <c r="W3" s="37">
+      <c r="W3" s="34">
         <v>4611</v>
       </c>
-      <c r="X3" s="37">
+      <c r="X3" s="34">
         <v>9038</v>
       </c>
-      <c r="Y3" s="37">
+      <c r="Y3" s="34">
         <v>10758</v>
       </c>
-      <c r="Z3" s="37">
+      <c r="Z3" s="34">
         <v>1260</v>
       </c>
-      <c r="AA3" s="37">
+      <c r="AA3" s="34">
         <v>3413</v>
       </c>
-      <c r="AB3" s="37">
+      <c r="AB3" s="34">
         <v>339</v>
       </c>
-      <c r="AC3" s="37">
+      <c r="AC3" s="34">
         <v>3073</v>
       </c>
     </row>
@@ -39188,28 +39209,28 @@
         <f t="shared" ref="U4:U32" si="8">U3+1</f>
         <v>2</v>
       </c>
-      <c r="V4" s="37">
+      <c r="V4" s="34">
         <v>3025</v>
       </c>
-      <c r="W4" s="37">
+      <c r="W4" s="34">
         <v>4736</v>
       </c>
-      <c r="X4" s="37">
+      <c r="X4" s="34">
         <v>9043</v>
       </c>
-      <c r="Y4" s="37">
+      <c r="Y4" s="34">
         <v>10760</v>
       </c>
-      <c r="Z4" s="37">
+      <c r="Z4" s="34">
         <v>1261</v>
       </c>
-      <c r="AA4" s="37">
+      <c r="AA4" s="34">
         <v>3419</v>
       </c>
-      <c r="AB4" s="37">
+      <c r="AB4" s="34">
         <v>340</v>
       </c>
-      <c r="AC4" s="37">
+      <c r="AC4" s="34">
         <v>3079</v>
       </c>
     </row>
@@ -39284,28 +39305,28 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="V5" s="37">
+      <c r="V5" s="34">
         <v>3146</v>
       </c>
-      <c r="W5" s="37">
+      <c r="W5" s="34">
         <v>4811</v>
       </c>
-      <c r="X5" s="37">
+      <c r="X5" s="34">
         <v>9043</v>
       </c>
-      <c r="Y5" s="37">
+      <c r="Y5" s="34">
         <v>10761</v>
       </c>
-      <c r="Z5" s="37">
+      <c r="Z5" s="34">
         <v>1261</v>
       </c>
-      <c r="AA5" s="37">
+      <c r="AA5" s="34">
         <v>3424</v>
       </c>
-      <c r="AB5" s="37">
+      <c r="AB5" s="34">
         <v>341</v>
       </c>
-      <c r="AC5" s="37">
+      <c r="AC5" s="34">
         <v>3083</v>
       </c>
     </row>
@@ -39380,28 +39401,28 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="V6" s="37">
+      <c r="V6" s="34">
         <v>3240</v>
       </c>
-      <c r="W6" s="37">
+      <c r="W6" s="34">
         <v>4914</v>
       </c>
-      <c r="X6" s="37">
+      <c r="X6" s="34">
         <v>9048</v>
       </c>
-      <c r="Y6" s="37">
+      <c r="Y6" s="34">
         <v>10762</v>
       </c>
-      <c r="Z6" s="37">
+      <c r="Z6" s="34">
         <v>1261</v>
       </c>
-      <c r="AA6" s="37">
+      <c r="AA6" s="34">
         <v>3429</v>
       </c>
-      <c r="AB6" s="37">
+      <c r="AB6" s="34">
         <v>341</v>
       </c>
-      <c r="AC6" s="37">
+      <c r="AC6" s="34">
         <v>3088</v>
       </c>
     </row>
@@ -39476,28 +39497,28 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="V7" s="37">
+      <c r="V7" s="34">
         <v>3301</v>
       </c>
-      <c r="W7" s="37">
+      <c r="W7" s="34">
         <v>4990</v>
       </c>
-      <c r="X7" s="37">
+      <c r="X7" s="34">
         <v>9053</v>
       </c>
-      <c r="Y7" s="37">
+      <c r="Y7" s="34">
         <v>10763</v>
       </c>
-      <c r="Z7" s="37">
+      <c r="Z7" s="34">
         <v>1261</v>
       </c>
-      <c r="AA7" s="37">
+      <c r="AA7" s="34">
         <v>3435</v>
       </c>
-      <c r="AB7" s="37">
+      <c r="AB7" s="34">
         <v>342</v>
       </c>
-      <c r="AC7" s="37">
+      <c r="AC7" s="34">
         <v>3092</v>
       </c>
     </row>
@@ -39572,28 +39593,28 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="V8" s="37">
+      <c r="V8" s="34">
         <v>3332</v>
       </c>
-      <c r="W8" s="37">
+      <c r="W8" s="34">
         <v>5122</v>
       </c>
-      <c r="X8" s="37">
+      <c r="X8" s="34">
         <v>9056</v>
       </c>
-      <c r="Y8" s="37">
+      <c r="Y8" s="34">
         <v>10763</v>
       </c>
-      <c r="Z8" s="37">
+      <c r="Z8" s="34">
         <v>1261</v>
       </c>
-      <c r="AA8" s="37">
+      <c r="AA8" s="34">
         <v>3437</v>
       </c>
-      <c r="AB8" s="37">
+      <c r="AB8" s="34">
         <v>342</v>
       </c>
-      <c r="AC8" s="37">
+      <c r="AC8" s="34">
         <v>3094</v>
       </c>
     </row>
@@ -39668,28 +39689,28 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="V9" s="37">
+      <c r="V9" s="34">
         <v>3369</v>
       </c>
-      <c r="W9" s="37">
+      <c r="W9" s="34">
         <v>5122</v>
       </c>
-      <c r="X9" s="37">
+      <c r="X9" s="34">
         <v>9059</v>
       </c>
-      <c r="Y9" s="37">
+      <c r="Y9" s="34">
         <v>10764</v>
       </c>
-      <c r="Z9" s="37">
+      <c r="Z9" s="34">
         <v>1262</v>
       </c>
-      <c r="AA9" s="37">
+      <c r="AA9" s="34">
         <v>3445</v>
       </c>
-      <c r="AB9" s="37">
+      <c r="AB9" s="34">
         <v>342</v>
       </c>
-      <c r="AC9" s="37">
+      <c r="AC9" s="34">
         <v>3102</v>
       </c>
     </row>
@@ -39764,28 +39785,28 @@
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="V10" s="37">
+      <c r="V10" s="34">
         <v>3461</v>
       </c>
-      <c r="W10" s="37">
+      <c r="W10" s="34">
         <v>5204</v>
       </c>
-      <c r="X10" s="37">
+      <c r="X10" s="34">
         <v>9059</v>
       </c>
-      <c r="Y10" s="37">
+      <c r="Y10" s="34">
         <v>10765</v>
       </c>
-      <c r="Z10" s="37">
+      <c r="Z10" s="34">
         <v>1262</v>
       </c>
-      <c r="AA10" s="37">
+      <c r="AA10" s="34">
         <v>3447</v>
       </c>
-      <c r="AB10" s="37">
+      <c r="AB10" s="34">
         <v>343</v>
       </c>
-      <c r="AC10" s="37">
+      <c r="AC10" s="34">
         <v>3104</v>
       </c>
     </row>
@@ -39860,28 +39881,28 @@
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="V11" s="37">
+      <c r="V11" s="34">
         <v>3541</v>
       </c>
-      <c r="W11" s="37">
+      <c r="W11" s="34">
         <v>5240</v>
       </c>
-      <c r="X11" s="37">
+      <c r="X11" s="34">
         <v>9059</v>
       </c>
-      <c r="Y11" s="37">
+      <c r="Y11" s="34">
         <v>10765</v>
       </c>
-      <c r="Z11" s="37">
+      <c r="Z11" s="34">
         <v>1262</v>
       </c>
-      <c r="AA11" s="37">
+      <c r="AA11" s="34">
         <v>3454</v>
       </c>
-      <c r="AB11" s="37">
+      <c r="AB11" s="34">
         <v>344</v>
       </c>
-      <c r="AC11" s="37">
+      <c r="AC11" s="34">
         <v>3110</v>
       </c>
     </row>
@@ -39956,28 +39977,28 @@
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="V12" s="37">
+      <c r="V12" s="34">
         <v>3647</v>
       </c>
-      <c r="W12" s="37">
+      <c r="W12" s="34">
         <v>5316</v>
       </c>
-      <c r="X12" s="37">
+      <c r="X12" s="34">
         <v>9059</v>
       </c>
-      <c r="Y12" s="37">
+      <c r="Y12" s="34">
         <v>10765</v>
       </c>
-      <c r="Z12" s="37">
+      <c r="Z12" s="34">
         <v>1262</v>
       </c>
-      <c r="AA12" s="37">
+      <c r="AA12" s="34">
         <v>3459</v>
       </c>
-      <c r="AB12" s="37">
+      <c r="AB12" s="34">
         <v>344</v>
       </c>
-      <c r="AC12" s="37">
+      <c r="AC12" s="34">
         <v>3114</v>
       </c>
     </row>
@@ -40052,28 +40073,28 @@
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="V13" s="37">
+      <c r="V13" s="34">
         <v>3717</v>
       </c>
-      <c r="W13" s="37">
+      <c r="W13" s="34">
         <v>5332</v>
       </c>
-      <c r="X13" s="37">
+      <c r="X13" s="34">
         <v>9072</v>
       </c>
-      <c r="Y13" s="37">
+      <c r="Y13" s="34">
         <v>10765</v>
       </c>
-      <c r="Z13" s="37">
+      <c r="Z13" s="34">
         <v>1262</v>
       </c>
-      <c r="AA13" s="37">
+      <c r="AA13" s="34">
         <v>3464</v>
       </c>
-      <c r="AB13" s="37">
+      <c r="AB13" s="34">
         <v>345</v>
       </c>
-      <c r="AC13" s="37">
+      <c r="AC13" s="34">
         <v>3118</v>
       </c>
     </row>
@@ -40148,28 +40169,28 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="V14" s="37">
+      <c r="V14" s="34">
         <v>3819</v>
       </c>
-      <c r="W14" s="37">
+      <c r="W14" s="34">
         <v>5471</v>
       </c>
-      <c r="X14" s="37">
+      <c r="X14" s="34">
         <v>9076</v>
       </c>
-      <c r="Y14" s="37">
+      <c r="Y14" s="34">
         <v>10767</v>
       </c>
-      <c r="Z14" s="37">
+      <c r="Z14" s="34">
         <v>1263</v>
       </c>
-      <c r="AA14" s="37">
+      <c r="AA14" s="34">
         <v>3469</v>
       </c>
-      <c r="AB14" s="37">
+      <c r="AB14" s="34">
         <v>346</v>
       </c>
-      <c r="AC14" s="37">
+      <c r="AC14" s="34">
         <v>3122</v>
       </c>
     </row>
@@ -40243,28 +40264,28 @@
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="V15" s="37">
+      <c r="V15" s="34">
         <v>3835</v>
       </c>
-      <c r="W15" s="37">
+      <c r="W15" s="34">
         <v>5538</v>
       </c>
-      <c r="X15" s="37">
+      <c r="X15" s="34">
         <v>9081</v>
       </c>
-      <c r="Y15" s="37">
+      <c r="Y15" s="34">
         <v>10768</v>
       </c>
-      <c r="Z15" s="37">
+      <c r="Z15" s="34">
         <v>1263</v>
       </c>
-      <c r="AA15" s="37">
+      <c r="AA15" s="34">
         <v>3472</v>
       </c>
-      <c r="AB15" s="37">
+      <c r="AB15" s="34">
         <v>346</v>
       </c>
-      <c r="AC15" s="37">
+      <c r="AC15" s="34">
         <v>3135</v>
       </c>
     </row>
@@ -40339,28 +40360,28 @@
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="V16" s="37">
+      <c r="V16" s="34">
         <v>3879</v>
       </c>
-      <c r="W16" s="37">
+      <c r="W16" s="34">
         <v>5598</v>
       </c>
-      <c r="X16" s="37">
+      <c r="X16" s="34">
         <v>9085</v>
       </c>
-      <c r="Y16" s="37">
+      <c r="Y16" s="34">
         <v>10769</v>
       </c>
-      <c r="Z16" s="37">
+      <c r="Z16" s="34">
         <v>1263</v>
       </c>
-      <c r="AA16" s="37">
+      <c r="AA16" s="34">
         <v>3480</v>
       </c>
-      <c r="AB16" s="37">
+      <c r="AB16" s="34">
         <v>346</v>
       </c>
-      <c r="AC16" s="37">
+      <c r="AC16" s="34">
         <v>3135</v>
       </c>
     </row>
@@ -40435,28 +40456,28 @@
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="V17" s="37">
+      <c r="V17" s="34">
         <v>3959</v>
       </c>
-      <c r="W17" s="37">
+      <c r="W17" s="34">
         <v>5660</v>
       </c>
-      <c r="X17" s="37">
+      <c r="X17" s="34">
         <v>9090</v>
       </c>
-      <c r="Y17" s="37">
+      <c r="Y17" s="34">
         <v>10770</v>
       </c>
-      <c r="Z17" s="37">
+      <c r="Z17" s="34">
         <v>1264</v>
       </c>
-      <c r="AA17" s="37">
+      <c r="AA17" s="34">
         <v>3482</v>
       </c>
-      <c r="AB17" s="37">
+      <c r="AB17" s="34">
         <v>347</v>
       </c>
-      <c r="AC17" s="37">
+      <c r="AC17" s="34">
         <v>3135</v>
       </c>
     </row>
@@ -40531,28 +40552,28 @@
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="V18" s="37">
+      <c r="V18" s="34">
         <v>4062</v>
       </c>
-      <c r="W18" s="37">
+      <c r="W18" s="34">
         <v>5699</v>
       </c>
-      <c r="X18" s="37">
+      <c r="X18" s="34">
         <v>9092</v>
       </c>
-      <c r="Y18" s="37">
+      <c r="Y18" s="34">
         <v>10771</v>
       </c>
-      <c r="Z18" s="37">
+      <c r="Z18" s="34">
         <v>1264</v>
       </c>
-      <c r="AA18" s="37">
+      <c r="AA18" s="34">
         <v>3484</v>
       </c>
-      <c r="AB18" s="37">
+      <c r="AB18" s="34">
         <v>350</v>
       </c>
-      <c r="AC18" s="37">
+      <c r="AC18" s="34">
         <v>3141</v>
       </c>
     </row>
@@ -40627,28 +40648,28 @@
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="V19" s="37">
+      <c r="V19" s="34">
         <v>4205</v>
       </c>
-      <c r="W19" s="37">
+      <c r="W19" s="34">
         <v>5881</v>
       </c>
-      <c r="X19" s="37">
+      <c r="X19" s="34">
         <v>9101</v>
       </c>
-      <c r="Y19" s="37">
+      <c r="Y19" s="34">
         <v>10772</v>
       </c>
-      <c r="Z19" s="37">
+      <c r="Z19" s="34">
         <v>1264</v>
       </c>
-      <c r="AA19" s="37">
+      <c r="AA19" s="34">
         <v>3500</v>
       </c>
-      <c r="AB19" s="37">
+      <c r="AB19" s="34">
         <v>350</v>
       </c>
-      <c r="AC19" s="37">
+      <c r="AC19" s="34">
         <v>3151</v>
       </c>
     </row>
@@ -40723,28 +40744,28 @@
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="V20" s="37">
+      <c r="V20" s="34">
         <v>4205</v>
       </c>
-      <c r="W20" s="37">
+      <c r="W20" s="34">
         <v>5881</v>
       </c>
-      <c r="X20" s="37">
+      <c r="X20" s="34">
         <v>9101</v>
       </c>
-      <c r="Y20" s="37">
+      <c r="Y20" s="34">
         <v>10772</v>
       </c>
-      <c r="Z20" s="37">
+      <c r="Z20" s="34">
         <v>1264</v>
       </c>
-      <c r="AA20" s="37">
+      <c r="AA20" s="34">
         <v>3500</v>
       </c>
-      <c r="AB20" s="37">
+      <c r="AB20" s="34">
         <v>350</v>
       </c>
-      <c r="AC20" s="37">
+      <c r="AC20" s="34">
         <v>3151</v>
       </c>
     </row>
@@ -40819,28 +40840,28 @@
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="V21" s="37">
+      <c r="V21" s="34">
         <v>4216</v>
       </c>
-      <c r="W21" s="37">
+      <c r="W21" s="34">
         <v>5931</v>
       </c>
-      <c r="X21" s="37">
+      <c r="X21" s="34">
         <v>9103</v>
       </c>
-      <c r="Y21" s="37">
+      <c r="Y21" s="34">
         <v>10772</v>
       </c>
-      <c r="Z21" s="37">
+      <c r="Z21" s="34">
         <v>1264</v>
       </c>
-      <c r="AA21" s="37">
+      <c r="AA21" s="34">
         <v>3516</v>
       </c>
-      <c r="AB21" s="37">
+      <c r="AB21" s="34">
         <v>350</v>
       </c>
-      <c r="AC21" s="37">
+      <c r="AC21" s="34">
         <v>3169</v>
       </c>
     </row>
@@ -40915,28 +40936,28 @@
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="V22" s="37">
+      <c r="V22" s="34">
         <v>4216</v>
       </c>
-      <c r="W22" s="37">
+      <c r="W22" s="34">
         <v>5931</v>
       </c>
-      <c r="X22" s="37">
+      <c r="X22" s="34">
         <v>9103</v>
       </c>
-      <c r="Y22" s="37">
+      <c r="Y22" s="34">
         <v>10772</v>
       </c>
-      <c r="Z22" s="37">
+      <c r="Z22" s="34">
         <v>1264</v>
       </c>
-      <c r="AA22" s="37">
+      <c r="AA22" s="34">
         <v>3516</v>
       </c>
-      <c r="AB22" s="37">
+      <c r="AB22" s="34">
         <v>350</v>
       </c>
-      <c r="AC22" s="37">
+      <c r="AC22" s="34">
         <v>3169</v>
       </c>
     </row>
@@ -41011,28 +41032,28 @@
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="V23" s="37">
+      <c r="V23" s="34">
         <v>4276</v>
       </c>
-      <c r="W23" s="37">
+      <c r="W23" s="34">
         <v>6079</v>
       </c>
-      <c r="X23" s="37">
+      <c r="X23" s="34">
         <v>9112</v>
       </c>
-      <c r="Y23" s="37">
+      <c r="Y23" s="34">
         <v>10774</v>
       </c>
-      <c r="Z23" s="37">
+      <c r="Z23" s="34">
         <v>1265</v>
       </c>
-      <c r="AA23" s="37">
+      <c r="AA23" s="34">
         <v>3516</v>
       </c>
-      <c r="AB23" s="37">
+      <c r="AB23" s="34">
         <v>350</v>
       </c>
-      <c r="AC23" s="37">
+      <c r="AC23" s="34">
         <v>3169</v>
       </c>
     </row>
@@ -41107,28 +41128,28 @@
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="V24" s="37">
+      <c r="V24" s="34">
         <v>4310</v>
       </c>
-      <c r="W24" s="37">
+      <c r="W24" s="34">
         <v>6226</v>
       </c>
-      <c r="X24" s="37">
+      <c r="X24" s="34">
         <v>9114</v>
       </c>
-      <c r="Y24" s="37">
+      <c r="Y24" s="34">
         <v>10774</v>
       </c>
-      <c r="Z24" s="37">
+      <c r="Z24" s="34">
         <v>1265</v>
       </c>
-      <c r="AA24" s="37">
+      <c r="AA24" s="34">
         <v>3521</v>
       </c>
-      <c r="AB24" s="37">
+      <c r="AB24" s="34">
         <v>350</v>
       </c>
-      <c r="AC24" s="37">
+      <c r="AC24" s="34">
         <v>3171</v>
       </c>
     </row>
@@ -41203,28 +41224,28 @@
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="V25" s="37">
+      <c r="V25" s="34">
         <v>4401</v>
       </c>
-      <c r="W25" s="37">
+      <c r="W25" s="34">
         <v>6242</v>
       </c>
-      <c r="X25" s="37">
+      <c r="X25" s="34">
         <v>9119</v>
       </c>
-      <c r="Y25" s="37">
+      <c r="Y25" s="34">
         <v>10774</v>
       </c>
-      <c r="Z25" s="37">
+      <c r="Z25" s="34">
         <v>1265</v>
       </c>
-      <c r="AA25" s="37">
+      <c r="AA25" s="34">
         <v>3524</v>
       </c>
-      <c r="AB25" s="37">
+      <c r="AB25" s="34">
         <v>350</v>
       </c>
-      <c r="AC25" s="37">
+      <c r="AC25" s="34">
         <v>3179</v>
       </c>
     </row>
@@ -41295,32 +41316,32 @@
         <v>4</v>
       </c>
       <c r="T26" s="4"/>
-      <c r="U26" s="38">
+      <c r="U26" s="35">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="V26" s="37">
+      <c r="V26" s="34">
         <v>4494</v>
       </c>
-      <c r="W26" s="37">
+      <c r="W26" s="34">
         <v>6283</v>
       </c>
-      <c r="X26" s="37">
+      <c r="X26" s="34">
         <v>9121</v>
       </c>
-      <c r="Y26" s="37">
+      <c r="Y26" s="34">
         <v>10776</v>
       </c>
-      <c r="Z26" s="37">
+      <c r="Z26" s="34">
         <v>1265</v>
       </c>
-      <c r="AA26" s="37">
+      <c r="AA26" s="34">
         <v>3532</v>
       </c>
-      <c r="AB26" s="37">
+      <c r="AB26" s="34">
         <v>351</v>
       </c>
-      <c r="AC26" s="37">
+      <c r="AC26" s="34">
         <v>3180</v>
       </c>
     </row>
@@ -41395,28 +41416,28 @@
         <f t="shared" si="8"/>
         <v>25</v>
       </c>
-      <c r="V27" s="37">
+      <c r="V27" s="34">
         <v>4569</v>
       </c>
-      <c r="W27" s="37">
+      <c r="W27" s="34">
         <v>6389</v>
       </c>
-      <c r="X27" s="37">
+      <c r="X27" s="34">
         <v>9128</v>
       </c>
-      <c r="Y27" s="37">
+      <c r="Y27" s="34">
         <v>10776</v>
       </c>
-      <c r="Z27" s="37">
+      <c r="Z27" s="34">
         <v>1265</v>
       </c>
-      <c r="AA27" s="37">
+      <c r="AA27" s="34">
         <v>3536</v>
       </c>
-      <c r="AB27" s="37">
+      <c r="AB27" s="34">
         <v>352</v>
       </c>
-      <c r="AC27" s="37">
+      <c r="AC27" s="34">
         <v>3184</v>
       </c>
     </row>
@@ -41491,28 +41512,28 @@
         <f t="shared" si="8"/>
         <v>26</v>
       </c>
-      <c r="V28" s="37">
+      <c r="V28" s="34">
         <v>4603</v>
       </c>
-      <c r="W28" s="37">
+      <c r="W28" s="34">
         <v>6457</v>
       </c>
-      <c r="X28" s="37">
+      <c r="X28" s="34">
         <v>9129</v>
       </c>
-      <c r="Y28" s="37">
+      <c r="Y28" s="34">
         <v>10777</v>
       </c>
-      <c r="Z28" s="37">
+      <c r="Z28" s="34">
         <v>1265</v>
       </c>
-      <c r="AA28" s="37">
+      <c r="AA28" s="34">
         <v>3540</v>
       </c>
-      <c r="AB28" s="37">
+      <c r="AB28" s="34">
         <v>352</v>
       </c>
-      <c r="AC28" s="37">
+      <c r="AC28" s="34">
         <v>3188</v>
       </c>
     </row>
@@ -41587,28 +41608,28 @@
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
-      <c r="V29" s="37">
+      <c r="V29" s="34">
         <v>4660</v>
       </c>
-      <c r="W29" s="37">
+      <c r="W29" s="34">
         <v>6551</v>
       </c>
-      <c r="X29" s="37">
+      <c r="X29" s="34">
         <v>9133</v>
       </c>
-      <c r="Y29" s="37">
+      <c r="Y29" s="34">
         <v>10778</v>
       </c>
-      <c r="Z29" s="37">
+      <c r="Z29" s="34">
         <v>1266</v>
       </c>
-      <c r="AA29" s="37">
+      <c r="AA29" s="34">
         <v>3540</v>
       </c>
-      <c r="AB29" s="37">
+      <c r="AB29" s="34">
         <v>352</v>
       </c>
-      <c r="AC29" s="37">
+      <c r="AC29" s="34">
         <v>3193</v>
       </c>
     </row>
@@ -41683,28 +41704,28 @@
         <f t="shared" si="8"/>
         <v>28</v>
       </c>
-      <c r="V30" s="37">
+      <c r="V30" s="34">
         <v>4672</v>
       </c>
-      <c r="W30" s="37">
+      <c r="W30" s="34">
         <v>6586</v>
       </c>
-      <c r="X30" s="37">
+      <c r="X30" s="34">
         <v>9138</v>
       </c>
-      <c r="Y30" s="37">
+      <c r="Y30" s="34">
         <v>10779</v>
       </c>
-      <c r="Z30" s="37">
+      <c r="Z30" s="34">
         <v>1266</v>
       </c>
-      <c r="AA30" s="37">
+      <c r="AA30" s="34">
         <v>3548</v>
       </c>
-      <c r="AB30" s="37">
+      <c r="AB30" s="34">
         <v>352</v>
       </c>
-      <c r="AC30" s="37">
+      <c r="AC30" s="34">
         <v>3196</v>
       </c>
     </row>
@@ -41779,28 +41800,28 @@
         <f t="shared" si="8"/>
         <v>29</v>
       </c>
-      <c r="V31" s="37">
+      <c r="V31" s="34">
         <v>4765</v>
       </c>
-      <c r="W31" s="37">
+      <c r="W31" s="34">
         <v>6659</v>
       </c>
-      <c r="X31" s="37">
+      <c r="X31" s="34">
         <v>9140</v>
       </c>
-      <c r="Y31" s="37">
+      <c r="Y31" s="34">
         <v>10780</v>
       </c>
-      <c r="Z31" s="37">
+      <c r="Z31" s="34">
         <v>1266</v>
       </c>
-      <c r="AA31" s="37">
+      <c r="AA31" s="34">
         <v>3556</v>
       </c>
-      <c r="AB31" s="37">
+      <c r="AB31" s="34">
         <v>353</v>
       </c>
-      <c r="AC31" s="37">
+      <c r="AC31" s="34">
         <v>3203</v>
       </c>
     </row>
@@ -41810,28 +41831,28 @@
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-      <c r="V32" s="37">
+      <c r="V32" s="34">
         <v>4765</v>
       </c>
-      <c r="W32" s="37">
+      <c r="W32" s="34">
         <v>6659</v>
       </c>
-      <c r="X32" s="37">
+      <c r="X32" s="34">
         <v>9140</v>
       </c>
-      <c r="Y32" s="37">
+      <c r="Y32" s="34">
         <v>10780</v>
       </c>
-      <c r="Z32" s="37">
+      <c r="Z32" s="34">
         <v>1266</v>
       </c>
-      <c r="AA32" s="37">
+      <c r="AA32" s="34">
         <v>3556</v>
       </c>
-      <c r="AB32" s="37">
+      <c r="AB32" s="34">
         <v>353</v>
       </c>
-      <c r="AC32" s="37">
+      <c r="AC32" s="34">
         <v>3203</v>
       </c>
     </row>
@@ -41916,15 +41937,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="34"/>
-      <c r="B69" s="34"/>
-      <c r="C69" s="34"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="34"/>
-      <c r="G69" s="34"/>
-      <c r="H69" s="34"/>
-      <c r="I69" s="34"/>
+      <c r="A69" s="38"/>
+      <c r="B69" s="38"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="38"/>
+      <c r="G69" s="38"/>
+      <c r="H69" s="38"/>
+      <c r="I69" s="38"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -41949,15 +41970,15 @@
       <c r="I71" s="21"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="35"/>
-      <c r="B74" s="35"/>
-      <c r="C74" s="35"/>
-      <c r="D74" s="35"/>
-      <c r="E74" s="35"/>
-      <c r="F74" s="35"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="35"/>
-      <c r="I74" s="35"/>
+      <c r="A74" s="39"/>
+      <c r="B74" s="39"/>
+      <c r="C74" s="39"/>
+      <c r="D74" s="39"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="39"/>
+      <c r="G74" s="39"/>
+      <c r="H74" s="39"/>
+      <c r="I74" s="39"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -41993,15 +42014,15 @@
       <c r="I77" s="23"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="36"/>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-      <c r="G78" s="36"/>
-      <c r="H78" s="36"/>
-      <c r="I78" s="36"/>
+      <c r="A78" s="40"/>
+      <c r="B78" s="40"/>
+      <c r="C78" s="40"/>
+      <c r="D78" s="40"/>
+      <c r="E78" s="40"/>
+      <c r="F78" s="40"/>
+      <c r="G78" s="40"/>
+      <c r="H78" s="40"/>
+      <c r="I78" s="40"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -42037,15 +42058,15 @@
       <c r="B84" s="21"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="35"/>
-      <c r="B86" s="35"/>
-      <c r="C86" s="35"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="35"/>
-      <c r="F86" s="35"/>
-      <c r="G86" s="35"/>
-      <c r="H86" s="35"/>
-      <c r="I86" s="35"/>
+      <c r="A86" s="39"/>
+      <c r="B86" s="39"/>
+      <c r="C86" s="39"/>
+      <c r="D86" s="39"/>
+      <c r="E86" s="39"/>
+      <c r="F86" s="39"/>
+      <c r="G86" s="39"/>
+      <c r="H86" s="39"/>
+      <c r="I86" s="39"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -42148,15 +42169,15 @@
       <c r="B97" s="24"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="34"/>
-      <c r="B99" s="34"/>
-      <c r="C99" s="34"/>
-      <c r="D99" s="34"/>
-      <c r="E99" s="34"/>
-      <c r="F99" s="34"/>
-      <c r="G99" s="34"/>
-      <c r="H99" s="34"/>
-      <c r="I99" s="34"/>
+      <c r="A99" s="38"/>
+      <c r="B99" s="38"/>
+      <c r="C99" s="38"/>
+      <c r="D99" s="38"/>
+      <c r="E99" s="38"/>
+      <c r="F99" s="38"/>
+      <c r="G99" s="38"/>
+      <c r="H99" s="38"/>
+      <c r="I99" s="38"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E76778F-2A8E-4F44-9CD3-17070D8D40CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49B2D96-1907-454A-A7EE-ED8FC9F78A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -34489,7 +34489,7 @@
         <v>45809</v>
       </c>
       <c r="B2" s="29">
-        <v>1009.5539995399999</v>
+        <v>1003.1699995399999</v>
       </c>
       <c r="C2" s="29">
         <v>183.79199990000001</v>
@@ -34526,15 +34526,14 @@
       <c r="M2" s="13">
         <v>5</v>
       </c>
-      <c r="N2" s="13">
-        <f t="shared" ref="N2:N31" si="2">AA3-AA2</f>
-        <v>7</v>
-      </c>
-      <c r="O2" s="6">
-        <v>0</v>
+      <c r="N2" s="29">
+        <v>276.91199938999995</v>
+      </c>
+      <c r="O2" s="7">
+        <v>58.7279999</v>
       </c>
       <c r="P2" s="13">
-        <f t="shared" ref="P2:P31" si="3">AB3-AB2</f>
+        <f t="shared" ref="P2:P31" si="2">AB3-AB2</f>
         <v>1</v>
       </c>
       <c r="Q2" s="6">
@@ -34544,7 +34543,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="13">
-        <f t="shared" ref="S2:S31" si="4">AC3-AC2</f>
+        <f t="shared" ref="S2:S31" si="3">AC3-AC2</f>
         <v>7</v>
       </c>
       <c r="U2" s="8">
@@ -34587,7 +34586,7 @@
         <v>45810</v>
       </c>
       <c r="B3" s="31">
-        <v>1403.55599957</v>
+        <v>1403.5559995699996</v>
       </c>
       <c r="C3" s="32">
         <v>179.08799991000001</v>
@@ -34624,25 +34623,24 @@
       <c r="M3" s="13">
         <v>5</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="29">
+        <v>218.73599947999992</v>
+      </c>
+      <c r="O3" s="7">
+        <v>50.159999910000003</v>
+      </c>
+      <c r="P3" s="13">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
-      </c>
-      <c r="P3" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>0</v>
+      </c>
+      <c r="R3" s="6">
+        <v>0</v>
+      </c>
+      <c r="S3" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>0</v>
-      </c>
-      <c r="R3" s="6">
-        <v>0</v>
-      </c>
-      <c r="S3" s="13">
-        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="U3" s="12">
@@ -34678,10 +34676,10 @@
         <v>45811</v>
       </c>
       <c r="B4" s="31">
-        <v>1343.3279994500001</v>
+        <v>1343.327999449999</v>
       </c>
       <c r="C4" s="32">
-        <v>184.42199995999999</v>
+        <v>184.42199996000002</v>
       </c>
       <c r="D4" s="29">
         <v>43</v>
@@ -34715,29 +34713,28 @@
       <c r="M4" s="13">
         <v>5</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="29">
+        <v>294.69599936000009</v>
+      </c>
+      <c r="O4" s="7">
+        <v>62.087999889999992</v>
+      </c>
+      <c r="P4" s="13">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0</v>
+      </c>
+      <c r="S4" s="13">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
-      <c r="P4" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6">
-        <v>0</v>
-      </c>
-      <c r="S4" s="13">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
       <c r="U4" s="14">
-        <f t="shared" ref="U4:U32" si="5">U3+1</f>
+        <f t="shared" ref="U4:U32" si="4">U3+1</f>
         <v>2</v>
       </c>
       <c r="V4" s="6">
@@ -34770,10 +34767,10 @@
         <v>45812</v>
       </c>
       <c r="B5" s="31">
-        <v>1366.4279994599999</v>
+        <v>1366.4279994599997</v>
       </c>
       <c r="C5" s="32">
-        <v>209.83199991000001</v>
+        <v>209.83199991000004</v>
       </c>
       <c r="D5" s="29">
         <v>43</v>
@@ -34807,29 +34804,28 @@
       <c r="M5" s="13">
         <v>5</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="29">
+        <v>270.38399930999987</v>
+      </c>
+      <c r="O5" s="7">
+        <v>59.231999910000006</v>
+      </c>
+      <c r="P5" s="13">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6">
+        <v>0</v>
+      </c>
+      <c r="S5" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6">
-        <v>0</v>
-      </c>
-      <c r="S5" s="13">
+        <v>3</v>
+      </c>
+      <c r="U5" s="14">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="U5" s="14">
-        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="V5" s="6">
@@ -34899,29 +34895,28 @@
       <c r="M6" s="13">
         <v>5</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="29">
+        <v>271.94399931000004</v>
+      </c>
+      <c r="O6" s="7">
+        <v>60.383999889999991</v>
+      </c>
+      <c r="P6" s="13">
         <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="13">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6">
-        <v>0</v>
-      </c>
-      <c r="S6" s="13">
+      <c r="U6" s="14">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="U6" s="14">
-        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="V6" s="6">
@@ -34954,10 +34949,10 @@
         <v>45814</v>
       </c>
       <c r="B7" s="31">
-        <v>1233.5819996299999</v>
+        <v>1233.5819996300004</v>
       </c>
       <c r="C7" s="32">
-        <v>181.98599991</v>
+        <v>181.98599990999998</v>
       </c>
       <c r="D7" s="29">
         <v>43</v>
@@ -34991,29 +34986,28 @@
       <c r="M7" s="13">
         <v>5</v>
       </c>
-      <c r="N7" s="13">
+      <c r="N7" s="29">
+        <v>270.07199934000005</v>
+      </c>
+      <c r="O7" s="7">
+        <v>50.903999910000003</v>
+      </c>
+      <c r="P7" s="13">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>0</v>
+      </c>
+      <c r="R7" s="6">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6">
-        <v>0</v>
-      </c>
-      <c r="S7" s="13">
+        <v>3</v>
+      </c>
+      <c r="U7" s="14">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="U7" s="14">
-        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="V7" s="6">
@@ -35046,10 +35040,10 @@
         <v>45815</v>
       </c>
       <c r="B8" s="31">
-        <v>1000.48199957</v>
+        <v>1000.4819995699999</v>
       </c>
       <c r="C8" s="32">
-        <v>171.31799996000001</v>
+        <v>171.31799996000004</v>
       </c>
       <c r="D8" s="29">
         <v>43</v>
@@ -35083,29 +35077,28 @@
       <c r="M8" s="13">
         <v>5</v>
       </c>
-      <c r="N8" s="13">
+      <c r="N8" s="29">
+        <v>307.19999936999983</v>
+      </c>
+      <c r="O8" s="7">
+        <v>58.775999880000015</v>
+      </c>
+      <c r="P8" s="13">
         <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>0</v>
+      </c>
+      <c r="R8" s="6">
+        <v>0</v>
+      </c>
+      <c r="S8" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="13">
+        <v>4</v>
+      </c>
+      <c r="U8" s="14">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="U8" s="14">
-        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="V8" s="6">
@@ -35175,29 +35168,28 @@
       <c r="M9" s="13">
         <v>5</v>
       </c>
-      <c r="N9" s="13">
+      <c r="N9" s="29">
+        <v>298.75199937999969</v>
+      </c>
+      <c r="O9" s="7">
+        <v>51.5999999</v>
+      </c>
+      <c r="P9" s="13">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>0</v>
+      </c>
+      <c r="R9" s="6">
+        <v>0</v>
+      </c>
+      <c r="S9" s="13">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>0</v>
-      </c>
-      <c r="R9" s="6">
-        <v>0</v>
-      </c>
-      <c r="S9" s="13">
+      <c r="U9" s="14">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="U9" s="14">
-        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="V9" s="6">
@@ -35230,10 +35222,10 @@
         <v>45817</v>
       </c>
       <c r="B10" s="33">
-        <v>1438.7099994600001</v>
+        <v>1438.7099994600003</v>
       </c>
       <c r="C10" s="33">
-        <v>200.04599991000001</v>
+        <v>200.04599990999998</v>
       </c>
       <c r="D10" s="29">
         <v>43</v>
@@ -35267,29 +35259,28 @@
       <c r="M10" s="13">
         <v>5</v>
       </c>
-      <c r="N10" s="13">
+      <c r="N10" s="29">
+        <v>284.18399930999988</v>
+      </c>
+      <c r="O10" s="7">
+        <v>61.7279999</v>
+      </c>
+      <c r="P10" s="13">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="O10" s="6">
-        <v>0</v>
-      </c>
-      <c r="P10" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>0</v>
+      </c>
+      <c r="R10" s="6">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>0</v>
-      </c>
-      <c r="R10" s="6">
-        <v>0</v>
-      </c>
-      <c r="S10" s="13">
+        <v>0</v>
+      </c>
+      <c r="U10" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="14">
-        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="V10" s="6">
@@ -35322,10 +35313,10 @@
         <v>45818</v>
       </c>
       <c r="B11" s="33">
-        <v>1480.0799995</v>
+        <v>1480.0799995000002</v>
       </c>
       <c r="C11" s="33">
-        <v>218.48399993000001</v>
+        <v>218.48399992999998</v>
       </c>
       <c r="D11" s="29">
         <v>43</v>
@@ -35359,29 +35350,28 @@
       <c r="M11" s="13">
         <v>5</v>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="29">
+        <v>257.42399933000002</v>
+      </c>
+      <c r="O11" s="7">
+        <v>57.263999889999994</v>
+      </c>
+      <c r="P11" s="13">
         <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="O11" s="6">
-        <v>0</v>
-      </c>
-      <c r="P11" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>0</v>
+      </c>
+      <c r="R11" s="6">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>0</v>
-      </c>
-      <c r="R11" s="6">
-        <v>0</v>
-      </c>
-      <c r="S11" s="13">
+        <v>8</v>
+      </c>
+      <c r="U11" s="14">
         <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="U11" s="14">
-        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="V11" s="6">
@@ -35414,7 +35404,7 @@
         <v>45819</v>
       </c>
       <c r="B12" s="33">
-        <v>1338.1199994599999</v>
+        <v>1338.1199994600001</v>
       </c>
       <c r="C12" s="33">
         <v>196.81199991</v>
@@ -35451,29 +35441,28 @@
       <c r="M12" s="13">
         <v>5</v>
       </c>
-      <c r="N12" s="13">
+      <c r="N12" s="29">
+        <v>234.59999937999976</v>
+      </c>
+      <c r="O12" s="7">
+        <v>53.855999909999987</v>
+      </c>
+      <c r="P12" s="13">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>0</v>
-      </c>
-      <c r="R12" s="6">
-        <v>0</v>
-      </c>
-      <c r="S12" s="13">
+      <c r="U12" s="14">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="U12" s="14">
-        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="V12" s="6">
@@ -35505,11 +35494,11 @@
       <c r="A13" s="5">
         <v>45820</v>
       </c>
-      <c r="B13" s="6">
-        <v>0</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0</v>
+      <c r="B13" s="7">
+        <v>1172.72399954</v>
+      </c>
+      <c r="C13" s="7">
+        <v>182.99399991000001</v>
       </c>
       <c r="D13" s="29">
         <v>43</v>
@@ -35543,29 +35532,28 @@
       <c r="M13" s="13">
         <v>5</v>
       </c>
-      <c r="N13" s="13">
+      <c r="N13" s="29">
+        <v>218.42399931000006</v>
+      </c>
+      <c r="O13" s="7">
+        <v>59.23199988999999</v>
+      </c>
+      <c r="P13" s="13">
         <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="O13" s="6">
-        <v>0</v>
-      </c>
-      <c r="P13" s="13">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>0</v>
-      </c>
-      <c r="R13" s="6">
-        <v>0</v>
-      </c>
-      <c r="S13" s="13">
+      <c r="U13" s="14">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="U13" s="14">
-        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="V13" s="6">
@@ -35597,11 +35585,11 @@
       <c r="A14" s="5">
         <v>45821</v>
       </c>
-      <c r="B14" s="6">
-        <v>0</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0</v>
+      <c r="B14" s="7">
+        <v>1072.5959995599997</v>
+      </c>
+      <c r="C14" s="7">
+        <v>179.17199994999999</v>
       </c>
       <c r="D14" s="29">
         <v>43</v>
@@ -35635,29 +35623,28 @@
       <c r="M14" s="13">
         <v>5</v>
       </c>
-      <c r="N14" s="13">
+      <c r="N14" s="29">
+        <v>236.87999939999992</v>
+      </c>
+      <c r="O14" s="7">
+        <v>49.919999920000002</v>
+      </c>
+      <c r="P14" s="13">
         <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="O14" s="6">
-        <v>0</v>
-      </c>
-      <c r="P14" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>0</v>
+      </c>
+      <c r="R14" s="6">
+        <v>0</v>
+      </c>
+      <c r="S14" s="13">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>0</v>
-      </c>
-      <c r="R14" s="6">
-        <v>0</v>
-      </c>
-      <c r="S14" s="13">
+        <v>7</v>
+      </c>
+      <c r="U14" s="14">
         <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="U14" s="14">
-        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="V14" s="6">
@@ -35689,11 +35676,11 @@
       <c r="A15" s="5">
         <v>45822</v>
       </c>
-      <c r="B15" s="6">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0</v>
+      <c r="B15" s="7">
+        <v>954.02999946999989</v>
+      </c>
+      <c r="C15" s="7">
+        <v>150.77999991000002</v>
       </c>
       <c r="D15" s="29">
         <v>43</v>
@@ -35726,29 +35713,28 @@
       <c r="M15" s="13">
         <v>5</v>
       </c>
-      <c r="N15" s="13">
+      <c r="N15" s="29">
+        <v>249.3839993399998</v>
+      </c>
+      <c r="O15" s="7">
+        <v>56.927999889999995</v>
+      </c>
+      <c r="P15" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O15" s="6">
-        <v>0</v>
-      </c>
-      <c r="P15" s="13">
+      <c r="Q15" s="6">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6">
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="6">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6">
-        <v>0</v>
-      </c>
-      <c r="S15" s="13">
+      <c r="U15" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="14">
-        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="V15" s="6">
@@ -35780,11 +35766,11 @@
       <c r="A16" s="5">
         <v>45823</v>
       </c>
-      <c r="B16" s="6">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0</v>
+      <c r="B16" s="7">
+        <v>836.55599950999988</v>
+      </c>
+      <c r="C16" s="7">
+        <v>164.80799992999997</v>
       </c>
       <c r="D16" s="29">
         <v>43</v>
@@ -35806,7 +35792,7 @@
         <v>38</v>
       </c>
       <c r="J16" s="13">
-        <f t="shared" ref="J16:J31" si="6">Y17-Y16</f>
+        <f t="shared" ref="J16:J31" si="5">Y17-Y16</f>
         <v>1</v>
       </c>
       <c r="K16" s="6">
@@ -35818,29 +35804,28 @@
       <c r="M16" s="13">
         <v>5</v>
       </c>
-      <c r="N16" s="13">
+      <c r="N16" s="29">
+        <v>245.54399935999982</v>
+      </c>
+      <c r="O16" s="7">
+        <v>48.695999909999998</v>
+      </c>
+      <c r="P16" s="13">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6">
+        <v>0</v>
+      </c>
+      <c r="S16" s="13">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="O16" s="6">
-        <v>0</v>
-      </c>
-      <c r="P16" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6">
-        <v>0</v>
-      </c>
-      <c r="S16" s="13">
+      <c r="U16" s="14">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="U16" s="14">
-        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="V16" s="6">
@@ -35873,11 +35858,11 @@
       <c r="A17" s="5">
         <v>45824</v>
       </c>
-      <c r="B17" s="6">
-        <v>0</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0</v>
+      <c r="B17" s="7">
+        <v>1224.4259995499992</v>
+      </c>
+      <c r="C17" s="7">
+        <v>204.11999993999996</v>
       </c>
       <c r="D17" s="29">
         <v>43</v>
@@ -35899,7 +35884,7 @@
         <v>38</v>
       </c>
       <c r="J17" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K17" s="6">
@@ -35911,29 +35896,28 @@
       <c r="M17" s="13">
         <v>5</v>
       </c>
-      <c r="N17" s="13">
+      <c r="N17" s="29">
+        <v>238.60799944999999</v>
+      </c>
+      <c r="O17" s="7">
+        <v>61.103999920000007</v>
+      </c>
+      <c r="P17" s="13">
         <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6">
+        <v>0</v>
+      </c>
+      <c r="S17" s="13">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="O17" s="6">
-        <v>0</v>
-      </c>
-      <c r="P17" s="13">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="Q17" s="6">
-        <v>0</v>
-      </c>
-      <c r="R17" s="6">
-        <v>0</v>
-      </c>
-      <c r="S17" s="13">
+      <c r="U17" s="14">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="U17" s="14">
-        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="V17" s="6">
@@ -35965,11 +35949,11 @@
       <c r="A18" s="5">
         <v>45825</v>
       </c>
-      <c r="B18" s="6">
-        <v>0</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0</v>
+      <c r="B18" s="7">
+        <v>1213.6739995099997</v>
+      </c>
+      <c r="C18" s="7">
+        <v>181.48199990000003</v>
       </c>
       <c r="D18" s="29">
         <v>43</v>
@@ -35991,7 +35975,7 @@
         <v>38</v>
       </c>
       <c r="J18" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="K18" s="6">
@@ -36003,29 +35987,28 @@
       <c r="M18" s="13">
         <v>5</v>
       </c>
-      <c r="N18" s="13">
+      <c r="N18" s="29">
+        <v>280.77599930999969</v>
+      </c>
+      <c r="O18" s="7">
+        <v>58.439999899999997</v>
+      </c>
+      <c r="P18" s="13">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>0</v>
+      </c>
+      <c r="R18" s="6">
+        <v>0</v>
+      </c>
+      <c r="S18" s="13">
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="O18" s="6">
-        <v>0</v>
-      </c>
-      <c r="P18" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6">
-        <v>0</v>
-      </c>
-      <c r="R18" s="6">
-        <v>0</v>
-      </c>
-      <c r="S18" s="13">
+      <c r="U18" s="14">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="U18" s="14">
-        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="V18" s="6">
@@ -36057,11 +36040,11 @@
       <c r="A19" s="5">
         <v>45826</v>
       </c>
-      <c r="B19" s="6">
-        <v>0</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0</v>
+      <c r="B19" s="7">
+        <v>1310.2739995399993</v>
+      </c>
+      <c r="C19" s="7">
+        <v>180.97799992</v>
       </c>
       <c r="D19" s="29">
         <v>43</v>
@@ -36083,7 +36066,7 @@
         <v>38</v>
       </c>
       <c r="J19" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K19" s="6">
@@ -36095,30 +36078,29 @@
       <c r="M19" s="13">
         <v>5</v>
       </c>
-      <c r="N19" s="13">
+      <c r="N19" s="29">
+        <v>266.35199933999979</v>
+      </c>
+      <c r="O19" s="7">
+        <v>61.583999880000007</v>
+      </c>
+      <c r="P19" s="13">
         <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="O19" s="6">
-        <v>0</v>
-      </c>
-      <c r="P19" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6">
+        <v>0</v>
+      </c>
+      <c r="S19" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6">
-        <v>0</v>
-      </c>
-      <c r="S19" s="13">
-        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="T19" s="17"/>
       <c r="U19" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="V19" s="6">
@@ -36150,11 +36132,11 @@
       <c r="A20" s="5">
         <v>45827</v>
       </c>
-      <c r="B20" s="6">
-        <v>0</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0</v>
+      <c r="B20" s="7">
+        <v>911.56799946999968</v>
+      </c>
+      <c r="C20" s="7">
+        <v>168.5039999</v>
       </c>
       <c r="D20" s="29">
         <v>43</v>
@@ -36176,7 +36158,7 @@
         <v>38</v>
       </c>
       <c r="J20" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K20" s="6">
@@ -36188,29 +36170,28 @@
       <c r="M20" s="13">
         <v>5</v>
       </c>
-      <c r="N20" s="13">
+      <c r="N20" s="29">
+        <v>306.4799993999996</v>
+      </c>
+      <c r="O20" s="7">
+        <v>57.959999910000008</v>
+      </c>
+      <c r="P20" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O20" s="6">
-        <v>0</v>
-      </c>
-      <c r="P20" s="13">
+      <c r="Q20" s="6">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6">
+        <v>0</v>
+      </c>
+      <c r="S20" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="6">
-        <v>0</v>
-      </c>
-      <c r="R20" s="6">
-        <v>0</v>
-      </c>
-      <c r="S20" s="13">
+      <c r="U20" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U20" s="14">
-        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="V20" s="6">
@@ -36242,11 +36223,11 @@
       <c r="A21" s="5">
         <v>45828</v>
       </c>
-      <c r="B21" s="6">
-        <v>0</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0</v>
+      <c r="B21" s="7">
+        <v>996.32399944999884</v>
+      </c>
+      <c r="C21" s="7">
+        <v>166.10999993000001</v>
       </c>
       <c r="D21" s="29">
         <v>43</v>
@@ -36268,7 +36249,7 @@
         <v>38</v>
       </c>
       <c r="J21" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K21" s="6">
@@ -36280,29 +36261,28 @@
       <c r="M21" s="13">
         <v>5</v>
       </c>
-      <c r="N21" s="13">
+      <c r="N21" s="29">
+        <v>307.53599938999997</v>
+      </c>
+      <c r="O21" s="7">
+        <v>62.831999879999998</v>
+      </c>
+      <c r="P21" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O21" s="6">
-        <v>0</v>
-      </c>
-      <c r="P21" s="13">
+      <c r="Q21" s="6">
+        <v>0</v>
+      </c>
+      <c r="R21" s="6">
+        <v>0</v>
+      </c>
+      <c r="S21" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="6">
-        <v>0</v>
-      </c>
-      <c r="R21" s="6">
-        <v>0</v>
-      </c>
-      <c r="S21" s="13">
+      <c r="U21" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="14">
-        <f t="shared" si="5"/>
         <v>19</v>
       </c>
       <c r="V21" s="6">
@@ -36334,11 +36314,11 @@
       <c r="A22" s="5">
         <v>45829</v>
       </c>
-      <c r="B22" s="6">
-        <v>0</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0</v>
+      <c r="B22" s="7">
+        <v>1084.3979994999995</v>
+      </c>
+      <c r="C22" s="7">
+        <v>182.44799993000001</v>
       </c>
       <c r="D22" s="29">
         <v>43</v>
@@ -36360,7 +36340,7 @@
         <v>38</v>
       </c>
       <c r="J22" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K22" s="6">
@@ -36372,29 +36352,28 @@
       <c r="M22" s="13">
         <v>5</v>
       </c>
-      <c r="N22" s="13">
+      <c r="N22" s="29">
+        <v>310.70399932999993</v>
+      </c>
+      <c r="O22" s="7">
+        <v>61.223999889999995</v>
+      </c>
+      <c r="P22" s="13">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="O22" s="6">
-        <v>0</v>
-      </c>
-      <c r="P22" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>0</v>
+      </c>
+      <c r="R22" s="6">
+        <v>0</v>
+      </c>
+      <c r="S22" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="6">
-        <v>0</v>
-      </c>
-      <c r="R22" s="6">
-        <v>0</v>
-      </c>
-      <c r="S22" s="13">
+        <v>4</v>
+      </c>
+      <c r="U22" s="14">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="U22" s="14">
-        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="V22" s="6">
@@ -36426,11 +36405,11 @@
       <c r="A23" s="5">
         <v>45830</v>
       </c>
-      <c r="B23" s="6">
-        <v>0</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0</v>
+      <c r="B23" s="7">
+        <v>909.04799958000001</v>
+      </c>
+      <c r="C23" s="7">
+        <v>152.54399995999998</v>
       </c>
       <c r="D23" s="29">
         <v>43</v>
@@ -36452,7 +36431,7 @@
         <v>38</v>
       </c>
       <c r="J23" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K23" s="6">
@@ -36464,29 +36443,28 @@
       <c r="M23" s="13">
         <v>5</v>
       </c>
-      <c r="N23" s="13">
+      <c r="N23" s="29">
+        <v>306.8159992799998</v>
+      </c>
+      <c r="O23" s="7">
+        <v>57.695999899999997</v>
+      </c>
+      <c r="P23" s="13">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>0</v>
+      </c>
+      <c r="R23" s="6">
+        <v>0</v>
+      </c>
+      <c r="S23" s="13">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="O23" s="6">
-        <v>0</v>
-      </c>
-      <c r="P23" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="6">
-        <v>0</v>
-      </c>
-      <c r="R23" s="6">
-        <v>0</v>
-      </c>
-      <c r="S23" s="13">
+      <c r="U23" s="14">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="U23" s="14">
-        <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="V23" s="9">
@@ -36518,11 +36496,11 @@
       <c r="A24" s="5">
         <v>45831</v>
       </c>
-      <c r="B24" s="6">
-        <v>0</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0</v>
+      <c r="B24" s="7">
+        <v>1544.9279994999988</v>
+      </c>
+      <c r="C24" s="7">
+        <v>240.32399992000001</v>
       </c>
       <c r="D24" s="29">
         <v>43</v>
@@ -36544,7 +36522,7 @@
         <v>38</v>
       </c>
       <c r="J24" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K24" s="6">
@@ -36556,29 +36534,28 @@
       <c r="M24" s="13">
         <v>5</v>
       </c>
-      <c r="N24" s="13">
+      <c r="N24" s="29">
+        <v>275.3279993499998</v>
+      </c>
+      <c r="O24" s="7">
+        <v>66.887999909999991</v>
+      </c>
+      <c r="P24" s="13">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0</v>
+      </c>
+      <c r="R24" s="6">
+        <v>0</v>
+      </c>
+      <c r="S24" s="13">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="O24" s="6">
-        <v>0</v>
-      </c>
-      <c r="P24" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="6">
-        <v>0</v>
-      </c>
-      <c r="R24" s="6">
-        <v>0</v>
-      </c>
-      <c r="S24" s="13">
+      <c r="U24" s="14">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="U24" s="14">
-        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="V24" s="9">
@@ -36610,11 +36587,11 @@
       <c r="A25" s="5">
         <v>45832</v>
       </c>
-      <c r="B25" s="6">
-        <v>0</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0</v>
+      <c r="B25" s="7">
+        <v>1439.96999949</v>
+      </c>
+      <c r="C25" s="7">
+        <v>219.99599992999998</v>
       </c>
       <c r="D25" s="29">
         <v>43</v>
@@ -36636,7 +36613,7 @@
         <v>38</v>
       </c>
       <c r="J25" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K25" s="6">
@@ -36648,29 +36625,28 @@
       <c r="M25" s="13">
         <v>5</v>
       </c>
-      <c r="N25" s="13">
+      <c r="N25" s="29">
+        <v>248.49599941999989</v>
+      </c>
+      <c r="O25" s="7">
+        <v>61.775999880000001</v>
+      </c>
+      <c r="P25" s="13">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="O25" s="6">
-        <v>0</v>
-      </c>
-      <c r="P25" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>0</v>
+      </c>
+      <c r="R25" s="6">
+        <v>0</v>
+      </c>
+      <c r="S25" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>0</v>
-      </c>
-      <c r="R25" s="6">
-        <v>0</v>
-      </c>
-      <c r="S25" s="13">
+        <v>3</v>
+      </c>
+      <c r="U25" s="14">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="U25" s="14">
-        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="V25" s="34">
@@ -36702,11 +36678,11 @@
       <c r="A26" s="5">
         <v>45833</v>
       </c>
-      <c r="B26" s="6">
-        <v>0</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0</v>
+      <c r="B26" s="7">
+        <v>1284.7379994599999</v>
+      </c>
+      <c r="C26" s="7">
+        <v>211.63799988999997</v>
       </c>
       <c r="D26" s="29">
         <v>43</v>
@@ -36728,7 +36704,7 @@
         <v>38</v>
       </c>
       <c r="J26" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K26" s="6">
@@ -36740,29 +36716,28 @@
       <c r="M26" s="13">
         <v>5</v>
       </c>
-      <c r="N26" s="13">
+      <c r="N26" s="29">
+        <v>265.36799933999993</v>
+      </c>
+      <c r="O26" s="7">
+        <v>55.703999900000007</v>
+      </c>
+      <c r="P26" s="13">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="O26" s="6">
-        <v>0</v>
-      </c>
-      <c r="P26" s="13">
+        <v>59</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>0</v>
+      </c>
+      <c r="R26" s="6">
+        <v>0</v>
+      </c>
+      <c r="S26" s="13">
         <f t="shared" si="3"/>
-        <v>59</v>
-      </c>
-      <c r="Q26" s="6">
-        <v>0</v>
-      </c>
-      <c r="R26" s="6">
-        <v>0</v>
-      </c>
-      <c r="S26" s="13">
+        <v>0</v>
+      </c>
+      <c r="U26" s="35">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="35">
-        <f t="shared" si="5"/>
         <v>24</v>
       </c>
       <c r="V26" s="6">
@@ -36794,11 +36769,11 @@
       <c r="A27" s="5">
         <v>45834</v>
       </c>
-      <c r="B27" s="6">
-        <v>0</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0</v>
+      <c r="B27" s="7">
+        <v>1338.5819995099987</v>
+      </c>
+      <c r="C27" s="7">
+        <v>190.34399994999998</v>
       </c>
       <c r="D27" s="29">
         <v>43</v>
@@ -36820,7 +36795,7 @@
         <v>38</v>
       </c>
       <c r="J27" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="K27" s="6">
@@ -36832,29 +36807,28 @@
       <c r="M27" s="13">
         <v>5</v>
       </c>
-      <c r="N27" s="13">
+      <c r="N27" s="29">
+        <v>246.43199937999987</v>
+      </c>
+      <c r="O27" s="7">
+        <v>60.263999900000002</v>
+      </c>
+      <c r="P27" s="13">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="O27" s="6">
-        <v>0</v>
-      </c>
-      <c r="P27" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>0</v>
+      </c>
+      <c r="R27" s="6">
+        <v>0</v>
+      </c>
+      <c r="S27" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="6">
-        <v>0</v>
-      </c>
-      <c r="R27" s="6">
-        <v>0</v>
-      </c>
-      <c r="S27" s="13">
+        <v>7</v>
+      </c>
+      <c r="U27" s="14">
         <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="U27" s="14">
-        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="V27" s="6">
@@ -36886,11 +36860,11 @@
       <c r="A28" s="5">
         <v>45835</v>
       </c>
-      <c r="B28" s="6">
-        <v>0</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0</v>
+      <c r="B28" s="7">
+        <v>1159.1999995100002</v>
+      </c>
+      <c r="C28" s="7">
+        <v>183.91799988999998</v>
       </c>
       <c r="D28" s="29">
         <v>43</v>
@@ -36912,7 +36886,7 @@
         <v>38</v>
       </c>
       <c r="J28" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K28" s="6">
@@ -36924,29 +36898,28 @@
       <c r="M28" s="13">
         <v>5</v>
       </c>
-      <c r="N28" s="13">
+      <c r="N28" s="29">
+        <v>249.74399931999994</v>
+      </c>
+      <c r="O28" s="7">
+        <v>54.815999890000001</v>
+      </c>
+      <c r="P28" s="13">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="O28" s="6">
-        <v>0</v>
-      </c>
-      <c r="P28" s="13">
+        <v>-57</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0</v>
+      </c>
+      <c r="R28" s="6">
+        <v>0</v>
+      </c>
+      <c r="S28" s="13">
         <f t="shared" si="3"/>
-        <v>-57</v>
-      </c>
-      <c r="Q28" s="6">
-        <v>0</v>
-      </c>
-      <c r="R28" s="6">
-        <v>0</v>
-      </c>
-      <c r="S28" s="13">
+        <v>3</v>
+      </c>
+      <c r="U28" s="18">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="U28" s="18">
-        <f t="shared" si="5"/>
         <v>26</v>
       </c>
       <c r="V28" s="19">
@@ -36978,11 +36951,11 @@
       <c r="A29" s="5">
         <v>45836</v>
       </c>
-      <c r="B29" s="6">
-        <v>0</v>
-      </c>
-      <c r="C29" s="6">
-        <v>0</v>
+      <c r="B29" s="7">
+        <v>937.5659994600004</v>
+      </c>
+      <c r="C29" s="7">
+        <v>152.66999990999997</v>
       </c>
       <c r="D29" s="29">
         <v>43</v>
@@ -37004,7 +36977,7 @@
         <v>38</v>
       </c>
       <c r="J29" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K29" s="6">
@@ -37016,29 +36989,28 @@
       <c r="M29" s="13">
         <v>5</v>
       </c>
-      <c r="N29" s="13">
+      <c r="N29" s="29">
+        <v>273.47999938999976</v>
+      </c>
+      <c r="O29" s="7">
+        <v>64.199999910000003</v>
+      </c>
+      <c r="P29" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O29" s="6">
-        <v>0</v>
-      </c>
-      <c r="P29" s="13">
+      <c r="Q29" s="6">
+        <v>0</v>
+      </c>
+      <c r="R29" s="6">
+        <v>0</v>
+      </c>
+      <c r="S29" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="6">
-        <v>0</v>
-      </c>
-      <c r="R29" s="6">
-        <v>0</v>
-      </c>
-      <c r="S29" s="13">
+      <c r="U29" s="18">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U29" s="18">
-        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="V29" s="15">
@@ -37070,11 +37042,11 @@
       <c r="A30" s="5">
         <v>45837</v>
       </c>
-      <c r="B30" s="6">
-        <v>0</v>
-      </c>
-      <c r="C30" s="6">
-        <v>0</v>
+      <c r="B30" s="7">
+        <v>928.78799944999992</v>
+      </c>
+      <c r="C30" s="7">
+        <v>166.78199988999998</v>
       </c>
       <c r="D30" s="29">
         <v>43</v>
@@ -37096,7 +37068,7 @@
         <v>38</v>
       </c>
       <c r="J30" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="K30" s="6">
@@ -37108,29 +37080,28 @@
       <c r="M30" s="13">
         <v>5</v>
       </c>
-      <c r="N30" s="13">
+      <c r="N30" s="29">
+        <v>291.28799944999969</v>
+      </c>
+      <c r="O30" s="7">
+        <v>59.903999889999994</v>
+      </c>
+      <c r="P30" s="13">
         <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>0</v>
+      </c>
+      <c r="R30" s="6">
+        <v>0</v>
+      </c>
+      <c r="S30" s="13">
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="O30" s="6">
-        <v>0</v>
-      </c>
-      <c r="P30" s="13">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Q30" s="6">
-        <v>0</v>
-      </c>
-      <c r="R30" s="6">
-        <v>0</v>
-      </c>
-      <c r="S30" s="13">
+      <c r="U30" s="18">
         <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="U30" s="18">
-        <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="V30" s="15">
@@ -37162,11 +37133,11 @@
       <c r="A31" s="5">
         <v>45838</v>
       </c>
-      <c r="B31" s="6">
-        <v>0</v>
-      </c>
-      <c r="C31" s="6">
-        <v>0</v>
+      <c r="B31" s="7">
+        <v>1388.7299995399999</v>
+      </c>
+      <c r="C31" s="7">
+        <v>196.76999993000001</v>
       </c>
       <c r="D31" s="29">
         <v>43</v>
@@ -37188,7 +37159,7 @@
         <v>38</v>
       </c>
       <c r="J31" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K31" s="6">
@@ -37200,29 +37171,28 @@
       <c r="M31" s="13">
         <v>5</v>
       </c>
-      <c r="N31" s="13">
+      <c r="N31" s="29">
+        <v>236.15999938999974</v>
+      </c>
+      <c r="O31" s="7">
+        <v>52.031999909999996</v>
+      </c>
+      <c r="P31" s="13">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>0</v>
+      </c>
+      <c r="R31" s="6">
+        <v>0</v>
+      </c>
+      <c r="S31" s="13">
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="O31" s="6">
-        <v>0</v>
-      </c>
-      <c r="P31" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>0</v>
-      </c>
-      <c r="R31" s="6">
-        <v>0</v>
-      </c>
-      <c r="S31" s="13">
+      <c r="U31" s="18">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="U31" s="18">
-        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="V31" s="15">
@@ -37252,7 +37222,7 @@
     </row>
     <row r="32" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="U32" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="V32" s="15">

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31C4811-E148-4C08-8D32-F8BB08CBC2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4A19BE-5ED1-40D6-8889-9B1FDEDCE2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4A19BE-5ED1-40D6-8889-9B1FDEDCE2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18B5523-7689-42D1-AFBA-F8A608014833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -31490,14 +31490,30 @@
       <c r="U2" s="8">
         <v>0</v>
       </c>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
+      <c r="V2" s="15">
+        <v>7715</v>
+      </c>
+      <c r="W2" s="15">
+        <v>9620</v>
+      </c>
+      <c r="X2" s="15">
+        <v>9372</v>
+      </c>
+      <c r="Y2" s="15">
+        <v>10821</v>
+      </c>
+      <c r="Z2" s="15">
+        <v>1276</v>
+      </c>
+      <c r="AA2" s="15">
+        <v>3811</v>
+      </c>
+      <c r="AB2" s="15">
+        <v>382</v>
+      </c>
+      <c r="AC2" s="15">
+        <v>3429</v>
+      </c>
       <c r="AE2" s="10" t="s">
         <v>29</v>
       </c>
@@ -31519,49 +31535,49 @@
       </c>
       <c r="D3" s="13">
         <f t="shared" ref="D3:D32" si="8">V4-V3</f>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="E3" s="13">
         <v>0</v>
       </c>
       <c r="F3" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="G3" s="13">
         <v>0</v>
       </c>
       <c r="H3" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I3" s="13">
         <v>0</v>
       </c>
       <c r="J3" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="13">
         <v>0</v>
       </c>
       <c r="L3" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="13">
         <v>0</v>
       </c>
       <c r="N3" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O3" s="13">
         <v>0</v>
       </c>
       <c r="P3" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="13">
         <v>0</v>
@@ -31571,20 +31587,36 @@
       </c>
       <c r="S3" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T3" s="4"/>
       <c r="U3" s="12">
         <v>1</v>
       </c>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
+      <c r="V3" s="15">
+        <v>7715</v>
+      </c>
+      <c r="W3" s="15">
+        <v>9620</v>
+      </c>
+      <c r="X3" s="15">
+        <v>9372</v>
+      </c>
+      <c r="Y3" s="15">
+        <v>10821</v>
+      </c>
+      <c r="Z3" s="15">
+        <v>1276</v>
+      </c>
+      <c r="AA3" s="15">
+        <v>3811</v>
+      </c>
+      <c r="AB3" s="15">
+        <v>382</v>
+      </c>
+      <c r="AC3" s="15">
+        <v>3429</v>
+      </c>
     </row>
     <row r="4" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="28">
@@ -31599,49 +31631,49 @@
       </c>
       <c r="D4" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-7841</v>
       </c>
       <c r="E4" s="13">
         <v>0</v>
       </c>
       <c r="F4" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-9748</v>
       </c>
       <c r="G4" s="13">
         <v>0</v>
       </c>
       <c r="H4" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-9379</v>
       </c>
       <c r="I4" s="13">
         <v>0</v>
       </c>
       <c r="J4" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-10822</v>
       </c>
       <c r="K4" s="13">
         <v>0</v>
       </c>
       <c r="L4" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1277</v>
       </c>
       <c r="M4" s="13">
         <v>0</v>
       </c>
       <c r="N4" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-3821</v>
       </c>
       <c r="O4" s="13">
         <v>0</v>
       </c>
       <c r="P4" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-383</v>
       </c>
       <c r="Q4" s="13">
         <v>0</v>
@@ -31651,21 +31683,37 @@
       </c>
       <c r="S4" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-3437</v>
       </c>
       <c r="T4" s="4"/>
       <c r="U4" s="14">
         <f t="shared" ref="U4:U32" si="9">U3+1</f>
         <v>2</v>
       </c>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
+      <c r="V4" s="6">
+        <v>7841</v>
+      </c>
+      <c r="W4" s="6">
+        <v>9748</v>
+      </c>
+      <c r="X4" s="6">
+        <v>9379</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>10822</v>
+      </c>
+      <c r="Z4" s="6">
+        <v>1277</v>
+      </c>
+      <c r="AA4" s="6">
+        <v>3821</v>
+      </c>
+      <c r="AB4" s="6">
+        <v>383</v>
+      </c>
+      <c r="AC4" s="6">
+        <v>3437</v>
+      </c>
     </row>
     <row r="5" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="28">
@@ -37300,19 +37348,19 @@
       </c>
       <c r="D29" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="E29" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7.54</v>
       </c>
       <c r="F29" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G29" s="7">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="H29" s="29">
         <v>137</v>
@@ -37322,7 +37370,7 @@
       </c>
       <c r="J29" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="6">
         <v>0</v>
@@ -37351,7 +37399,7 @@
       </c>
       <c r="S29" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" s="18">
         <f t="shared" si="7"/>
@@ -37394,19 +37442,19 @@
       </c>
       <c r="D30" s="7">
         <f t="shared" si="3"/>
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="E30" s="7">
         <f t="shared" si="4"/>
-        <v>9.23</v>
+        <v>1.69</v>
       </c>
       <c r="F30" s="7">
         <f t="shared" si="5"/>
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="G30" s="7">
         <f t="shared" si="6"/>
-        <v>12.74</v>
+        <v>6.76</v>
       </c>
       <c r="H30" s="29">
         <v>137</v>
@@ -37416,7 +37464,7 @@
       </c>
       <c r="J30" s="13">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" s="6">
         <v>0</v>
@@ -37445,23 +37493,23 @@
       </c>
       <c r="S30" s="13">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U30" s="18">
         <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="V30" s="15">
-        <v>7610</v>
+        <v>7668</v>
       </c>
       <c r="W30" s="15">
-        <v>9459</v>
+        <v>9505</v>
       </c>
       <c r="X30" s="15">
-        <v>9359</v>
+        <v>9364</v>
       </c>
       <c r="Y30" s="15">
-        <v>10819</v>
+        <v>10820</v>
       </c>
       <c r="Z30" s="15">
         <v>1276</v>
@@ -37473,7 +37521,7 @@
         <v>381</v>
       </c>
       <c r="AC30" s="15">
-        <v>3419</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18B5523-7689-42D1-AFBA-F8A608014833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5C6A11-446C-4948-9D28-7E601B5A8FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -816,12 +816,9 @@
   <cols>
     <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -1199,40 +1196,40 @@
         <v>11147.95</v>
       </c>
       <c r="D7" s="42">
-        <v>0</v>
+        <v>1093.8501000000001</v>
       </c>
       <c r="E7" s="42">
-        <v>0</v>
+        <v>491.43989999999997</v>
       </c>
       <c r="F7" s="42">
-        <v>0</v>
+        <v>964.29570000000001</v>
       </c>
       <c r="G7" s="42">
-        <v>0</v>
+        <v>433.23429999999996</v>
       </c>
       <c r="H7" s="42">
-        <v>0</v>
+        <v>3648.3404999999998</v>
       </c>
       <c r="I7" s="42">
-        <v>0</v>
+        <v>1639.1095</v>
       </c>
       <c r="J7" s="42">
-        <v>0</v>
+        <v>1095.6717000000001</v>
       </c>
       <c r="K7" s="42">
-        <v>0</v>
+        <v>492.25830000000002</v>
       </c>
       <c r="L7" s="42">
-        <v>0</v>
+        <v>906.23910000000001</v>
       </c>
       <c r="M7" s="42">
-        <v>0</v>
+        <v>407.15090000000004</v>
       </c>
       <c r="N7" s="42">
-        <v>0</v>
+        <v>6962.7</v>
       </c>
       <c r="O7" s="42">
-        <v>0</v>
+        <v>3143.83</v>
       </c>
       <c r="P7" s="42">
         <v>0</v>
@@ -31631,49 +31628,49 @@
       </c>
       <c r="D4" s="13">
         <f t="shared" si="8"/>
-        <v>-7841</v>
+        <v>0</v>
       </c>
       <c r="E4" s="13">
         <v>0</v>
       </c>
       <c r="F4" s="13">
         <f t="shared" si="0"/>
-        <v>-9748</v>
+        <v>0</v>
       </c>
       <c r="G4" s="13">
         <v>0</v>
       </c>
       <c r="H4" s="13">
         <f t="shared" si="1"/>
-        <v>-9379</v>
+        <v>0</v>
       </c>
       <c r="I4" s="13">
         <v>0</v>
       </c>
       <c r="J4" s="13">
         <f t="shared" si="2"/>
-        <v>-10822</v>
+        <v>0</v>
       </c>
       <c r="K4" s="13">
         <v>0</v>
       </c>
       <c r="L4" s="13">
         <f t="shared" si="3"/>
-        <v>-1277</v>
+        <v>0</v>
       </c>
       <c r="M4" s="13">
         <v>0</v>
       </c>
       <c r="N4" s="13">
         <f t="shared" si="4"/>
-        <v>-3821</v>
+        <v>0</v>
       </c>
       <c r="O4" s="13">
         <v>0</v>
       </c>
       <c r="P4" s="13">
         <f t="shared" si="5"/>
-        <v>-383</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="13">
         <v>0</v>
@@ -31683,7 +31680,7 @@
       </c>
       <c r="S4" s="13">
         <f t="shared" si="6"/>
-        <v>-3437</v>
+        <v>0</v>
       </c>
       <c r="T4" s="4"/>
       <c r="U4" s="14">
@@ -31728,28 +31725,28 @@
       </c>
       <c r="D5" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="E5" s="13">
         <v>0</v>
       </c>
       <c r="F5" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="G5" s="13">
         <v>0</v>
       </c>
       <c r="H5" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I5" s="13">
         <v>0</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="13">
         <v>0</v>
@@ -31763,14 +31760,14 @@
       </c>
       <c r="N5" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O5" s="13">
         <v>0</v>
       </c>
       <c r="P5" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="13">
         <v>0</v>
@@ -31780,21 +31777,37 @@
       </c>
       <c r="S5" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T5" s="4"/>
       <c r="U5" s="14">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
+      <c r="V5" s="6">
+        <v>7841</v>
+      </c>
+      <c r="W5" s="6">
+        <v>9748</v>
+      </c>
+      <c r="X5" s="6">
+        <v>9379</v>
+      </c>
+      <c r="Y5" s="6">
+        <v>10822</v>
+      </c>
+      <c r="Z5" s="6">
+        <v>1277</v>
+      </c>
+      <c r="AA5" s="6">
+        <v>3821</v>
+      </c>
+      <c r="AB5" s="6">
+        <v>383</v>
+      </c>
+      <c r="AC5" s="6">
+        <v>3437</v>
+      </c>
     </row>
     <row r="6" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="28">
@@ -31809,28 +31822,28 @@
       </c>
       <c r="D6" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E6" s="13">
         <v>0</v>
       </c>
       <c r="F6" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="G6" s="13">
         <v>0</v>
       </c>
       <c r="H6" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I6" s="13">
         <v>0</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" s="13">
         <v>0</v>
@@ -31844,14 +31857,14 @@
       </c>
       <c r="N6" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O6" s="13">
         <v>0</v>
       </c>
       <c r="P6" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="13">
         <v>0</v>
@@ -31861,21 +31874,37 @@
       </c>
       <c r="S6" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T6" s="4"/>
       <c r="U6" s="14">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
-      <c r="AB6" s="6"/>
-      <c r="AC6" s="6"/>
+      <c r="V6" s="6">
+        <v>7973</v>
+      </c>
+      <c r="W6" s="6">
+        <v>9741</v>
+      </c>
+      <c r="X6" s="6">
+        <v>9387</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>10823</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>1277</v>
+      </c>
+      <c r="AA6" s="6">
+        <v>3826</v>
+      </c>
+      <c r="AB6" s="6">
+        <v>384</v>
+      </c>
+      <c r="AC6" s="6">
+        <v>3442</v>
+      </c>
     </row>
     <row r="7" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="28">
@@ -31890,21 +31919,21 @@
       </c>
       <c r="D7" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E7" s="13">
         <v>0</v>
       </c>
       <c r="F7" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G7" s="13">
         <v>0</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" s="13">
         <v>0</v>
@@ -31925,7 +31954,7 @@
       </c>
       <c r="N7" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O7" s="13">
         <v>0</v>
@@ -31942,21 +31971,37 @@
       </c>
       <c r="S7" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T7" s="4"/>
       <c r="U7" s="14">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="6"/>
+      <c r="V7" s="6">
+        <v>8029</v>
+      </c>
+      <c r="W7" s="6">
+        <v>9902</v>
+      </c>
+      <c r="X7" s="6">
+        <v>9396</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>10825</v>
+      </c>
+      <c r="Z7" s="6">
+        <v>1277</v>
+      </c>
+      <c r="AA7" s="6">
+        <v>3832</v>
+      </c>
+      <c r="AB7" s="6">
+        <v>385</v>
+      </c>
+      <c r="AC7" s="6">
+        <v>3447</v>
+      </c>
     </row>
     <row r="8" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="28">
@@ -31978,21 +32023,21 @@
       </c>
       <c r="F8" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G8" s="13">
         <v>0</v>
       </c>
       <c r="H8" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I8" s="13">
         <v>0</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-156</v>
       </c>
       <c r="K8" s="13">
         <v>0</v>
@@ -32030,14 +32075,30 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="6"/>
+      <c r="V8" s="6">
+        <v>8037</v>
+      </c>
+      <c r="W8" s="6">
+        <v>9928</v>
+      </c>
+      <c r="X8" s="6">
+        <v>9398</v>
+      </c>
+      <c r="Y8" s="6">
+        <v>10825</v>
+      </c>
+      <c r="Z8" s="6">
+        <v>1277</v>
+      </c>
+      <c r="AA8" s="6">
+        <v>3836</v>
+      </c>
+      <c r="AB8" s="6">
+        <v>385</v>
+      </c>
+      <c r="AC8" s="6">
+        <v>3451</v>
+      </c>
     </row>
     <row r="9" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="28">
@@ -32052,28 +32113,28 @@
       </c>
       <c r="D9" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="E9" s="13">
         <v>0</v>
       </c>
       <c r="F9" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G9" s="13">
         <v>0</v>
       </c>
       <c r="H9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I9" s="13">
         <v>0</v>
       </c>
       <c r="J9" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="K9" s="13">
         <v>0</v>
@@ -32087,14 +32148,14 @@
       </c>
       <c r="N9" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O9" s="13">
         <v>0</v>
       </c>
       <c r="P9" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="13">
         <v>0</v>
@@ -32104,21 +32165,37 @@
       </c>
       <c r="S9" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T9" s="4"/>
       <c r="U9" s="14">
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="6"/>
-      <c r="AB9" s="6"/>
-      <c r="AC9" s="6"/>
+      <c r="V9" s="6">
+        <v>8037</v>
+      </c>
+      <c r="W9" s="6">
+        <v>9972</v>
+      </c>
+      <c r="X9" s="6">
+        <v>9409</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>10669</v>
+      </c>
+      <c r="Z9" s="6">
+        <v>1277</v>
+      </c>
+      <c r="AA9" s="6">
+        <v>3836</v>
+      </c>
+      <c r="AB9" s="6">
+        <v>385</v>
+      </c>
+      <c r="AC9" s="6">
+        <v>3451</v>
+      </c>
     </row>
     <row r="10" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="28">
@@ -32133,14 +32210,14 @@
       </c>
       <c r="D10" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E10" s="13">
         <v>0</v>
       </c>
       <c r="F10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G10" s="13">
         <v>0</v>
@@ -32168,7 +32245,7 @@
       </c>
       <c r="N10" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O10" s="13">
         <v>0</v>
@@ -32185,21 +32262,37 @@
       </c>
       <c r="S10" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T10" s="4"/>
       <c r="U10" s="14">
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="6"/>
-      <c r="AB10" s="6"/>
-      <c r="AC10" s="6"/>
+      <c r="V10" s="6">
+        <v>8106</v>
+      </c>
+      <c r="W10" s="6">
+        <v>10003</v>
+      </c>
+      <c r="X10" s="6">
+        <v>9414</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>10826</v>
+      </c>
+      <c r="Z10" s="6">
+        <v>1277</v>
+      </c>
+      <c r="AA10" s="6">
+        <v>3844</v>
+      </c>
+      <c r="AB10" s="6">
+        <v>386</v>
+      </c>
+      <c r="AC10" s="6">
+        <v>3458</v>
+      </c>
     </row>
     <row r="11" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="28">
@@ -32214,49 +32307,49 @@
       </c>
       <c r="D11" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E11" s="13">
         <v>0</v>
       </c>
       <c r="F11" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G11" s="13">
         <v>0</v>
       </c>
       <c r="H11" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I11" s="13">
         <v>0</v>
       </c>
       <c r="J11" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="13">
         <v>0</v>
       </c>
       <c r="L11" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11511</v>
       </c>
       <c r="M11" s="13">
         <v>0</v>
       </c>
       <c r="N11" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O11" s="13">
         <v>0</v>
       </c>
       <c r="P11" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="13">
         <v>0</v>
@@ -32266,21 +32359,37 @@
       </c>
       <c r="S11" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T11" s="4"/>
       <c r="U11" s="14">
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="6"/>
-      <c r="AB11" s="6"/>
-      <c r="AC11" s="6"/>
+      <c r="V11" s="6">
+        <v>8171</v>
+      </c>
+      <c r="W11" s="6">
+        <v>10046</v>
+      </c>
+      <c r="X11" s="6">
+        <v>9414</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>10826</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>1277</v>
+      </c>
+      <c r="AA11" s="6">
+        <v>3847</v>
+      </c>
+      <c r="AB11" s="6">
+        <v>386</v>
+      </c>
+      <c r="AC11" s="6">
+        <v>3461</v>
+      </c>
     </row>
     <row r="12" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="28">
@@ -32295,49 +32404,49 @@
       </c>
       <c r="D12" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-8216</v>
       </c>
       <c r="E12" s="13">
         <v>0</v>
       </c>
       <c r="F12" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-10080</v>
       </c>
       <c r="G12" s="13">
         <v>0</v>
       </c>
       <c r="H12" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-9421</v>
       </c>
       <c r="I12" s="13">
         <v>0</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-10827</v>
       </c>
       <c r="K12" s="13">
         <v>0</v>
       </c>
       <c r="L12" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-12788</v>
       </c>
       <c r="M12" s="13">
         <v>0</v>
       </c>
       <c r="N12" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-3851</v>
       </c>
       <c r="O12" s="13">
         <v>0</v>
       </c>
       <c r="P12" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-387</v>
       </c>
       <c r="Q12" s="13">
         <v>0</v>
@@ -32347,21 +32456,37 @@
       </c>
       <c r="S12" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-3464</v>
       </c>
       <c r="T12" s="4"/>
       <c r="U12" s="14">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="6"/>
-      <c r="AA12" s="6"/>
-      <c r="AB12" s="6"/>
-      <c r="AC12" s="6"/>
+      <c r="V12" s="6">
+        <v>8216</v>
+      </c>
+      <c r="W12" s="6">
+        <v>10080</v>
+      </c>
+      <c r="X12" s="6">
+        <v>9421</v>
+      </c>
+      <c r="Y12" s="6">
+        <v>10827</v>
+      </c>
+      <c r="Z12" s="6">
+        <v>12788</v>
+      </c>
+      <c r="AA12" s="6">
+        <v>3851</v>
+      </c>
+      <c r="AB12" s="6">
+        <v>387</v>
+      </c>
+      <c r="AC12" s="6">
+        <v>3464</v>
+      </c>
     </row>
     <row r="13" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
@@ -34819,23 +34944,22 @@
         <v>8.06</v>
       </c>
       <c r="H2" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I2" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J2" s="13">
-        <f t="shared" ref="J2:J14" si="0">Y3-Y2</f>
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K2" s="6">
-        <v>0</v>
-      </c>
-      <c r="L2" s="13">
-        <v>35</v>
-      </c>
-      <c r="M2" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L2" s="29">
+        <v>30</v>
+      </c>
+      <c r="M2" s="29">
+        <v>10</v>
       </c>
       <c r="N2" s="29">
         <v>276.91199938999995</v>
@@ -34844,7 +34968,7 @@
         <v>58.7279999</v>
       </c>
       <c r="P2" s="13">
-        <f t="shared" ref="P2:P31" si="1">AB3-AB2</f>
+        <f t="shared" ref="P2:P31" si="0">AB3-AB2</f>
         <v>1</v>
       </c>
       <c r="Q2" s="6">
@@ -34854,7 +34978,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="13">
-        <f t="shared" ref="S2:S31" si="2">AC3-AC2</f>
+        <f t="shared" ref="S2:S31" si="1">AC3-AC2</f>
         <v>7</v>
       </c>
       <c r="U2" s="8">
@@ -34903,39 +35027,38 @@
         <v>179.08799991000001</v>
       </c>
       <c r="D3" s="7">
-        <f t="shared" ref="D3:D31" si="3">V4-V3</f>
+        <f t="shared" ref="D3:D31" si="2">V4-V3</f>
         <v>32</v>
       </c>
       <c r="E3" s="7">
-        <f t="shared" ref="E3:E31" si="4">D3*0.13</f>
+        <f t="shared" ref="E3:E31" si="3">D3*0.13</f>
         <v>4.16</v>
       </c>
       <c r="F3" s="7">
-        <f t="shared" ref="F3:F30" si="5">W4-W3</f>
+        <f t="shared" ref="F3:F30" si="4">W4-W3</f>
         <v>85</v>
       </c>
       <c r="G3" s="7">
-        <f t="shared" ref="G3:G31" si="6">F3*0.13</f>
+        <f t="shared" ref="G3:G31" si="5">F3*0.13</f>
         <v>11.05</v>
       </c>
       <c r="H3" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I3" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J3" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K3" s="6">
-        <v>0</v>
-      </c>
-      <c r="L3" s="13">
-        <v>35</v>
-      </c>
-      <c r="M3" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L3" s="29">
+        <v>30</v>
+      </c>
+      <c r="M3" s="29">
+        <v>10</v>
       </c>
       <c r="N3" s="29">
         <v>218.73599947999992</v>
@@ -34944,17 +35067,17 @@
         <v>50.159999910000003</v>
       </c>
       <c r="P3" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>0</v>
+      </c>
+      <c r="R3" s="6">
+        <v>0</v>
+      </c>
+      <c r="S3" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>0</v>
-      </c>
-      <c r="R3" s="6">
-        <v>0</v>
-      </c>
-      <c r="S3" s="13">
-        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="U3" s="12">
@@ -34996,39 +35119,38 @@
         <v>184.42199996000002</v>
       </c>
       <c r="D4" s="7">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="E4" s="7">
         <f t="shared" si="3"/>
-        <v>63</v>
-      </c>
-      <c r="E4" s="7">
+        <v>8.19</v>
+      </c>
+      <c r="F4" s="7">
         <f t="shared" si="4"/>
-        <v>8.19</v>
-      </c>
-      <c r="F4" s="7">
+        <v>15</v>
+      </c>
+      <c r="G4" s="7">
         <f t="shared" si="5"/>
-        <v>15</v>
-      </c>
-      <c r="G4" s="7">
-        <f t="shared" si="6"/>
         <v>1.9500000000000002</v>
       </c>
       <c r="H4" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I4" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J4" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K4" s="6">
-        <v>0</v>
-      </c>
-      <c r="L4" s="13">
-        <v>35</v>
-      </c>
-      <c r="M4" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L4" s="29">
+        <v>30</v>
+      </c>
+      <c r="M4" s="29">
+        <v>10</v>
       </c>
       <c r="N4" s="29">
         <v>294.69599936000009</v>
@@ -35037,21 +35159,21 @@
         <v>62.087999889999992</v>
       </c>
       <c r="P4" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0</v>
+      </c>
+      <c r="S4" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6">
-        <v>0</v>
-      </c>
-      <c r="S4" s="13">
-        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="U4" s="14">
-        <f t="shared" ref="U4:U32" si="7">U3+1</f>
+        <f t="shared" ref="U4:U32" si="6">U3+1</f>
         <v>2</v>
       </c>
       <c r="V4" s="6">
@@ -35090,62 +35212,61 @@
         <v>209.83199991000004</v>
       </c>
       <c r="D5" s="7">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="E5" s="7">
         <f t="shared" si="3"/>
-        <v>95</v>
-      </c>
-      <c r="E5" s="7">
+        <v>12.35</v>
+      </c>
+      <c r="F5" s="7">
         <f t="shared" si="4"/>
-        <v>12.35</v>
-      </c>
-      <c r="F5" s="7">
+        <v>73</v>
+      </c>
+      <c r="G5" s="7">
         <f t="shared" si="5"/>
-        <v>73</v>
-      </c>
-      <c r="G5" s="7">
-        <f t="shared" si="6"/>
         <v>9.49</v>
       </c>
       <c r="H5" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I5" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J5" s="13">
+        <v>36</v>
+      </c>
+      <c r="K5" s="6">
+        <v>12</v>
+      </c>
+      <c r="L5" s="29">
+        <v>30</v>
+      </c>
+      <c r="M5" s="29">
+        <v>10</v>
+      </c>
+      <c r="N5" s="29">
+        <v>270.38399930999987</v>
+      </c>
+      <c r="O5" s="7">
+        <v>59.231999910000006</v>
+      </c>
+      <c r="P5" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K5" s="6">
-        <v>0</v>
-      </c>
-      <c r="L5" s="13">
-        <v>35</v>
-      </c>
-      <c r="M5" s="13">
-        <v>5</v>
-      </c>
-      <c r="N5" s="29">
-        <v>270.38399930999987</v>
-      </c>
-      <c r="O5" s="7">
-        <v>59.231999910000006</v>
-      </c>
-      <c r="P5" s="13">
+      <c r="Q5" s="6">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6">
+        <v>0</v>
+      </c>
+      <c r="S5" s="13">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6">
-        <v>0</v>
-      </c>
-      <c r="S5" s="13">
-        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="U5" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="V5" s="6">
@@ -35184,62 +35305,61 @@
         <v>198.70199993</v>
       </c>
       <c r="D6" s="7">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E6" s="7">
         <f t="shared" si="3"/>
-        <v>57</v>
-      </c>
-      <c r="E6" s="7">
+        <v>7.41</v>
+      </c>
+      <c r="F6" s="7">
         <f t="shared" si="4"/>
-        <v>7.41</v>
-      </c>
-      <c r="F6" s="7">
+        <v>28</v>
+      </c>
+      <c r="G6" s="7">
         <f t="shared" si="5"/>
-        <v>28</v>
-      </c>
-      <c r="G6" s="7">
-        <f t="shared" si="6"/>
         <v>3.64</v>
       </c>
       <c r="H6" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I6" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J6" s="13">
+        <v>36</v>
+      </c>
+      <c r="K6" s="6">
+        <v>12</v>
+      </c>
+      <c r="L6" s="29">
+        <v>30</v>
+      </c>
+      <c r="M6" s="29">
+        <v>10</v>
+      </c>
+      <c r="N6" s="29">
+        <v>271.94399931000004</v>
+      </c>
+      <c r="O6" s="7">
+        <v>60.383999889999991</v>
+      </c>
+      <c r="P6" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="13">
-        <v>35</v>
-      </c>
-      <c r="M6" s="13">
-        <v>5</v>
-      </c>
-      <c r="N6" s="29">
-        <v>271.94399931000004</v>
-      </c>
-      <c r="O6" s="7">
-        <v>60.383999889999991</v>
-      </c>
-      <c r="P6" s="13">
+      <c r="Q6" s="6">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6">
-        <v>0</v>
-      </c>
-      <c r="S6" s="13">
-        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="U6" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="V6" s="6">
@@ -35278,39 +35398,38 @@
         <v>181.98599990999998</v>
       </c>
       <c r="D7" s="7">
+        <f t="shared" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="E7" s="7">
         <f t="shared" si="3"/>
-        <v>83</v>
-      </c>
-      <c r="E7" s="7">
+        <v>10.790000000000001</v>
+      </c>
+      <c r="F7" s="7">
         <f t="shared" si="4"/>
-        <v>10.790000000000001</v>
-      </c>
-      <c r="F7" s="7">
+        <v>80</v>
+      </c>
+      <c r="G7" s="7">
         <f t="shared" si="5"/>
-        <v>80</v>
-      </c>
-      <c r="G7" s="7">
-        <f t="shared" si="6"/>
         <v>10.4</v>
       </c>
       <c r="H7" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I7" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J7" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="13">
-        <v>35</v>
-      </c>
-      <c r="M7" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L7" s="29">
+        <v>30</v>
+      </c>
+      <c r="M7" s="29">
+        <v>10</v>
       </c>
       <c r="N7" s="29">
         <v>270.07199934000005</v>
@@ -35319,21 +35438,21 @@
         <v>50.903999910000003</v>
       </c>
       <c r="P7" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>0</v>
+      </c>
+      <c r="R7" s="6">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6">
-        <v>0</v>
-      </c>
-      <c r="S7" s="13">
-        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="U7" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="V7" s="6">
@@ -35372,62 +35491,61 @@
         <v>171.31799996000004</v>
       </c>
       <c r="D8" s="7">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="E8" s="7">
         <f t="shared" si="3"/>
-        <v>34</v>
-      </c>
-      <c r="E8" s="7">
+        <v>4.42</v>
+      </c>
+      <c r="F8" s="7">
         <f t="shared" si="4"/>
-        <v>4.42</v>
-      </c>
-      <c r="F8" s="7">
+        <v>30</v>
+      </c>
+      <c r="G8" s="7">
         <f t="shared" si="5"/>
+        <v>3.9000000000000004</v>
+      </c>
+      <c r="H8" s="29">
+        <v>118</v>
+      </c>
+      <c r="I8" s="7">
+        <v>39.333333333333336</v>
+      </c>
+      <c r="J8" s="13">
+        <v>36</v>
+      </c>
+      <c r="K8" s="6">
+        <v>12</v>
+      </c>
+      <c r="L8" s="29">
         <v>30</v>
       </c>
-      <c r="G8" s="7">
-        <f t="shared" si="6"/>
-        <v>3.9000000000000004</v>
-      </c>
-      <c r="H8" s="29">
-        <v>137</v>
-      </c>
-      <c r="I8" s="7">
-        <v>38</v>
-      </c>
-      <c r="J8" s="13">
+      <c r="M8" s="29">
+        <v>10</v>
+      </c>
+      <c r="N8" s="29">
+        <v>307.19999936999983</v>
+      </c>
+      <c r="O8" s="7">
+        <v>58.775999880000015</v>
+      </c>
+      <c r="P8" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="13">
-        <v>35</v>
-      </c>
-      <c r="M8" s="13">
-        <v>5</v>
-      </c>
-      <c r="N8" s="29">
-        <v>307.19999936999983</v>
-      </c>
-      <c r="O8" s="7">
-        <v>58.775999880000015</v>
-      </c>
-      <c r="P8" s="13">
+      <c r="Q8" s="6">
+        <v>0</v>
+      </c>
+      <c r="R8" s="6">
+        <v>0</v>
+      </c>
+      <c r="S8" s="13">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="13">
-        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="U8" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="V8" s="6">
@@ -35466,39 +35584,38 @@
         <v>175.55999992</v>
       </c>
       <c r="D9" s="7">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="E9" s="7">
         <f t="shared" si="3"/>
-        <v>47</v>
-      </c>
-      <c r="E9" s="7">
+        <v>6.11</v>
+      </c>
+      <c r="F9" s="7">
         <f t="shared" si="4"/>
-        <v>6.11</v>
-      </c>
-      <c r="F9" s="7">
+        <v>63</v>
+      </c>
+      <c r="G9" s="7">
         <f t="shared" si="5"/>
-        <v>63</v>
-      </c>
-      <c r="G9" s="7">
-        <f t="shared" si="6"/>
         <v>8.19</v>
       </c>
       <c r="H9" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I9" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J9" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="13">
-        <v>35</v>
-      </c>
-      <c r="M9" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L9" s="29">
+        <v>30</v>
+      </c>
+      <c r="M9" s="29">
+        <v>10</v>
       </c>
       <c r="N9" s="29">
         <v>298.75199937999969</v>
@@ -35507,21 +35624,21 @@
         <v>51.5999999</v>
       </c>
       <c r="P9" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>0</v>
+      </c>
+      <c r="R9" s="6">
+        <v>0</v>
+      </c>
+      <c r="S9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>0</v>
-      </c>
-      <c r="R9" s="6">
-        <v>0</v>
-      </c>
-      <c r="S9" s="13">
-        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="U9" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="V9" s="6">
@@ -35560,62 +35677,61 @@
         <v>200.04599990999998</v>
       </c>
       <c r="D10" s="7">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="E10" s="7">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="E10" s="7">
+        <v>0.65</v>
+      </c>
+      <c r="F10" s="7">
         <f t="shared" si="4"/>
-        <v>0.65</v>
-      </c>
-      <c r="F10" s="7">
+        <v>35</v>
+      </c>
+      <c r="G10" s="7">
         <f t="shared" si="5"/>
-        <v>35</v>
-      </c>
-      <c r="G10" s="7">
-        <f t="shared" si="6"/>
         <v>4.55</v>
       </c>
       <c r="H10" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I10" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J10" s="13">
+        <v>36</v>
+      </c>
+      <c r="K10" s="6">
+        <v>12</v>
+      </c>
+      <c r="L10" s="29">
+        <v>30</v>
+      </c>
+      <c r="M10" s="29">
+        <v>10</v>
+      </c>
+      <c r="N10" s="29">
+        <v>284.18399930999988</v>
+      </c>
+      <c r="O10" s="7">
+        <v>61.7279999</v>
+      </c>
+      <c r="P10" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="13">
-        <v>35</v>
-      </c>
-      <c r="M10" s="13">
-        <v>5</v>
-      </c>
-      <c r="N10" s="29">
-        <v>284.18399930999988</v>
-      </c>
-      <c r="O10" s="7">
-        <v>61.7279999</v>
-      </c>
-      <c r="P10" s="13">
+      <c r="Q10" s="6">
+        <v>0</v>
+      </c>
+      <c r="R10" s="6">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>0</v>
-      </c>
-      <c r="R10" s="6">
-        <v>0</v>
-      </c>
-      <c r="S10" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U10" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="V10" s="6">
@@ -35654,39 +35770,38 @@
         <v>218.48399992999998</v>
       </c>
       <c r="D11" s="7">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E11" s="7">
         <f t="shared" si="3"/>
-        <v>57</v>
-      </c>
-      <c r="E11" s="7">
+        <v>7.41</v>
+      </c>
+      <c r="F11" s="7">
         <f t="shared" si="4"/>
-        <v>7.41</v>
-      </c>
-      <c r="F11" s="7">
+        <v>83</v>
+      </c>
+      <c r="G11" s="7">
         <f t="shared" si="5"/>
-        <v>83</v>
-      </c>
-      <c r="G11" s="7">
-        <f t="shared" si="6"/>
         <v>10.790000000000001</v>
       </c>
       <c r="H11" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I11" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J11" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K11" s="6">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13">
-        <v>35</v>
-      </c>
-      <c r="M11" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L11" s="29">
+        <v>30</v>
+      </c>
+      <c r="M11" s="29">
+        <v>10</v>
       </c>
       <c r="N11" s="29">
         <v>257.42399933000002</v>
@@ -35695,21 +35810,21 @@
         <v>57.263999889999994</v>
       </c>
       <c r="P11" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>0</v>
+      </c>
+      <c r="R11" s="6">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>0</v>
-      </c>
-      <c r="R11" s="6">
-        <v>0</v>
-      </c>
-      <c r="S11" s="13">
-        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="U11" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="V11" s="6">
@@ -35748,39 +35863,38 @@
         <v>196.81199991</v>
       </c>
       <c r="D12" s="7">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="E12" s="7">
         <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="E12" s="7">
+        <v>1.9500000000000002</v>
+      </c>
+      <c r="F12" s="7">
         <f t="shared" si="4"/>
-        <v>1.9500000000000002</v>
-      </c>
-      <c r="F12" s="7">
+        <v>20</v>
+      </c>
+      <c r="G12" s="7">
         <f t="shared" si="5"/>
-        <v>20</v>
-      </c>
-      <c r="G12" s="7">
-        <f t="shared" si="6"/>
         <v>2.6</v>
       </c>
       <c r="H12" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I12" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J12" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K12" s="6">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13">
-        <v>35</v>
-      </c>
-      <c r="M12" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L12" s="29">
+        <v>30</v>
+      </c>
+      <c r="M12" s="29">
+        <v>10</v>
       </c>
       <c r="N12" s="29">
         <v>234.59999937999976</v>
@@ -35789,21 +35903,21 @@
         <v>53.855999909999987</v>
       </c>
       <c r="P12" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>0</v>
-      </c>
-      <c r="R12" s="6">
-        <v>0</v>
-      </c>
-      <c r="S12" s="13">
-        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="U12" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="V12" s="6">
@@ -35842,39 +35956,38 @@
         <v>182.99399991000001</v>
       </c>
       <c r="D13" s="7">
+        <f t="shared" si="2"/>
+        <v>112</v>
+      </c>
+      <c r="E13" s="7">
         <f t="shared" si="3"/>
-        <v>112</v>
-      </c>
-      <c r="E13" s="7">
+        <v>14.56</v>
+      </c>
+      <c r="F13" s="7">
         <f t="shared" si="4"/>
-        <v>14.56</v>
-      </c>
-      <c r="F13" s="7">
+        <v>109</v>
+      </c>
+      <c r="G13" s="7">
         <f t="shared" si="5"/>
-        <v>109</v>
-      </c>
-      <c r="G13" s="7">
-        <f t="shared" si="6"/>
         <v>14.17</v>
       </c>
       <c r="H13" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I13" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J13" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K13" s="6">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13">
-        <v>35</v>
-      </c>
-      <c r="M13" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L13" s="29">
+        <v>30</v>
+      </c>
+      <c r="M13" s="29">
+        <v>10</v>
       </c>
       <c r="N13" s="29">
         <v>218.42399931000006</v>
@@ -35883,21 +35996,21 @@
         <v>59.23199988999999</v>
       </c>
       <c r="P13" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>0</v>
-      </c>
-      <c r="R13" s="6">
-        <v>0</v>
-      </c>
-      <c r="S13" s="13">
-        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="U13" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="V13" s="6">
@@ -35936,39 +36049,38 @@
         <v>179.17199994999999</v>
       </c>
       <c r="D14" s="7">
+        <f t="shared" si="2"/>
+        <v>65</v>
+      </c>
+      <c r="E14" s="7">
         <f t="shared" si="3"/>
-        <v>65</v>
-      </c>
-      <c r="E14" s="7">
+        <v>8.4500000000000011</v>
+      </c>
+      <c r="F14" s="7">
         <f t="shared" si="4"/>
-        <v>8.4500000000000011</v>
-      </c>
-      <c r="F14" s="7">
+        <v>95</v>
+      </c>
+      <c r="G14" s="7">
         <f t="shared" si="5"/>
-        <v>95</v>
-      </c>
-      <c r="G14" s="7">
-        <f t="shared" si="6"/>
         <v>12.35</v>
       </c>
       <c r="H14" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I14" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J14" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K14" s="6">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13">
-        <v>35</v>
-      </c>
-      <c r="M14" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L14" s="29">
+        <v>30</v>
+      </c>
+      <c r="M14" s="29">
+        <v>10</v>
       </c>
       <c r="N14" s="29">
         <v>236.87999939999992</v>
@@ -35977,21 +36089,21 @@
         <v>49.919999920000002</v>
       </c>
       <c r="P14" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>0</v>
+      </c>
+      <c r="R14" s="6">
+        <v>0</v>
+      </c>
+      <c r="S14" s="13">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>0</v>
-      </c>
-      <c r="R14" s="6">
-        <v>0</v>
-      </c>
-      <c r="S14" s="13">
-        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="U14" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="V14" s="6">
@@ -36030,38 +36142,38 @@
         <v>150.77999991000002</v>
       </c>
       <c r="D15" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E15" s="7">
+      <c r="F15" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F15" s="7">
+      <c r="G15" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G15" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
       <c r="H15" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I15" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J15" s="13">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K15" s="6">
-        <v>0</v>
-      </c>
-      <c r="L15" s="13">
-        <v>35</v>
-      </c>
-      <c r="M15" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L15" s="29">
+        <v>30</v>
+      </c>
+      <c r="M15" s="29">
+        <v>10</v>
       </c>
       <c r="N15" s="29">
         <v>249.3839993399998</v>
@@ -36070,21 +36182,21 @@
         <v>56.927999889999995</v>
       </c>
       <c r="P15" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6">
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="6">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6">
-        <v>0</v>
-      </c>
-      <c r="S15" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
       <c r="U15" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="V15" s="6">
@@ -36123,39 +36235,38 @@
         <v>164.80799992999997</v>
       </c>
       <c r="D16" s="7">
+        <f t="shared" si="2"/>
+        <v>43</v>
+      </c>
+      <c r="E16" s="7">
         <f t="shared" si="3"/>
-        <v>43</v>
-      </c>
-      <c r="E16" s="7">
-        <f t="shared" si="4"/>
         <v>5.59</v>
       </c>
       <c r="F16" s="7">
+        <f>W17-W16</f>
+        <v>44</v>
+      </c>
+      <c r="G16" s="7">
         <f t="shared" si="5"/>
-        <v>44</v>
-      </c>
-      <c r="G16" s="7">
-        <f t="shared" si="6"/>
         <v>5.7200000000000006</v>
       </c>
       <c r="H16" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I16" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J16" s="13">
-        <f t="shared" ref="J16:J31" si="8">Y17-Y16</f>
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K16" s="6">
-        <v>0</v>
-      </c>
-      <c r="L16" s="13">
-        <v>35</v>
-      </c>
-      <c r="M16" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L16" s="29">
+        <v>30</v>
+      </c>
+      <c r="M16" s="29">
+        <v>10</v>
       </c>
       <c r="N16" s="29">
         <v>245.54399935999982</v>
@@ -36164,21 +36275,21 @@
         <v>48.695999909999998</v>
       </c>
       <c r="P16" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6">
+        <v>0</v>
+      </c>
+      <c r="S16" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6">
-        <v>0</v>
-      </c>
-      <c r="S16" s="13">
-        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="U16" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="V16" s="6">
@@ -36218,39 +36329,38 @@
         <v>204.11999993999996</v>
       </c>
       <c r="D17" s="7">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="E17" s="7">
         <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="E17" s="7">
+        <v>0.65</v>
+      </c>
+      <c r="F17" s="7">
         <f t="shared" si="4"/>
-        <v>0.65</v>
-      </c>
-      <c r="F17" s="7">
+        <v>20</v>
+      </c>
+      <c r="G17" s="7">
         <f t="shared" si="5"/>
-        <v>20</v>
-      </c>
-      <c r="G17" s="7">
-        <f t="shared" si="6"/>
         <v>2.6</v>
       </c>
       <c r="H17" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I17" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J17" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K17" s="6">
-        <v>0</v>
-      </c>
-      <c r="L17" s="13">
-        <v>35</v>
-      </c>
-      <c r="M17" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L17" s="29">
+        <v>30</v>
+      </c>
+      <c r="M17" s="29">
+        <v>10</v>
       </c>
       <c r="N17" s="29">
         <v>238.60799944999999</v>
@@ -36259,21 +36369,21 @@
         <v>61.103999920000007</v>
       </c>
       <c r="P17" s="13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6">
+        <v>0</v>
+      </c>
+      <c r="S17" s="13">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="Q17" s="6">
-        <v>0</v>
-      </c>
-      <c r="R17" s="6">
-        <v>0</v>
-      </c>
-      <c r="S17" s="13">
-        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="U17" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="V17" s="6">
@@ -36312,39 +36422,38 @@
         <v>181.48199990000003</v>
       </c>
       <c r="D18" s="7">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="E18" s="7">
         <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="E18" s="7">
-        <f t="shared" si="4"/>
         <v>6.5</v>
       </c>
       <c r="F18" s="7">
+        <f>W19-W18</f>
+        <v>32</v>
+      </c>
+      <c r="G18" s="7">
         <f t="shared" si="5"/>
-        <v>32</v>
-      </c>
-      <c r="G18" s="7">
-        <f t="shared" si="6"/>
         <v>4.16</v>
       </c>
       <c r="H18" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I18" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J18" s="13">
-        <f t="shared" si="8"/>
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K18" s="6">
-        <v>0</v>
-      </c>
-      <c r="L18" s="13">
-        <v>35</v>
-      </c>
-      <c r="M18" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L18" s="29">
+        <v>30</v>
+      </c>
+      <c r="M18" s="29">
+        <v>10</v>
       </c>
       <c r="N18" s="29">
         <v>280.77599930999969</v>
@@ -36353,21 +36462,21 @@
         <v>58.439999899999997</v>
       </c>
       <c r="P18" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>0</v>
+      </c>
+      <c r="R18" s="6">
+        <v>0</v>
+      </c>
+      <c r="S18" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6">
-        <v>0</v>
-      </c>
-      <c r="R18" s="6">
-        <v>0</v>
-      </c>
-      <c r="S18" s="13">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="U18" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="V18" s="6">
@@ -36406,39 +36515,38 @@
         <v>180.97799992</v>
       </c>
       <c r="D19" s="7">
+        <f t="shared" si="2"/>
+        <v>134</v>
+      </c>
+      <c r="E19" s="7">
         <f t="shared" si="3"/>
-        <v>134</v>
-      </c>
-      <c r="E19" s="7">
-        <f t="shared" si="4"/>
         <v>17.420000000000002</v>
       </c>
       <c r="F19" s="7">
+        <f>W20-W19</f>
+        <v>110</v>
+      </c>
+      <c r="G19" s="7">
         <f t="shared" si="5"/>
-        <v>110</v>
-      </c>
-      <c r="G19" s="7">
-        <f t="shared" si="6"/>
         <v>14.3</v>
       </c>
       <c r="H19" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I19" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J19" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K19" s="6">
-        <v>0</v>
-      </c>
-      <c r="L19" s="13">
-        <v>35</v>
-      </c>
-      <c r="M19" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L19" s="29">
+        <v>30</v>
+      </c>
+      <c r="M19" s="29">
+        <v>10</v>
       </c>
       <c r="N19" s="29">
         <v>266.35199933999979</v>
@@ -36447,22 +36555,22 @@
         <v>61.583999880000007</v>
       </c>
       <c r="P19" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6">
+        <v>0</v>
+      </c>
+      <c r="S19" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6">
-        <v>0</v>
-      </c>
-      <c r="S19" s="13">
-        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="T19" s="17"/>
       <c r="U19" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="V19" s="6">
@@ -36501,39 +36609,38 @@
         <v>168.5039999</v>
       </c>
       <c r="D20" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E20" s="7">
+      <c r="F20" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F20" s="7">
+      <c r="G20" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G20" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
       <c r="H20" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I20" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J20" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K20" s="6">
-        <v>0</v>
-      </c>
-      <c r="L20" s="13">
-        <v>35</v>
-      </c>
-      <c r="M20" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L20" s="29">
+        <v>30</v>
+      </c>
+      <c r="M20" s="29">
+        <v>10</v>
       </c>
       <c r="N20" s="29">
         <v>306.4799993999996</v>
@@ -36542,21 +36649,21 @@
         <v>57.959999910000008</v>
       </c>
       <c r="P20" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6">
+        <v>0</v>
+      </c>
+      <c r="S20" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="6">
-        <v>0</v>
-      </c>
-      <c r="R20" s="6">
-        <v>0</v>
-      </c>
-      <c r="S20" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
       <c r="U20" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="V20" s="6">
@@ -36595,39 +36702,38 @@
         <v>166.10999993000001</v>
       </c>
       <c r="D21" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E21" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E21" s="7">
+      <c r="F21" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F21" s="7">
+      <c r="G21" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G21" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
       <c r="H21" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I21" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J21" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K21" s="6">
-        <v>0</v>
-      </c>
-      <c r="L21" s="13">
-        <v>35</v>
-      </c>
-      <c r="M21" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L21" s="29">
+        <v>30</v>
+      </c>
+      <c r="M21" s="29">
+        <v>10</v>
       </c>
       <c r="N21" s="29">
         <v>307.53599938999997</v>
@@ -36636,21 +36742,21 @@
         <v>62.831999879999998</v>
       </c>
       <c r="P21" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>0</v>
+      </c>
+      <c r="R21" s="6">
+        <v>0</v>
+      </c>
+      <c r="S21" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="6">
-        <v>0</v>
-      </c>
-      <c r="R21" s="6">
-        <v>0</v>
-      </c>
-      <c r="S21" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
       <c r="U21" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="V21" s="6">
@@ -36689,39 +36795,38 @@
         <v>182.44799993000001</v>
       </c>
       <c r="D22" s="7">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="E22" s="7">
         <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="E22" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="F22" s="7">
         <f t="shared" si="4"/>
-        <v>2.6</v>
-      </c>
-      <c r="F22" s="7">
+        <v>29</v>
+      </c>
+      <c r="G22" s="7">
         <f t="shared" si="5"/>
-        <v>29</v>
-      </c>
-      <c r="G22" s="7">
-        <f t="shared" si="6"/>
         <v>3.77</v>
       </c>
       <c r="H22" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I22" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J22" s="13">
-        <f t="shared" si="8"/>
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K22" s="6">
-        <v>0</v>
-      </c>
-      <c r="L22" s="13">
-        <v>35</v>
-      </c>
-      <c r="M22" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L22" s="29">
+        <v>30</v>
+      </c>
+      <c r="M22" s="29">
+        <v>10</v>
       </c>
       <c r="N22" s="29">
         <v>310.70399932999993</v>
@@ -36730,21 +36835,21 @@
         <v>61.223999889999995</v>
       </c>
       <c r="P22" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>0</v>
+      </c>
+      <c r="R22" s="6">
+        <v>0</v>
+      </c>
+      <c r="S22" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="6">
-        <v>0</v>
-      </c>
-      <c r="R22" s="6">
-        <v>0</v>
-      </c>
-      <c r="S22" s="13">
-        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="U22" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="V22" s="6">
@@ -36783,39 +36888,38 @@
         <v>152.54399995999998</v>
       </c>
       <c r="D23" s="7">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="E23" s="7">
         <f t="shared" si="3"/>
-        <v>28</v>
-      </c>
-      <c r="E23" s="7">
+        <v>3.64</v>
+      </c>
+      <c r="F23" s="7">
         <f t="shared" si="4"/>
-        <v>3.64</v>
-      </c>
-      <c r="F23" s="7">
+        <v>55</v>
+      </c>
+      <c r="G23" s="7">
         <f t="shared" si="5"/>
-        <v>55</v>
-      </c>
-      <c r="G23" s="7">
-        <f t="shared" si="6"/>
         <v>7.15</v>
       </c>
       <c r="H23" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I23" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J23" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K23" s="6">
-        <v>0</v>
-      </c>
-      <c r="L23" s="13">
-        <v>35</v>
-      </c>
-      <c r="M23" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L23" s="29">
+        <v>30</v>
+      </c>
+      <c r="M23" s="29">
+        <v>10</v>
       </c>
       <c r="N23" s="29">
         <v>306.8159992799998</v>
@@ -36824,21 +36928,21 @@
         <v>57.695999899999997</v>
       </c>
       <c r="P23" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>0</v>
+      </c>
+      <c r="R23" s="6">
+        <v>0</v>
+      </c>
+      <c r="S23" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="6">
-        <v>0</v>
-      </c>
-      <c r="R23" s="6">
-        <v>0</v>
-      </c>
-      <c r="S23" s="13">
-        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="U23" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="V23" s="9">
@@ -36877,39 +36981,38 @@
         <v>240.32399992000001</v>
       </c>
       <c r="D24" s="7">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="E24" s="7">
         <f t="shared" si="3"/>
-        <v>34</v>
-      </c>
-      <c r="E24" s="7">
+        <v>4.42</v>
+      </c>
+      <c r="F24" s="7">
         <f t="shared" si="4"/>
-        <v>4.42</v>
-      </c>
-      <c r="F24" s="7">
+        <v>56</v>
+      </c>
+      <c r="G24" s="7">
         <f t="shared" si="5"/>
-        <v>56</v>
-      </c>
-      <c r="G24" s="7">
-        <f t="shared" si="6"/>
         <v>7.28</v>
       </c>
       <c r="H24" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I24" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J24" s="13">
-        <f t="shared" si="8"/>
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K24" s="6">
-        <v>0</v>
-      </c>
-      <c r="L24" s="13">
-        <v>35</v>
-      </c>
-      <c r="M24" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L24" s="29">
+        <v>30</v>
+      </c>
+      <c r="M24" s="29">
+        <v>10</v>
       </c>
       <c r="N24" s="29">
         <v>275.3279993499998</v>
@@ -36918,21 +37021,21 @@
         <v>66.887999909999991</v>
       </c>
       <c r="P24" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0</v>
+      </c>
+      <c r="R24" s="6">
+        <v>0</v>
+      </c>
+      <c r="S24" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="6">
-        <v>0</v>
-      </c>
-      <c r="R24" s="6">
-        <v>0</v>
-      </c>
-      <c r="S24" s="13">
-        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="U24" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="V24" s="9">
@@ -36971,39 +37074,38 @@
         <v>219.99599992999998</v>
       </c>
       <c r="D25" s="7">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="E25" s="7">
         <f t="shared" si="3"/>
-        <v>57</v>
-      </c>
-      <c r="E25" s="7">
+        <v>7.41</v>
+      </c>
+      <c r="F25" s="7">
         <f t="shared" si="4"/>
-        <v>7.41</v>
-      </c>
-      <c r="F25" s="7">
+        <v>67</v>
+      </c>
+      <c r="G25" s="7">
         <f t="shared" si="5"/>
-        <v>67</v>
-      </c>
-      <c r="G25" s="7">
-        <f t="shared" si="6"/>
         <v>8.7100000000000009</v>
       </c>
       <c r="H25" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I25" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J25" s="13">
-        <f t="shared" si="8"/>
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K25" s="6">
-        <v>0</v>
-      </c>
-      <c r="L25" s="13">
-        <v>35</v>
-      </c>
-      <c r="M25" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L25" s="29">
+        <v>30</v>
+      </c>
+      <c r="M25" s="29">
+        <v>10</v>
       </c>
       <c r="N25" s="29">
         <v>248.49599941999989</v>
@@ -37012,21 +37114,21 @@
         <v>61.775999880000001</v>
       </c>
       <c r="P25" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>0</v>
+      </c>
+      <c r="R25" s="6">
+        <v>0</v>
+      </c>
+      <c r="S25" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>0</v>
-      </c>
-      <c r="R25" s="6">
-        <v>0</v>
-      </c>
-      <c r="S25" s="13">
-        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="U25" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="V25" s="34">
@@ -37065,39 +37167,38 @@
         <v>211.63799988999997</v>
       </c>
       <c r="D26" s="7">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="E26" s="7">
         <f t="shared" si="3"/>
-        <v>63</v>
-      </c>
-      <c r="E26" s="7">
+        <v>8.19</v>
+      </c>
+      <c r="F26" s="7">
         <f t="shared" si="4"/>
-        <v>8.19</v>
-      </c>
-      <c r="F26" s="7">
+        <v>70</v>
+      </c>
+      <c r="G26" s="7">
         <f t="shared" si="5"/>
-        <v>70</v>
-      </c>
-      <c r="G26" s="7">
-        <f t="shared" si="6"/>
         <v>9.1</v>
       </c>
       <c r="H26" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I26" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J26" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K26" s="6">
-        <v>0</v>
-      </c>
-      <c r="L26" s="13">
-        <v>35</v>
-      </c>
-      <c r="M26" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L26" s="29">
+        <v>30</v>
+      </c>
+      <c r="M26" s="29">
+        <v>10</v>
       </c>
       <c r="N26" s="29">
         <v>265.36799933999993</v>
@@ -37106,21 +37207,21 @@
         <v>55.703999900000007</v>
       </c>
       <c r="P26" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>0</v>
+      </c>
+      <c r="R26" s="6">
+        <v>0</v>
+      </c>
+      <c r="S26" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="6">
-        <v>0</v>
-      </c>
-      <c r="R26" s="6">
-        <v>0</v>
-      </c>
-      <c r="S26" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
       <c r="U26" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="V26" s="6">
@@ -37159,39 +37260,38 @@
         <v>190.34399994999998</v>
       </c>
       <c r="D27" s="7">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="E27" s="7">
         <f t="shared" si="3"/>
-        <v>33</v>
-      </c>
-      <c r="E27" s="7">
+        <v>4.29</v>
+      </c>
+      <c r="F27" s="7">
         <f t="shared" si="4"/>
-        <v>4.29</v>
-      </c>
-      <c r="F27" s="7">
+        <v>34</v>
+      </c>
+      <c r="G27" s="7">
         <f t="shared" si="5"/>
-        <v>34</v>
-      </c>
-      <c r="G27" s="7">
-        <f t="shared" si="6"/>
         <v>4.42</v>
       </c>
       <c r="H27" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I27" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J27" s="13">
-        <f t="shared" si="8"/>
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K27" s="6">
-        <v>0</v>
-      </c>
-      <c r="L27" s="13">
-        <v>35</v>
-      </c>
-      <c r="M27" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L27" s="29">
+        <v>30</v>
+      </c>
+      <c r="M27" s="29">
+        <v>10</v>
       </c>
       <c r="N27" s="29">
         <v>246.43199937999987</v>
@@ -37200,21 +37300,21 @@
         <v>60.263999900000002</v>
       </c>
       <c r="P27" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>0</v>
+      </c>
+      <c r="R27" s="6">
+        <v>0</v>
+      </c>
+      <c r="S27" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="6">
-        <v>0</v>
-      </c>
-      <c r="R27" s="6">
-        <v>0</v>
-      </c>
-      <c r="S27" s="13">
-        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="U27" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>25</v>
       </c>
       <c r="V27" s="6">
@@ -37253,39 +37353,38 @@
         <v>183.91799988999998</v>
       </c>
       <c r="D28" s="7">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="E28" s="7">
         <f t="shared" si="3"/>
-        <v>49</v>
-      </c>
-      <c r="E28" s="7">
+        <v>6.37</v>
+      </c>
+      <c r="F28" s="7">
         <f t="shared" si="4"/>
-        <v>6.37</v>
-      </c>
-      <c r="F28" s="7">
+        <v>28</v>
+      </c>
+      <c r="G28" s="7">
         <f t="shared" si="5"/>
-        <v>28</v>
-      </c>
-      <c r="G28" s="7">
-        <f t="shared" si="6"/>
         <v>3.64</v>
       </c>
       <c r="H28" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I28" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J28" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K28" s="6">
-        <v>0</v>
-      </c>
-      <c r="L28" s="13">
-        <v>35</v>
-      </c>
-      <c r="M28" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L28" s="29">
+        <v>30</v>
+      </c>
+      <c r="M28" s="29">
+        <v>10</v>
       </c>
       <c r="N28" s="29">
         <v>249.74399931999994</v>
@@ -37294,21 +37393,21 @@
         <v>54.815999890000001</v>
       </c>
       <c r="P28" s="13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0</v>
+      </c>
+      <c r="R28" s="6">
+        <v>0</v>
+      </c>
+      <c r="S28" s="13">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="Q28" s="6">
-        <v>0</v>
-      </c>
-      <c r="R28" s="6">
-        <v>0</v>
-      </c>
-      <c r="S28" s="13">
-        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="U28" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
       <c r="V28" s="19">
@@ -37347,39 +37446,38 @@
         <v>152.66999990999997</v>
       </c>
       <c r="D29" s="7">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="E29" s="7">
         <f t="shared" si="3"/>
-        <v>58</v>
-      </c>
-      <c r="E29" s="7">
+        <v>7.54</v>
+      </c>
+      <c r="F29" s="7">
         <f t="shared" si="4"/>
-        <v>7.54</v>
-      </c>
-      <c r="F29" s="7">
+        <v>46</v>
+      </c>
+      <c r="G29" s="7">
         <f t="shared" si="5"/>
-        <v>46</v>
-      </c>
-      <c r="G29" s="7">
-        <f t="shared" si="6"/>
         <v>5.98</v>
       </c>
       <c r="H29" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I29" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J29" s="13">
-        <f t="shared" si="8"/>
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K29" s="6">
-        <v>0</v>
-      </c>
-      <c r="L29" s="13">
-        <v>35</v>
-      </c>
-      <c r="M29" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L29" s="29">
+        <v>30</v>
+      </c>
+      <c r="M29" s="29">
+        <v>10</v>
       </c>
       <c r="N29" s="29">
         <v>273.47999938999976</v>
@@ -37388,21 +37486,21 @@
         <v>64.199999910000003</v>
       </c>
       <c r="P29" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="6">
+        <v>0</v>
+      </c>
+      <c r="R29" s="6">
+        <v>0</v>
+      </c>
+      <c r="S29" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="6">
-        <v>0</v>
-      </c>
-      <c r="R29" s="6">
-        <v>0</v>
-      </c>
-      <c r="S29" s="13">
-        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="U29" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>27</v>
       </c>
       <c r="V29" s="15">
@@ -37441,39 +37539,38 @@
         <v>166.78199988999998</v>
       </c>
       <c r="D30" s="7">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="E30" s="7">
         <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="E30" s="7">
+        <v>1.69</v>
+      </c>
+      <c r="F30" s="7">
         <f t="shared" si="4"/>
-        <v>1.69</v>
-      </c>
-      <c r="F30" s="7">
+        <v>52</v>
+      </c>
+      <c r="G30" s="7">
         <f t="shared" si="5"/>
-        <v>52</v>
-      </c>
-      <c r="G30" s="7">
-        <f t="shared" si="6"/>
         <v>6.76</v>
       </c>
       <c r="H30" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I30" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J30" s="13">
-        <f t="shared" si="8"/>
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K30" s="6">
-        <v>0</v>
-      </c>
-      <c r="L30" s="13">
-        <v>35</v>
-      </c>
-      <c r="M30" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L30" s="29">
+        <v>30</v>
+      </c>
+      <c r="M30" s="29">
+        <v>10</v>
       </c>
       <c r="N30" s="29">
         <v>291.28799944999969</v>
@@ -37482,21 +37579,21 @@
         <v>59.903999889999994</v>
       </c>
       <c r="P30" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>0</v>
+      </c>
+      <c r="R30" s="6">
+        <v>0</v>
+      </c>
+      <c r="S30" s="13">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q30" s="6">
-        <v>0</v>
-      </c>
-      <c r="R30" s="6">
-        <v>0</v>
-      </c>
-      <c r="S30" s="13">
-        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="U30" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>28</v>
       </c>
       <c r="V30" s="15">
@@ -37535,11 +37632,11 @@
         <v>196.76999993000001</v>
       </c>
       <c r="D31" s="7">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="E31" s="7">
         <f t="shared" si="3"/>
-        <v>34</v>
-      </c>
-      <c r="E31" s="7">
-        <f t="shared" si="4"/>
         <v>4.42</v>
       </c>
       <c r="F31" s="7">
@@ -37547,27 +37644,26 @@
         <v>63</v>
       </c>
       <c r="G31" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.19</v>
       </c>
       <c r="H31" s="29">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="I31" s="7">
-        <v>38</v>
+        <v>39.333333333333336</v>
       </c>
       <c r="J31" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K31" s="6">
-        <v>0</v>
-      </c>
-      <c r="L31" s="13">
-        <v>35</v>
-      </c>
-      <c r="M31" s="13">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="L31" s="29">
+        <v>30</v>
+      </c>
+      <c r="M31" s="29">
+        <v>10</v>
       </c>
       <c r="N31" s="29">
         <v>236.15999938999974</v>
@@ -37576,21 +37672,21 @@
         <v>52.031999909999996</v>
       </c>
       <c r="P31" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>0</v>
+      </c>
+      <c r="R31" s="6">
+        <v>0</v>
+      </c>
+      <c r="S31" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>0</v>
-      </c>
-      <c r="R31" s="6">
-        <v>0</v>
-      </c>
-      <c r="S31" s="13">
-        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="U31" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="V31" s="15">
@@ -37624,7 +37720,7 @@
       <c r="F32" s="37"/>
       <c r="G32" s="37"/>
       <c r="U32" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="V32" s="15">
@@ -38918,7 +39014,7 @@
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="F2:F31" formula="1"/>
+    <ignoredError sqref="F3:F15 F20:F31 F17" formula="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5C6A11-446C-4948-9D28-7E601B5A8FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96152EB8-A8BB-442B-BE52-2F68580DD470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -418,7 +418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -549,6 +549,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -811,17 +813,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{343B5D31-DB35-40E5-8AAC-64B51E6DA6BC}">
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.140625" bestFit="1" customWidth="1"/>
@@ -895,46 +897,46 @@
         <v>33</v>
       </c>
       <c r="B2" s="42">
-        <v>0</v>
+        <v>33257.08</v>
       </c>
       <c r="C2" s="42">
-        <v>0</v>
+        <v>11421.12</v>
       </c>
       <c r="D2" s="42">
-        <v>0</v>
+        <v>1005.039</v>
       </c>
       <c r="E2" s="42">
-        <v>0</v>
+        <v>430.73099999999999</v>
       </c>
       <c r="F2" s="42">
-        <v>0</v>
+        <v>2233.7629999999999</v>
       </c>
       <c r="G2" s="42">
-        <v>0</v>
+        <v>957.327</v>
       </c>
       <c r="H2" s="42">
-        <v>0</v>
+        <v>3425.681</v>
       </c>
       <c r="I2" s="42">
-        <v>0</v>
+        <v>1468.1489999999999</v>
       </c>
       <c r="J2" s="42">
-        <v>0</v>
+        <v>905.95399999999995</v>
       </c>
       <c r="K2" s="42">
-        <v>0</v>
+        <v>388.26600000000002</v>
       </c>
       <c r="L2" s="42">
-        <v>0</v>
+        <v>679.46900000000005</v>
       </c>
       <c r="M2" s="42">
-        <v>0</v>
+        <v>291.20099999999996</v>
       </c>
       <c r="N2" s="42">
-        <v>0</v>
+        <v>7546.52</v>
       </c>
       <c r="O2" s="42">
-        <v>0</v>
+        <v>3690.74</v>
       </c>
       <c r="P2" s="42">
         <v>0</v>
@@ -954,46 +956,46 @@
         <v>34</v>
       </c>
       <c r="B3" s="42">
-        <v>0</v>
+        <v>34662.639999999999</v>
       </c>
       <c r="C3" s="42">
-        <v>0</v>
+        <v>12923.27</v>
       </c>
       <c r="D3" s="42">
-        <v>0</v>
+        <v>1301.9720000000002</v>
       </c>
       <c r="E3" s="42">
-        <v>0</v>
+        <v>557.98799999999994</v>
       </c>
       <c r="F3" s="42">
-        <v>0</v>
+        <v>2088.422</v>
       </c>
       <c r="G3" s="42">
-        <v>0</v>
+        <v>895.03800000000001</v>
       </c>
       <c r="H3" s="42">
-        <v>0</v>
+        <v>2921.0790000000002</v>
       </c>
       <c r="I3" s="42">
-        <v>0</v>
+        <v>1251.8910000000001</v>
       </c>
       <c r="J3" s="42">
-        <v>0</v>
+        <v>1145.5150000000001</v>
       </c>
       <c r="K3" s="42">
-        <v>0</v>
+        <v>490.935</v>
       </c>
       <c r="L3" s="42">
-        <v>0</v>
+        <v>687.30200000000002</v>
       </c>
       <c r="M3" s="42">
-        <v>0</v>
+        <v>294.55799999999999</v>
       </c>
       <c r="N3" s="42">
-        <v>0</v>
+        <v>7279.59</v>
       </c>
       <c r="O3" s="42">
-        <v>0</v>
+        <v>3440.58</v>
       </c>
       <c r="P3" s="42">
         <v>0</v>
@@ -1013,46 +1015,46 @@
         <v>35</v>
       </c>
       <c r="B4" s="42">
-        <v>0</v>
+        <v>38732.559999999998</v>
       </c>
       <c r="C4" s="42">
-        <v>0</v>
+        <v>15148.14</v>
       </c>
       <c r="D4" s="42">
-        <v>0</v>
+        <v>1557.6750000000002</v>
       </c>
       <c r="E4" s="42">
-        <v>0</v>
+        <v>667.57499999999993</v>
       </c>
       <c r="F4" s="42">
-        <v>0</v>
+        <v>2790.0039999999999</v>
       </c>
       <c r="G4" s="42">
-        <v>0</v>
+        <v>1195.7159999999999</v>
       </c>
       <c r="H4" s="42">
-        <v>0</v>
+        <v>3189.4030000000002</v>
       </c>
       <c r="I4" s="42">
-        <v>0</v>
+        <v>1366.8869999999999</v>
       </c>
       <c r="J4" s="42">
-        <v>0</v>
+        <v>1139.068</v>
       </c>
       <c r="K4" s="42">
-        <v>0</v>
+        <v>488.17199999999997</v>
       </c>
       <c r="L4" s="42">
-        <v>0</v>
+        <v>854.28700000000003</v>
       </c>
       <c r="M4" s="42">
-        <v>0</v>
+        <v>366.12299999999999</v>
       </c>
       <c r="N4" s="42">
-        <v>0</v>
+        <v>8302.77</v>
       </c>
       <c r="O4" s="42">
-        <v>0</v>
+        <v>4094.98</v>
       </c>
       <c r="P4" s="42">
         <v>0</v>
@@ -1072,46 +1074,46 @@
         <v>36</v>
       </c>
       <c r="B5" s="42">
-        <v>0</v>
+        <v>32733.990000000005</v>
       </c>
       <c r="C5" s="42">
-        <v>0</v>
+        <v>13320.42</v>
       </c>
       <c r="D5" s="42">
-        <v>0</v>
+        <v>1614.8509999999999</v>
       </c>
       <c r="E5" s="42">
-        <v>0</v>
+        <v>692.07899999999995</v>
       </c>
       <c r="F5" s="42">
-        <v>0</v>
+        <v>2178.3229999999999</v>
       </c>
       <c r="G5" s="42">
-        <v>0</v>
+        <v>933.56699999999989</v>
       </c>
       <c r="H5" s="42">
-        <v>0</v>
+        <v>3332.7980000000002</v>
       </c>
       <c r="I5" s="42">
-        <v>0</v>
+        <v>1428.3420000000001</v>
       </c>
       <c r="J5" s="42">
-        <v>0</v>
+        <v>57.882999999999996</v>
       </c>
       <c r="K5" s="42">
-        <v>0</v>
+        <v>24.806999999999999</v>
       </c>
       <c r="L5" s="42">
-        <v>0</v>
+        <v>847.30799999999999</v>
       </c>
       <c r="M5" s="42">
-        <v>0</v>
+        <v>363.13200000000001</v>
       </c>
       <c r="N5" s="42">
-        <v>0</v>
+        <v>7360.23</v>
       </c>
       <c r="O5" s="42">
-        <v>0</v>
+        <v>3442.02</v>
       </c>
       <c r="P5" s="42">
         <v>0</v>
@@ -1131,46 +1133,46 @@
         <v>37</v>
       </c>
       <c r="B6" s="42">
-        <v>0</v>
+        <v>29658.6</v>
       </c>
       <c r="C6" s="42">
-        <v>0</v>
+        <v>11856.09</v>
       </c>
       <c r="D6" s="42">
-        <v>0</v>
+        <v>1413.5519999999999</v>
       </c>
       <c r="E6" s="42">
-        <v>0</v>
+        <v>605.80799999999999</v>
       </c>
       <c r="F6" s="42">
-        <v>0</v>
+        <v>1600.9770000000001</v>
       </c>
       <c r="G6" s="42">
-        <v>0</v>
+        <v>686.13300000000004</v>
       </c>
       <c r="H6" s="42">
-        <v>0</v>
+        <v>3361.0920000000006</v>
       </c>
       <c r="I6" s="42">
-        <v>0</v>
+        <v>1440.4680000000001</v>
       </c>
       <c r="J6" s="42">
-        <v>0</v>
+        <v>1038.4780000000001</v>
       </c>
       <c r="K6" s="42">
-        <v>0</v>
+        <v>445.06199999999995</v>
       </c>
       <c r="L6" s="42">
-        <v>0</v>
+        <v>1036.8610000000001</v>
       </c>
       <c r="M6" s="42">
-        <v>0</v>
+        <v>444.36899999999997</v>
       </c>
       <c r="N6" s="42">
-        <v>0</v>
+        <v>6618.68</v>
       </c>
       <c r="O6" s="42">
-        <v>0</v>
+        <v>3472.13</v>
       </c>
       <c r="P6" s="42">
         <v>0</v>
@@ -1597,6 +1599,13 @@
       <c r="S13" s="42">
         <v>0</v>
       </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="E16" s="48"/>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96152EB8-A8BB-442B-BE52-2F68580DD470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7087546A-9556-4AEC-8092-C803F1EDD517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -542,6 +542,8 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -549,8 +551,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1601,11 +1601,11 @@
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="E16" s="48"/>
+      <c r="E16" s="45"/>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -4732,15 +4732,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="45"/>
-      <c r="B69" s="45"/>
-      <c r="C69" s="45"/>
-      <c r="D69" s="45"/>
-      <c r="E69" s="45"/>
-      <c r="F69" s="45"/>
-      <c r="G69" s="45"/>
-      <c r="H69" s="45"/>
-      <c r="I69" s="45"/>
+      <c r="A69" s="47"/>
+      <c r="B69" s="47"/>
+      <c r="C69" s="47"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="47"/>
+      <c r="G69" s="47"/>
+      <c r="H69" s="47"/>
+      <c r="I69" s="47"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -4765,15 +4765,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="46"/>
-      <c r="B74" s="46"/>
-      <c r="C74" s="46"/>
-      <c r="D74" s="46"/>
-      <c r="E74" s="46"/>
-      <c r="F74" s="46"/>
-      <c r="G74" s="46"/>
-      <c r="H74" s="46"/>
-      <c r="I74" s="46"/>
+      <c r="A74" s="48"/>
+      <c r="B74" s="48"/>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -4809,15 +4809,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="47"/>
-      <c r="B78" s="47"/>
-      <c r="C78" s="47"/>
-      <c r="D78" s="47"/>
-      <c r="E78" s="47"/>
-      <c r="F78" s="47"/>
-      <c r="G78" s="47"/>
-      <c r="H78" s="47"/>
-      <c r="I78" s="47"/>
+      <c r="A78" s="49"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="49"/>
+      <c r="D78" s="49"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="49"/>
+      <c r="G78" s="49"/>
+      <c r="H78" s="49"/>
+      <c r="I78" s="49"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -4853,15 +4853,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="46"/>
-      <c r="B86" s="46"/>
-      <c r="C86" s="46"/>
-      <c r="D86" s="46"/>
-      <c r="E86" s="46"/>
-      <c r="F86" s="46"/>
-      <c r="G86" s="46"/>
-      <c r="H86" s="46"/>
-      <c r="I86" s="46"/>
+      <c r="A86" s="48"/>
+      <c r="B86" s="48"/>
+      <c r="C86" s="48"/>
+      <c r="D86" s="48"/>
+      <c r="E86" s="48"/>
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="48"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -4964,15 +4964,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="45"/>
-      <c r="B99" s="45"/>
-      <c r="C99" s="45"/>
-      <c r="D99" s="45"/>
-      <c r="E99" s="45"/>
-      <c r="F99" s="45"/>
-      <c r="G99" s="45"/>
-      <c r="H99" s="45"/>
-      <c r="I99" s="45"/>
+      <c r="A99" s="47"/>
+      <c r="B99" s="47"/>
+      <c r="C99" s="47"/>
+      <c r="D99" s="47"/>
+      <c r="E99" s="47"/>
+      <c r="F99" s="47"/>
+      <c r="G99" s="47"/>
+      <c r="H99" s="47"/>
+      <c r="I99" s="47"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -8138,14 +8138,14 @@
     <row r="34" spans="1:29" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -8522,15 +8522,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="45"/>
-      <c r="B71" s="45"/>
-      <c r="C71" s="45"/>
-      <c r="D71" s="45"/>
-      <c r="E71" s="45"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="45"/>
-      <c r="H71" s="45"/>
-      <c r="I71" s="45"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -8555,15 +8555,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="46"/>
-      <c r="B76" s="46"/>
-      <c r="C76" s="46"/>
-      <c r="D76" s="46"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="46"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -8599,15 +8599,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="47"/>
-      <c r="B80" s="47"/>
-      <c r="C80" s="47"/>
-      <c r="D80" s="47"/>
-      <c r="E80" s="47"/>
-      <c r="F80" s="47"/>
-      <c r="G80" s="47"/>
-      <c r="H80" s="47"/>
-      <c r="I80" s="47"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -8643,15 +8643,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="46"/>
-      <c r="B88" s="46"/>
-      <c r="C88" s="46"/>
-      <c r="D88" s="46"/>
-      <c r="E88" s="46"/>
-      <c r="F88" s="46"/>
-      <c r="G88" s="46"/>
-      <c r="H88" s="46"/>
-      <c r="I88" s="46"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -8754,15 +8754,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="45"/>
-      <c r="B101" s="45"/>
-      <c r="C101" s="45"/>
-      <c r="D101" s="45"/>
-      <c r="E101" s="45"/>
-      <c r="F101" s="45"/>
-      <c r="G101" s="45"/>
-      <c r="H101" s="45"/>
-      <c r="I101" s="45"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -11103,14 +11103,14 @@
     </row>
     <row r="32" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
@@ -11487,15 +11487,15 @@
       <c r="I66" s="1"/>
     </row>
     <row r="67" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="45"/>
-      <c r="B67" s="45"/>
-      <c r="C67" s="45"/>
-      <c r="D67" s="45"/>
-      <c r="E67" s="45"/>
-      <c r="F67" s="45"/>
-      <c r="G67" s="45"/>
-      <c r="H67" s="45"/>
-      <c r="I67" s="45"/>
+      <c r="A67" s="47"/>
+      <c r="B67" s="47"/>
+      <c r="C67" s="47"/>
+      <c r="D67" s="47"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="47"/>
+      <c r="G67" s="47"/>
+      <c r="H67" s="47"/>
+      <c r="I67" s="47"/>
     </row>
     <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
@@ -11520,15 +11520,15 @@
       <c r="I69" s="23"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="46"/>
-      <c r="B72" s="46"/>
-      <c r="C72" s="46"/>
-      <c r="D72" s="46"/>
-      <c r="E72" s="46"/>
-      <c r="F72" s="46"/>
-      <c r="G72" s="46"/>
-      <c r="H72" s="46"/>
-      <c r="I72" s="46"/>
+      <c r="A72" s="48"/>
+      <c r="B72" s="48"/>
+      <c r="C72" s="48"/>
+      <c r="D72" s="48"/>
+      <c r="E72" s="48"/>
+      <c r="F72" s="48"/>
+      <c r="G72" s="48"/>
+      <c r="H72" s="48"/>
+      <c r="I72" s="48"/>
     </row>
     <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
@@ -11564,15 +11564,15 @@
       <c r="I75" s="25"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="47"/>
-      <c r="B76" s="47"/>
-      <c r="C76" s="47"/>
-      <c r="D76" s="47"/>
-      <c r="E76" s="47"/>
-      <c r="F76" s="47"/>
-      <c r="G76" s="47"/>
-      <c r="H76" s="47"/>
-      <c r="I76" s="47"/>
+      <c r="A76" s="49"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="49"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -11608,15 +11608,15 @@
       <c r="B82" s="23"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="46"/>
-      <c r="B84" s="46"/>
-      <c r="C84" s="46"/>
-      <c r="D84" s="46"/>
-      <c r="E84" s="46"/>
-      <c r="F84" s="46"/>
-      <c r="G84" s="46"/>
-      <c r="H84" s="46"/>
-      <c r="I84" s="46"/>
+      <c r="A84" s="48"/>
+      <c r="B84" s="48"/>
+      <c r="C84" s="48"/>
+      <c r="D84" s="48"/>
+      <c r="E84" s="48"/>
+      <c r="F84" s="48"/>
+      <c r="G84" s="48"/>
+      <c r="H84" s="48"/>
+      <c r="I84" s="48"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
@@ -11719,15 +11719,15 @@
       <c r="B95" s="26"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="45"/>
-      <c r="B97" s="45"/>
-      <c r="C97" s="45"/>
-      <c r="D97" s="45"/>
-      <c r="E97" s="45"/>
-      <c r="F97" s="45"/>
-      <c r="G97" s="45"/>
-      <c r="H97" s="45"/>
-      <c r="I97" s="45"/>
+      <c r="A97" s="47"/>
+      <c r="B97" s="47"/>
+      <c r="C97" s="47"/>
+      <c r="D97" s="47"/>
+      <c r="E97" s="47"/>
+      <c r="F97" s="47"/>
+      <c r="G97" s="47"/>
+      <c r="H97" s="47"/>
+      <c r="I97" s="47"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
@@ -14243,14 +14243,14 @@
     <row r="34" spans="1:20" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -14627,15 +14627,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="45"/>
-      <c r="B71" s="45"/>
-      <c r="C71" s="45"/>
-      <c r="D71" s="45"/>
-      <c r="E71" s="45"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="45"/>
-      <c r="H71" s="45"/>
-      <c r="I71" s="45"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -14660,15 +14660,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="46"/>
-      <c r="B76" s="46"/>
-      <c r="C76" s="46"/>
-      <c r="D76" s="46"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="46"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -14704,15 +14704,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="47"/>
-      <c r="B80" s="47"/>
-      <c r="C80" s="47"/>
-      <c r="D80" s="47"/>
-      <c r="E80" s="47"/>
-      <c r="F80" s="47"/>
-      <c r="G80" s="47"/>
-      <c r="H80" s="47"/>
-      <c r="I80" s="47"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -14748,15 +14748,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="46"/>
-      <c r="B88" s="46"/>
-      <c r="C88" s="46"/>
-      <c r="D88" s="46"/>
-      <c r="E88" s="46"/>
-      <c r="F88" s="46"/>
-      <c r="G88" s="46"/>
-      <c r="H88" s="46"/>
-      <c r="I88" s="46"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -14859,15 +14859,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="45"/>
-      <c r="B101" s="45"/>
-      <c r="C101" s="45"/>
-      <c r="D101" s="45"/>
-      <c r="E101" s="45"/>
-      <c r="F101" s="45"/>
-      <c r="G101" s="45"/>
-      <c r="H101" s="45"/>
-      <c r="I101" s="45"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -17568,14 +17568,14 @@
     </row>
     <row r="35" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="45"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
     </row>
     <row r="36" spans="1:20" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -17953,15 +17953,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="45"/>
-      <c r="B70" s="45"/>
-      <c r="C70" s="45"/>
-      <c r="D70" s="45"/>
-      <c r="E70" s="45"/>
-      <c r="F70" s="45"/>
-      <c r="G70" s="45"/>
-      <c r="H70" s="45"/>
-      <c r="I70" s="45"/>
+      <c r="A70" s="47"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -17986,15 +17986,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="46"/>
-      <c r="B75" s="46"/>
-      <c r="C75" s="46"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="46"/>
+      <c r="A75" s="48"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -18030,15 +18030,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="47"/>
-      <c r="B79" s="47"/>
-      <c r="C79" s="47"/>
-      <c r="D79" s="47"/>
-      <c r="E79" s="47"/>
-      <c r="F79" s="47"/>
-      <c r="G79" s="47"/>
-      <c r="H79" s="47"/>
-      <c r="I79" s="47"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -18074,15 +18074,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="46"/>
-      <c r="B87" s="46"/>
-      <c r="C87" s="46"/>
-      <c r="D87" s="46"/>
-      <c r="E87" s="46"/>
-      <c r="F87" s="46"/>
-      <c r="G87" s="46"/>
-      <c r="H87" s="46"/>
-      <c r="I87" s="46"/>
+      <c r="A87" s="48"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -18185,15 +18185,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="45"/>
-      <c r="B100" s="45"/>
-      <c r="C100" s="45"/>
-      <c r="D100" s="45"/>
-      <c r="E100" s="45"/>
-      <c r="F100" s="45"/>
-      <c r="G100" s="45"/>
-      <c r="H100" s="45"/>
-      <c r="I100" s="45"/>
+      <c r="A100" s="47"/>
+      <c r="B100" s="47"/>
+      <c r="C100" s="47"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="47"/>
+      <c r="I100" s="47"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -20786,14 +20786,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="45"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -21171,15 +21171,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="45"/>
-      <c r="B70" s="45"/>
-      <c r="C70" s="45"/>
-      <c r="D70" s="45"/>
-      <c r="E70" s="45"/>
-      <c r="F70" s="45"/>
-      <c r="G70" s="45"/>
-      <c r="H70" s="45"/>
-      <c r="I70" s="45"/>
+      <c r="A70" s="47"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -21204,15 +21204,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="46"/>
-      <c r="B75" s="46"/>
-      <c r="C75" s="46"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="46"/>
+      <c r="A75" s="48"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -21248,15 +21248,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="47"/>
-      <c r="B79" s="47"/>
-      <c r="C79" s="47"/>
-      <c r="D79" s="47"/>
-      <c r="E79" s="47"/>
-      <c r="F79" s="47"/>
-      <c r="G79" s="47"/>
-      <c r="H79" s="47"/>
-      <c r="I79" s="47"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -21292,15 +21292,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="46"/>
-      <c r="B87" s="46"/>
-      <c r="C87" s="46"/>
-      <c r="D87" s="46"/>
-      <c r="E87" s="46"/>
-      <c r="F87" s="46"/>
-      <c r="G87" s="46"/>
-      <c r="H87" s="46"/>
-      <c r="I87" s="46"/>
+      <c r="A87" s="48"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -21403,15 +21403,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="45"/>
-      <c r="B100" s="45"/>
-      <c r="C100" s="45"/>
-      <c r="D100" s="45"/>
-      <c r="E100" s="45"/>
-      <c r="F100" s="45"/>
-      <c r="G100" s="45"/>
-      <c r="H100" s="45"/>
-      <c r="I100" s="45"/>
+      <c r="A100" s="47"/>
+      <c r="B100" s="47"/>
+      <c r="C100" s="47"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="47"/>
+      <c r="I100" s="47"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -24080,14 +24080,14 @@
     <row r="34" spans="1:29" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -24465,15 +24465,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="45"/>
-      <c r="B71" s="45"/>
-      <c r="C71" s="45"/>
-      <c r="D71" s="45"/>
-      <c r="E71" s="45"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="45"/>
-      <c r="H71" s="45"/>
-      <c r="I71" s="45"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -24498,15 +24498,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="46"/>
-      <c r="B76" s="46"/>
-      <c r="C76" s="46"/>
-      <c r="D76" s="46"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="46"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -24542,15 +24542,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="47"/>
-      <c r="B80" s="47"/>
-      <c r="C80" s="47"/>
-      <c r="D80" s="47"/>
-      <c r="E80" s="47"/>
-      <c r="F80" s="47"/>
-      <c r="G80" s="47"/>
-      <c r="H80" s="47"/>
-      <c r="I80" s="47"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -24586,15 +24586,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="46"/>
-      <c r="B88" s="46"/>
-      <c r="C88" s="46"/>
-      <c r="D88" s="46"/>
-      <c r="E88" s="46"/>
-      <c r="F88" s="46"/>
-      <c r="G88" s="46"/>
-      <c r="H88" s="46"/>
-      <c r="I88" s="46"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -24697,15 +24697,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="45"/>
-      <c r="B101" s="45"/>
-      <c r="C101" s="45"/>
-      <c r="D101" s="45"/>
-      <c r="E101" s="45"/>
-      <c r="F101" s="45"/>
-      <c r="G101" s="45"/>
-      <c r="H101" s="45"/>
-      <c r="I101" s="45"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -27307,14 +27307,14 @@
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="47"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
@@ -27692,15 +27692,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="45"/>
-      <c r="B69" s="45"/>
-      <c r="C69" s="45"/>
-      <c r="D69" s="45"/>
-      <c r="E69" s="45"/>
-      <c r="F69" s="45"/>
-      <c r="G69" s="45"/>
-      <c r="H69" s="45"/>
-      <c r="I69" s="45"/>
+      <c r="A69" s="47"/>
+      <c r="B69" s="47"/>
+      <c r="C69" s="47"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="47"/>
+      <c r="G69" s="47"/>
+      <c r="H69" s="47"/>
+      <c r="I69" s="47"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -27725,15 +27725,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="46"/>
-      <c r="B74" s="46"/>
-      <c r="C74" s="46"/>
-      <c r="D74" s="46"/>
-      <c r="E74" s="46"/>
-      <c r="F74" s="46"/>
-      <c r="G74" s="46"/>
-      <c r="H74" s="46"/>
-      <c r="I74" s="46"/>
+      <c r="A74" s="48"/>
+      <c r="B74" s="48"/>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -27769,15 +27769,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="47"/>
-      <c r="B78" s="47"/>
-      <c r="C78" s="47"/>
-      <c r="D78" s="47"/>
-      <c r="E78" s="47"/>
-      <c r="F78" s="47"/>
-      <c r="G78" s="47"/>
-      <c r="H78" s="47"/>
-      <c r="I78" s="47"/>
+      <c r="A78" s="49"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="49"/>
+      <c r="D78" s="49"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="49"/>
+      <c r="G78" s="49"/>
+      <c r="H78" s="49"/>
+      <c r="I78" s="49"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -27813,15 +27813,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="46"/>
-      <c r="B86" s="46"/>
-      <c r="C86" s="46"/>
-      <c r="D86" s="46"/>
-      <c r="E86" s="46"/>
-      <c r="F86" s="46"/>
-      <c r="G86" s="46"/>
-      <c r="H86" s="46"/>
-      <c r="I86" s="46"/>
+      <c r="A86" s="48"/>
+      <c r="B86" s="48"/>
+      <c r="C86" s="48"/>
+      <c r="D86" s="48"/>
+      <c r="E86" s="48"/>
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="48"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -27924,15 +27924,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="45"/>
-      <c r="B99" s="45"/>
-      <c r="C99" s="45"/>
-      <c r="D99" s="45"/>
-      <c r="E99" s="45"/>
-      <c r="F99" s="45"/>
-      <c r="G99" s="45"/>
-      <c r="H99" s="45"/>
-      <c r="I99" s="45"/>
+      <c r="A99" s="47"/>
+      <c r="B99" s="47"/>
+      <c r="C99" s="47"/>
+      <c r="D99" s="47"/>
+      <c r="E99" s="47"/>
+      <c r="F99" s="47"/>
+      <c r="G99" s="47"/>
+      <c r="H99" s="47"/>
+      <c r="I99" s="47"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -30630,14 +30630,14 @@
     </row>
     <row r="35" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="45"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
     </row>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -31015,15 +31015,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="45"/>
-      <c r="B70" s="45"/>
-      <c r="C70" s="45"/>
-      <c r="D70" s="45"/>
-      <c r="E70" s="45"/>
-      <c r="F70" s="45"/>
-      <c r="G70" s="45"/>
-      <c r="H70" s="45"/>
-      <c r="I70" s="45"/>
+      <c r="A70" s="47"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -31048,15 +31048,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="46"/>
-      <c r="B75" s="46"/>
-      <c r="C75" s="46"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="46"/>
+      <c r="A75" s="48"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -31092,15 +31092,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="47"/>
-      <c r="B79" s="47"/>
-      <c r="C79" s="47"/>
-      <c r="D79" s="47"/>
-      <c r="E79" s="47"/>
-      <c r="F79" s="47"/>
-      <c r="G79" s="47"/>
-      <c r="H79" s="47"/>
-      <c r="I79" s="47"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -31136,15 +31136,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="46"/>
-      <c r="B87" s="46"/>
-      <c r="C87" s="46"/>
-      <c r="D87" s="46"/>
-      <c r="E87" s="46"/>
-      <c r="F87" s="46"/>
-      <c r="G87" s="46"/>
-      <c r="H87" s="46"/>
-      <c r="I87" s="46"/>
+      <c r="A87" s="48"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -31247,15 +31247,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="45"/>
-      <c r="B100" s="45"/>
-      <c r="C100" s="45"/>
-      <c r="D100" s="45"/>
-      <c r="E100" s="45"/>
-      <c r="F100" s="45"/>
-      <c r="G100" s="45"/>
-      <c r="H100" s="45"/>
-      <c r="I100" s="45"/>
+      <c r="A100" s="47"/>
+      <c r="B100" s="47"/>
+      <c r="C100" s="47"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="47"/>
+      <c r="I100" s="47"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -32344,7 +32344,7 @@
       </c>
       <c r="L11" s="13">
         <f t="shared" si="3"/>
-        <v>11511</v>
+        <v>1</v>
       </c>
       <c r="M11" s="13">
         <v>0</v>
@@ -32413,49 +32413,49 @@
       </c>
       <c r="D12" s="13">
         <f t="shared" si="8"/>
-        <v>-8216</v>
+        <v>0</v>
       </c>
       <c r="E12" s="13">
         <v>0</v>
       </c>
       <c r="F12" s="13">
         <f t="shared" si="0"/>
-        <v>-10080</v>
+        <v>0</v>
       </c>
       <c r="G12" s="13">
         <v>0</v>
       </c>
       <c r="H12" s="13">
         <f t="shared" si="1"/>
-        <v>-9421</v>
+        <v>3</v>
       </c>
       <c r="I12" s="13">
         <v>0</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="2"/>
-        <v>-10827</v>
+        <v>0</v>
       </c>
       <c r="K12" s="13">
         <v>0</v>
       </c>
       <c r="L12" s="13">
         <f t="shared" si="3"/>
-        <v>-12788</v>
+        <v>0</v>
       </c>
       <c r="M12" s="13">
         <v>0</v>
       </c>
       <c r="N12" s="13">
         <f t="shared" si="4"/>
-        <v>-3851</v>
+        <v>1</v>
       </c>
       <c r="O12" s="13">
         <v>0</v>
       </c>
       <c r="P12" s="13">
         <f t="shared" si="5"/>
-        <v>-387</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="13">
         <v>0</v>
@@ -32465,7 +32465,7 @@
       </c>
       <c r="S12" s="13">
         <f t="shared" si="6"/>
-        <v>-3464</v>
+        <v>1</v>
       </c>
       <c r="T12" s="4"/>
       <c r="U12" s="14">
@@ -32485,7 +32485,7 @@
         <v>10827</v>
       </c>
       <c r="Z12" s="6">
-        <v>12788</v>
+        <v>1278</v>
       </c>
       <c r="AA12" s="6">
         <v>3851</v>
@@ -32569,14 +32569,30 @@
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
-      <c r="V13" s="15"/>
-      <c r="W13" s="15"/>
-      <c r="X13" s="15"/>
-      <c r="Y13" s="15"/>
-      <c r="Z13" s="15"/>
-      <c r="AA13" s="15"/>
-      <c r="AB13" s="15"/>
-      <c r="AC13" s="15"/>
+      <c r="V13" s="15">
+        <v>8216</v>
+      </c>
+      <c r="W13" s="15">
+        <v>10080</v>
+      </c>
+      <c r="X13" s="15">
+        <v>9424</v>
+      </c>
+      <c r="Y13" s="15">
+        <v>10827</v>
+      </c>
+      <c r="Z13" s="15">
+        <v>1278</v>
+      </c>
+      <c r="AA13" s="15">
+        <v>3852</v>
+      </c>
+      <c r="AB13" s="6">
+        <v>387</v>
+      </c>
+      <c r="AC13" s="15">
+        <v>3465</v>
+      </c>
     </row>
     <row r="14" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="28">
@@ -32591,28 +32607,28 @@
       </c>
       <c r="D14" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="E14" s="13">
         <v>0</v>
       </c>
       <c r="F14" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="G14" s="13">
         <v>0</v>
       </c>
       <c r="H14" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I14" s="13">
         <v>0</v>
       </c>
       <c r="J14" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" s="13">
         <v>0</v>
@@ -32626,14 +32642,14 @@
       </c>
       <c r="N14" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O14" s="13">
         <v>0</v>
       </c>
       <c r="P14" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="13">
         <v>0</v>
@@ -32643,21 +32659,37 @@
       </c>
       <c r="S14" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T14" s="4"/>
       <c r="U14" s="14">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="6"/>
-      <c r="AB14" s="6"/>
-      <c r="AC14" s="6"/>
+      <c r="V14" s="15">
+        <v>8216</v>
+      </c>
+      <c r="W14" s="15">
+        <v>10080</v>
+      </c>
+      <c r="X14" s="15">
+        <v>9424</v>
+      </c>
+      <c r="Y14" s="15">
+        <v>10827</v>
+      </c>
+      <c r="Z14" s="15">
+        <v>1278</v>
+      </c>
+      <c r="AA14" s="15">
+        <v>3852</v>
+      </c>
+      <c r="AB14" s="6">
+        <v>387</v>
+      </c>
+      <c r="AC14" s="15">
+        <v>3465</v>
+      </c>
     </row>
     <row r="15" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="28">
@@ -32730,14 +32762,30 @@
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="6"/>
-      <c r="AB15" s="6"/>
-      <c r="AC15" s="6"/>
+      <c r="V15" s="6">
+        <v>8325</v>
+      </c>
+      <c r="W15" s="6">
+        <v>10224</v>
+      </c>
+      <c r="X15" s="6">
+        <v>9435</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>10829</v>
+      </c>
+      <c r="Z15" s="6">
+        <v>1278</v>
+      </c>
+      <c r="AA15" s="6">
+        <v>3860</v>
+      </c>
+      <c r="AB15" s="6">
+        <v>388</v>
+      </c>
+      <c r="AC15" s="6">
+        <v>3471</v>
+      </c>
     </row>
     <row r="16" spans="1:32" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="28">
@@ -32752,21 +32800,21 @@
       </c>
       <c r="D16" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E16" s="13">
         <v>0</v>
       </c>
       <c r="F16" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="G16" s="13">
         <v>0</v>
       </c>
       <c r="H16" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I16" s="13">
         <v>0</v>
@@ -32780,21 +32828,21 @@
       </c>
       <c r="L16" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="13">
         <v>0</v>
       </c>
       <c r="N16" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O16" s="13">
         <v>0</v>
       </c>
       <c r="P16" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="13">
         <v>0</v>
@@ -32804,21 +32852,37 @@
       </c>
       <c r="S16" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T16" s="4"/>
       <c r="U16" s="14">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="16"/>
-      <c r="Z16" s="16"/>
-      <c r="AA16" s="16"/>
-      <c r="AB16" s="16"/>
-      <c r="AC16" s="16"/>
+      <c r="V16" s="6">
+        <v>8325</v>
+      </c>
+      <c r="W16" s="6">
+        <v>10224</v>
+      </c>
+      <c r="X16" s="6">
+        <v>9435</v>
+      </c>
+      <c r="Y16" s="6">
+        <v>10829</v>
+      </c>
+      <c r="Z16" s="6">
+        <v>1278</v>
+      </c>
+      <c r="AA16" s="6">
+        <v>3860</v>
+      </c>
+      <c r="AB16" s="6">
+        <v>388</v>
+      </c>
+      <c r="AC16" s="6">
+        <v>3471</v>
+      </c>
     </row>
     <row r="17" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="28">
@@ -32833,49 +32897,49 @@
       </c>
       <c r="D17" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-8385</v>
       </c>
       <c r="E17" s="13">
         <v>0</v>
       </c>
       <c r="F17" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-10345</v>
       </c>
       <c r="G17" s="13">
         <v>0</v>
       </c>
       <c r="H17" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-9442</v>
       </c>
       <c r="I17" s="13">
         <v>0</v>
       </c>
       <c r="J17" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-10829</v>
       </c>
       <c r="K17" s="13">
         <v>0</v>
       </c>
       <c r="L17" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1279</v>
       </c>
       <c r="M17" s="13">
         <v>0</v>
       </c>
       <c r="N17" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-3871</v>
       </c>
       <c r="O17" s="13">
         <v>0</v>
       </c>
       <c r="P17" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-389</v>
       </c>
       <c r="Q17" s="13">
         <v>0</v>
@@ -32885,21 +32949,37 @@
       </c>
       <c r="S17" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-3481</v>
       </c>
       <c r="T17" s="4"/>
       <c r="U17" s="14">
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="16"/>
-      <c r="AB17" s="16"/>
-      <c r="AC17" s="16"/>
+      <c r="V17" s="16">
+        <v>8385</v>
+      </c>
+      <c r="W17" s="16">
+        <v>10345</v>
+      </c>
+      <c r="X17" s="16">
+        <v>9442</v>
+      </c>
+      <c r="Y17" s="16">
+        <v>10829</v>
+      </c>
+      <c r="Z17" s="16">
+        <v>1279</v>
+      </c>
+      <c r="AA17" s="16">
+        <v>3871</v>
+      </c>
+      <c r="AB17" s="16">
+        <v>389</v>
+      </c>
+      <c r="AC17" s="16">
+        <v>3481</v>
+      </c>
     </row>
     <row r="18" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="28">
@@ -34129,14 +34209,14 @@
     </row>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -34514,15 +34594,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="45"/>
-      <c r="B71" s="45"/>
-      <c r="C71" s="45"/>
-      <c r="D71" s="45"/>
-      <c r="E71" s="45"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="45"/>
-      <c r="H71" s="45"/>
-      <c r="I71" s="45"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -34547,15 +34627,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="46"/>
-      <c r="B76" s="46"/>
-      <c r="C76" s="46"/>
-      <c r="D76" s="46"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="46"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -34591,15 +34671,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="47"/>
-      <c r="B80" s="47"/>
-      <c r="C80" s="47"/>
-      <c r="D80" s="47"/>
-      <c r="E80" s="47"/>
-      <c r="F80" s="47"/>
-      <c r="G80" s="47"/>
-      <c r="H80" s="47"/>
-      <c r="I80" s="47"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -34635,15 +34715,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="46"/>
-      <c r="B88" s="46"/>
-      <c r="C88" s="46"/>
-      <c r="D88" s="46"/>
-      <c r="E88" s="46"/>
-      <c r="F88" s="46"/>
-      <c r="G88" s="46"/>
-      <c r="H88" s="46"/>
-      <c r="I88" s="46"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -34746,15 +34826,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="45"/>
-      <c r="B101" s="45"/>
-      <c r="C101" s="45"/>
-      <c r="D101" s="45"/>
-      <c r="E101" s="45"/>
-      <c r="F101" s="45"/>
-      <c r="G101" s="45"/>
-      <c r="H101" s="45"/>
-      <c r="I101" s="45"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -37771,22 +37851,22 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="45"/>
-      <c r="J35" s="45"/>
-      <c r="K35" s="45"/>
-      <c r="L35" s="45"/>
-      <c r="M35" s="45"/>
-      <c r="N35" s="45"/>
-      <c r="O35" s="45"/>
-      <c r="P35" s="45"/>
-      <c r="Q35" s="45"/>
-      <c r="R35" s="45"/>
-      <c r="S35" s="45"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="47"/>
+      <c r="K35" s="47"/>
+      <c r="L35" s="47"/>
+      <c r="M35" s="47"/>
+      <c r="N35" s="47"/>
+      <c r="O35" s="47"/>
+      <c r="P35" s="47"/>
+      <c r="Q35" s="47"/>
+      <c r="R35" s="47"/>
+      <c r="S35" s="47"/>
     </row>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -38504,25 +38584,25 @@
       <c r="S69" s="1"/>
     </row>
     <row r="70" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="45"/>
-      <c r="B70" s="45"/>
-      <c r="C70" s="45"/>
-      <c r="D70" s="45"/>
-      <c r="E70" s="45"/>
-      <c r="F70" s="45"/>
-      <c r="G70" s="45"/>
-      <c r="H70" s="45"/>
-      <c r="I70" s="45"/>
-      <c r="J70" s="45"/>
-      <c r="K70" s="45"/>
-      <c r="L70" s="45"/>
-      <c r="M70" s="45"/>
-      <c r="N70" s="45"/>
-      <c r="O70" s="45"/>
-      <c r="P70" s="45"/>
-      <c r="Q70" s="45"/>
-      <c r="R70" s="45"/>
-      <c r="S70" s="45"/>
+      <c r="A70" s="47"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
+      <c r="J70" s="47"/>
+      <c r="K70" s="47"/>
+      <c r="L70" s="47"/>
+      <c r="M70" s="47"/>
+      <c r="N70" s="47"/>
+      <c r="O70" s="47"/>
+      <c r="P70" s="47"/>
+      <c r="Q70" s="47"/>
+      <c r="R70" s="47"/>
+      <c r="S70" s="47"/>
     </row>
     <row r="71" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -38567,25 +38647,25 @@
       <c r="S72" s="23"/>
     </row>
     <row r="75" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="46"/>
-      <c r="B75" s="46"/>
-      <c r="C75" s="46"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="46"/>
-      <c r="J75" s="46"/>
-      <c r="K75" s="46"/>
-      <c r="L75" s="46"/>
-      <c r="M75" s="46"/>
-      <c r="N75" s="46"/>
-      <c r="O75" s="46"/>
-      <c r="P75" s="46"/>
-      <c r="Q75" s="46"/>
-      <c r="R75" s="46"/>
-      <c r="S75" s="46"/>
+      <c r="A75" s="48"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
+      <c r="J75" s="48"/>
+      <c r="K75" s="48"/>
+      <c r="L75" s="48"/>
+      <c r="M75" s="48"/>
+      <c r="N75" s="48"/>
+      <c r="O75" s="48"/>
+      <c r="P75" s="48"/>
+      <c r="Q75" s="48"/>
+      <c r="R75" s="48"/>
+      <c r="S75" s="48"/>
     </row>
     <row r="76" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -38651,25 +38731,25 @@
       <c r="S78" s="25"/>
     </row>
     <row r="79" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="47"/>
-      <c r="B79" s="47"/>
-      <c r="C79" s="47"/>
-      <c r="D79" s="47"/>
-      <c r="E79" s="47"/>
-      <c r="F79" s="47"/>
-      <c r="G79" s="47"/>
-      <c r="H79" s="47"/>
-      <c r="I79" s="47"/>
-      <c r="J79" s="47"/>
-      <c r="K79" s="47"/>
-      <c r="L79" s="47"/>
-      <c r="M79" s="47"/>
-      <c r="N79" s="47"/>
-      <c r="O79" s="47"/>
-      <c r="P79" s="47"/>
-      <c r="Q79" s="47"/>
-      <c r="R79" s="47"/>
-      <c r="S79" s="47"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49"/>
+      <c r="J79" s="49"/>
+      <c r="K79" s="49"/>
+      <c r="L79" s="49"/>
+      <c r="M79" s="49"/>
+      <c r="N79" s="49"/>
+      <c r="O79" s="49"/>
+      <c r="P79" s="49"/>
+      <c r="Q79" s="49"/>
+      <c r="R79" s="49"/>
+      <c r="S79" s="49"/>
     </row>
     <row r="80" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -38733,25 +38813,25 @@
       <c r="E85" s="23"/>
     </row>
     <row r="87" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="46"/>
-      <c r="B87" s="46"/>
-      <c r="C87" s="46"/>
-      <c r="D87" s="46"/>
-      <c r="E87" s="46"/>
-      <c r="F87" s="46"/>
-      <c r="G87" s="46"/>
-      <c r="H87" s="46"/>
-      <c r="I87" s="46"/>
-      <c r="J87" s="46"/>
-      <c r="K87" s="46"/>
-      <c r="L87" s="46"/>
-      <c r="M87" s="46"/>
-      <c r="N87" s="46"/>
-      <c r="O87" s="46"/>
-      <c r="P87" s="46"/>
-      <c r="Q87" s="46"/>
-      <c r="R87" s="46"/>
-      <c r="S87" s="46"/>
+      <c r="A87" s="48"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
+      <c r="J87" s="48"/>
+      <c r="K87" s="48"/>
+      <c r="L87" s="48"/>
+      <c r="M87" s="48"/>
+      <c r="N87" s="48"/>
+      <c r="O87" s="48"/>
+      <c r="P87" s="48"/>
+      <c r="Q87" s="48"/>
+      <c r="R87" s="48"/>
+      <c r="S87" s="48"/>
     </row>
     <row r="88" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -38943,25 +39023,25 @@
       <c r="E98" s="26"/>
     </row>
     <row r="100" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="45"/>
-      <c r="B100" s="45"/>
-      <c r="C100" s="45"/>
-      <c r="D100" s="45"/>
-      <c r="E100" s="45"/>
-      <c r="F100" s="45"/>
-      <c r="G100" s="45"/>
-      <c r="H100" s="45"/>
-      <c r="I100" s="45"/>
-      <c r="J100" s="45"/>
-      <c r="K100" s="45"/>
-      <c r="L100" s="45"/>
-      <c r="M100" s="45"/>
-      <c r="N100" s="45"/>
-      <c r="O100" s="45"/>
-      <c r="P100" s="45"/>
-      <c r="Q100" s="45"/>
-      <c r="R100" s="45"/>
-      <c r="S100" s="45"/>
+      <c r="A100" s="47"/>
+      <c r="B100" s="47"/>
+      <c r="C100" s="47"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="47"/>
+      <c r="I100" s="47"/>
+      <c r="J100" s="47"/>
+      <c r="K100" s="47"/>
+      <c r="L100" s="47"/>
+      <c r="M100" s="47"/>
+      <c r="N100" s="47"/>
+      <c r="O100" s="47"/>
+      <c r="P100" s="47"/>
+      <c r="Q100" s="47"/>
+      <c r="R100" s="47"/>
+      <c r="S100" s="47"/>
     </row>
     <row r="101" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -42170,14 +42250,14 @@
     <row r="34" spans="1:29" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -42555,15 +42635,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="45"/>
-      <c r="B71" s="45"/>
-      <c r="C71" s="45"/>
-      <c r="D71" s="45"/>
-      <c r="E71" s="45"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="45"/>
-      <c r="H71" s="45"/>
-      <c r="I71" s="45"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -42588,15 +42668,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="46"/>
-      <c r="B76" s="46"/>
-      <c r="C76" s="46"/>
-      <c r="D76" s="46"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="46"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -42632,15 +42712,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="47"/>
-      <c r="B80" s="47"/>
-      <c r="C80" s="47"/>
-      <c r="D80" s="47"/>
-      <c r="E80" s="47"/>
-      <c r="F80" s="47"/>
-      <c r="G80" s="47"/>
-      <c r="H80" s="47"/>
-      <c r="I80" s="47"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -42676,15 +42756,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="46"/>
-      <c r="B88" s="46"/>
-      <c r="C88" s="46"/>
-      <c r="D88" s="46"/>
-      <c r="E88" s="46"/>
-      <c r="F88" s="46"/>
-      <c r="G88" s="46"/>
-      <c r="H88" s="46"/>
-      <c r="I88" s="46"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -42787,15 +42867,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="45"/>
-      <c r="B101" s="45"/>
-      <c r="C101" s="45"/>
-      <c r="D101" s="45"/>
-      <c r="E101" s="45"/>
-      <c r="F101" s="45"/>
-      <c r="G101" s="45"/>
-      <c r="H101" s="45"/>
-      <c r="I101" s="45"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7087546A-9556-4AEC-8092-C803F1EDD517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDBA4D3-649D-4BE8-9569-6D9FB66BC390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -31741,7 +31741,7 @@
       </c>
       <c r="F5" s="13">
         <f t="shared" si="0"/>
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="G5" s="13">
         <v>0</v>
@@ -31838,7 +31838,7 @@
       </c>
       <c r="F6" s="13">
         <f t="shared" si="0"/>
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G6" s="13">
         <v>0</v>
@@ -31894,7 +31894,7 @@
         <v>7973</v>
       </c>
       <c r="W6" s="6">
-        <v>9741</v>
+        <v>9748</v>
       </c>
       <c r="X6" s="6">
         <v>9387</v>
@@ -32046,7 +32046,7 @@
       </c>
       <c r="J8" s="13">
         <f t="shared" si="2"/>
-        <v>-156</v>
+        <v>0</v>
       </c>
       <c r="K8" s="13">
         <v>0</v>
@@ -32143,7 +32143,7 @@
       </c>
       <c r="J9" s="13">
         <f t="shared" si="2"/>
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="K9" s="13">
         <v>0</v>
@@ -32191,7 +32191,7 @@
         <v>9409</v>
       </c>
       <c r="Y9" s="6">
-        <v>10669</v>
+        <v>10825</v>
       </c>
       <c r="Z9" s="6">
         <v>1277</v>
@@ -32897,49 +32897,49 @@
       </c>
       <c r="D17" s="13">
         <f t="shared" si="8"/>
-        <v>-8385</v>
+        <v>0</v>
       </c>
       <c r="E17" s="13">
         <v>0</v>
       </c>
       <c r="F17" s="13">
         <f t="shared" si="0"/>
-        <v>-10345</v>
+        <v>0</v>
       </c>
       <c r="G17" s="13">
         <v>0</v>
       </c>
       <c r="H17" s="13">
         <f t="shared" si="1"/>
-        <v>-9442</v>
+        <v>0</v>
       </c>
       <c r="I17" s="13">
         <v>0</v>
       </c>
       <c r="J17" s="13">
         <f t="shared" si="10"/>
-        <v>-10829</v>
+        <v>0</v>
       </c>
       <c r="K17" s="13">
         <v>0</v>
       </c>
       <c r="L17" s="13">
         <f t="shared" si="3"/>
-        <v>-1279</v>
+        <v>0</v>
       </c>
       <c r="M17" s="13">
         <v>0</v>
       </c>
       <c r="N17" s="13">
         <f t="shared" si="4"/>
-        <v>-3871</v>
+        <v>0</v>
       </c>
       <c r="O17" s="13">
         <v>0</v>
       </c>
       <c r="P17" s="13">
         <f t="shared" si="5"/>
-        <v>-389</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="13">
         <v>0</v>
@@ -32949,7 +32949,7 @@
       </c>
       <c r="S17" s="13">
         <f t="shared" si="6"/>
-        <v>-3481</v>
+        <v>0</v>
       </c>
       <c r="T17" s="4"/>
       <c r="U17" s="14">
@@ -32994,28 +32994,28 @@
       </c>
       <c r="D18" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="E18" s="13">
         <v>0</v>
       </c>
       <c r="F18" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G18" s="13">
         <v>0</v>
       </c>
       <c r="H18" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I18" s="13">
         <v>0</v>
       </c>
       <c r="J18" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="13">
         <v>0</v>
@@ -33029,14 +33029,14 @@
       </c>
       <c r="N18" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O18" s="13">
         <v>0</v>
       </c>
       <c r="P18" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="13">
         <v>0</v>
@@ -33046,21 +33046,37 @@
       </c>
       <c r="S18" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T18" s="4"/>
       <c r="U18" s="14">
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
-      <c r="Y18" s="16"/>
-      <c r="Z18" s="16"/>
-      <c r="AA18" s="16"/>
-      <c r="AB18" s="16"/>
-      <c r="AC18" s="16"/>
+      <c r="V18" s="16">
+        <v>8385</v>
+      </c>
+      <c r="W18" s="16">
+        <v>10345</v>
+      </c>
+      <c r="X18" s="16">
+        <v>9442</v>
+      </c>
+      <c r="Y18" s="16">
+        <v>10829</v>
+      </c>
+      <c r="Z18" s="16">
+        <v>1279</v>
+      </c>
+      <c r="AA18" s="16">
+        <v>3871</v>
+      </c>
+      <c r="AB18" s="16">
+        <v>389</v>
+      </c>
+      <c r="AC18" s="16">
+        <v>3481</v>
+      </c>
     </row>
     <row r="19" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="28">
@@ -33075,28 +33091,28 @@
       </c>
       <c r="D19" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="E19" s="13">
         <v>0</v>
       </c>
       <c r="F19" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G19" s="13">
         <v>0</v>
       </c>
       <c r="H19" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" s="13">
         <v>0</v>
       </c>
       <c r="J19" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19" s="13">
         <v>0</v>
@@ -33110,14 +33126,14 @@
       </c>
       <c r="N19" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O19" s="13">
         <v>0</v>
       </c>
       <c r="P19" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q19" s="13">
         <v>0</v>
@@ -33127,21 +33143,37 @@
       </c>
       <c r="S19" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T19" s="17"/>
       <c r="U19" s="18">
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="V19" s="19"/>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19"/>
-      <c r="Y19" s="19"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="19"/>
-      <c r="AB19" s="19"/>
-      <c r="AC19" s="19"/>
+      <c r="V19" s="19">
+        <v>8491</v>
+      </c>
+      <c r="W19" s="19">
+        <v>10414</v>
+      </c>
+      <c r="X19" s="19">
+        <v>9451</v>
+      </c>
+      <c r="Y19" s="19">
+        <v>10830</v>
+      </c>
+      <c r="Z19" s="19">
+        <v>1279</v>
+      </c>
+      <c r="AA19" s="19">
+        <v>3877</v>
+      </c>
+      <c r="AB19" s="19">
+        <v>390</v>
+      </c>
+      <c r="AC19" s="19">
+        <v>3486</v>
+      </c>
     </row>
     <row r="20" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="28">
@@ -33156,14 +33188,14 @@
       </c>
       <c r="D20" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E20" s="13">
         <v>0</v>
       </c>
       <c r="F20" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G20" s="13">
         <v>0</v>
@@ -33184,7 +33216,7 @@
       </c>
       <c r="L20" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="13">
         <v>0</v>
@@ -33215,14 +33247,30 @@
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="V20" s="15"/>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
-      <c r="Y20" s="15"/>
-      <c r="Z20" s="15"/>
-      <c r="AA20" s="15"/>
-      <c r="AB20" s="15"/>
-      <c r="AC20" s="15"/>
+      <c r="V20" s="15">
+        <v>8554</v>
+      </c>
+      <c r="W20" s="15">
+        <v>10465</v>
+      </c>
+      <c r="X20" s="15">
+        <v>9454</v>
+      </c>
+      <c r="Y20" s="15">
+        <v>10832</v>
+      </c>
+      <c r="Z20" s="15">
+        <v>1279</v>
+      </c>
+      <c r="AA20" s="15">
+        <v>3885</v>
+      </c>
+      <c r="AB20" s="15">
+        <v>405</v>
+      </c>
+      <c r="AC20" s="15">
+        <v>3497</v>
+      </c>
     </row>
     <row r="21" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="28">
@@ -33237,21 +33285,21 @@
       </c>
       <c r="D21" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E21" s="13">
         <v>0</v>
       </c>
       <c r="F21" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="G21" s="13">
         <v>0</v>
       </c>
       <c r="H21" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I21" s="13">
         <v>0</v>
@@ -33272,7 +33320,7 @@
       </c>
       <c r="N21" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O21" s="13">
         <v>0</v>
@@ -33289,21 +33337,37 @@
       </c>
       <c r="S21" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T21" s="4"/>
       <c r="U21" s="18">
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="V21" s="15"/>
-      <c r="W21" s="15"/>
-      <c r="X21" s="15"/>
-      <c r="Y21" s="15"/>
-      <c r="Z21" s="15"/>
-      <c r="AA21" s="15"/>
-      <c r="AB21" s="15"/>
-      <c r="AC21" s="15"/>
+      <c r="V21" s="15">
+        <v>8567</v>
+      </c>
+      <c r="W21" s="15">
+        <v>10505</v>
+      </c>
+      <c r="X21" s="15">
+        <v>9454</v>
+      </c>
+      <c r="Y21" s="15">
+        <v>10832</v>
+      </c>
+      <c r="Z21" s="15">
+        <v>1280</v>
+      </c>
+      <c r="AA21" s="15">
+        <v>3885</v>
+      </c>
+      <c r="AB21" s="15">
+        <v>405</v>
+      </c>
+      <c r="AC21" s="15">
+        <v>3497</v>
+      </c>
     </row>
     <row r="22" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="28">
@@ -33318,49 +33382,49 @@
       </c>
       <c r="D22" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-8632</v>
       </c>
       <c r="E22" s="13">
         <v>0</v>
       </c>
       <c r="F22" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-10674</v>
       </c>
       <c r="G22" s="13">
         <v>0</v>
       </c>
       <c r="H22" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-9465</v>
       </c>
       <c r="I22" s="13">
         <v>0</v>
       </c>
       <c r="J22" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-10832</v>
       </c>
       <c r="K22" s="13">
         <v>0</v>
       </c>
       <c r="L22" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1280</v>
       </c>
       <c r="M22" s="13">
         <v>0</v>
       </c>
       <c r="N22" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-3887</v>
       </c>
       <c r="O22" s="13">
         <v>0</v>
       </c>
       <c r="P22" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-405</v>
       </c>
       <c r="Q22" s="13">
         <v>0</v>
@@ -33370,21 +33434,37 @@
       </c>
       <c r="S22" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-3495</v>
       </c>
       <c r="T22" s="4"/>
       <c r="U22" s="18">
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="V22" s="15"/>
-      <c r="W22" s="15"/>
-      <c r="X22" s="15"/>
-      <c r="Y22" s="15"/>
-      <c r="Z22" s="15"/>
-      <c r="AA22" s="15"/>
-      <c r="AB22" s="15"/>
-      <c r="AC22" s="15"/>
+      <c r="V22" s="15">
+        <v>8632</v>
+      </c>
+      <c r="W22" s="15">
+        <v>10674</v>
+      </c>
+      <c r="X22" s="15">
+        <v>9465</v>
+      </c>
+      <c r="Y22" s="15">
+        <v>10832</v>
+      </c>
+      <c r="Z22" s="15">
+        <v>1280</v>
+      </c>
+      <c r="AA22" s="15">
+        <v>3887</v>
+      </c>
+      <c r="AB22" s="15">
+        <v>405</v>
+      </c>
+      <c r="AC22" s="15">
+        <v>3495</v>
+      </c>
     </row>
     <row r="23" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="28">

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDBA4D3-649D-4BE8-9569-6D9FB66BC390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260F76C7-97CF-4BD9-BF8B-1827F6472FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33337,7 +33337,7 @@
       </c>
       <c r="S21" s="13">
         <f t="shared" si="6"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T21" s="4"/>
       <c r="U21" s="18">
@@ -33382,49 +33382,49 @@
       </c>
       <c r="D22" s="13">
         <f t="shared" si="8"/>
-        <v>-8632</v>
+        <v>49</v>
       </c>
       <c r="E22" s="13">
         <v>0</v>
       </c>
       <c r="F22" s="13">
         <f t="shared" si="0"/>
-        <v>-10674</v>
+        <v>91</v>
       </c>
       <c r="G22" s="13">
         <v>0</v>
       </c>
       <c r="H22" s="13">
         <f t="shared" si="1"/>
-        <v>-9465</v>
+        <v>0</v>
       </c>
       <c r="I22" s="13">
         <v>0</v>
       </c>
       <c r="J22" s="13">
         <f t="shared" si="10"/>
-        <v>-10832</v>
+        <v>0</v>
       </c>
       <c r="K22" s="13">
         <v>0</v>
       </c>
       <c r="L22" s="13">
         <f t="shared" si="3"/>
-        <v>-1280</v>
+        <v>0</v>
       </c>
       <c r="M22" s="13">
         <v>0</v>
       </c>
       <c r="N22" s="13">
         <f t="shared" si="4"/>
-        <v>-3887</v>
+        <v>8</v>
       </c>
       <c r="O22" s="13">
         <v>0</v>
       </c>
       <c r="P22" s="13">
         <f t="shared" si="5"/>
-        <v>-405</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="13">
         <v>0</v>
@@ -33434,7 +33434,7 @@
       </c>
       <c r="S22" s="13">
         <f t="shared" si="6"/>
-        <v>-3495</v>
+        <v>6</v>
       </c>
       <c r="T22" s="4"/>
       <c r="U22" s="18">
@@ -33463,7 +33463,7 @@
         <v>405</v>
       </c>
       <c r="AC22" s="15">
-        <v>3495</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="23" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
@@ -33538,14 +33538,30 @@
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="V23" s="15"/>
-      <c r="W23" s="15"/>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="15"/>
-      <c r="Z23" s="15"/>
-      <c r="AA23" s="15"/>
-      <c r="AB23" s="15"/>
-      <c r="AC23" s="15"/>
+      <c r="V23" s="15">
+        <v>8681</v>
+      </c>
+      <c r="W23" s="15">
+        <v>10765</v>
+      </c>
+      <c r="X23" s="15">
+        <v>9465</v>
+      </c>
+      <c r="Y23" s="15">
+        <v>10832</v>
+      </c>
+      <c r="Z23" s="15">
+        <v>1280</v>
+      </c>
+      <c r="AA23" s="15">
+        <v>3895</v>
+      </c>
+      <c r="AB23" s="15">
+        <v>405</v>
+      </c>
+      <c r="AC23" s="15">
+        <v>3503</v>
+      </c>
     </row>
     <row r="24" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="28">
@@ -33560,49 +33576,49 @@
       </c>
       <c r="D24" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-8681</v>
       </c>
       <c r="E24" s="13">
         <v>0</v>
       </c>
       <c r="F24" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-10765</v>
       </c>
       <c r="G24" s="13">
         <v>0</v>
       </c>
       <c r="H24" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-9465</v>
       </c>
       <c r="I24" s="13">
         <v>0</v>
       </c>
       <c r="J24" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-10832</v>
       </c>
       <c r="K24" s="13">
         <v>0</v>
       </c>
       <c r="L24" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1280</v>
       </c>
       <c r="M24" s="13">
         <v>0</v>
       </c>
       <c r="N24" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-3895</v>
       </c>
       <c r="O24" s="13">
         <v>0</v>
       </c>
       <c r="P24" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-405</v>
       </c>
       <c r="Q24" s="13">
         <v>0</v>
@@ -33612,21 +33628,37 @@
       </c>
       <c r="S24" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-3503</v>
       </c>
       <c r="T24" s="4"/>
       <c r="U24" s="18">
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="V24" s="15"/>
-      <c r="W24" s="15"/>
-      <c r="X24" s="15"/>
-      <c r="Y24" s="15"/>
-      <c r="Z24" s="15"/>
-      <c r="AA24" s="15"/>
-      <c r="AB24" s="15"/>
-      <c r="AC24" s="15"/>
+      <c r="V24" s="15">
+        <v>8681</v>
+      </c>
+      <c r="W24" s="15">
+        <v>10765</v>
+      </c>
+      <c r="X24" s="15">
+        <v>9465</v>
+      </c>
+      <c r="Y24" s="15">
+        <v>10832</v>
+      </c>
+      <c r="Z24" s="15">
+        <v>1280</v>
+      </c>
+      <c r="AA24" s="15">
+        <v>3895</v>
+      </c>
+      <c r="AB24" s="15">
+        <v>405</v>
+      </c>
+      <c r="AC24" s="15">
+        <v>3503</v>
+      </c>
     </row>
     <row r="25" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="28">

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D11F365-5DD6-4184-988B-B0CC53526407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ADD5581-8F95-444E-9BDF-DA503C2E671C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34002,49 +34002,49 @@
       </c>
       <c r="D24" s="13">
         <f t="shared" si="8"/>
-        <v>-8681</v>
+        <v>0</v>
       </c>
       <c r="E24" s="13">
         <v>0</v>
       </c>
       <c r="F24" s="13">
         <f t="shared" si="0"/>
-        <v>-10765</v>
+        <v>0</v>
       </c>
       <c r="G24" s="13">
         <v>0</v>
       </c>
       <c r="H24" s="13">
         <f t="shared" si="1"/>
-        <v>-9465</v>
+        <v>0</v>
       </c>
       <c r="I24" s="13">
         <v>0</v>
       </c>
       <c r="J24" s="13">
         <f t="shared" si="10"/>
-        <v>-10832</v>
+        <v>0</v>
       </c>
       <c r="K24" s="13">
         <v>0</v>
       </c>
       <c r="L24" s="13">
         <f t="shared" si="3"/>
-        <v>-1280</v>
+        <v>0</v>
       </c>
       <c r="M24" s="13">
         <v>0</v>
       </c>
       <c r="N24" s="13">
         <f t="shared" si="4"/>
-        <v>-3895</v>
+        <v>0</v>
       </c>
       <c r="O24" s="13">
         <v>0</v>
       </c>
       <c r="P24" s="13">
         <f t="shared" si="5"/>
-        <v>-405</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="13">
         <v>0</v>
@@ -34054,7 +34054,7 @@
       </c>
       <c r="S24" s="13">
         <f t="shared" si="6"/>
-        <v>-3503</v>
+        <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
         <v>67</v>
@@ -34164,14 +34164,30 @@
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15"/>
-      <c r="AA25" s="15"/>
-      <c r="AB25" s="15"/>
-      <c r="AC25" s="15"/>
-      <c r="AD25" s="15"/>
+      <c r="W25" s="15">
+        <v>8681</v>
+      </c>
+      <c r="X25" s="15">
+        <v>10765</v>
+      </c>
+      <c r="Y25" s="15">
+        <v>9465</v>
+      </c>
+      <c r="Z25" s="15">
+        <v>10832</v>
+      </c>
+      <c r="AA25" s="15">
+        <v>1280</v>
+      </c>
+      <c r="AB25" s="15">
+        <v>3895</v>
+      </c>
+      <c r="AC25" s="15">
+        <v>405</v>
+      </c>
+      <c r="AD25" s="15">
+        <v>3503</v>
+      </c>
     </row>
     <row r="26" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="28">
@@ -34186,28 +34202,28 @@
       </c>
       <c r="D26" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="E26" s="13">
         <v>0</v>
       </c>
       <c r="F26" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="G26" s="13">
         <v>0</v>
       </c>
       <c r="H26" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I26" s="13">
         <v>0</v>
       </c>
       <c r="J26" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K26" s="13">
         <v>0</v>
@@ -34221,7 +34237,7 @@
       </c>
       <c r="N26" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O26" s="13">
         <v>0</v>
@@ -34238,7 +34254,7 @@
       </c>
       <c r="S26" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T26" s="6" t="s">
         <v>64</v>
@@ -34248,14 +34264,30 @@
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="W26" s="21"/>
-      <c r="X26" s="21"/>
-      <c r="Y26" s="21"/>
-      <c r="Z26" s="21"/>
-      <c r="AA26" s="21"/>
-      <c r="AB26" s="21"/>
-      <c r="AC26" s="21"/>
-      <c r="AD26" s="21"/>
+      <c r="W26" s="15">
+        <v>8681</v>
+      </c>
+      <c r="X26" s="15">
+        <v>10765</v>
+      </c>
+      <c r="Y26" s="15">
+        <v>9465</v>
+      </c>
+      <c r="Z26" s="15">
+        <v>10832</v>
+      </c>
+      <c r="AA26" s="15">
+        <v>1280</v>
+      </c>
+      <c r="AB26" s="15">
+        <v>3895</v>
+      </c>
+      <c r="AC26" s="15">
+        <v>405</v>
+      </c>
+      <c r="AD26" s="15">
+        <v>3503</v>
+      </c>
     </row>
     <row r="27" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="28">
@@ -34270,21 +34302,21 @@
       </c>
       <c r="D27" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="E27" s="13">
         <v>0</v>
       </c>
       <c r="F27" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G27" s="13">
         <v>0</v>
       </c>
       <c r="H27" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I27" s="13">
         <v>0</v>
@@ -34305,7 +34337,7 @@
       </c>
       <c r="N27" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O27" s="13">
         <v>0</v>
@@ -34322,7 +34354,7 @@
       </c>
       <c r="S27" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T27" s="6" t="s">
         <v>51</v>
@@ -34332,14 +34364,30 @@
         <f t="shared" si="9"/>
         <v>25</v>
       </c>
-      <c r="W27" s="15"/>
-      <c r="X27" s="15"/>
-      <c r="Y27" s="15"/>
-      <c r="Z27" s="15"/>
-      <c r="AA27" s="15"/>
-      <c r="AB27" s="15"/>
-      <c r="AC27" s="15"/>
-      <c r="AD27" s="15"/>
+      <c r="W27" s="15">
+        <v>8885</v>
+      </c>
+      <c r="X27" s="15">
+        <v>10907</v>
+      </c>
+      <c r="Y27" s="15">
+        <v>9479</v>
+      </c>
+      <c r="Z27" s="15">
+        <v>10835</v>
+      </c>
+      <c r="AA27" s="15">
+        <v>1280</v>
+      </c>
+      <c r="AB27" s="15">
+        <v>3910</v>
+      </c>
+      <c r="AC27" s="15">
+        <v>405</v>
+      </c>
+      <c r="AD27" s="15">
+        <v>3516</v>
+      </c>
     </row>
     <row r="28" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="28">
@@ -34361,35 +34409,35 @@
       </c>
       <c r="F28" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G28" s="13">
         <v>0</v>
       </c>
       <c r="H28" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I28" s="13">
         <v>0</v>
       </c>
       <c r="J28" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="13">
         <v>0</v>
       </c>
       <c r="L28" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="13">
         <v>0</v>
       </c>
       <c r="N28" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O28" s="13">
         <v>0</v>
@@ -34406,7 +34454,7 @@
       </c>
       <c r="S28" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T28" s="6" t="s">
         <v>51</v>
@@ -34416,14 +34464,30 @@
         <f t="shared" si="9"/>
         <v>26</v>
       </c>
-      <c r="W28" s="15"/>
-      <c r="X28" s="15"/>
-      <c r="Y28" s="15"/>
-      <c r="Z28" s="15"/>
-      <c r="AA28" s="15"/>
-      <c r="AB28" s="15"/>
-      <c r="AC28" s="15"/>
-      <c r="AD28" s="15"/>
+      <c r="W28" s="15">
+        <v>8963</v>
+      </c>
+      <c r="X28" s="15">
+        <v>10966</v>
+      </c>
+      <c r="Y28" s="15">
+        <v>9484</v>
+      </c>
+      <c r="Z28" s="15">
+        <v>10835</v>
+      </c>
+      <c r="AA28" s="15">
+        <v>1280</v>
+      </c>
+      <c r="AB28" s="15">
+        <v>3915</v>
+      </c>
+      <c r="AC28" s="15">
+        <v>405</v>
+      </c>
+      <c r="AD28" s="15">
+        <v>3519</v>
+      </c>
     </row>
     <row r="29" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="28">
@@ -34438,49 +34502,49 @@
       </c>
       <c r="D29" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-8963</v>
       </c>
       <c r="E29" s="13">
         <v>0</v>
       </c>
       <c r="F29" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-11014</v>
       </c>
       <c r="G29" s="13">
         <v>0</v>
       </c>
       <c r="H29" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-9490</v>
       </c>
       <c r="I29" s="13">
         <v>0</v>
       </c>
       <c r="J29" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-10836</v>
       </c>
       <c r="K29" s="13">
         <v>0</v>
       </c>
       <c r="L29" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1281</v>
       </c>
       <c r="M29" s="13">
         <v>0</v>
       </c>
       <c r="N29" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-3918</v>
       </c>
       <c r="O29" s="13">
         <v>0</v>
       </c>
       <c r="P29" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-405</v>
       </c>
       <c r="Q29" s="13">
         <v>0</v>
@@ -34490,7 +34554,7 @@
       </c>
       <c r="S29" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-3523</v>
       </c>
       <c r="T29" s="6" t="s">
         <v>63</v>
@@ -34500,14 +34564,30 @@
         <f t="shared" si="9"/>
         <v>27</v>
       </c>
-      <c r="W29" s="15"/>
-      <c r="X29" s="15"/>
-      <c r="Y29" s="15"/>
-      <c r="Z29" s="15"/>
-      <c r="AA29" s="15"/>
-      <c r="AB29" s="15"/>
-      <c r="AC29" s="15"/>
-      <c r="AD29" s="15"/>
+      <c r="W29" s="15">
+        <v>8963</v>
+      </c>
+      <c r="X29" s="15">
+        <v>11014</v>
+      </c>
+      <c r="Y29" s="15">
+        <v>9490</v>
+      </c>
+      <c r="Z29" s="15">
+        <v>10836</v>
+      </c>
+      <c r="AA29" s="15">
+        <v>1281</v>
+      </c>
+      <c r="AB29" s="15">
+        <v>3918</v>
+      </c>
+      <c r="AC29" s="15">
+        <v>405</v>
+      </c>
+      <c r="AD29" s="15">
+        <v>3523</v>
+      </c>
     </row>
     <row r="30" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="28">

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ADD5581-8F95-444E-9BDF-DA503C2E671C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB3B011-D59E-4108-82E9-60A1C72902B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -264,7 +264,7 @@
     <numFmt numFmtId="166" formatCode="_-&quot;R$ &quot;* #,##0.000_-;&quot;-R$ &quot;* #,##0.000_-;_-&quot;R$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="[$R$ -416]#,##0.00"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -354,6 +354,13 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -471,7 +478,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -601,6 +608,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1301,10 +1311,10 @@
         <v>39</v>
       </c>
       <c r="B8" s="41">
-        <v>0</v>
+        <v>30377.200000000001</v>
       </c>
       <c r="C8" s="41">
-        <v>0</v>
+        <v>12141.35</v>
       </c>
       <c r="D8" s="41">
         <v>0</v>
@@ -1337,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="N8" s="41">
-        <v>0</v>
+        <v>6888.16</v>
       </c>
       <c r="O8" s="41">
-        <v>0</v>
+        <v>3678.28</v>
       </c>
       <c r="P8" s="41">
         <v>0</v>
@@ -28499,14 +28509,30 @@
       <c r="V2" s="8">
         <v>0</v>
       </c>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
+      <c r="W2" s="15">
+        <v>9135</v>
+      </c>
+      <c r="X2" s="15">
+        <v>11194</v>
+      </c>
+      <c r="Y2" s="15">
+        <v>9505</v>
+      </c>
+      <c r="Z2" s="15">
+        <v>10839</v>
+      </c>
+      <c r="AA2" s="15">
+        <v>1282</v>
+      </c>
+      <c r="AB2" s="15">
+        <v>3934</v>
+      </c>
+      <c r="AC2" s="15">
+        <v>396</v>
+      </c>
+      <c r="AD2" s="15">
+        <v>3537</v>
+      </c>
       <c r="AF2" s="10" t="s">
         <v>29</v>
       </c>
@@ -28587,14 +28613,30 @@
       <c r="V3" s="12">
         <v>1</v>
       </c>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="13"/>
+      <c r="W3" s="49">
+        <v>9135</v>
+      </c>
+      <c r="X3" s="49">
+        <v>11194</v>
+      </c>
+      <c r="Y3" s="49">
+        <v>9505</v>
+      </c>
+      <c r="Z3" s="49">
+        <v>10839</v>
+      </c>
+      <c r="AA3" s="49">
+        <v>1282</v>
+      </c>
+      <c r="AB3" s="49">
+        <v>3934</v>
+      </c>
+      <c r="AC3" s="49">
+        <v>396</v>
+      </c>
+      <c r="AD3" s="49">
+        <v>3537</v>
+      </c>
     </row>
     <row r="4" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="28">
@@ -28669,14 +28711,30 @@
         <f t="shared" ref="V4:V32" si="9">V3+1</f>
         <v>2</v>
       </c>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
+      <c r="W4" s="49">
+        <v>9135</v>
+      </c>
+      <c r="X4" s="49">
+        <v>11194</v>
+      </c>
+      <c r="Y4" s="49">
+        <v>9505</v>
+      </c>
+      <c r="Z4" s="49">
+        <v>10839</v>
+      </c>
+      <c r="AA4" s="49">
+        <v>1282</v>
+      </c>
+      <c r="AB4" s="49">
+        <v>3934</v>
+      </c>
+      <c r="AC4" s="49">
+        <v>396</v>
+      </c>
+      <c r="AD4" s="49">
+        <v>3537</v>
+      </c>
     </row>
     <row r="5" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="28">
@@ -28691,28 +28749,28 @@
       </c>
       <c r="D5" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="E5" s="13">
         <v>0</v>
       </c>
       <c r="F5" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G5" s="13">
         <v>0</v>
       </c>
       <c r="H5" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I5" s="13">
         <v>0</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="13">
         <v>0</v>
@@ -28726,14 +28784,14 @@
       </c>
       <c r="N5" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O5" s="13">
         <v>0</v>
       </c>
       <c r="P5" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="13">
         <v>0</v>
@@ -28743,7 +28801,7 @@
       </c>
       <c r="S5" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="T5" s="6"/>
       <c r="U5" s="4"/>
@@ -28751,14 +28809,30 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
+      <c r="W5" s="49">
+        <v>9135</v>
+      </c>
+      <c r="X5" s="49">
+        <v>11194</v>
+      </c>
+      <c r="Y5" s="49">
+        <v>9505</v>
+      </c>
+      <c r="Z5" s="49">
+        <v>10839</v>
+      </c>
+      <c r="AA5" s="49">
+        <v>1282</v>
+      </c>
+      <c r="AB5" s="49">
+        <v>3934</v>
+      </c>
+      <c r="AC5" s="49">
+        <v>396</v>
+      </c>
+      <c r="AD5" s="49">
+        <v>3537</v>
+      </c>
     </row>
     <row r="6" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="28">
@@ -28773,28 +28847,28 @@
       </c>
       <c r="D6" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E6" s="13">
         <v>0</v>
       </c>
       <c r="F6" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G6" s="13">
         <v>0</v>
       </c>
       <c r="H6" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6" s="13">
         <v>0</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="13">
         <v>0</v>
@@ -28808,7 +28882,7 @@
       </c>
       <c r="N6" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O6" s="13">
         <v>0</v>
@@ -28825,7 +28899,7 @@
       </c>
       <c r="S6" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T6" s="6"/>
       <c r="U6" s="4"/>
@@ -28833,14 +28907,30 @@
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
-      <c r="AB6" s="6"/>
-      <c r="AC6" s="6"/>
-      <c r="AD6" s="6"/>
+      <c r="W6" s="6">
+        <v>9282</v>
+      </c>
+      <c r="X6" s="6">
+        <v>11374</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>9527</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>10841</v>
+      </c>
+      <c r="AA6" s="6">
+        <v>1282</v>
+      </c>
+      <c r="AB6" s="6">
+        <v>3950</v>
+      </c>
+      <c r="AC6" s="6">
+        <v>398</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>3551</v>
+      </c>
     </row>
     <row r="7" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="28">
@@ -28855,49 +28945,49 @@
       </c>
       <c r="D7" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-9325</v>
       </c>
       <c r="E7" s="13">
         <v>0</v>
       </c>
       <c r="F7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-11425</v>
       </c>
       <c r="G7" s="13">
         <v>0</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9531</v>
       </c>
       <c r="I7" s="13">
         <v>0</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-10842</v>
       </c>
       <c r="K7" s="13">
         <v>0</v>
       </c>
       <c r="L7" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1282</v>
       </c>
       <c r="M7" s="13">
         <v>0</v>
       </c>
       <c r="N7" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-3953</v>
       </c>
       <c r="O7" s="13">
         <v>0</v>
       </c>
       <c r="P7" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-398</v>
       </c>
       <c r="Q7" s="13">
         <v>0</v>
@@ -28907,7 +28997,7 @@
       </c>
       <c r="S7" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3553</v>
       </c>
       <c r="T7" s="6"/>
       <c r="U7" s="4"/>
@@ -28915,14 +29005,30 @@
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="6"/>
+      <c r="W7" s="6">
+        <v>9325</v>
+      </c>
+      <c r="X7" s="6">
+        <v>11425</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>9531</v>
+      </c>
+      <c r="Z7" s="6">
+        <v>10842</v>
+      </c>
+      <c r="AA7" s="6">
+        <v>1282</v>
+      </c>
+      <c r="AB7" s="6">
+        <v>3953</v>
+      </c>
+      <c r="AC7" s="6">
+        <v>398</v>
+      </c>
+      <c r="AD7" s="6">
+        <v>3553</v>
+      </c>
     </row>
     <row r="8" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="28">
@@ -32062,7 +32168,7 @@
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="14">
-        <f t="shared" ref="V4:V32" si="9">V3+1</f>
+        <f t="shared" ref="V4:V33" si="9">V3+1</f>
         <v>2</v>
       </c>
       <c r="W4" s="6">
@@ -34502,49 +34608,49 @@
       </c>
       <c r="D29" s="13">
         <f t="shared" si="8"/>
-        <v>-8963</v>
+        <v>0</v>
       </c>
       <c r="E29" s="13">
         <v>0</v>
       </c>
       <c r="F29" s="13">
         <f t="shared" si="0"/>
-        <v>-11014</v>
+        <v>0</v>
       </c>
       <c r="G29" s="13">
         <v>0</v>
       </c>
       <c r="H29" s="13">
         <f t="shared" si="1"/>
-        <v>-9490</v>
+        <v>0</v>
       </c>
       <c r="I29" s="13">
         <v>0</v>
       </c>
       <c r="J29" s="13">
         <f t="shared" si="10"/>
-        <v>-10836</v>
+        <v>0</v>
       </c>
       <c r="K29" s="13">
         <v>0</v>
       </c>
       <c r="L29" s="13">
         <f t="shared" si="3"/>
-        <v>-1281</v>
+        <v>0</v>
       </c>
       <c r="M29" s="13">
         <v>0</v>
       </c>
       <c r="N29" s="13">
         <f t="shared" si="4"/>
-        <v>-3918</v>
+        <v>0</v>
       </c>
       <c r="O29" s="13">
         <v>0</v>
       </c>
       <c r="P29" s="13">
         <f t="shared" si="5"/>
-        <v>-405</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="13">
         <v>0</v>
@@ -34554,7 +34660,7 @@
       </c>
       <c r="S29" s="13">
         <f t="shared" si="6"/>
-        <v>-3523</v>
+        <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
         <v>63</v>
@@ -34602,28 +34708,28 @@
       </c>
       <c r="D30" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="E30" s="13">
         <v>0</v>
       </c>
       <c r="F30" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="G30" s="13">
         <v>0</v>
       </c>
       <c r="H30" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I30" s="13">
         <v>0</v>
       </c>
       <c r="J30" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="13">
         <v>0</v>
@@ -34637,14 +34743,14 @@
       </c>
       <c r="N30" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O30" s="13">
         <v>0</v>
       </c>
       <c r="P30" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="Q30" s="13">
         <v>0</v>
@@ -34654,7 +34760,7 @@
       </c>
       <c r="S30" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T30" s="6" t="s">
         <v>62</v>
@@ -34664,14 +34770,30 @@
         <f t="shared" si="9"/>
         <v>28</v>
       </c>
-      <c r="W30" s="15"/>
-      <c r="X30" s="15"/>
-      <c r="Y30" s="15"/>
-      <c r="Z30" s="15"/>
-      <c r="AA30" s="15"/>
-      <c r="AB30" s="15"/>
-      <c r="AC30" s="15"/>
-      <c r="AD30" s="15"/>
+      <c r="W30" s="15">
+        <v>8963</v>
+      </c>
+      <c r="X30" s="15">
+        <v>11014</v>
+      </c>
+      <c r="Y30" s="15">
+        <v>9490</v>
+      </c>
+      <c r="Z30" s="15">
+        <v>10836</v>
+      </c>
+      <c r="AA30" s="15">
+        <v>1281</v>
+      </c>
+      <c r="AB30" s="15">
+        <v>3918</v>
+      </c>
+      <c r="AC30" s="15">
+        <v>405</v>
+      </c>
+      <c r="AD30" s="15">
+        <v>3523</v>
+      </c>
     </row>
     <row r="31" spans="1:30" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A31" s="28">
@@ -34748,14 +34870,30 @@
         <f t="shared" si="9"/>
         <v>29</v>
       </c>
-      <c r="W31" s="15"/>
-      <c r="X31" s="15"/>
-      <c r="Y31" s="15"/>
-      <c r="Z31" s="15"/>
-      <c r="AA31" s="15"/>
-      <c r="AB31" s="15"/>
-      <c r="AC31" s="15"/>
-      <c r="AD31" s="15"/>
+      <c r="W31" s="15">
+        <v>9050</v>
+      </c>
+      <c r="X31" s="15">
+        <v>11093</v>
+      </c>
+      <c r="Y31" s="15">
+        <v>9498</v>
+      </c>
+      <c r="Z31" s="15">
+        <v>10837</v>
+      </c>
+      <c r="AA31" s="15">
+        <v>1281</v>
+      </c>
+      <c r="AB31" s="15">
+        <v>3927</v>
+      </c>
+      <c r="AC31" s="15">
+        <v>395</v>
+      </c>
+      <c r="AD31" s="15">
+        <v>3531</v>
+      </c>
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="28">
@@ -34770,49 +34908,49 @@
       </c>
       <c r="D32" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E32" s="13">
         <v>0</v>
       </c>
       <c r="F32" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="G32" s="13">
         <v>0</v>
       </c>
       <c r="H32" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I32" s="13">
         <v>0</v>
       </c>
       <c r="J32" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" s="13">
         <v>0</v>
       </c>
       <c r="L32" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="13">
         <v>0</v>
       </c>
       <c r="N32" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O32" s="13">
         <v>0</v>
       </c>
       <c r="P32" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="13">
         <v>0</v>
@@ -34822,7 +34960,7 @@
       </c>
       <c r="S32" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T32" s="6" t="s">
         <v>65</v>
@@ -34832,25 +34970,61 @@
         <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="W32" s="15"/>
-      <c r="X32" s="15"/>
-      <c r="Y32" s="15"/>
-      <c r="Z32" s="15"/>
-      <c r="AA32" s="15"/>
-      <c r="AB32" s="15"/>
-      <c r="AC32" s="15"/>
-      <c r="AD32" s="15"/>
+      <c r="W32" s="15">
+        <v>9050</v>
+      </c>
+      <c r="X32" s="15">
+        <v>11093</v>
+      </c>
+      <c r="Y32" s="15">
+        <v>9498</v>
+      </c>
+      <c r="Z32" s="15">
+        <v>10837</v>
+      </c>
+      <c r="AA32" s="15">
+        <v>1281</v>
+      </c>
+      <c r="AB32" s="15">
+        <v>3927</v>
+      </c>
+      <c r="AC32" s="15">
+        <v>395</v>
+      </c>
+      <c r="AD32" s="15">
+        <v>3531</v>
+      </c>
     </row>
     <row r="33" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="U33" s="4"/>
-      <c r="W33" s="15"/>
-      <c r="X33" s="15"/>
-      <c r="Y33" s="15"/>
-      <c r="Z33" s="15"/>
-      <c r="AA33" s="15"/>
-      <c r="AB33" s="15"/>
-      <c r="AC33" s="15"/>
-      <c r="AD33" s="15"/>
+      <c r="V33" s="18">
+        <f t="shared" si="9"/>
+        <v>31</v>
+      </c>
+      <c r="W33" s="15">
+        <v>9135</v>
+      </c>
+      <c r="X33" s="15">
+        <v>11194</v>
+      </c>
+      <c r="Y33" s="15">
+        <v>9505</v>
+      </c>
+      <c r="Z33" s="15">
+        <v>10839</v>
+      </c>
+      <c r="AA33" s="15">
+        <v>1282</v>
+      </c>
+      <c r="AB33" s="15">
+        <v>3934</v>
+      </c>
+      <c r="AC33" s="15">
+        <v>396</v>
+      </c>
+      <c r="AD33" s="15">
+        <v>3537</v>
+      </c>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB3B011-D59E-4108-82E9-60A1C72902B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A482AD9-890A-4B79-BF37-16F29A6CDAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -478,7 +478,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -601,6 +601,9 @@
     </xf>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -608,8 +611,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4826,15 +4829,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="46"/>
-      <c r="B69" s="46"/>
-      <c r="C69" s="46"/>
-      <c r="D69" s="46"/>
-      <c r="E69" s="46"/>
-      <c r="F69" s="46"/>
-      <c r="G69" s="46"/>
-      <c r="H69" s="46"/>
-      <c r="I69" s="46"/>
+      <c r="A69" s="47"/>
+      <c r="B69" s="47"/>
+      <c r="C69" s="47"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="47"/>
+      <c r="G69" s="47"/>
+      <c r="H69" s="47"/>
+      <c r="I69" s="47"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -4859,15 +4862,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="47"/>
-      <c r="B74" s="47"/>
-      <c r="C74" s="47"/>
-      <c r="D74" s="47"/>
-      <c r="E74" s="47"/>
-      <c r="F74" s="47"/>
-      <c r="G74" s="47"/>
-      <c r="H74" s="47"/>
-      <c r="I74" s="47"/>
+      <c r="A74" s="48"/>
+      <c r="B74" s="48"/>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -4903,15 +4906,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="48"/>
-      <c r="B78" s="48"/>
-      <c r="C78" s="48"/>
-      <c r="D78" s="48"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="48"/>
-      <c r="G78" s="48"/>
-      <c r="H78" s="48"/>
-      <c r="I78" s="48"/>
+      <c r="A78" s="49"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="49"/>
+      <c r="D78" s="49"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="49"/>
+      <c r="G78" s="49"/>
+      <c r="H78" s="49"/>
+      <c r="I78" s="49"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -4947,15 +4950,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="47"/>
-      <c r="B86" s="47"/>
-      <c r="C86" s="47"/>
-      <c r="D86" s="47"/>
-      <c r="E86" s="47"/>
-      <c r="F86" s="47"/>
-      <c r="G86" s="47"/>
-      <c r="H86" s="47"/>
-      <c r="I86" s="47"/>
+      <c r="A86" s="48"/>
+      <c r="B86" s="48"/>
+      <c r="C86" s="48"/>
+      <c r="D86" s="48"/>
+      <c r="E86" s="48"/>
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="48"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -5058,15 +5061,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="46"/>
-      <c r="B99" s="46"/>
-      <c r="C99" s="46"/>
-      <c r="D99" s="46"/>
-      <c r="E99" s="46"/>
-      <c r="F99" s="46"/>
-      <c r="G99" s="46"/>
-      <c r="H99" s="46"/>
-      <c r="I99" s="46"/>
+      <c r="A99" s="47"/>
+      <c r="B99" s="47"/>
+      <c r="C99" s="47"/>
+      <c r="D99" s="47"/>
+      <c r="E99" s="47"/>
+      <c r="F99" s="47"/>
+      <c r="G99" s="47"/>
+      <c r="H99" s="47"/>
+      <c r="I99" s="47"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -8266,14 +8269,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -8650,15 +8653,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="46"/>
-      <c r="B71" s="46"/>
-      <c r="C71" s="46"/>
-      <c r="D71" s="46"/>
-      <c r="E71" s="46"/>
-      <c r="F71" s="46"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="46"/>
-      <c r="I71" s="46"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -8683,15 +8686,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="47"/>
-      <c r="B76" s="47"/>
-      <c r="C76" s="47"/>
-      <c r="D76" s="47"/>
-      <c r="E76" s="47"/>
-      <c r="F76" s="47"/>
-      <c r="G76" s="47"/>
-      <c r="H76" s="47"/>
-      <c r="I76" s="47"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -8727,15 +8730,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="48"/>
-      <c r="B80" s="48"/>
-      <c r="C80" s="48"/>
-      <c r="D80" s="48"/>
-      <c r="E80" s="48"/>
-      <c r="F80" s="48"/>
-      <c r="G80" s="48"/>
-      <c r="H80" s="48"/>
-      <c r="I80" s="48"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -8771,15 +8774,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="47"/>
-      <c r="B88" s="47"/>
-      <c r="C88" s="47"/>
-      <c r="D88" s="47"/>
-      <c r="E88" s="47"/>
-      <c r="F88" s="47"/>
-      <c r="G88" s="47"/>
-      <c r="H88" s="47"/>
-      <c r="I88" s="47"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -8882,15 +8885,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="46"/>
-      <c r="B101" s="46"/>
-      <c r="C101" s="46"/>
-      <c r="D101" s="46"/>
-      <c r="E101" s="46"/>
-      <c r="F101" s="46"/>
-      <c r="G101" s="46"/>
-      <c r="H101" s="46"/>
-      <c r="I101" s="46"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -11264,14 +11267,14 @@
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="46"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="46"/>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
       <c r="T32" s="27"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
@@ -11649,15 +11652,15 @@
       <c r="I66" s="1"/>
     </row>
     <row r="67" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="46"/>
-      <c r="B67" s="46"/>
-      <c r="C67" s="46"/>
-      <c r="D67" s="46"/>
-      <c r="E67" s="46"/>
-      <c r="F67" s="46"/>
-      <c r="G67" s="46"/>
-      <c r="H67" s="46"/>
-      <c r="I67" s="46"/>
+      <c r="A67" s="47"/>
+      <c r="B67" s="47"/>
+      <c r="C67" s="47"/>
+      <c r="D67" s="47"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="47"/>
+      <c r="G67" s="47"/>
+      <c r="H67" s="47"/>
+      <c r="I67" s="47"/>
     </row>
     <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
@@ -11682,15 +11685,15 @@
       <c r="I69" s="23"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="47"/>
-      <c r="B72" s="47"/>
-      <c r="C72" s="47"/>
-      <c r="D72" s="47"/>
-      <c r="E72" s="47"/>
-      <c r="F72" s="47"/>
-      <c r="G72" s="47"/>
-      <c r="H72" s="47"/>
-      <c r="I72" s="47"/>
+      <c r="A72" s="48"/>
+      <c r="B72" s="48"/>
+      <c r="C72" s="48"/>
+      <c r="D72" s="48"/>
+      <c r="E72" s="48"/>
+      <c r="F72" s="48"/>
+      <c r="G72" s="48"/>
+      <c r="H72" s="48"/>
+      <c r="I72" s="48"/>
     </row>
     <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
@@ -11726,15 +11729,15 @@
       <c r="I75" s="25"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="48"/>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
+      <c r="A76" s="49"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="49"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -11770,15 +11773,15 @@
       <c r="B82" s="23"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="47"/>
-      <c r="B84" s="47"/>
-      <c r="C84" s="47"/>
-      <c r="D84" s="47"/>
-      <c r="E84" s="47"/>
-      <c r="F84" s="47"/>
-      <c r="G84" s="47"/>
-      <c r="H84" s="47"/>
-      <c r="I84" s="47"/>
+      <c r="A84" s="48"/>
+      <c r="B84" s="48"/>
+      <c r="C84" s="48"/>
+      <c r="D84" s="48"/>
+      <c r="E84" s="48"/>
+      <c r="F84" s="48"/>
+      <c r="G84" s="48"/>
+      <c r="H84" s="48"/>
+      <c r="I84" s="48"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
@@ -11881,15 +11884,15 @@
       <c r="B95" s="26"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="46"/>
-      <c r="B97" s="46"/>
-      <c r="C97" s="46"/>
-      <c r="D97" s="46"/>
-      <c r="E97" s="46"/>
-      <c r="F97" s="46"/>
-      <c r="G97" s="46"/>
-      <c r="H97" s="46"/>
-      <c r="I97" s="46"/>
+      <c r="A97" s="47"/>
+      <c r="B97" s="47"/>
+      <c r="C97" s="47"/>
+      <c r="D97" s="47"/>
+      <c r="E97" s="47"/>
+      <c r="F97" s="47"/>
+      <c r="G97" s="47"/>
+      <c r="H97" s="47"/>
+      <c r="I97" s="47"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
@@ -14439,14 +14442,14 @@
     <row r="34" spans="1:21" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -14823,15 +14826,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="46"/>
-      <c r="B71" s="46"/>
-      <c r="C71" s="46"/>
-      <c r="D71" s="46"/>
-      <c r="E71" s="46"/>
-      <c r="F71" s="46"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="46"/>
-      <c r="I71" s="46"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -14856,15 +14859,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="47"/>
-      <c r="B76" s="47"/>
-      <c r="C76" s="47"/>
-      <c r="D76" s="47"/>
-      <c r="E76" s="47"/>
-      <c r="F76" s="47"/>
-      <c r="G76" s="47"/>
-      <c r="H76" s="47"/>
-      <c r="I76" s="47"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -14900,15 +14903,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="48"/>
-      <c r="B80" s="48"/>
-      <c r="C80" s="48"/>
-      <c r="D80" s="48"/>
-      <c r="E80" s="48"/>
-      <c r="F80" s="48"/>
-      <c r="G80" s="48"/>
-      <c r="H80" s="48"/>
-      <c r="I80" s="48"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -14944,15 +14947,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="47"/>
-      <c r="B88" s="47"/>
-      <c r="C88" s="47"/>
-      <c r="D88" s="47"/>
-      <c r="E88" s="47"/>
-      <c r="F88" s="47"/>
-      <c r="G88" s="47"/>
-      <c r="H88" s="47"/>
-      <c r="I88" s="47"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -15055,15 +15058,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="46"/>
-      <c r="B101" s="46"/>
-      <c r="C101" s="46"/>
-      <c r="D101" s="46"/>
-      <c r="E101" s="46"/>
-      <c r="F101" s="46"/>
-      <c r="G101" s="46"/>
-      <c r="H101" s="46"/>
-      <c r="I101" s="46"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -17798,14 +17801,14 @@
     </row>
     <row r="35" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
     </row>
     <row r="36" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -18183,15 +18186,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="46"/>
-      <c r="B70" s="46"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46"/>
-      <c r="I70" s="46"/>
+      <c r="A70" s="47"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -18216,15 +18219,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="47"/>
-      <c r="B75" s="47"/>
-      <c r="C75" s="47"/>
-      <c r="D75" s="47"/>
-      <c r="E75" s="47"/>
-      <c r="F75" s="47"/>
-      <c r="G75" s="47"/>
-      <c r="H75" s="47"/>
-      <c r="I75" s="47"/>
+      <c r="A75" s="48"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -18260,15 +18263,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="48"/>
-      <c r="B79" s="48"/>
-      <c r="C79" s="48"/>
-      <c r="D79" s="48"/>
-      <c r="E79" s="48"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="48"/>
-      <c r="H79" s="48"/>
-      <c r="I79" s="48"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -18304,15 +18307,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="47"/>
-      <c r="B87" s="47"/>
-      <c r="C87" s="47"/>
-      <c r="D87" s="47"/>
-      <c r="E87" s="47"/>
-      <c r="F87" s="47"/>
-      <c r="G87" s="47"/>
-      <c r="H87" s="47"/>
-      <c r="I87" s="47"/>
+      <c r="A87" s="48"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -18415,15 +18418,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="46"/>
-      <c r="B100" s="46"/>
-      <c r="C100" s="46"/>
-      <c r="D100" s="46"/>
-      <c r="E100" s="46"/>
-      <c r="F100" s="46"/>
-      <c r="G100" s="46"/>
-      <c r="H100" s="46"/>
-      <c r="I100" s="46"/>
+      <c r="A100" s="47"/>
+      <c r="B100" s="47"/>
+      <c r="C100" s="47"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="47"/>
+      <c r="I100" s="47"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -21050,14 +21053,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -21435,15 +21438,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="46"/>
-      <c r="B70" s="46"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46"/>
-      <c r="I70" s="46"/>
+      <c r="A70" s="47"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -21468,15 +21471,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="47"/>
-      <c r="B75" s="47"/>
-      <c r="C75" s="47"/>
-      <c r="D75" s="47"/>
-      <c r="E75" s="47"/>
-      <c r="F75" s="47"/>
-      <c r="G75" s="47"/>
-      <c r="H75" s="47"/>
-      <c r="I75" s="47"/>
+      <c r="A75" s="48"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -21512,15 +21515,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="48"/>
-      <c r="B79" s="48"/>
-      <c r="C79" s="48"/>
-      <c r="D79" s="48"/>
-      <c r="E79" s="48"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="48"/>
-      <c r="H79" s="48"/>
-      <c r="I79" s="48"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -21556,15 +21559,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="47"/>
-      <c r="B87" s="47"/>
-      <c r="C87" s="47"/>
-      <c r="D87" s="47"/>
-      <c r="E87" s="47"/>
-      <c r="F87" s="47"/>
-      <c r="G87" s="47"/>
-      <c r="H87" s="47"/>
-      <c r="I87" s="47"/>
+      <c r="A87" s="48"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -21667,15 +21670,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="46"/>
-      <c r="B100" s="46"/>
-      <c r="C100" s="46"/>
-      <c r="D100" s="46"/>
-      <c r="E100" s="46"/>
-      <c r="F100" s="46"/>
-      <c r="G100" s="46"/>
-      <c r="H100" s="46"/>
-      <c r="I100" s="46"/>
+      <c r="A100" s="47"/>
+      <c r="B100" s="47"/>
+      <c r="C100" s="47"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="47"/>
+      <c r="I100" s="47"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -24378,14 +24381,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -24763,15 +24766,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="46"/>
-      <c r="B71" s="46"/>
-      <c r="C71" s="46"/>
-      <c r="D71" s="46"/>
-      <c r="E71" s="46"/>
-      <c r="F71" s="46"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="46"/>
-      <c r="I71" s="46"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -24796,15 +24799,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="47"/>
-      <c r="B76" s="47"/>
-      <c r="C76" s="47"/>
-      <c r="D76" s="47"/>
-      <c r="E76" s="47"/>
-      <c r="F76" s="47"/>
-      <c r="G76" s="47"/>
-      <c r="H76" s="47"/>
-      <c r="I76" s="47"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -24840,15 +24843,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="48"/>
-      <c r="B80" s="48"/>
-      <c r="C80" s="48"/>
-      <c r="D80" s="48"/>
-      <c r="E80" s="48"/>
-      <c r="F80" s="48"/>
-      <c r="G80" s="48"/>
-      <c r="H80" s="48"/>
-      <c r="I80" s="48"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -24884,15 +24887,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="47"/>
-      <c r="B88" s="47"/>
-      <c r="C88" s="47"/>
-      <c r="D88" s="47"/>
-      <c r="E88" s="47"/>
-      <c r="F88" s="47"/>
-      <c r="G88" s="47"/>
-      <c r="H88" s="47"/>
-      <c r="I88" s="47"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -24995,15 +24998,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="46"/>
-      <c r="B101" s="46"/>
-      <c r="C101" s="46"/>
-      <c r="D101" s="46"/>
-      <c r="E101" s="46"/>
-      <c r="F101" s="46"/>
-      <c r="G101" s="46"/>
-      <c r="H101" s="46"/>
-      <c r="I101" s="46"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -27639,14 +27642,14 @@
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="46"/>
-      <c r="I34" s="46"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="47"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
@@ -28024,15 +28027,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="46"/>
-      <c r="B69" s="46"/>
-      <c r="C69" s="46"/>
-      <c r="D69" s="46"/>
-      <c r="E69" s="46"/>
-      <c r="F69" s="46"/>
-      <c r="G69" s="46"/>
-      <c r="H69" s="46"/>
-      <c r="I69" s="46"/>
+      <c r="A69" s="47"/>
+      <c r="B69" s="47"/>
+      <c r="C69" s="47"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="47"/>
+      <c r="G69" s="47"/>
+      <c r="H69" s="47"/>
+      <c r="I69" s="47"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -28057,15 +28060,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="47"/>
-      <c r="B74" s="47"/>
-      <c r="C74" s="47"/>
-      <c r="D74" s="47"/>
-      <c r="E74" s="47"/>
-      <c r="F74" s="47"/>
-      <c r="G74" s="47"/>
-      <c r="H74" s="47"/>
-      <c r="I74" s="47"/>
+      <c r="A74" s="48"/>
+      <c r="B74" s="48"/>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -28101,15 +28104,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="48"/>
-      <c r="B78" s="48"/>
-      <c r="C78" s="48"/>
-      <c r="D78" s="48"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="48"/>
-      <c r="G78" s="48"/>
-      <c r="H78" s="48"/>
-      <c r="I78" s="48"/>
+      <c r="A78" s="49"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="49"/>
+      <c r="D78" s="49"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="49"/>
+      <c r="G78" s="49"/>
+      <c r="H78" s="49"/>
+      <c r="I78" s="49"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -28145,15 +28148,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="47"/>
-      <c r="B86" s="47"/>
-      <c r="C86" s="47"/>
-      <c r="D86" s="47"/>
-      <c r="E86" s="47"/>
-      <c r="F86" s="47"/>
-      <c r="G86" s="47"/>
-      <c r="H86" s="47"/>
-      <c r="I86" s="47"/>
+      <c r="A86" s="48"/>
+      <c r="B86" s="48"/>
+      <c r="C86" s="48"/>
+      <c r="D86" s="48"/>
+      <c r="E86" s="48"/>
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="48"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -28256,15 +28259,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="46"/>
-      <c r="B99" s="46"/>
-      <c r="C99" s="46"/>
-      <c r="D99" s="46"/>
-      <c r="E99" s="46"/>
-      <c r="F99" s="46"/>
-      <c r="G99" s="46"/>
-      <c r="H99" s="46"/>
-      <c r="I99" s="46"/>
+      <c r="A99" s="47"/>
+      <c r="B99" s="47"/>
+      <c r="C99" s="47"/>
+      <c r="D99" s="47"/>
+      <c r="E99" s="47"/>
+      <c r="F99" s="47"/>
+      <c r="G99" s="47"/>
+      <c r="H99" s="47"/>
+      <c r="I99" s="47"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -28339,7 +28342,7 @@
     <col min="7" max="7" width="13.42578125" customWidth="1"/>
     <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="12" max="12" width="3.42578125" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
@@ -28449,49 +28452,49 @@
         <v>0</v>
       </c>
       <c r="D2" s="13">
-        <f t="shared" ref="D2:D32" si="0">W3-W2</f>
+        <f>W3-W2</f>
         <v>0</v>
       </c>
       <c r="E2" s="13">
         <v>0</v>
       </c>
       <c r="F2" s="13">
-        <f t="shared" ref="F2:F32" si="1">X3-X2</f>
+        <f t="shared" ref="F2:F32" si="0">X3-X2</f>
         <v>0</v>
       </c>
       <c r="G2" s="13">
         <v>0</v>
       </c>
       <c r="H2" s="13">
-        <f t="shared" ref="H2:H32" si="2">Y3-Y2</f>
+        <f t="shared" ref="H2:H32" si="1">Y3-Y2</f>
         <v>0</v>
       </c>
       <c r="I2" s="13">
         <v>0</v>
       </c>
       <c r="J2" s="13">
-        <f t="shared" ref="J2:J14" si="3">Z3-Z2</f>
+        <f t="shared" ref="J2:J14" si="2">Z3-Z2</f>
         <v>0</v>
       </c>
       <c r="K2" s="13">
         <v>0</v>
       </c>
       <c r="L2" s="13">
-        <f t="shared" ref="L2:L32" si="4">AA3-AA2</f>
+        <f t="shared" ref="L2:L32" si="3">AA3-AA2</f>
         <v>0</v>
       </c>
       <c r="M2" s="13">
         <v>0</v>
       </c>
       <c r="N2" s="13">
-        <f t="shared" ref="N2:N32" si="5">AB3-AB2</f>
+        <f t="shared" ref="N2:N32" si="4">AB3-AB2</f>
         <v>0</v>
       </c>
       <c r="O2" s="13">
         <v>0</v>
       </c>
       <c r="P2" s="13">
-        <f t="shared" ref="P2:P32" si="6">AC3-AC2</f>
+        <f t="shared" ref="P2:P32" si="5">AC3-AC2</f>
         <v>0</v>
       </c>
       <c r="Q2" s="13">
@@ -28501,7 +28504,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="13">
-        <f t="shared" ref="S2:S32" si="7">AD3-AD2</f>
+        <f t="shared" ref="S2:S32" si="6">AD3-AD2</f>
         <v>0</v>
       </c>
       <c r="T2" s="6"/>
@@ -28543,7 +28546,7 @@
     </row>
     <row r="3" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="28">
-        <f t="shared" ref="A3:A32" si="8">A2+1</f>
+        <f t="shared" ref="A3:A32" si="7">A2+1</f>
         <v>45871</v>
       </c>
       <c r="B3" s="13">
@@ -28553,59 +28556,59 @@
         <v>0</v>
       </c>
       <c r="D3" s="13">
+        <f t="shared" ref="D2:D32" si="8">W4-W3</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="13">
+        <v>0</v>
+      </c>
+      <c r="F3" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E3" s="13">
-        <v>0</v>
-      </c>
-      <c r="F3" s="13">
+      <c r="G3" s="13">
+        <v>0</v>
+      </c>
+      <c r="H3" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G3" s="13">
-        <v>0</v>
-      </c>
-      <c r="H3" s="13">
+      <c r="I3" s="13">
+        <v>0</v>
+      </c>
+      <c r="J3" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I3" s="13">
-        <v>0</v>
-      </c>
-      <c r="J3" s="13">
+      <c r="K3" s="13">
+        <v>0</v>
+      </c>
+      <c r="L3" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K3" s="13">
-        <v>0</v>
-      </c>
-      <c r="L3" s="13">
+      <c r="M3" s="13">
+        <v>0</v>
+      </c>
+      <c r="N3" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M3" s="13">
-        <v>0</v>
-      </c>
-      <c r="N3" s="13">
+      <c r="O3" s="13">
+        <v>0</v>
+      </c>
+      <c r="P3" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O3" s="13">
-        <v>0</v>
-      </c>
-      <c r="P3" s="13">
+      <c r="Q3" s="13">
+        <v>0</v>
+      </c>
+      <c r="R3" s="13">
+        <v>0</v>
+      </c>
+      <c r="S3" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="13">
-        <v>0</v>
-      </c>
-      <c r="R3" s="13">
-        <v>0</v>
-      </c>
-      <c r="S3" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T3" s="6"/>
@@ -28613,96 +28616,96 @@
       <c r="V3" s="12">
         <v>1</v>
       </c>
-      <c r="W3" s="49">
+      <c r="W3" s="46">
         <v>9135</v>
       </c>
-      <c r="X3" s="49">
+      <c r="X3" s="46">
         <v>11194</v>
       </c>
-      <c r="Y3" s="49">
+      <c r="Y3" s="46">
         <v>9505</v>
       </c>
-      <c r="Z3" s="49">
+      <c r="Z3" s="46">
         <v>10839</v>
       </c>
-      <c r="AA3" s="49">
+      <c r="AA3" s="46">
         <v>1282</v>
       </c>
-      <c r="AB3" s="49">
+      <c r="AB3" s="46">
         <v>3934</v>
       </c>
-      <c r="AC3" s="49">
+      <c r="AC3" s="46">
         <v>396</v>
       </c>
-      <c r="AD3" s="49">
+      <c r="AD3" s="46">
         <v>3537</v>
       </c>
     </row>
     <row r="4" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="28">
+        <f t="shared" si="7"/>
+        <v>45872</v>
+      </c>
+      <c r="B4" s="13">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13">
         <f t="shared" si="8"/>
-        <v>45872</v>
-      </c>
-      <c r="B4" s="13">
-        <v>0</v>
-      </c>
-      <c r="C4" s="13">
-        <v>0</v>
-      </c>
-      <c r="D4" s="13">
+        <v>0</v>
+      </c>
+      <c r="E4" s="13">
+        <v>0</v>
+      </c>
+      <c r="F4" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E4" s="13">
-        <v>0</v>
-      </c>
-      <c r="F4" s="13">
+      <c r="G4" s="13">
+        <v>0</v>
+      </c>
+      <c r="H4" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G4" s="13">
-        <v>0</v>
-      </c>
-      <c r="H4" s="13">
+      <c r="I4" s="13">
+        <v>0</v>
+      </c>
+      <c r="J4" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I4" s="13">
-        <v>0</v>
-      </c>
-      <c r="J4" s="13">
+      <c r="K4" s="13">
+        <v>0</v>
+      </c>
+      <c r="L4" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K4" s="13">
-        <v>0</v>
-      </c>
-      <c r="L4" s="13">
+      <c r="M4" s="13">
+        <v>0</v>
+      </c>
+      <c r="N4" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M4" s="13">
-        <v>0</v>
-      </c>
-      <c r="N4" s="13">
+      <c r="O4" s="13">
+        <v>0</v>
+      </c>
+      <c r="P4" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O4" s="13">
-        <v>0</v>
-      </c>
-      <c r="P4" s="13">
+      <c r="Q4" s="13">
+        <v>0</v>
+      </c>
+      <c r="R4" s="13">
+        <v>0</v>
+      </c>
+      <c r="S4" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>0</v>
-      </c>
-      <c r="R4" s="13">
-        <v>0</v>
-      </c>
-      <c r="S4" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T4" s="6"/>
@@ -28711,96 +28714,96 @@
         <f t="shared" ref="V4:V32" si="9">V3+1</f>
         <v>2</v>
       </c>
-      <c r="W4" s="49">
+      <c r="W4" s="46">
         <v>9135</v>
       </c>
-      <c r="X4" s="49">
+      <c r="X4" s="46">
         <v>11194</v>
       </c>
-      <c r="Y4" s="49">
+      <c r="Y4" s="46">
         <v>9505</v>
       </c>
-      <c r="Z4" s="49">
+      <c r="Z4" s="46">
         <v>10839</v>
       </c>
-      <c r="AA4" s="49">
+      <c r="AA4" s="46">
         <v>1282</v>
       </c>
-      <c r="AB4" s="49">
+      <c r="AB4" s="46">
         <v>3934</v>
       </c>
-      <c r="AC4" s="49">
+      <c r="AC4" s="46">
         <v>396</v>
       </c>
-      <c r="AD4" s="49">
+      <c r="AD4" s="46">
         <v>3537</v>
       </c>
     </row>
     <row r="5" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="28">
+        <f t="shared" si="7"/>
+        <v>45873</v>
+      </c>
+      <c r="B5" s="13">
+        <v>0</v>
+      </c>
+      <c r="C5" s="13">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13">
         <f t="shared" si="8"/>
-        <v>45873</v>
-      </c>
-      <c r="B5" s="13">
-        <v>0</v>
-      </c>
-      <c r="C5" s="13">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13">
+        <v>147</v>
+      </c>
+      <c r="E5" s="13">
+        <v>0</v>
+      </c>
+      <c r="F5" s="13">
         <f t="shared" si="0"/>
-        <v>147</v>
-      </c>
-      <c r="E5" s="13">
-        <v>0</v>
-      </c>
-      <c r="F5" s="13">
+        <v>180</v>
+      </c>
+      <c r="G5" s="13">
+        <v>0</v>
+      </c>
+      <c r="H5" s="13">
         <f t="shared" si="1"/>
-        <v>180</v>
-      </c>
-      <c r="G5" s="13">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13">
+        <v>22</v>
+      </c>
+      <c r="I5" s="13">
+        <v>0</v>
+      </c>
+      <c r="J5" s="13">
         <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="I5" s="13">
-        <v>0</v>
-      </c>
-      <c r="J5" s="13">
+        <v>2</v>
+      </c>
+      <c r="K5" s="13">
+        <v>0</v>
+      </c>
+      <c r="L5" s="13">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="13">
+        <v>0</v>
+      </c>
+      <c r="N5" s="13">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="O5" s="13">
+        <v>0</v>
+      </c>
+      <c r="P5" s="13">
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="K5" s="13">
-        <v>0</v>
-      </c>
-      <c r="L5" s="13">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="13">
-        <v>0</v>
-      </c>
-      <c r="N5" s="13">
-        <f t="shared" si="5"/>
-        <v>16</v>
-      </c>
-      <c r="O5" s="13">
-        <v>0</v>
-      </c>
-      <c r="P5" s="13">
+      <c r="Q5" s="13">
+        <v>0</v>
+      </c>
+      <c r="R5" s="13">
+        <v>0</v>
+      </c>
+      <c r="S5" s="13">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>0</v>
-      </c>
-      <c r="R5" s="13">
-        <v>0</v>
-      </c>
-      <c r="S5" s="13">
-        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="T5" s="6"/>
@@ -28809,96 +28812,96 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="W5" s="49">
+      <c r="W5" s="46">
         <v>9135</v>
       </c>
-      <c r="X5" s="49">
+      <c r="X5" s="46">
         <v>11194</v>
       </c>
-      <c r="Y5" s="49">
+      <c r="Y5" s="46">
         <v>9505</v>
       </c>
-      <c r="Z5" s="49">
+      <c r="Z5" s="46">
         <v>10839</v>
       </c>
-      <c r="AA5" s="49">
+      <c r="AA5" s="46">
         <v>1282</v>
       </c>
-      <c r="AB5" s="49">
+      <c r="AB5" s="46">
         <v>3934</v>
       </c>
-      <c r="AC5" s="49">
+      <c r="AC5" s="46">
         <v>396</v>
       </c>
-      <c r="AD5" s="49">
+      <c r="AD5" s="46">
         <v>3537</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="28">
+        <f t="shared" si="7"/>
+        <v>45874</v>
+      </c>
+      <c r="B6" s="13">
+        <v>0</v>
+      </c>
+      <c r="C6" s="13">
+        <v>0</v>
+      </c>
+      <c r="D6" s="13">
         <f t="shared" si="8"/>
-        <v>45874</v>
-      </c>
-      <c r="B6" s="13">
-        <v>0</v>
-      </c>
-      <c r="C6" s="13">
-        <v>0</v>
-      </c>
-      <c r="D6" s="13">
+        <v>43</v>
+      </c>
+      <c r="E6" s="13">
+        <v>0</v>
+      </c>
+      <c r="F6" s="13">
         <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="E6" s="13">
-        <v>0</v>
-      </c>
-      <c r="F6" s="13">
+        <v>51</v>
+      </c>
+      <c r="G6" s="13">
+        <v>0</v>
+      </c>
+      <c r="H6" s="13">
         <f t="shared" si="1"/>
-        <v>51</v>
-      </c>
-      <c r="G6" s="13">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13">
+        <v>4</v>
+      </c>
+      <c r="I6" s="13">
+        <v>0</v>
+      </c>
+      <c r="J6" s="13">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="I6" s="13">
-        <v>0</v>
-      </c>
-      <c r="J6" s="13">
+        <v>1</v>
+      </c>
+      <c r="K6" s="13">
+        <v>0</v>
+      </c>
+      <c r="L6" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K6" s="13">
-        <v>0</v>
-      </c>
-      <c r="L6" s="13">
+        <v>0</v>
+      </c>
+      <c r="M6" s="13">
+        <v>0</v>
+      </c>
+      <c r="N6" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="13">
-        <v>0</v>
-      </c>
-      <c r="N6" s="13">
+        <v>3</v>
+      </c>
+      <c r="O6" s="13">
+        <v>0</v>
+      </c>
+      <c r="P6" s="13">
         <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="O6" s="13">
-        <v>0</v>
-      </c>
-      <c r="P6" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>0</v>
+      </c>
+      <c r="R6" s="13">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>0</v>
-      </c>
-      <c r="R6" s="13">
-        <v>0</v>
-      </c>
-      <c r="S6" s="13">
-        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T6" s="6"/>
@@ -28934,69 +28937,69 @@
     </row>
     <row r="7" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="28">
+        <f t="shared" si="7"/>
+        <v>45875</v>
+      </c>
+      <c r="B7" s="13">
+        <v>0</v>
+      </c>
+      <c r="C7" s="13">
+        <v>0</v>
+      </c>
+      <c r="D7" s="13">
         <f t="shared" si="8"/>
-        <v>45875</v>
-      </c>
-      <c r="B7" s="13">
-        <v>0</v>
-      </c>
-      <c r="C7" s="13">
-        <v>0</v>
-      </c>
-      <c r="D7" s="13">
+        <v>-9325</v>
+      </c>
+      <c r="E7" s="13">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13">
         <f t="shared" si="0"/>
-        <v>-9325</v>
-      </c>
-      <c r="E7" s="13">
-        <v>0</v>
-      </c>
-      <c r="F7" s="13">
+        <v>-11425</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13">
         <f t="shared" si="1"/>
-        <v>-11425</v>
-      </c>
-      <c r="G7" s="13">
-        <v>0</v>
-      </c>
-      <c r="H7" s="13">
+        <v>-9531</v>
+      </c>
+      <c r="I7" s="13">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13">
         <f t="shared" si="2"/>
-        <v>-9531</v>
-      </c>
-      <c r="I7" s="13">
-        <v>0</v>
-      </c>
-      <c r="J7" s="13">
+        <v>-10842</v>
+      </c>
+      <c r="K7" s="13">
+        <v>0</v>
+      </c>
+      <c r="L7" s="13">
         <f t="shared" si="3"/>
-        <v>-10842</v>
-      </c>
-      <c r="K7" s="13">
-        <v>0</v>
-      </c>
-      <c r="L7" s="13">
+        <v>-1282</v>
+      </c>
+      <c r="M7" s="13">
+        <v>0</v>
+      </c>
+      <c r="N7" s="13">
         <f t="shared" si="4"/>
-        <v>-1282</v>
-      </c>
-      <c r="M7" s="13">
-        <v>0</v>
-      </c>
-      <c r="N7" s="13">
+        <v>-3953</v>
+      </c>
+      <c r="O7" s="13">
+        <v>0</v>
+      </c>
+      <c r="P7" s="13">
         <f t="shared" si="5"/>
-        <v>-3953</v>
-      </c>
-      <c r="O7" s="13">
-        <v>0</v>
-      </c>
-      <c r="P7" s="13">
+        <v>-398</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>0</v>
+      </c>
+      <c r="R7" s="13">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13">
         <f t="shared" si="6"/>
-        <v>-398</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>0</v>
-      </c>
-      <c r="R7" s="13">
-        <v>0</v>
-      </c>
-      <c r="S7" s="13">
-        <f t="shared" si="7"/>
         <v>-3553</v>
       </c>
       <c r="T7" s="6"/>
@@ -29032,69 +29035,69 @@
     </row>
     <row r="8" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="28">
+        <f t="shared" si="7"/>
+        <v>45876</v>
+      </c>
+      <c r="B8" s="13">
+        <v>0</v>
+      </c>
+      <c r="C8" s="13">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13">
         <f t="shared" si="8"/>
-        <v>45876</v>
-      </c>
-      <c r="B8" s="13">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13">
-        <v>0</v>
-      </c>
-      <c r="D8" s="13">
+        <v>0</v>
+      </c>
+      <c r="E8" s="13">
+        <v>0</v>
+      </c>
+      <c r="F8" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E8" s="13">
-        <v>0</v>
-      </c>
-      <c r="F8" s="13">
+      <c r="G8" s="13">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" s="13">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13">
+      <c r="I8" s="13">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I8" s="13">
-        <v>0</v>
-      </c>
-      <c r="J8" s="13">
+      <c r="K8" s="13">
+        <v>0</v>
+      </c>
+      <c r="L8" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K8" s="13">
-        <v>0</v>
-      </c>
-      <c r="L8" s="13">
+      <c r="M8" s="13">
+        <v>0</v>
+      </c>
+      <c r="N8" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M8" s="13">
-        <v>0</v>
-      </c>
-      <c r="N8" s="13">
+      <c r="O8" s="13">
+        <v>0</v>
+      </c>
+      <c r="P8" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O8" s="13">
-        <v>0</v>
-      </c>
-      <c r="P8" s="13">
+      <c r="Q8" s="13">
+        <v>0</v>
+      </c>
+      <c r="R8" s="13">
+        <v>0</v>
+      </c>
+      <c r="S8" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>0</v>
-      </c>
-      <c r="R8" s="13">
-        <v>0</v>
-      </c>
-      <c r="S8" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T8" s="6"/>
@@ -29114,69 +29117,69 @@
     </row>
     <row r="9" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="28">
+        <f t="shared" si="7"/>
+        <v>45877</v>
+      </c>
+      <c r="B9" s="13">
+        <v>0</v>
+      </c>
+      <c r="C9" s="13">
+        <v>0</v>
+      </c>
+      <c r="D9" s="13">
         <f t="shared" si="8"/>
-        <v>45877</v>
-      </c>
-      <c r="B9" s="13">
-        <v>0</v>
-      </c>
-      <c r="C9" s="13">
-        <v>0</v>
-      </c>
-      <c r="D9" s="13">
+        <v>0</v>
+      </c>
+      <c r="E9" s="13">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E9" s="13">
-        <v>0</v>
-      </c>
-      <c r="F9" s="13">
+      <c r="G9" s="13">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" s="13">
-        <v>0</v>
-      </c>
-      <c r="H9" s="13">
+      <c r="I9" s="13">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I9" s="13">
-        <v>0</v>
-      </c>
-      <c r="J9" s="13">
+      <c r="K9" s="13">
+        <v>0</v>
+      </c>
+      <c r="L9" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K9" s="13">
-        <v>0</v>
-      </c>
-      <c r="L9" s="13">
+      <c r="M9" s="13">
+        <v>0</v>
+      </c>
+      <c r="N9" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M9" s="13">
-        <v>0</v>
-      </c>
-      <c r="N9" s="13">
+      <c r="O9" s="13">
+        <v>0</v>
+      </c>
+      <c r="P9" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O9" s="13">
-        <v>0</v>
-      </c>
-      <c r="P9" s="13">
+      <c r="Q9" s="13">
+        <v>0</v>
+      </c>
+      <c r="R9" s="13">
+        <v>0</v>
+      </c>
+      <c r="S9" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>0</v>
-      </c>
-      <c r="R9" s="13">
-        <v>0</v>
-      </c>
-      <c r="S9" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T9" s="6"/>
@@ -29196,69 +29199,69 @@
     </row>
     <row r="10" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="28">
+        <f t="shared" si="7"/>
+        <v>45878</v>
+      </c>
+      <c r="B10" s="13">
+        <v>0</v>
+      </c>
+      <c r="C10" s="13">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13">
         <f t="shared" si="8"/>
-        <v>45878</v>
-      </c>
-      <c r="B10" s="13">
-        <v>0</v>
-      </c>
-      <c r="C10" s="13">
-        <v>0</v>
-      </c>
-      <c r="D10" s="13">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13">
+        <v>0</v>
+      </c>
+      <c r="F10" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10" s="13">
-        <v>0</v>
-      </c>
-      <c r="F10" s="13">
+      <c r="G10" s="13">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G10" s="13">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13">
+      <c r="I10" s="13">
+        <v>0</v>
+      </c>
+      <c r="J10" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I10" s="13">
-        <v>0</v>
-      </c>
-      <c r="J10" s="13">
+      <c r="K10" s="13">
+        <v>0</v>
+      </c>
+      <c r="L10" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K10" s="13">
-        <v>0</v>
-      </c>
-      <c r="L10" s="13">
+      <c r="M10" s="13">
+        <v>0</v>
+      </c>
+      <c r="N10" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M10" s="13">
-        <v>0</v>
-      </c>
-      <c r="N10" s="13">
+      <c r="O10" s="13">
+        <v>0</v>
+      </c>
+      <c r="P10" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O10" s="13">
-        <v>0</v>
-      </c>
-      <c r="P10" s="13">
+      <c r="Q10" s="13">
+        <v>0</v>
+      </c>
+      <c r="R10" s="13">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>0</v>
-      </c>
-      <c r="R10" s="13">
-        <v>0</v>
-      </c>
-      <c r="S10" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T10" s="6"/>
@@ -29278,69 +29281,69 @@
     </row>
     <row r="11" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="28">
+        <f t="shared" si="7"/>
+        <v>45879</v>
+      </c>
+      <c r="B11" s="13">
+        <v>0</v>
+      </c>
+      <c r="C11" s="13">
+        <v>0</v>
+      </c>
+      <c r="D11" s="13">
         <f t="shared" si="8"/>
-        <v>45879</v>
-      </c>
-      <c r="B11" s="13">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13">
-        <v>0</v>
-      </c>
-      <c r="D11" s="13">
+        <v>0</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E11" s="13">
-        <v>0</v>
-      </c>
-      <c r="F11" s="13">
+      <c r="G11" s="13">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G11" s="13">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13">
+      <c r="I11" s="13">
+        <v>0</v>
+      </c>
+      <c r="J11" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I11" s="13">
-        <v>0</v>
-      </c>
-      <c r="J11" s="13">
+      <c r="K11" s="13">
+        <v>0</v>
+      </c>
+      <c r="L11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K11" s="13">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13">
+      <c r="M11" s="13">
+        <v>0</v>
+      </c>
+      <c r="N11" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M11" s="13">
-        <v>0</v>
-      </c>
-      <c r="N11" s="13">
+      <c r="O11" s="13">
+        <v>0</v>
+      </c>
+      <c r="P11" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="13">
-        <v>0</v>
-      </c>
-      <c r="P11" s="13">
+      <c r="Q11" s="13">
+        <v>0</v>
+      </c>
+      <c r="R11" s="13">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>0</v>
-      </c>
-      <c r="R11" s="13">
-        <v>0</v>
-      </c>
-      <c r="S11" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T11" s="6"/>
@@ -29360,69 +29363,69 @@
     </row>
     <row r="12" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="28">
+        <f t="shared" si="7"/>
+        <v>45880</v>
+      </c>
+      <c r="B12" s="13">
+        <v>0</v>
+      </c>
+      <c r="C12" s="13">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13">
         <f t="shared" si="8"/>
-        <v>45880</v>
-      </c>
-      <c r="B12" s="13">
-        <v>0</v>
-      </c>
-      <c r="C12" s="13">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E12" s="13">
-        <v>0</v>
-      </c>
-      <c r="F12" s="13">
+      <c r="G12" s="13">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G12" s="13">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13">
+      <c r="I12" s="13">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I12" s="13">
-        <v>0</v>
-      </c>
-      <c r="J12" s="13">
+      <c r="K12" s="13">
+        <v>0</v>
+      </c>
+      <c r="L12" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K12" s="13">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13">
+      <c r="M12" s="13">
+        <v>0</v>
+      </c>
+      <c r="N12" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M12" s="13">
-        <v>0</v>
-      </c>
-      <c r="N12" s="13">
+      <c r="O12" s="13">
+        <v>0</v>
+      </c>
+      <c r="P12" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O12" s="13">
-        <v>0</v>
-      </c>
-      <c r="P12" s="13">
+      <c r="Q12" s="13">
+        <v>0</v>
+      </c>
+      <c r="R12" s="13">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>0</v>
-      </c>
-      <c r="R12" s="13">
-        <v>0</v>
-      </c>
-      <c r="S12" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T12" s="6"/>
@@ -29442,69 +29445,69 @@
     </row>
     <row r="13" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
+        <f t="shared" si="7"/>
+        <v>45881</v>
+      </c>
+      <c r="B13" s="13">
+        <v>0</v>
+      </c>
+      <c r="C13" s="13">
+        <v>0</v>
+      </c>
+      <c r="D13" s="13">
         <f t="shared" si="8"/>
-        <v>45881</v>
-      </c>
-      <c r="B13" s="13">
-        <v>0</v>
-      </c>
-      <c r="C13" s="13">
-        <v>0</v>
-      </c>
-      <c r="D13" s="13">
+        <v>0</v>
+      </c>
+      <c r="E13" s="13">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E13" s="13">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13">
+      <c r="G13" s="13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G13" s="13">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13">
+      <c r="I13" s="13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I13" s="13">
-        <v>0</v>
-      </c>
-      <c r="J13" s="13">
+      <c r="K13" s="13">
+        <v>0</v>
+      </c>
+      <c r="L13" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K13" s="13">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13">
+      <c r="M13" s="13">
+        <v>0</v>
+      </c>
+      <c r="N13" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M13" s="13">
-        <v>0</v>
-      </c>
-      <c r="N13" s="13">
+      <c r="O13" s="13">
+        <v>0</v>
+      </c>
+      <c r="P13" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O13" s="13">
-        <v>0</v>
-      </c>
-      <c r="P13" s="13">
+      <c r="Q13" s="13">
+        <v>0</v>
+      </c>
+      <c r="R13" s="13">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>0</v>
-      </c>
-      <c r="R13" s="13">
-        <v>0</v>
-      </c>
-      <c r="S13" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T13" s="6"/>
@@ -29524,69 +29527,69 @@
     </row>
     <row r="14" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="28">
+        <f t="shared" si="7"/>
+        <v>45882</v>
+      </c>
+      <c r="B14" s="13">
+        <v>0</v>
+      </c>
+      <c r="C14" s="13">
+        <v>0</v>
+      </c>
+      <c r="D14" s="13">
         <f t="shared" si="8"/>
-        <v>45882</v>
-      </c>
-      <c r="B14" s="13">
-        <v>0</v>
-      </c>
-      <c r="C14" s="13">
-        <v>0</v>
-      </c>
-      <c r="D14" s="13">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E14" s="13">
-        <v>0</v>
-      </c>
-      <c r="F14" s="13">
+      <c r="G14" s="13">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G14" s="13">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13">
+      <c r="I14" s="13">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I14" s="13">
-        <v>0</v>
-      </c>
-      <c r="J14" s="13">
+      <c r="K14" s="13">
+        <v>0</v>
+      </c>
+      <c r="L14" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K14" s="13">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13">
+      <c r="M14" s="13">
+        <v>0</v>
+      </c>
+      <c r="N14" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M14" s="13">
-        <v>0</v>
-      </c>
-      <c r="N14" s="13">
+      <c r="O14" s="13">
+        <v>0</v>
+      </c>
+      <c r="P14" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O14" s="13">
-        <v>0</v>
-      </c>
-      <c r="P14" s="13">
+      <c r="Q14" s="13">
+        <v>0</v>
+      </c>
+      <c r="R14" s="13">
+        <v>0</v>
+      </c>
+      <c r="S14" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>0</v>
-      </c>
-      <c r="R14" s="13">
-        <v>0</v>
-      </c>
-      <c r="S14" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T14" s="6"/>
@@ -29606,31 +29609,31 @@
     </row>
     <row r="15" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="28">
+        <f t="shared" si="7"/>
+        <v>45883</v>
+      </c>
+      <c r="B15" s="13">
+        <v>0</v>
+      </c>
+      <c r="C15" s="13">
+        <v>0</v>
+      </c>
+      <c r="D15" s="13">
         <f t="shared" si="8"/>
-        <v>45883</v>
-      </c>
-      <c r="B15" s="13">
-        <v>0</v>
-      </c>
-      <c r="C15" s="13">
-        <v>0</v>
-      </c>
-      <c r="D15" s="13">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13">
+        <v>0</v>
+      </c>
+      <c r="F15" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E15" s="13">
-        <v>0</v>
-      </c>
-      <c r="F15" s="13">
+      <c r="G15" s="13">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="13">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="13">
@@ -29643,31 +29646,31 @@
         <v>0</v>
       </c>
       <c r="L15" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="13">
+        <v>0</v>
+      </c>
+      <c r="N15" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M15" s="13">
-        <v>0</v>
-      </c>
-      <c r="N15" s="13">
+      <c r="O15" s="13">
+        <v>0</v>
+      </c>
+      <c r="P15" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O15" s="13">
-        <v>0</v>
-      </c>
-      <c r="P15" s="13">
+      <c r="Q15" s="13">
+        <v>0</v>
+      </c>
+      <c r="R15" s="13">
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>0</v>
-      </c>
-      <c r="R15" s="13">
-        <v>0</v>
-      </c>
-      <c r="S15" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T15" s="6"/>
@@ -29687,31 +29690,31 @@
     </row>
     <row r="16" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="28">
+        <f t="shared" si="7"/>
+        <v>45884</v>
+      </c>
+      <c r="B16" s="13">
+        <v>0</v>
+      </c>
+      <c r="C16" s="13">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13">
         <f t="shared" si="8"/>
-        <v>45884</v>
-      </c>
-      <c r="B16" s="13">
-        <v>0</v>
-      </c>
-      <c r="C16" s="13">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13">
+        <v>0</v>
+      </c>
+      <c r="E16" s="13">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E16" s="13">
-        <v>0</v>
-      </c>
-      <c r="F16" s="13">
+      <c r="G16" s="13">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="13">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I16" s="13">
@@ -29725,31 +29728,31 @@
         <v>0</v>
       </c>
       <c r="L16" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="13">
+        <v>0</v>
+      </c>
+      <c r="N16" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M16" s="13">
-        <v>0</v>
-      </c>
-      <c r="N16" s="13">
+      <c r="O16" s="13">
+        <v>0</v>
+      </c>
+      <c r="P16" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O16" s="13">
-        <v>0</v>
-      </c>
-      <c r="P16" s="13">
+      <c r="Q16" s="13">
+        <v>0</v>
+      </c>
+      <c r="R16" s="13">
+        <v>0</v>
+      </c>
+      <c r="S16" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="13">
-        <v>0</v>
-      </c>
-      <c r="R16" s="13">
-        <v>0</v>
-      </c>
-      <c r="S16" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T16" s="6"/>
@@ -29769,31 +29772,31 @@
     </row>
     <row r="17" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="28">
+        <f t="shared" si="7"/>
+        <v>45885</v>
+      </c>
+      <c r="B17" s="13">
+        <v>0</v>
+      </c>
+      <c r="C17" s="13">
+        <v>0</v>
+      </c>
+      <c r="D17" s="13">
         <f t="shared" si="8"/>
-        <v>45885</v>
-      </c>
-      <c r="B17" s="13">
-        <v>0</v>
-      </c>
-      <c r="C17" s="13">
-        <v>0</v>
-      </c>
-      <c r="D17" s="13">
+        <v>0</v>
+      </c>
+      <c r="E17" s="13">
+        <v>0</v>
+      </c>
+      <c r="F17" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E17" s="13">
-        <v>0</v>
-      </c>
-      <c r="F17" s="13">
+      <c r="G17" s="13">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="13">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I17" s="13">
@@ -29807,31 +29810,31 @@
         <v>0</v>
       </c>
       <c r="L17" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="13">
+        <v>0</v>
+      </c>
+      <c r="N17" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M17" s="13">
-        <v>0</v>
-      </c>
-      <c r="N17" s="13">
+      <c r="O17" s="13">
+        <v>0</v>
+      </c>
+      <c r="P17" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O17" s="13">
-        <v>0</v>
-      </c>
-      <c r="P17" s="13">
+      <c r="Q17" s="13">
+        <v>0</v>
+      </c>
+      <c r="R17" s="13">
+        <v>0</v>
+      </c>
+      <c r="S17" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="13">
-        <v>0</v>
-      </c>
-      <c r="R17" s="13">
-        <v>0</v>
-      </c>
-      <c r="S17" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T17" s="6"/>
@@ -29851,31 +29854,31 @@
     </row>
     <row r="18" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="28">
+        <f t="shared" si="7"/>
+        <v>45886</v>
+      </c>
+      <c r="B18" s="13">
+        <v>0</v>
+      </c>
+      <c r="C18" s="13">
+        <v>0</v>
+      </c>
+      <c r="D18" s="13">
         <f t="shared" si="8"/>
-        <v>45886</v>
-      </c>
-      <c r="B18" s="13">
-        <v>0</v>
-      </c>
-      <c r="C18" s="13">
-        <v>0</v>
-      </c>
-      <c r="D18" s="13">
+        <v>0</v>
+      </c>
+      <c r="E18" s="13">
+        <v>0</v>
+      </c>
+      <c r="F18" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E18" s="13">
-        <v>0</v>
-      </c>
-      <c r="F18" s="13">
+      <c r="G18" s="13">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="13">
-        <v>0</v>
-      </c>
-      <c r="H18" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I18" s="13">
@@ -29889,31 +29892,31 @@
         <v>0</v>
       </c>
       <c r="L18" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="13">
+        <v>0</v>
+      </c>
+      <c r="N18" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M18" s="13">
-        <v>0</v>
-      </c>
-      <c r="N18" s="13">
+      <c r="O18" s="13">
+        <v>0</v>
+      </c>
+      <c r="P18" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O18" s="13">
-        <v>0</v>
-      </c>
-      <c r="P18" s="13">
+      <c r="Q18" s="13">
+        <v>0</v>
+      </c>
+      <c r="R18" s="13">
+        <v>0</v>
+      </c>
+      <c r="S18" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>0</v>
-      </c>
-      <c r="R18" s="13">
-        <v>0</v>
-      </c>
-      <c r="S18" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T18" s="6"/>
@@ -29933,31 +29936,31 @@
     </row>
     <row r="19" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="28">
+        <f t="shared" si="7"/>
+        <v>45887</v>
+      </c>
+      <c r="B19" s="13">
+        <v>0</v>
+      </c>
+      <c r="C19" s="13">
+        <v>0</v>
+      </c>
+      <c r="D19" s="13">
         <f t="shared" si="8"/>
-        <v>45887</v>
-      </c>
-      <c r="B19" s="13">
-        <v>0</v>
-      </c>
-      <c r="C19" s="13">
-        <v>0</v>
-      </c>
-      <c r="D19" s="13">
+        <v>0</v>
+      </c>
+      <c r="E19" s="13">
+        <v>0</v>
+      </c>
+      <c r="F19" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E19" s="13">
-        <v>0</v>
-      </c>
-      <c r="F19" s="13">
+      <c r="G19" s="13">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="13">
-        <v>0</v>
-      </c>
-      <c r="H19" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I19" s="13">
@@ -29971,31 +29974,31 @@
         <v>0</v>
       </c>
       <c r="L19" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="13">
+        <v>0</v>
+      </c>
+      <c r="N19" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M19" s="13">
-        <v>0</v>
-      </c>
-      <c r="N19" s="13">
+      <c r="O19" s="13">
+        <v>0</v>
+      </c>
+      <c r="P19" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O19" s="13">
-        <v>0</v>
-      </c>
-      <c r="P19" s="13">
+      <c r="Q19" s="13">
+        <v>0</v>
+      </c>
+      <c r="R19" s="13">
+        <v>0</v>
+      </c>
+      <c r="S19" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="13">
-        <v>0</v>
-      </c>
-      <c r="R19" s="13">
-        <v>0</v>
-      </c>
-      <c r="S19" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T19" s="6"/>
@@ -30015,31 +30018,31 @@
     </row>
     <row r="20" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="28">
+        <f t="shared" si="7"/>
+        <v>45888</v>
+      </c>
+      <c r="B20" s="13">
+        <v>0</v>
+      </c>
+      <c r="C20" s="13">
+        <v>0</v>
+      </c>
+      <c r="D20" s="13">
         <f t="shared" si="8"/>
-        <v>45888</v>
-      </c>
-      <c r="B20" s="13">
-        <v>0</v>
-      </c>
-      <c r="C20" s="13">
-        <v>0</v>
-      </c>
-      <c r="D20" s="13">
+        <v>0</v>
+      </c>
+      <c r="E20" s="13">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E20" s="13">
-        <v>0</v>
-      </c>
-      <c r="F20" s="13">
+      <c r="G20" s="13">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="13">
-        <v>0</v>
-      </c>
-      <c r="H20" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I20" s="13">
@@ -30053,31 +30056,31 @@
         <v>0</v>
       </c>
       <c r="L20" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="13">
+        <v>0</v>
+      </c>
+      <c r="N20" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M20" s="13">
-        <v>0</v>
-      </c>
-      <c r="N20" s="13">
+      <c r="O20" s="13">
+        <v>0</v>
+      </c>
+      <c r="P20" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O20" s="13">
-        <v>0</v>
-      </c>
-      <c r="P20" s="13">
+      <c r="Q20" s="13">
+        <v>0</v>
+      </c>
+      <c r="R20" s="13">
+        <v>0</v>
+      </c>
+      <c r="S20" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="13">
-        <v>0</v>
-      </c>
-      <c r="R20" s="13">
-        <v>0</v>
-      </c>
-      <c r="S20" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T20" s="6"/>
@@ -30097,31 +30100,31 @@
     </row>
     <row r="21" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="28">
+        <f t="shared" si="7"/>
+        <v>45889</v>
+      </c>
+      <c r="B21" s="13">
+        <v>0</v>
+      </c>
+      <c r="C21" s="13">
+        <v>0</v>
+      </c>
+      <c r="D21" s="13">
         <f t="shared" si="8"/>
-        <v>45889</v>
-      </c>
-      <c r="B21" s="13">
-        <v>0</v>
-      </c>
-      <c r="C21" s="13">
-        <v>0</v>
-      </c>
-      <c r="D21" s="13">
+        <v>0</v>
+      </c>
+      <c r="E21" s="13">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E21" s="13">
-        <v>0</v>
-      </c>
-      <c r="F21" s="13">
+      <c r="G21" s="13">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="13">
-        <v>0</v>
-      </c>
-      <c r="H21" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I21" s="13">
@@ -30135,31 +30138,31 @@
         <v>0</v>
       </c>
       <c r="L21" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="13">
+        <v>0</v>
+      </c>
+      <c r="N21" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M21" s="13">
-        <v>0</v>
-      </c>
-      <c r="N21" s="13">
+      <c r="O21" s="13">
+        <v>0</v>
+      </c>
+      <c r="P21" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O21" s="13">
-        <v>0</v>
-      </c>
-      <c r="P21" s="13">
+      <c r="Q21" s="13">
+        <v>0</v>
+      </c>
+      <c r="R21" s="13">
+        <v>0</v>
+      </c>
+      <c r="S21" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="13">
-        <v>0</v>
-      </c>
-      <c r="R21" s="13">
-        <v>0</v>
-      </c>
-      <c r="S21" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T21" s="6"/>
@@ -30179,31 +30182,31 @@
     </row>
     <row r="22" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="28">
+        <f t="shared" si="7"/>
+        <v>45890</v>
+      </c>
+      <c r="B22" s="13">
+        <v>0</v>
+      </c>
+      <c r="C22" s="13">
+        <v>0</v>
+      </c>
+      <c r="D22" s="13">
         <f t="shared" si="8"/>
-        <v>45890</v>
-      </c>
-      <c r="B22" s="13">
-        <v>0</v>
-      </c>
-      <c r="C22" s="13">
-        <v>0</v>
-      </c>
-      <c r="D22" s="13">
+        <v>0</v>
+      </c>
+      <c r="E22" s="13">
+        <v>0</v>
+      </c>
+      <c r="F22" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E22" s="13">
-        <v>0</v>
-      </c>
-      <c r="F22" s="13">
+      <c r="G22" s="13">
+        <v>0</v>
+      </c>
+      <c r="H22" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="13">
-        <v>0</v>
-      </c>
-      <c r="H22" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I22" s="13">
@@ -30217,31 +30220,31 @@
         <v>0</v>
       </c>
       <c r="L22" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="13">
+        <v>0</v>
+      </c>
+      <c r="N22" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M22" s="13">
-        <v>0</v>
-      </c>
-      <c r="N22" s="13">
+      <c r="O22" s="13">
+        <v>0</v>
+      </c>
+      <c r="P22" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O22" s="13">
-        <v>0</v>
-      </c>
-      <c r="P22" s="13">
+      <c r="Q22" s="13">
+        <v>0</v>
+      </c>
+      <c r="R22" s="13">
+        <v>0</v>
+      </c>
+      <c r="S22" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>0</v>
-      </c>
-      <c r="R22" s="13">
-        <v>0</v>
-      </c>
-      <c r="S22" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T22" s="6"/>
@@ -30261,31 +30264,31 @@
     </row>
     <row r="23" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="28">
+        <f t="shared" si="7"/>
+        <v>45891</v>
+      </c>
+      <c r="B23" s="13">
+        <v>0</v>
+      </c>
+      <c r="C23" s="13">
+        <v>0</v>
+      </c>
+      <c r="D23" s="13">
         <f t="shared" si="8"/>
-        <v>45891</v>
-      </c>
-      <c r="B23" s="13">
-        <v>0</v>
-      </c>
-      <c r="C23" s="13">
-        <v>0</v>
-      </c>
-      <c r="D23" s="13">
+        <v>0</v>
+      </c>
+      <c r="E23" s="13">
+        <v>0</v>
+      </c>
+      <c r="F23" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E23" s="13">
-        <v>0</v>
-      </c>
-      <c r="F23" s="13">
+      <c r="G23" s="13">
+        <v>0</v>
+      </c>
+      <c r="H23" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="13">
-        <v>0</v>
-      </c>
-      <c r="H23" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I23" s="13">
@@ -30299,31 +30302,31 @@
         <v>0</v>
       </c>
       <c r="L23" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="13">
+        <v>0</v>
+      </c>
+      <c r="N23" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M23" s="13">
-        <v>0</v>
-      </c>
-      <c r="N23" s="13">
+      <c r="O23" s="13">
+        <v>0</v>
+      </c>
+      <c r="P23" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O23" s="13">
-        <v>0</v>
-      </c>
-      <c r="P23" s="13">
+      <c r="Q23" s="13">
+        <v>0</v>
+      </c>
+      <c r="R23" s="13">
+        <v>0</v>
+      </c>
+      <c r="S23" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="13">
-        <v>0</v>
-      </c>
-      <c r="R23" s="13">
-        <v>0</v>
-      </c>
-      <c r="S23" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T23" s="6"/>
@@ -30343,31 +30346,31 @@
     </row>
     <row r="24" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="28">
+        <f t="shared" si="7"/>
+        <v>45892</v>
+      </c>
+      <c r="B24" s="13">
+        <v>0</v>
+      </c>
+      <c r="C24" s="13">
+        <v>0</v>
+      </c>
+      <c r="D24" s="13">
         <f t="shared" si="8"/>
-        <v>45892</v>
-      </c>
-      <c r="B24" s="13">
-        <v>0</v>
-      </c>
-      <c r="C24" s="13">
-        <v>0</v>
-      </c>
-      <c r="D24" s="13">
+        <v>0</v>
+      </c>
+      <c r="E24" s="13">
+        <v>0</v>
+      </c>
+      <c r="F24" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E24" s="13">
-        <v>0</v>
-      </c>
-      <c r="F24" s="13">
+      <c r="G24" s="13">
+        <v>0</v>
+      </c>
+      <c r="H24" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="13">
-        <v>0</v>
-      </c>
-      <c r="H24" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I24" s="13">
@@ -30381,31 +30384,31 @@
         <v>0</v>
       </c>
       <c r="L24" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="13">
+        <v>0</v>
+      </c>
+      <c r="N24" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M24" s="13">
-        <v>0</v>
-      </c>
-      <c r="N24" s="13">
+      <c r="O24" s="13">
+        <v>0</v>
+      </c>
+      <c r="P24" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O24" s="13">
-        <v>0</v>
-      </c>
-      <c r="P24" s="13">
+      <c r="Q24" s="13">
+        <v>0</v>
+      </c>
+      <c r="R24" s="13">
+        <v>0</v>
+      </c>
+      <c r="S24" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="13">
-        <v>0</v>
-      </c>
-      <c r="R24" s="13">
-        <v>0</v>
-      </c>
-      <c r="S24" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T24" s="6"/>
@@ -30425,31 +30428,31 @@
     </row>
     <row r="25" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="28">
+        <f t="shared" si="7"/>
+        <v>45893</v>
+      </c>
+      <c r="B25" s="13">
+        <v>0</v>
+      </c>
+      <c r="C25" s="13">
+        <v>0</v>
+      </c>
+      <c r="D25" s="13">
         <f t="shared" si="8"/>
-        <v>45893</v>
-      </c>
-      <c r="B25" s="13">
-        <v>0</v>
-      </c>
-      <c r="C25" s="13">
-        <v>0</v>
-      </c>
-      <c r="D25" s="13">
+        <v>0</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0</v>
+      </c>
+      <c r="F25" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E25" s="13">
-        <v>0</v>
-      </c>
-      <c r="F25" s="13">
+      <c r="G25" s="13">
+        <v>0</v>
+      </c>
+      <c r="H25" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="13">
-        <v>0</v>
-      </c>
-      <c r="H25" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I25" s="13">
@@ -30463,31 +30466,31 @@
         <v>0</v>
       </c>
       <c r="L25" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="13">
+        <v>0</v>
+      </c>
+      <c r="N25" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M25" s="13">
-        <v>0</v>
-      </c>
-      <c r="N25" s="13">
+      <c r="O25" s="13">
+        <v>0</v>
+      </c>
+      <c r="P25" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O25" s="13">
-        <v>0</v>
-      </c>
-      <c r="P25" s="13">
+      <c r="Q25" s="13">
+        <v>0</v>
+      </c>
+      <c r="R25" s="13">
+        <v>0</v>
+      </c>
+      <c r="S25" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="13">
-        <v>0</v>
-      </c>
-      <c r="R25" s="13">
-        <v>0</v>
-      </c>
-      <c r="S25" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T25" s="6"/>
@@ -30507,31 +30510,31 @@
     </row>
     <row r="26" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="28">
+        <f t="shared" si="7"/>
+        <v>45894</v>
+      </c>
+      <c r="B26" s="13">
+        <v>0</v>
+      </c>
+      <c r="C26" s="13">
+        <v>0</v>
+      </c>
+      <c r="D26" s="13">
         <f t="shared" si="8"/>
-        <v>45894</v>
-      </c>
-      <c r="B26" s="13">
-        <v>0</v>
-      </c>
-      <c r="C26" s="13">
-        <v>0</v>
-      </c>
-      <c r="D26" s="13">
+        <v>0</v>
+      </c>
+      <c r="E26" s="13">
+        <v>0</v>
+      </c>
+      <c r="F26" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="13">
-        <v>0</v>
-      </c>
-      <c r="F26" s="13">
+      <c r="G26" s="13">
+        <v>0</v>
+      </c>
+      <c r="H26" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="13">
-        <v>0</v>
-      </c>
-      <c r="H26" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I26" s="13">
@@ -30545,31 +30548,31 @@
         <v>0</v>
       </c>
       <c r="L26" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="13">
+        <v>0</v>
+      </c>
+      <c r="N26" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M26" s="13">
-        <v>0</v>
-      </c>
-      <c r="N26" s="13">
+      <c r="O26" s="13">
+        <v>0</v>
+      </c>
+      <c r="P26" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O26" s="13">
-        <v>0</v>
-      </c>
-      <c r="P26" s="13">
+      <c r="Q26" s="13">
+        <v>0</v>
+      </c>
+      <c r="R26" s="13">
+        <v>0</v>
+      </c>
+      <c r="S26" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="13">
-        <v>0</v>
-      </c>
-      <c r="R26" s="13">
-        <v>0</v>
-      </c>
-      <c r="S26" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T26" s="6"/>
@@ -30589,31 +30592,31 @@
     </row>
     <row r="27" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="28">
+        <f t="shared" si="7"/>
+        <v>45895</v>
+      </c>
+      <c r="B27" s="13">
+        <v>0</v>
+      </c>
+      <c r="C27" s="13">
+        <v>0</v>
+      </c>
+      <c r="D27" s="13">
         <f t="shared" si="8"/>
-        <v>45895</v>
-      </c>
-      <c r="B27" s="13">
-        <v>0</v>
-      </c>
-      <c r="C27" s="13">
-        <v>0</v>
-      </c>
-      <c r="D27" s="13">
+        <v>0</v>
+      </c>
+      <c r="E27" s="13">
+        <v>0</v>
+      </c>
+      <c r="F27" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E27" s="13">
-        <v>0</v>
-      </c>
-      <c r="F27" s="13">
+      <c r="G27" s="13">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="13">
-        <v>0</v>
-      </c>
-      <c r="H27" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I27" s="13">
@@ -30627,31 +30630,31 @@
         <v>0</v>
       </c>
       <c r="L27" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="13">
+        <v>0</v>
+      </c>
+      <c r="N27" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M27" s="13">
-        <v>0</v>
-      </c>
-      <c r="N27" s="13">
+      <c r="O27" s="13">
+        <v>0</v>
+      </c>
+      <c r="P27" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O27" s="13">
-        <v>0</v>
-      </c>
-      <c r="P27" s="13">
+      <c r="Q27" s="13">
+        <v>0</v>
+      </c>
+      <c r="R27" s="13">
+        <v>0</v>
+      </c>
+      <c r="S27" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="13">
-        <v>0</v>
-      </c>
-      <c r="R27" s="13">
-        <v>0</v>
-      </c>
-      <c r="S27" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T27" s="6"/>
@@ -30671,31 +30674,31 @@
     </row>
     <row r="28" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="28">
+        <f t="shared" si="7"/>
+        <v>45896</v>
+      </c>
+      <c r="B28" s="13">
+        <v>0</v>
+      </c>
+      <c r="C28" s="13">
+        <v>0</v>
+      </c>
+      <c r="D28" s="13">
         <f t="shared" si="8"/>
-        <v>45896</v>
-      </c>
-      <c r="B28" s="13">
-        <v>0</v>
-      </c>
-      <c r="C28" s="13">
-        <v>0</v>
-      </c>
-      <c r="D28" s="13">
+        <v>0</v>
+      </c>
+      <c r="E28" s="13">
+        <v>0</v>
+      </c>
+      <c r="F28" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="13">
-        <v>0</v>
-      </c>
-      <c r="F28" s="13">
+      <c r="G28" s="13">
+        <v>0</v>
+      </c>
+      <c r="H28" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G28" s="13">
-        <v>0</v>
-      </c>
-      <c r="H28" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I28" s="13">
@@ -30709,31 +30712,31 @@
         <v>0</v>
       </c>
       <c r="L28" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="13">
+        <v>0</v>
+      </c>
+      <c r="N28" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M28" s="13">
-        <v>0</v>
-      </c>
-      <c r="N28" s="13">
+      <c r="O28" s="13">
+        <v>0</v>
+      </c>
+      <c r="P28" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O28" s="13">
-        <v>0</v>
-      </c>
-      <c r="P28" s="13">
+      <c r="Q28" s="13">
+        <v>0</v>
+      </c>
+      <c r="R28" s="13">
+        <v>0</v>
+      </c>
+      <c r="S28" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="13">
-        <v>0</v>
-      </c>
-      <c r="R28" s="13">
-        <v>0</v>
-      </c>
-      <c r="S28" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T28" s="6"/>
@@ -30753,31 +30756,31 @@
     </row>
     <row r="29" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="28">
+        <f t="shared" si="7"/>
+        <v>45897</v>
+      </c>
+      <c r="B29" s="13">
+        <v>0</v>
+      </c>
+      <c r="C29" s="13">
+        <v>0</v>
+      </c>
+      <c r="D29" s="13">
         <f t="shared" si="8"/>
-        <v>45897</v>
-      </c>
-      <c r="B29" s="13">
-        <v>0</v>
-      </c>
-      <c r="C29" s="13">
-        <v>0</v>
-      </c>
-      <c r="D29" s="13">
+        <v>0</v>
+      </c>
+      <c r="E29" s="13">
+        <v>0</v>
+      </c>
+      <c r="F29" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E29" s="13">
-        <v>0</v>
-      </c>
-      <c r="F29" s="13">
+      <c r="G29" s="13">
+        <v>0</v>
+      </c>
+      <c r="H29" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="13">
-        <v>0</v>
-      </c>
-      <c r="H29" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I29" s="13">
@@ -30791,31 +30794,31 @@
         <v>0</v>
       </c>
       <c r="L29" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="13">
+        <v>0</v>
+      </c>
+      <c r="N29" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M29" s="13">
-        <v>0</v>
-      </c>
-      <c r="N29" s="13">
+      <c r="O29" s="13">
+        <v>0</v>
+      </c>
+      <c r="P29" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O29" s="13">
-        <v>0</v>
-      </c>
-      <c r="P29" s="13">
+      <c r="Q29" s="13">
+        <v>0</v>
+      </c>
+      <c r="R29" s="13">
+        <v>0</v>
+      </c>
+      <c r="S29" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="13">
-        <v>0</v>
-      </c>
-      <c r="R29" s="13">
-        <v>0</v>
-      </c>
-      <c r="S29" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T29" s="6"/>
@@ -30835,31 +30838,31 @@
     </row>
     <row r="30" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="28">
+        <f t="shared" si="7"/>
+        <v>45898</v>
+      </c>
+      <c r="B30" s="13">
+        <v>0</v>
+      </c>
+      <c r="C30" s="13">
+        <v>0</v>
+      </c>
+      <c r="D30" s="13">
         <f t="shared" si="8"/>
-        <v>45898</v>
-      </c>
-      <c r="B30" s="13">
-        <v>0</v>
-      </c>
-      <c r="C30" s="13">
-        <v>0</v>
-      </c>
-      <c r="D30" s="13">
+        <v>0</v>
+      </c>
+      <c r="E30" s="13">
+        <v>0</v>
+      </c>
+      <c r="F30" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E30" s="13">
-        <v>0</v>
-      </c>
-      <c r="F30" s="13">
+      <c r="G30" s="13">
+        <v>0</v>
+      </c>
+      <c r="H30" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="13">
-        <v>0</v>
-      </c>
-      <c r="H30" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I30" s="13">
@@ -30873,31 +30876,31 @@
         <v>0</v>
       </c>
       <c r="L30" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="13">
+        <v>0</v>
+      </c>
+      <c r="N30" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M30" s="13">
-        <v>0</v>
-      </c>
-      <c r="N30" s="13">
+      <c r="O30" s="13">
+        <v>0</v>
+      </c>
+      <c r="P30" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O30" s="13">
-        <v>0</v>
-      </c>
-      <c r="P30" s="13">
+      <c r="Q30" s="13">
+        <v>0</v>
+      </c>
+      <c r="R30" s="13">
+        <v>0</v>
+      </c>
+      <c r="S30" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="13">
-        <v>0</v>
-      </c>
-      <c r="R30" s="13">
-        <v>0</v>
-      </c>
-      <c r="S30" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T30" s="6"/>
@@ -30917,31 +30920,31 @@
     </row>
     <row r="31" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="28">
+        <f t="shared" si="7"/>
+        <v>45899</v>
+      </c>
+      <c r="B31" s="13">
+        <v>0</v>
+      </c>
+      <c r="C31" s="13">
+        <v>0</v>
+      </c>
+      <c r="D31" s="13">
         <f t="shared" si="8"/>
-        <v>45899</v>
-      </c>
-      <c r="B31" s="13">
-        <v>0</v>
-      </c>
-      <c r="C31" s="13">
-        <v>0</v>
-      </c>
-      <c r="D31" s="13">
+        <v>0</v>
+      </c>
+      <c r="E31" s="13">
+        <v>0</v>
+      </c>
+      <c r="F31" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E31" s="13">
-        <v>0</v>
-      </c>
-      <c r="F31" s="13">
+      <c r="G31" s="13">
+        <v>0</v>
+      </c>
+      <c r="H31" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="13">
-        <v>0</v>
-      </c>
-      <c r="H31" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I31" s="13">
@@ -30955,31 +30958,31 @@
         <v>0</v>
       </c>
       <c r="L31" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="13">
+        <v>0</v>
+      </c>
+      <c r="N31" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M31" s="13">
-        <v>0</v>
-      </c>
-      <c r="N31" s="13">
+      <c r="O31" s="13">
+        <v>0</v>
+      </c>
+      <c r="P31" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O31" s="13">
-        <v>0</v>
-      </c>
-      <c r="P31" s="13">
+      <c r="Q31" s="13">
+        <v>0</v>
+      </c>
+      <c r="R31" s="13">
+        <v>0</v>
+      </c>
+      <c r="S31" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="13">
-        <v>0</v>
-      </c>
-      <c r="R31" s="13">
-        <v>0</v>
-      </c>
-      <c r="S31" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T31" s="6"/>
@@ -30999,31 +31002,31 @@
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="28">
+        <f t="shared" si="7"/>
+        <v>45900</v>
+      </c>
+      <c r="B32" s="13">
+        <v>0</v>
+      </c>
+      <c r="C32" s="13">
+        <v>0</v>
+      </c>
+      <c r="D32" s="13">
         <f t="shared" si="8"/>
-        <v>45900</v>
-      </c>
-      <c r="B32" s="13">
-        <v>0</v>
-      </c>
-      <c r="C32" s="13">
-        <v>0</v>
-      </c>
-      <c r="D32" s="13">
+        <v>0</v>
+      </c>
+      <c r="E32" s="13">
+        <v>0</v>
+      </c>
+      <c r="F32" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E32" s="13">
-        <v>0</v>
-      </c>
-      <c r="F32" s="13">
+      <c r="G32" s="13">
+        <v>0</v>
+      </c>
+      <c r="H32" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="13">
-        <v>0</v>
-      </c>
-      <c r="H32" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I32" s="13">
@@ -31037,31 +31040,31 @@
         <v>0</v>
       </c>
       <c r="L32" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M32" s="13">
+        <v>0</v>
+      </c>
+      <c r="N32" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M32" s="13">
-        <v>0</v>
-      </c>
-      <c r="N32" s="13">
+      <c r="O32" s="13">
+        <v>0</v>
+      </c>
+      <c r="P32" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O32" s="13">
-        <v>0</v>
-      </c>
-      <c r="P32" s="13">
+      <c r="Q32" s="13">
+        <v>0</v>
+      </c>
+      <c r="R32" s="13">
+        <v>0</v>
+      </c>
+      <c r="S32" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="13">
-        <v>0</v>
-      </c>
-      <c r="R32" s="13">
-        <v>0</v>
-      </c>
-      <c r="S32" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T32" s="6"/>
@@ -31092,14 +31095,14 @@
     </row>
     <row r="35" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -31477,15 +31480,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="46"/>
-      <c r="B70" s="46"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46"/>
-      <c r="I70" s="46"/>
+      <c r="A70" s="47"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -31510,15 +31513,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="47"/>
-      <c r="B75" s="47"/>
-      <c r="C75" s="47"/>
-      <c r="D75" s="47"/>
-      <c r="E75" s="47"/>
-      <c r="F75" s="47"/>
-      <c r="G75" s="47"/>
-      <c r="H75" s="47"/>
-      <c r="I75" s="47"/>
+      <c r="A75" s="48"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -31554,15 +31557,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="48"/>
-      <c r="B79" s="48"/>
-      <c r="C79" s="48"/>
-      <c r="D79" s="48"/>
-      <c r="E79" s="48"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="48"/>
-      <c r="H79" s="48"/>
-      <c r="I79" s="48"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -31598,15 +31601,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="47"/>
-      <c r="B87" s="47"/>
-      <c r="C87" s="47"/>
-      <c r="D87" s="47"/>
-      <c r="E87" s="47"/>
-      <c r="F87" s="47"/>
-      <c r="G87" s="47"/>
-      <c r="H87" s="47"/>
-      <c r="I87" s="47"/>
+      <c r="A87" s="48"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -31709,15 +31712,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="46"/>
-      <c r="B100" s="46"/>
-      <c r="C100" s="46"/>
-      <c r="D100" s="46"/>
-      <c r="E100" s="46"/>
-      <c r="F100" s="46"/>
-      <c r="G100" s="46"/>
-      <c r="H100" s="46"/>
-      <c r="I100" s="46"/>
+      <c r="A100" s="47"/>
+      <c r="B100" s="47"/>
+      <c r="C100" s="47"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="47"/>
+      <c r="I100" s="47"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -35028,14 +35031,14 @@
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -35413,15 +35416,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="46"/>
-      <c r="B71" s="46"/>
-      <c r="C71" s="46"/>
-      <c r="D71" s="46"/>
-      <c r="E71" s="46"/>
-      <c r="F71" s="46"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="46"/>
-      <c r="I71" s="46"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -35446,15 +35449,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="47"/>
-      <c r="B76" s="47"/>
-      <c r="C76" s="47"/>
-      <c r="D76" s="47"/>
-      <c r="E76" s="47"/>
-      <c r="F76" s="47"/>
-      <c r="G76" s="47"/>
-      <c r="H76" s="47"/>
-      <c r="I76" s="47"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -35490,15 +35493,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="48"/>
-      <c r="B80" s="48"/>
-      <c r="C80" s="48"/>
-      <c r="D80" s="48"/>
-      <c r="E80" s="48"/>
-      <c r="F80" s="48"/>
-      <c r="G80" s="48"/>
-      <c r="H80" s="48"/>
-      <c r="I80" s="48"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -35534,15 +35537,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="47"/>
-      <c r="B88" s="47"/>
-      <c r="C88" s="47"/>
-      <c r="D88" s="47"/>
-      <c r="E88" s="47"/>
-      <c r="F88" s="47"/>
-      <c r="G88" s="47"/>
-      <c r="H88" s="47"/>
-      <c r="I88" s="47"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -35645,15 +35648,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="46"/>
-      <c r="B101" s="46"/>
-      <c r="C101" s="46"/>
-      <c r="D101" s="46"/>
-      <c r="E101" s="46"/>
-      <c r="F101" s="46"/>
-      <c r="G101" s="46"/>
-      <c r="H101" s="46"/>
-      <c r="I101" s="46"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -38705,22 +38708,22 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="46"/>
-      <c r="N35" s="46"/>
-      <c r="O35" s="46"/>
-      <c r="P35" s="46"/>
-      <c r="Q35" s="46"/>
-      <c r="R35" s="46"/>
-      <c r="S35" s="46"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="47"/>
+      <c r="K35" s="47"/>
+      <c r="L35" s="47"/>
+      <c r="M35" s="47"/>
+      <c r="N35" s="47"/>
+      <c r="O35" s="47"/>
+      <c r="P35" s="47"/>
+      <c r="Q35" s="47"/>
+      <c r="R35" s="47"/>
+      <c r="S35" s="47"/>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -39438,25 +39441,25 @@
       <c r="S69" s="1"/>
     </row>
     <row r="70" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="46"/>
-      <c r="B70" s="46"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="46"/>
-      <c r="I70" s="46"/>
-      <c r="J70" s="46"/>
-      <c r="K70" s="46"/>
-      <c r="L70" s="46"/>
-      <c r="M70" s="46"/>
-      <c r="N70" s="46"/>
-      <c r="O70" s="46"/>
-      <c r="P70" s="46"/>
-      <c r="Q70" s="46"/>
-      <c r="R70" s="46"/>
-      <c r="S70" s="46"/>
+      <c r="A70" s="47"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
+      <c r="J70" s="47"/>
+      <c r="K70" s="47"/>
+      <c r="L70" s="47"/>
+      <c r="M70" s="47"/>
+      <c r="N70" s="47"/>
+      <c r="O70" s="47"/>
+      <c r="P70" s="47"/>
+      <c r="Q70" s="47"/>
+      <c r="R70" s="47"/>
+      <c r="S70" s="47"/>
     </row>
     <row r="71" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -39501,25 +39504,25 @@
       <c r="S72" s="23"/>
     </row>
     <row r="75" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="47"/>
-      <c r="B75" s="47"/>
-      <c r="C75" s="47"/>
-      <c r="D75" s="47"/>
-      <c r="E75" s="47"/>
-      <c r="F75" s="47"/>
-      <c r="G75" s="47"/>
-      <c r="H75" s="47"/>
-      <c r="I75" s="47"/>
-      <c r="J75" s="47"/>
-      <c r="K75" s="47"/>
-      <c r="L75" s="47"/>
-      <c r="M75" s="47"/>
-      <c r="N75" s="47"/>
-      <c r="O75" s="47"/>
-      <c r="P75" s="47"/>
-      <c r="Q75" s="47"/>
-      <c r="R75" s="47"/>
-      <c r="S75" s="47"/>
+      <c r="A75" s="48"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
+      <c r="J75" s="48"/>
+      <c r="K75" s="48"/>
+      <c r="L75" s="48"/>
+      <c r="M75" s="48"/>
+      <c r="N75" s="48"/>
+      <c r="O75" s="48"/>
+      <c r="P75" s="48"/>
+      <c r="Q75" s="48"/>
+      <c r="R75" s="48"/>
+      <c r="S75" s="48"/>
     </row>
     <row r="76" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -39585,25 +39588,25 @@
       <c r="S78" s="25"/>
     </row>
     <row r="79" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="48"/>
-      <c r="B79" s="48"/>
-      <c r="C79" s="48"/>
-      <c r="D79" s="48"/>
-      <c r="E79" s="48"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="48"/>
-      <c r="H79" s="48"/>
-      <c r="I79" s="48"/>
-      <c r="J79" s="48"/>
-      <c r="K79" s="48"/>
-      <c r="L79" s="48"/>
-      <c r="M79" s="48"/>
-      <c r="N79" s="48"/>
-      <c r="O79" s="48"/>
-      <c r="P79" s="48"/>
-      <c r="Q79" s="48"/>
-      <c r="R79" s="48"/>
-      <c r="S79" s="48"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49"/>
+      <c r="J79" s="49"/>
+      <c r="K79" s="49"/>
+      <c r="L79" s="49"/>
+      <c r="M79" s="49"/>
+      <c r="N79" s="49"/>
+      <c r="O79" s="49"/>
+      <c r="P79" s="49"/>
+      <c r="Q79" s="49"/>
+      <c r="R79" s="49"/>
+      <c r="S79" s="49"/>
     </row>
     <row r="80" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -39667,25 +39670,25 @@
       <c r="E85" s="23"/>
     </row>
     <row r="87" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="47"/>
-      <c r="B87" s="47"/>
-      <c r="C87" s="47"/>
-      <c r="D87" s="47"/>
-      <c r="E87" s="47"/>
-      <c r="F87" s="47"/>
-      <c r="G87" s="47"/>
-      <c r="H87" s="47"/>
-      <c r="I87" s="47"/>
-      <c r="J87" s="47"/>
-      <c r="K87" s="47"/>
-      <c r="L87" s="47"/>
-      <c r="M87" s="47"/>
-      <c r="N87" s="47"/>
-      <c r="O87" s="47"/>
-      <c r="P87" s="47"/>
-      <c r="Q87" s="47"/>
-      <c r="R87" s="47"/>
-      <c r="S87" s="47"/>
+      <c r="A87" s="48"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
+      <c r="J87" s="48"/>
+      <c r="K87" s="48"/>
+      <c r="L87" s="48"/>
+      <c r="M87" s="48"/>
+      <c r="N87" s="48"/>
+      <c r="O87" s="48"/>
+      <c r="P87" s="48"/>
+      <c r="Q87" s="48"/>
+      <c r="R87" s="48"/>
+      <c r="S87" s="48"/>
     </row>
     <row r="88" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -39877,25 +39880,25 @@
       <c r="E98" s="26"/>
     </row>
     <row r="100" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="46"/>
-      <c r="B100" s="46"/>
-      <c r="C100" s="46"/>
-      <c r="D100" s="46"/>
-      <c r="E100" s="46"/>
-      <c r="F100" s="46"/>
-      <c r="G100" s="46"/>
-      <c r="H100" s="46"/>
-      <c r="I100" s="46"/>
-      <c r="J100" s="46"/>
-      <c r="K100" s="46"/>
-      <c r="L100" s="46"/>
-      <c r="M100" s="46"/>
-      <c r="N100" s="46"/>
-      <c r="O100" s="46"/>
-      <c r="P100" s="46"/>
-      <c r="Q100" s="46"/>
-      <c r="R100" s="46"/>
-      <c r="S100" s="46"/>
+      <c r="A100" s="47"/>
+      <c r="B100" s="47"/>
+      <c r="C100" s="47"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="47"/>
+      <c r="I100" s="47"/>
+      <c r="J100" s="47"/>
+      <c r="K100" s="47"/>
+      <c r="L100" s="47"/>
+      <c r="M100" s="47"/>
+      <c r="N100" s="47"/>
+      <c r="O100" s="47"/>
+      <c r="P100" s="47"/>
+      <c r="Q100" s="47"/>
+      <c r="R100" s="47"/>
+      <c r="S100" s="47"/>
     </row>
     <row r="101" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -43138,14 +43141,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="46"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -43523,15 +43526,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="46"/>
-      <c r="B71" s="46"/>
-      <c r="C71" s="46"/>
-      <c r="D71" s="46"/>
-      <c r="E71" s="46"/>
-      <c r="F71" s="46"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="46"/>
-      <c r="I71" s="46"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -43556,15 +43559,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="47"/>
-      <c r="B76" s="47"/>
-      <c r="C76" s="47"/>
-      <c r="D76" s="47"/>
-      <c r="E76" s="47"/>
-      <c r="F76" s="47"/>
-      <c r="G76" s="47"/>
-      <c r="H76" s="47"/>
-      <c r="I76" s="47"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -43600,15 +43603,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="48"/>
-      <c r="B80" s="48"/>
-      <c r="C80" s="48"/>
-      <c r="D80" s="48"/>
-      <c r="E80" s="48"/>
-      <c r="F80" s="48"/>
-      <c r="G80" s="48"/>
-      <c r="H80" s="48"/>
-      <c r="I80" s="48"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -43644,15 +43647,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="47"/>
-      <c r="B88" s="47"/>
-      <c r="C88" s="47"/>
-      <c r="D88" s="47"/>
-      <c r="E88" s="47"/>
-      <c r="F88" s="47"/>
-      <c r="G88" s="47"/>
-      <c r="H88" s="47"/>
-      <c r="I88" s="47"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -43755,15 +43758,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="46"/>
-      <c r="B101" s="46"/>
-      <c r="C101" s="46"/>
-      <c r="D101" s="46"/>
-      <c r="E101" s="46"/>
-      <c r="F101" s="46"/>
-      <c r="G101" s="46"/>
-      <c r="H101" s="46"/>
-      <c r="I101" s="46"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A482AD9-890A-4B79-BF37-16F29A6CDAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23170D55-AB78-45B2-A656-14E99083120E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -604,6 +604,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -611,9 +614,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -4829,15 +4829,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="47"/>
-      <c r="B69" s="47"/>
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="47"/>
-      <c r="G69" s="47"/>
-      <c r="H69" s="47"/>
-      <c r="I69" s="47"/>
+      <c r="A69" s="48"/>
+      <c r="B69" s="48"/>
+      <c r="C69" s="48"/>
+      <c r="D69" s="48"/>
+      <c r="E69" s="48"/>
+      <c r="F69" s="48"/>
+      <c r="G69" s="48"/>
+      <c r="H69" s="48"/>
+      <c r="I69" s="48"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -4862,15 +4862,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="48"/>
-      <c r="B74" s="48"/>
-      <c r="C74" s="48"/>
-      <c r="D74" s="48"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="48"/>
-      <c r="G74" s="48"/>
-      <c r="H74" s="48"/>
-      <c r="I74" s="48"/>
+      <c r="A74" s="49"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="49"/>
+      <c r="D74" s="49"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="49"/>
+      <c r="G74" s="49"/>
+      <c r="H74" s="49"/>
+      <c r="I74" s="49"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -4906,15 +4906,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="49"/>
-      <c r="B78" s="49"/>
-      <c r="C78" s="49"/>
-      <c r="D78" s="49"/>
-      <c r="E78" s="49"/>
-      <c r="F78" s="49"/>
-      <c r="G78" s="49"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="49"/>
+      <c r="A78" s="50"/>
+      <c r="B78" s="50"/>
+      <c r="C78" s="50"/>
+      <c r="D78" s="50"/>
+      <c r="E78" s="50"/>
+      <c r="F78" s="50"/>
+      <c r="G78" s="50"/>
+      <c r="H78" s="50"/>
+      <c r="I78" s="50"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -4950,15 +4950,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="48"/>
-      <c r="B86" s="48"/>
-      <c r="C86" s="48"/>
-      <c r="D86" s="48"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="48"/>
-      <c r="G86" s="48"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="48"/>
+      <c r="A86" s="49"/>
+      <c r="B86" s="49"/>
+      <c r="C86" s="49"/>
+      <c r="D86" s="49"/>
+      <c r="E86" s="49"/>
+      <c r="F86" s="49"/>
+      <c r="G86" s="49"/>
+      <c r="H86" s="49"/>
+      <c r="I86" s="49"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -5061,15 +5061,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="47"/>
-      <c r="B99" s="47"/>
-      <c r="C99" s="47"/>
-      <c r="D99" s="47"/>
-      <c r="E99" s="47"/>
-      <c r="F99" s="47"/>
-      <c r="G99" s="47"/>
-      <c r="H99" s="47"/>
-      <c r="I99" s="47"/>
+      <c r="A99" s="48"/>
+      <c r="B99" s="48"/>
+      <c r="C99" s="48"/>
+      <c r="D99" s="48"/>
+      <c r="E99" s="48"/>
+      <c r="F99" s="48"/>
+      <c r="G99" s="48"/>
+      <c r="H99" s="48"/>
+      <c r="I99" s="48"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -8269,14 +8269,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -8653,15 +8653,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="47"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="47"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="47"/>
-      <c r="I71" s="47"/>
+      <c r="A71" s="48"/>
+      <c r="B71" s="48"/>
+      <c r="C71" s="48"/>
+      <c r="D71" s="48"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -8686,15 +8686,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="48"/>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
+      <c r="A76" s="49"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="49"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -8730,15 +8730,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="49"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49"/>
+      <c r="A80" s="50"/>
+      <c r="B80" s="50"/>
+      <c r="C80" s="50"/>
+      <c r="D80" s="50"/>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50"/>
+      <c r="H80" s="50"/>
+      <c r="I80" s="50"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -8774,15 +8774,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="48"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
+      <c r="A88" s="49"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="49"/>
+      <c r="D88" s="49"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
+      <c r="H88" s="49"/>
+      <c r="I88" s="49"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -8885,15 +8885,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="47"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="47"/>
-      <c r="D101" s="47"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="47"/>
-      <c r="G101" s="47"/>
-      <c r="H101" s="47"/>
-      <c r="I101" s="47"/>
+      <c r="A101" s="48"/>
+      <c r="B101" s="48"/>
+      <c r="C101" s="48"/>
+      <c r="D101" s="48"/>
+      <c r="E101" s="48"/>
+      <c r="F101" s="48"/>
+      <c r="G101" s="48"/>
+      <c r="H101" s="48"/>
+      <c r="I101" s="48"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -11267,14 +11267,14 @@
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="47"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="48"/>
       <c r="T32" s="27"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
@@ -11652,15 +11652,15 @@
       <c r="I66" s="1"/>
     </row>
     <row r="67" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="47"/>
-      <c r="B67" s="47"/>
-      <c r="C67" s="47"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="47"/>
-      <c r="G67" s="47"/>
-      <c r="H67" s="47"/>
-      <c r="I67" s="47"/>
+      <c r="A67" s="48"/>
+      <c r="B67" s="48"/>
+      <c r="C67" s="48"/>
+      <c r="D67" s="48"/>
+      <c r="E67" s="48"/>
+      <c r="F67" s="48"/>
+      <c r="G67" s="48"/>
+      <c r="H67" s="48"/>
+      <c r="I67" s="48"/>
     </row>
     <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
@@ -11685,15 +11685,15 @@
       <c r="I69" s="23"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="48"/>
-      <c r="B72" s="48"/>
-      <c r="C72" s="48"/>
-      <c r="D72" s="48"/>
-      <c r="E72" s="48"/>
-      <c r="F72" s="48"/>
-      <c r="G72" s="48"/>
-      <c r="H72" s="48"/>
-      <c r="I72" s="48"/>
+      <c r="A72" s="49"/>
+      <c r="B72" s="49"/>
+      <c r="C72" s="49"/>
+      <c r="D72" s="49"/>
+      <c r="E72" s="49"/>
+      <c r="F72" s="49"/>
+      <c r="G72" s="49"/>
+      <c r="H72" s="49"/>
+      <c r="I72" s="49"/>
     </row>
     <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
@@ -11729,15 +11729,15 @@
       <c r="I75" s="25"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="49"/>
-      <c r="B76" s="49"/>
-      <c r="C76" s="49"/>
-      <c r="D76" s="49"/>
-      <c r="E76" s="49"/>
-      <c r="F76" s="49"/>
-      <c r="G76" s="49"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="49"/>
+      <c r="A76" s="50"/>
+      <c r="B76" s="50"/>
+      <c r="C76" s="50"/>
+      <c r="D76" s="50"/>
+      <c r="E76" s="50"/>
+      <c r="F76" s="50"/>
+      <c r="G76" s="50"/>
+      <c r="H76" s="50"/>
+      <c r="I76" s="50"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -11773,15 +11773,15 @@
       <c r="B82" s="23"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="48"/>
-      <c r="B84" s="48"/>
-      <c r="C84" s="48"/>
-      <c r="D84" s="48"/>
-      <c r="E84" s="48"/>
-      <c r="F84" s="48"/>
-      <c r="G84" s="48"/>
-      <c r="H84" s="48"/>
-      <c r="I84" s="48"/>
+      <c r="A84" s="49"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="49"/>
+      <c r="D84" s="49"/>
+      <c r="E84" s="49"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="49"/>
+      <c r="H84" s="49"/>
+      <c r="I84" s="49"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
@@ -11884,15 +11884,15 @@
       <c r="B95" s="26"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="47"/>
-      <c r="B97" s="47"/>
-      <c r="C97" s="47"/>
-      <c r="D97" s="47"/>
-      <c r="E97" s="47"/>
-      <c r="F97" s="47"/>
-      <c r="G97" s="47"/>
-      <c r="H97" s="47"/>
-      <c r="I97" s="47"/>
+      <c r="A97" s="48"/>
+      <c r="B97" s="48"/>
+      <c r="C97" s="48"/>
+      <c r="D97" s="48"/>
+      <c r="E97" s="48"/>
+      <c r="F97" s="48"/>
+      <c r="G97" s="48"/>
+      <c r="H97" s="48"/>
+      <c r="I97" s="48"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
@@ -14442,14 +14442,14 @@
     <row r="34" spans="1:21" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
     </row>
     <row r="37" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -14826,15 +14826,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="47"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="47"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="47"/>
-      <c r="I71" s="47"/>
+      <c r="A71" s="48"/>
+      <c r="B71" s="48"/>
+      <c r="C71" s="48"/>
+      <c r="D71" s="48"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -14859,15 +14859,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="48"/>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
+      <c r="A76" s="49"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="49"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -14903,15 +14903,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="49"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49"/>
+      <c r="A80" s="50"/>
+      <c r="B80" s="50"/>
+      <c r="C80" s="50"/>
+      <c r="D80" s="50"/>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50"/>
+      <c r="H80" s="50"/>
+      <c r="I80" s="50"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -14947,15 +14947,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="48"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
+      <c r="A88" s="49"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="49"/>
+      <c r="D88" s="49"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
+      <c r="H88" s="49"/>
+      <c r="I88" s="49"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -15058,15 +15058,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="47"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="47"/>
-      <c r="D101" s="47"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="47"/>
-      <c r="G101" s="47"/>
-      <c r="H101" s="47"/>
-      <c r="I101" s="47"/>
+      <c r="A101" s="48"/>
+      <c r="B101" s="48"/>
+      <c r="C101" s="48"/>
+      <c r="D101" s="48"/>
+      <c r="E101" s="48"/>
+      <c r="F101" s="48"/>
+      <c r="G101" s="48"/>
+      <c r="H101" s="48"/>
+      <c r="I101" s="48"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -17801,14 +17801,14 @@
     </row>
     <row r="35" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48"/>
     </row>
     <row r="36" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -18186,15 +18186,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="47"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="47"/>
-      <c r="F70" s="47"/>
-      <c r="G70" s="47"/>
-      <c r="H70" s="47"/>
-      <c r="I70" s="47"/>
+      <c r="A70" s="48"/>
+      <c r="B70" s="48"/>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -18219,15 +18219,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="48"/>
-      <c r="B75" s="48"/>
-      <c r="C75" s="48"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
+      <c r="A75" s="49"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="49"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="49"/>
+      <c r="H75" s="49"/>
+      <c r="I75" s="49"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -18263,15 +18263,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="49"/>
-      <c r="B79" s="49"/>
-      <c r="C79" s="49"/>
-      <c r="D79" s="49"/>
-      <c r="E79" s="49"/>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49"/>
+      <c r="A79" s="50"/>
+      <c r="B79" s="50"/>
+      <c r="C79" s="50"/>
+      <c r="D79" s="50"/>
+      <c r="E79" s="50"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50"/>
+      <c r="H79" s="50"/>
+      <c r="I79" s="50"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -18307,15 +18307,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="48"/>
-      <c r="B87" s="48"/>
-      <c r="C87" s="48"/>
-      <c r="D87" s="48"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48"/>
+      <c r="A87" s="49"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="49"/>
+      <c r="D87" s="49"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="49"/>
+      <c r="H87" s="49"/>
+      <c r="I87" s="49"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -18418,15 +18418,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="47"/>
-      <c r="B100" s="47"/>
-      <c r="C100" s="47"/>
-      <c r="D100" s="47"/>
-      <c r="E100" s="47"/>
-      <c r="F100" s="47"/>
-      <c r="G100" s="47"/>
-      <c r="H100" s="47"/>
-      <c r="I100" s="47"/>
+      <c r="A100" s="48"/>
+      <c r="B100" s="48"/>
+      <c r="C100" s="48"/>
+      <c r="D100" s="48"/>
+      <c r="E100" s="48"/>
+      <c r="F100" s="48"/>
+      <c r="G100" s="48"/>
+      <c r="H100" s="48"/>
+      <c r="I100" s="48"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -21053,14 +21053,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -21438,15 +21438,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="47"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="47"/>
-      <c r="F70" s="47"/>
-      <c r="G70" s="47"/>
-      <c r="H70" s="47"/>
-      <c r="I70" s="47"/>
+      <c r="A70" s="48"/>
+      <c r="B70" s="48"/>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -21471,15 +21471,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="48"/>
-      <c r="B75" s="48"/>
-      <c r="C75" s="48"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
+      <c r="A75" s="49"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="49"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="49"/>
+      <c r="H75" s="49"/>
+      <c r="I75" s="49"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -21515,15 +21515,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="49"/>
-      <c r="B79" s="49"/>
-      <c r="C79" s="49"/>
-      <c r="D79" s="49"/>
-      <c r="E79" s="49"/>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49"/>
+      <c r="A79" s="50"/>
+      <c r="B79" s="50"/>
+      <c r="C79" s="50"/>
+      <c r="D79" s="50"/>
+      <c r="E79" s="50"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50"/>
+      <c r="H79" s="50"/>
+      <c r="I79" s="50"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -21559,15 +21559,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="48"/>
-      <c r="B87" s="48"/>
-      <c r="C87" s="48"/>
-      <c r="D87" s="48"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48"/>
+      <c r="A87" s="49"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="49"/>
+      <c r="D87" s="49"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="49"/>
+      <c r="H87" s="49"/>
+      <c r="I87" s="49"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -21670,15 +21670,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="47"/>
-      <c r="B100" s="47"/>
-      <c r="C100" s="47"/>
-      <c r="D100" s="47"/>
-      <c r="E100" s="47"/>
-      <c r="F100" s="47"/>
-      <c r="G100" s="47"/>
-      <c r="H100" s="47"/>
-      <c r="I100" s="47"/>
+      <c r="A100" s="48"/>
+      <c r="B100" s="48"/>
+      <c r="C100" s="48"/>
+      <c r="D100" s="48"/>
+      <c r="E100" s="48"/>
+      <c r="F100" s="48"/>
+      <c r="G100" s="48"/>
+      <c r="H100" s="48"/>
+      <c r="I100" s="48"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -24381,14 +24381,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -24766,15 +24766,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="47"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="47"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="47"/>
-      <c r="I71" s="47"/>
+      <c r="A71" s="48"/>
+      <c r="B71" s="48"/>
+      <c r="C71" s="48"/>
+      <c r="D71" s="48"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -24799,15 +24799,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="48"/>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
+      <c r="A76" s="49"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="49"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -24843,15 +24843,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="49"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49"/>
+      <c r="A80" s="50"/>
+      <c r="B80" s="50"/>
+      <c r="C80" s="50"/>
+      <c r="D80" s="50"/>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50"/>
+      <c r="H80" s="50"/>
+      <c r="I80" s="50"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -24887,15 +24887,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="48"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
+      <c r="A88" s="49"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="49"/>
+      <c r="D88" s="49"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
+      <c r="H88" s="49"/>
+      <c r="I88" s="49"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -24998,15 +24998,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="47"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="47"/>
-      <c r="D101" s="47"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="47"/>
-      <c r="G101" s="47"/>
-      <c r="H101" s="47"/>
-      <c r="I101" s="47"/>
+      <c r="A101" s="48"/>
+      <c r="B101" s="48"/>
+      <c r="C101" s="48"/>
+      <c r="D101" s="48"/>
+      <c r="E101" s="48"/>
+      <c r="F101" s="48"/>
+      <c r="G101" s="48"/>
+      <c r="H101" s="48"/>
+      <c r="I101" s="48"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -27642,14 +27642,14 @@
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="47"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="48"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
@@ -28027,15 +28027,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="47"/>
-      <c r="B69" s="47"/>
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="47"/>
-      <c r="G69" s="47"/>
-      <c r="H69" s="47"/>
-      <c r="I69" s="47"/>
+      <c r="A69" s="48"/>
+      <c r="B69" s="48"/>
+      <c r="C69" s="48"/>
+      <c r="D69" s="48"/>
+      <c r="E69" s="48"/>
+      <c r="F69" s="48"/>
+      <c r="G69" s="48"/>
+      <c r="H69" s="48"/>
+      <c r="I69" s="48"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -28060,15 +28060,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="48"/>
-      <c r="B74" s="48"/>
-      <c r="C74" s="48"/>
-      <c r="D74" s="48"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="48"/>
-      <c r="G74" s="48"/>
-      <c r="H74" s="48"/>
-      <c r="I74" s="48"/>
+      <c r="A74" s="49"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="49"/>
+      <c r="D74" s="49"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="49"/>
+      <c r="G74" s="49"/>
+      <c r="H74" s="49"/>
+      <c r="I74" s="49"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -28104,15 +28104,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="49"/>
-      <c r="B78" s="49"/>
-      <c r="C78" s="49"/>
-      <c r="D78" s="49"/>
-      <c r="E78" s="49"/>
-      <c r="F78" s="49"/>
-      <c r="G78" s="49"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="49"/>
+      <c r="A78" s="50"/>
+      <c r="B78" s="50"/>
+      <c r="C78" s="50"/>
+      <c r="D78" s="50"/>
+      <c r="E78" s="50"/>
+      <c r="F78" s="50"/>
+      <c r="G78" s="50"/>
+      <c r="H78" s="50"/>
+      <c r="I78" s="50"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -28148,15 +28148,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="48"/>
-      <c r="B86" s="48"/>
-      <c r="C86" s="48"/>
-      <c r="D86" s="48"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="48"/>
-      <c r="G86" s="48"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="48"/>
+      <c r="A86" s="49"/>
+      <c r="B86" s="49"/>
+      <c r="C86" s="49"/>
+      <c r="D86" s="49"/>
+      <c r="E86" s="49"/>
+      <c r="F86" s="49"/>
+      <c r="G86" s="49"/>
+      <c r="H86" s="49"/>
+      <c r="I86" s="49"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -28259,15 +28259,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="47"/>
-      <c r="B99" s="47"/>
-      <c r="C99" s="47"/>
-      <c r="D99" s="47"/>
-      <c r="E99" s="47"/>
-      <c r="F99" s="47"/>
-      <c r="G99" s="47"/>
-      <c r="H99" s="47"/>
-      <c r="I99" s="47"/>
+      <c r="A99" s="48"/>
+      <c r="B99" s="48"/>
+      <c r="C99" s="48"/>
+      <c r="D99" s="48"/>
+      <c r="E99" s="48"/>
+      <c r="F99" s="48"/>
+      <c r="G99" s="48"/>
+      <c r="H99" s="48"/>
+      <c r="I99" s="48"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -28556,7 +28556,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="13">
-        <f t="shared" ref="D2:D32" si="8">W4-W3</f>
+        <f t="shared" ref="D3:D32" si="8">W4-W3</f>
         <v>0</v>
       </c>
       <c r="E3" s="13">
@@ -28569,7 +28569,7 @@
       <c r="G3" s="13">
         <v>0</v>
       </c>
-      <c r="H3" s="50">
+      <c r="H3" s="47">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -31095,14 +31095,14 @@
     </row>
     <row r="35" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48"/>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -31480,15 +31480,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="47"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="47"/>
-      <c r="F70" s="47"/>
-      <c r="G70" s="47"/>
-      <c r="H70" s="47"/>
-      <c r="I70" s="47"/>
+      <c r="A70" s="48"/>
+      <c r="B70" s="48"/>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -31513,15 +31513,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="48"/>
-      <c r="B75" s="48"/>
-      <c r="C75" s="48"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
+      <c r="A75" s="49"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="49"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="49"/>
+      <c r="H75" s="49"/>
+      <c r="I75" s="49"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -31557,15 +31557,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="49"/>
-      <c r="B79" s="49"/>
-      <c r="C79" s="49"/>
-      <c r="D79" s="49"/>
-      <c r="E79" s="49"/>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49"/>
+      <c r="A79" s="50"/>
+      <c r="B79" s="50"/>
+      <c r="C79" s="50"/>
+      <c r="D79" s="50"/>
+      <c r="E79" s="50"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50"/>
+      <c r="H79" s="50"/>
+      <c r="I79" s="50"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -31601,15 +31601,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="48"/>
-      <c r="B87" s="48"/>
-      <c r="C87" s="48"/>
-      <c r="D87" s="48"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48"/>
+      <c r="A87" s="49"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="49"/>
+      <c r="D87" s="49"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="49"/>
+      <c r="H87" s="49"/>
+      <c r="I87" s="49"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -31712,15 +31712,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="47"/>
-      <c r="B100" s="47"/>
-      <c r="C100" s="47"/>
-      <c r="D100" s="47"/>
-      <c r="E100" s="47"/>
-      <c r="F100" s="47"/>
-      <c r="G100" s="47"/>
-      <c r="H100" s="47"/>
-      <c r="I100" s="47"/>
+      <c r="A100" s="48"/>
+      <c r="B100" s="48"/>
+      <c r="C100" s="48"/>
+      <c r="D100" s="48"/>
+      <c r="E100" s="48"/>
+      <c r="F100" s="48"/>
+      <c r="G100" s="48"/>
+      <c r="H100" s="48"/>
+      <c r="I100" s="48"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -31900,10 +31900,10 @@
         <v>45839</v>
       </c>
       <c r="B2" s="29">
-        <v>0</v>
+        <v>1265.1659994699999</v>
       </c>
       <c r="C2" s="29">
-        <v>0</v>
+        <v>182.48999995999995</v>
       </c>
       <c r="D2" s="13">
         <f>W3-W2</f>
@@ -31940,15 +31940,14 @@
       <c r="M2" s="13">
         <v>0</v>
       </c>
-      <c r="N2" s="13">
-        <f t="shared" ref="N2:N32" si="4">AB3-AB2</f>
-        <v>0</v>
-      </c>
-      <c r="O2" s="13">
-        <v>0</v>
+      <c r="N2" s="29">
+        <v>273.19199933999994</v>
+      </c>
+      <c r="O2" s="29">
+        <v>58.631999890000003</v>
       </c>
       <c r="P2" s="13">
-        <f t="shared" ref="P2:P32" si="5">AC3-AC2</f>
+        <f t="shared" ref="P2:P32" si="4">AC3-AC2</f>
         <v>0</v>
       </c>
       <c r="Q2" s="13">
@@ -31958,7 +31957,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="13">
-        <f t="shared" ref="S2:S32" si="6">AD3-AD2</f>
+        <f t="shared" ref="S2:S32" si="5">AD3-AD2</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -32002,17 +32001,17 @@
     </row>
     <row r="3" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="28">
-        <f t="shared" ref="A3:A32" si="7">A2+1</f>
+        <f t="shared" ref="A3:A32" si="6">A2+1</f>
         <v>45840</v>
       </c>
       <c r="B3" s="29">
-        <v>0</v>
+        <v>1292.8019995300003</v>
       </c>
       <c r="C3" s="29">
-        <v>0</v>
+        <v>194.16599989000002</v>
       </c>
       <c r="D3" s="13">
-        <f t="shared" ref="D3:D32" si="8">W4-W3</f>
+        <f t="shared" ref="D3:D32" si="7">W4-W3</f>
         <v>126</v>
       </c>
       <c r="E3" s="13">
@@ -32046,25 +32045,24 @@
       <c r="M3" s="13">
         <v>0</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="29">
+        <v>244.2479993499999</v>
+      </c>
+      <c r="O3" s="29">
+        <v>53.351999930000005</v>
+      </c>
+      <c r="P3" s="13">
         <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="O3" s="13">
-        <v>0</v>
-      </c>
-      <c r="P3" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="13">
+        <v>0</v>
+      </c>
+      <c r="R3" s="13">
+        <v>0</v>
+      </c>
+      <c r="S3" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q3" s="13">
-        <v>0</v>
-      </c>
-      <c r="R3" s="13">
-        <v>0</v>
-      </c>
-      <c r="S3" s="13">
-        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -32101,17 +32099,17 @@
     </row>
     <row r="4" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A4" s="28">
+        <f t="shared" si="6"/>
+        <v>45841</v>
+      </c>
+      <c r="B4" s="29">
+        <v>1286.6699994699998</v>
+      </c>
+      <c r="C4" s="29">
+        <v>188.95799991000001</v>
+      </c>
+      <c r="D4" s="13">
         <f t="shared" si="7"/>
-        <v>45841</v>
-      </c>
-      <c r="B4" s="29">
-        <v>0</v>
-      </c>
-      <c r="C4" s="29">
-        <v>0</v>
-      </c>
-      <c r="D4" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E4" s="13">
@@ -32145,25 +32143,24 @@
       <c r="M4" s="13">
         <v>0</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="29">
+        <v>238.70399939999993</v>
+      </c>
+      <c r="O4" s="29">
+        <v>47.591999919999992</v>
+      </c>
+      <c r="P4" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O4" s="13">
-        <v>0</v>
-      </c>
-      <c r="P4" s="13">
+      <c r="Q4" s="13">
+        <v>0</v>
+      </c>
+      <c r="R4" s="13">
+        <v>0</v>
+      </c>
+      <c r="S4" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>0</v>
-      </c>
-      <c r="R4" s="13">
-        <v>0</v>
-      </c>
-      <c r="S4" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -32171,7 +32168,7 @@
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="14">
-        <f t="shared" ref="V4:V33" si="9">V3+1</f>
+        <f t="shared" ref="V4:V33" si="8">V3+1</f>
         <v>2</v>
       </c>
       <c r="W4" s="6">
@@ -32201,17 +32198,17 @@
     </row>
     <row r="5" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="28">
+        <f t="shared" si="6"/>
+        <v>45842</v>
+      </c>
+      <c r="B5" s="29">
+        <v>1114.3019995800003</v>
+      </c>
+      <c r="C5" s="29">
+        <v>146.36999994000001</v>
+      </c>
+      <c r="D5" s="13">
         <f t="shared" si="7"/>
-        <v>45842</v>
-      </c>
-      <c r="B5" s="29">
-        <v>0</v>
-      </c>
-      <c r="C5" s="29">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13">
-        <f t="shared" si="8"/>
         <v>132</v>
       </c>
       <c r="E5" s="13">
@@ -32245,25 +32242,24 @@
       <c r="M5" s="13">
         <v>0</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="29">
+        <v>261.69599937999982</v>
+      </c>
+      <c r="O5" s="29">
+        <v>46.919999890000007</v>
+      </c>
+      <c r="P5" s="13">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="O5" s="13">
-        <v>0</v>
-      </c>
-      <c r="P5" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>0</v>
+      </c>
+      <c r="R5" s="13">
+        <v>0</v>
+      </c>
+      <c r="S5" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>0</v>
-      </c>
-      <c r="R5" s="13">
-        <v>0</v>
-      </c>
-      <c r="S5" s="13">
-        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -32271,7 +32267,7 @@
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="W5" s="6">
@@ -32301,17 +32297,17 @@
     </row>
     <row r="6" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="28">
+        <f t="shared" si="6"/>
+        <v>45843</v>
+      </c>
+      <c r="B6" s="29">
+        <v>849.28199943000027</v>
+      </c>
+      <c r="C6" s="29">
+        <v>149.56199989999999</v>
+      </c>
+      <c r="D6" s="13">
         <f t="shared" si="7"/>
-        <v>45843</v>
-      </c>
-      <c r="B6" s="29">
-        <v>0</v>
-      </c>
-      <c r="C6" s="29">
-        <v>0</v>
-      </c>
-      <c r="D6" s="13">
-        <f t="shared" si="8"/>
         <v>56</v>
       </c>
       <c r="E6" s="13">
@@ -32345,25 +32341,24 @@
       <c r="M6" s="13">
         <v>0</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="29">
+        <v>243.26399940999994</v>
+      </c>
+      <c r="O6" s="29">
+        <v>57.911999910000006</v>
+      </c>
+      <c r="P6" s="13">
         <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="O6" s="13">
-        <v>0</v>
-      </c>
-      <c r="P6" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>0</v>
+      </c>
+      <c r="R6" s="13">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>0</v>
-      </c>
-      <c r="R6" s="13">
-        <v>0</v>
-      </c>
-      <c r="S6" s="13">
-        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -32371,7 +32366,7 @@
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="W6" s="6">
@@ -32401,17 +32396,17 @@
     </row>
     <row r="7" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="28">
+        <f t="shared" si="6"/>
+        <v>45844</v>
+      </c>
+      <c r="B7" s="29">
+        <v>897.16199945999983</v>
+      </c>
+      <c r="C7" s="29">
+        <v>156.28199990000002</v>
+      </c>
+      <c r="D7" s="13">
         <f t="shared" si="7"/>
-        <v>45844</v>
-      </c>
-      <c r="B7" s="29">
-        <v>0</v>
-      </c>
-      <c r="C7" s="29">
-        <v>0</v>
-      </c>
-      <c r="D7" s="13">
-        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="E7" s="13">
@@ -32445,25 +32440,24 @@
       <c r="M7" s="13">
         <v>0</v>
       </c>
-      <c r="N7" s="13">
+      <c r="N7" s="29">
+        <v>255.88799939000006</v>
+      </c>
+      <c r="O7" s="29">
+        <v>61.943999909999995</v>
+      </c>
+      <c r="P7" s="13">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="O7" s="13">
-        <v>0</v>
-      </c>
-      <c r="P7" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>0</v>
+      </c>
+      <c r="R7" s="13">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>0</v>
-      </c>
-      <c r="R7" s="13">
-        <v>0</v>
-      </c>
-      <c r="S7" s="13">
-        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -32471,7 +32465,7 @@
       </c>
       <c r="U7" s="4"/>
       <c r="V7" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="W7" s="6">
@@ -32501,17 +32495,17 @@
     </row>
     <row r="8" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="28">
+        <f t="shared" si="6"/>
+        <v>45845</v>
+      </c>
+      <c r="B8" s="29">
+        <v>1313.3819995899992</v>
+      </c>
+      <c r="C8" s="29">
+        <v>192.14999990999999</v>
+      </c>
+      <c r="D8" s="13">
         <f t="shared" si="7"/>
-        <v>45845</v>
-      </c>
-      <c r="B8" s="29">
-        <v>0</v>
-      </c>
-      <c r="C8" s="29">
-        <v>0</v>
-      </c>
-      <c r="D8" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E8" s="13">
@@ -32545,25 +32539,24 @@
       <c r="M8" s="13">
         <v>0</v>
       </c>
-      <c r="N8" s="13">
+      <c r="N8" s="29">
+        <v>237.64799939999963</v>
+      </c>
+      <c r="O8" s="29">
+        <v>63.479999890000009</v>
+      </c>
+      <c r="P8" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O8" s="13">
-        <v>0</v>
-      </c>
-      <c r="P8" s="13">
+      <c r="Q8" s="13">
+        <v>0</v>
+      </c>
+      <c r="R8" s="13">
+        <v>0</v>
+      </c>
+      <c r="S8" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>0</v>
-      </c>
-      <c r="R8" s="13">
-        <v>0</v>
-      </c>
-      <c r="S8" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -32571,7 +32564,7 @@
       </c>
       <c r="U8" s="4"/>
       <c r="V8" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="W8" s="6">
@@ -32601,17 +32594,17 @@
     </row>
     <row r="9" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="28">
+        <f t="shared" si="6"/>
+        <v>45846</v>
+      </c>
+      <c r="B9" s="29">
+        <v>1279.6979995599997</v>
+      </c>
+      <c r="C9" s="29">
+        <v>183.20399994000005</v>
+      </c>
+      <c r="D9" s="13">
         <f t="shared" si="7"/>
-        <v>45846</v>
-      </c>
-      <c r="B9" s="29">
-        <v>0</v>
-      </c>
-      <c r="C9" s="29">
-        <v>0</v>
-      </c>
-      <c r="D9" s="13">
-        <f t="shared" si="8"/>
         <v>69</v>
       </c>
       <c r="E9" s="13">
@@ -32645,25 +32638,24 @@
       <c r="M9" s="13">
         <v>0</v>
       </c>
-      <c r="N9" s="13">
+      <c r="N9" s="29">
+        <v>233.6159993399998</v>
+      </c>
+      <c r="O9" s="29">
+        <v>49.703999919999994</v>
+      </c>
+      <c r="P9" s="13">
         <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="O9" s="13">
-        <v>0</v>
-      </c>
-      <c r="P9" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>0</v>
+      </c>
+      <c r="R9" s="13">
+        <v>0</v>
+      </c>
+      <c r="S9" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>0</v>
-      </c>
-      <c r="R9" s="13">
-        <v>0</v>
-      </c>
-      <c r="S9" s="13">
-        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -32671,7 +32663,7 @@
       </c>
       <c r="U9" s="4"/>
       <c r="V9" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="W9" s="6">
@@ -32701,17 +32693,17 @@
     </row>
     <row r="10" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="28">
+        <f t="shared" si="6"/>
+        <v>45847</v>
+      </c>
+      <c r="B10" s="29">
+        <v>1214.9759995200002</v>
+      </c>
+      <c r="C10" s="29">
+        <v>190.30199987999998</v>
+      </c>
+      <c r="D10" s="13">
         <f t="shared" si="7"/>
-        <v>45847</v>
-      </c>
-      <c r="B10" s="29">
-        <v>0</v>
-      </c>
-      <c r="C10" s="29">
-        <v>0</v>
-      </c>
-      <c r="D10" s="13">
-        <f t="shared" si="8"/>
         <v>65</v>
       </c>
       <c r="E10" s="13">
@@ -32745,25 +32737,24 @@
       <c r="M10" s="13">
         <v>0</v>
       </c>
-      <c r="N10" s="13">
+      <c r="N10" s="29">
+        <v>221.99999943999987</v>
+      </c>
+      <c r="O10" s="29">
+        <v>63.287999890000002</v>
+      </c>
+      <c r="P10" s="13">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="O10" s="13">
-        <v>0</v>
-      </c>
-      <c r="P10" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>0</v>
+      </c>
+      <c r="R10" s="13">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>0</v>
-      </c>
-      <c r="R10" s="13">
-        <v>0</v>
-      </c>
-      <c r="S10" s="13">
-        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="T10" s="6" t="s">
@@ -32771,7 +32762,7 @@
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="W10" s="6">
@@ -32801,17 +32792,17 @@
     </row>
     <row r="11" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="28">
+        <f t="shared" si="6"/>
+        <v>45848</v>
+      </c>
+      <c r="B11" s="29">
+        <v>1220.2679994999999</v>
+      </c>
+      <c r="C11" s="29">
+        <v>177.15599992000003</v>
+      </c>
+      <c r="D11" s="13">
         <f t="shared" si="7"/>
-        <v>45848</v>
-      </c>
-      <c r="B11" s="29">
-        <v>0</v>
-      </c>
-      <c r="C11" s="29">
-        <v>0</v>
-      </c>
-      <c r="D11" s="13">
-        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="E11" s="13">
@@ -32845,25 +32836,24 @@
       <c r="M11" s="13">
         <v>0</v>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="29">
+        <v>239.39999935999995</v>
+      </c>
+      <c r="O11" s="29">
+        <v>48.239999900000008</v>
+      </c>
+      <c r="P11" s="13">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="O11" s="13">
-        <v>0</v>
-      </c>
-      <c r="P11" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>0</v>
+      </c>
+      <c r="R11" s="13">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>0</v>
-      </c>
-      <c r="R11" s="13">
-        <v>0</v>
-      </c>
-      <c r="S11" s="13">
-        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="T11" s="6" t="s">
@@ -32871,7 +32861,7 @@
       </c>
       <c r="U11" s="4"/>
       <c r="V11" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="W11" s="6">
@@ -32901,17 +32891,17 @@
     </row>
     <row r="12" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="28">
+        <f t="shared" si="6"/>
+        <v>45849</v>
+      </c>
+      <c r="B12" s="29">
+        <v>1060.20599956</v>
+      </c>
+      <c r="C12" s="29">
+        <v>145.10999994000002</v>
+      </c>
+      <c r="D12" s="13">
         <f t="shared" si="7"/>
-        <v>45849</v>
-      </c>
-      <c r="B12" s="29">
-        <v>0</v>
-      </c>
-      <c r="C12" s="29">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E12" s="13">
@@ -32945,25 +32935,24 @@
       <c r="M12" s="13">
         <v>0</v>
       </c>
-      <c r="N12" s="13">
+      <c r="N12" s="29">
+        <v>272.44799940999985</v>
+      </c>
+      <c r="O12" s="29">
+        <v>54.503999889999996</v>
+      </c>
+      <c r="P12" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="O12" s="13">
-        <v>0</v>
-      </c>
-      <c r="P12" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>0</v>
+      </c>
+      <c r="R12" s="13">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>0</v>
-      </c>
-      <c r="R12" s="13">
-        <v>0</v>
-      </c>
-      <c r="S12" s="13">
-        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="T12" s="6" t="s">
@@ -32971,7 +32960,7 @@
       </c>
       <c r="U12" s="4"/>
       <c r="V12" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="W12" s="6">
@@ -33001,17 +32990,17 @@
     </row>
     <row r="13" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
+        <f t="shared" si="6"/>
+        <v>45850</v>
+      </c>
+      <c r="B13" s="29">
+        <v>876.28799956000012</v>
+      </c>
+      <c r="C13" s="29">
+        <v>138.13799994999999</v>
+      </c>
+      <c r="D13" s="13">
         <f t="shared" si="7"/>
-        <v>45850</v>
-      </c>
-      <c r="B13" s="29">
-        <v>0</v>
-      </c>
-      <c r="C13" s="29">
-        <v>0</v>
-      </c>
-      <c r="D13" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E13" s="13">
@@ -33045,25 +33034,24 @@
       <c r="M13" s="13">
         <v>0</v>
       </c>
-      <c r="N13" s="13">
+      <c r="N13" s="29">
+        <v>273.93599928999976</v>
+      </c>
+      <c r="O13" s="29">
+        <v>50.255999900000006</v>
+      </c>
+      <c r="P13" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O13" s="13">
-        <v>0</v>
-      </c>
-      <c r="P13" s="13">
+      <c r="Q13" s="13">
+        <v>0</v>
+      </c>
+      <c r="R13" s="13">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>0</v>
-      </c>
-      <c r="R13" s="13">
-        <v>0</v>
-      </c>
-      <c r="S13" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -33071,7 +33059,7 @@
       </c>
       <c r="U13" s="4"/>
       <c r="V13" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="W13" s="15">
@@ -33101,17 +33089,17 @@
     </row>
     <row r="14" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="28">
+        <f t="shared" si="6"/>
+        <v>45851</v>
+      </c>
+      <c r="B14" s="29">
+        <v>1047.0179995099998</v>
+      </c>
+      <c r="C14" s="29">
+        <v>164.00999991999998</v>
+      </c>
+      <c r="D14" s="13">
         <f t="shared" si="7"/>
-        <v>45851</v>
-      </c>
-      <c r="B14" s="29">
-        <v>0</v>
-      </c>
-      <c r="C14" s="29">
-        <v>0</v>
-      </c>
-      <c r="D14" s="13">
-        <f t="shared" si="8"/>
         <v>109</v>
       </c>
       <c r="E14" s="13">
@@ -33145,25 +33133,24 @@
       <c r="M14" s="13">
         <v>0</v>
       </c>
-      <c r="N14" s="13">
+      <c r="N14" s="29">
+        <v>266.95199932999975</v>
+      </c>
+      <c r="O14" s="29">
+        <v>59.44799991</v>
+      </c>
+      <c r="P14" s="13">
         <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="O14" s="13">
-        <v>0</v>
-      </c>
-      <c r="P14" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="13">
+        <v>0</v>
+      </c>
+      <c r="R14" s="13">
+        <v>0</v>
+      </c>
+      <c r="S14" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>0</v>
-      </c>
-      <c r="R14" s="13">
-        <v>0</v>
-      </c>
-      <c r="S14" s="13">
-        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="T14" s="6" t="s">
@@ -33171,7 +33158,7 @@
       </c>
       <c r="U14" s="4"/>
       <c r="V14" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="W14" s="15">
@@ -33201,17 +33188,17 @@
     </row>
     <row r="15" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="28">
+        <f t="shared" si="6"/>
+        <v>45852</v>
+      </c>
+      <c r="B15" s="29">
+        <v>1153.5719994499998</v>
+      </c>
+      <c r="C15" s="29">
+        <v>183.37199992999999</v>
+      </c>
+      <c r="D15" s="13">
         <f t="shared" si="7"/>
-        <v>45852</v>
-      </c>
-      <c r="B15" s="29">
-        <v>0</v>
-      </c>
-      <c r="C15" s="29">
-        <v>0</v>
-      </c>
-      <c r="D15" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E15" s="13">
@@ -33244,25 +33231,24 @@
       <c r="M15" s="13">
         <v>0</v>
       </c>
-      <c r="N15" s="13">
+      <c r="N15" s="29">
+        <v>237.09599936999976</v>
+      </c>
+      <c r="O15" s="29">
+        <v>57.767999929999995</v>
+      </c>
+      <c r="P15" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O15" s="13">
-        <v>0</v>
-      </c>
-      <c r="P15" s="13">
+      <c r="Q15" s="13">
+        <v>0</v>
+      </c>
+      <c r="R15" s="13">
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>0</v>
-      </c>
-      <c r="R15" s="13">
-        <v>0</v>
-      </c>
-      <c r="S15" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T15" s="6" t="s">
@@ -33270,7 +33256,7 @@
       </c>
       <c r="U15" s="4"/>
       <c r="V15" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="W15" s="6">
@@ -33300,17 +33286,17 @@
     </row>
     <row r="16" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="28">
+        <f t="shared" si="6"/>
+        <v>45853</v>
+      </c>
+      <c r="B16" s="29">
+        <v>1309.0139995399991</v>
+      </c>
+      <c r="C16" s="29">
+        <v>175.81199992000001</v>
+      </c>
+      <c r="D16" s="13">
         <f t="shared" si="7"/>
-        <v>45853</v>
-      </c>
-      <c r="B16" s="29">
-        <v>0</v>
-      </c>
-      <c r="C16" s="29">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13">
-        <f t="shared" si="8"/>
         <v>60</v>
       </c>
       <c r="E16" s="13">
@@ -33331,7 +33317,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="13">
-        <f t="shared" ref="J16:J32" si="10">Z17-Z16</f>
+        <f t="shared" ref="J16:J32" si="9">Z17-Z16</f>
         <v>0</v>
       </c>
       <c r="K16" s="13">
@@ -33344,25 +33330,24 @@
       <c r="M16" s="13">
         <v>0</v>
       </c>
-      <c r="N16" s="13">
+      <c r="N16" s="29">
+        <v>251.08799935999988</v>
+      </c>
+      <c r="O16" s="29">
+        <v>57.599999870000005</v>
+      </c>
+      <c r="P16" s="13">
         <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="O16" s="13">
-        <v>0</v>
-      </c>
-      <c r="P16" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="13">
+        <v>0</v>
+      </c>
+      <c r="R16" s="13">
+        <v>0</v>
+      </c>
+      <c r="S16" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q16" s="13">
-        <v>0</v>
-      </c>
-      <c r="R16" s="13">
-        <v>0</v>
-      </c>
-      <c r="S16" s="13">
-        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="T16" s="6" t="s">
@@ -33370,7 +33355,7 @@
       </c>
       <c r="U16" s="4"/>
       <c r="V16" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="W16" s="6">
@@ -33400,17 +33385,17 @@
     </row>
     <row r="17" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="28">
+        <f t="shared" si="6"/>
+        <v>45854</v>
+      </c>
+      <c r="B17" s="29">
+        <v>1347.1919995400003</v>
+      </c>
+      <c r="C17" s="29">
+        <v>201.51599995000004</v>
+      </c>
+      <c r="D17" s="13">
         <f t="shared" si="7"/>
-        <v>45854</v>
-      </c>
-      <c r="B17" s="29">
-        <v>0</v>
-      </c>
-      <c r="C17" s="29">
-        <v>0</v>
-      </c>
-      <c r="D17" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E17" s="13">
@@ -33431,7 +33416,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K17" s="13">
@@ -33444,25 +33429,24 @@
       <c r="M17" s="13">
         <v>0</v>
       </c>
-      <c r="N17" s="13">
+      <c r="N17" s="29">
+        <v>249.23999939999999</v>
+      </c>
+      <c r="O17" s="29">
+        <v>48.911999910000006</v>
+      </c>
+      <c r="P17" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O17" s="13">
-        <v>0</v>
-      </c>
-      <c r="P17" s="13">
+      <c r="Q17" s="13">
+        <v>0</v>
+      </c>
+      <c r="R17" s="13">
+        <v>0</v>
+      </c>
+      <c r="S17" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="13">
-        <v>0</v>
-      </c>
-      <c r="R17" s="13">
-        <v>0</v>
-      </c>
-      <c r="S17" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T17" s="6" t="s">
@@ -33470,7 +33454,7 @@
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="W17" s="16">
@@ -33500,17 +33484,17 @@
     </row>
     <row r="18" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="28">
+        <f t="shared" si="6"/>
+        <v>45855</v>
+      </c>
+      <c r="B18" s="29">
+        <v>1301.621999519999</v>
+      </c>
+      <c r="C18" s="29">
+        <v>221.17199995000004</v>
+      </c>
+      <c r="D18" s="13">
         <f t="shared" si="7"/>
-        <v>45855</v>
-      </c>
-      <c r="B18" s="29">
-        <v>0</v>
-      </c>
-      <c r="C18" s="29">
-        <v>0</v>
-      </c>
-      <c r="D18" s="13">
-        <f t="shared" si="8"/>
         <v>106</v>
       </c>
       <c r="E18" s="13">
@@ -33531,7 +33515,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K18" s="13">
@@ -33544,25 +33528,24 @@
       <c r="M18" s="13">
         <v>0</v>
       </c>
-      <c r="N18" s="13">
+      <c r="N18" s="29">
+        <v>241.43999937000009</v>
+      </c>
+      <c r="O18" s="29">
+        <v>49.607999879999994</v>
+      </c>
+      <c r="P18" s="13">
         <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="O18" s="13">
-        <v>0</v>
-      </c>
-      <c r="P18" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="13">
+        <v>0</v>
+      </c>
+      <c r="R18" s="13">
+        <v>0</v>
+      </c>
+      <c r="S18" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>0</v>
-      </c>
-      <c r="R18" s="13">
-        <v>0</v>
-      </c>
-      <c r="S18" s="13">
-        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="T18" s="6" t="s">
@@ -33570,7 +33553,7 @@
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="W18" s="16">
@@ -33600,17 +33583,17 @@
     </row>
     <row r="19" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="28">
+        <f t="shared" si="6"/>
+        <v>45856</v>
+      </c>
+      <c r="B19" s="29">
+        <v>1110.6059995199996</v>
+      </c>
+      <c r="C19" s="29">
+        <v>155.48399988999995</v>
+      </c>
+      <c r="D19" s="13">
         <f t="shared" si="7"/>
-        <v>45856</v>
-      </c>
-      <c r="B19" s="29">
-        <v>0</v>
-      </c>
-      <c r="C19" s="29">
-        <v>0</v>
-      </c>
-      <c r="D19" s="13">
-        <f t="shared" si="8"/>
         <v>63</v>
       </c>
       <c r="E19" s="13">
@@ -33631,7 +33614,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="K19" s="13">
@@ -33644,25 +33627,24 @@
       <c r="M19" s="13">
         <v>0</v>
       </c>
-      <c r="N19" s="13">
+      <c r="N19" s="29">
+        <v>232.10399942999979</v>
+      </c>
+      <c r="O19" s="29">
+        <v>43.3439999</v>
+      </c>
+      <c r="P19" s="13">
         <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="O19" s="13">
-        <v>0</v>
-      </c>
-      <c r="P19" s="13">
+        <v>15</v>
+      </c>
+      <c r="Q19" s="13">
+        <v>0</v>
+      </c>
+      <c r="R19" s="13">
+        <v>0</v>
+      </c>
+      <c r="S19" s="13">
         <f t="shared" si="5"/>
-        <v>15</v>
-      </c>
-      <c r="Q19" s="13">
-        <v>0</v>
-      </c>
-      <c r="R19" s="13">
-        <v>0</v>
-      </c>
-      <c r="S19" s="13">
-        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="T19" s="6" t="s">
@@ -33670,7 +33652,7 @@
       </c>
       <c r="U19" s="17"/>
       <c r="V19" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="W19" s="19">
@@ -33700,17 +33682,17 @@
     </row>
     <row r="20" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="28">
+        <f t="shared" si="6"/>
+        <v>45857</v>
+      </c>
+      <c r="B20" s="29">
+        <v>1008.4199995799994</v>
+      </c>
+      <c r="C20" s="29">
+        <v>204.45599989000002</v>
+      </c>
+      <c r="D20" s="13">
         <f t="shared" si="7"/>
-        <v>45857</v>
-      </c>
-      <c r="B20" s="29">
-        <v>0</v>
-      </c>
-      <c r="C20" s="29">
-        <v>0</v>
-      </c>
-      <c r="D20" s="13">
-        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="E20" s="13">
@@ -33731,7 +33713,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K20" s="13">
@@ -33744,25 +33726,24 @@
       <c r="M20" s="13">
         <v>0</v>
       </c>
-      <c r="N20" s="13">
+      <c r="N20" s="29">
+        <v>274.1519993600001</v>
+      </c>
+      <c r="O20" s="29">
+        <v>53.015999870000009</v>
+      </c>
+      <c r="P20" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O20" s="13">
-        <v>0</v>
-      </c>
-      <c r="P20" s="13">
+      <c r="Q20" s="13">
+        <v>0</v>
+      </c>
+      <c r="R20" s="13">
+        <v>0</v>
+      </c>
+      <c r="S20" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="13">
-        <v>0</v>
-      </c>
-      <c r="R20" s="13">
-        <v>0</v>
-      </c>
-      <c r="S20" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -33770,7 +33751,7 @@
       </c>
       <c r="U20" s="4"/>
       <c r="V20" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="W20" s="15">
@@ -33800,17 +33781,17 @@
     </row>
     <row r="21" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="28">
+        <f t="shared" si="6"/>
+        <v>45858</v>
+      </c>
+      <c r="B21" s="29">
+        <v>979.85999952999919</v>
+      </c>
+      <c r="C21" s="29">
+        <v>176.69399991</v>
+      </c>
+      <c r="D21" s="13">
         <f t="shared" si="7"/>
-        <v>45858</v>
-      </c>
-      <c r="B21" s="29">
-        <v>0</v>
-      </c>
-      <c r="C21" s="29">
-        <v>0</v>
-      </c>
-      <c r="D21" s="13">
-        <f t="shared" si="8"/>
         <v>65</v>
       </c>
       <c r="E21" s="13">
@@ -33831,7 +33812,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K21" s="13">
@@ -33844,25 +33825,24 @@
       <c r="M21" s="13">
         <v>0</v>
       </c>
-      <c r="N21" s="13">
+      <c r="N21" s="29">
+        <v>255.64799941999971</v>
+      </c>
+      <c r="O21" s="29">
+        <v>49.031999899999995</v>
+      </c>
+      <c r="P21" s="13">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="O21" s="13">
-        <v>0</v>
-      </c>
-      <c r="P21" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="13">
+        <v>0</v>
+      </c>
+      <c r="R21" s="13">
+        <v>0</v>
+      </c>
+      <c r="S21" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="13">
-        <v>0</v>
-      </c>
-      <c r="R21" s="13">
-        <v>0</v>
-      </c>
-      <c r="S21" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -33870,7 +33850,7 @@
       </c>
       <c r="U21" s="4"/>
       <c r="V21" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="W21" s="15">
@@ -33900,17 +33880,17 @@
     </row>
     <row r="22" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="28">
+        <f t="shared" si="6"/>
+        <v>45859</v>
+      </c>
+      <c r="B22" s="29">
+        <v>1254.3719995099996</v>
+      </c>
+      <c r="C22" s="29">
+        <v>191.64599992999999</v>
+      </c>
+      <c r="D22" s="13">
         <f t="shared" si="7"/>
-        <v>45859</v>
-      </c>
-      <c r="B22" s="29">
-        <v>0</v>
-      </c>
-      <c r="C22" s="29">
-        <v>0</v>
-      </c>
-      <c r="D22" s="13">
-        <f t="shared" si="8"/>
         <v>49</v>
       </c>
       <c r="E22" s="13">
@@ -33931,7 +33911,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K22" s="13">
@@ -33944,25 +33924,24 @@
       <c r="M22" s="13">
         <v>0</v>
       </c>
-      <c r="N22" s="13">
+      <c r="N22" s="29">
+        <v>264.26399941999972</v>
+      </c>
+      <c r="O22" s="29">
+        <v>59.85599989</v>
+      </c>
+      <c r="P22" s="13">
         <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="O22" s="13">
-        <v>0</v>
-      </c>
-      <c r="P22" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>0</v>
+      </c>
+      <c r="R22" s="13">
+        <v>0</v>
+      </c>
+      <c r="S22" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>0</v>
-      </c>
-      <c r="R22" s="13">
-        <v>0</v>
-      </c>
-      <c r="S22" s="13">
-        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="T22" s="6" t="s">
@@ -33970,7 +33949,7 @@
       </c>
       <c r="U22" s="4"/>
       <c r="V22" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="W22" s="15">
@@ -34000,17 +33979,17 @@
     </row>
     <row r="23" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="28">
+        <f t="shared" si="6"/>
+        <v>45860</v>
+      </c>
+      <c r="B23" s="29">
+        <v>1495.4939995000002</v>
+      </c>
+      <c r="C23" s="29">
+        <v>213.06599991999997</v>
+      </c>
+      <c r="D23" s="13">
         <f t="shared" si="7"/>
-        <v>45860</v>
-      </c>
-      <c r="B23" s="29">
-        <v>0</v>
-      </c>
-      <c r="C23" s="29">
-        <v>0</v>
-      </c>
-      <c r="D23" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E23" s="13">
@@ -34031,7 +34010,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K23" s="13">
@@ -34044,25 +34023,24 @@
       <c r="M23" s="13">
         <v>0</v>
       </c>
-      <c r="N23" s="13">
+      <c r="N23" s="29">
+        <v>280.87199934999984</v>
+      </c>
+      <c r="O23" s="29">
+        <v>56.519999890000001</v>
+      </c>
+      <c r="P23" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O23" s="13">
-        <v>0</v>
-      </c>
-      <c r="P23" s="13">
+      <c r="Q23" s="13">
+        <v>0</v>
+      </c>
+      <c r="R23" s="13">
+        <v>0</v>
+      </c>
+      <c r="S23" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="13">
-        <v>0</v>
-      </c>
-      <c r="R23" s="13">
-        <v>0</v>
-      </c>
-      <c r="S23" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
@@ -34070,7 +34048,7 @@
       </c>
       <c r="U23" s="4"/>
       <c r="V23" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="W23" s="15">
@@ -34100,17 +34078,17 @@
     </row>
     <row r="24" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="28">
+        <f t="shared" si="6"/>
+        <v>45861</v>
+      </c>
+      <c r="B24" s="29">
+        <v>1533.1679994099998</v>
+      </c>
+      <c r="C24" s="29">
+        <v>238.01399993000001</v>
+      </c>
+      <c r="D24" s="13">
         <f t="shared" si="7"/>
-        <v>45861</v>
-      </c>
-      <c r="B24" s="29">
-        <v>0</v>
-      </c>
-      <c r="C24" s="29">
-        <v>0</v>
-      </c>
-      <c r="D24" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E24" s="13">
@@ -34131,7 +34109,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K24" s="13">
@@ -34144,25 +34122,24 @@
       <c r="M24" s="13">
         <v>0</v>
       </c>
-      <c r="N24" s="13">
+      <c r="N24" s="29">
+        <v>270.69599941999996</v>
+      </c>
+      <c r="O24" s="29">
+        <v>63.119999909999997</v>
+      </c>
+      <c r="P24" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O24" s="13">
-        <v>0</v>
-      </c>
-      <c r="P24" s="13">
+      <c r="Q24" s="13">
+        <v>0</v>
+      </c>
+      <c r="R24" s="13">
+        <v>0</v>
+      </c>
+      <c r="S24" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="13">
-        <v>0</v>
-      </c>
-      <c r="R24" s="13">
-        <v>0</v>
-      </c>
-      <c r="S24" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -34170,7 +34147,7 @@
       </c>
       <c r="U24" s="4"/>
       <c r="V24" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="W24" s="15">
@@ -34200,17 +34177,17 @@
     </row>
     <row r="25" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="28">
+        <f t="shared" si="6"/>
+        <v>45862</v>
+      </c>
+      <c r="B25" s="29">
+        <v>1690.6679994699996</v>
+      </c>
+      <c r="C25" s="29">
+        <v>238.22399992999996</v>
+      </c>
+      <c r="D25" s="13">
         <f t="shared" si="7"/>
-        <v>45862</v>
-      </c>
-      <c r="B25" s="29">
-        <v>0</v>
-      </c>
-      <c r="C25" s="29">
-        <v>0</v>
-      </c>
-      <c r="D25" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E25" s="13">
@@ -34231,7 +34208,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K25" s="13">
@@ -34244,25 +34221,24 @@
       <c r="M25" s="13">
         <v>0</v>
       </c>
-      <c r="N25" s="13">
+      <c r="N25" s="29">
+        <v>294.16799943999979</v>
+      </c>
+      <c r="O25" s="29">
+        <v>55.607999909999997</v>
+      </c>
+      <c r="P25" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O25" s="13">
-        <v>0</v>
-      </c>
-      <c r="P25" s="13">
+      <c r="Q25" s="13">
+        <v>0</v>
+      </c>
+      <c r="R25" s="13">
+        <v>0</v>
+      </c>
+      <c r="S25" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="13">
-        <v>0</v>
-      </c>
-      <c r="R25" s="13">
-        <v>0</v>
-      </c>
-      <c r="S25" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -34270,7 +34246,7 @@
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>23</v>
       </c>
       <c r="W25" s="15">
@@ -34300,17 +34276,17 @@
     </row>
     <row r="26" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="28">
+        <f t="shared" si="6"/>
+        <v>45863</v>
+      </c>
+      <c r="B26" s="29">
+        <v>1235.5559994999996</v>
+      </c>
+      <c r="C26" s="29">
+        <v>165.14399989999998</v>
+      </c>
+      <c r="D26" s="13">
         <f t="shared" si="7"/>
-        <v>45863</v>
-      </c>
-      <c r="B26" s="29">
-        <v>0</v>
-      </c>
-      <c r="C26" s="29">
-        <v>0</v>
-      </c>
-      <c r="D26" s="13">
-        <f t="shared" si="8"/>
         <v>204</v>
       </c>
       <c r="E26" s="13">
@@ -34331,7 +34307,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="K26" s="13">
@@ -34344,25 +34320,24 @@
       <c r="M26" s="13">
         <v>0</v>
       </c>
-      <c r="N26" s="13">
+      <c r="N26" s="29">
+        <v>297.31199934999978</v>
+      </c>
+      <c r="O26" s="29">
+        <v>55.487999910000006</v>
+      </c>
+      <c r="P26" s="13">
         <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="O26" s="13">
-        <v>0</v>
-      </c>
-      <c r="P26" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="13">
+        <v>0</v>
+      </c>
+      <c r="R26" s="13">
+        <v>0</v>
+      </c>
+      <c r="S26" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="13">
-        <v>0</v>
-      </c>
-      <c r="R26" s="13">
-        <v>0</v>
-      </c>
-      <c r="S26" s="13">
-        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -34370,7 +34345,7 @@
       </c>
       <c r="U26" s="4"/>
       <c r="V26" s="20">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
       <c r="W26" s="15">
@@ -34400,17 +34375,17 @@
     </row>
     <row r="27" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="28">
+        <f t="shared" si="6"/>
+        <v>45864</v>
+      </c>
+      <c r="B27" s="29">
+        <v>915.51599949999991</v>
+      </c>
+      <c r="C27" s="29">
+        <v>158.25599991999997</v>
+      </c>
+      <c r="D27" s="13">
         <f t="shared" si="7"/>
-        <v>45864</v>
-      </c>
-      <c r="B27" s="29">
-        <v>0</v>
-      </c>
-      <c r="C27" s="29">
-        <v>0</v>
-      </c>
-      <c r="D27" s="13">
-        <f t="shared" si="8"/>
         <v>78</v>
       </c>
       <c r="E27" s="13">
@@ -34431,7 +34406,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K27" s="13">
@@ -34444,25 +34419,24 @@
       <c r="M27" s="13">
         <v>0</v>
       </c>
-      <c r="N27" s="13">
+      <c r="N27" s="29">
+        <v>285.45599935999996</v>
+      </c>
+      <c r="O27" s="29">
+        <v>53.327999879999993</v>
+      </c>
+      <c r="P27" s="13">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="O27" s="13">
-        <v>0</v>
-      </c>
-      <c r="P27" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="13">
+        <v>0</v>
+      </c>
+      <c r="R27" s="13">
+        <v>0</v>
+      </c>
+      <c r="S27" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="13">
-        <v>0</v>
-      </c>
-      <c r="R27" s="13">
-        <v>0</v>
-      </c>
-      <c r="S27" s="13">
-        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="T27" s="6" t="s">
@@ -34470,7 +34444,7 @@
       </c>
       <c r="U27" s="4"/>
       <c r="V27" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>25</v>
       </c>
       <c r="W27" s="15">
@@ -34500,17 +34474,17 @@
     </row>
     <row r="28" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="28">
+        <f t="shared" si="6"/>
+        <v>45865</v>
+      </c>
+      <c r="B28" s="29">
+        <v>931.85399950999954</v>
+      </c>
+      <c r="C28" s="29">
+        <v>160.06199992999998</v>
+      </c>
+      <c r="D28" s="13">
         <f t="shared" si="7"/>
-        <v>45865</v>
-      </c>
-      <c r="B28" s="29">
-        <v>0</v>
-      </c>
-      <c r="C28" s="29">
-        <v>0</v>
-      </c>
-      <c r="D28" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E28" s="13">
@@ -34531,7 +34505,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K28" s="13">
@@ -34544,25 +34518,24 @@
       <c r="M28" s="13">
         <v>0</v>
       </c>
-      <c r="N28" s="13">
+      <c r="N28" s="29">
+        <v>295.63199934999972</v>
+      </c>
+      <c r="O28" s="29">
+        <v>56.92799990999999</v>
+      </c>
+      <c r="P28" s="13">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="O28" s="13">
-        <v>0</v>
-      </c>
-      <c r="P28" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="13">
+        <v>0</v>
+      </c>
+      <c r="R28" s="13">
+        <v>0</v>
+      </c>
+      <c r="S28" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="13">
-        <v>0</v>
-      </c>
-      <c r="R28" s="13">
-        <v>0</v>
-      </c>
-      <c r="S28" s="13">
-        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="T28" s="6" t="s">
@@ -34570,7 +34543,7 @@
       </c>
       <c r="U28" s="4"/>
       <c r="V28" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>26</v>
       </c>
       <c r="W28" s="15">
@@ -34600,17 +34573,17 @@
     </row>
     <row r="29" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="28">
+        <f t="shared" si="6"/>
+        <v>45866</v>
+      </c>
+      <c r="B29" s="29">
+        <v>1491.1259994800002</v>
+      </c>
+      <c r="C29" s="29">
+        <v>187.86599992999999</v>
+      </c>
+      <c r="D29" s="13">
         <f t="shared" si="7"/>
-        <v>45866</v>
-      </c>
-      <c r="B29" s="29">
-        <v>0</v>
-      </c>
-      <c r="C29" s="29">
-        <v>0</v>
-      </c>
-      <c r="D29" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E29" s="13">
@@ -34631,7 +34604,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K29" s="13">
@@ -34644,25 +34617,24 @@
       <c r="M29" s="13">
         <v>0</v>
       </c>
-      <c r="N29" s="13">
+      <c r="N29" s="29">
+        <v>274.46399932999992</v>
+      </c>
+      <c r="O29" s="29">
+        <v>54.455999929999997</v>
+      </c>
+      <c r="P29" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O29" s="13">
-        <v>0</v>
-      </c>
-      <c r="P29" s="13">
+      <c r="Q29" s="13">
+        <v>0</v>
+      </c>
+      <c r="R29" s="13">
+        <v>0</v>
+      </c>
+      <c r="S29" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="13">
-        <v>0</v>
-      </c>
-      <c r="R29" s="13">
-        <v>0</v>
-      </c>
-      <c r="S29" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
@@ -34670,7 +34642,7 @@
       </c>
       <c r="U29" s="4"/>
       <c r="V29" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="W29" s="15">
@@ -34700,17 +34672,17 @@
     </row>
     <row r="30" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="28">
+        <f t="shared" si="6"/>
+        <v>45867</v>
+      </c>
+      <c r="B30" s="29">
+        <v>1269.1979995199997</v>
+      </c>
+      <c r="C30" s="29">
+        <v>213.06599994000004</v>
+      </c>
+      <c r="D30" s="13">
         <f t="shared" si="7"/>
-        <v>45867</v>
-      </c>
-      <c r="B30" s="29">
-        <v>0</v>
-      </c>
-      <c r="C30" s="29">
-        <v>0</v>
-      </c>
-      <c r="D30" s="13">
-        <f t="shared" si="8"/>
         <v>87</v>
       </c>
       <c r="E30" s="13">
@@ -34731,7 +34703,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K30" s="13">
@@ -34744,25 +34716,24 @@
       <c r="M30" s="13">
         <v>0</v>
       </c>
-      <c r="N30" s="13">
+      <c r="N30" s="29">
+        <v>226.48799934999997</v>
+      </c>
+      <c r="O30" s="29">
+        <v>47.639999899999999</v>
+      </c>
+      <c r="P30" s="13">
         <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="O30" s="13">
-        <v>0</v>
-      </c>
-      <c r="P30" s="13">
+        <v>-10</v>
+      </c>
+      <c r="Q30" s="13">
+        <v>0</v>
+      </c>
+      <c r="R30" s="13">
+        <v>0</v>
+      </c>
+      <c r="S30" s="13">
         <f t="shared" si="5"/>
-        <v>-10</v>
-      </c>
-      <c r="Q30" s="13">
-        <v>0</v>
-      </c>
-      <c r="R30" s="13">
-        <v>0</v>
-      </c>
-      <c r="S30" s="13">
-        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="T30" s="6" t="s">
@@ -34770,7 +34741,7 @@
       </c>
       <c r="U30" s="4"/>
       <c r="V30" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>28</v>
       </c>
       <c r="W30" s="15">
@@ -34800,17 +34771,17 @@
     </row>
     <row r="31" spans="1:30" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A31" s="28">
+        <f t="shared" si="6"/>
+        <v>45868</v>
+      </c>
+      <c r="B31" s="29">
+        <v>1219.5959995000001</v>
+      </c>
+      <c r="C31" s="29">
+        <v>190.80599993999996</v>
+      </c>
+      <c r="D31" s="13">
         <f t="shared" si="7"/>
-        <v>45868</v>
-      </c>
-      <c r="B31" s="29">
-        <v>0</v>
-      </c>
-      <c r="C31" s="29">
-        <v>0</v>
-      </c>
-      <c r="D31" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E31" s="13">
@@ -34831,7 +34802,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K31" s="13">
@@ -34844,25 +34815,24 @@
       <c r="M31" s="13">
         <v>0</v>
       </c>
-      <c r="N31" s="13">
+      <c r="N31" s="29">
+        <v>233.9999993399997</v>
+      </c>
+      <c r="O31" s="29">
+        <v>48.023999929999995</v>
+      </c>
+      <c r="P31" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O31" s="13">
-        <v>0</v>
-      </c>
-      <c r="P31" s="13">
+      <c r="Q31" s="13">
+        <v>0</v>
+      </c>
+      <c r="R31" s="13">
+        <v>0</v>
+      </c>
+      <c r="S31" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="13">
-        <v>0</v>
-      </c>
-      <c r="R31" s="13">
-        <v>0</v>
-      </c>
-      <c r="S31" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T31" s="6" t="s">
@@ -34870,7 +34840,7 @@
       </c>
       <c r="U31" s="4"/>
       <c r="V31" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>29</v>
       </c>
       <c r="W31" s="15">
@@ -34900,17 +34870,17 @@
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="28">
+        <f t="shared" si="6"/>
+        <v>45869</v>
+      </c>
+      <c r="B32" s="29">
+        <v>1298.9339995499995</v>
+      </c>
+      <c r="C32" s="29">
+        <v>200.59199991999998</v>
+      </c>
+      <c r="D32" s="13">
         <f t="shared" si="7"/>
-        <v>45869</v>
-      </c>
-      <c r="B32" s="29">
-        <v>0</v>
-      </c>
-      <c r="C32" s="29">
-        <v>0</v>
-      </c>
-      <c r="D32" s="13">
-        <f t="shared" si="8"/>
         <v>85</v>
       </c>
       <c r="E32" s="13">
@@ -34931,7 +34901,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="K32" s="13">
@@ -34944,25 +34914,24 @@
       <c r="M32" s="13">
         <v>0</v>
       </c>
-      <c r="N32" s="13">
+      <c r="N32" s="29">
+        <v>228.04799942999989</v>
+      </c>
+      <c r="O32" s="29">
+        <v>55.175999879999999</v>
+      </c>
+      <c r="P32" s="13">
         <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="O32" s="13">
-        <v>0</v>
-      </c>
-      <c r="P32" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="13">
+        <v>0</v>
+      </c>
+      <c r="R32" s="13">
+        <v>0</v>
+      </c>
+      <c r="S32" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q32" s="13">
-        <v>0</v>
-      </c>
-      <c r="R32" s="13">
-        <v>0</v>
-      </c>
-      <c r="S32" s="13">
-        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="T32" s="6" t="s">
@@ -34970,7 +34939,7 @@
       </c>
       <c r="U32" s="4"/>
       <c r="V32" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
       <c r="W32" s="15">
@@ -35001,7 +34970,7 @@
     <row r="33" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="U33" s="4"/>
       <c r="V33" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="W33" s="15">
@@ -35031,14 +35000,14 @@
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -35416,15 +35385,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="47"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="47"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="47"/>
-      <c r="I71" s="47"/>
+      <c r="A71" s="48"/>
+      <c r="B71" s="48"/>
+      <c r="C71" s="48"/>
+      <c r="D71" s="48"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -35449,15 +35418,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="48"/>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
+      <c r="A76" s="49"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="49"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -35493,15 +35462,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="49"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49"/>
+      <c r="A80" s="50"/>
+      <c r="B80" s="50"/>
+      <c r="C80" s="50"/>
+      <c r="D80" s="50"/>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50"/>
+      <c r="H80" s="50"/>
+      <c r="I80" s="50"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -35537,15 +35506,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="48"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
+      <c r="A88" s="49"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="49"/>
+      <c r="D88" s="49"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
+      <c r="H88" s="49"/>
+      <c r="I88" s="49"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -35648,15 +35617,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="47"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="47"/>
-      <c r="D101" s="47"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="47"/>
-      <c r="G101" s="47"/>
-      <c r="H101" s="47"/>
-      <c r="I101" s="47"/>
+      <c r="A101" s="48"/>
+      <c r="B101" s="48"/>
+      <c r="C101" s="48"/>
+      <c r="D101" s="48"/>
+      <c r="E101" s="48"/>
+      <c r="F101" s="48"/>
+      <c r="G101" s="48"/>
+      <c r="H101" s="48"/>
+      <c r="I101" s="48"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -38708,22 +38677,22 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="47"/>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47"/>
-      <c r="S35" s="47"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="48"/>
+      <c r="L35" s="48"/>
+      <c r="M35" s="48"/>
+      <c r="N35" s="48"/>
+      <c r="O35" s="48"/>
+      <c r="P35" s="48"/>
+      <c r="Q35" s="48"/>
+      <c r="R35" s="48"/>
+      <c r="S35" s="48"/>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -39441,25 +39410,25 @@
       <c r="S69" s="1"/>
     </row>
     <row r="70" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="47"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="47"/>
-      <c r="F70" s="47"/>
-      <c r="G70" s="47"/>
-      <c r="H70" s="47"/>
-      <c r="I70" s="47"/>
-      <c r="J70" s="47"/>
-      <c r="K70" s="47"/>
-      <c r="L70" s="47"/>
-      <c r="M70" s="47"/>
-      <c r="N70" s="47"/>
-      <c r="O70" s="47"/>
-      <c r="P70" s="47"/>
-      <c r="Q70" s="47"/>
-      <c r="R70" s="47"/>
-      <c r="S70" s="47"/>
+      <c r="A70" s="48"/>
+      <c r="B70" s="48"/>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="48"/>
+      <c r="K70" s="48"/>
+      <c r="L70" s="48"/>
+      <c r="M70" s="48"/>
+      <c r="N70" s="48"/>
+      <c r="O70" s="48"/>
+      <c r="P70" s="48"/>
+      <c r="Q70" s="48"/>
+      <c r="R70" s="48"/>
+      <c r="S70" s="48"/>
     </row>
     <row r="71" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -39504,25 +39473,25 @@
       <c r="S72" s="23"/>
     </row>
     <row r="75" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="48"/>
-      <c r="B75" s="48"/>
-      <c r="C75" s="48"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
-      <c r="J75" s="48"/>
-      <c r="K75" s="48"/>
-      <c r="L75" s="48"/>
-      <c r="M75" s="48"/>
-      <c r="N75" s="48"/>
-      <c r="O75" s="48"/>
-      <c r="P75" s="48"/>
-      <c r="Q75" s="48"/>
-      <c r="R75" s="48"/>
-      <c r="S75" s="48"/>
+      <c r="A75" s="49"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="49"/>
+      <c r="E75" s="49"/>
+      <c r="F75" s="49"/>
+      <c r="G75" s="49"/>
+      <c r="H75" s="49"/>
+      <c r="I75" s="49"/>
+      <c r="J75" s="49"/>
+      <c r="K75" s="49"/>
+      <c r="L75" s="49"/>
+      <c r="M75" s="49"/>
+      <c r="N75" s="49"/>
+      <c r="O75" s="49"/>
+      <c r="P75" s="49"/>
+      <c r="Q75" s="49"/>
+      <c r="R75" s="49"/>
+      <c r="S75" s="49"/>
     </row>
     <row r="76" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -39588,25 +39557,25 @@
       <c r="S78" s="25"/>
     </row>
     <row r="79" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="49"/>
-      <c r="B79" s="49"/>
-      <c r="C79" s="49"/>
-      <c r="D79" s="49"/>
-      <c r="E79" s="49"/>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49"/>
-      <c r="J79" s="49"/>
-      <c r="K79" s="49"/>
-      <c r="L79" s="49"/>
-      <c r="M79" s="49"/>
-      <c r="N79" s="49"/>
-      <c r="O79" s="49"/>
-      <c r="P79" s="49"/>
-      <c r="Q79" s="49"/>
-      <c r="R79" s="49"/>
-      <c r="S79" s="49"/>
+      <c r="A79" s="50"/>
+      <c r="B79" s="50"/>
+      <c r="C79" s="50"/>
+      <c r="D79" s="50"/>
+      <c r="E79" s="50"/>
+      <c r="F79" s="50"/>
+      <c r="G79" s="50"/>
+      <c r="H79" s="50"/>
+      <c r="I79" s="50"/>
+      <c r="J79" s="50"/>
+      <c r="K79" s="50"/>
+      <c r="L79" s="50"/>
+      <c r="M79" s="50"/>
+      <c r="N79" s="50"/>
+      <c r="O79" s="50"/>
+      <c r="P79" s="50"/>
+      <c r="Q79" s="50"/>
+      <c r="R79" s="50"/>
+      <c r="S79" s="50"/>
     </row>
     <row r="80" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -39670,25 +39639,25 @@
       <c r="E85" s="23"/>
     </row>
     <row r="87" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="48"/>
-      <c r="B87" s="48"/>
-      <c r="C87" s="48"/>
-      <c r="D87" s="48"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48"/>
-      <c r="J87" s="48"/>
-      <c r="K87" s="48"/>
-      <c r="L87" s="48"/>
-      <c r="M87" s="48"/>
-      <c r="N87" s="48"/>
-      <c r="O87" s="48"/>
-      <c r="P87" s="48"/>
-      <c r="Q87" s="48"/>
-      <c r="R87" s="48"/>
-      <c r="S87" s="48"/>
+      <c r="A87" s="49"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="49"/>
+      <c r="D87" s="49"/>
+      <c r="E87" s="49"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="49"/>
+      <c r="H87" s="49"/>
+      <c r="I87" s="49"/>
+      <c r="J87" s="49"/>
+      <c r="K87" s="49"/>
+      <c r="L87" s="49"/>
+      <c r="M87" s="49"/>
+      <c r="N87" s="49"/>
+      <c r="O87" s="49"/>
+      <c r="P87" s="49"/>
+      <c r="Q87" s="49"/>
+      <c r="R87" s="49"/>
+      <c r="S87" s="49"/>
     </row>
     <row r="88" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -39880,25 +39849,25 @@
       <c r="E98" s="26"/>
     </row>
     <row r="100" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="47"/>
-      <c r="B100" s="47"/>
-      <c r="C100" s="47"/>
-      <c r="D100" s="47"/>
-      <c r="E100" s="47"/>
-      <c r="F100" s="47"/>
-      <c r="G100" s="47"/>
-      <c r="H100" s="47"/>
-      <c r="I100" s="47"/>
-      <c r="J100" s="47"/>
-      <c r="K100" s="47"/>
-      <c r="L100" s="47"/>
-      <c r="M100" s="47"/>
-      <c r="N100" s="47"/>
-      <c r="O100" s="47"/>
-      <c r="P100" s="47"/>
-      <c r="Q100" s="47"/>
-      <c r="R100" s="47"/>
-      <c r="S100" s="47"/>
+      <c r="A100" s="48"/>
+      <c r="B100" s="48"/>
+      <c r="C100" s="48"/>
+      <c r="D100" s="48"/>
+      <c r="E100" s="48"/>
+      <c r="F100" s="48"/>
+      <c r="G100" s="48"/>
+      <c r="H100" s="48"/>
+      <c r="I100" s="48"/>
+      <c r="J100" s="48"/>
+      <c r="K100" s="48"/>
+      <c r="L100" s="48"/>
+      <c r="M100" s="48"/>
+      <c r="N100" s="48"/>
+      <c r="O100" s="48"/>
+      <c r="P100" s="48"/>
+      <c r="Q100" s="48"/>
+      <c r="R100" s="48"/>
+      <c r="S100" s="48"/>
     </row>
     <row r="101" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -43141,14 +43110,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -43526,15 +43495,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="47"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="47"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="47"/>
-      <c r="I71" s="47"/>
+      <c r="A71" s="48"/>
+      <c r="B71" s="48"/>
+      <c r="C71" s="48"/>
+      <c r="D71" s="48"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -43559,15 +43528,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="48"/>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
+      <c r="A76" s="49"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="49"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -43603,15 +43572,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="49"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49"/>
+      <c r="A80" s="50"/>
+      <c r="B80" s="50"/>
+      <c r="C80" s="50"/>
+      <c r="D80" s="50"/>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50"/>
+      <c r="H80" s="50"/>
+      <c r="I80" s="50"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -43647,15 +43616,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="48"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
+      <c r="A88" s="49"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="49"/>
+      <c r="D88" s="49"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
+      <c r="H88" s="49"/>
+      <c r="I88" s="49"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -43758,15 +43727,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="47"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="47"/>
-      <c r="D101" s="47"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="47"/>
-      <c r="G101" s="47"/>
-      <c r="H101" s="47"/>
-      <c r="I101" s="47"/>
+      <c r="A101" s="48"/>
+      <c r="B101" s="48"/>
+      <c r="C101" s="48"/>
+      <c r="D101" s="48"/>
+      <c r="E101" s="48"/>
+      <c r="F101" s="48"/>
+      <c r="G101" s="48"/>
+      <c r="H101" s="48"/>
+      <c r="I101" s="48"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23170D55-AB78-45B2-A656-14E99083120E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BDBCE4-EABA-451F-8D79-F7FBE5ED2FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -264,7 +264,7 @@
     <numFmt numFmtId="166" formatCode="_-&quot;R$ &quot;* #,##0.000_-;&quot;-R$ &quot;* #,##0.000_-;_-&quot;R$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="[$R$ -416]#,##0.00"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -354,13 +354,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -478,7 +471,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -601,9 +594,6 @@
     </xf>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1320,34 +1310,34 @@
         <v>12141.35</v>
       </c>
       <c r="D8" s="41">
-        <v>0</v>
+        <v>1056.74</v>
       </c>
       <c r="E8" s="41">
-        <v>0</v>
+        <v>474.77</v>
       </c>
       <c r="F8" s="41">
-        <v>0</v>
+        <v>1111.7</v>
       </c>
       <c r="G8" s="41">
-        <v>0</v>
+        <v>499.45</v>
       </c>
       <c r="H8" s="41">
-        <v>0</v>
+        <v>3638.02</v>
       </c>
       <c r="I8" s="41">
-        <v>0</v>
+        <v>1634.4749999999999</v>
       </c>
       <c r="J8" s="41">
-        <v>0</v>
+        <v>60.92</v>
       </c>
       <c r="K8" s="41">
-        <v>0</v>
+        <v>27.36</v>
       </c>
       <c r="L8" s="41">
-        <v>0</v>
+        <v>934.17719999999997</v>
       </c>
       <c r="M8" s="41">
-        <v>0</v>
+        <v>419.7</v>
       </c>
       <c r="N8" s="41">
         <v>6888.16</v>
@@ -4829,15 +4819,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="48"/>
-      <c r="B69" s="48"/>
-      <c r="C69" s="48"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="48"/>
-      <c r="H69" s="48"/>
-      <c r="I69" s="48"/>
+      <c r="A69" s="47"/>
+      <c r="B69" s="47"/>
+      <c r="C69" s="47"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="47"/>
+      <c r="G69" s="47"/>
+      <c r="H69" s="47"/>
+      <c r="I69" s="47"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -4862,15 +4852,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="49"/>
-      <c r="B74" s="49"/>
-      <c r="C74" s="49"/>
-      <c r="D74" s="49"/>
-      <c r="E74" s="49"/>
-      <c r="F74" s="49"/>
-      <c r="G74" s="49"/>
-      <c r="H74" s="49"/>
-      <c r="I74" s="49"/>
+      <c r="A74" s="48"/>
+      <c r="B74" s="48"/>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -4906,15 +4896,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="50"/>
-      <c r="B78" s="50"/>
-      <c r="C78" s="50"/>
-      <c r="D78" s="50"/>
-      <c r="E78" s="50"/>
-      <c r="F78" s="50"/>
-      <c r="G78" s="50"/>
-      <c r="H78" s="50"/>
-      <c r="I78" s="50"/>
+      <c r="A78" s="49"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="49"/>
+      <c r="D78" s="49"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="49"/>
+      <c r="G78" s="49"/>
+      <c r="H78" s="49"/>
+      <c r="I78" s="49"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -4950,15 +4940,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="49"/>
-      <c r="B86" s="49"/>
-      <c r="C86" s="49"/>
-      <c r="D86" s="49"/>
-      <c r="E86" s="49"/>
-      <c r="F86" s="49"/>
-      <c r="G86" s="49"/>
-      <c r="H86" s="49"/>
-      <c r="I86" s="49"/>
+      <c r="A86" s="48"/>
+      <c r="B86" s="48"/>
+      <c r="C86" s="48"/>
+      <c r="D86" s="48"/>
+      <c r="E86" s="48"/>
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="48"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -5061,15 +5051,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="48"/>
-      <c r="B99" s="48"/>
-      <c r="C99" s="48"/>
-      <c r="D99" s="48"/>
-      <c r="E99" s="48"/>
-      <c r="F99" s="48"/>
-      <c r="G99" s="48"/>
-      <c r="H99" s="48"/>
-      <c r="I99" s="48"/>
+      <c r="A99" s="47"/>
+      <c r="B99" s="47"/>
+      <c r="C99" s="47"/>
+      <c r="D99" s="47"/>
+      <c r="E99" s="47"/>
+      <c r="F99" s="47"/>
+      <c r="G99" s="47"/>
+      <c r="H99" s="47"/>
+      <c r="I99" s="47"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -8269,14 +8259,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -8653,15 +8643,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="48"/>
-      <c r="B71" s="48"/>
-      <c r="C71" s="48"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="48"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -8686,15 +8676,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="49"/>
-      <c r="B76" s="49"/>
-      <c r="C76" s="49"/>
-      <c r="D76" s="49"/>
-      <c r="E76" s="49"/>
-      <c r="F76" s="49"/>
-      <c r="G76" s="49"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="49"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -8730,15 +8720,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="50"/>
-      <c r="B80" s="50"/>
-      <c r="C80" s="50"/>
-      <c r="D80" s="50"/>
-      <c r="E80" s="50"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="50"/>
-      <c r="H80" s="50"/>
-      <c r="I80" s="50"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -8774,15 +8764,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="49"/>
-      <c r="B88" s="49"/>
-      <c r="C88" s="49"/>
-      <c r="D88" s="49"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="49"/>
-      <c r="G88" s="49"/>
-      <c r="H88" s="49"/>
-      <c r="I88" s="49"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -8885,15 +8875,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="48"/>
-      <c r="B101" s="48"/>
-      <c r="C101" s="48"/>
-      <c r="D101" s="48"/>
-      <c r="E101" s="48"/>
-      <c r="F101" s="48"/>
-      <c r="G101" s="48"/>
-      <c r="H101" s="48"/>
-      <c r="I101" s="48"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -11267,14 +11257,14 @@
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="48"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="48"/>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
       <c r="T32" s="27"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
@@ -11652,15 +11642,15 @@
       <c r="I66" s="1"/>
     </row>
     <row r="67" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="48"/>
-      <c r="B67" s="48"/>
-      <c r="C67" s="48"/>
-      <c r="D67" s="48"/>
-      <c r="E67" s="48"/>
-      <c r="F67" s="48"/>
-      <c r="G67" s="48"/>
-      <c r="H67" s="48"/>
-      <c r="I67" s="48"/>
+      <c r="A67" s="47"/>
+      <c r="B67" s="47"/>
+      <c r="C67" s="47"/>
+      <c r="D67" s="47"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="47"/>
+      <c r="G67" s="47"/>
+      <c r="H67" s="47"/>
+      <c r="I67" s="47"/>
     </row>
     <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
@@ -11685,15 +11675,15 @@
       <c r="I69" s="23"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="49"/>
-      <c r="B72" s="49"/>
-      <c r="C72" s="49"/>
-      <c r="D72" s="49"/>
-      <c r="E72" s="49"/>
-      <c r="F72" s="49"/>
-      <c r="G72" s="49"/>
-      <c r="H72" s="49"/>
-      <c r="I72" s="49"/>
+      <c r="A72" s="48"/>
+      <c r="B72" s="48"/>
+      <c r="C72" s="48"/>
+      <c r="D72" s="48"/>
+      <c r="E72" s="48"/>
+      <c r="F72" s="48"/>
+      <c r="G72" s="48"/>
+      <c r="H72" s="48"/>
+      <c r="I72" s="48"/>
     </row>
     <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
@@ -11729,15 +11719,15 @@
       <c r="I75" s="25"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="50"/>
-      <c r="B76" s="50"/>
-      <c r="C76" s="50"/>
-      <c r="D76" s="50"/>
-      <c r="E76" s="50"/>
-      <c r="F76" s="50"/>
-      <c r="G76" s="50"/>
-      <c r="H76" s="50"/>
-      <c r="I76" s="50"/>
+      <c r="A76" s="49"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="49"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -11773,15 +11763,15 @@
       <c r="B82" s="23"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="49"/>
-      <c r="B84" s="49"/>
-      <c r="C84" s="49"/>
-      <c r="D84" s="49"/>
-      <c r="E84" s="49"/>
-      <c r="F84" s="49"/>
-      <c r="G84" s="49"/>
-      <c r="H84" s="49"/>
-      <c r="I84" s="49"/>
+      <c r="A84" s="48"/>
+      <c r="B84" s="48"/>
+      <c r="C84" s="48"/>
+      <c r="D84" s="48"/>
+      <c r="E84" s="48"/>
+      <c r="F84" s="48"/>
+      <c r="G84" s="48"/>
+      <c r="H84" s="48"/>
+      <c r="I84" s="48"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
@@ -11884,15 +11874,15 @@
       <c r="B95" s="26"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="48"/>
-      <c r="B97" s="48"/>
-      <c r="C97" s="48"/>
-      <c r="D97" s="48"/>
-      <c r="E97" s="48"/>
-      <c r="F97" s="48"/>
-      <c r="G97" s="48"/>
-      <c r="H97" s="48"/>
-      <c r="I97" s="48"/>
+      <c r="A97" s="47"/>
+      <c r="B97" s="47"/>
+      <c r="C97" s="47"/>
+      <c r="D97" s="47"/>
+      <c r="E97" s="47"/>
+      <c r="F97" s="47"/>
+      <c r="G97" s="47"/>
+      <c r="H97" s="47"/>
+      <c r="I97" s="47"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
@@ -14442,14 +14432,14 @@
     <row r="34" spans="1:21" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -14826,15 +14816,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="48"/>
-      <c r="B71" s="48"/>
-      <c r="C71" s="48"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="48"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -14859,15 +14849,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="49"/>
-      <c r="B76" s="49"/>
-      <c r="C76" s="49"/>
-      <c r="D76" s="49"/>
-      <c r="E76" s="49"/>
-      <c r="F76" s="49"/>
-      <c r="G76" s="49"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="49"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -14903,15 +14893,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="50"/>
-      <c r="B80" s="50"/>
-      <c r="C80" s="50"/>
-      <c r="D80" s="50"/>
-      <c r="E80" s="50"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="50"/>
-      <c r="H80" s="50"/>
-      <c r="I80" s="50"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -14947,15 +14937,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="49"/>
-      <c r="B88" s="49"/>
-      <c r="C88" s="49"/>
-      <c r="D88" s="49"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="49"/>
-      <c r="G88" s="49"/>
-      <c r="H88" s="49"/>
-      <c r="I88" s="49"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -15058,15 +15048,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="48"/>
-      <c r="B101" s="48"/>
-      <c r="C101" s="48"/>
-      <c r="D101" s="48"/>
-      <c r="E101" s="48"/>
-      <c r="F101" s="48"/>
-      <c r="G101" s="48"/>
-      <c r="H101" s="48"/>
-      <c r="I101" s="48"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -17801,14 +17791,14 @@
     </row>
     <row r="35" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
     </row>
     <row r="36" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -18186,15 +18176,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="48"/>
-      <c r="B70" s="48"/>
-      <c r="C70" s="48"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="48"/>
-      <c r="G70" s="48"/>
-      <c r="H70" s="48"/>
-      <c r="I70" s="48"/>
+      <c r="A70" s="47"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -18219,15 +18209,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="49"/>
-      <c r="B75" s="49"/>
-      <c r="C75" s="49"/>
-      <c r="D75" s="49"/>
-      <c r="E75" s="49"/>
-      <c r="F75" s="49"/>
-      <c r="G75" s="49"/>
-      <c r="H75" s="49"/>
-      <c r="I75" s="49"/>
+      <c r="A75" s="48"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -18263,15 +18253,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="50"/>
-      <c r="B79" s="50"/>
-      <c r="C79" s="50"/>
-      <c r="D79" s="50"/>
-      <c r="E79" s="50"/>
-      <c r="F79" s="50"/>
-      <c r="G79" s="50"/>
-      <c r="H79" s="50"/>
-      <c r="I79" s="50"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -18307,15 +18297,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="49"/>
-      <c r="B87" s="49"/>
-      <c r="C87" s="49"/>
-      <c r="D87" s="49"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="49"/>
-      <c r="G87" s="49"/>
-      <c r="H87" s="49"/>
-      <c r="I87" s="49"/>
+      <c r="A87" s="48"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -18418,15 +18408,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="48"/>
-      <c r="B100" s="48"/>
-      <c r="C100" s="48"/>
-      <c r="D100" s="48"/>
-      <c r="E100" s="48"/>
-      <c r="F100" s="48"/>
-      <c r="G100" s="48"/>
-      <c r="H100" s="48"/>
-      <c r="I100" s="48"/>
+      <c r="A100" s="47"/>
+      <c r="B100" s="47"/>
+      <c r="C100" s="47"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="47"/>
+      <c r="I100" s="47"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -21053,14 +21043,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -21438,15 +21428,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="48"/>
-      <c r="B70" s="48"/>
-      <c r="C70" s="48"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="48"/>
-      <c r="G70" s="48"/>
-      <c r="H70" s="48"/>
-      <c r="I70" s="48"/>
+      <c r="A70" s="47"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -21471,15 +21461,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="49"/>
-      <c r="B75" s="49"/>
-      <c r="C75" s="49"/>
-      <c r="D75" s="49"/>
-      <c r="E75" s="49"/>
-      <c r="F75" s="49"/>
-      <c r="G75" s="49"/>
-      <c r="H75" s="49"/>
-      <c r="I75" s="49"/>
+      <c r="A75" s="48"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -21515,15 +21505,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="50"/>
-      <c r="B79" s="50"/>
-      <c r="C79" s="50"/>
-      <c r="D79" s="50"/>
-      <c r="E79" s="50"/>
-      <c r="F79" s="50"/>
-      <c r="G79" s="50"/>
-      <c r="H79" s="50"/>
-      <c r="I79" s="50"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -21559,15 +21549,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="49"/>
-      <c r="B87" s="49"/>
-      <c r="C87" s="49"/>
-      <c r="D87" s="49"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="49"/>
-      <c r="G87" s="49"/>
-      <c r="H87" s="49"/>
-      <c r="I87" s="49"/>
+      <c r="A87" s="48"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -21670,15 +21660,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="48"/>
-      <c r="B100" s="48"/>
-      <c r="C100" s="48"/>
-      <c r="D100" s="48"/>
-      <c r="E100" s="48"/>
-      <c r="F100" s="48"/>
-      <c r="G100" s="48"/>
-      <c r="H100" s="48"/>
-      <c r="I100" s="48"/>
+      <c r="A100" s="47"/>
+      <c r="B100" s="47"/>
+      <c r="C100" s="47"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="47"/>
+      <c r="I100" s="47"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -24381,14 +24371,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -24766,15 +24756,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="48"/>
-      <c r="B71" s="48"/>
-      <c r="C71" s="48"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="48"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -24799,15 +24789,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="49"/>
-      <c r="B76" s="49"/>
-      <c r="C76" s="49"/>
-      <c r="D76" s="49"/>
-      <c r="E76" s="49"/>
-      <c r="F76" s="49"/>
-      <c r="G76" s="49"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="49"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -24843,15 +24833,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="50"/>
-      <c r="B80" s="50"/>
-      <c r="C80" s="50"/>
-      <c r="D80" s="50"/>
-      <c r="E80" s="50"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="50"/>
-      <c r="H80" s="50"/>
-      <c r="I80" s="50"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -24887,15 +24877,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="49"/>
-      <c r="B88" s="49"/>
-      <c r="C88" s="49"/>
-      <c r="D88" s="49"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="49"/>
-      <c r="G88" s="49"/>
-      <c r="H88" s="49"/>
-      <c r="I88" s="49"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -24998,15 +24988,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="48"/>
-      <c r="B101" s="48"/>
-      <c r="C101" s="48"/>
-      <c r="D101" s="48"/>
-      <c r="E101" s="48"/>
-      <c r="F101" s="48"/>
-      <c r="G101" s="48"/>
-      <c r="H101" s="48"/>
-      <c r="I101" s="48"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -27642,14 +27632,14 @@
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="48"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="48"/>
-      <c r="I34" s="48"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="47"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
@@ -28027,15 +28017,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="48"/>
-      <c r="B69" s="48"/>
-      <c r="C69" s="48"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="48"/>
-      <c r="H69" s="48"/>
-      <c r="I69" s="48"/>
+      <c r="A69" s="47"/>
+      <c r="B69" s="47"/>
+      <c r="C69" s="47"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="47"/>
+      <c r="F69" s="47"/>
+      <c r="G69" s="47"/>
+      <c r="H69" s="47"/>
+      <c r="I69" s="47"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -28060,15 +28050,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="49"/>
-      <c r="B74" s="49"/>
-      <c r="C74" s="49"/>
-      <c r="D74" s="49"/>
-      <c r="E74" s="49"/>
-      <c r="F74" s="49"/>
-      <c r="G74" s="49"/>
-      <c r="H74" s="49"/>
-      <c r="I74" s="49"/>
+      <c r="A74" s="48"/>
+      <c r="B74" s="48"/>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -28104,15 +28094,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="50"/>
-      <c r="B78" s="50"/>
-      <c r="C78" s="50"/>
-      <c r="D78" s="50"/>
-      <c r="E78" s="50"/>
-      <c r="F78" s="50"/>
-      <c r="G78" s="50"/>
-      <c r="H78" s="50"/>
-      <c r="I78" s="50"/>
+      <c r="A78" s="49"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="49"/>
+      <c r="D78" s="49"/>
+      <c r="E78" s="49"/>
+      <c r="F78" s="49"/>
+      <c r="G78" s="49"/>
+      <c r="H78" s="49"/>
+      <c r="I78" s="49"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -28148,15 +28138,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="49"/>
-      <c r="B86" s="49"/>
-      <c r="C86" s="49"/>
-      <c r="D86" s="49"/>
-      <c r="E86" s="49"/>
-      <c r="F86" s="49"/>
-      <c r="G86" s="49"/>
-      <c r="H86" s="49"/>
-      <c r="I86" s="49"/>
+      <c r="A86" s="48"/>
+      <c r="B86" s="48"/>
+      <c r="C86" s="48"/>
+      <c r="D86" s="48"/>
+      <c r="E86" s="48"/>
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="48"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -28259,15 +28249,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="48"/>
-      <c r="B99" s="48"/>
-      <c r="C99" s="48"/>
-      <c r="D99" s="48"/>
-      <c r="E99" s="48"/>
-      <c r="F99" s="48"/>
-      <c r="G99" s="48"/>
-      <c r="H99" s="48"/>
-      <c r="I99" s="48"/>
+      <c r="A99" s="47"/>
+      <c r="B99" s="47"/>
+      <c r="C99" s="47"/>
+      <c r="D99" s="47"/>
+      <c r="E99" s="47"/>
+      <c r="F99" s="47"/>
+      <c r="G99" s="47"/>
+      <c r="H99" s="47"/>
+      <c r="I99" s="47"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -28569,7 +28559,7 @@
       <c r="G3" s="13">
         <v>0</v>
       </c>
-      <c r="H3" s="47">
+      <c r="H3" s="46">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -28616,28 +28606,28 @@
       <c r="V3" s="12">
         <v>1</v>
       </c>
-      <c r="W3" s="46">
+      <c r="W3" s="15">
         <v>9135</v>
       </c>
-      <c r="X3" s="46">
+      <c r="X3" s="15">
         <v>11194</v>
       </c>
-      <c r="Y3" s="46">
+      <c r="Y3" s="15">
         <v>9505</v>
       </c>
-      <c r="Z3" s="46">
+      <c r="Z3" s="15">
         <v>10839</v>
       </c>
-      <c r="AA3" s="46">
+      <c r="AA3" s="15">
         <v>1282</v>
       </c>
-      <c r="AB3" s="46">
+      <c r="AB3" s="15">
         <v>3934</v>
       </c>
-      <c r="AC3" s="46">
+      <c r="AC3" s="15">
         <v>396</v>
       </c>
-      <c r="AD3" s="46">
+      <c r="AD3" s="15">
         <v>3537</v>
       </c>
     </row>
@@ -28714,28 +28704,28 @@
         <f t="shared" ref="V4:V32" si="9">V3+1</f>
         <v>2</v>
       </c>
-      <c r="W4" s="46">
+      <c r="W4" s="15">
         <v>9135</v>
       </c>
-      <c r="X4" s="46">
+      <c r="X4" s="15">
         <v>11194</v>
       </c>
-      <c r="Y4" s="46">
+      <c r="Y4" s="15">
         <v>9505</v>
       </c>
-      <c r="Z4" s="46">
+      <c r="Z4" s="15">
         <v>10839</v>
       </c>
-      <c r="AA4" s="46">
+      <c r="AA4" s="15">
         <v>1282</v>
       </c>
-      <c r="AB4" s="46">
+      <c r="AB4" s="15">
         <v>3934</v>
       </c>
-      <c r="AC4" s="46">
+      <c r="AC4" s="15">
         <v>396</v>
       </c>
-      <c r="AD4" s="46">
+      <c r="AD4" s="15">
         <v>3537</v>
       </c>
     </row>
@@ -28812,28 +28802,28 @@
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="W5" s="46">
+      <c r="W5" s="15">
         <v>9135</v>
       </c>
-      <c r="X5" s="46">
+      <c r="X5" s="15">
         <v>11194</v>
       </c>
-      <c r="Y5" s="46">
+      <c r="Y5" s="15">
         <v>9505</v>
       </c>
-      <c r="Z5" s="46">
+      <c r="Z5" s="15">
         <v>10839</v>
       </c>
-      <c r="AA5" s="46">
+      <c r="AA5" s="15">
         <v>1282</v>
       </c>
-      <c r="AB5" s="46">
+      <c r="AB5" s="15">
         <v>3934</v>
       </c>
-      <c r="AC5" s="46">
+      <c r="AC5" s="15">
         <v>396</v>
       </c>
-      <c r="AD5" s="46">
+      <c r="AD5" s="15">
         <v>3537</v>
       </c>
     </row>
@@ -28948,49 +28938,49 @@
       </c>
       <c r="D7" s="13">
         <f t="shared" si="8"/>
-        <v>-9325</v>
+        <v>61</v>
       </c>
       <c r="E7" s="13">
         <v>0</v>
       </c>
       <c r="F7" s="13">
         <f t="shared" si="0"/>
-        <v>-11425</v>
+        <v>20</v>
       </c>
       <c r="G7" s="13">
         <v>0</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="1"/>
-        <v>-9531</v>
+        <v>4</v>
       </c>
       <c r="I7" s="13">
         <v>0</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="2"/>
-        <v>-10842</v>
+        <v>0</v>
       </c>
       <c r="K7" s="13">
         <v>0</v>
       </c>
       <c r="L7" s="13">
         <f t="shared" si="3"/>
-        <v>-1282</v>
+        <v>0</v>
       </c>
       <c r="M7" s="13">
         <v>0</v>
       </c>
       <c r="N7" s="13">
         <f t="shared" si="4"/>
-        <v>-3953</v>
+        <v>5</v>
       </c>
       <c r="O7" s="13">
         <v>0</v>
       </c>
       <c r="P7" s="13">
         <f t="shared" si="5"/>
-        <v>-398</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="13">
         <v>0</v>
@@ -29000,7 +28990,7 @@
       </c>
       <c r="S7" s="13">
         <f t="shared" si="6"/>
-        <v>-3553</v>
+        <v>5</v>
       </c>
       <c r="T7" s="6"/>
       <c r="U7" s="4"/>
@@ -29046,49 +29036,49 @@
       </c>
       <c r="D8" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E8" s="13">
         <v>0</v>
       </c>
       <c r="F8" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G8" s="13">
         <v>0</v>
       </c>
       <c r="H8" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I8" s="13">
         <v>0</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="13">
         <v>0</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="13">
         <v>0</v>
       </c>
       <c r="N8" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8" s="13">
         <v>0</v>
       </c>
       <c r="P8" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="13">
         <v>0</v>
@@ -29098,7 +29088,7 @@
       </c>
       <c r="S8" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" s="6"/>
       <c r="U8" s="4"/>
@@ -29106,14 +29096,30 @@
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
+      <c r="W8" s="6">
+        <v>9386</v>
+      </c>
+      <c r="X8" s="6">
+        <v>11445</v>
+      </c>
+      <c r="Y8" s="6">
+        <v>9535</v>
+      </c>
+      <c r="Z8" s="6">
+        <v>10842</v>
+      </c>
+      <c r="AA8" s="6">
+        <v>1282</v>
+      </c>
+      <c r="AB8" s="6">
+        <v>3958</v>
+      </c>
+      <c r="AC8" s="6">
+        <v>399</v>
+      </c>
+      <c r="AD8" s="6">
+        <v>3558</v>
+      </c>
     </row>
     <row r="9" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="28">
@@ -29128,14 +29134,14 @@
       </c>
       <c r="D9" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="E9" s="13">
         <v>0</v>
       </c>
       <c r="F9" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G9" s="13">
         <v>0</v>
@@ -29149,7 +29155,7 @@
       </c>
       <c r="J9" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="13">
         <v>0</v>
@@ -29163,14 +29169,14 @@
       </c>
       <c r="N9" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O9" s="13">
         <v>0</v>
       </c>
       <c r="P9" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="13">
         <v>0</v>
@@ -29180,7 +29186,7 @@
       </c>
       <c r="S9" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T9" s="6"/>
       <c r="U9" s="4"/>
@@ -29188,14 +29194,30 @@
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="6"/>
-      <c r="AB9" s="6"/>
-      <c r="AC9" s="6"/>
-      <c r="AD9" s="6"/>
+      <c r="W9" s="6">
+        <v>9405</v>
+      </c>
+      <c r="X9" s="6">
+        <v>11492</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>9541</v>
+      </c>
+      <c r="Z9" s="6">
+        <v>10843</v>
+      </c>
+      <c r="AA9" s="6">
+        <v>1283</v>
+      </c>
+      <c r="AB9" s="6">
+        <v>3961</v>
+      </c>
+      <c r="AC9" s="6">
+        <v>400</v>
+      </c>
+      <c r="AD9" s="6">
+        <v>3561</v>
+      </c>
     </row>
     <row r="10" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="28">
@@ -29210,21 +29232,21 @@
       </c>
       <c r="D10" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="E10" s="13">
         <v>0</v>
       </c>
       <c r="F10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G10" s="13">
         <v>0</v>
       </c>
       <c r="H10" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I10" s="13">
         <v>0</v>
@@ -29245,7 +29267,7 @@
       </c>
       <c r="N10" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O10" s="13">
         <v>0</v>
@@ -29270,14 +29292,30 @@
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="6"/>
-      <c r="AB10" s="6"/>
-      <c r="AC10" s="6"/>
-      <c r="AD10" s="6"/>
+      <c r="W10" s="6">
+        <v>9474</v>
+      </c>
+      <c r="X10" s="6">
+        <v>11521</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>9541</v>
+      </c>
+      <c r="Z10" s="6">
+        <v>10844</v>
+      </c>
+      <c r="AA10" s="6">
+        <v>1283</v>
+      </c>
+      <c r="AB10" s="6">
+        <v>3968</v>
+      </c>
+      <c r="AC10" s="6">
+        <v>401</v>
+      </c>
+      <c r="AD10" s="6">
+        <v>3568</v>
+      </c>
     </row>
     <row r="11" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="28">
@@ -29292,21 +29330,21 @@
       </c>
       <c r="D11" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="13">
         <v>0</v>
       </c>
       <c r="F11" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G11" s="13">
         <v>0</v>
       </c>
       <c r="H11" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I11" s="13">
         <v>0</v>
@@ -29320,14 +29358,14 @@
       </c>
       <c r="L11" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="13">
         <v>0</v>
       </c>
       <c r="N11" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O11" s="13">
         <v>0</v>
@@ -29344,7 +29382,7 @@
       </c>
       <c r="S11" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T11" s="6"/>
       <c r="U11" s="4"/>
@@ -29352,14 +29390,30 @@
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="6"/>
-      <c r="AB11" s="6"/>
-      <c r="AC11" s="6"/>
-      <c r="AD11" s="6"/>
+      <c r="W11" s="6">
+        <v>9520</v>
+      </c>
+      <c r="X11" s="6">
+        <v>11560</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>9551</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>10844</v>
+      </c>
+      <c r="AA11" s="6">
+        <v>1283</v>
+      </c>
+      <c r="AB11" s="6">
+        <v>3970</v>
+      </c>
+      <c r="AC11" s="6">
+        <v>401</v>
+      </c>
+      <c r="AD11" s="6">
+        <v>3568</v>
+      </c>
     </row>
     <row r="12" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="28">
@@ -29374,28 +29428,28 @@
       </c>
       <c r="D12" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E12" s="13">
         <v>0</v>
       </c>
       <c r="F12" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G12" s="13">
         <v>0</v>
       </c>
       <c r="H12" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I12" s="13">
         <v>0</v>
       </c>
       <c r="J12" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" s="13">
         <v>0</v>
@@ -29434,14 +29488,30 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="6"/>
-      <c r="AA12" s="6"/>
-      <c r="AB12" s="6"/>
-      <c r="AC12" s="6"/>
-      <c r="AD12" s="6"/>
+      <c r="W12" s="6">
+        <v>9523</v>
+      </c>
+      <c r="X12" s="6">
+        <v>11590</v>
+      </c>
+      <c r="Y12" s="6">
+        <v>9559</v>
+      </c>
+      <c r="Z12" s="6">
+        <v>10844</v>
+      </c>
+      <c r="AA12" s="6">
+        <v>1284</v>
+      </c>
+      <c r="AB12" s="6">
+        <v>3973</v>
+      </c>
+      <c r="AC12" s="6">
+        <v>401</v>
+      </c>
+      <c r="AD12" s="6">
+        <v>3572</v>
+      </c>
     </row>
     <row r="13" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
@@ -29456,28 +29526,28 @@
       </c>
       <c r="D13" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E13" s="13">
         <v>0</v>
       </c>
       <c r="F13" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G13" s="13">
         <v>0</v>
       </c>
       <c r="H13" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I13" s="13">
         <v>0</v>
       </c>
       <c r="J13" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="13">
         <v>0</v>
@@ -29491,14 +29561,14 @@
       </c>
       <c r="N13" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O13" s="13">
         <v>0</v>
       </c>
       <c r="P13" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="13">
         <v>0</v>
@@ -29508,7 +29578,7 @@
       </c>
       <c r="S13" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T13" s="6"/>
       <c r="U13" s="4"/>
@@ -29516,14 +29586,30 @@
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
-      <c r="W13" s="15"/>
-      <c r="X13" s="15"/>
-      <c r="Y13" s="15"/>
-      <c r="Z13" s="15"/>
-      <c r="AA13" s="15"/>
-      <c r="AB13" s="15"/>
-      <c r="AC13" s="15"/>
-      <c r="AD13" s="15"/>
+      <c r="W13" s="15">
+        <v>9536</v>
+      </c>
+      <c r="X13" s="15">
+        <v>11641</v>
+      </c>
+      <c r="Y13" s="15">
+        <v>9563</v>
+      </c>
+      <c r="Z13" s="15">
+        <v>10846</v>
+      </c>
+      <c r="AA13" s="15">
+        <v>1284</v>
+      </c>
+      <c r="AB13" s="15">
+        <v>3973</v>
+      </c>
+      <c r="AC13" s="15">
+        <v>401</v>
+      </c>
+      <c r="AD13" s="15">
+        <v>3572</v>
+      </c>
     </row>
     <row r="14" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="28">
@@ -29538,21 +29624,21 @@
       </c>
       <c r="D14" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E14" s="13">
         <v>0</v>
       </c>
       <c r="F14" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G14" s="13">
         <v>0</v>
       </c>
       <c r="H14" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14" s="13">
         <v>0</v>
@@ -29566,14 +29652,14 @@
       </c>
       <c r="L14" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="13">
         <v>0</v>
       </c>
       <c r="N14" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O14" s="13">
         <v>0</v>
@@ -29598,14 +29684,30 @@
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="6"/>
-      <c r="AB14" s="6"/>
-      <c r="AC14" s="6"/>
-      <c r="AD14" s="6"/>
+      <c r="W14" s="6">
+        <v>9578</v>
+      </c>
+      <c r="X14" s="6">
+        <v>11677</v>
+      </c>
+      <c r="Y14" s="6">
+        <v>9569</v>
+      </c>
+      <c r="Z14" s="6">
+        <v>10847</v>
+      </c>
+      <c r="AA14" s="6">
+        <v>1284</v>
+      </c>
+      <c r="AB14" s="6">
+        <v>3980</v>
+      </c>
+      <c r="AC14" s="6">
+        <v>402</v>
+      </c>
+      <c r="AD14" s="6">
+        <v>3581</v>
+      </c>
     </row>
     <row r="15" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="28">
@@ -29620,21 +29722,21 @@
       </c>
       <c r="D15" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E15" s="13">
         <v>0</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G15" s="13">
         <v>0</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" s="13">
         <v>0</v>
@@ -29654,14 +29756,14 @@
       </c>
       <c r="N15" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O15" s="13">
         <v>0</v>
       </c>
       <c r="P15" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="13">
         <v>0</v>
@@ -29671,7 +29773,7 @@
       </c>
       <c r="S15" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T15" s="6"/>
       <c r="U15" s="4"/>
@@ -29679,14 +29781,30 @@
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="6"/>
-      <c r="AB15" s="6"/>
-      <c r="AC15" s="6"/>
-      <c r="AD15" s="6"/>
+      <c r="W15" s="6">
+        <v>9585</v>
+      </c>
+      <c r="X15" s="6">
+        <v>11693</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>9572</v>
+      </c>
+      <c r="Z15" s="6">
+        <v>10847</v>
+      </c>
+      <c r="AA15" s="6">
+        <v>1285</v>
+      </c>
+      <c r="AB15" s="6">
+        <v>3984</v>
+      </c>
+      <c r="AC15" s="6">
+        <v>402</v>
+      </c>
+      <c r="AD15" s="6">
+        <v>3581</v>
+      </c>
     </row>
     <row r="16" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="28">
@@ -29701,28 +29819,28 @@
       </c>
       <c r="D16" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="E16" s="13">
         <v>0</v>
       </c>
       <c r="F16" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G16" s="13">
         <v>0</v>
       </c>
       <c r="H16" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I16" s="13">
         <v>0</v>
       </c>
       <c r="J16" s="13">
         <f t="shared" ref="J16:J32" si="10">Z17-Z16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="13">
         <v>0</v>
@@ -29736,14 +29854,14 @@
       </c>
       <c r="N16" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O16" s="13">
         <v>0</v>
       </c>
       <c r="P16" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="13">
         <v>0</v>
@@ -29753,7 +29871,7 @@
       </c>
       <c r="S16" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="4"/>
@@ -29761,14 +29879,30 @@
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="16"/>
-      <c r="Z16" s="16"/>
-      <c r="AA16" s="16"/>
-      <c r="AB16" s="16"/>
-      <c r="AC16" s="16"/>
-      <c r="AD16" s="16"/>
+      <c r="W16" s="16">
+        <v>9675</v>
+      </c>
+      <c r="X16" s="16">
+        <v>11788</v>
+      </c>
+      <c r="Y16" s="16">
+        <v>9574</v>
+      </c>
+      <c r="Z16" s="16">
+        <v>10847</v>
+      </c>
+      <c r="AA16" s="16">
+        <v>1285</v>
+      </c>
+      <c r="AB16" s="16">
+        <v>3988</v>
+      </c>
+      <c r="AC16" s="16">
+        <v>403</v>
+      </c>
+      <c r="AD16" s="16">
+        <v>3585</v>
+      </c>
     </row>
     <row r="17" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="28">
@@ -29783,49 +29917,49 @@
       </c>
       <c r="D17" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-9728</v>
       </c>
       <c r="E17" s="13">
         <v>0</v>
       </c>
       <c r="F17" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-11852</v>
       </c>
       <c r="G17" s="13">
         <v>0</v>
       </c>
       <c r="H17" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-9583</v>
       </c>
       <c r="I17" s="13">
         <v>0</v>
       </c>
       <c r="J17" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-10848</v>
       </c>
       <c r="K17" s="13">
         <v>0</v>
       </c>
       <c r="L17" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1285</v>
       </c>
       <c r="M17" s="13">
         <v>0</v>
       </c>
       <c r="N17" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-3993</v>
       </c>
       <c r="O17" s="13">
         <v>0</v>
       </c>
       <c r="P17" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-404</v>
       </c>
       <c r="Q17" s="13">
         <v>0</v>
@@ -29835,7 +29969,7 @@
       </c>
       <c r="S17" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-3589</v>
       </c>
       <c r="T17" s="6"/>
       <c r="U17" s="4"/>
@@ -29843,14 +29977,30 @@
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="16"/>
-      <c r="AB17" s="16"/>
-      <c r="AC17" s="16"/>
-      <c r="AD17" s="16"/>
+      <c r="W17" s="16">
+        <v>9728</v>
+      </c>
+      <c r="X17" s="16">
+        <v>11852</v>
+      </c>
+      <c r="Y17" s="16">
+        <v>9583</v>
+      </c>
+      <c r="Z17" s="16">
+        <v>10848</v>
+      </c>
+      <c r="AA17" s="16">
+        <v>1285</v>
+      </c>
+      <c r="AB17" s="16">
+        <v>3993</v>
+      </c>
+      <c r="AC17" s="16">
+        <v>404</v>
+      </c>
+      <c r="AD17" s="16">
+        <v>3589</v>
+      </c>
     </row>
     <row r="18" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="28">
@@ -29865,49 +30015,49 @@
       </c>
       <c r="D18" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9771</v>
       </c>
       <c r="E18" s="13">
         <v>0</v>
       </c>
       <c r="F18" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11971</v>
       </c>
       <c r="G18" s="13">
         <v>0</v>
       </c>
       <c r="H18" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9587</v>
       </c>
       <c r="I18" s="13">
         <v>0</v>
       </c>
       <c r="J18" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>10850</v>
       </c>
       <c r="K18" s="13">
         <v>0</v>
       </c>
       <c r="L18" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1285</v>
       </c>
       <c r="M18" s="13">
         <v>0</v>
       </c>
       <c r="N18" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4001</v>
       </c>
       <c r="O18" s="13">
         <v>0</v>
       </c>
       <c r="P18" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="Q18" s="13">
         <v>0</v>
@@ -29917,7 +30067,7 @@
       </c>
       <c r="S18" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3596</v>
       </c>
       <c r="T18" s="6"/>
       <c r="U18" s="4"/>
@@ -29947,28 +30097,28 @@
       </c>
       <c r="D19" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E19" s="13">
         <v>0</v>
       </c>
       <c r="F19" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G19" s="13">
         <v>0</v>
       </c>
       <c r="H19" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" s="13">
         <v>0</v>
       </c>
       <c r="J19" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="13">
         <v>0</v>
@@ -29982,7 +30132,7 @@
       </c>
       <c r="N19" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O19" s="13">
         <v>0</v>
@@ -29999,7 +30149,7 @@
       </c>
       <c r="S19" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T19" s="6"/>
       <c r="U19" s="17"/>
@@ -30007,14 +30157,30 @@
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19"/>
-      <c r="Y19" s="19"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="19"/>
-      <c r="AB19" s="19"/>
-      <c r="AC19" s="19"/>
-      <c r="AD19" s="19"/>
+      <c r="W19" s="19">
+        <v>9771</v>
+      </c>
+      <c r="X19" s="19">
+        <v>11971</v>
+      </c>
+      <c r="Y19" s="19">
+        <v>9587</v>
+      </c>
+      <c r="Z19" s="19">
+        <v>10850</v>
+      </c>
+      <c r="AA19" s="19">
+        <v>1285</v>
+      </c>
+      <c r="AB19" s="19">
+        <v>4001</v>
+      </c>
+      <c r="AC19" s="19">
+        <v>404</v>
+      </c>
+      <c r="AD19" s="19">
+        <v>3596</v>
+      </c>
     </row>
     <row r="20" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="28">
@@ -30029,49 +30195,49 @@
       </c>
       <c r="D20" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-9782</v>
       </c>
       <c r="E20" s="13">
         <v>0</v>
       </c>
       <c r="F20" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-12030</v>
       </c>
       <c r="G20" s="13">
         <v>0</v>
       </c>
       <c r="H20" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-9590</v>
       </c>
       <c r="I20" s="13">
         <v>0</v>
       </c>
       <c r="J20" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>-10851</v>
       </c>
       <c r="K20" s="13">
         <v>0</v>
       </c>
       <c r="L20" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-1285</v>
       </c>
       <c r="M20" s="13">
         <v>0</v>
       </c>
       <c r="N20" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-4005</v>
       </c>
       <c r="O20" s="13">
         <v>0</v>
       </c>
       <c r="P20" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-404</v>
       </c>
       <c r="Q20" s="13">
         <v>0</v>
@@ -30081,7 +30247,7 @@
       </c>
       <c r="S20" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-3600</v>
       </c>
       <c r="T20" s="6"/>
       <c r="U20" s="4"/>
@@ -30089,14 +30255,30 @@
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
-      <c r="Y20" s="15"/>
-      <c r="Z20" s="15"/>
-      <c r="AA20" s="15"/>
-      <c r="AB20" s="15"/>
-      <c r="AC20" s="15"/>
-      <c r="AD20" s="15"/>
+      <c r="W20" s="15">
+        <v>9782</v>
+      </c>
+      <c r="X20" s="15">
+        <v>12030</v>
+      </c>
+      <c r="Y20" s="15">
+        <v>9590</v>
+      </c>
+      <c r="Z20" s="15">
+        <v>10851</v>
+      </c>
+      <c r="AA20" s="15">
+        <v>1285</v>
+      </c>
+      <c r="AB20" s="15">
+        <v>4005</v>
+      </c>
+      <c r="AC20" s="15">
+        <v>404</v>
+      </c>
+      <c r="AD20" s="15">
+        <v>3600</v>
+      </c>
     </row>
     <row r="21" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="28">
@@ -31095,14 +31277,14 @@
     </row>
     <row r="35" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="48"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -31480,15 +31662,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="48"/>
-      <c r="B70" s="48"/>
-      <c r="C70" s="48"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="48"/>
-      <c r="G70" s="48"/>
-      <c r="H70" s="48"/>
-      <c r="I70" s="48"/>
+      <c r="A70" s="47"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -31513,15 +31695,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="49"/>
-      <c r="B75" s="49"/>
-      <c r="C75" s="49"/>
-      <c r="D75" s="49"/>
-      <c r="E75" s="49"/>
-      <c r="F75" s="49"/>
-      <c r="G75" s="49"/>
-      <c r="H75" s="49"/>
-      <c r="I75" s="49"/>
+      <c r="A75" s="48"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -31557,15 +31739,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="50"/>
-      <c r="B79" s="50"/>
-      <c r="C79" s="50"/>
-      <c r="D79" s="50"/>
-      <c r="E79" s="50"/>
-      <c r="F79" s="50"/>
-      <c r="G79" s="50"/>
-      <c r="H79" s="50"/>
-      <c r="I79" s="50"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -31601,15 +31783,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="49"/>
-      <c r="B87" s="49"/>
-      <c r="C87" s="49"/>
-      <c r="D87" s="49"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="49"/>
-      <c r="G87" s="49"/>
-      <c r="H87" s="49"/>
-      <c r="I87" s="49"/>
+      <c r="A87" s="48"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -31712,15 +31894,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="48"/>
-      <c r="B100" s="48"/>
-      <c r="C100" s="48"/>
-      <c r="D100" s="48"/>
-      <c r="E100" s="48"/>
-      <c r="F100" s="48"/>
-      <c r="G100" s="48"/>
-      <c r="H100" s="48"/>
-      <c r="I100" s="48"/>
+      <c r="A100" s="47"/>
+      <c r="B100" s="47"/>
+      <c r="C100" s="47"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="47"/>
+      <c r="I100" s="47"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -31795,7 +31977,7 @@
     <col min="7" max="7" width="13.42578125" customWidth="1"/>
     <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="12" max="12" width="7" customWidth="1"/>
+    <col min="12" max="12" width="13.140625" customWidth="1"/>
     <col min="20" max="20" width="47.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -31934,11 +32116,10 @@
         <v>0</v>
       </c>
       <c r="L2" s="13">
-        <f t="shared" ref="L2:L32" si="3">AA3-AA2</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M2" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N2" s="29">
         <v>273.19199933999994</v>
@@ -31947,7 +32128,7 @@
         <v>58.631999890000003</v>
       </c>
       <c r="P2" s="13">
-        <f t="shared" ref="P2:P32" si="4">AC3-AC2</f>
+        <f t="shared" ref="P2:P32" si="3">AC3-AC2</f>
         <v>0</v>
       </c>
       <c r="Q2" s="13">
@@ -31957,7 +32138,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="13">
-        <f t="shared" ref="S2:S32" si="5">AD3-AD2</f>
+        <f t="shared" ref="S2:S32" si="4">AD3-AD2</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -32001,7 +32182,7 @@
     </row>
     <row r="3" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="28">
-        <f t="shared" ref="A3:A32" si="6">A2+1</f>
+        <f t="shared" ref="A3:A32" si="5">A2+1</f>
         <v>45840</v>
       </c>
       <c r="B3" s="29">
@@ -32011,7 +32192,7 @@
         <v>194.16599989000002</v>
       </c>
       <c r="D3" s="13">
-        <f t="shared" ref="D3:D32" si="7">W4-W3</f>
+        <f t="shared" ref="D3:D32" si="6">W4-W3</f>
         <v>126</v>
       </c>
       <c r="E3" s="13">
@@ -32039,30 +32220,29 @@
         <v>0</v>
       </c>
       <c r="L3" s="13">
+        <v>29</v>
+      </c>
+      <c r="M3" s="13">
+        <v>10</v>
+      </c>
+      <c r="N3" s="29">
+        <v>244.2479993499999</v>
+      </c>
+      <c r="O3" s="29">
+        <v>53.351999930000005</v>
+      </c>
+      <c r="P3" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="M3" s="13">
-        <v>0</v>
-      </c>
-      <c r="N3" s="29">
-        <v>244.2479993499999</v>
-      </c>
-      <c r="O3" s="29">
-        <v>53.351999930000005</v>
-      </c>
-      <c r="P3" s="13">
+      <c r="Q3" s="13">
+        <v>0</v>
+      </c>
+      <c r="R3" s="13">
+        <v>0</v>
+      </c>
+      <c r="S3" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q3" s="13">
-        <v>0</v>
-      </c>
-      <c r="R3" s="13">
-        <v>0</v>
-      </c>
-      <c r="S3" s="13">
-        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -32099,7 +32279,7 @@
     </row>
     <row r="4" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A4" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45841</v>
       </c>
       <c r="B4" s="29">
@@ -32109,7 +32289,7 @@
         <v>188.95799991000001</v>
       </c>
       <c r="D4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E4" s="13">
@@ -32137,11 +32317,10 @@
         <v>0</v>
       </c>
       <c r="L4" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M4" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N4" s="29">
         <v>238.70399939999993</v>
@@ -32150,17 +32329,17 @@
         <v>47.591999919999992</v>
       </c>
       <c r="P4" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>0</v>
+      </c>
+      <c r="R4" s="13">
+        <v>0</v>
+      </c>
+      <c r="S4" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>0</v>
-      </c>
-      <c r="R4" s="13">
-        <v>0</v>
-      </c>
-      <c r="S4" s="13">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -32168,7 +32347,7 @@
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="14">
-        <f t="shared" ref="V4:V33" si="8">V3+1</f>
+        <f t="shared" ref="V4:V33" si="7">V3+1</f>
         <v>2</v>
       </c>
       <c r="W4" s="6">
@@ -32198,7 +32377,7 @@
     </row>
     <row r="5" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45842</v>
       </c>
       <c r="B5" s="29">
@@ -32208,7 +32387,7 @@
         <v>146.36999994000001</v>
       </c>
       <c r="D5" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>132</v>
       </c>
       <c r="E5" s="13">
@@ -32236,11 +32415,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M5" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N5" s="29">
         <v>261.69599937999982</v>
@@ -32249,17 +32427,17 @@
         <v>46.919999890000007</v>
       </c>
       <c r="P5" s="13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>0</v>
+      </c>
+      <c r="R5" s="13">
+        <v>0</v>
+      </c>
+      <c r="S5" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>0</v>
-      </c>
-      <c r="R5" s="13">
-        <v>0</v>
-      </c>
-      <c r="S5" s="13">
-        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -32267,7 +32445,7 @@
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="W5" s="6">
@@ -32297,7 +32475,7 @@
     </row>
     <row r="6" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45843</v>
       </c>
       <c r="B6" s="29">
@@ -32307,7 +32485,7 @@
         <v>149.56199989999999</v>
       </c>
       <c r="D6" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>56</v>
       </c>
       <c r="E6" s="13">
@@ -32335,11 +32513,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M6" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N6" s="29">
         <v>243.26399940999994</v>
@@ -32348,17 +32525,17 @@
         <v>57.911999910000006</v>
       </c>
       <c r="P6" s="13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>0</v>
+      </c>
+      <c r="R6" s="13">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>0</v>
-      </c>
-      <c r="R6" s="13">
-        <v>0</v>
-      </c>
-      <c r="S6" s="13">
-        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -32366,7 +32543,7 @@
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="W6" s="6">
@@ -32396,7 +32573,7 @@
     </row>
     <row r="7" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45844</v>
       </c>
       <c r="B7" s="29">
@@ -32406,7 +32583,7 @@
         <v>156.28199990000002</v>
       </c>
       <c r="D7" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="E7" s="13">
@@ -32434,11 +32611,10 @@
         <v>0</v>
       </c>
       <c r="L7" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M7" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N7" s="29">
         <v>255.88799939000006</v>
@@ -32447,17 +32623,17 @@
         <v>61.943999909999995</v>
       </c>
       <c r="P7" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>0</v>
+      </c>
+      <c r="R7" s="13">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>0</v>
-      </c>
-      <c r="R7" s="13">
-        <v>0</v>
-      </c>
-      <c r="S7" s="13">
-        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -32465,7 +32641,7 @@
       </c>
       <c r="U7" s="4"/>
       <c r="V7" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="W7" s="6">
@@ -32495,7 +32671,7 @@
     </row>
     <row r="8" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45845</v>
       </c>
       <c r="B8" s="29">
@@ -32505,7 +32681,7 @@
         <v>192.14999990999999</v>
       </c>
       <c r="D8" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E8" s="13">
@@ -32533,11 +32709,10 @@
         <v>0</v>
       </c>
       <c r="L8" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M8" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N8" s="29">
         <v>237.64799939999963</v>
@@ -32546,17 +32721,17 @@
         <v>63.479999890000009</v>
       </c>
       <c r="P8" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>0</v>
+      </c>
+      <c r="R8" s="13">
+        <v>0</v>
+      </c>
+      <c r="S8" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>0</v>
-      </c>
-      <c r="R8" s="13">
-        <v>0</v>
-      </c>
-      <c r="S8" s="13">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -32564,7 +32739,7 @@
       </c>
       <c r="U8" s="4"/>
       <c r="V8" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="W8" s="6">
@@ -32594,7 +32769,7 @@
     </row>
     <row r="9" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45846</v>
       </c>
       <c r="B9" s="29">
@@ -32604,7 +32779,7 @@
         <v>183.20399994000005</v>
       </c>
       <c r="D9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>69</v>
       </c>
       <c r="E9" s="13">
@@ -32632,11 +32807,10 @@
         <v>0</v>
       </c>
       <c r="L9" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M9" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N9" s="29">
         <v>233.6159993399998</v>
@@ -32645,17 +32819,17 @@
         <v>49.703999919999994</v>
       </c>
       <c r="P9" s="13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>0</v>
+      </c>
+      <c r="R9" s="13">
+        <v>0</v>
+      </c>
+      <c r="S9" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>0</v>
-      </c>
-      <c r="R9" s="13">
-        <v>0</v>
-      </c>
-      <c r="S9" s="13">
-        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -32663,7 +32837,7 @@
       </c>
       <c r="U9" s="4"/>
       <c r="V9" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="W9" s="6">
@@ -32693,7 +32867,7 @@
     </row>
     <row r="10" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45847</v>
       </c>
       <c r="B10" s="29">
@@ -32703,7 +32877,7 @@
         <v>190.30199987999998</v>
       </c>
       <c r="D10" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>65</v>
       </c>
       <c r="E10" s="13">
@@ -32731,11 +32905,10 @@
         <v>0</v>
       </c>
       <c r="L10" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M10" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N10" s="29">
         <v>221.99999943999987</v>
@@ -32744,17 +32917,17 @@
         <v>63.287999890000002</v>
       </c>
       <c r="P10" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>0</v>
+      </c>
+      <c r="R10" s="13">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>0</v>
-      </c>
-      <c r="R10" s="13">
-        <v>0</v>
-      </c>
-      <c r="S10" s="13">
-        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="T10" s="6" t="s">
@@ -32762,7 +32935,7 @@
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="W10" s="6">
@@ -32792,7 +32965,7 @@
     </row>
     <row r="11" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45848</v>
       </c>
       <c r="B11" s="29">
@@ -32802,7 +32975,7 @@
         <v>177.15599992000003</v>
       </c>
       <c r="D11" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>45</v>
       </c>
       <c r="E11" s="13">
@@ -32830,30 +33003,29 @@
         <v>0</v>
       </c>
       <c r="L11" s="13">
+        <v>29</v>
+      </c>
+      <c r="M11" s="13">
+        <v>10</v>
+      </c>
+      <c r="N11" s="29">
+        <v>239.39999935999995</v>
+      </c>
+      <c r="O11" s="29">
+        <v>48.239999900000008</v>
+      </c>
+      <c r="P11" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="M11" s="13">
-        <v>0</v>
-      </c>
-      <c r="N11" s="29">
-        <v>239.39999935999995</v>
-      </c>
-      <c r="O11" s="29">
-        <v>48.239999900000008</v>
-      </c>
-      <c r="P11" s="13">
+      <c r="Q11" s="13">
+        <v>0</v>
+      </c>
+      <c r="R11" s="13">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>0</v>
-      </c>
-      <c r="R11" s="13">
-        <v>0</v>
-      </c>
-      <c r="S11" s="13">
-        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="T11" s="6" t="s">
@@ -32861,7 +33033,7 @@
       </c>
       <c r="U11" s="4"/>
       <c r="V11" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="W11" s="6">
@@ -32891,7 +33063,7 @@
     </row>
     <row r="12" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45849</v>
       </c>
       <c r="B12" s="29">
@@ -32901,7 +33073,7 @@
         <v>145.10999994000002</v>
       </c>
       <c r="D12" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E12" s="13">
@@ -32929,11 +33101,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M12" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N12" s="29">
         <v>272.44799940999985</v>
@@ -32942,17 +33113,17 @@
         <v>54.503999889999996</v>
       </c>
       <c r="P12" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>0</v>
+      </c>
+      <c r="R12" s="13">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>0</v>
-      </c>
-      <c r="R12" s="13">
-        <v>0</v>
-      </c>
-      <c r="S12" s="13">
-        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="T12" s="6" t="s">
@@ -32960,7 +33131,7 @@
       </c>
       <c r="U12" s="4"/>
       <c r="V12" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="W12" s="6">
@@ -32990,7 +33161,7 @@
     </row>
     <row r="13" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45850</v>
       </c>
       <c r="B13" s="29">
@@ -33000,7 +33171,7 @@
         <v>138.13799994999999</v>
       </c>
       <c r="D13" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E13" s="13">
@@ -33028,11 +33199,10 @@
         <v>0</v>
       </c>
       <c r="L13" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M13" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N13" s="29">
         <v>273.93599928999976</v>
@@ -33041,17 +33211,17 @@
         <v>50.255999900000006</v>
       </c>
       <c r="P13" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="13">
+        <v>0</v>
+      </c>
+      <c r="R13" s="13">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>0</v>
-      </c>
-      <c r="R13" s="13">
-        <v>0</v>
-      </c>
-      <c r="S13" s="13">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -33059,7 +33229,7 @@
       </c>
       <c r="U13" s="4"/>
       <c r="V13" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="W13" s="15">
@@ -33089,7 +33259,7 @@
     </row>
     <row r="14" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45851</v>
       </c>
       <c r="B14" s="29">
@@ -33099,7 +33269,7 @@
         <v>164.00999991999998</v>
       </c>
       <c r="D14" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>109</v>
       </c>
       <c r="E14" s="13">
@@ -33127,11 +33297,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M14" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N14" s="29">
         <v>266.95199932999975</v>
@@ -33140,17 +33309,17 @@
         <v>59.44799991</v>
       </c>
       <c r="P14" s="13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="13">
+        <v>0</v>
+      </c>
+      <c r="R14" s="13">
+        <v>0</v>
+      </c>
+      <c r="S14" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>0</v>
-      </c>
-      <c r="R14" s="13">
-        <v>0</v>
-      </c>
-      <c r="S14" s="13">
-        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="T14" s="6" t="s">
@@ -33158,7 +33327,7 @@
       </c>
       <c r="U14" s="4"/>
       <c r="V14" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="W14" s="15">
@@ -33188,7 +33357,7 @@
     </row>
     <row r="15" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45852</v>
       </c>
       <c r="B15" s="29">
@@ -33198,7 +33367,7 @@
         <v>183.37199992999999</v>
       </c>
       <c r="D15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E15" s="13">
@@ -33225,11 +33394,10 @@
         <v>0</v>
       </c>
       <c r="L15" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M15" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N15" s="29">
         <v>237.09599936999976</v>
@@ -33238,17 +33406,17 @@
         <v>57.767999929999995</v>
       </c>
       <c r="P15" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13">
+        <v>0</v>
+      </c>
+      <c r="R15" s="13">
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>0</v>
-      </c>
-      <c r="R15" s="13">
-        <v>0</v>
-      </c>
-      <c r="S15" s="13">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T15" s="6" t="s">
@@ -33256,7 +33424,7 @@
       </c>
       <c r="U15" s="4"/>
       <c r="V15" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="W15" s="6">
@@ -33286,7 +33454,7 @@
     </row>
     <row r="16" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45853</v>
       </c>
       <c r="B16" s="29">
@@ -33296,7 +33464,7 @@
         <v>175.81199992000001</v>
       </c>
       <c r="D16" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="E16" s="13">
@@ -33317,37 +33485,36 @@
         <v>0</v>
       </c>
       <c r="J16" s="13">
-        <f t="shared" ref="J16:J32" si="9">Z17-Z16</f>
+        <f t="shared" ref="J16:J32" si="8">Z17-Z16</f>
         <v>0</v>
       </c>
       <c r="K16" s="13">
         <v>0</v>
       </c>
       <c r="L16" s="13">
+        <v>29</v>
+      </c>
+      <c r="M16" s="13">
+        <v>10</v>
+      </c>
+      <c r="N16" s="29">
+        <v>251.08799935999988</v>
+      </c>
+      <c r="O16" s="29">
+        <v>57.599999870000005</v>
+      </c>
+      <c r="P16" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="M16" s="13">
-        <v>0</v>
-      </c>
-      <c r="N16" s="29">
-        <v>251.08799935999988</v>
-      </c>
-      <c r="O16" s="29">
-        <v>57.599999870000005</v>
-      </c>
-      <c r="P16" s="13">
+      <c r="Q16" s="13">
+        <v>0</v>
+      </c>
+      <c r="R16" s="13">
+        <v>0</v>
+      </c>
+      <c r="S16" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q16" s="13">
-        <v>0</v>
-      </c>
-      <c r="R16" s="13">
-        <v>0</v>
-      </c>
-      <c r="S16" s="13">
-        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="T16" s="6" t="s">
@@ -33355,7 +33522,7 @@
       </c>
       <c r="U16" s="4"/>
       <c r="V16" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="W16" s="6">
@@ -33385,7 +33552,7 @@
     </row>
     <row r="17" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45854</v>
       </c>
       <c r="B17" s="29">
@@ -33395,7 +33562,7 @@
         <v>201.51599995000004</v>
       </c>
       <c r="D17" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E17" s="13">
@@ -33416,18 +33583,17 @@
         <v>0</v>
       </c>
       <c r="J17" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K17" s="13">
         <v>0</v>
       </c>
       <c r="L17" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M17" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N17" s="29">
         <v>249.23999939999999</v>
@@ -33436,17 +33602,17 @@
         <v>48.911999910000006</v>
       </c>
       <c r="P17" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="13">
+        <v>0</v>
+      </c>
+      <c r="R17" s="13">
+        <v>0</v>
+      </c>
+      <c r="S17" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="13">
-        <v>0</v>
-      </c>
-      <c r="R17" s="13">
-        <v>0</v>
-      </c>
-      <c r="S17" s="13">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T17" s="6" t="s">
@@ -33454,7 +33620,7 @@
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="W17" s="16">
@@ -33484,7 +33650,7 @@
     </row>
     <row r="18" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45855</v>
       </c>
       <c r="B18" s="29">
@@ -33494,7 +33660,7 @@
         <v>221.17199995000004</v>
       </c>
       <c r="D18" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>106</v>
       </c>
       <c r="E18" s="13">
@@ -33515,18 +33681,17 @@
         <v>0</v>
       </c>
       <c r="J18" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K18" s="13">
         <v>0</v>
       </c>
       <c r="L18" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M18" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N18" s="29">
         <v>241.43999937000009</v>
@@ -33535,17 +33700,17 @@
         <v>49.607999879999994</v>
       </c>
       <c r="P18" s="13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="Q18" s="13">
+        <v>0</v>
+      </c>
+      <c r="R18" s="13">
+        <v>0</v>
+      </c>
+      <c r="S18" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>0</v>
-      </c>
-      <c r="R18" s="13">
-        <v>0</v>
-      </c>
-      <c r="S18" s="13">
-        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="T18" s="6" t="s">
@@ -33553,7 +33718,7 @@
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="W18" s="16">
@@ -33583,7 +33748,7 @@
     </row>
     <row r="19" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45856</v>
       </c>
       <c r="B19" s="29">
@@ -33593,7 +33758,7 @@
         <v>155.48399988999995</v>
       </c>
       <c r="D19" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>63</v>
       </c>
       <c r="E19" s="13">
@@ -33614,18 +33779,17 @@
         <v>0</v>
       </c>
       <c r="J19" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="K19" s="13">
         <v>0</v>
       </c>
       <c r="L19" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M19" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N19" s="29">
         <v>232.10399942999979</v>
@@ -33634,17 +33798,17 @@
         <v>43.3439999</v>
       </c>
       <c r="P19" s="13">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="Q19" s="13">
+        <v>0</v>
+      </c>
+      <c r="R19" s="13">
+        <v>0</v>
+      </c>
+      <c r="S19" s="13">
         <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="Q19" s="13">
-        <v>0</v>
-      </c>
-      <c r="R19" s="13">
-        <v>0</v>
-      </c>
-      <c r="S19" s="13">
-        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="T19" s="6" t="s">
@@ -33652,7 +33816,7 @@
       </c>
       <c r="U19" s="17"/>
       <c r="V19" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="W19" s="19">
@@ -33682,7 +33846,7 @@
     </row>
     <row r="20" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45857</v>
       </c>
       <c r="B20" s="29">
@@ -33692,7 +33856,7 @@
         <v>204.45599989000002</v>
       </c>
       <c r="D20" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="E20" s="13">
@@ -33713,18 +33877,17 @@
         <v>0</v>
       </c>
       <c r="J20" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K20" s="13">
         <v>0</v>
       </c>
       <c r="L20" s="13">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M20" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N20" s="29">
         <v>274.1519993600001</v>
@@ -33733,17 +33896,17 @@
         <v>53.015999870000009</v>
       </c>
       <c r="P20" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="13">
+        <v>0</v>
+      </c>
+      <c r="R20" s="13">
+        <v>0</v>
+      </c>
+      <c r="S20" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="13">
-        <v>0</v>
-      </c>
-      <c r="R20" s="13">
-        <v>0</v>
-      </c>
-      <c r="S20" s="13">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -33751,7 +33914,7 @@
       </c>
       <c r="U20" s="4"/>
       <c r="V20" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="W20" s="15">
@@ -33781,7 +33944,7 @@
     </row>
     <row r="21" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45858</v>
       </c>
       <c r="B21" s="29">
@@ -33791,7 +33954,7 @@
         <v>176.69399991</v>
       </c>
       <c r="D21" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>65</v>
       </c>
       <c r="E21" s="13">
@@ -33812,18 +33975,17 @@
         <v>0</v>
       </c>
       <c r="J21" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K21" s="13">
         <v>0</v>
       </c>
       <c r="L21" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M21" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N21" s="29">
         <v>255.64799941999971</v>
@@ -33832,17 +33994,17 @@
         <v>49.031999899999995</v>
       </c>
       <c r="P21" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="13">
+        <v>0</v>
+      </c>
+      <c r="R21" s="13">
+        <v>0</v>
+      </c>
+      <c r="S21" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="13">
-        <v>0</v>
-      </c>
-      <c r="R21" s="13">
-        <v>0</v>
-      </c>
-      <c r="S21" s="13">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -33850,7 +34012,7 @@
       </c>
       <c r="U21" s="4"/>
       <c r="V21" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="W21" s="15">
@@ -33880,7 +34042,7 @@
     </row>
     <row r="22" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45859</v>
       </c>
       <c r="B22" s="29">
@@ -33890,7 +34052,7 @@
         <v>191.64599992999999</v>
       </c>
       <c r="D22" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>49</v>
       </c>
       <c r="E22" s="13">
@@ -33911,18 +34073,17 @@
         <v>0</v>
       </c>
       <c r="J22" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K22" s="13">
         <v>0</v>
       </c>
       <c r="L22" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M22" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N22" s="29">
         <v>264.26399941999972</v>
@@ -33931,17 +34092,17 @@
         <v>59.85599989</v>
       </c>
       <c r="P22" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>0</v>
+      </c>
+      <c r="R22" s="13">
+        <v>0</v>
+      </c>
+      <c r="S22" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>0</v>
-      </c>
-      <c r="R22" s="13">
-        <v>0</v>
-      </c>
-      <c r="S22" s="13">
-        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="T22" s="6" t="s">
@@ -33949,7 +34110,7 @@
       </c>
       <c r="U22" s="4"/>
       <c r="V22" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="W22" s="15">
@@ -33979,7 +34140,7 @@
     </row>
     <row r="23" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45860</v>
       </c>
       <c r="B23" s="29">
@@ -33989,7 +34150,7 @@
         <v>213.06599991999997</v>
       </c>
       <c r="D23" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E23" s="13">
@@ -34010,18 +34171,17 @@
         <v>0</v>
       </c>
       <c r="J23" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K23" s="13">
         <v>0</v>
       </c>
       <c r="L23" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M23" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N23" s="29">
         <v>280.87199934999984</v>
@@ -34030,17 +34190,17 @@
         <v>56.519999890000001</v>
       </c>
       <c r="P23" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="13">
+        <v>0</v>
+      </c>
+      <c r="R23" s="13">
+        <v>0</v>
+      </c>
+      <c r="S23" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="13">
-        <v>0</v>
-      </c>
-      <c r="R23" s="13">
-        <v>0</v>
-      </c>
-      <c r="S23" s="13">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
@@ -34048,7 +34208,7 @@
       </c>
       <c r="U23" s="4"/>
       <c r="V23" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>21</v>
       </c>
       <c r="W23" s="15">
@@ -34078,7 +34238,7 @@
     </row>
     <row r="24" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45861</v>
       </c>
       <c r="B24" s="29">
@@ -34088,7 +34248,7 @@
         <v>238.01399993000001</v>
       </c>
       <c r="D24" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E24" s="13">
@@ -34109,18 +34269,17 @@
         <v>0</v>
       </c>
       <c r="J24" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K24" s="13">
         <v>0</v>
       </c>
       <c r="L24" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M24" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N24" s="29">
         <v>270.69599941999996</v>
@@ -34129,17 +34288,17 @@
         <v>63.119999909999997</v>
       </c>
       <c r="P24" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>0</v>
+      </c>
+      <c r="R24" s="13">
+        <v>0</v>
+      </c>
+      <c r="S24" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="13">
-        <v>0</v>
-      </c>
-      <c r="R24" s="13">
-        <v>0</v>
-      </c>
-      <c r="S24" s="13">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -34147,7 +34306,7 @@
       </c>
       <c r="U24" s="4"/>
       <c r="V24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="W24" s="15">
@@ -34177,7 +34336,7 @@
     </row>
     <row r="25" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45862</v>
       </c>
       <c r="B25" s="29">
@@ -34187,7 +34346,7 @@
         <v>238.22399992999996</v>
       </c>
       <c r="D25" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E25" s="13">
@@ -34208,18 +34367,17 @@
         <v>0</v>
       </c>
       <c r="J25" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K25" s="13">
         <v>0</v>
       </c>
       <c r="L25" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M25" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N25" s="29">
         <v>294.16799943999979</v>
@@ -34228,17 +34386,17 @@
         <v>55.607999909999997</v>
       </c>
       <c r="P25" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="13">
+        <v>0</v>
+      </c>
+      <c r="R25" s="13">
+        <v>0</v>
+      </c>
+      <c r="S25" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="13">
-        <v>0</v>
-      </c>
-      <c r="R25" s="13">
-        <v>0</v>
-      </c>
-      <c r="S25" s="13">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -34246,7 +34404,7 @@
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>23</v>
       </c>
       <c r="W25" s="15">
@@ -34276,7 +34434,7 @@
     </row>
     <row r="26" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45863</v>
       </c>
       <c r="B26" s="29">
@@ -34286,7 +34444,7 @@
         <v>165.14399989999998</v>
       </c>
       <c r="D26" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>204</v>
       </c>
       <c r="E26" s="13">
@@ -34307,18 +34465,17 @@
         <v>0</v>
       </c>
       <c r="J26" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="K26" s="13">
         <v>0</v>
       </c>
       <c r="L26" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M26" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N26" s="29">
         <v>297.31199934999978</v>
@@ -34327,17 +34484,17 @@
         <v>55.487999910000006</v>
       </c>
       <c r="P26" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="13">
+        <v>0</v>
+      </c>
+      <c r="R26" s="13">
+        <v>0</v>
+      </c>
+      <c r="S26" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="13">
-        <v>0</v>
-      </c>
-      <c r="R26" s="13">
-        <v>0</v>
-      </c>
-      <c r="S26" s="13">
-        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -34345,7 +34502,7 @@
       </c>
       <c r="U26" s="4"/>
       <c r="V26" s="20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
       <c r="W26" s="15">
@@ -34375,7 +34532,7 @@
     </row>
     <row r="27" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45864</v>
       </c>
       <c r="B27" s="29">
@@ -34385,7 +34542,7 @@
         <v>158.25599991999997</v>
       </c>
       <c r="D27" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>78</v>
       </c>
       <c r="E27" s="13">
@@ -34406,18 +34563,17 @@
         <v>0</v>
       </c>
       <c r="J27" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K27" s="13">
         <v>0</v>
       </c>
       <c r="L27" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M27" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N27" s="29">
         <v>285.45599935999996</v>
@@ -34426,17 +34582,17 @@
         <v>53.327999879999993</v>
       </c>
       <c r="P27" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="13">
+        <v>0</v>
+      </c>
+      <c r="R27" s="13">
+        <v>0</v>
+      </c>
+      <c r="S27" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="13">
-        <v>0</v>
-      </c>
-      <c r="R27" s="13">
-        <v>0</v>
-      </c>
-      <c r="S27" s="13">
-        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="T27" s="6" t="s">
@@ -34444,7 +34600,7 @@
       </c>
       <c r="U27" s="4"/>
       <c r="V27" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="W27" s="15">
@@ -34474,7 +34630,7 @@
     </row>
     <row r="28" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45865</v>
       </c>
       <c r="B28" s="29">
@@ -34484,7 +34640,7 @@
         <v>160.06199992999998</v>
       </c>
       <c r="D28" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E28" s="13">
@@ -34505,18 +34661,17 @@
         <v>0</v>
       </c>
       <c r="J28" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K28" s="13">
         <v>0</v>
       </c>
       <c r="L28" s="13">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M28" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N28" s="29">
         <v>295.63199934999972</v>
@@ -34525,17 +34680,17 @@
         <v>56.92799990999999</v>
       </c>
       <c r="P28" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="13">
+        <v>0</v>
+      </c>
+      <c r="R28" s="13">
+        <v>0</v>
+      </c>
+      <c r="S28" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="13">
-        <v>0</v>
-      </c>
-      <c r="R28" s="13">
-        <v>0</v>
-      </c>
-      <c r="S28" s="13">
-        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="T28" s="6" t="s">
@@ -34543,7 +34698,7 @@
       </c>
       <c r="U28" s="4"/>
       <c r="V28" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="W28" s="15">
@@ -34573,7 +34728,7 @@
     </row>
     <row r="29" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45866</v>
       </c>
       <c r="B29" s="29">
@@ -34583,7 +34738,7 @@
         <v>187.86599992999999</v>
       </c>
       <c r="D29" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E29" s="13">
@@ -34604,18 +34759,17 @@
         <v>0</v>
       </c>
       <c r="J29" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K29" s="13">
         <v>0</v>
       </c>
       <c r="L29" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M29" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N29" s="29">
         <v>274.46399932999992</v>
@@ -34624,17 +34778,17 @@
         <v>54.455999929999997</v>
       </c>
       <c r="P29" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="13">
+        <v>0</v>
+      </c>
+      <c r="R29" s="13">
+        <v>0</v>
+      </c>
+      <c r="S29" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="13">
-        <v>0</v>
-      </c>
-      <c r="R29" s="13">
-        <v>0</v>
-      </c>
-      <c r="S29" s="13">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
@@ -34642,7 +34796,7 @@
       </c>
       <c r="U29" s="4"/>
       <c r="V29" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>27</v>
       </c>
       <c r="W29" s="15">
@@ -34672,7 +34826,7 @@
     </row>
     <row r="30" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45867</v>
       </c>
       <c r="B30" s="29">
@@ -34682,7 +34836,7 @@
         <v>213.06599994000004</v>
       </c>
       <c r="D30" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>87</v>
       </c>
       <c r="E30" s="13">
@@ -34703,18 +34857,17 @@
         <v>0</v>
       </c>
       <c r="J30" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K30" s="13">
         <v>0</v>
       </c>
       <c r="L30" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M30" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N30" s="29">
         <v>226.48799934999997</v>
@@ -34723,17 +34876,17 @@
         <v>47.639999899999999</v>
       </c>
       <c r="P30" s="13">
+        <f t="shared" si="3"/>
+        <v>-10</v>
+      </c>
+      <c r="Q30" s="13">
+        <v>0</v>
+      </c>
+      <c r="R30" s="13">
+        <v>0</v>
+      </c>
+      <c r="S30" s="13">
         <f t="shared" si="4"/>
-        <v>-10</v>
-      </c>
-      <c r="Q30" s="13">
-        <v>0</v>
-      </c>
-      <c r="R30" s="13">
-        <v>0</v>
-      </c>
-      <c r="S30" s="13">
-        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="T30" s="6" t="s">
@@ -34741,7 +34894,7 @@
       </c>
       <c r="U30" s="4"/>
       <c r="V30" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="W30" s="15">
@@ -34771,7 +34924,7 @@
     </row>
     <row r="31" spans="1:30" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A31" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45868</v>
       </c>
       <c r="B31" s="29">
@@ -34781,7 +34934,7 @@
         <v>190.80599993999996</v>
       </c>
       <c r="D31" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E31" s="13">
@@ -34802,18 +34955,17 @@
         <v>0</v>
       </c>
       <c r="J31" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K31" s="13">
         <v>0</v>
       </c>
       <c r="L31" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M31" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N31" s="29">
         <v>233.9999993399997</v>
@@ -34822,17 +34974,17 @@
         <v>48.023999929999995</v>
       </c>
       <c r="P31" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="13">
+        <v>0</v>
+      </c>
+      <c r="R31" s="13">
+        <v>0</v>
+      </c>
+      <c r="S31" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="13">
-        <v>0</v>
-      </c>
-      <c r="R31" s="13">
-        <v>0</v>
-      </c>
-      <c r="S31" s="13">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T31" s="6" t="s">
@@ -34840,7 +34992,7 @@
       </c>
       <c r="U31" s="4"/>
       <c r="V31" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>29</v>
       </c>
       <c r="W31" s="15">
@@ -34870,7 +35022,7 @@
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>45869</v>
       </c>
       <c r="B32" s="29">
@@ -34880,7 +35032,7 @@
         <v>200.59199991999998</v>
       </c>
       <c r="D32" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>85</v>
       </c>
       <c r="E32" s="13">
@@ -34901,37 +35053,36 @@
         <v>0</v>
       </c>
       <c r="J32" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="K32" s="13">
         <v>0</v>
       </c>
       <c r="L32" s="13">
+        <v>29</v>
+      </c>
+      <c r="M32" s="13">
+        <v>10</v>
+      </c>
+      <c r="N32" s="29">
+        <v>228.04799942999989</v>
+      </c>
+      <c r="O32" s="29">
+        <v>55.175999879999999</v>
+      </c>
+      <c r="P32" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="M32" s="13">
-        <v>0</v>
-      </c>
-      <c r="N32" s="29">
-        <v>228.04799942999989</v>
-      </c>
-      <c r="O32" s="29">
-        <v>55.175999879999999</v>
-      </c>
-      <c r="P32" s="13">
+      <c r="Q32" s="13">
+        <v>0</v>
+      </c>
+      <c r="R32" s="13">
+        <v>0</v>
+      </c>
+      <c r="S32" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q32" s="13">
-        <v>0</v>
-      </c>
-      <c r="R32" s="13">
-        <v>0</v>
-      </c>
-      <c r="S32" s="13">
-        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="T32" s="6" t="s">
@@ -34939,7 +35090,7 @@
       </c>
       <c r="U32" s="4"/>
       <c r="V32" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="W32" s="15">
@@ -34970,7 +35121,7 @@
     <row r="33" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="U33" s="4"/>
       <c r="V33" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>31</v>
       </c>
       <c r="W33" s="15">
@@ -35000,14 +35151,14 @@
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -35385,15 +35536,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="48"/>
-      <c r="B71" s="48"/>
-      <c r="C71" s="48"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="48"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -35418,15 +35569,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="49"/>
-      <c r="B76" s="49"/>
-      <c r="C76" s="49"/>
-      <c r="D76" s="49"/>
-      <c r="E76" s="49"/>
-      <c r="F76" s="49"/>
-      <c r="G76" s="49"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="49"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -35462,15 +35613,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="50"/>
-      <c r="B80" s="50"/>
-      <c r="C80" s="50"/>
-      <c r="D80" s="50"/>
-      <c r="E80" s="50"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="50"/>
-      <c r="H80" s="50"/>
-      <c r="I80" s="50"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -35506,15 +35657,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="49"/>
-      <c r="B88" s="49"/>
-      <c r="C88" s="49"/>
-      <c r="D88" s="49"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="49"/>
-      <c r="G88" s="49"/>
-      <c r="H88" s="49"/>
-      <c r="I88" s="49"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -35617,15 +35768,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="48"/>
-      <c r="B101" s="48"/>
-      <c r="C101" s="48"/>
-      <c r="D101" s="48"/>
-      <c r="E101" s="48"/>
-      <c r="F101" s="48"/>
-      <c r="G101" s="48"/>
-      <c r="H101" s="48"/>
-      <c r="I101" s="48"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -38677,22 +38828,22 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="48"/>
-      <c r="N35" s="48"/>
-      <c r="O35" s="48"/>
-      <c r="P35" s="48"/>
-      <c r="Q35" s="48"/>
-      <c r="R35" s="48"/>
-      <c r="S35" s="48"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="47"/>
+      <c r="K35" s="47"/>
+      <c r="L35" s="47"/>
+      <c r="M35" s="47"/>
+      <c r="N35" s="47"/>
+      <c r="O35" s="47"/>
+      <c r="P35" s="47"/>
+      <c r="Q35" s="47"/>
+      <c r="R35" s="47"/>
+      <c r="S35" s="47"/>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -39410,25 +39561,25 @@
       <c r="S69" s="1"/>
     </row>
     <row r="70" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="48"/>
-      <c r="B70" s="48"/>
-      <c r="C70" s="48"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="48"/>
-      <c r="G70" s="48"/>
-      <c r="H70" s="48"/>
-      <c r="I70" s="48"/>
-      <c r="J70" s="48"/>
-      <c r="K70" s="48"/>
-      <c r="L70" s="48"/>
-      <c r="M70" s="48"/>
-      <c r="N70" s="48"/>
-      <c r="O70" s="48"/>
-      <c r="P70" s="48"/>
-      <c r="Q70" s="48"/>
-      <c r="R70" s="48"/>
-      <c r="S70" s="48"/>
+      <c r="A70" s="47"/>
+      <c r="B70" s="47"/>
+      <c r="C70" s="47"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="47"/>
+      <c r="F70" s="47"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="47"/>
+      <c r="I70" s="47"/>
+      <c r="J70" s="47"/>
+      <c r="K70" s="47"/>
+      <c r="L70" s="47"/>
+      <c r="M70" s="47"/>
+      <c r="N70" s="47"/>
+      <c r="O70" s="47"/>
+      <c r="P70" s="47"/>
+      <c r="Q70" s="47"/>
+      <c r="R70" s="47"/>
+      <c r="S70" s="47"/>
     </row>
     <row r="71" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -39473,25 +39624,25 @@
       <c r="S72" s="23"/>
     </row>
     <row r="75" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="49"/>
-      <c r="B75" s="49"/>
-      <c r="C75" s="49"/>
-      <c r="D75" s="49"/>
-      <c r="E75" s="49"/>
-      <c r="F75" s="49"/>
-      <c r="G75" s="49"/>
-      <c r="H75" s="49"/>
-      <c r="I75" s="49"/>
-      <c r="J75" s="49"/>
-      <c r="K75" s="49"/>
-      <c r="L75" s="49"/>
-      <c r="M75" s="49"/>
-      <c r="N75" s="49"/>
-      <c r="O75" s="49"/>
-      <c r="P75" s="49"/>
-      <c r="Q75" s="49"/>
-      <c r="R75" s="49"/>
-      <c r="S75" s="49"/>
+      <c r="A75" s="48"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="48"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
+      <c r="J75" s="48"/>
+      <c r="K75" s="48"/>
+      <c r="L75" s="48"/>
+      <c r="M75" s="48"/>
+      <c r="N75" s="48"/>
+      <c r="O75" s="48"/>
+      <c r="P75" s="48"/>
+      <c r="Q75" s="48"/>
+      <c r="R75" s="48"/>
+      <c r="S75" s="48"/>
     </row>
     <row r="76" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -39557,25 +39708,25 @@
       <c r="S78" s="25"/>
     </row>
     <row r="79" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="50"/>
-      <c r="B79" s="50"/>
-      <c r="C79" s="50"/>
-      <c r="D79" s="50"/>
-      <c r="E79" s="50"/>
-      <c r="F79" s="50"/>
-      <c r="G79" s="50"/>
-      <c r="H79" s="50"/>
-      <c r="I79" s="50"/>
-      <c r="J79" s="50"/>
-      <c r="K79" s="50"/>
-      <c r="L79" s="50"/>
-      <c r="M79" s="50"/>
-      <c r="N79" s="50"/>
-      <c r="O79" s="50"/>
-      <c r="P79" s="50"/>
-      <c r="Q79" s="50"/>
-      <c r="R79" s="50"/>
-      <c r="S79" s="50"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="49"/>
+      <c r="E79" s="49"/>
+      <c r="F79" s="49"/>
+      <c r="G79" s="49"/>
+      <c r="H79" s="49"/>
+      <c r="I79" s="49"/>
+      <c r="J79" s="49"/>
+      <c r="K79" s="49"/>
+      <c r="L79" s="49"/>
+      <c r="M79" s="49"/>
+      <c r="N79" s="49"/>
+      <c r="O79" s="49"/>
+      <c r="P79" s="49"/>
+      <c r="Q79" s="49"/>
+      <c r="R79" s="49"/>
+      <c r="S79" s="49"/>
     </row>
     <row r="80" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -39639,25 +39790,25 @@
       <c r="E85" s="23"/>
     </row>
     <row r="87" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="49"/>
-      <c r="B87" s="49"/>
-      <c r="C87" s="49"/>
-      <c r="D87" s="49"/>
-      <c r="E87" s="49"/>
-      <c r="F87" s="49"/>
-      <c r="G87" s="49"/>
-      <c r="H87" s="49"/>
-      <c r="I87" s="49"/>
-      <c r="J87" s="49"/>
-      <c r="K87" s="49"/>
-      <c r="L87" s="49"/>
-      <c r="M87" s="49"/>
-      <c r="N87" s="49"/>
-      <c r="O87" s="49"/>
-      <c r="P87" s="49"/>
-      <c r="Q87" s="49"/>
-      <c r="R87" s="49"/>
-      <c r="S87" s="49"/>
+      <c r="A87" s="48"/>
+      <c r="B87" s="48"/>
+      <c r="C87" s="48"/>
+      <c r="D87" s="48"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
+      <c r="J87" s="48"/>
+      <c r="K87" s="48"/>
+      <c r="L87" s="48"/>
+      <c r="M87" s="48"/>
+      <c r="N87" s="48"/>
+      <c r="O87" s="48"/>
+      <c r="P87" s="48"/>
+      <c r="Q87" s="48"/>
+      <c r="R87" s="48"/>
+      <c r="S87" s="48"/>
     </row>
     <row r="88" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -39849,25 +40000,25 @@
       <c r="E98" s="26"/>
     </row>
     <row r="100" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="48"/>
-      <c r="B100" s="48"/>
-      <c r="C100" s="48"/>
-      <c r="D100" s="48"/>
-      <c r="E100" s="48"/>
-      <c r="F100" s="48"/>
-      <c r="G100" s="48"/>
-      <c r="H100" s="48"/>
-      <c r="I100" s="48"/>
-      <c r="J100" s="48"/>
-      <c r="K100" s="48"/>
-      <c r="L100" s="48"/>
-      <c r="M100" s="48"/>
-      <c r="N100" s="48"/>
-      <c r="O100" s="48"/>
-      <c r="P100" s="48"/>
-      <c r="Q100" s="48"/>
-      <c r="R100" s="48"/>
-      <c r="S100" s="48"/>
+      <c r="A100" s="47"/>
+      <c r="B100" s="47"/>
+      <c r="C100" s="47"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
+      <c r="G100" s="47"/>
+      <c r="H100" s="47"/>
+      <c r="I100" s="47"/>
+      <c r="J100" s="47"/>
+      <c r="K100" s="47"/>
+      <c r="L100" s="47"/>
+      <c r="M100" s="47"/>
+      <c r="N100" s="47"/>
+      <c r="O100" s="47"/>
+      <c r="P100" s="47"/>
+      <c r="Q100" s="47"/>
+      <c r="R100" s="47"/>
+      <c r="S100" s="47"/>
     </row>
     <row r="101" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -43110,14 +43261,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -43495,15 +43646,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="48"/>
-      <c r="B71" s="48"/>
-      <c r="C71" s="48"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="48"/>
+      <c r="A71" s="47"/>
+      <c r="B71" s="47"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -43528,15 +43679,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="49"/>
-      <c r="B76" s="49"/>
-      <c r="C76" s="49"/>
-      <c r="D76" s="49"/>
-      <c r="E76" s="49"/>
-      <c r="F76" s="49"/>
-      <c r="G76" s="49"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="49"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -43572,15 +43723,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="50"/>
-      <c r="B80" s="50"/>
-      <c r="C80" s="50"/>
-      <c r="D80" s="50"/>
-      <c r="E80" s="50"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="50"/>
-      <c r="H80" s="50"/>
-      <c r="I80" s="50"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="49"/>
+      <c r="E80" s="49"/>
+      <c r="F80" s="49"/>
+      <c r="G80" s="49"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -43616,15 +43767,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="49"/>
-      <c r="B88" s="49"/>
-      <c r="C88" s="49"/>
-      <c r="D88" s="49"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="49"/>
-      <c r="G88" s="49"/>
-      <c r="H88" s="49"/>
-      <c r="I88" s="49"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -43727,15 +43878,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="48"/>
-      <c r="B101" s="48"/>
-      <c r="C101" s="48"/>
-      <c r="D101" s="48"/>
-      <c r="E101" s="48"/>
-      <c r="F101" s="48"/>
-      <c r="G101" s="48"/>
-      <c r="H101" s="48"/>
-      <c r="I101" s="48"/>
+      <c r="A101" s="47"/>
+      <c r="B101" s="47"/>
+      <c r="C101" s="47"/>
+      <c r="D101" s="47"/>
+      <c r="E101" s="47"/>
+      <c r="F101" s="47"/>
+      <c r="G101" s="47"/>
+      <c r="H101" s="47"/>
+      <c r="I101" s="47"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BDBCE4-EABA-451F-8D79-F7FBE5ED2FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A52729-C590-4C91-A551-D361418B69E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="89">
   <si>
     <t>Data</t>
   </si>
@@ -251,6 +251,69 @@
   </si>
   <si>
     <t>VOT ASSESSORIA PARLAMENTAR</t>
+  </si>
+  <si>
+    <t>REU OBRAS/DOC</t>
+  </si>
+  <si>
+    <t>REU OBRAS, SELEÇÃO GERAL (TÉRMINO)</t>
+  </si>
+  <si>
+    <t>SEM EXPEDIENTE</t>
+  </si>
+  <si>
+    <t>SD POR UM DIA (ALQQ)</t>
+  </si>
+  <si>
+    <t>EXPEDIENTE ADM</t>
+  </si>
+  <si>
+    <t>EVENTO ALQQ (APOIO A PREFEITURA),PCI ESLog</t>
+  </si>
+  <si>
+    <t>REU OFICIAIS,REU OBRAS</t>
+  </si>
+  <si>
+    <t>PCI 4º BECMB,CAMPO CFC,DFPC</t>
+  </si>
+  <si>
+    <t>PCI 4º BECMB,CAMPO CFC,FERIADO</t>
+  </si>
+  <si>
+    <t>FERIADO,PCI ESLog</t>
+  </si>
+  <si>
+    <t>FORMATURA GERAL, PCI ESLog</t>
+  </si>
+  <si>
+    <t>REU AGENDA</t>
+  </si>
+  <si>
+    <t>REU AGENDA,PCI ESLog</t>
+  </si>
+  <si>
+    <t>PCI ESLog</t>
+  </si>
+  <si>
+    <t>REU OBRAS, 1ª CH TIA/TAT,SELEÇÃO GERAL (INÍCIO),REU ADM</t>
+  </si>
+  <si>
+    <t>FERIADO</t>
+  </si>
+  <si>
+    <t>1ª CH TIA/TAT, REU EFETIVO S1</t>
+  </si>
+  <si>
+    <t>1ª CH TIA/TAT,JANTAR DIA DOS PAIS(ALQQ)</t>
+  </si>
+  <si>
+    <t>PCI 4º BECMB,CAMPO CFC</t>
+  </si>
+  <si>
+    <t>EXPEDIENTE NO ALQQ</t>
+  </si>
+  <si>
+    <t>APOIO LOG - OP ATLAS</t>
   </si>
 </sst>
 </file>
@@ -28333,6 +28396,7 @@
     <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
     <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
@@ -28497,7 +28561,9 @@
         <f t="shared" ref="S2:S32" si="6">AD3-AD2</f>
         <v>0</v>
       </c>
-      <c r="T2" s="6"/>
+      <c r="T2" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="U2" s="4"/>
       <c r="V2" s="8">
         <v>0</v>
@@ -28601,7 +28667,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T3" s="6"/>
+      <c r="T3" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="U3" s="4"/>
       <c r="V3" s="12">
         <v>1</v>
@@ -28698,7 +28766,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T4" s="6"/>
+      <c r="T4" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U4" s="4"/>
       <c r="V4" s="14">
         <f t="shared" ref="V4:V32" si="9">V3+1</f>
@@ -28796,7 +28866,9 @@
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="T5" s="6"/>
+      <c r="T5" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U5" s="4"/>
       <c r="V5" s="14">
         <f t="shared" si="9"/>
@@ -28827,7 +28899,7 @@
         <v>3537</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="28">
         <f t="shared" si="7"/>
         <v>45874</v>
@@ -28894,7 +28966,9 @@
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="T6" s="6"/>
+      <c r="T6" s="6" t="s">
+        <v>82</v>
+      </c>
       <c r="U6" s="4"/>
       <c r="V6" s="14">
         <f t="shared" si="9"/>
@@ -28992,7 +29066,9 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="T7" s="6"/>
+      <c r="T7" s="6" t="s">
+        <v>83</v>
+      </c>
       <c r="U7" s="4"/>
       <c r="V7" s="14">
         <f t="shared" si="9"/>
@@ -29023,7 +29099,7 @@
         <v>3553</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="28">
         <f t="shared" si="7"/>
         <v>45876</v>
@@ -29090,7 +29166,9 @@
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="T8" s="6"/>
+      <c r="T8" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="U8" s="4"/>
       <c r="V8" s="14">
         <f t="shared" si="9"/>
@@ -29121,7 +29199,7 @@
         <v>3558</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="28">
         <f t="shared" si="7"/>
         <v>45877</v>
@@ -29188,7 +29266,9 @@
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="T9" s="6"/>
+      <c r="T9" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="U9" s="4"/>
       <c r="V9" s="14">
         <f t="shared" si="9"/>
@@ -29286,7 +29366,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T10" s="6"/>
+      <c r="T10" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U10" s="4"/>
       <c r="V10" s="14">
         <f t="shared" si="9"/>
@@ -29384,7 +29466,9 @@
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="T11" s="6"/>
+      <c r="T11" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U11" s="4"/>
       <c r="V11" s="14">
         <f t="shared" si="9"/>
@@ -29415,7 +29499,7 @@
         <v>3568</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A12" s="28">
         <f t="shared" si="7"/>
         <v>45880</v>
@@ -29482,7 +29566,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T12" s="6"/>
+      <c r="T12" s="6" t="s">
+        <v>86</v>
+      </c>
       <c r="U12" s="4"/>
       <c r="V12" s="14">
         <f t="shared" si="9"/>
@@ -29513,7 +29599,7 @@
         <v>3572</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
         <f t="shared" si="7"/>
         <v>45881</v>
@@ -29580,7 +29666,9 @@
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="T13" s="6"/>
+      <c r="T13" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="U13" s="4"/>
       <c r="V13" s="14">
         <f t="shared" si="9"/>
@@ -29611,7 +29699,7 @@
         <v>3572</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A14" s="28">
         <f t="shared" si="7"/>
         <v>45882</v>
@@ -29678,7 +29766,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T14" s="6"/>
+      <c r="T14" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="U14" s="4"/>
       <c r="V14" s="14">
         <f t="shared" si="9"/>
@@ -29709,7 +29799,7 @@
         <v>3581</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A15" s="28">
         <f t="shared" si="7"/>
         <v>45883</v>
@@ -29775,7 +29865,9 @@
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="T15" s="6"/>
+      <c r="T15" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="U15" s="4"/>
       <c r="V15" s="14">
         <f t="shared" si="9"/>
@@ -29806,7 +29898,7 @@
         <v>3581</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A16" s="28">
         <f t="shared" si="7"/>
         <v>45884</v>
@@ -29873,7 +29965,9 @@
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="T16" s="6"/>
+      <c r="T16" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="U16" s="4"/>
       <c r="V16" s="14">
         <f t="shared" si="9"/>
@@ -29917,49 +30011,49 @@
       </c>
       <c r="D17" s="13">
         <f t="shared" si="8"/>
-        <v>-9728</v>
+        <v>0</v>
       </c>
       <c r="E17" s="13">
         <v>0</v>
       </c>
       <c r="F17" s="13">
         <f t="shared" si="0"/>
-        <v>-11852</v>
+        <v>0</v>
       </c>
       <c r="G17" s="13">
         <v>0</v>
       </c>
       <c r="H17" s="13">
         <f t="shared" si="1"/>
-        <v>-9583</v>
+        <v>0</v>
       </c>
       <c r="I17" s="13">
         <v>0</v>
       </c>
       <c r="J17" s="13">
         <f t="shared" si="10"/>
-        <v>-10848</v>
+        <v>0</v>
       </c>
       <c r="K17" s="13">
         <v>0</v>
       </c>
       <c r="L17" s="13">
         <f t="shared" si="3"/>
-        <v>-1285</v>
+        <v>0</v>
       </c>
       <c r="M17" s="13">
         <v>0</v>
       </c>
       <c r="N17" s="13">
         <f t="shared" si="4"/>
-        <v>-3993</v>
+        <v>0</v>
       </c>
       <c r="O17" s="13">
         <v>0</v>
       </c>
       <c r="P17" s="13">
         <f t="shared" si="5"/>
-        <v>-404</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="13">
         <v>0</v>
@@ -29969,9 +30063,11 @@
       </c>
       <c r="S17" s="13">
         <f t="shared" si="6"/>
-        <v>-3589</v>
-      </c>
-      <c r="T17" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U17" s="4"/>
       <c r="V17" s="14">
         <f t="shared" si="9"/>
@@ -30015,49 +30111,49 @@
       </c>
       <c r="D18" s="13">
         <f t="shared" si="8"/>
-        <v>9771</v>
+        <v>43</v>
       </c>
       <c r="E18" s="13">
         <v>0</v>
       </c>
       <c r="F18" s="13">
         <f t="shared" si="0"/>
-        <v>11971</v>
+        <v>119</v>
       </c>
       <c r="G18" s="13">
         <v>0</v>
       </c>
       <c r="H18" s="13">
         <f t="shared" si="1"/>
-        <v>9587</v>
+        <v>4</v>
       </c>
       <c r="I18" s="13">
         <v>0</v>
       </c>
       <c r="J18" s="13">
         <f t="shared" si="10"/>
-        <v>10850</v>
+        <v>2</v>
       </c>
       <c r="K18" s="13">
         <v>0</v>
       </c>
       <c r="L18" s="13">
         <f t="shared" si="3"/>
-        <v>1285</v>
+        <v>0</v>
       </c>
       <c r="M18" s="13">
         <v>0</v>
       </c>
       <c r="N18" s="13">
         <f t="shared" si="4"/>
-        <v>4001</v>
+        <v>8</v>
       </c>
       <c r="O18" s="13">
         <v>0</v>
       </c>
       <c r="P18" s="13">
         <f t="shared" si="5"/>
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="13">
         <v>0</v>
@@ -30067,24 +30163,42 @@
       </c>
       <c r="S18" s="13">
         <f t="shared" si="6"/>
-        <v>3596</v>
-      </c>
-      <c r="T18" s="6"/>
+        <v>7</v>
+      </c>
+      <c r="T18" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U18" s="4"/>
       <c r="V18" s="14">
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
-      <c r="Y18" s="16"/>
-      <c r="Z18" s="16"/>
-      <c r="AA18" s="16"/>
-      <c r="AB18" s="16"/>
-      <c r="AC18" s="16"/>
-      <c r="AD18" s="16"/>
-    </row>
-    <row r="19" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="W18" s="16">
+        <v>9728</v>
+      </c>
+      <c r="X18" s="16">
+        <v>11852</v>
+      </c>
+      <c r="Y18" s="16">
+        <v>9583</v>
+      </c>
+      <c r="Z18" s="16">
+        <v>10848</v>
+      </c>
+      <c r="AA18" s="16">
+        <v>1285</v>
+      </c>
+      <c r="AB18" s="16">
+        <v>3993</v>
+      </c>
+      <c r="AC18" s="16">
+        <v>404</v>
+      </c>
+      <c r="AD18" s="16">
+        <v>3589</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A19" s="28">
         <f t="shared" si="7"/>
         <v>45887</v>
@@ -30151,7 +30265,9 @@
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="T19" s="6"/>
+      <c r="T19" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="U19" s="17"/>
       <c r="V19" s="18">
         <f t="shared" si="9"/>
@@ -30249,7 +30365,9 @@
         <f t="shared" si="6"/>
         <v>-3600</v>
       </c>
-      <c r="T20" s="6"/>
+      <c r="T20" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="U20" s="4"/>
       <c r="V20" s="18">
         <f t="shared" si="9"/>
@@ -30347,7 +30465,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T21" s="6"/>
+      <c r="T21" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="U21" s="4"/>
       <c r="V21" s="18">
         <f t="shared" si="9"/>
@@ -30362,7 +30482,7 @@
       <c r="AC21" s="15"/>
       <c r="AD21" s="15"/>
     </row>
-    <row r="22" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A22" s="28">
         <f t="shared" si="7"/>
         <v>45890</v>
@@ -30429,7 +30549,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T22" s="6"/>
+      <c r="T22" s="6" t="s">
+        <v>69</v>
+      </c>
       <c r="U22" s="4"/>
       <c r="V22" s="18">
         <f t="shared" si="9"/>
@@ -30511,7 +30633,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T23" s="6"/>
+      <c r="T23" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="U23" s="4"/>
       <c r="V23" s="18">
         <f t="shared" si="9"/>
@@ -30593,7 +30717,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T24" s="6"/>
+      <c r="T24" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="U24" s="4"/>
       <c r="V24" s="18">
         <f t="shared" si="9"/>
@@ -30675,7 +30801,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T25" s="6"/>
+      <c r="T25" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U25" s="4"/>
       <c r="V25" s="18">
         <f t="shared" si="9"/>
@@ -30757,7 +30885,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T26" s="6"/>
+      <c r="T26" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="U26" s="4"/>
       <c r="V26" s="20">
         <f t="shared" si="9"/>
@@ -30772,7 +30902,7 @@
       <c r="AC26" s="21"/>
       <c r="AD26" s="21"/>
     </row>
-    <row r="27" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A27" s="28">
         <f t="shared" si="7"/>
         <v>45895</v>
@@ -30839,7 +30969,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T27" s="6"/>
+      <c r="T27" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="U27" s="4"/>
       <c r="V27" s="18">
         <f t="shared" si="9"/>
@@ -30854,7 +30986,7 @@
       <c r="AC27" s="15"/>
       <c r="AD27" s="15"/>
     </row>
-    <row r="28" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A28" s="28">
         <f t="shared" si="7"/>
         <v>45896</v>
@@ -30921,7 +31053,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T28" s="6"/>
+      <c r="T28" s="6" t="s">
+        <v>80</v>
+      </c>
       <c r="U28" s="4"/>
       <c r="V28" s="18">
         <f t="shared" si="9"/>
@@ -31003,7 +31137,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T29" s="6"/>
+      <c r="T29" s="6" t="s">
+        <v>77</v>
+      </c>
       <c r="U29" s="4"/>
       <c r="V29" s="18">
         <f t="shared" si="9"/>
@@ -31018,7 +31154,7 @@
       <c r="AC29" s="15"/>
       <c r="AD29" s="15"/>
     </row>
-    <row r="30" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="28">
         <f t="shared" si="7"/>
         <v>45898</v>
@@ -31085,7 +31221,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T30" s="6"/>
+      <c r="T30" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="U30" s="4"/>
       <c r="V30" s="18">
         <f t="shared" si="9"/>
@@ -31167,7 +31305,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T31" s="6"/>
+      <c r="T31" s="6" t="s">
+        <v>81</v>
+      </c>
       <c r="U31" s="4"/>
       <c r="V31" s="18">
         <f t="shared" si="9"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A52729-C590-4C91-A551-D361418B69E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2CBD53-5D46-4B58-9148-D8BE62EACF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -1426,10 +1426,10 @@
         <v>40</v>
       </c>
       <c r="B9" s="41">
-        <v>0</v>
+        <v>34465.15</v>
       </c>
       <c r="C9" s="41">
-        <v>0</v>
+        <v>12666.75</v>
       </c>
       <c r="D9" s="41">
         <v>0</v>
@@ -1462,10 +1462,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="41">
-        <v>0</v>
+        <v>8025.6900000000005</v>
       </c>
       <c r="O9" s="41">
-        <v>0</v>
+        <v>3709.53</v>
       </c>
       <c r="P9" s="41">
         <v>0</v>
@@ -25245,49 +25245,49 @@
       </c>
       <c r="D2" s="6">
         <f t="shared" ref="D2:D31" si="0">W3-W2</f>
-        <v>0</v>
+        <v>10512</v>
       </c>
       <c r="E2" s="6">
         <v>0</v>
       </c>
       <c r="F2" s="6">
         <f t="shared" ref="F2:F31" si="1">X3-X2</f>
-        <v>0</v>
+        <v>13072</v>
       </c>
       <c r="G2" s="6">
         <v>0</v>
       </c>
       <c r="H2" s="6">
         <f t="shared" ref="H2:H31" si="2">Y3-Y2</f>
-        <v>0</v>
+        <v>9649</v>
       </c>
       <c r="I2" s="6">
         <v>0</v>
       </c>
       <c r="J2" s="6">
         <f t="shared" ref="J2:J14" si="3">Z3-Z2</f>
-        <v>0</v>
+        <v>10861</v>
       </c>
       <c r="K2" s="6">
         <v>0</v>
       </c>
       <c r="L2" s="6">
         <f t="shared" ref="L2:L31" si="4">AA3-AA2</f>
-        <v>0</v>
+        <v>1288</v>
       </c>
       <c r="M2" s="6">
         <v>0</v>
       </c>
       <c r="N2" s="6">
         <f t="shared" ref="N2:N31" si="5">AB3-AB2</f>
-        <v>0</v>
+        <v>4072</v>
       </c>
       <c r="O2" s="6">
         <v>0</v>
       </c>
       <c r="P2" s="6">
         <f t="shared" ref="P2:P31" si="6">AC3-AC2</f>
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="Q2" s="6">
         <v>0</v>
@@ -25297,7 +25297,7 @@
       </c>
       <c r="S2" s="6">
         <f t="shared" ref="S2:S31" si="7">AD3-AD2</f>
-        <v>0</v>
+        <v>3660</v>
       </c>
       <c r="T2" s="6"/>
       <c r="U2" s="4"/>
@@ -25332,28 +25332,28 @@
       </c>
       <c r="D3" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E3" s="6">
         <v>0</v>
       </c>
       <c r="F3" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G3" s="6">
         <v>0</v>
       </c>
       <c r="H3" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I3" s="6">
         <v>0</v>
       </c>
       <c r="J3" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="6">
         <v>0</v>
@@ -25367,14 +25367,14 @@
       </c>
       <c r="N3" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O3" s="6">
         <v>0</v>
       </c>
       <c r="P3" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="6">
         <v>0</v>
@@ -25384,21 +25384,37 @@
       </c>
       <c r="S3" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T3" s="6"/>
       <c r="U3" s="4"/>
       <c r="V3" s="12">
         <v>1</v>
       </c>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="13"/>
+      <c r="W3" s="13">
+        <v>10512</v>
+      </c>
+      <c r="X3" s="13">
+        <v>13072</v>
+      </c>
+      <c r="Y3" s="13">
+        <v>9649</v>
+      </c>
+      <c r="Z3" s="13">
+        <v>10861</v>
+      </c>
+      <c r="AA3" s="13">
+        <v>1288</v>
+      </c>
+      <c r="AB3" s="13">
+        <v>4072</v>
+      </c>
+      <c r="AC3" s="13">
+        <v>412</v>
+      </c>
+      <c r="AD3" s="13">
+        <v>3660</v>
+      </c>
     </row>
     <row r="4" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
@@ -25412,49 +25428,49 @@
       </c>
       <c r="D4" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-10596</v>
       </c>
       <c r="E4" s="6">
         <v>0</v>
       </c>
       <c r="F4" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-13112</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
       </c>
       <c r="H4" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9654</v>
       </c>
       <c r="I4" s="6">
         <v>0</v>
       </c>
       <c r="J4" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-10862</v>
       </c>
       <c r="K4" s="6">
         <v>0</v>
       </c>
       <c r="L4" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1288</v>
       </c>
       <c r="M4" s="6">
         <v>0</v>
       </c>
       <c r="N4" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4076</v>
       </c>
       <c r="O4" s="6">
         <v>0</v>
       </c>
       <c r="P4" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-413</v>
       </c>
       <c r="Q4" s="6">
         <v>0</v>
@@ -25464,7 +25480,7 @@
       </c>
       <c r="S4" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3663</v>
       </c>
       <c r="T4" s="6"/>
       <c r="U4" s="4"/>
@@ -25472,14 +25488,30 @@
         <f t="shared" ref="V4:V32" si="8">V3+1</f>
         <v>2</v>
       </c>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
+      <c r="W4" s="6">
+        <v>10596</v>
+      </c>
+      <c r="X4" s="6">
+        <v>13112</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>9654</v>
+      </c>
+      <c r="Z4" s="6">
+        <v>10862</v>
+      </c>
+      <c r="AA4" s="6">
+        <v>1288</v>
+      </c>
+      <c r="AB4" s="6">
+        <v>4076</v>
+      </c>
+      <c r="AC4" s="6">
+        <v>413</v>
+      </c>
+      <c r="AD4" s="6">
+        <v>3663</v>
+      </c>
     </row>
     <row r="5" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
@@ -28771,7 +28803,7 @@
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="14">
-        <f t="shared" ref="V4:V32" si="9">V3+1</f>
+        <f t="shared" ref="V4:V33" si="9">V3+1</f>
         <v>2</v>
       </c>
       <c r="W4" s="15">
@@ -30311,49 +30343,49 @@
       </c>
       <c r="D20" s="13">
         <f t="shared" si="8"/>
-        <v>-9782</v>
+        <v>80</v>
       </c>
       <c r="E20" s="13">
         <v>0</v>
       </c>
       <c r="F20" s="13">
         <f t="shared" si="0"/>
-        <v>-12030</v>
+        <v>69</v>
       </c>
       <c r="G20" s="13">
         <v>0</v>
       </c>
       <c r="H20" s="13">
         <f t="shared" si="1"/>
-        <v>-9590</v>
+        <v>5</v>
       </c>
       <c r="I20" s="13">
         <v>0</v>
       </c>
       <c r="J20" s="13">
         <f t="shared" si="10"/>
-        <v>-10851</v>
+        <v>0</v>
       </c>
       <c r="K20" s="13">
         <v>0</v>
       </c>
       <c r="L20" s="13">
         <f t="shared" si="3"/>
-        <v>-1285</v>
+        <v>0</v>
       </c>
       <c r="M20" s="13">
         <v>0</v>
       </c>
       <c r="N20" s="13">
         <f t="shared" si="4"/>
-        <v>-4005</v>
+        <v>-2995</v>
       </c>
       <c r="O20" s="13">
         <v>0</v>
       </c>
       <c r="P20" s="13">
         <f t="shared" si="5"/>
-        <v>-404</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="13">
         <v>0</v>
@@ -30363,7 +30395,7 @@
       </c>
       <c r="S20" s="13">
         <f t="shared" si="6"/>
-        <v>-3600</v>
+        <v>4</v>
       </c>
       <c r="T20" s="6" t="s">
         <v>68</v>
@@ -30462,7 +30494,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="13">
-        <f t="shared" si="6"/>
+        <f>AD22-AD21</f>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -30473,14 +30505,30 @@
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="W21" s="15"/>
-      <c r="X21" s="15"/>
-      <c r="Y21" s="15"/>
-      <c r="Z21" s="15"/>
-      <c r="AA21" s="15"/>
-      <c r="AB21" s="15"/>
-      <c r="AC21" s="15"/>
-      <c r="AD21" s="15"/>
+      <c r="W21" s="15">
+        <v>9862</v>
+      </c>
+      <c r="X21" s="15">
+        <v>12099</v>
+      </c>
+      <c r="Y21" s="15">
+        <v>9595</v>
+      </c>
+      <c r="Z21" s="15">
+        <v>10851</v>
+      </c>
+      <c r="AA21" s="15">
+        <v>1285</v>
+      </c>
+      <c r="AB21" s="15">
+        <v>1010</v>
+      </c>
+      <c r="AC21" s="15">
+        <v>405</v>
+      </c>
+      <c r="AD21" s="15">
+        <v>3604</v>
+      </c>
     </row>
     <row r="22" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A22" s="28">
@@ -30557,14 +30605,30 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="W22" s="15"/>
-      <c r="X22" s="15"/>
-      <c r="Y22" s="15"/>
-      <c r="Z22" s="15"/>
-      <c r="AA22" s="15"/>
-      <c r="AB22" s="15"/>
-      <c r="AC22" s="15"/>
-      <c r="AD22" s="15"/>
+      <c r="W22" s="15">
+        <v>9862</v>
+      </c>
+      <c r="X22" s="15">
+        <v>12099</v>
+      </c>
+      <c r="Y22" s="15">
+        <v>9595</v>
+      </c>
+      <c r="Z22" s="15">
+        <v>10851</v>
+      </c>
+      <c r="AA22" s="15">
+        <v>1285</v>
+      </c>
+      <c r="AB22" s="15">
+        <v>1010</v>
+      </c>
+      <c r="AC22" s="15">
+        <v>405</v>
+      </c>
+      <c r="AD22" s="15">
+        <v>3604</v>
+      </c>
     </row>
     <row r="23" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="28">
@@ -30641,14 +30705,30 @@
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="W23" s="15"/>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="15"/>
-      <c r="Z23" s="15"/>
-      <c r="AA23" s="15"/>
-      <c r="AB23" s="15"/>
-      <c r="AC23" s="15"/>
-      <c r="AD23" s="15"/>
+      <c r="W23" s="15">
+        <v>9862</v>
+      </c>
+      <c r="X23" s="15">
+        <v>12099</v>
+      </c>
+      <c r="Y23" s="15">
+        <v>9595</v>
+      </c>
+      <c r="Z23" s="15">
+        <v>10851</v>
+      </c>
+      <c r="AA23" s="15">
+        <v>1285</v>
+      </c>
+      <c r="AB23" s="15">
+        <v>1010</v>
+      </c>
+      <c r="AC23" s="15">
+        <v>405</v>
+      </c>
+      <c r="AD23" s="15">
+        <v>3604</v>
+      </c>
     </row>
     <row r="24" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="28">
@@ -30663,49 +30743,49 @@
       </c>
       <c r="D24" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="E24" s="13">
         <v>0</v>
       </c>
       <c r="F24" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="G24" s="13">
         <v>0</v>
       </c>
       <c r="H24" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I24" s="13">
         <v>0</v>
       </c>
       <c r="J24" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K24" s="13">
         <v>0</v>
       </c>
       <c r="L24" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="13">
         <v>0</v>
       </c>
       <c r="N24" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3021</v>
       </c>
       <c r="O24" s="13">
         <v>0</v>
       </c>
       <c r="P24" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="13">
         <v>0</v>
@@ -30715,7 +30795,7 @@
       </c>
       <c r="S24" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T24" s="6" t="s">
         <v>71</v>
@@ -30725,14 +30805,30 @@
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="W24" s="15"/>
-      <c r="X24" s="15"/>
-      <c r="Y24" s="15"/>
-      <c r="Z24" s="15"/>
-      <c r="AA24" s="15"/>
-      <c r="AB24" s="15"/>
-      <c r="AC24" s="15"/>
-      <c r="AD24" s="15"/>
+      <c r="W24" s="15">
+        <v>9862</v>
+      </c>
+      <c r="X24" s="15">
+        <v>12099</v>
+      </c>
+      <c r="Y24" s="15">
+        <v>9595</v>
+      </c>
+      <c r="Z24" s="15">
+        <v>10851</v>
+      </c>
+      <c r="AA24" s="15">
+        <v>1285</v>
+      </c>
+      <c r="AB24" s="15">
+        <v>1010</v>
+      </c>
+      <c r="AC24" s="15">
+        <v>405</v>
+      </c>
+      <c r="AD24" s="15">
+        <v>3604</v>
+      </c>
     </row>
     <row r="25" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="28">
@@ -30809,14 +30905,30 @@
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15"/>
-      <c r="AA25" s="15"/>
-      <c r="AB25" s="15"/>
-      <c r="AC25" s="15"/>
-      <c r="AD25" s="15"/>
+      <c r="W25" s="21">
+        <v>10085</v>
+      </c>
+      <c r="X25" s="21">
+        <v>12626</v>
+      </c>
+      <c r="Y25" s="21">
+        <v>9616</v>
+      </c>
+      <c r="Z25" s="21">
+        <v>10855</v>
+      </c>
+      <c r="AA25" s="21">
+        <v>1286</v>
+      </c>
+      <c r="AB25" s="21">
+        <v>4031</v>
+      </c>
+      <c r="AC25" s="21">
+        <v>408</v>
+      </c>
+      <c r="AD25" s="21">
+        <v>3622</v>
+      </c>
     </row>
     <row r="26" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="28">
@@ -30893,14 +31005,30 @@
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="W26" s="21"/>
-      <c r="X26" s="21"/>
-      <c r="Y26" s="21"/>
-      <c r="Z26" s="21"/>
-      <c r="AA26" s="21"/>
-      <c r="AB26" s="21"/>
-      <c r="AC26" s="21"/>
-      <c r="AD26" s="21"/>
+      <c r="W26" s="21">
+        <v>10085</v>
+      </c>
+      <c r="X26" s="21">
+        <v>12626</v>
+      </c>
+      <c r="Y26" s="21">
+        <v>9616</v>
+      </c>
+      <c r="Z26" s="21">
+        <v>10855</v>
+      </c>
+      <c r="AA26" s="21">
+        <v>1286</v>
+      </c>
+      <c r="AB26" s="21">
+        <v>4031</v>
+      </c>
+      <c r="AC26" s="21">
+        <v>408</v>
+      </c>
+      <c r="AD26" s="21">
+        <v>3622</v>
+      </c>
     </row>
     <row r="27" spans="1:30" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A27" s="28">
@@ -30915,28 +31043,28 @@
       </c>
       <c r="D27" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E27" s="13">
         <v>0</v>
       </c>
       <c r="F27" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="G27" s="13">
         <v>0</v>
       </c>
       <c r="H27" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I27" s="13">
         <v>0</v>
       </c>
       <c r="J27" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="13">
         <v>0</v>
@@ -30950,7 +31078,7 @@
       </c>
       <c r="N27" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O27" s="13">
         <v>0</v>
@@ -30967,7 +31095,7 @@
       </c>
       <c r="S27" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T27" s="6" t="s">
         <v>73</v>
@@ -30977,14 +31105,30 @@
         <f t="shared" si="9"/>
         <v>25</v>
       </c>
-      <c r="W27" s="15"/>
-      <c r="X27" s="15"/>
-      <c r="Y27" s="15"/>
-      <c r="Z27" s="15"/>
-      <c r="AA27" s="15"/>
-      <c r="AB27" s="15"/>
-      <c r="AC27" s="15"/>
-      <c r="AD27" s="15"/>
+      <c r="W27" s="21">
+        <v>10085</v>
+      </c>
+      <c r="X27" s="21">
+        <v>12626</v>
+      </c>
+      <c r="Y27" s="21">
+        <v>9616</v>
+      </c>
+      <c r="Z27" s="21">
+        <v>10855</v>
+      </c>
+      <c r="AA27" s="21">
+        <v>1286</v>
+      </c>
+      <c r="AB27" s="21">
+        <v>4031</v>
+      </c>
+      <c r="AC27" s="21">
+        <v>408</v>
+      </c>
+      <c r="AD27" s="21">
+        <v>3622</v>
+      </c>
     </row>
     <row r="28" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A28" s="28">
@@ -30999,14 +31143,14 @@
       </c>
       <c r="D28" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E28" s="13">
         <v>0</v>
       </c>
       <c r="F28" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G28" s="13">
         <v>0</v>
@@ -31020,28 +31164,28 @@
       </c>
       <c r="J28" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="13">
         <v>0</v>
       </c>
       <c r="L28" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="13">
         <v>0</v>
       </c>
       <c r="N28" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O28" s="13">
         <v>0</v>
       </c>
       <c r="P28" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="13">
         <v>0</v>
@@ -31051,7 +31195,7 @@
       </c>
       <c r="S28" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T28" s="6" t="s">
         <v>80</v>
@@ -31061,14 +31205,30 @@
         <f t="shared" si="9"/>
         <v>26</v>
       </c>
-      <c r="W28" s="15"/>
-      <c r="X28" s="15"/>
-      <c r="Y28" s="15"/>
-      <c r="Z28" s="15"/>
-      <c r="AA28" s="15"/>
-      <c r="AB28" s="15"/>
-      <c r="AC28" s="15"/>
-      <c r="AD28" s="15"/>
+      <c r="W28" s="15">
+        <v>10140</v>
+      </c>
+      <c r="X28" s="15">
+        <v>12740</v>
+      </c>
+      <c r="Y28" s="15">
+        <v>9620</v>
+      </c>
+      <c r="Z28" s="15">
+        <v>10856</v>
+      </c>
+      <c r="AA28" s="15">
+        <v>1286</v>
+      </c>
+      <c r="AB28" s="15">
+        <v>4044</v>
+      </c>
+      <c r="AC28" s="15">
+        <v>408</v>
+      </c>
+      <c r="AD28" s="15">
+        <v>3635</v>
+      </c>
     </row>
     <row r="29" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="28">
@@ -31083,28 +31243,28 @@
       </c>
       <c r="D29" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E29" s="13">
         <v>0</v>
       </c>
       <c r="F29" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G29" s="13">
         <v>0</v>
       </c>
       <c r="H29" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I29" s="13">
         <v>0</v>
       </c>
       <c r="J29" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="13">
         <v>0</v>
@@ -31118,7 +31278,7 @@
       </c>
       <c r="N29" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O29" s="13">
         <v>0</v>
@@ -31135,7 +31295,7 @@
       </c>
       <c r="S29" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T29" s="6" t="s">
         <v>77</v>
@@ -31145,14 +31305,30 @@
         <f t="shared" si="9"/>
         <v>27</v>
       </c>
-      <c r="W29" s="15"/>
-      <c r="X29" s="15"/>
-      <c r="Y29" s="15"/>
-      <c r="Z29" s="15"/>
-      <c r="AA29" s="15"/>
-      <c r="AB29" s="15"/>
-      <c r="AC29" s="15"/>
-      <c r="AD29" s="15"/>
+      <c r="W29" s="15">
+        <v>10216</v>
+      </c>
+      <c r="X29" s="15">
+        <v>12796</v>
+      </c>
+      <c r="Y29" s="15">
+        <v>9620</v>
+      </c>
+      <c r="Z29" s="15">
+        <v>10857</v>
+      </c>
+      <c r="AA29" s="15">
+        <v>1287</v>
+      </c>
+      <c r="AB29" s="15">
+        <v>4049</v>
+      </c>
+      <c r="AC29" s="15">
+        <v>410</v>
+      </c>
+      <c r="AD29" s="15">
+        <v>3638</v>
+      </c>
     </row>
     <row r="30" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="28">
@@ -31167,28 +31343,28 @@
       </c>
       <c r="D30" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E30" s="13">
         <v>0</v>
       </c>
       <c r="F30" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G30" s="13">
         <v>0</v>
       </c>
       <c r="H30" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I30" s="13">
         <v>0</v>
       </c>
       <c r="J30" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="13">
         <v>0</v>
@@ -31229,14 +31405,30 @@
         <f t="shared" si="9"/>
         <v>28</v>
       </c>
-      <c r="W30" s="15"/>
-      <c r="X30" s="15"/>
-      <c r="Y30" s="15"/>
-      <c r="Z30" s="15"/>
-      <c r="AA30" s="15"/>
-      <c r="AB30" s="15"/>
-      <c r="AC30" s="15"/>
-      <c r="AD30" s="15"/>
+      <c r="W30" s="15">
+        <v>10311</v>
+      </c>
+      <c r="X30" s="15">
+        <v>12871</v>
+      </c>
+      <c r="Y30" s="15">
+        <v>9632</v>
+      </c>
+      <c r="Z30" s="15">
+        <v>10858</v>
+      </c>
+      <c r="AA30" s="15">
+        <v>1287</v>
+      </c>
+      <c r="AB30" s="15">
+        <v>4051</v>
+      </c>
+      <c r="AC30" s="15">
+        <v>410</v>
+      </c>
+      <c r="AD30" s="15">
+        <v>3640</v>
+      </c>
     </row>
     <row r="31" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="28">
@@ -31251,21 +31443,21 @@
       </c>
       <c r="D31" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="E31" s="13">
         <v>0</v>
       </c>
       <c r="F31" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="G31" s="13">
         <v>0</v>
       </c>
       <c r="H31" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I31" s="13">
         <v>0</v>
@@ -31279,21 +31471,21 @@
       </c>
       <c r="L31" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="13">
         <v>0</v>
       </c>
       <c r="N31" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O31" s="13">
         <v>0</v>
       </c>
       <c r="P31" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q31" s="13">
         <v>0</v>
@@ -31303,7 +31495,7 @@
       </c>
       <c r="S31" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>81</v>
@@ -31313,14 +31505,30 @@
         <f t="shared" si="9"/>
         <v>29</v>
       </c>
-      <c r="W31" s="15"/>
-      <c r="X31" s="15"/>
-      <c r="Y31" s="15"/>
-      <c r="Z31" s="15"/>
-      <c r="AA31" s="15"/>
-      <c r="AB31" s="15"/>
-      <c r="AC31" s="15"/>
-      <c r="AD31" s="15"/>
+      <c r="W31" s="15">
+        <v>10320</v>
+      </c>
+      <c r="X31" s="15">
+        <v>12882</v>
+      </c>
+      <c r="Y31" s="15">
+        <v>9636</v>
+      </c>
+      <c r="Z31" s="15">
+        <v>10859</v>
+      </c>
+      <c r="AA31" s="15">
+        <v>1287</v>
+      </c>
+      <c r="AB31" s="15">
+        <v>4051</v>
+      </c>
+      <c r="AC31" s="15">
+        <v>410</v>
+      </c>
+      <c r="AD31" s="15">
+        <v>3640</v>
+      </c>
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="28">
@@ -31335,28 +31543,28 @@
       </c>
       <c r="D32" s="13">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E32" s="13">
         <v>0</v>
       </c>
       <c r="F32" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G32" s="13">
         <v>0</v>
       </c>
       <c r="H32" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I32" s="13">
         <v>0</v>
       </c>
       <c r="J32" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" s="13">
         <v>0</v>
@@ -31370,7 +31578,7 @@
       </c>
       <c r="N32" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O32" s="13">
         <v>0</v>
@@ -31386,8 +31594,8 @@
         <v>0</v>
       </c>
       <c r="S32" s="13">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>AD33-AD32</f>
+        <v>14</v>
       </c>
       <c r="T32" s="6"/>
       <c r="U32" s="4"/>
@@ -31395,25 +31603,61 @@
         <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="W32" s="15"/>
-      <c r="X32" s="15"/>
-      <c r="Y32" s="15"/>
-      <c r="Z32" s="15"/>
-      <c r="AA32" s="15"/>
-      <c r="AB32" s="15"/>
-      <c r="AC32" s="15"/>
-      <c r="AD32" s="15"/>
+      <c r="W32" s="15">
+        <v>10456</v>
+      </c>
+      <c r="X32" s="15">
+        <v>13010</v>
+      </c>
+      <c r="Y32" s="15">
+        <v>9639</v>
+      </c>
+      <c r="Z32" s="15">
+        <v>10859</v>
+      </c>
+      <c r="AA32" s="15">
+        <v>1288</v>
+      </c>
+      <c r="AB32" s="15">
+        <v>4063</v>
+      </c>
+      <c r="AC32" s="15">
+        <v>412</v>
+      </c>
+      <c r="AD32" s="15">
+        <v>3651</v>
+      </c>
     </row>
     <row r="33" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="U33" s="4"/>
-      <c r="W33" s="15"/>
-      <c r="X33" s="15"/>
-      <c r="Y33" s="15"/>
-      <c r="Z33" s="15"/>
-      <c r="AA33" s="15"/>
-      <c r="AB33" s="15"/>
-      <c r="AC33" s="15"/>
-      <c r="AD33" s="15"/>
+      <c r="V33" s="18">
+        <f t="shared" si="9"/>
+        <v>31</v>
+      </c>
+      <c r="W33" s="15">
+        <v>10491</v>
+      </c>
+      <c r="X33" s="15">
+        <v>13042</v>
+      </c>
+      <c r="Y33" s="15">
+        <v>9644</v>
+      </c>
+      <c r="Z33" s="15">
+        <v>10861</v>
+      </c>
+      <c r="AA33" s="15">
+        <v>1288</v>
+      </c>
+      <c r="AB33" s="15">
+        <v>4067</v>
+      </c>
+      <c r="AC33" s="15">
+        <v>412</v>
+      </c>
+      <c r="AD33" s="15">
+        <v>3665</v>
+      </c>
     </row>
     <row r="35" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2CBD53-5D46-4B58-9148-D8BE62EACF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C60820-4B8C-4DAB-834D-BC4FF39321A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -320,12 +320,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="165" formatCode="_-&quot;R$ &quot;* #,##0.00_-;&quot;-R$ &quot;* #,##0.00_-;_-&quot;R$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-&quot;R$ &quot;* #,##0.000_-;&quot;-R$ &quot;* #,##0.000_-;_-&quot;R$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="[$R$ -416]#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;???_-;_-@_-"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -534,7 +536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -667,6 +669,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -28416,7 +28430,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AG102"/>
+  <dimension ref="A1:AN102"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -28429,9 +28443,11 @@
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
     <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="23" customWidth="1"/>
+    <col min="36" max="36" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -28527,7 +28543,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>45870</v>
       </c>
@@ -28590,7 +28606,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="13">
-        <f t="shared" ref="S2:S32" si="6">AD3-AD2</f>
+        <f t="shared" ref="S2:S31" si="6">AD3-AD2</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -28625,14 +28641,17 @@
         <v>3537</v>
       </c>
       <c r="AF2" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AG2" s="11">
         <f t="array" ref="AG2">_xlfn.IFS(AF2="Verde",0,AF2="Amarela",1.885,AF2="Vermelha P1",4.463,AF2="Vermelha P2",7.877)</f>
-        <v>4.4630000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+        <v>7.8769999999999998</v>
+      </c>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
+    </row>
+    <row r="3" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="28">
         <f t="shared" ref="A3:A32" si="7">A2+1</f>
         <v>45871</v>
@@ -28730,8 +28749,11 @@
       <c r="AD3" s="15">
         <v>3537</v>
       </c>
-    </row>
-    <row r="4" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AI3" s="50"/>
+      <c r="AJ3" s="51"/>
+      <c r="AK3" s="51"/>
+    </row>
+    <row r="4" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="28">
         <f t="shared" si="7"/>
         <v>45872</v>
@@ -28830,8 +28852,11 @@
       <c r="AD4" s="15">
         <v>3537</v>
       </c>
-    </row>
-    <row r="5" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AI4" s="50"/>
+      <c r="AJ4" s="51"/>
+      <c r="AK4" s="51"/>
+    </row>
+    <row r="5" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="28">
         <f t="shared" si="7"/>
         <v>45873</v>
@@ -28930,8 +28955,11 @@
       <c r="AD5" s="15">
         <v>3537</v>
       </c>
-    </row>
-    <row r="6" spans="1:33" ht="51" x14ac:dyDescent="0.2">
+      <c r="AI5" s="50"/>
+      <c r="AJ5" s="51"/>
+      <c r="AK5" s="51"/>
+    </row>
+    <row r="6" spans="1:40" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="28">
         <f t="shared" si="7"/>
         <v>45874</v>
@@ -29030,8 +29058,11 @@
       <c r="AD6" s="6">
         <v>3551</v>
       </c>
-    </row>
-    <row r="7" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AI6" s="50"/>
+      <c r="AJ6" s="51"/>
+      <c r="AK6" s="51"/>
+    </row>
+    <row r="7" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="28">
         <f t="shared" si="7"/>
         <v>45875</v>
@@ -29130,8 +29161,10 @@
       <c r="AD7" s="6">
         <v>3553</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AJ7" s="51"/>
+      <c r="AK7" s="51"/>
+    </row>
+    <row r="8" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="28">
         <f t="shared" si="7"/>
         <v>45876</v>
@@ -29230,8 +29263,14 @@
       <c r="AD8" s="6">
         <v>3558</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AH8" s="52"/>
+      <c r="AI8" s="52"/>
+      <c r="AJ8" s="52"/>
+      <c r="AK8" s="53"/>
+      <c r="AL8" s="53"/>
+      <c r="AM8" s="53"/>
+    </row>
+    <row r="9" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="28">
         <f t="shared" si="7"/>
         <v>45877</v>
@@ -29330,8 +29369,13 @@
       <c r="AD9" s="6">
         <v>3561</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AH9" s="50"/>
+      <c r="AI9" s="50"/>
+      <c r="AL9" s="51"/>
+      <c r="AM9" s="54"/>
+      <c r="AN9" s="54"/>
+    </row>
+    <row r="10" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="28">
         <f t="shared" si="7"/>
         <v>45878</v>
@@ -29430,8 +29474,13 @@
       <c r="AD10" s="6">
         <v>3568</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="AH10" s="50"/>
+      <c r="AI10" s="50"/>
+      <c r="AL10" s="51"/>
+      <c r="AM10" s="54"/>
+      <c r="AN10" s="54"/>
+    </row>
+    <row r="11" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="28">
         <f t="shared" si="7"/>
         <v>45879</v>
@@ -29530,8 +29579,13 @@
       <c r="AD11" s="6">
         <v>3568</v>
       </c>
-    </row>
-    <row r="12" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AH11" s="50"/>
+      <c r="AI11" s="50"/>
+      <c r="AL11" s="51"/>
+      <c r="AM11" s="54"/>
+      <c r="AN11" s="54"/>
+    </row>
+    <row r="12" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A12" s="28">
         <f t="shared" si="7"/>
         <v>45880</v>
@@ -29630,8 +29684,13 @@
       <c r="AD12" s="6">
         <v>3572</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AH12" s="50"/>
+      <c r="AI12" s="50"/>
+      <c r="AL12" s="51"/>
+      <c r="AM12" s="54"/>
+      <c r="AN12" s="54"/>
+    </row>
+    <row r="13" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
         <f t="shared" si="7"/>
         <v>45881</v>
@@ -29730,8 +29789,13 @@
       <c r="AD13" s="15">
         <v>3572</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AH13" s="50"/>
+      <c r="AI13" s="50"/>
+      <c r="AL13" s="51"/>
+      <c r="AM13" s="54"/>
+      <c r="AN13" s="54"/>
+    </row>
+    <row r="14" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A14" s="28">
         <f t="shared" si="7"/>
         <v>45882</v>
@@ -29830,8 +29894,9 @@
       <c r="AD14" s="6">
         <v>3581</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AN14" s="54"/>
+    </row>
+    <row r="15" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A15" s="28">
         <f t="shared" si="7"/>
         <v>45883</v>
@@ -29929,8 +29994,9 @@
       <c r="AD15" s="6">
         <v>3581</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AI15" s="55"/>
+    </row>
+    <row r="16" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A16" s="28">
         <f t="shared" si="7"/>
         <v>45884</v>
@@ -32311,7 +32377,9 @@
       <c r="I102" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="AK8:AM8"/>
     <mergeCell ref="A100:I100"/>
     <mergeCell ref="B35:I35"/>
     <mergeCell ref="A70:I70"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C60820-4B8C-4DAB-834D-BC4FF39321A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A270C7E4-9A9E-4F8C-AD5C-7CDED42FD258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -662,6 +662,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -670,17 +676,11 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -4896,15 +4896,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="47"/>
-      <c r="B69" s="47"/>
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="47"/>
-      <c r="G69" s="47"/>
-      <c r="H69" s="47"/>
-      <c r="I69" s="47"/>
+      <c r="A69" s="51"/>
+      <c r="B69" s="51"/>
+      <c r="C69" s="51"/>
+      <c r="D69" s="51"/>
+      <c r="E69" s="51"/>
+      <c r="F69" s="51"/>
+      <c r="G69" s="51"/>
+      <c r="H69" s="51"/>
+      <c r="I69" s="51"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -4929,15 +4929,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="48"/>
-      <c r="B74" s="48"/>
-      <c r="C74" s="48"/>
-      <c r="D74" s="48"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="48"/>
-      <c r="G74" s="48"/>
-      <c r="H74" s="48"/>
-      <c r="I74" s="48"/>
+      <c r="A74" s="52"/>
+      <c r="B74" s="52"/>
+      <c r="C74" s="52"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="52"/>
+      <c r="F74" s="52"/>
+      <c r="G74" s="52"/>
+      <c r="H74" s="52"/>
+      <c r="I74" s="52"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -4973,15 +4973,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="49"/>
-      <c r="B78" s="49"/>
-      <c r="C78" s="49"/>
-      <c r="D78" s="49"/>
-      <c r="E78" s="49"/>
-      <c r="F78" s="49"/>
-      <c r="G78" s="49"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="49"/>
+      <c r="A78" s="53"/>
+      <c r="B78" s="53"/>
+      <c r="C78" s="53"/>
+      <c r="D78" s="53"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53"/>
+      <c r="H78" s="53"/>
+      <c r="I78" s="53"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -5017,15 +5017,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="48"/>
-      <c r="B86" s="48"/>
-      <c r="C86" s="48"/>
-      <c r="D86" s="48"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="48"/>
-      <c r="G86" s="48"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="48"/>
+      <c r="A86" s="52"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="52"/>
+      <c r="D86" s="52"/>
+      <c r="E86" s="52"/>
+      <c r="F86" s="52"/>
+      <c r="G86" s="52"/>
+      <c r="H86" s="52"/>
+      <c r="I86" s="52"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -5128,15 +5128,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="47"/>
-      <c r="B99" s="47"/>
-      <c r="C99" s="47"/>
-      <c r="D99" s="47"/>
-      <c r="E99" s="47"/>
-      <c r="F99" s="47"/>
-      <c r="G99" s="47"/>
-      <c r="H99" s="47"/>
-      <c r="I99" s="47"/>
+      <c r="A99" s="51"/>
+      <c r="B99" s="51"/>
+      <c r="C99" s="51"/>
+      <c r="D99" s="51"/>
+      <c r="E99" s="51"/>
+      <c r="F99" s="51"/>
+      <c r="G99" s="51"/>
+      <c r="H99" s="51"/>
+      <c r="I99" s="51"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -8336,14 +8336,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -8720,15 +8720,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="47"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="47"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="47"/>
-      <c r="I71" s="47"/>
+      <c r="A71" s="51"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="51"/>
+      <c r="D71" s="51"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="51"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="51"/>
+      <c r="I71" s="51"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -8753,15 +8753,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="48"/>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -8797,15 +8797,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="49"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49"/>
+      <c r="A80" s="53"/>
+      <c r="B80" s="53"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -8841,15 +8841,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="48"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
+      <c r="A88" s="52"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="52"/>
+      <c r="G88" s="52"/>
+      <c r="H88" s="52"/>
+      <c r="I88" s="52"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -8952,15 +8952,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="47"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="47"/>
-      <c r="D101" s="47"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="47"/>
-      <c r="G101" s="47"/>
-      <c r="H101" s="47"/>
-      <c r="I101" s="47"/>
+      <c r="A101" s="51"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="51"/>
+      <c r="G101" s="51"/>
+      <c r="H101" s="51"/>
+      <c r="I101" s="51"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -11334,14 +11334,14 @@
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="47"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="51"/>
       <c r="T32" s="27"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
@@ -11719,15 +11719,15 @@
       <c r="I66" s="1"/>
     </row>
     <row r="67" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="47"/>
-      <c r="B67" s="47"/>
-      <c r="C67" s="47"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="47"/>
-      <c r="G67" s="47"/>
-      <c r="H67" s="47"/>
-      <c r="I67" s="47"/>
+      <c r="A67" s="51"/>
+      <c r="B67" s="51"/>
+      <c r="C67" s="51"/>
+      <c r="D67" s="51"/>
+      <c r="E67" s="51"/>
+      <c r="F67" s="51"/>
+      <c r="G67" s="51"/>
+      <c r="H67" s="51"/>
+      <c r="I67" s="51"/>
     </row>
     <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
@@ -11752,15 +11752,15 @@
       <c r="I69" s="23"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="48"/>
-      <c r="B72" s="48"/>
-      <c r="C72" s="48"/>
-      <c r="D72" s="48"/>
-      <c r="E72" s="48"/>
-      <c r="F72" s="48"/>
-      <c r="G72" s="48"/>
-      <c r="H72" s="48"/>
-      <c r="I72" s="48"/>
+      <c r="A72" s="52"/>
+      <c r="B72" s="52"/>
+      <c r="C72" s="52"/>
+      <c r="D72" s="52"/>
+      <c r="E72" s="52"/>
+      <c r="F72" s="52"/>
+      <c r="G72" s="52"/>
+      <c r="H72" s="52"/>
+      <c r="I72" s="52"/>
     </row>
     <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
@@ -11796,15 +11796,15 @@
       <c r="I75" s="25"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="49"/>
-      <c r="B76" s="49"/>
-      <c r="C76" s="49"/>
-      <c r="D76" s="49"/>
-      <c r="E76" s="49"/>
-      <c r="F76" s="49"/>
-      <c r="G76" s="49"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="49"/>
+      <c r="A76" s="53"/>
+      <c r="B76" s="53"/>
+      <c r="C76" s="53"/>
+      <c r="D76" s="53"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
+      <c r="H76" s="53"/>
+      <c r="I76" s="53"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -11840,15 +11840,15 @@
       <c r="B82" s="23"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="48"/>
-      <c r="B84" s="48"/>
-      <c r="C84" s="48"/>
-      <c r="D84" s="48"/>
-      <c r="E84" s="48"/>
-      <c r="F84" s="48"/>
-      <c r="G84" s="48"/>
-      <c r="H84" s="48"/>
-      <c r="I84" s="48"/>
+      <c r="A84" s="52"/>
+      <c r="B84" s="52"/>
+      <c r="C84" s="52"/>
+      <c r="D84" s="52"/>
+      <c r="E84" s="52"/>
+      <c r="F84" s="52"/>
+      <c r="G84" s="52"/>
+      <c r="H84" s="52"/>
+      <c r="I84" s="52"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
@@ -11951,15 +11951,15 @@
       <c r="B95" s="26"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="47"/>
-      <c r="B97" s="47"/>
-      <c r="C97" s="47"/>
-      <c r="D97" s="47"/>
-      <c r="E97" s="47"/>
-      <c r="F97" s="47"/>
-      <c r="G97" s="47"/>
-      <c r="H97" s="47"/>
-      <c r="I97" s="47"/>
+      <c r="A97" s="51"/>
+      <c r="B97" s="51"/>
+      <c r="C97" s="51"/>
+      <c r="D97" s="51"/>
+      <c r="E97" s="51"/>
+      <c r="F97" s="51"/>
+      <c r="G97" s="51"/>
+      <c r="H97" s="51"/>
+      <c r="I97" s="51"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
@@ -14509,14 +14509,14 @@
     <row r="34" spans="1:21" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
     </row>
     <row r="37" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -14893,15 +14893,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="47"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="47"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="47"/>
-      <c r="I71" s="47"/>
+      <c r="A71" s="51"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="51"/>
+      <c r="D71" s="51"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="51"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="51"/>
+      <c r="I71" s="51"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -14926,15 +14926,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="48"/>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -14970,15 +14970,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="49"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49"/>
+      <c r="A80" s="53"/>
+      <c r="B80" s="53"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -15014,15 +15014,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="48"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
+      <c r="A88" s="52"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="52"/>
+      <c r="G88" s="52"/>
+      <c r="H88" s="52"/>
+      <c r="I88" s="52"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -15125,15 +15125,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="47"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="47"/>
-      <c r="D101" s="47"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="47"/>
-      <c r="G101" s="47"/>
-      <c r="H101" s="47"/>
-      <c r="I101" s="47"/>
+      <c r="A101" s="51"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="51"/>
+      <c r="G101" s="51"/>
+      <c r="H101" s="51"/>
+      <c r="I101" s="51"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -17868,14 +17868,14 @@
     </row>
     <row r="35" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
     </row>
     <row r="36" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -18253,15 +18253,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="47"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="47"/>
-      <c r="F70" s="47"/>
-      <c r="G70" s="47"/>
-      <c r="H70" s="47"/>
-      <c r="I70" s="47"/>
+      <c r="A70" s="51"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="51"/>
+      <c r="I70" s="51"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -18286,15 +18286,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="48"/>
-      <c r="B75" s="48"/>
-      <c r="C75" s="48"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
+      <c r="A75" s="52"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="F75" s="52"/>
+      <c r="G75" s="52"/>
+      <c r="H75" s="52"/>
+      <c r="I75" s="52"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -18330,15 +18330,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="49"/>
-      <c r="B79" s="49"/>
-      <c r="C79" s="49"/>
-      <c r="D79" s="49"/>
-      <c r="E79" s="49"/>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49"/>
+      <c r="A79" s="53"/>
+      <c r="B79" s="53"/>
+      <c r="C79" s="53"/>
+      <c r="D79" s="53"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
+      <c r="H79" s="53"/>
+      <c r="I79" s="53"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -18374,15 +18374,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="48"/>
-      <c r="B87" s="48"/>
-      <c r="C87" s="48"/>
-      <c r="D87" s="48"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48"/>
+      <c r="A87" s="52"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="52"/>
+      <c r="E87" s="52"/>
+      <c r="F87" s="52"/>
+      <c r="G87" s="52"/>
+      <c r="H87" s="52"/>
+      <c r="I87" s="52"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -18485,15 +18485,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="47"/>
-      <c r="B100" s="47"/>
-      <c r="C100" s="47"/>
-      <c r="D100" s="47"/>
-      <c r="E100" s="47"/>
-      <c r="F100" s="47"/>
-      <c r="G100" s="47"/>
-      <c r="H100" s="47"/>
-      <c r="I100" s="47"/>
+      <c r="A100" s="51"/>
+      <c r="B100" s="51"/>
+      <c r="C100" s="51"/>
+      <c r="D100" s="51"/>
+      <c r="E100" s="51"/>
+      <c r="F100" s="51"/>
+      <c r="G100" s="51"/>
+      <c r="H100" s="51"/>
+      <c r="I100" s="51"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -21120,14 +21120,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -21505,15 +21505,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="47"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="47"/>
-      <c r="F70" s="47"/>
-      <c r="G70" s="47"/>
-      <c r="H70" s="47"/>
-      <c r="I70" s="47"/>
+      <c r="A70" s="51"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="51"/>
+      <c r="I70" s="51"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -21538,15 +21538,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="48"/>
-      <c r="B75" s="48"/>
-      <c r="C75" s="48"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
+      <c r="A75" s="52"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="F75" s="52"/>
+      <c r="G75" s="52"/>
+      <c r="H75" s="52"/>
+      <c r="I75" s="52"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -21582,15 +21582,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="49"/>
-      <c r="B79" s="49"/>
-      <c r="C79" s="49"/>
-      <c r="D79" s="49"/>
-      <c r="E79" s="49"/>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49"/>
+      <c r="A79" s="53"/>
+      <c r="B79" s="53"/>
+      <c r="C79" s="53"/>
+      <c r="D79" s="53"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
+      <c r="H79" s="53"/>
+      <c r="I79" s="53"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -21626,15 +21626,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="48"/>
-      <c r="B87" s="48"/>
-      <c r="C87" s="48"/>
-      <c r="D87" s="48"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48"/>
+      <c r="A87" s="52"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="52"/>
+      <c r="E87" s="52"/>
+      <c r="F87" s="52"/>
+      <c r="G87" s="52"/>
+      <c r="H87" s="52"/>
+      <c r="I87" s="52"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -21737,15 +21737,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="47"/>
-      <c r="B100" s="47"/>
-      <c r="C100" s="47"/>
-      <c r="D100" s="47"/>
-      <c r="E100" s="47"/>
-      <c r="F100" s="47"/>
-      <c r="G100" s="47"/>
-      <c r="H100" s="47"/>
-      <c r="I100" s="47"/>
+      <c r="A100" s="51"/>
+      <c r="B100" s="51"/>
+      <c r="C100" s="51"/>
+      <c r="D100" s="51"/>
+      <c r="E100" s="51"/>
+      <c r="F100" s="51"/>
+      <c r="G100" s="51"/>
+      <c r="H100" s="51"/>
+      <c r="I100" s="51"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -24448,14 +24448,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -24833,15 +24833,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="47"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="47"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="47"/>
-      <c r="I71" s="47"/>
+      <c r="A71" s="51"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="51"/>
+      <c r="D71" s="51"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="51"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="51"/>
+      <c r="I71" s="51"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -24866,15 +24866,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="48"/>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -24910,15 +24910,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="49"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49"/>
+      <c r="A80" s="53"/>
+      <c r="B80" s="53"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -24954,15 +24954,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="48"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
+      <c r="A88" s="52"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="52"/>
+      <c r="G88" s="52"/>
+      <c r="H88" s="52"/>
+      <c r="I88" s="52"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -25065,15 +25065,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="47"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="47"/>
-      <c r="D101" s="47"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="47"/>
-      <c r="G101" s="47"/>
-      <c r="H101" s="47"/>
-      <c r="I101" s="47"/>
+      <c r="A101" s="51"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="51"/>
+      <c r="G101" s="51"/>
+      <c r="H101" s="51"/>
+      <c r="I101" s="51"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -25148,7 +25148,7 @@
     <col min="7" max="7" width="13.42578125" customWidth="1"/>
     <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="12" max="12" width="3.42578125" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
@@ -25442,49 +25442,49 @@
       </c>
       <c r="D4" s="6">
         <f t="shared" si="0"/>
-        <v>-10596</v>
+        <v>83</v>
       </c>
       <c r="E4" s="6">
         <v>0</v>
       </c>
       <c r="F4" s="6">
         <f t="shared" si="1"/>
-        <v>-13112</v>
+        <v>53</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
       </c>
       <c r="H4" s="6">
         <f t="shared" si="2"/>
-        <v>-9654</v>
+        <v>4</v>
       </c>
       <c r="I4" s="6">
         <v>0</v>
       </c>
       <c r="J4" s="6">
         <f t="shared" si="3"/>
-        <v>-10862</v>
+        <v>1</v>
       </c>
       <c r="K4" s="6">
         <v>0</v>
       </c>
       <c r="L4" s="6">
         <f t="shared" si="4"/>
-        <v>-1288</v>
+        <v>0</v>
       </c>
       <c r="M4" s="6">
         <v>0</v>
       </c>
       <c r="N4" s="6">
         <f t="shared" si="5"/>
-        <v>-4076</v>
+        <v>4</v>
       </c>
       <c r="O4" s="6">
         <v>0</v>
       </c>
       <c r="P4" s="6">
         <f t="shared" si="6"/>
-        <v>-413</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="6">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="S4" s="6">
         <f t="shared" si="7"/>
-        <v>-3663</v>
+        <v>3</v>
       </c>
       <c r="T4" s="6"/>
       <c r="U4" s="4"/>
@@ -25539,49 +25539,49 @@
       </c>
       <c r="D5" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-10679</v>
       </c>
       <c r="E5" s="6">
         <v>0</v>
       </c>
       <c r="F5" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-13165</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
       </c>
       <c r="H5" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9658</v>
       </c>
       <c r="I5" s="6">
         <v>0</v>
       </c>
       <c r="J5" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-10863</v>
       </c>
       <c r="K5" s="6">
         <v>0</v>
       </c>
       <c r="L5" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1288</v>
       </c>
       <c r="M5" s="6">
         <v>0</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4080</v>
       </c>
       <c r="O5" s="6">
         <v>0</v>
       </c>
       <c r="P5" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-413</v>
       </c>
       <c r="Q5" s="6">
         <v>0</v>
@@ -25591,7 +25591,7 @@
       </c>
       <c r="S5" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3666</v>
       </c>
       <c r="T5" s="6"/>
       <c r="U5" s="4"/>
@@ -25599,14 +25599,30 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
+      <c r="W5" s="6">
+        <v>10679</v>
+      </c>
+      <c r="X5" s="6">
+        <v>13165</v>
+      </c>
+      <c r="Y5" s="6">
+        <v>9658</v>
+      </c>
+      <c r="Z5" s="6">
+        <v>10863</v>
+      </c>
+      <c r="AA5" s="6">
+        <v>1288</v>
+      </c>
+      <c r="AB5" s="6">
+        <v>4080</v>
+      </c>
+      <c r="AC5" s="6">
+        <v>413</v>
+      </c>
+      <c r="AD5" s="6">
+        <v>3666</v>
+      </c>
     </row>
     <row r="6" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
@@ -27741,14 +27757,14 @@
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="47"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="51"/>
+      <c r="I34" s="51"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
@@ -28126,15 +28142,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="47"/>
-      <c r="B69" s="47"/>
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="47"/>
-      <c r="G69" s="47"/>
-      <c r="H69" s="47"/>
-      <c r="I69" s="47"/>
+      <c r="A69" s="51"/>
+      <c r="B69" s="51"/>
+      <c r="C69" s="51"/>
+      <c r="D69" s="51"/>
+      <c r="E69" s="51"/>
+      <c r="F69" s="51"/>
+      <c r="G69" s="51"/>
+      <c r="H69" s="51"/>
+      <c r="I69" s="51"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -28159,15 +28175,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="48"/>
-      <c r="B74" s="48"/>
-      <c r="C74" s="48"/>
-      <c r="D74" s="48"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="48"/>
-      <c r="G74" s="48"/>
-      <c r="H74" s="48"/>
-      <c r="I74" s="48"/>
+      <c r="A74" s="52"/>
+      <c r="B74" s="52"/>
+      <c r="C74" s="52"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="52"/>
+      <c r="F74" s="52"/>
+      <c r="G74" s="52"/>
+      <c r="H74" s="52"/>
+      <c r="I74" s="52"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -28203,15 +28219,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="49"/>
-      <c r="B78" s="49"/>
-      <c r="C78" s="49"/>
-      <c r="D78" s="49"/>
-      <c r="E78" s="49"/>
-      <c r="F78" s="49"/>
-      <c r="G78" s="49"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="49"/>
+      <c r="A78" s="53"/>
+      <c r="B78" s="53"/>
+      <c r="C78" s="53"/>
+      <c r="D78" s="53"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53"/>
+      <c r="H78" s="53"/>
+      <c r="I78" s="53"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -28247,15 +28263,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="48"/>
-      <c r="B86" s="48"/>
-      <c r="C86" s="48"/>
-      <c r="D86" s="48"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="48"/>
-      <c r="G86" s="48"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="48"/>
+      <c r="A86" s="52"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="52"/>
+      <c r="D86" s="52"/>
+      <c r="E86" s="52"/>
+      <c r="F86" s="52"/>
+      <c r="G86" s="52"/>
+      <c r="H86" s="52"/>
+      <c r="I86" s="52"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -28358,15 +28374,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="47"/>
-      <c r="B99" s="47"/>
-      <c r="C99" s="47"/>
-      <c r="D99" s="47"/>
-      <c r="E99" s="47"/>
-      <c r="F99" s="47"/>
-      <c r="G99" s="47"/>
-      <c r="H99" s="47"/>
-      <c r="I99" s="47"/>
+      <c r="A99" s="51"/>
+      <c r="B99" s="51"/>
+      <c r="C99" s="51"/>
+      <c r="D99" s="51"/>
+      <c r="E99" s="51"/>
+      <c r="F99" s="51"/>
+      <c r="G99" s="51"/>
+      <c r="H99" s="51"/>
+      <c r="I99" s="51"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -28547,11 +28563,11 @@
       <c r="A2" s="5">
         <v>45870</v>
       </c>
-      <c r="B2" s="13">
-        <v>0</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0</v>
+      <c r="B2" s="29">
+        <v>1050.20999953</v>
+      </c>
+      <c r="C2" s="29">
+        <v>185.30399991000002</v>
       </c>
       <c r="D2" s="13">
         <f>W3-W2</f>
@@ -28588,15 +28604,14 @@
       <c r="M2" s="13">
         <v>0</v>
       </c>
-      <c r="N2" s="13">
-        <f t="shared" ref="N2:N32" si="4">AB3-AB2</f>
-        <v>0</v>
-      </c>
-      <c r="O2" s="13">
-        <v>0</v>
+      <c r="N2" s="29">
+        <v>250.15199932999991</v>
+      </c>
+      <c r="O2" s="29">
+        <v>55.439999880000009</v>
       </c>
       <c r="P2" s="13">
-        <f t="shared" ref="P2:P32" si="5">AC3-AC2</f>
+        <f t="shared" ref="P2:P32" si="4">AC3-AC2</f>
         <v>0</v>
       </c>
       <c r="Q2" s="13">
@@ -28606,7 +28621,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="13">
-        <f t="shared" ref="S2:S31" si="6">AD3-AD2</f>
+        <f t="shared" ref="S2:S31" si="5">AD3-AD2</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -28647,23 +28662,23 @@
         <f t="array" ref="AG2">_xlfn.IFS(AF2="Verde",0,AF2="Amarela",1.885,AF2="Vermelha P1",4.463,AF2="Vermelha P2",7.877)</f>
         <v>7.8769999999999998</v>
       </c>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
+      <c r="AI2" s="47"/>
+      <c r="AJ2" s="48"/>
+      <c r="AK2" s="48"/>
     </row>
     <row r="3" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="28">
-        <f t="shared" ref="A3:A32" si="7">A2+1</f>
+        <f t="shared" ref="A3:A32" si="6">A2+1</f>
         <v>45871</v>
       </c>
-      <c r="B3" s="13">
-        <v>0</v>
-      </c>
-      <c r="C3" s="13">
-        <v>0</v>
+      <c r="B3" s="29">
+        <v>981.91799947000027</v>
+      </c>
+      <c r="C3" s="29">
+        <v>175.93799990000002</v>
       </c>
       <c r="D3" s="13">
-        <f t="shared" ref="D3:D32" si="8">W4-W3</f>
+        <f t="shared" ref="D3:D32" si="7">W4-W3</f>
         <v>0</v>
       </c>
       <c r="E3" s="13">
@@ -28697,25 +28712,24 @@
       <c r="M3" s="13">
         <v>0</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="29">
+        <v>269.23199937999982</v>
+      </c>
+      <c r="O3" s="29">
+        <v>58.75199988</v>
+      </c>
+      <c r="P3" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O3" s="13">
-        <v>0</v>
-      </c>
-      <c r="P3" s="13">
+      <c r="Q3" s="13">
+        <v>0</v>
+      </c>
+      <c r="R3" s="13">
+        <v>0</v>
+      </c>
+      <c r="S3" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="13">
-        <v>0</v>
-      </c>
-      <c r="R3" s="13">
-        <v>0</v>
-      </c>
-      <c r="S3" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -28749,23 +28763,23 @@
       <c r="AD3" s="15">
         <v>3537</v>
       </c>
-      <c r="AI3" s="50"/>
-      <c r="AJ3" s="51"/>
-      <c r="AK3" s="51"/>
+      <c r="AI3" s="47"/>
+      <c r="AJ3" s="48"/>
+      <c r="AK3" s="48"/>
     </row>
     <row r="4" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="28">
+        <f t="shared" si="6"/>
+        <v>45872</v>
+      </c>
+      <c r="B4" s="29">
+        <v>909.46799953999994</v>
+      </c>
+      <c r="C4" s="29">
+        <v>151.15799993000002</v>
+      </c>
+      <c r="D4" s="13">
         <f t="shared" si="7"/>
-        <v>45872</v>
-      </c>
-      <c r="B4" s="13">
-        <v>0</v>
-      </c>
-      <c r="C4" s="13">
-        <v>0</v>
-      </c>
-      <c r="D4" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E4" s="13">
@@ -28799,25 +28813,24 @@
       <c r="M4" s="13">
         <v>0</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="29">
+        <v>251.61599932999988</v>
+      </c>
+      <c r="O4" s="29">
+        <v>49.031999909999996</v>
+      </c>
+      <c r="P4" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O4" s="13">
-        <v>0</v>
-      </c>
-      <c r="P4" s="13">
+      <c r="Q4" s="13">
+        <v>0</v>
+      </c>
+      <c r="R4" s="13">
+        <v>0</v>
+      </c>
+      <c r="S4" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>0</v>
-      </c>
-      <c r="R4" s="13">
-        <v>0</v>
-      </c>
-      <c r="S4" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -28825,7 +28838,7 @@
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="14">
-        <f t="shared" ref="V4:V33" si="9">V3+1</f>
+        <f t="shared" ref="V4:V33" si="8">V3+1</f>
         <v>2</v>
       </c>
       <c r="W4" s="15">
@@ -28852,23 +28865,23 @@
       <c r="AD4" s="15">
         <v>3537</v>
       </c>
-      <c r="AI4" s="50"/>
-      <c r="AJ4" s="51"/>
-      <c r="AK4" s="51"/>
+      <c r="AI4" s="47"/>
+      <c r="AJ4" s="48"/>
+      <c r="AK4" s="48"/>
     </row>
     <row r="5" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="28">
+        <f t="shared" si="6"/>
+        <v>45873</v>
+      </c>
+      <c r="B5" s="29">
+        <v>1187.92799952</v>
+      </c>
+      <c r="C5" s="29">
+        <v>176.39999990000001</v>
+      </c>
+      <c r="D5" s="13">
         <f t="shared" si="7"/>
-        <v>45873</v>
-      </c>
-      <c r="B5" s="13">
-        <v>0</v>
-      </c>
-      <c r="C5" s="13">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13">
-        <f t="shared" si="8"/>
         <v>147</v>
       </c>
       <c r="E5" s="13">
@@ -28902,25 +28915,24 @@
       <c r="M5" s="13">
         <v>0</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="29">
+        <v>273.88799932999984</v>
+      </c>
+      <c r="O5" s="29">
+        <v>59.375999899999997</v>
+      </c>
+      <c r="P5" s="13">
         <f t="shared" si="4"/>
-        <v>16</v>
-      </c>
-      <c r="O5" s="13">
-        <v>0</v>
-      </c>
-      <c r="P5" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>0</v>
+      </c>
+      <c r="R5" s="13">
+        <v>0</v>
+      </c>
+      <c r="S5" s="13">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>0</v>
-      </c>
-      <c r="R5" s="13">
-        <v>0</v>
-      </c>
-      <c r="S5" s="13">
-        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -28928,7 +28940,7 @@
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="W5" s="15">
@@ -28955,23 +28967,23 @@
       <c r="AD5" s="15">
         <v>3537</v>
       </c>
-      <c r="AI5" s="50"/>
-      <c r="AJ5" s="51"/>
-      <c r="AK5" s="51"/>
+      <c r="AI5" s="47"/>
+      <c r="AJ5" s="48"/>
+      <c r="AK5" s="48"/>
     </row>
     <row r="6" spans="1:40" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="28">
+        <f t="shared" si="6"/>
+        <v>45874</v>
+      </c>
+      <c r="B6" s="29">
+        <v>1195.6979995199993</v>
+      </c>
+      <c r="C6" s="29">
+        <v>178.2479999</v>
+      </c>
+      <c r="D6" s="13">
         <f t="shared" si="7"/>
-        <v>45874</v>
-      </c>
-      <c r="B6" s="13">
-        <v>0</v>
-      </c>
-      <c r="C6" s="13">
-        <v>0</v>
-      </c>
-      <c r="D6" s="13">
-        <f t="shared" si="8"/>
         <v>43</v>
       </c>
       <c r="E6" s="13">
@@ -29005,25 +29017,24 @@
       <c r="M6" s="13">
         <v>0</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="29">
+        <v>263.99999931999992</v>
+      </c>
+      <c r="O6" s="29">
+        <v>52.079999899999997</v>
+      </c>
+      <c r="P6" s="13">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="O6" s="13">
-        <v>0</v>
-      </c>
-      <c r="P6" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>0</v>
+      </c>
+      <c r="R6" s="13">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>0</v>
-      </c>
-      <c r="R6" s="13">
-        <v>0</v>
-      </c>
-      <c r="S6" s="13">
-        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -29031,7 +29042,7 @@
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="W6" s="6">
@@ -29058,23 +29069,23 @@
       <c r="AD6" s="6">
         <v>3551</v>
       </c>
-      <c r="AI6" s="50"/>
-      <c r="AJ6" s="51"/>
-      <c r="AK6" s="51"/>
+      <c r="AI6" s="47"/>
+      <c r="AJ6" s="48"/>
+      <c r="AK6" s="48"/>
     </row>
     <row r="7" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="28">
+        <f t="shared" si="6"/>
+        <v>45875</v>
+      </c>
+      <c r="B7" s="29">
+        <v>975.44999952999933</v>
+      </c>
+      <c r="C7" s="29">
+        <v>182.0279999</v>
+      </c>
+      <c r="D7" s="13">
         <f t="shared" si="7"/>
-        <v>45875</v>
-      </c>
-      <c r="B7" s="13">
-        <v>0</v>
-      </c>
-      <c r="C7" s="13">
-        <v>0</v>
-      </c>
-      <c r="D7" s="13">
-        <f t="shared" si="8"/>
         <v>61</v>
       </c>
       <c r="E7" s="13">
@@ -29108,25 +29119,24 @@
       <c r="M7" s="13">
         <v>0</v>
       </c>
-      <c r="N7" s="13">
+      <c r="N7" s="29">
+        <v>269.03999940999984</v>
+      </c>
+      <c r="O7" s="29">
+        <v>52.05599989000001</v>
+      </c>
+      <c r="P7" s="13">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="O7" s="13">
-        <v>0</v>
-      </c>
-      <c r="P7" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>0</v>
+      </c>
+      <c r="R7" s="13">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>0</v>
-      </c>
-      <c r="R7" s="13">
-        <v>0</v>
-      </c>
-      <c r="S7" s="13">
-        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -29134,7 +29144,7 @@
       </c>
       <c r="U7" s="4"/>
       <c r="V7" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="W7" s="6">
@@ -29161,22 +29171,22 @@
       <c r="AD7" s="6">
         <v>3553</v>
       </c>
-      <c r="AJ7" s="51"/>
-      <c r="AK7" s="51"/>
+      <c r="AJ7" s="48"/>
+      <c r="AK7" s="48"/>
     </row>
     <row r="8" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="28">
+        <f t="shared" si="6"/>
+        <v>45876</v>
+      </c>
+      <c r="B8" s="29">
+        <v>1538.165999489999</v>
+      </c>
+      <c r="C8" s="29">
+        <v>225.11999994000001</v>
+      </c>
+      <c r="D8" s="13">
         <f t="shared" si="7"/>
-        <v>45876</v>
-      </c>
-      <c r="B8" s="13">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13">
-        <v>0</v>
-      </c>
-      <c r="D8" s="13">
-        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="E8" s="13">
@@ -29210,25 +29220,24 @@
       <c r="M8" s="13">
         <v>0</v>
       </c>
-      <c r="N8" s="13">
+      <c r="N8" s="29">
+        <v>260.87999933999964</v>
+      </c>
+      <c r="O8" s="29">
+        <v>60.839999890000001</v>
+      </c>
+      <c r="P8" s="13">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="O8" s="13">
-        <v>0</v>
-      </c>
-      <c r="P8" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>0</v>
+      </c>
+      <c r="R8" s="13">
+        <v>0</v>
+      </c>
+      <c r="S8" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>0</v>
-      </c>
-      <c r="R8" s="13">
-        <v>0</v>
-      </c>
-      <c r="S8" s="13">
-        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -29236,7 +29245,7 @@
       </c>
       <c r="U8" s="4"/>
       <c r="V8" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="W8" s="6">
@@ -29263,26 +29272,26 @@
       <c r="AD8" s="6">
         <v>3558</v>
       </c>
-      <c r="AH8" s="52"/>
-      <c r="AI8" s="52"/>
-      <c r="AJ8" s="52"/>
-      <c r="AK8" s="53"/>
-      <c r="AL8" s="53"/>
-      <c r="AM8" s="53"/>
+      <c r="AH8" s="54"/>
+      <c r="AI8" s="54"/>
+      <c r="AJ8" s="54"/>
+      <c r="AK8" s="55"/>
+      <c r="AL8" s="55"/>
+      <c r="AM8" s="55"/>
     </row>
     <row r="9" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="28">
+        <f t="shared" si="6"/>
+        <v>45877</v>
+      </c>
+      <c r="B9" s="29">
+        <v>1316.9519995299991</v>
+      </c>
+      <c r="C9" s="29">
+        <v>202.01999991</v>
+      </c>
+      <c r="D9" s="13">
         <f t="shared" si="7"/>
-        <v>45877</v>
-      </c>
-      <c r="B9" s="13">
-        <v>0</v>
-      </c>
-      <c r="C9" s="13">
-        <v>0</v>
-      </c>
-      <c r="D9" s="13">
-        <f t="shared" si="8"/>
         <v>69</v>
       </c>
       <c r="E9" s="13">
@@ -29316,25 +29325,24 @@
       <c r="M9" s="13">
         <v>0</v>
       </c>
-      <c r="N9" s="13">
+      <c r="N9" s="29">
+        <v>277.10399936999966</v>
+      </c>
+      <c r="O9" s="29">
+        <v>49.511999879999998</v>
+      </c>
+      <c r="P9" s="13">
         <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="O9" s="13">
-        <v>0</v>
-      </c>
-      <c r="P9" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>0</v>
+      </c>
+      <c r="R9" s="13">
+        <v>0</v>
+      </c>
+      <c r="S9" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>0</v>
-      </c>
-      <c r="R9" s="13">
-        <v>0</v>
-      </c>
-      <c r="S9" s="13">
-        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -29342,7 +29350,7 @@
       </c>
       <c r="U9" s="4"/>
       <c r="V9" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="W9" s="6">
@@ -29369,25 +29377,25 @@
       <c r="AD9" s="6">
         <v>3561</v>
       </c>
-      <c r="AH9" s="50"/>
-      <c r="AI9" s="50"/>
-      <c r="AL9" s="51"/>
-      <c r="AM9" s="54"/>
-      <c r="AN9" s="54"/>
+      <c r="AH9" s="47"/>
+      <c r="AI9" s="47"/>
+      <c r="AL9" s="48"/>
+      <c r="AM9" s="49"/>
+      <c r="AN9" s="49"/>
     </row>
     <row r="10" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="28">
+        <f t="shared" si="6"/>
+        <v>45878</v>
+      </c>
+      <c r="B10" s="29">
+        <v>992.92199946999961</v>
+      </c>
+      <c r="C10" s="29">
+        <v>163.12799993999997</v>
+      </c>
+      <c r="D10" s="13">
         <f t="shared" si="7"/>
-        <v>45878</v>
-      </c>
-      <c r="B10" s="13">
-        <v>0</v>
-      </c>
-      <c r="C10" s="13">
-        <v>0</v>
-      </c>
-      <c r="D10" s="13">
-        <f t="shared" si="8"/>
         <v>46</v>
       </c>
       <c r="E10" s="13">
@@ -29421,25 +29429,24 @@
       <c r="M10" s="13">
         <v>0</v>
       </c>
-      <c r="N10" s="13">
+      <c r="N10" s="29">
+        <v>251.39999929999985</v>
+      </c>
+      <c r="O10" s="29">
+        <v>45.959999910000001</v>
+      </c>
+      <c r="P10" s="13">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="O10" s="13">
-        <v>0</v>
-      </c>
-      <c r="P10" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>0</v>
+      </c>
+      <c r="R10" s="13">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>0</v>
-      </c>
-      <c r="R10" s="13">
-        <v>0</v>
-      </c>
-      <c r="S10" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T10" s="6" t="s">
@@ -29447,7 +29454,7 @@
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="W10" s="6">
@@ -29474,25 +29481,25 @@
       <c r="AD10" s="6">
         <v>3568</v>
       </c>
-      <c r="AH10" s="50"/>
-      <c r="AI10" s="50"/>
-      <c r="AL10" s="51"/>
-      <c r="AM10" s="54"/>
-      <c r="AN10" s="54"/>
+      <c r="AH10" s="47"/>
+      <c r="AI10" s="47"/>
+      <c r="AL10" s="48"/>
+      <c r="AM10" s="49"/>
+      <c r="AN10" s="49"/>
     </row>
     <row r="11" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="28">
+        <f t="shared" si="6"/>
+        <v>45879</v>
+      </c>
+      <c r="B11" s="29">
+        <v>841.34399949999988</v>
+      </c>
+      <c r="C11" s="29">
+        <v>143.72399992999999</v>
+      </c>
+      <c r="D11" s="13">
         <f t="shared" si="7"/>
-        <v>45879</v>
-      </c>
-      <c r="B11" s="13">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13">
-        <v>0</v>
-      </c>
-      <c r="D11" s="13">
-        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="E11" s="13">
@@ -29526,25 +29533,24 @@
       <c r="M11" s="13">
         <v>0</v>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="29">
+        <v>232.34399937999984</v>
+      </c>
+      <c r="O11" s="29">
+        <v>57.167999909999999</v>
+      </c>
+      <c r="P11" s="13">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="O11" s="13">
-        <v>0</v>
-      </c>
-      <c r="P11" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>0</v>
+      </c>
+      <c r="R11" s="13">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>0</v>
-      </c>
-      <c r="R11" s="13">
-        <v>0</v>
-      </c>
-      <c r="S11" s="13">
-        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="T11" s="6" t="s">
@@ -29552,7 +29558,7 @@
       </c>
       <c r="U11" s="4"/>
       <c r="V11" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="W11" s="6">
@@ -29579,25 +29585,25 @@
       <c r="AD11" s="6">
         <v>3568</v>
       </c>
-      <c r="AH11" s="50"/>
-      <c r="AI11" s="50"/>
-      <c r="AL11" s="51"/>
-      <c r="AM11" s="54"/>
-      <c r="AN11" s="54"/>
+      <c r="AH11" s="47"/>
+      <c r="AI11" s="47"/>
+      <c r="AL11" s="48"/>
+      <c r="AM11" s="49"/>
+      <c r="AN11" s="49"/>
     </row>
     <row r="12" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A12" s="28">
+        <f t="shared" si="6"/>
+        <v>45880</v>
+      </c>
+      <c r="B12" s="29">
+        <v>1162.3079994799989</v>
+      </c>
+      <c r="C12" s="29">
+        <v>190.46999993</v>
+      </c>
+      <c r="D12" s="13">
         <f t="shared" si="7"/>
-        <v>45880</v>
-      </c>
-      <c r="B12" s="13">
-        <v>0</v>
-      </c>
-      <c r="C12" s="13">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13">
-        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="E12" s="13">
@@ -29631,25 +29637,24 @@
       <c r="M12" s="13">
         <v>0</v>
       </c>
-      <c r="N12" s="13">
+      <c r="N12" s="29">
+        <v>227.95199947999987</v>
+      </c>
+      <c r="O12" s="29">
+        <v>55.751999879999985</v>
+      </c>
+      <c r="P12" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O12" s="13">
-        <v>0</v>
-      </c>
-      <c r="P12" s="13">
+      <c r="Q12" s="13">
+        <v>0</v>
+      </c>
+      <c r="R12" s="13">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>0</v>
-      </c>
-      <c r="R12" s="13">
-        <v>0</v>
-      </c>
-      <c r="S12" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T12" s="6" t="s">
@@ -29657,7 +29662,7 @@
       </c>
       <c r="U12" s="4"/>
       <c r="V12" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="W12" s="6">
@@ -29684,25 +29689,25 @@
       <c r="AD12" s="6">
         <v>3572</v>
       </c>
-      <c r="AH12" s="50"/>
-      <c r="AI12" s="50"/>
-      <c r="AL12" s="51"/>
-      <c r="AM12" s="54"/>
-      <c r="AN12" s="54"/>
+      <c r="AH12" s="47"/>
+      <c r="AI12" s="47"/>
+      <c r="AL12" s="48"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
     </row>
     <row r="13" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
+        <f t="shared" si="6"/>
+        <v>45881</v>
+      </c>
+      <c r="B13" s="29">
+        <v>1301.0759995600001</v>
+      </c>
+      <c r="C13" s="29">
+        <v>234.65399993999998</v>
+      </c>
+      <c r="D13" s="13">
         <f t="shared" si="7"/>
-        <v>45881</v>
-      </c>
-      <c r="B13" s="13">
-        <v>0</v>
-      </c>
-      <c r="C13" s="13">
-        <v>0</v>
-      </c>
-      <c r="D13" s="13">
-        <f t="shared" si="8"/>
         <v>42</v>
       </c>
       <c r="E13" s="13">
@@ -29736,25 +29741,24 @@
       <c r="M13" s="13">
         <v>0</v>
       </c>
-      <c r="N13" s="13">
+      <c r="N13" s="29">
+        <v>247.17599935999982</v>
+      </c>
+      <c r="O13" s="29">
+        <v>58.679999909999999</v>
+      </c>
+      <c r="P13" s="13">
         <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="O13" s="13">
-        <v>0</v>
-      </c>
-      <c r="P13" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="13">
+        <v>0</v>
+      </c>
+      <c r="R13" s="13">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="13">
-        <v>0</v>
-      </c>
-      <c r="R13" s="13">
-        <v>0</v>
-      </c>
-      <c r="S13" s="13">
-        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -29762,7 +29766,7 @@
       </c>
       <c r="U13" s="4"/>
       <c r="V13" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="W13" s="15">
@@ -29789,25 +29793,25 @@
       <c r="AD13" s="15">
         <v>3572</v>
       </c>
-      <c r="AH13" s="50"/>
-      <c r="AI13" s="50"/>
-      <c r="AL13" s="51"/>
-      <c r="AM13" s="54"/>
-      <c r="AN13" s="54"/>
+      <c r="AH13" s="47"/>
+      <c r="AI13" s="47"/>
+      <c r="AL13" s="48"/>
+      <c r="AM13" s="49"/>
+      <c r="AN13" s="49"/>
     </row>
     <row r="14" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A14" s="28">
+        <f t="shared" si="6"/>
+        <v>45882</v>
+      </c>
+      <c r="B14" s="29">
+        <v>1500.5759995000003</v>
+      </c>
+      <c r="C14" s="29">
+        <v>232.09199993999999</v>
+      </c>
+      <c r="D14" s="13">
         <f t="shared" si="7"/>
-        <v>45882</v>
-      </c>
-      <c r="B14" s="13">
-        <v>0</v>
-      </c>
-      <c r="C14" s="13">
-        <v>0</v>
-      </c>
-      <c r="D14" s="13">
-        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="E14" s="13">
@@ -29841,25 +29845,24 @@
       <c r="M14" s="13">
         <v>0</v>
       </c>
-      <c r="N14" s="13">
+      <c r="N14" s="29">
+        <v>258.83999937000016</v>
+      </c>
+      <c r="O14" s="29">
+        <v>54.287999900000003</v>
+      </c>
+      <c r="P14" s="13">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="O14" s="13">
-        <v>0</v>
-      </c>
-      <c r="P14" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="13">
+        <v>0</v>
+      </c>
+      <c r="R14" s="13">
+        <v>0</v>
+      </c>
+      <c r="S14" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>0</v>
-      </c>
-      <c r="R14" s="13">
-        <v>0</v>
-      </c>
-      <c r="S14" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T14" s="6" t="s">
@@ -29867,7 +29870,7 @@
       </c>
       <c r="U14" s="4"/>
       <c r="V14" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="W14" s="6">
@@ -29894,21 +29897,21 @@
       <c r="AD14" s="6">
         <v>3581</v>
       </c>
-      <c r="AN14" s="54"/>
+      <c r="AN14" s="49"/>
     </row>
     <row r="15" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A15" s="28">
+        <f t="shared" si="6"/>
+        <v>45883</v>
+      </c>
+      <c r="B15" s="29">
+        <v>1602.25799944</v>
+      </c>
+      <c r="C15" s="29">
+        <v>214.19999989999999</v>
+      </c>
+      <c r="D15" s="13">
         <f t="shared" si="7"/>
-        <v>45883</v>
-      </c>
-      <c r="B15" s="13">
-        <v>0</v>
-      </c>
-      <c r="C15" s="13">
-        <v>0</v>
-      </c>
-      <c r="D15" s="13">
-        <f t="shared" si="8"/>
         <v>90</v>
       </c>
       <c r="E15" s="13">
@@ -29941,25 +29944,24 @@
       <c r="M15" s="13">
         <v>0</v>
       </c>
-      <c r="N15" s="13">
+      <c r="N15" s="29">
+        <v>299.83199936999978</v>
+      </c>
+      <c r="O15" s="29">
+        <v>60.935999920000015</v>
+      </c>
+      <c r="P15" s="13">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="O15" s="13">
-        <v>0</v>
-      </c>
-      <c r="P15" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="13">
+        <v>0</v>
+      </c>
+      <c r="R15" s="13">
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q15" s="13">
-        <v>0</v>
-      </c>
-      <c r="R15" s="13">
-        <v>0</v>
-      </c>
-      <c r="S15" s="13">
-        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="T15" s="6" t="s">
@@ -29967,7 +29969,7 @@
       </c>
       <c r="U15" s="4"/>
       <c r="V15" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="W15" s="6">
@@ -29994,21 +29996,21 @@
       <c r="AD15" s="6">
         <v>3581</v>
       </c>
-      <c r="AI15" s="55"/>
+      <c r="AI15" s="50"/>
     </row>
     <row r="16" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A16" s="28">
+        <f t="shared" si="6"/>
+        <v>45884</v>
+      </c>
+      <c r="B16" s="29">
+        <v>1123.9619995199994</v>
+      </c>
+      <c r="C16" s="29">
+        <v>181.60799991000002</v>
+      </c>
+      <c r="D16" s="13">
         <f t="shared" si="7"/>
-        <v>45884</v>
-      </c>
-      <c r="B16" s="13">
-        <v>0</v>
-      </c>
-      <c r="C16" s="13">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13">
-        <f t="shared" si="8"/>
         <v>53</v>
       </c>
       <c r="E16" s="13">
@@ -30029,7 +30031,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="13">
-        <f t="shared" ref="J16:J32" si="10">Z17-Z16</f>
+        <f t="shared" ref="J16:J32" si="9">Z17-Z16</f>
         <v>1</v>
       </c>
       <c r="K16" s="13">
@@ -30042,25 +30044,24 @@
       <c r="M16" s="13">
         <v>0</v>
       </c>
-      <c r="N16" s="13">
+      <c r="N16" s="29">
+        <v>258.45599932999994</v>
+      </c>
+      <c r="O16" s="29">
+        <v>61.87199992</v>
+      </c>
+      <c r="P16" s="13">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="O16" s="13">
-        <v>0</v>
-      </c>
-      <c r="P16" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="13">
+        <v>0</v>
+      </c>
+      <c r="R16" s="13">
+        <v>0</v>
+      </c>
+      <c r="S16" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q16" s="13">
-        <v>0</v>
-      </c>
-      <c r="R16" s="13">
-        <v>0</v>
-      </c>
-      <c r="S16" s="13">
-        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="T16" s="6" t="s">
@@ -30068,7 +30069,7 @@
       </c>
       <c r="U16" s="4"/>
       <c r="V16" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="W16" s="16">
@@ -30098,17 +30099,17 @@
     </row>
     <row r="17" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="28">
+        <f t="shared" si="6"/>
+        <v>45885</v>
+      </c>
+      <c r="B17" s="29">
+        <v>1055.5019995599994</v>
+      </c>
+      <c r="C17" s="29">
+        <v>184.84199990999997</v>
+      </c>
+      <c r="D17" s="13">
         <f t="shared" si="7"/>
-        <v>45885</v>
-      </c>
-      <c r="B17" s="13">
-        <v>0</v>
-      </c>
-      <c r="C17" s="13">
-        <v>0</v>
-      </c>
-      <c r="D17" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E17" s="13">
@@ -30129,7 +30130,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K17" s="13">
@@ -30142,25 +30143,24 @@
       <c r="M17" s="13">
         <v>0</v>
       </c>
-      <c r="N17" s="13">
+      <c r="N17" s="29">
+        <v>259.39199942999977</v>
+      </c>
+      <c r="O17" s="29">
+        <v>56.687999900000001</v>
+      </c>
+      <c r="P17" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O17" s="13">
-        <v>0</v>
-      </c>
-      <c r="P17" s="13">
+      <c r="Q17" s="13">
+        <v>0</v>
+      </c>
+      <c r="R17" s="13">
+        <v>0</v>
+      </c>
+      <c r="S17" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="13">
-        <v>0</v>
-      </c>
-      <c r="R17" s="13">
-        <v>0</v>
-      </c>
-      <c r="S17" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T17" s="6" t="s">
@@ -30168,7 +30168,7 @@
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="W17" s="16">
@@ -30198,17 +30198,17 @@
     </row>
     <row r="18" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="28">
+        <f t="shared" si="6"/>
+        <v>45886</v>
+      </c>
+      <c r="B18" s="29">
+        <v>1154.2859995499996</v>
+      </c>
+      <c r="C18" s="29">
+        <v>197.60999991</v>
+      </c>
+      <c r="D18" s="13">
         <f t="shared" si="7"/>
-        <v>45886</v>
-      </c>
-      <c r="B18" s="13">
-        <v>0</v>
-      </c>
-      <c r="C18" s="13">
-        <v>0</v>
-      </c>
-      <c r="D18" s="13">
-        <f t="shared" si="8"/>
         <v>43</v>
       </c>
       <c r="E18" s="13">
@@ -30229,7 +30229,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="K18" s="13">
@@ -30242,25 +30242,24 @@
       <c r="M18" s="13">
         <v>0</v>
       </c>
-      <c r="N18" s="13">
+      <c r="N18" s="29">
+        <v>277.94399946999999</v>
+      </c>
+      <c r="O18" s="29">
+        <v>62.567999910000005</v>
+      </c>
+      <c r="P18" s="13">
         <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="O18" s="13">
-        <v>0</v>
-      </c>
-      <c r="P18" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="13">
+        <v>0</v>
+      </c>
+      <c r="R18" s="13">
+        <v>0</v>
+      </c>
+      <c r="S18" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>0</v>
-      </c>
-      <c r="R18" s="13">
-        <v>0</v>
-      </c>
-      <c r="S18" s="13">
-        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="T18" s="6" t="s">
@@ -30268,7 +30267,7 @@
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="W18" s="16">
@@ -30298,17 +30297,17 @@
     </row>
     <row r="19" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A19" s="28">
+        <f t="shared" si="6"/>
+        <v>45887</v>
+      </c>
+      <c r="B19" s="29">
+        <v>1681.5119994899992</v>
+      </c>
+      <c r="C19" s="29">
+        <v>259.05599991000003</v>
+      </c>
+      <c r="D19" s="13">
         <f t="shared" si="7"/>
-        <v>45887</v>
-      </c>
-      <c r="B19" s="13">
-        <v>0</v>
-      </c>
-      <c r="C19" s="13">
-        <v>0</v>
-      </c>
-      <c r="D19" s="13">
-        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="E19" s="13">
@@ -30329,7 +30328,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K19" s="13">
@@ -30342,25 +30341,24 @@
       <c r="M19" s="13">
         <v>0</v>
       </c>
-      <c r="N19" s="13">
+      <c r="N19" s="29">
+        <v>281.27999936999993</v>
+      </c>
+      <c r="O19" s="29">
+        <v>61.583999900000009</v>
+      </c>
+      <c r="P19" s="13">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="O19" s="13">
-        <v>0</v>
-      </c>
-      <c r="P19" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="13">
+        <v>0</v>
+      </c>
+      <c r="R19" s="13">
+        <v>0</v>
+      </c>
+      <c r="S19" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="13">
-        <v>0</v>
-      </c>
-      <c r="R19" s="13">
-        <v>0</v>
-      </c>
-      <c r="S19" s="13">
-        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="T19" s="6" t="s">
@@ -30368,7 +30366,7 @@
       </c>
       <c r="U19" s="17"/>
       <c r="V19" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="W19" s="19">
@@ -30398,17 +30396,17 @@
     </row>
     <row r="20" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="28">
+        <f t="shared" si="6"/>
+        <v>45888</v>
+      </c>
+      <c r="B20" s="29">
+        <v>1700.5379995000005</v>
+      </c>
+      <c r="C20" s="29">
+        <v>254.05799991000001</v>
+      </c>
+      <c r="D20" s="13">
         <f t="shared" si="7"/>
-        <v>45888</v>
-      </c>
-      <c r="B20" s="13">
-        <v>0</v>
-      </c>
-      <c r="C20" s="13">
-        <v>0</v>
-      </c>
-      <c r="D20" s="13">
-        <f t="shared" si="8"/>
         <v>80</v>
       </c>
       <c r="E20" s="13">
@@ -30429,7 +30427,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K20" s="13">
@@ -30442,25 +30440,24 @@
       <c r="M20" s="13">
         <v>0</v>
       </c>
-      <c r="N20" s="13">
+      <c r="N20" s="29">
+        <v>293.13599932</v>
+      </c>
+      <c r="O20" s="29">
+        <v>69.09599990000001</v>
+      </c>
+      <c r="P20" s="13">
         <f t="shared" si="4"/>
-        <v>-2995</v>
-      </c>
-      <c r="O20" s="13">
-        <v>0</v>
-      </c>
-      <c r="P20" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="13">
+        <v>0</v>
+      </c>
+      <c r="R20" s="13">
+        <v>0</v>
+      </c>
+      <c r="S20" s="13">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q20" s="13">
-        <v>0</v>
-      </c>
-      <c r="R20" s="13">
-        <v>0</v>
-      </c>
-      <c r="S20" s="13">
-        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -30468,7 +30465,7 @@
       </c>
       <c r="U20" s="4"/>
       <c r="V20" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="W20" s="15">
@@ -30498,17 +30495,17 @@
     </row>
     <row r="21" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="28">
+        <f t="shared" si="6"/>
+        <v>45889</v>
+      </c>
+      <c r="B21" s="29">
+        <v>1751.3579994899997</v>
+      </c>
+      <c r="C21" s="29">
+        <v>249.52199989999997</v>
+      </c>
+      <c r="D21" s="13">
         <f t="shared" si="7"/>
-        <v>45889</v>
-      </c>
-      <c r="B21" s="13">
-        <v>0</v>
-      </c>
-      <c r="C21" s="13">
-        <v>0</v>
-      </c>
-      <c r="D21" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E21" s="13">
@@ -30529,7 +30526,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K21" s="13">
@@ -30542,15 +30539,14 @@
       <c r="M21" s="13">
         <v>0</v>
       </c>
-      <c r="N21" s="13">
+      <c r="N21" s="29">
+        <v>304.48799938000002</v>
+      </c>
+      <c r="O21" s="29">
+        <v>66.38399991</v>
+      </c>
+      <c r="P21" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="13">
-        <v>0</v>
-      </c>
-      <c r="P21" s="13">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q21" s="13">
@@ -30568,7 +30564,7 @@
       </c>
       <c r="U21" s="4"/>
       <c r="V21" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="W21" s="15">
@@ -30598,17 +30594,17 @@
     </row>
     <row r="22" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A22" s="28">
+        <f t="shared" si="6"/>
+        <v>45890</v>
+      </c>
+      <c r="B22" s="29">
+        <v>1812.0059994099988</v>
+      </c>
+      <c r="C22" s="29">
+        <v>297.69599991000001</v>
+      </c>
+      <c r="D22" s="13">
         <f t="shared" si="7"/>
-        <v>45890</v>
-      </c>
-      <c r="B22" s="13">
-        <v>0</v>
-      </c>
-      <c r="C22" s="13">
-        <v>0</v>
-      </c>
-      <c r="D22" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E22" s="13">
@@ -30629,7 +30625,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K22" s="13">
@@ -30642,25 +30638,24 @@
       <c r="M22" s="13">
         <v>0</v>
       </c>
-      <c r="N22" s="13">
+      <c r="N22" s="29">
+        <v>343.60799934999983</v>
+      </c>
+      <c r="O22" s="29">
+        <v>68.543999890000009</v>
+      </c>
+      <c r="P22" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O22" s="13">
-        <v>0</v>
-      </c>
-      <c r="P22" s="13">
+      <c r="Q22" s="13">
+        <v>0</v>
+      </c>
+      <c r="R22" s="13">
+        <v>0</v>
+      </c>
+      <c r="S22" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="13">
-        <v>0</v>
-      </c>
-      <c r="R22" s="13">
-        <v>0</v>
-      </c>
-      <c r="S22" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
@@ -30668,7 +30663,7 @@
       </c>
       <c r="U22" s="4"/>
       <c r="V22" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="W22" s="15">
@@ -30698,17 +30693,17 @@
     </row>
     <row r="23" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="28">
+        <f t="shared" si="6"/>
+        <v>45891</v>
+      </c>
+      <c r="B23" s="29">
+        <v>1335.6419994500002</v>
+      </c>
+      <c r="C23" s="29">
+        <v>205.75799993999996</v>
+      </c>
+      <c r="D23" s="13">
         <f t="shared" si="7"/>
-        <v>45891</v>
-      </c>
-      <c r="B23" s="13">
-        <v>0</v>
-      </c>
-      <c r="C23" s="13">
-        <v>0</v>
-      </c>
-      <c r="D23" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E23" s="13">
@@ -30729,7 +30724,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K23" s="13">
@@ -30742,25 +30737,24 @@
       <c r="M23" s="13">
         <v>0</v>
       </c>
-      <c r="N23" s="13">
+      <c r="N23" s="29">
+        <v>341.73599936000016</v>
+      </c>
+      <c r="O23" s="29">
+        <v>62.687999879999992</v>
+      </c>
+      <c r="P23" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O23" s="13">
-        <v>0</v>
-      </c>
-      <c r="P23" s="13">
+      <c r="Q23" s="13">
+        <v>0</v>
+      </c>
+      <c r="R23" s="13">
+        <v>0</v>
+      </c>
+      <c r="S23" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="13">
-        <v>0</v>
-      </c>
-      <c r="R23" s="13">
-        <v>0</v>
-      </c>
-      <c r="S23" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
@@ -30768,7 +30762,7 @@
       </c>
       <c r="U23" s="4"/>
       <c r="V23" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>21</v>
       </c>
       <c r="W23" s="15">
@@ -30798,17 +30792,17 @@
     </row>
     <row r="24" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="28">
+        <f t="shared" si="6"/>
+        <v>45892</v>
+      </c>
+      <c r="B24" s="29">
+        <v>1132.2359994799995</v>
+      </c>
+      <c r="C24" s="29">
+        <v>196.26599993999997</v>
+      </c>
+      <c r="D24" s="13">
         <f t="shared" si="7"/>
-        <v>45892</v>
-      </c>
-      <c r="B24" s="13">
-        <v>0</v>
-      </c>
-      <c r="C24" s="13">
-        <v>0</v>
-      </c>
-      <c r="D24" s="13">
-        <f t="shared" si="8"/>
         <v>223</v>
       </c>
       <c r="E24" s="13">
@@ -30829,7 +30823,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="K24" s="13">
@@ -30842,25 +30836,24 @@
       <c r="M24" s="13">
         <v>0</v>
       </c>
-      <c r="N24" s="13">
+      <c r="N24" s="29">
+        <v>306.07199935999989</v>
+      </c>
+      <c r="O24" s="29">
+        <v>70.199999890000001</v>
+      </c>
+      <c r="P24" s="13">
         <f t="shared" si="4"/>
-        <v>3021</v>
-      </c>
-      <c r="O24" s="13">
-        <v>0</v>
-      </c>
-      <c r="P24" s="13">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>0</v>
+      </c>
+      <c r="R24" s="13">
+        <v>0</v>
+      </c>
+      <c r="S24" s="13">
         <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="Q24" s="13">
-        <v>0</v>
-      </c>
-      <c r="R24" s="13">
-        <v>0</v>
-      </c>
-      <c r="S24" s="13">
-        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -30868,7 +30861,7 @@
       </c>
       <c r="U24" s="4"/>
       <c r="V24" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="W24" s="15">
@@ -30898,17 +30891,17 @@
     </row>
     <row r="25" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="28">
+        <f t="shared" si="6"/>
+        <v>45893</v>
+      </c>
+      <c r="B25" s="29">
+        <v>1166.5919994999995</v>
+      </c>
+      <c r="C25" s="29">
+        <v>222.72599991999999</v>
+      </c>
+      <c r="D25" s="13">
         <f t="shared" si="7"/>
-        <v>45893</v>
-      </c>
-      <c r="B25" s="13">
-        <v>0</v>
-      </c>
-      <c r="C25" s="13">
-        <v>0</v>
-      </c>
-      <c r="D25" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E25" s="13">
@@ -30929,7 +30922,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K25" s="13">
@@ -30942,25 +30935,24 @@
       <c r="M25" s="13">
         <v>0</v>
       </c>
-      <c r="N25" s="13">
+      <c r="N25" s="29">
+        <v>316.55999934999988</v>
+      </c>
+      <c r="O25" s="29">
+        <v>65.255999880000005</v>
+      </c>
+      <c r="P25" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O25" s="13">
-        <v>0</v>
-      </c>
-      <c r="P25" s="13">
+      <c r="Q25" s="13">
+        <v>0</v>
+      </c>
+      <c r="R25" s="13">
+        <v>0</v>
+      </c>
+      <c r="S25" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="13">
-        <v>0</v>
-      </c>
-      <c r="R25" s="13">
-        <v>0</v>
-      </c>
-      <c r="S25" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -30968,7 +30960,7 @@
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>23</v>
       </c>
       <c r="W25" s="21">
@@ -30998,17 +30990,17 @@
     </row>
     <row r="26" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="28">
+        <f t="shared" si="6"/>
+        <v>45894</v>
+      </c>
+      <c r="B26" s="29">
+        <v>1295.0699995099997</v>
+      </c>
+      <c r="C26" s="29">
+        <v>237.38399989999999</v>
+      </c>
+      <c r="D26" s="13">
         <f t="shared" si="7"/>
-        <v>45894</v>
-      </c>
-      <c r="B26" s="13">
-        <v>0</v>
-      </c>
-      <c r="C26" s="13">
-        <v>0</v>
-      </c>
-      <c r="D26" s="13">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E26" s="13">
@@ -31029,7 +31021,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K26" s="13">
@@ -31042,25 +31034,24 @@
       <c r="M26" s="13">
         <v>0</v>
       </c>
-      <c r="N26" s="13">
+      <c r="N26" s="29">
+        <v>352.91999938999993</v>
+      </c>
+      <c r="O26" s="29">
+        <v>76.00799988</v>
+      </c>
+      <c r="P26" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O26" s="13">
-        <v>0</v>
-      </c>
-      <c r="P26" s="13">
+      <c r="Q26" s="13">
+        <v>0</v>
+      </c>
+      <c r="R26" s="13">
+        <v>0</v>
+      </c>
+      <c r="S26" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="13">
-        <v>0</v>
-      </c>
-      <c r="R26" s="13">
-        <v>0</v>
-      </c>
-      <c r="S26" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -31068,7 +31059,7 @@
       </c>
       <c r="U26" s="4"/>
       <c r="V26" s="20">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
       <c r="W26" s="21">
@@ -31098,17 +31089,17 @@
     </row>
     <row r="27" spans="1:30" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A27" s="28">
+        <f t="shared" si="6"/>
+        <v>45895</v>
+      </c>
+      <c r="B27" s="29">
+        <v>1794.36599948</v>
+      </c>
+      <c r="C27" s="29">
+        <v>259.85399989999996</v>
+      </c>
+      <c r="D27" s="13">
         <f t="shared" si="7"/>
-        <v>45895</v>
-      </c>
-      <c r="B27" s="13">
-        <v>0</v>
-      </c>
-      <c r="C27" s="13">
-        <v>0</v>
-      </c>
-      <c r="D27" s="13">
-        <f t="shared" si="8"/>
         <v>55</v>
       </c>
       <c r="E27" s="13">
@@ -31129,7 +31120,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K27" s="13">
@@ -31142,25 +31133,24 @@
       <c r="M27" s="13">
         <v>0</v>
       </c>
-      <c r="N27" s="13">
+      <c r="N27" s="29">
+        <v>345.47999932000005</v>
+      </c>
+      <c r="O27" s="29">
+        <v>71.039999929999993</v>
+      </c>
+      <c r="P27" s="13">
         <f t="shared" si="4"/>
-        <v>13</v>
-      </c>
-      <c r="O27" s="13">
-        <v>0</v>
-      </c>
-      <c r="P27" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="13">
+        <v>0</v>
+      </c>
+      <c r="R27" s="13">
+        <v>0</v>
+      </c>
+      <c r="S27" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="13">
-        <v>0</v>
-      </c>
-      <c r="R27" s="13">
-        <v>0</v>
-      </c>
-      <c r="S27" s="13">
-        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="T27" s="6" t="s">
@@ -31168,7 +31158,7 @@
       </c>
       <c r="U27" s="4"/>
       <c r="V27" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>25</v>
       </c>
       <c r="W27" s="21">
@@ -31198,17 +31188,17 @@
     </row>
     <row r="28" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A28" s="28">
+        <f t="shared" si="6"/>
+        <v>45896</v>
+      </c>
+      <c r="B28" s="29">
+        <v>1732.4159994400002</v>
+      </c>
+      <c r="C28" s="29">
+        <v>247.00199992</v>
+      </c>
+      <c r="D28" s="13">
         <f t="shared" si="7"/>
-        <v>45896</v>
-      </c>
-      <c r="B28" s="13">
-        <v>0</v>
-      </c>
-      <c r="C28" s="13">
-        <v>0</v>
-      </c>
-      <c r="D28" s="13">
-        <f t="shared" si="8"/>
         <v>76</v>
       </c>
       <c r="E28" s="13">
@@ -31229,7 +31219,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K28" s="13">
@@ -31242,25 +31232,24 @@
       <c r="M28" s="13">
         <v>0</v>
       </c>
-      <c r="N28" s="13">
+      <c r="N28" s="29">
+        <v>319.17599931999985</v>
+      </c>
+      <c r="O28" s="29">
+        <v>66.527999870000002</v>
+      </c>
+      <c r="P28" s="13">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="O28" s="13">
-        <v>0</v>
-      </c>
-      <c r="P28" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="13">
+        <v>0</v>
+      </c>
+      <c r="R28" s="13">
+        <v>0</v>
+      </c>
+      <c r="S28" s="13">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="Q28" s="13">
-        <v>0</v>
-      </c>
-      <c r="R28" s="13">
-        <v>0</v>
-      </c>
-      <c r="S28" s="13">
-        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="T28" s="6" t="s">
@@ -31268,7 +31257,7 @@
       </c>
       <c r="U28" s="4"/>
       <c r="V28" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>26</v>
       </c>
       <c r="W28" s="15">
@@ -31298,17 +31287,17 @@
     </row>
     <row r="29" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="28">
+        <f t="shared" si="6"/>
+        <v>45897</v>
+      </c>
+      <c r="B29" s="29">
+        <v>1754.8019994799997</v>
+      </c>
+      <c r="C29" s="29">
+        <v>236.37599990999999</v>
+      </c>
+      <c r="D29" s="13">
         <f t="shared" si="7"/>
-        <v>45897</v>
-      </c>
-      <c r="B29" s="13">
-        <v>0</v>
-      </c>
-      <c r="C29" s="13">
-        <v>0</v>
-      </c>
-      <c r="D29" s="13">
-        <f t="shared" si="8"/>
         <v>95</v>
       </c>
       <c r="E29" s="13">
@@ -31329,7 +31318,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K29" s="13">
@@ -31342,25 +31331,24 @@
       <c r="M29" s="13">
         <v>0</v>
       </c>
-      <c r="N29" s="13">
+      <c r="N29" s="29">
+        <v>361.05599924000001</v>
+      </c>
+      <c r="O29" s="29">
+        <v>67.127999890000012</v>
+      </c>
+      <c r="P29" s="13">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="O29" s="13">
-        <v>0</v>
-      </c>
-      <c r="P29" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="13">
+        <v>0</v>
+      </c>
+      <c r="R29" s="13">
+        <v>0</v>
+      </c>
+      <c r="S29" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="13">
-        <v>0</v>
-      </c>
-      <c r="R29" s="13">
-        <v>0</v>
-      </c>
-      <c r="S29" s="13">
-        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="T29" s="6" t="s">
@@ -31368,7 +31356,7 @@
       </c>
       <c r="U29" s="4"/>
       <c r="V29" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>27</v>
       </c>
       <c r="W29" s="15">
@@ -31398,17 +31386,17 @@
     </row>
     <row r="30" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="28">
+        <f t="shared" si="6"/>
+        <v>45898</v>
+      </c>
+      <c r="B30" s="29">
+        <v>1186.0799995499999</v>
+      </c>
+      <c r="C30" s="29">
+        <v>169.46999990000003</v>
+      </c>
+      <c r="D30" s="13">
         <f t="shared" si="7"/>
-        <v>45898</v>
-      </c>
-      <c r="B30" s="13">
-        <v>0</v>
-      </c>
-      <c r="C30" s="13">
-        <v>0</v>
-      </c>
-      <c r="D30" s="13">
-        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="E30" s="13">
@@ -31429,7 +31417,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="K30" s="13">
@@ -31442,25 +31430,24 @@
       <c r="M30" s="13">
         <v>0</v>
       </c>
-      <c r="N30" s="13">
+      <c r="N30" s="29">
+        <v>300.50399937000003</v>
+      </c>
+      <c r="O30" s="29">
+        <v>51.695999910000005</v>
+      </c>
+      <c r="P30" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O30" s="13">
-        <v>0</v>
-      </c>
-      <c r="P30" s="13">
+      <c r="Q30" s="13">
+        <v>0</v>
+      </c>
+      <c r="R30" s="13">
+        <v>0</v>
+      </c>
+      <c r="S30" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="13">
-        <v>0</v>
-      </c>
-      <c r="R30" s="13">
-        <v>0</v>
-      </c>
-      <c r="S30" s="13">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T30" s="6" t="s">
@@ -31468,7 +31455,7 @@
       </c>
       <c r="U30" s="4"/>
       <c r="V30" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>28</v>
       </c>
       <c r="W30" s="15">
@@ -31498,17 +31485,17 @@
     </row>
     <row r="31" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="28">
+        <f t="shared" si="6"/>
+        <v>45899</v>
+      </c>
+      <c r="B31" s="29">
+        <v>1044.8759995199989</v>
+      </c>
+      <c r="C31" s="29">
+        <v>189.37799994000002</v>
+      </c>
+      <c r="D31" s="13">
         <f t="shared" si="7"/>
-        <v>45899</v>
-      </c>
-      <c r="B31" s="13">
-        <v>0</v>
-      </c>
-      <c r="C31" s="13">
-        <v>0</v>
-      </c>
-      <c r="D31" s="13">
-        <f t="shared" si="8"/>
         <v>136</v>
       </c>
       <c r="E31" s="13">
@@ -31529,7 +31516,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K31" s="13">
@@ -31542,25 +31529,24 @@
       <c r="M31" s="13">
         <v>0</v>
       </c>
-      <c r="N31" s="13">
+      <c r="N31" s="29">
+        <v>308.30399930999977</v>
+      </c>
+      <c r="O31" s="29">
+        <v>57.863999920000005</v>
+      </c>
+      <c r="P31" s="13">
         <f t="shared" si="4"/>
-        <v>12</v>
-      </c>
-      <c r="O31" s="13">
-        <v>0</v>
-      </c>
-      <c r="P31" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="13">
+        <v>0</v>
+      </c>
+      <c r="R31" s="13">
+        <v>0</v>
+      </c>
+      <c r="S31" s="13">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="Q31" s="13">
-        <v>0</v>
-      </c>
-      <c r="R31" s="13">
-        <v>0</v>
-      </c>
-      <c r="S31" s="13">
-        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="T31" s="6" t="s">
@@ -31568,7 +31554,7 @@
       </c>
       <c r="U31" s="4"/>
       <c r="V31" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>29</v>
       </c>
       <c r="W31" s="15">
@@ -31598,17 +31584,17 @@
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="28">
+        <f t="shared" si="6"/>
+        <v>45900</v>
+      </c>
+      <c r="B32" s="29">
+        <v>1051.0919995099994</v>
+      </c>
+      <c r="C32" s="29">
+        <v>214.91399988000001</v>
+      </c>
+      <c r="D32" s="13">
         <f t="shared" si="7"/>
-        <v>45900</v>
-      </c>
-      <c r="B32" s="13">
-        <v>0</v>
-      </c>
-      <c r="C32" s="13">
-        <v>0</v>
-      </c>
-      <c r="D32" s="13">
-        <f t="shared" si="8"/>
         <v>35</v>
       </c>
       <c r="E32" s="13">
@@ -31629,7 +31615,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="K32" s="13">
@@ -31642,15 +31628,14 @@
       <c r="M32" s="13">
         <v>0</v>
       </c>
-      <c r="N32" s="13">
+      <c r="N32" s="29">
+        <v>273.71999938999977</v>
+      </c>
+      <c r="O32" s="29">
+        <v>53.255999909999986</v>
+      </c>
+      <c r="P32" s="13">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="O32" s="13">
-        <v>0</v>
-      </c>
-      <c r="P32" s="13">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q32" s="13">
@@ -31666,7 +31651,7 @@
       <c r="T32" s="6"/>
       <c r="U32" s="4"/>
       <c r="V32" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
       <c r="W32" s="15">
@@ -31697,7 +31682,7 @@
     <row r="33" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="U33" s="4"/>
       <c r="V33" s="18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="W33" s="15">
@@ -31727,14 +31712,14 @@
     </row>
     <row r="35" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -32112,15 +32097,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="47"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="47"/>
-      <c r="F70" s="47"/>
-      <c r="G70" s="47"/>
-      <c r="H70" s="47"/>
-      <c r="I70" s="47"/>
+      <c r="A70" s="51"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="51"/>
+      <c r="I70" s="51"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -32145,15 +32130,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="48"/>
-      <c r="B75" s="48"/>
-      <c r="C75" s="48"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
+      <c r="A75" s="52"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="F75" s="52"/>
+      <c r="G75" s="52"/>
+      <c r="H75" s="52"/>
+      <c r="I75" s="52"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -32189,15 +32174,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="49"/>
-      <c r="B79" s="49"/>
-      <c r="C79" s="49"/>
-      <c r="D79" s="49"/>
-      <c r="E79" s="49"/>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49"/>
+      <c r="A79" s="53"/>
+      <c r="B79" s="53"/>
+      <c r="C79" s="53"/>
+      <c r="D79" s="53"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
+      <c r="H79" s="53"/>
+      <c r="I79" s="53"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -32233,15 +32218,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="48"/>
-      <c r="B87" s="48"/>
-      <c r="C87" s="48"/>
-      <c r="D87" s="48"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48"/>
+      <c r="A87" s="52"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="52"/>
+      <c r="E87" s="52"/>
+      <c r="F87" s="52"/>
+      <c r="G87" s="52"/>
+      <c r="H87" s="52"/>
+      <c r="I87" s="52"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -32344,15 +32329,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="47"/>
-      <c r="B100" s="47"/>
-      <c r="C100" s="47"/>
-      <c r="D100" s="47"/>
-      <c r="E100" s="47"/>
-      <c r="F100" s="47"/>
-      <c r="G100" s="47"/>
-      <c r="H100" s="47"/>
-      <c r="I100" s="47"/>
+      <c r="A100" s="51"/>
+      <c r="B100" s="51"/>
+      <c r="C100" s="51"/>
+      <c r="D100" s="51"/>
+      <c r="E100" s="51"/>
+      <c r="F100" s="51"/>
+      <c r="G100" s="51"/>
+      <c r="H100" s="51"/>
+      <c r="I100" s="51"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -35603,14 +35588,14 @@
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -35988,15 +35973,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="47"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="47"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="47"/>
-      <c r="I71" s="47"/>
+      <c r="A71" s="51"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="51"/>
+      <c r="D71" s="51"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="51"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="51"/>
+      <c r="I71" s="51"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -36021,15 +36006,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="48"/>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -36065,15 +36050,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="49"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49"/>
+      <c r="A80" s="53"/>
+      <c r="B80" s="53"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -36109,15 +36094,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="48"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
+      <c r="A88" s="52"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="52"/>
+      <c r="G88" s="52"/>
+      <c r="H88" s="52"/>
+      <c r="I88" s="52"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -36220,15 +36205,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="47"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="47"/>
-      <c r="D101" s="47"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="47"/>
-      <c r="G101" s="47"/>
-      <c r="H101" s="47"/>
-      <c r="I101" s="47"/>
+      <c r="A101" s="51"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="51"/>
+      <c r="G101" s="51"/>
+      <c r="H101" s="51"/>
+      <c r="I101" s="51"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -39280,22 +39265,22 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="47"/>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47"/>
-      <c r="S35" s="47"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
+      <c r="J35" s="51"/>
+      <c r="K35" s="51"/>
+      <c r="L35" s="51"/>
+      <c r="M35" s="51"/>
+      <c r="N35" s="51"/>
+      <c r="O35" s="51"/>
+      <c r="P35" s="51"/>
+      <c r="Q35" s="51"/>
+      <c r="R35" s="51"/>
+      <c r="S35" s="51"/>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -40013,25 +39998,25 @@
       <c r="S69" s="1"/>
     </row>
     <row r="70" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="47"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="47"/>
-      <c r="F70" s="47"/>
-      <c r="G70" s="47"/>
-      <c r="H70" s="47"/>
-      <c r="I70" s="47"/>
-      <c r="J70" s="47"/>
-      <c r="K70" s="47"/>
-      <c r="L70" s="47"/>
-      <c r="M70" s="47"/>
-      <c r="N70" s="47"/>
-      <c r="O70" s="47"/>
-      <c r="P70" s="47"/>
-      <c r="Q70" s="47"/>
-      <c r="R70" s="47"/>
-      <c r="S70" s="47"/>
+      <c r="A70" s="51"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="51"/>
+      <c r="I70" s="51"/>
+      <c r="J70" s="51"/>
+      <c r="K70" s="51"/>
+      <c r="L70" s="51"/>
+      <c r="M70" s="51"/>
+      <c r="N70" s="51"/>
+      <c r="O70" s="51"/>
+      <c r="P70" s="51"/>
+      <c r="Q70" s="51"/>
+      <c r="R70" s="51"/>
+      <c r="S70" s="51"/>
     </row>
     <row r="71" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -40076,25 +40061,25 @@
       <c r="S72" s="23"/>
     </row>
     <row r="75" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="48"/>
-      <c r="B75" s="48"/>
-      <c r="C75" s="48"/>
-      <c r="D75" s="48"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
-      <c r="J75" s="48"/>
-      <c r="K75" s="48"/>
-      <c r="L75" s="48"/>
-      <c r="M75" s="48"/>
-      <c r="N75" s="48"/>
-      <c r="O75" s="48"/>
-      <c r="P75" s="48"/>
-      <c r="Q75" s="48"/>
-      <c r="R75" s="48"/>
-      <c r="S75" s="48"/>
+      <c r="A75" s="52"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="F75" s="52"/>
+      <c r="G75" s="52"/>
+      <c r="H75" s="52"/>
+      <c r="I75" s="52"/>
+      <c r="J75" s="52"/>
+      <c r="K75" s="52"/>
+      <c r="L75" s="52"/>
+      <c r="M75" s="52"/>
+      <c r="N75" s="52"/>
+      <c r="O75" s="52"/>
+      <c r="P75" s="52"/>
+      <c r="Q75" s="52"/>
+      <c r="R75" s="52"/>
+      <c r="S75" s="52"/>
     </row>
     <row r="76" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -40160,25 +40145,25 @@
       <c r="S78" s="25"/>
     </row>
     <row r="79" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="49"/>
-      <c r="B79" s="49"/>
-      <c r="C79" s="49"/>
-      <c r="D79" s="49"/>
-      <c r="E79" s="49"/>
-      <c r="F79" s="49"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="49"/>
-      <c r="J79" s="49"/>
-      <c r="K79" s="49"/>
-      <c r="L79" s="49"/>
-      <c r="M79" s="49"/>
-      <c r="N79" s="49"/>
-      <c r="O79" s="49"/>
-      <c r="P79" s="49"/>
-      <c r="Q79" s="49"/>
-      <c r="R79" s="49"/>
-      <c r="S79" s="49"/>
+      <c r="A79" s="53"/>
+      <c r="B79" s="53"/>
+      <c r="C79" s="53"/>
+      <c r="D79" s="53"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
+      <c r="H79" s="53"/>
+      <c r="I79" s="53"/>
+      <c r="J79" s="53"/>
+      <c r="K79" s="53"/>
+      <c r="L79" s="53"/>
+      <c r="M79" s="53"/>
+      <c r="N79" s="53"/>
+      <c r="O79" s="53"/>
+      <c r="P79" s="53"/>
+      <c r="Q79" s="53"/>
+      <c r="R79" s="53"/>
+      <c r="S79" s="53"/>
     </row>
     <row r="80" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -40242,25 +40227,25 @@
       <c r="E85" s="23"/>
     </row>
     <row r="87" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="48"/>
-      <c r="B87" s="48"/>
-      <c r="C87" s="48"/>
-      <c r="D87" s="48"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48"/>
-      <c r="J87" s="48"/>
-      <c r="K87" s="48"/>
-      <c r="L87" s="48"/>
-      <c r="M87" s="48"/>
-      <c r="N87" s="48"/>
-      <c r="O87" s="48"/>
-      <c r="P87" s="48"/>
-      <c r="Q87" s="48"/>
-      <c r="R87" s="48"/>
-      <c r="S87" s="48"/>
+      <c r="A87" s="52"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="52"/>
+      <c r="E87" s="52"/>
+      <c r="F87" s="52"/>
+      <c r="G87" s="52"/>
+      <c r="H87" s="52"/>
+      <c r="I87" s="52"/>
+      <c r="J87" s="52"/>
+      <c r="K87" s="52"/>
+      <c r="L87" s="52"/>
+      <c r="M87" s="52"/>
+      <c r="N87" s="52"/>
+      <c r="O87" s="52"/>
+      <c r="P87" s="52"/>
+      <c r="Q87" s="52"/>
+      <c r="R87" s="52"/>
+      <c r="S87" s="52"/>
     </row>
     <row r="88" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -40452,25 +40437,25 @@
       <c r="E98" s="26"/>
     </row>
     <row r="100" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="47"/>
-      <c r="B100" s="47"/>
-      <c r="C100" s="47"/>
-      <c r="D100" s="47"/>
-      <c r="E100" s="47"/>
-      <c r="F100" s="47"/>
-      <c r="G100" s="47"/>
-      <c r="H100" s="47"/>
-      <c r="I100" s="47"/>
-      <c r="J100" s="47"/>
-      <c r="K100" s="47"/>
-      <c r="L100" s="47"/>
-      <c r="M100" s="47"/>
-      <c r="N100" s="47"/>
-      <c r="O100" s="47"/>
-      <c r="P100" s="47"/>
-      <c r="Q100" s="47"/>
-      <c r="R100" s="47"/>
-      <c r="S100" s="47"/>
+      <c r="A100" s="51"/>
+      <c r="B100" s="51"/>
+      <c r="C100" s="51"/>
+      <c r="D100" s="51"/>
+      <c r="E100" s="51"/>
+      <c r="F100" s="51"/>
+      <c r="G100" s="51"/>
+      <c r="H100" s="51"/>
+      <c r="I100" s="51"/>
+      <c r="J100" s="51"/>
+      <c r="K100" s="51"/>
+      <c r="L100" s="51"/>
+      <c r="M100" s="51"/>
+      <c r="N100" s="51"/>
+      <c r="O100" s="51"/>
+      <c r="P100" s="51"/>
+      <c r="Q100" s="51"/>
+      <c r="R100" s="51"/>
+      <c r="S100" s="51"/>
     </row>
     <row r="101" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -43713,14 +43698,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -44098,15 +44083,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="47"/>
-      <c r="B71" s="47"/>
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="47"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="47"/>
-      <c r="I71" s="47"/>
+      <c r="A71" s="51"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="51"/>
+      <c r="D71" s="51"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="51"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="51"/>
+      <c r="I71" s="51"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -44131,15 +44116,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="48"/>
-      <c r="B76" s="48"/>
-      <c r="C76" s="48"/>
-      <c r="D76" s="48"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -44175,15 +44160,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="49"/>
-      <c r="B80" s="49"/>
-      <c r="C80" s="49"/>
-      <c r="D80" s="49"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="49"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49"/>
+      <c r="A80" s="53"/>
+      <c r="B80" s="53"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -44219,15 +44204,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="48"/>
-      <c r="B88" s="48"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
+      <c r="A88" s="52"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="52"/>
+      <c r="G88" s="52"/>
+      <c r="H88" s="52"/>
+      <c r="I88" s="52"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -44330,15 +44315,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="47"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="47"/>
-      <c r="D101" s="47"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="47"/>
-      <c r="G101" s="47"/>
-      <c r="H101" s="47"/>
-      <c r="I101" s="47"/>
+      <c r="A101" s="51"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="51"/>
+      <c r="G101" s="51"/>
+      <c r="H101" s="51"/>
+      <c r="I101" s="51"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A270C7E4-9A9E-4F8C-AD5C-7CDED42FD258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84721B69-2D56-44C0-827E-442DDC7AEF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -536,7 +536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -659,9 +659,6 @@
     </xf>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4896,15 +4893,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="51"/>
-      <c r="B69" s="51"/>
-      <c r="C69" s="51"/>
-      <c r="D69" s="51"/>
-      <c r="E69" s="51"/>
-      <c r="F69" s="51"/>
-      <c r="G69" s="51"/>
-      <c r="H69" s="51"/>
-      <c r="I69" s="51"/>
+      <c r="A69" s="50"/>
+      <c r="B69" s="50"/>
+      <c r="C69" s="50"/>
+      <c r="D69" s="50"/>
+      <c r="E69" s="50"/>
+      <c r="F69" s="50"/>
+      <c r="G69" s="50"/>
+      <c r="H69" s="50"/>
+      <c r="I69" s="50"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -4929,15 +4926,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="52"/>
-      <c r="B74" s="52"/>
-      <c r="C74" s="52"/>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="52"/>
-      <c r="G74" s="52"/>
-      <c r="H74" s="52"/>
-      <c r="I74" s="52"/>
+      <c r="A74" s="51"/>
+      <c r="B74" s="51"/>
+      <c r="C74" s="51"/>
+      <c r="D74" s="51"/>
+      <c r="E74" s="51"/>
+      <c r="F74" s="51"/>
+      <c r="G74" s="51"/>
+      <c r="H74" s="51"/>
+      <c r="I74" s="51"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -4973,15 +4970,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="53"/>
-      <c r="B78" s="53"/>
-      <c r="C78" s="53"/>
-      <c r="D78" s="53"/>
-      <c r="E78" s="53"/>
-      <c r="F78" s="53"/>
-      <c r="G78" s="53"/>
-      <c r="H78" s="53"/>
-      <c r="I78" s="53"/>
+      <c r="A78" s="52"/>
+      <c r="B78" s="52"/>
+      <c r="C78" s="52"/>
+      <c r="D78" s="52"/>
+      <c r="E78" s="52"/>
+      <c r="F78" s="52"/>
+      <c r="G78" s="52"/>
+      <c r="H78" s="52"/>
+      <c r="I78" s="52"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -5017,15 +5014,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="52"/>
-      <c r="B86" s="52"/>
-      <c r="C86" s="52"/>
-      <c r="D86" s="52"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="52"/>
-      <c r="G86" s="52"/>
-      <c r="H86" s="52"/>
-      <c r="I86" s="52"/>
+      <c r="A86" s="51"/>
+      <c r="B86" s="51"/>
+      <c r="C86" s="51"/>
+      <c r="D86" s="51"/>
+      <c r="E86" s="51"/>
+      <c r="F86" s="51"/>
+      <c r="G86" s="51"/>
+      <c r="H86" s="51"/>
+      <c r="I86" s="51"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -5128,15 +5125,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="51"/>
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
-      <c r="D99" s="51"/>
-      <c r="E99" s="51"/>
-      <c r="F99" s="51"/>
-      <c r="G99" s="51"/>
-      <c r="H99" s="51"/>
-      <c r="I99" s="51"/>
+      <c r="A99" s="50"/>
+      <c r="B99" s="50"/>
+      <c r="C99" s="50"/>
+      <c r="D99" s="50"/>
+      <c r="E99" s="50"/>
+      <c r="F99" s="50"/>
+      <c r="G99" s="50"/>
+      <c r="H99" s="50"/>
+      <c r="I99" s="50"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -8336,14 +8333,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="50"/>
+      <c r="I36" s="50"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -8720,15 +8717,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="51"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="51"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="51"/>
-      <c r="I71" s="51"/>
+      <c r="A71" s="50"/>
+      <c r="B71" s="50"/>
+      <c r="C71" s="50"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="50"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
+      <c r="H71" s="50"/>
+      <c r="I71" s="50"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -8753,15 +8750,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="52"/>
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
+      <c r="A76" s="51"/>
+      <c r="B76" s="51"/>
+      <c r="C76" s="51"/>
+      <c r="D76" s="51"/>
+      <c r="E76" s="51"/>
+      <c r="F76" s="51"/>
+      <c r="G76" s="51"/>
+      <c r="H76" s="51"/>
+      <c r="I76" s="51"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -8797,15 +8794,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="53"/>
-      <c r="B80" s="53"/>
-      <c r="C80" s="53"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53"/>
-      <c r="H80" s="53"/>
-      <c r="I80" s="53"/>
+      <c r="A80" s="52"/>
+      <c r="B80" s="52"/>
+      <c r="C80" s="52"/>
+      <c r="D80" s="52"/>
+      <c r="E80" s="52"/>
+      <c r="F80" s="52"/>
+      <c r="G80" s="52"/>
+      <c r="H80" s="52"/>
+      <c r="I80" s="52"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -8841,15 +8838,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="52"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="52"/>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
-      <c r="G88" s="52"/>
-      <c r="H88" s="52"/>
-      <c r="I88" s="52"/>
+      <c r="A88" s="51"/>
+      <c r="B88" s="51"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="51"/>
+      <c r="E88" s="51"/>
+      <c r="F88" s="51"/>
+      <c r="G88" s="51"/>
+      <c r="H88" s="51"/>
+      <c r="I88" s="51"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -8952,15 +8949,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="51"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
-      <c r="F101" s="51"/>
-      <c r="G101" s="51"/>
-      <c r="H101" s="51"/>
-      <c r="I101" s="51"/>
+      <c r="A101" s="50"/>
+      <c r="B101" s="50"/>
+      <c r="C101" s="50"/>
+      <c r="D101" s="50"/>
+      <c r="E101" s="50"/>
+      <c r="F101" s="50"/>
+      <c r="G101" s="50"/>
+      <c r="H101" s="50"/>
+      <c r="I101" s="50"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -11334,14 +11331,14 @@
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="51"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="50"/>
       <c r="T32" s="27"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
@@ -11719,15 +11716,15 @@
       <c r="I66" s="1"/>
     </row>
     <row r="67" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="51"/>
-      <c r="B67" s="51"/>
-      <c r="C67" s="51"/>
-      <c r="D67" s="51"/>
-      <c r="E67" s="51"/>
-      <c r="F67" s="51"/>
-      <c r="G67" s="51"/>
-      <c r="H67" s="51"/>
-      <c r="I67" s="51"/>
+      <c r="A67" s="50"/>
+      <c r="B67" s="50"/>
+      <c r="C67" s="50"/>
+      <c r="D67" s="50"/>
+      <c r="E67" s="50"/>
+      <c r="F67" s="50"/>
+      <c r="G67" s="50"/>
+      <c r="H67" s="50"/>
+      <c r="I67" s="50"/>
     </row>
     <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
@@ -11752,15 +11749,15 @@
       <c r="I69" s="23"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="52"/>
-      <c r="B72" s="52"/>
-      <c r="C72" s="52"/>
-      <c r="D72" s="52"/>
-      <c r="E72" s="52"/>
-      <c r="F72" s="52"/>
-      <c r="G72" s="52"/>
-      <c r="H72" s="52"/>
-      <c r="I72" s="52"/>
+      <c r="A72" s="51"/>
+      <c r="B72" s="51"/>
+      <c r="C72" s="51"/>
+      <c r="D72" s="51"/>
+      <c r="E72" s="51"/>
+      <c r="F72" s="51"/>
+      <c r="G72" s="51"/>
+      <c r="H72" s="51"/>
+      <c r="I72" s="51"/>
     </row>
     <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
@@ -11796,15 +11793,15 @@
       <c r="I75" s="25"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="53"/>
-      <c r="B76" s="53"/>
-      <c r="C76" s="53"/>
-      <c r="D76" s="53"/>
-      <c r="E76" s="53"/>
-      <c r="F76" s="53"/>
-      <c r="G76" s="53"/>
-      <c r="H76" s="53"/>
-      <c r="I76" s="53"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -11840,15 +11837,15 @@
       <c r="B82" s="23"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="52"/>
-      <c r="B84" s="52"/>
-      <c r="C84" s="52"/>
-      <c r="D84" s="52"/>
-      <c r="E84" s="52"/>
-      <c r="F84" s="52"/>
-      <c r="G84" s="52"/>
-      <c r="H84" s="52"/>
-      <c r="I84" s="52"/>
+      <c r="A84" s="51"/>
+      <c r="B84" s="51"/>
+      <c r="C84" s="51"/>
+      <c r="D84" s="51"/>
+      <c r="E84" s="51"/>
+      <c r="F84" s="51"/>
+      <c r="G84" s="51"/>
+      <c r="H84" s="51"/>
+      <c r="I84" s="51"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
@@ -11951,15 +11948,15 @@
       <c r="B95" s="26"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="51"/>
-      <c r="B97" s="51"/>
-      <c r="C97" s="51"/>
-      <c r="D97" s="51"/>
-      <c r="E97" s="51"/>
-      <c r="F97" s="51"/>
-      <c r="G97" s="51"/>
-      <c r="H97" s="51"/>
-      <c r="I97" s="51"/>
+      <c r="A97" s="50"/>
+      <c r="B97" s="50"/>
+      <c r="C97" s="50"/>
+      <c r="D97" s="50"/>
+      <c r="E97" s="50"/>
+      <c r="F97" s="50"/>
+      <c r="G97" s="50"/>
+      <c r="H97" s="50"/>
+      <c r="I97" s="50"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
@@ -14509,14 +14506,14 @@
     <row r="34" spans="1:21" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="50"/>
+      <c r="I36" s="50"/>
     </row>
     <row r="37" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -14893,15 +14890,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="51"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="51"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="51"/>
-      <c r="I71" s="51"/>
+      <c r="A71" s="50"/>
+      <c r="B71" s="50"/>
+      <c r="C71" s="50"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="50"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
+      <c r="H71" s="50"/>
+      <c r="I71" s="50"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -14926,15 +14923,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="52"/>
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
+      <c r="A76" s="51"/>
+      <c r="B76" s="51"/>
+      <c r="C76" s="51"/>
+      <c r="D76" s="51"/>
+      <c r="E76" s="51"/>
+      <c r="F76" s="51"/>
+      <c r="G76" s="51"/>
+      <c r="H76" s="51"/>
+      <c r="I76" s="51"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -14970,15 +14967,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="53"/>
-      <c r="B80" s="53"/>
-      <c r="C80" s="53"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53"/>
-      <c r="H80" s="53"/>
-      <c r="I80" s="53"/>
+      <c r="A80" s="52"/>
+      <c r="B80" s="52"/>
+      <c r="C80" s="52"/>
+      <c r="D80" s="52"/>
+      <c r="E80" s="52"/>
+      <c r="F80" s="52"/>
+      <c r="G80" s="52"/>
+      <c r="H80" s="52"/>
+      <c r="I80" s="52"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -15014,15 +15011,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="52"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="52"/>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
-      <c r="G88" s="52"/>
-      <c r="H88" s="52"/>
-      <c r="I88" s="52"/>
+      <c r="A88" s="51"/>
+      <c r="B88" s="51"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="51"/>
+      <c r="E88" s="51"/>
+      <c r="F88" s="51"/>
+      <c r="G88" s="51"/>
+      <c r="H88" s="51"/>
+      <c r="I88" s="51"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -15125,15 +15122,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="51"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
-      <c r="F101" s="51"/>
-      <c r="G101" s="51"/>
-      <c r="H101" s="51"/>
-      <c r="I101" s="51"/>
+      <c r="A101" s="50"/>
+      <c r="B101" s="50"/>
+      <c r="C101" s="50"/>
+      <c r="D101" s="50"/>
+      <c r="E101" s="50"/>
+      <c r="F101" s="50"/>
+      <c r="G101" s="50"/>
+      <c r="H101" s="50"/>
+      <c r="I101" s="50"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -17868,14 +17865,14 @@
     </row>
     <row r="35" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
+      <c r="B35" s="50"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="50"/>
     </row>
     <row r="36" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -18253,15 +18250,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="51"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="51"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="51"/>
-      <c r="I70" s="51"/>
+      <c r="A70" s="50"/>
+      <c r="B70" s="50"/>
+      <c r="C70" s="50"/>
+      <c r="D70" s="50"/>
+      <c r="E70" s="50"/>
+      <c r="F70" s="50"/>
+      <c r="G70" s="50"/>
+      <c r="H70" s="50"/>
+      <c r="I70" s="50"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -18286,15 +18283,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="52"/>
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="52"/>
+      <c r="A75" s="51"/>
+      <c r="B75" s="51"/>
+      <c r="C75" s="51"/>
+      <c r="D75" s="51"/>
+      <c r="E75" s="51"/>
+      <c r="F75" s="51"/>
+      <c r="G75" s="51"/>
+      <c r="H75" s="51"/>
+      <c r="I75" s="51"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -18330,15 +18327,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="53"/>
-      <c r="B79" s="53"/>
-      <c r="C79" s="53"/>
-      <c r="D79" s="53"/>
-      <c r="E79" s="53"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53"/>
-      <c r="H79" s="53"/>
-      <c r="I79" s="53"/>
+      <c r="A79" s="52"/>
+      <c r="B79" s="52"/>
+      <c r="C79" s="52"/>
+      <c r="D79" s="52"/>
+      <c r="E79" s="52"/>
+      <c r="F79" s="52"/>
+      <c r="G79" s="52"/>
+      <c r="H79" s="52"/>
+      <c r="I79" s="52"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -18374,15 +18371,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="52"/>
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
-      <c r="I87" s="52"/>
+      <c r="A87" s="51"/>
+      <c r="B87" s="51"/>
+      <c r="C87" s="51"/>
+      <c r="D87" s="51"/>
+      <c r="E87" s="51"/>
+      <c r="F87" s="51"/>
+      <c r="G87" s="51"/>
+      <c r="H87" s="51"/>
+      <c r="I87" s="51"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -18485,15 +18482,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="51"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
-      <c r="F100" s="51"/>
-      <c r="G100" s="51"/>
-      <c r="H100" s="51"/>
-      <c r="I100" s="51"/>
+      <c r="A100" s="50"/>
+      <c r="B100" s="50"/>
+      <c r="C100" s="50"/>
+      <c r="D100" s="50"/>
+      <c r="E100" s="50"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="50"/>
+      <c r="H100" s="50"/>
+      <c r="I100" s="50"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -21120,14 +21117,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
+      <c r="B35" s="50"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="50"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -21505,15 +21502,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="51"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="51"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="51"/>
-      <c r="I70" s="51"/>
+      <c r="A70" s="50"/>
+      <c r="B70" s="50"/>
+      <c r="C70" s="50"/>
+      <c r="D70" s="50"/>
+      <c r="E70" s="50"/>
+      <c r="F70" s="50"/>
+      <c r="G70" s="50"/>
+      <c r="H70" s="50"/>
+      <c r="I70" s="50"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -21538,15 +21535,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="52"/>
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="52"/>
+      <c r="A75" s="51"/>
+      <c r="B75" s="51"/>
+      <c r="C75" s="51"/>
+      <c r="D75" s="51"/>
+      <c r="E75" s="51"/>
+      <c r="F75" s="51"/>
+      <c r="G75" s="51"/>
+      <c r="H75" s="51"/>
+      <c r="I75" s="51"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -21582,15 +21579,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="53"/>
-      <c r="B79" s="53"/>
-      <c r="C79" s="53"/>
-      <c r="D79" s="53"/>
-      <c r="E79" s="53"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53"/>
-      <c r="H79" s="53"/>
-      <c r="I79" s="53"/>
+      <c r="A79" s="52"/>
+      <c r="B79" s="52"/>
+      <c r="C79" s="52"/>
+      <c r="D79" s="52"/>
+      <c r="E79" s="52"/>
+      <c r="F79" s="52"/>
+      <c r="G79" s="52"/>
+      <c r="H79" s="52"/>
+      <c r="I79" s="52"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -21626,15 +21623,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="52"/>
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
-      <c r="I87" s="52"/>
+      <c r="A87" s="51"/>
+      <c r="B87" s="51"/>
+      <c r="C87" s="51"/>
+      <c r="D87" s="51"/>
+      <c r="E87" s="51"/>
+      <c r="F87" s="51"/>
+      <c r="G87" s="51"/>
+      <c r="H87" s="51"/>
+      <c r="I87" s="51"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -21737,15 +21734,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="51"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
-      <c r="F100" s="51"/>
-      <c r="G100" s="51"/>
-      <c r="H100" s="51"/>
-      <c r="I100" s="51"/>
+      <c r="A100" s="50"/>
+      <c r="B100" s="50"/>
+      <c r="C100" s="50"/>
+      <c r="D100" s="50"/>
+      <c r="E100" s="50"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="50"/>
+      <c r="H100" s="50"/>
+      <c r="I100" s="50"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -24448,14 +24445,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="50"/>
+      <c r="I36" s="50"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -24833,15 +24830,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="51"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="51"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="51"/>
-      <c r="I71" s="51"/>
+      <c r="A71" s="50"/>
+      <c r="B71" s="50"/>
+      <c r="C71" s="50"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="50"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
+      <c r="H71" s="50"/>
+      <c r="I71" s="50"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -24866,15 +24863,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="52"/>
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
+      <c r="A76" s="51"/>
+      <c r="B76" s="51"/>
+      <c r="C76" s="51"/>
+      <c r="D76" s="51"/>
+      <c r="E76" s="51"/>
+      <c r="F76" s="51"/>
+      <c r="G76" s="51"/>
+      <c r="H76" s="51"/>
+      <c r="I76" s="51"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -24910,15 +24907,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="53"/>
-      <c r="B80" s="53"/>
-      <c r="C80" s="53"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53"/>
-      <c r="H80" s="53"/>
-      <c r="I80" s="53"/>
+      <c r="A80" s="52"/>
+      <c r="B80" s="52"/>
+      <c r="C80" s="52"/>
+      <c r="D80" s="52"/>
+      <c r="E80" s="52"/>
+      <c r="F80" s="52"/>
+      <c r="G80" s="52"/>
+      <c r="H80" s="52"/>
+      <c r="I80" s="52"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -24954,15 +24951,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="52"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="52"/>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
-      <c r="G88" s="52"/>
-      <c r="H88" s="52"/>
-      <c r="I88" s="52"/>
+      <c r="A88" s="51"/>
+      <c r="B88" s="51"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="51"/>
+      <c r="E88" s="51"/>
+      <c r="F88" s="51"/>
+      <c r="G88" s="51"/>
+      <c r="H88" s="51"/>
+      <c r="I88" s="51"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -25065,15 +25062,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="51"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
-      <c r="F101" s="51"/>
-      <c r="G101" s="51"/>
-      <c r="H101" s="51"/>
-      <c r="I101" s="51"/>
+      <c r="A101" s="50"/>
+      <c r="B101" s="50"/>
+      <c r="C101" s="50"/>
+      <c r="D101" s="50"/>
+      <c r="E101" s="50"/>
+      <c r="F101" s="50"/>
+      <c r="G101" s="50"/>
+      <c r="H101" s="50"/>
+      <c r="I101" s="50"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -25539,49 +25536,49 @@
       </c>
       <c r="D5" s="6">
         <f t="shared" si="0"/>
-        <v>-10679</v>
+        <v>87</v>
       </c>
       <c r="E5" s="6">
         <v>0</v>
       </c>
       <c r="F5" s="6">
         <f t="shared" si="1"/>
-        <v>-13165</v>
+        <v>77</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
       </c>
       <c r="H5" s="6">
         <f t="shared" si="2"/>
-        <v>-9658</v>
+        <v>3</v>
       </c>
       <c r="I5" s="6">
         <v>0</v>
       </c>
       <c r="J5" s="6">
         <f t="shared" si="3"/>
-        <v>-10863</v>
+        <v>1</v>
       </c>
       <c r="K5" s="6">
         <v>0</v>
       </c>
       <c r="L5" s="6">
         <f t="shared" si="4"/>
-        <v>-1288</v>
+        <v>0</v>
       </c>
       <c r="M5" s="6">
         <v>0</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" si="5"/>
-        <v>-4080</v>
+        <v>4</v>
       </c>
       <c r="O5" s="6">
         <v>0</v>
       </c>
       <c r="P5" s="6">
         <f t="shared" si="6"/>
-        <v>-413</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="6">
         <v>0</v>
@@ -25591,7 +25588,7 @@
       </c>
       <c r="S5" s="6">
         <f t="shared" si="7"/>
-        <v>-3666</v>
+        <v>3</v>
       </c>
       <c r="T5" s="6"/>
       <c r="U5" s="4"/>
@@ -25636,21 +25633,21 @@
       </c>
       <c r="D6" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E6" s="6">
         <v>0</v>
       </c>
       <c r="F6" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
       </c>
       <c r="H6" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I6" s="6">
         <v>0</v>
@@ -25664,14 +25661,14 @@
       </c>
       <c r="L6" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="6">
         <v>0</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" s="6">
         <v>0</v>
@@ -25688,7 +25685,7 @@
       </c>
       <c r="S6" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T6" s="6"/>
       <c r="U6" s="4"/>
@@ -25696,14 +25693,30 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
-      <c r="AB6" s="6"/>
-      <c r="AC6" s="6"/>
-      <c r="AD6" s="6"/>
+      <c r="W6" s="6">
+        <v>10766</v>
+      </c>
+      <c r="X6" s="6">
+        <v>13242</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>9661</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>10864</v>
+      </c>
+      <c r="AA6" s="6">
+        <v>1288</v>
+      </c>
+      <c r="AB6" s="6">
+        <v>4084</v>
+      </c>
+      <c r="AC6" s="6">
+        <v>414</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>3669</v>
+      </c>
     </row>
     <row r="7" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
@@ -25717,28 +25730,28 @@
       </c>
       <c r="D7" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E7" s="6">
         <v>0</v>
       </c>
       <c r="F7" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G7" s="6">
         <v>0</v>
       </c>
       <c r="H7" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I7" s="6">
         <v>0</v>
       </c>
       <c r="J7" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="6">
         <v>0</v>
@@ -25752,14 +25765,14 @@
       </c>
       <c r="N7" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O7" s="6">
         <v>0</v>
       </c>
       <c r="P7" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="6">
         <v>0</v>
@@ -25769,7 +25782,7 @@
       </c>
       <c r="S7" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T7" s="6"/>
       <c r="U7" s="4"/>
@@ -25777,14 +25790,30 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="6"/>
+      <c r="W7" s="6">
+        <v>10831</v>
+      </c>
+      <c r="X7" s="6">
+        <v>13361</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>9666</v>
+      </c>
+      <c r="Z7" s="6">
+        <v>10864</v>
+      </c>
+      <c r="AA7" s="6">
+        <v>1289</v>
+      </c>
+      <c r="AB7" s="6">
+        <v>4086</v>
+      </c>
+      <c r="AC7" s="6">
+        <v>414</v>
+      </c>
+      <c r="AD7" s="6">
+        <v>3671</v>
+      </c>
     </row>
     <row r="8" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
@@ -25798,28 +25827,28 @@
       </c>
       <c r="D8" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E8" s="6">
         <v>0</v>
       </c>
       <c r="F8" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G8" s="6">
         <v>0</v>
       </c>
       <c r="H8" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I8" s="6">
         <v>0</v>
       </c>
       <c r="J8" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="6">
         <v>0</v>
@@ -25833,7 +25862,7 @@
       </c>
       <c r="N8" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8" s="6">
         <v>0</v>
@@ -25850,7 +25879,7 @@
       </c>
       <c r="S8" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" s="6"/>
       <c r="U8" s="4"/>
@@ -25858,14 +25887,30 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
+      <c r="W8" s="6">
+        <v>10892</v>
+      </c>
+      <c r="X8" s="6">
+        <v>13394</v>
+      </c>
+      <c r="Y8" s="6">
+        <v>9671</v>
+      </c>
+      <c r="Z8" s="6">
+        <v>10865</v>
+      </c>
+      <c r="AA8" s="6">
+        <v>1289</v>
+      </c>
+      <c r="AB8" s="6">
+        <v>4093</v>
+      </c>
+      <c r="AC8" s="6">
+        <v>415</v>
+      </c>
+      <c r="AD8" s="6">
+        <v>3677</v>
+      </c>
     </row>
     <row r="9" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
@@ -25879,28 +25924,28 @@
       </c>
       <c r="D9" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E9" s="6">
         <v>0</v>
       </c>
       <c r="F9" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-291</v>
       </c>
       <c r="G9" s="6">
         <v>0</v>
       </c>
       <c r="H9" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I9" s="6">
         <v>0</v>
       </c>
       <c r="J9" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="6">
         <v>0</v>
@@ -25914,7 +25959,7 @@
       </c>
       <c r="N9" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O9" s="6">
         <v>0</v>
@@ -25931,7 +25976,7 @@
       </c>
       <c r="S9" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T9" s="6"/>
       <c r="U9" s="4"/>
@@ -25939,14 +25984,30 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="6"/>
-      <c r="AB9" s="6"/>
-      <c r="AC9" s="6"/>
-      <c r="AD9" s="6"/>
+      <c r="W9" s="6">
+        <v>10905</v>
+      </c>
+      <c r="X9" s="6">
+        <v>13446</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>9677</v>
+      </c>
+      <c r="Z9" s="6">
+        <v>10866</v>
+      </c>
+      <c r="AA9" s="6">
+        <v>1289</v>
+      </c>
+      <c r="AB9" s="6">
+        <v>4096</v>
+      </c>
+      <c r="AC9" s="6">
+        <v>415</v>
+      </c>
+      <c r="AD9" s="6">
+        <v>3680</v>
+      </c>
     </row>
     <row r="10" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
@@ -25960,49 +26021,49 @@
       </c>
       <c r="D10" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-10940</v>
       </c>
       <c r="E10" s="6">
         <v>0</v>
       </c>
       <c r="F10" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-13155</v>
       </c>
       <c r="G10" s="6">
         <v>0</v>
       </c>
       <c r="H10" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9682</v>
       </c>
       <c r="I10" s="6">
         <v>0</v>
       </c>
       <c r="J10" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-10867</v>
       </c>
       <c r="K10" s="6">
         <v>0</v>
       </c>
       <c r="L10" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1289</v>
       </c>
       <c r="M10" s="6">
         <v>0</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4102</v>
       </c>
       <c r="O10" s="6">
         <v>0</v>
       </c>
       <c r="P10" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-415</v>
       </c>
       <c r="Q10" s="6">
         <v>0</v>
@@ -26012,7 +26073,7 @@
       </c>
       <c r="S10" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3686</v>
       </c>
       <c r="T10" s="6"/>
       <c r="U10" s="4"/>
@@ -26020,14 +26081,30 @@
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="6"/>
-      <c r="AB10" s="6"/>
-      <c r="AC10" s="6"/>
-      <c r="AD10" s="6"/>
+      <c r="W10" s="6">
+        <v>10940</v>
+      </c>
+      <c r="X10" s="6">
+        <v>13155</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>9682</v>
+      </c>
+      <c r="Z10" s="6">
+        <v>10867</v>
+      </c>
+      <c r="AA10" s="6">
+        <v>1289</v>
+      </c>
+      <c r="AB10" s="6">
+        <v>4102</v>
+      </c>
+      <c r="AC10" s="6">
+        <v>415</v>
+      </c>
+      <c r="AD10" s="6">
+        <v>3686</v>
+      </c>
     </row>
     <row r="11" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
@@ -27757,14 +27834,14 @@
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="51"/>
-      <c r="I34" s="51"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="50"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
@@ -28142,15 +28219,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="51"/>
-      <c r="B69" s="51"/>
-      <c r="C69" s="51"/>
-      <c r="D69" s="51"/>
-      <c r="E69" s="51"/>
-      <c r="F69" s="51"/>
-      <c r="G69" s="51"/>
-      <c r="H69" s="51"/>
-      <c r="I69" s="51"/>
+      <c r="A69" s="50"/>
+      <c r="B69" s="50"/>
+      <c r="C69" s="50"/>
+      <c r="D69" s="50"/>
+      <c r="E69" s="50"/>
+      <c r="F69" s="50"/>
+      <c r="G69" s="50"/>
+      <c r="H69" s="50"/>
+      <c r="I69" s="50"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -28175,15 +28252,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="52"/>
-      <c r="B74" s="52"/>
-      <c r="C74" s="52"/>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="52"/>
-      <c r="G74" s="52"/>
-      <c r="H74" s="52"/>
-      <c r="I74" s="52"/>
+      <c r="A74" s="51"/>
+      <c r="B74" s="51"/>
+      <c r="C74" s="51"/>
+      <c r="D74" s="51"/>
+      <c r="E74" s="51"/>
+      <c r="F74" s="51"/>
+      <c r="G74" s="51"/>
+      <c r="H74" s="51"/>
+      <c r="I74" s="51"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -28219,15 +28296,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="53"/>
-      <c r="B78" s="53"/>
-      <c r="C78" s="53"/>
-      <c r="D78" s="53"/>
-      <c r="E78" s="53"/>
-      <c r="F78" s="53"/>
-      <c r="G78" s="53"/>
-      <c r="H78" s="53"/>
-      <c r="I78" s="53"/>
+      <c r="A78" s="52"/>
+      <c r="B78" s="52"/>
+      <c r="C78" s="52"/>
+      <c r="D78" s="52"/>
+      <c r="E78" s="52"/>
+      <c r="F78" s="52"/>
+      <c r="G78" s="52"/>
+      <c r="H78" s="52"/>
+      <c r="I78" s="52"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -28263,15 +28340,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="52"/>
-      <c r="B86" s="52"/>
-      <c r="C86" s="52"/>
-      <c r="D86" s="52"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="52"/>
-      <c r="G86" s="52"/>
-      <c r="H86" s="52"/>
-      <c r="I86" s="52"/>
+      <c r="A86" s="51"/>
+      <c r="B86" s="51"/>
+      <c r="C86" s="51"/>
+      <c r="D86" s="51"/>
+      <c r="E86" s="51"/>
+      <c r="F86" s="51"/>
+      <c r="G86" s="51"/>
+      <c r="H86" s="51"/>
+      <c r="I86" s="51"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -28374,15 +28451,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="51"/>
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
-      <c r="D99" s="51"/>
-      <c r="E99" s="51"/>
-      <c r="F99" s="51"/>
-      <c r="G99" s="51"/>
-      <c r="H99" s="51"/>
-      <c r="I99" s="51"/>
+      <c r="A99" s="50"/>
+      <c r="B99" s="50"/>
+      <c r="C99" s="50"/>
+      <c r="D99" s="50"/>
+      <c r="E99" s="50"/>
+      <c r="F99" s="50"/>
+      <c r="G99" s="50"/>
+      <c r="H99" s="50"/>
+      <c r="I99" s="50"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -28662,9 +28739,9 @@
         <f t="array" ref="AG2">_xlfn.IFS(AF2="Verde",0,AF2="Amarela",1.885,AF2="Vermelha P1",4.463,AF2="Vermelha P2",7.877)</f>
         <v>7.8769999999999998</v>
       </c>
-      <c r="AI2" s="47"/>
-      <c r="AJ2" s="48"/>
-      <c r="AK2" s="48"/>
+      <c r="AI2" s="46"/>
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
     </row>
     <row r="3" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="28">
@@ -28691,7 +28768,7 @@
       <c r="G3" s="13">
         <v>0</v>
       </c>
-      <c r="H3" s="46">
+      <c r="H3" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -28763,9 +28840,9 @@
       <c r="AD3" s="15">
         <v>3537</v>
       </c>
-      <c r="AI3" s="47"/>
-      <c r="AJ3" s="48"/>
-      <c r="AK3" s="48"/>
+      <c r="AI3" s="46"/>
+      <c r="AJ3" s="47"/>
+      <c r="AK3" s="47"/>
     </row>
     <row r="4" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="28">
@@ -28865,9 +28942,9 @@
       <c r="AD4" s="15">
         <v>3537</v>
       </c>
-      <c r="AI4" s="47"/>
-      <c r="AJ4" s="48"/>
-      <c r="AK4" s="48"/>
+      <c r="AI4" s="46"/>
+      <c r="AJ4" s="47"/>
+      <c r="AK4" s="47"/>
     </row>
     <row r="5" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="28">
@@ -28967,9 +29044,9 @@
       <c r="AD5" s="15">
         <v>3537</v>
       </c>
-      <c r="AI5" s="47"/>
-      <c r="AJ5" s="48"/>
-      <c r="AK5" s="48"/>
+      <c r="AI5" s="46"/>
+      <c r="AJ5" s="47"/>
+      <c r="AK5" s="47"/>
     </row>
     <row r="6" spans="1:40" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="28">
@@ -29069,9 +29146,9 @@
       <c r="AD6" s="6">
         <v>3551</v>
       </c>
-      <c r="AI6" s="47"/>
-      <c r="AJ6" s="48"/>
-      <c r="AK6" s="48"/>
+      <c r="AI6" s="46"/>
+      <c r="AJ6" s="47"/>
+      <c r="AK6" s="47"/>
     </row>
     <row r="7" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="28">
@@ -29171,8 +29248,8 @@
       <c r="AD7" s="6">
         <v>3553</v>
       </c>
-      <c r="AJ7" s="48"/>
-      <c r="AK7" s="48"/>
+      <c r="AJ7" s="47"/>
+      <c r="AK7" s="47"/>
     </row>
     <row r="8" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="28">
@@ -29272,12 +29349,12 @@
       <c r="AD8" s="6">
         <v>3558</v>
       </c>
-      <c r="AH8" s="54"/>
-      <c r="AI8" s="54"/>
-      <c r="AJ8" s="54"/>
-      <c r="AK8" s="55"/>
-      <c r="AL8" s="55"/>
-      <c r="AM8" s="55"/>
+      <c r="AH8" s="53"/>
+      <c r="AI8" s="53"/>
+      <c r="AJ8" s="53"/>
+      <c r="AK8" s="54"/>
+      <c r="AL8" s="54"/>
+      <c r="AM8" s="54"/>
     </row>
     <row r="9" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="28">
@@ -29377,11 +29454,11 @@
       <c r="AD9" s="6">
         <v>3561</v>
       </c>
-      <c r="AH9" s="47"/>
-      <c r="AI9" s="47"/>
-      <c r="AL9" s="48"/>
-      <c r="AM9" s="49"/>
-      <c r="AN9" s="49"/>
+      <c r="AH9" s="46"/>
+      <c r="AI9" s="46"/>
+      <c r="AL9" s="47"/>
+      <c r="AM9" s="48"/>
+      <c r="AN9" s="48"/>
     </row>
     <row r="10" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="28">
@@ -29481,11 +29558,11 @@
       <c r="AD10" s="6">
         <v>3568</v>
       </c>
-      <c r="AH10" s="47"/>
-      <c r="AI10" s="47"/>
-      <c r="AL10" s="48"/>
-      <c r="AM10" s="49"/>
-      <c r="AN10" s="49"/>
+      <c r="AH10" s="46"/>
+      <c r="AI10" s="46"/>
+      <c r="AL10" s="47"/>
+      <c r="AM10" s="48"/>
+      <c r="AN10" s="48"/>
     </row>
     <row r="11" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="28">
@@ -29585,11 +29662,11 @@
       <c r="AD11" s="6">
         <v>3568</v>
       </c>
-      <c r="AH11" s="47"/>
-      <c r="AI11" s="47"/>
-      <c r="AL11" s="48"/>
-      <c r="AM11" s="49"/>
-      <c r="AN11" s="49"/>
+      <c r="AH11" s="46"/>
+      <c r="AI11" s="46"/>
+      <c r="AL11" s="47"/>
+      <c r="AM11" s="48"/>
+      <c r="AN11" s="48"/>
     </row>
     <row r="12" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A12" s="28">
@@ -29689,11 +29766,11 @@
       <c r="AD12" s="6">
         <v>3572</v>
       </c>
-      <c r="AH12" s="47"/>
-      <c r="AI12" s="47"/>
-      <c r="AL12" s="48"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
+      <c r="AH12" s="46"/>
+      <c r="AI12" s="46"/>
+      <c r="AL12" s="47"/>
+      <c r="AM12" s="48"/>
+      <c r="AN12" s="48"/>
     </row>
     <row r="13" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
@@ -29793,11 +29870,11 @@
       <c r="AD13" s="15">
         <v>3572</v>
       </c>
-      <c r="AH13" s="47"/>
-      <c r="AI13" s="47"/>
-      <c r="AL13" s="48"/>
-      <c r="AM13" s="49"/>
-      <c r="AN13" s="49"/>
+      <c r="AH13" s="46"/>
+      <c r="AI13" s="46"/>
+      <c r="AL13" s="47"/>
+      <c r="AM13" s="48"/>
+      <c r="AN13" s="48"/>
     </row>
     <row r="14" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A14" s="28">
@@ -29897,7 +29974,7 @@
       <c r="AD14" s="6">
         <v>3581</v>
       </c>
-      <c r="AN14" s="49"/>
+      <c r="AN14" s="48"/>
     </row>
     <row r="15" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A15" s="28">
@@ -29996,7 +30073,7 @@
       <c r="AD15" s="6">
         <v>3581</v>
       </c>
-      <c r="AI15" s="50"/>
+      <c r="AI15" s="49"/>
     </row>
     <row r="16" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A16" s="28">
@@ -31712,14 +31789,14 @@
     </row>
     <row r="35" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
+      <c r="B35" s="50"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="50"/>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -32097,15 +32174,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="51"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="51"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="51"/>
-      <c r="I70" s="51"/>
+      <c r="A70" s="50"/>
+      <c r="B70" s="50"/>
+      <c r="C70" s="50"/>
+      <c r="D70" s="50"/>
+      <c r="E70" s="50"/>
+      <c r="F70" s="50"/>
+      <c r="G70" s="50"/>
+      <c r="H70" s="50"/>
+      <c r="I70" s="50"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -32130,15 +32207,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="52"/>
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="52"/>
+      <c r="A75" s="51"/>
+      <c r="B75" s="51"/>
+      <c r="C75" s="51"/>
+      <c r="D75" s="51"/>
+      <c r="E75" s="51"/>
+      <c r="F75" s="51"/>
+      <c r="G75" s="51"/>
+      <c r="H75" s="51"/>
+      <c r="I75" s="51"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -32174,15 +32251,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="53"/>
-      <c r="B79" s="53"/>
-      <c r="C79" s="53"/>
-      <c r="D79" s="53"/>
-      <c r="E79" s="53"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53"/>
-      <c r="H79" s="53"/>
-      <c r="I79" s="53"/>
+      <c r="A79" s="52"/>
+      <c r="B79" s="52"/>
+      <c r="C79" s="52"/>
+      <c r="D79" s="52"/>
+      <c r="E79" s="52"/>
+      <c r="F79" s="52"/>
+      <c r="G79" s="52"/>
+      <c r="H79" s="52"/>
+      <c r="I79" s="52"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -32218,15 +32295,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="52"/>
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
-      <c r="I87" s="52"/>
+      <c r="A87" s="51"/>
+      <c r="B87" s="51"/>
+      <c r="C87" s="51"/>
+      <c r="D87" s="51"/>
+      <c r="E87" s="51"/>
+      <c r="F87" s="51"/>
+      <c r="G87" s="51"/>
+      <c r="H87" s="51"/>
+      <c r="I87" s="51"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -32329,15 +32406,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="51"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
-      <c r="F100" s="51"/>
-      <c r="G100" s="51"/>
-      <c r="H100" s="51"/>
-      <c r="I100" s="51"/>
+      <c r="A100" s="50"/>
+      <c r="B100" s="50"/>
+      <c r="C100" s="50"/>
+      <c r="D100" s="50"/>
+      <c r="E100" s="50"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="50"/>
+      <c r="H100" s="50"/>
+      <c r="I100" s="50"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -32379,7 +32456,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -35588,14 +35665,14 @@
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="50"/>
+      <c r="I36" s="50"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -35973,15 +36050,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="51"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="51"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="51"/>
-      <c r="I71" s="51"/>
+      <c r="A71" s="50"/>
+      <c r="B71" s="50"/>
+      <c r="C71" s="50"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="50"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
+      <c r="H71" s="50"/>
+      <c r="I71" s="50"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -36006,15 +36083,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="52"/>
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
+      <c r="A76" s="51"/>
+      <c r="B76" s="51"/>
+      <c r="C76" s="51"/>
+      <c r="D76" s="51"/>
+      <c r="E76" s="51"/>
+      <c r="F76" s="51"/>
+      <c r="G76" s="51"/>
+      <c r="H76" s="51"/>
+      <c r="I76" s="51"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -36050,15 +36127,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="53"/>
-      <c r="B80" s="53"/>
-      <c r="C80" s="53"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53"/>
-      <c r="H80" s="53"/>
-      <c r="I80" s="53"/>
+      <c r="A80" s="52"/>
+      <c r="B80" s="52"/>
+      <c r="C80" s="52"/>
+      <c r="D80" s="52"/>
+      <c r="E80" s="52"/>
+      <c r="F80" s="52"/>
+      <c r="G80" s="52"/>
+      <c r="H80" s="52"/>
+      <c r="I80" s="52"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -36094,15 +36171,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="52"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="52"/>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
-      <c r="G88" s="52"/>
-      <c r="H88" s="52"/>
-      <c r="I88" s="52"/>
+      <c r="A88" s="51"/>
+      <c r="B88" s="51"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="51"/>
+      <c r="E88" s="51"/>
+      <c r="F88" s="51"/>
+      <c r="G88" s="51"/>
+      <c r="H88" s="51"/>
+      <c r="I88" s="51"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -36205,15 +36282,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="51"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
-      <c r="F101" s="51"/>
-      <c r="G101" s="51"/>
-      <c r="H101" s="51"/>
-      <c r="I101" s="51"/>
+      <c r="A101" s="50"/>
+      <c r="B101" s="50"/>
+      <c r="C101" s="50"/>
+      <c r="D101" s="50"/>
+      <c r="E101" s="50"/>
+      <c r="F101" s="50"/>
+      <c r="G101" s="50"/>
+      <c r="H101" s="50"/>
+      <c r="I101" s="50"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -39265,22 +39342,22 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
-      <c r="J35" s="51"/>
-      <c r="K35" s="51"/>
-      <c r="L35" s="51"/>
-      <c r="M35" s="51"/>
-      <c r="N35" s="51"/>
-      <c r="O35" s="51"/>
-      <c r="P35" s="51"/>
-      <c r="Q35" s="51"/>
-      <c r="R35" s="51"/>
-      <c r="S35" s="51"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="50"/>
+      <c r="J35" s="50"/>
+      <c r="K35" s="50"/>
+      <c r="L35" s="50"/>
+      <c r="M35" s="50"/>
+      <c r="N35" s="50"/>
+      <c r="O35" s="50"/>
+      <c r="P35" s="50"/>
+      <c r="Q35" s="50"/>
+      <c r="R35" s="50"/>
+      <c r="S35" s="50"/>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -39998,25 +40075,25 @@
       <c r="S69" s="1"/>
     </row>
     <row r="70" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="51"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="51"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="51"/>
-      <c r="I70" s="51"/>
-      <c r="J70" s="51"/>
-      <c r="K70" s="51"/>
-      <c r="L70" s="51"/>
-      <c r="M70" s="51"/>
-      <c r="N70" s="51"/>
-      <c r="O70" s="51"/>
-      <c r="P70" s="51"/>
-      <c r="Q70" s="51"/>
-      <c r="R70" s="51"/>
-      <c r="S70" s="51"/>
+      <c r="A70" s="50"/>
+      <c r="B70" s="50"/>
+      <c r="C70" s="50"/>
+      <c r="D70" s="50"/>
+      <c r="E70" s="50"/>
+      <c r="F70" s="50"/>
+      <c r="G70" s="50"/>
+      <c r="H70" s="50"/>
+      <c r="I70" s="50"/>
+      <c r="J70" s="50"/>
+      <c r="K70" s="50"/>
+      <c r="L70" s="50"/>
+      <c r="M70" s="50"/>
+      <c r="N70" s="50"/>
+      <c r="O70" s="50"/>
+      <c r="P70" s="50"/>
+      <c r="Q70" s="50"/>
+      <c r="R70" s="50"/>
+      <c r="S70" s="50"/>
     </row>
     <row r="71" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -40061,25 +40138,25 @@
       <c r="S72" s="23"/>
     </row>
     <row r="75" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="52"/>
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="52"/>
-      <c r="J75" s="52"/>
-      <c r="K75" s="52"/>
-      <c r="L75" s="52"/>
-      <c r="M75" s="52"/>
-      <c r="N75" s="52"/>
-      <c r="O75" s="52"/>
-      <c r="P75" s="52"/>
-      <c r="Q75" s="52"/>
-      <c r="R75" s="52"/>
-      <c r="S75" s="52"/>
+      <c r="A75" s="51"/>
+      <c r="B75" s="51"/>
+      <c r="C75" s="51"/>
+      <c r="D75" s="51"/>
+      <c r="E75" s="51"/>
+      <c r="F75" s="51"/>
+      <c r="G75" s="51"/>
+      <c r="H75" s="51"/>
+      <c r="I75" s="51"/>
+      <c r="J75" s="51"/>
+      <c r="K75" s="51"/>
+      <c r="L75" s="51"/>
+      <c r="M75" s="51"/>
+      <c r="N75" s="51"/>
+      <c r="O75" s="51"/>
+      <c r="P75" s="51"/>
+      <c r="Q75" s="51"/>
+      <c r="R75" s="51"/>
+      <c r="S75" s="51"/>
     </row>
     <row r="76" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -40145,25 +40222,25 @@
       <c r="S78" s="25"/>
     </row>
     <row r="79" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="53"/>
-      <c r="B79" s="53"/>
-      <c r="C79" s="53"/>
-      <c r="D79" s="53"/>
-      <c r="E79" s="53"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53"/>
-      <c r="H79" s="53"/>
-      <c r="I79" s="53"/>
-      <c r="J79" s="53"/>
-      <c r="K79" s="53"/>
-      <c r="L79" s="53"/>
-      <c r="M79" s="53"/>
-      <c r="N79" s="53"/>
-      <c r="O79" s="53"/>
-      <c r="P79" s="53"/>
-      <c r="Q79" s="53"/>
-      <c r="R79" s="53"/>
-      <c r="S79" s="53"/>
+      <c r="A79" s="52"/>
+      <c r="B79" s="52"/>
+      <c r="C79" s="52"/>
+      <c r="D79" s="52"/>
+      <c r="E79" s="52"/>
+      <c r="F79" s="52"/>
+      <c r="G79" s="52"/>
+      <c r="H79" s="52"/>
+      <c r="I79" s="52"/>
+      <c r="J79" s="52"/>
+      <c r="K79" s="52"/>
+      <c r="L79" s="52"/>
+      <c r="M79" s="52"/>
+      <c r="N79" s="52"/>
+      <c r="O79" s="52"/>
+      <c r="P79" s="52"/>
+      <c r="Q79" s="52"/>
+      <c r="R79" s="52"/>
+      <c r="S79" s="52"/>
     </row>
     <row r="80" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -40227,25 +40304,25 @@
       <c r="E85" s="23"/>
     </row>
     <row r="87" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="52"/>
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
-      <c r="I87" s="52"/>
-      <c r="J87" s="52"/>
-      <c r="K87" s="52"/>
-      <c r="L87" s="52"/>
-      <c r="M87" s="52"/>
-      <c r="N87" s="52"/>
-      <c r="O87" s="52"/>
-      <c r="P87" s="52"/>
-      <c r="Q87" s="52"/>
-      <c r="R87" s="52"/>
-      <c r="S87" s="52"/>
+      <c r="A87" s="51"/>
+      <c r="B87" s="51"/>
+      <c r="C87" s="51"/>
+      <c r="D87" s="51"/>
+      <c r="E87" s="51"/>
+      <c r="F87" s="51"/>
+      <c r="G87" s="51"/>
+      <c r="H87" s="51"/>
+      <c r="I87" s="51"/>
+      <c r="J87" s="51"/>
+      <c r="K87" s="51"/>
+      <c r="L87" s="51"/>
+      <c r="M87" s="51"/>
+      <c r="N87" s="51"/>
+      <c r="O87" s="51"/>
+      <c r="P87" s="51"/>
+      <c r="Q87" s="51"/>
+      <c r="R87" s="51"/>
+      <c r="S87" s="51"/>
     </row>
     <row r="88" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -40437,25 +40514,25 @@
       <c r="E98" s="26"/>
     </row>
     <row r="100" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="51"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
-      <c r="F100" s="51"/>
-      <c r="G100" s="51"/>
-      <c r="H100" s="51"/>
-      <c r="I100" s="51"/>
-      <c r="J100" s="51"/>
-      <c r="K100" s="51"/>
-      <c r="L100" s="51"/>
-      <c r="M100" s="51"/>
-      <c r="N100" s="51"/>
-      <c r="O100" s="51"/>
-      <c r="P100" s="51"/>
-      <c r="Q100" s="51"/>
-      <c r="R100" s="51"/>
-      <c r="S100" s="51"/>
+      <c r="A100" s="50"/>
+      <c r="B100" s="50"/>
+      <c r="C100" s="50"/>
+      <c r="D100" s="50"/>
+      <c r="E100" s="50"/>
+      <c r="F100" s="50"/>
+      <c r="G100" s="50"/>
+      <c r="H100" s="50"/>
+      <c r="I100" s="50"/>
+      <c r="J100" s="50"/>
+      <c r="K100" s="50"/>
+      <c r="L100" s="50"/>
+      <c r="M100" s="50"/>
+      <c r="N100" s="50"/>
+      <c r="O100" s="50"/>
+      <c r="P100" s="50"/>
+      <c r="Q100" s="50"/>
+      <c r="R100" s="50"/>
+      <c r="S100" s="50"/>
     </row>
     <row r="101" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -43698,14 +43775,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="50"/>
+      <c r="I36" s="50"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -44083,15 +44160,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="51"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="51"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="51"/>
-      <c r="I71" s="51"/>
+      <c r="A71" s="50"/>
+      <c r="B71" s="50"/>
+      <c r="C71" s="50"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="50"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
+      <c r="H71" s="50"/>
+      <c r="I71" s="50"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -44116,15 +44193,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="52"/>
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
+      <c r="A76" s="51"/>
+      <c r="B76" s="51"/>
+      <c r="C76" s="51"/>
+      <c r="D76" s="51"/>
+      <c r="E76" s="51"/>
+      <c r="F76" s="51"/>
+      <c r="G76" s="51"/>
+      <c r="H76" s="51"/>
+      <c r="I76" s="51"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -44160,15 +44237,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="53"/>
-      <c r="B80" s="53"/>
-      <c r="C80" s="53"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53"/>
-      <c r="H80" s="53"/>
-      <c r="I80" s="53"/>
+      <c r="A80" s="52"/>
+      <c r="B80" s="52"/>
+      <c r="C80" s="52"/>
+      <c r="D80" s="52"/>
+      <c r="E80" s="52"/>
+      <c r="F80" s="52"/>
+      <c r="G80" s="52"/>
+      <c r="H80" s="52"/>
+      <c r="I80" s="52"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -44204,15 +44281,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="52"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="52"/>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
-      <c r="G88" s="52"/>
-      <c r="H88" s="52"/>
-      <c r="I88" s="52"/>
+      <c r="A88" s="51"/>
+      <c r="B88" s="51"/>
+      <c r="C88" s="51"/>
+      <c r="D88" s="51"/>
+      <c r="E88" s="51"/>
+      <c r="F88" s="51"/>
+      <c r="G88" s="51"/>
+      <c r="H88" s="51"/>
+      <c r="I88" s="51"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -44315,15 +44392,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="51"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
-      <c r="F101" s="51"/>
-      <c r="G101" s="51"/>
-      <c r="H101" s="51"/>
-      <c r="I101" s="51"/>
+      <c r="A101" s="50"/>
+      <c r="B101" s="50"/>
+      <c r="C101" s="50"/>
+      <c r="D101" s="50"/>
+      <c r="E101" s="50"/>
+      <c r="F101" s="50"/>
+      <c r="G101" s="50"/>
+      <c r="H101" s="50"/>
+      <c r="I101" s="50"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84721B69-2D56-44C0-827E-442DDC7AEF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27146BBE-671B-455C-BAFE-2D055887FD17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25256,49 +25256,49 @@
       </c>
       <c r="D2" s="6">
         <f t="shared" ref="D2:D31" si="0">W3-W2</f>
-        <v>10512</v>
+        <v>21</v>
       </c>
       <c r="E2" s="6">
         <v>0</v>
       </c>
       <c r="F2" s="6">
         <f t="shared" ref="F2:F31" si="1">X3-X2</f>
-        <v>13072</v>
+        <v>30</v>
       </c>
       <c r="G2" s="6">
         <v>0</v>
       </c>
       <c r="H2" s="6">
         <f t="shared" ref="H2:H31" si="2">Y3-Y2</f>
-        <v>9649</v>
+        <v>5</v>
       </c>
       <c r="I2" s="6">
         <v>0</v>
       </c>
       <c r="J2" s="6">
         <f t="shared" ref="J2:J14" si="3">Z3-Z2</f>
-        <v>10861</v>
+        <v>0</v>
       </c>
       <c r="K2" s="6">
         <v>0</v>
       </c>
       <c r="L2" s="6">
         <f t="shared" ref="L2:L31" si="4">AA3-AA2</f>
-        <v>1288</v>
+        <v>0</v>
       </c>
       <c r="M2" s="6">
         <v>0</v>
       </c>
       <c r="N2" s="6">
         <f t="shared" ref="N2:N31" si="5">AB3-AB2</f>
-        <v>4072</v>
+        <v>5</v>
       </c>
       <c r="O2" s="6">
         <v>0</v>
       </c>
       <c r="P2" s="6">
         <f t="shared" ref="P2:P31" si="6">AC3-AC2</f>
-        <v>412</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="6">
         <v>0</v>
@@ -25308,21 +25308,37 @@
       </c>
       <c r="S2" s="6">
         <f t="shared" ref="S2:S31" si="7">AD3-AD2</f>
-        <v>3660</v>
+        <v>0</v>
       </c>
       <c r="T2" s="6"/>
       <c r="U2" s="4"/>
       <c r="V2" s="8">
         <v>0</v>
       </c>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
+      <c r="W2" s="15">
+        <v>10491</v>
+      </c>
+      <c r="X2" s="15">
+        <v>13042</v>
+      </c>
+      <c r="Y2" s="15">
+        <v>9644</v>
+      </c>
+      <c r="Z2" s="15">
+        <v>10861</v>
+      </c>
+      <c r="AA2" s="15">
+        <v>1288</v>
+      </c>
+      <c r="AB2" s="15">
+        <v>4067</v>
+      </c>
+      <c r="AC2" s="15">
+        <v>412</v>
+      </c>
+      <c r="AD2" s="15">
+        <v>3660</v>
+      </c>
       <c r="AF2" s="10" t="s">
         <v>29</v>
       </c>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27146BBE-671B-455C-BAFE-2D055887FD17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37061773-AB62-4D0F-B3FB-9300CA33FBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -536,7 +536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -678,6 +678,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1443,34 +1445,34 @@
         <v>12666.75</v>
       </c>
       <c r="D9" s="41">
-        <v>0</v>
+        <v>1057.021</v>
       </c>
       <c r="E9" s="41">
-        <v>0</v>
+        <v>453.00899999999996</v>
       </c>
       <c r="F9" s="41">
-        <v>0</v>
+        <v>1199.492</v>
       </c>
       <c r="G9" s="41">
-        <v>0</v>
+        <v>514.06799999999998</v>
       </c>
       <c r="H9" s="41">
-        <v>0</v>
+        <v>4666.942</v>
       </c>
       <c r="I9" s="41">
-        <v>0</v>
+        <v>2000.1179999999999</v>
       </c>
       <c r="J9" s="41">
-        <v>0</v>
+        <v>1162.2729999999999</v>
       </c>
       <c r="K9" s="41">
-        <v>0</v>
+        <v>498.11700000000002</v>
       </c>
       <c r="L9" s="41">
-        <v>0</v>
+        <v>1192.8</v>
       </c>
       <c r="M9" s="41">
-        <v>0</v>
+        <v>511.2</v>
       </c>
       <c r="N9" s="41">
         <v>8025.6900000000005</v>
@@ -1728,7 +1730,9 @@
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="D16" s="56"/>
       <c r="E16" s="44"/>
+      <c r="F16" s="47"/>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.2">
       <c r="D17" s="45"/>
@@ -25947,7 +25951,7 @@
       </c>
       <c r="F9" s="6">
         <f t="shared" si="1"/>
-        <v>-291</v>
+        <v>0</v>
       </c>
       <c r="G9" s="6">
         <v>0</v>
@@ -26044,7 +26048,7 @@
       </c>
       <c r="F10" s="6">
         <f t="shared" si="1"/>
-        <v>-13155</v>
+        <v>-13446</v>
       </c>
       <c r="G10" s="6">
         <v>0</v>
@@ -26101,7 +26105,7 @@
         <v>10940</v>
       </c>
       <c r="X10" s="6">
-        <v>13155</v>
+        <v>13446</v>
       </c>
       <c r="Y10" s="6">
         <v>9682</v>
@@ -28550,7 +28554,7 @@
     <col min="7" max="7" width="13.42578125" customWidth="1"/>
     <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
     <col min="20" max="20" width="23" customWidth="1"/>
     <col min="36" max="36" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -28676,26 +28680,23 @@
       <c r="G2" s="13">
         <v>0</v>
       </c>
-      <c r="H2" s="13">
-        <f t="shared" ref="H2:H32" si="1">Y3-Y2</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="13">
-        <v>0</v>
-      </c>
-      <c r="J2" s="13">
-        <f t="shared" ref="J2:J14" si="2">Z3-Z2</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="13">
-        <v>0</v>
-      </c>
-      <c r="L2" s="13">
-        <f t="shared" ref="L2:L32" si="3">AA3-AA2</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="13">
-        <v>0</v>
+      <c r="H2" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I2" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J2" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K2" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L2" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M2" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N2" s="29">
         <v>250.15199932999991</v>
@@ -28704,7 +28705,7 @@
         <v>55.439999880000009</v>
       </c>
       <c r="P2" s="13">
-        <f t="shared" ref="P2:P32" si="4">AC3-AC2</f>
+        <f t="shared" ref="P2:P32" si="1">AC3-AC2</f>
         <v>0</v>
       </c>
       <c r="Q2" s="13">
@@ -28714,7 +28715,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="13">
-        <f t="shared" ref="S2:S31" si="5">AD3-AD2</f>
+        <f t="shared" ref="S2:S31" si="2">AD3-AD2</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -28761,7 +28762,7 @@
     </row>
     <row r="3" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="28">
-        <f t="shared" ref="A3:A32" si="6">A2+1</f>
+        <f t="shared" ref="A3:A32" si="3">A2+1</f>
         <v>45871</v>
       </c>
       <c r="B3" s="29">
@@ -28771,7 +28772,7 @@
         <v>175.93799990000002</v>
       </c>
       <c r="D3" s="13">
-        <f t="shared" ref="D3:D32" si="7">W4-W3</f>
+        <f t="shared" ref="D3:D32" si="4">W4-W3</f>
         <v>0</v>
       </c>
       <c r="E3" s="13">
@@ -28784,26 +28785,23 @@
       <c r="G3" s="13">
         <v>0</v>
       </c>
-      <c r="H3" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I3" s="13">
-        <v>0</v>
-      </c>
-      <c r="J3" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K3" s="13">
-        <v>0</v>
-      </c>
-      <c r="L3" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M3" s="13">
-        <v>0</v>
+      <c r="H3" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I3" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J3" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K3" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L3" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M3" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N3" s="29">
         <v>269.23199937999982</v>
@@ -28812,7 +28810,7 @@
         <v>58.75199988</v>
       </c>
       <c r="P3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q3" s="13">
@@ -28822,7 +28820,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -28862,7 +28860,7 @@
     </row>
     <row r="4" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45872</v>
       </c>
       <c r="B4" s="29">
@@ -28872,7 +28870,7 @@
         <v>151.15799993000002</v>
       </c>
       <c r="D4" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E4" s="13">
@@ -28885,26 +28883,23 @@
       <c r="G4" s="13">
         <v>0</v>
       </c>
-      <c r="H4" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I4" s="13">
-        <v>0</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="13">
-        <v>0</v>
-      </c>
-      <c r="L4" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M4" s="13">
-        <v>0</v>
+      <c r="H4" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I4" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J4" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K4" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L4" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M4" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N4" s="29">
         <v>251.61599932999988</v>
@@ -28913,7 +28908,7 @@
         <v>49.031999909999996</v>
       </c>
       <c r="P4" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q4" s="13">
@@ -28923,7 +28918,7 @@
         <v>0</v>
       </c>
       <c r="S4" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -28931,7 +28926,7 @@
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="14">
-        <f t="shared" ref="V4:V33" si="8">V3+1</f>
+        <f t="shared" ref="V4:V33" si="5">V3+1</f>
         <v>2</v>
       </c>
       <c r="W4" s="15">
@@ -28964,7 +28959,7 @@
     </row>
     <row r="5" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45873</v>
       </c>
       <c r="B5" s="29">
@@ -28974,7 +28969,7 @@
         <v>176.39999990000001</v>
       </c>
       <c r="D5" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>147</v>
       </c>
       <c r="E5" s="13">
@@ -28987,26 +28982,23 @@
       <c r="G5" s="13">
         <v>0</v>
       </c>
-      <c r="H5" s="13">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="I5" s="13">
-        <v>0</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="K5" s="13">
-        <v>0</v>
-      </c>
-      <c r="L5" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="13">
-        <v>0</v>
+      <c r="H5" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I5" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J5" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K5" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L5" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M5" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N5" s="29">
         <v>273.88799932999984</v>
@@ -29015,7 +29007,7 @@
         <v>59.375999899999997</v>
       </c>
       <c r="P5" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="Q5" s="13">
@@ -29025,7 +29017,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -29033,7 +29025,7 @@
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="W5" s="15">
@@ -29066,7 +29058,7 @@
     </row>
     <row r="6" spans="1:40" ht="51" x14ac:dyDescent="0.2">
       <c r="A6" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45874</v>
       </c>
       <c r="B6" s="29">
@@ -29076,7 +29068,7 @@
         <v>178.2479999</v>
       </c>
       <c r="D6" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>43</v>
       </c>
       <c r="E6" s="13">
@@ -29089,26 +29081,23 @@
       <c r="G6" s="13">
         <v>0</v>
       </c>
-      <c r="H6" s="13">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="I6" s="13">
-        <v>0</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="K6" s="13">
-        <v>0</v>
-      </c>
-      <c r="L6" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="13">
-        <v>0</v>
+      <c r="H6" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I6" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J6" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K6" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L6" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M6" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N6" s="29">
         <v>263.99999931999992</v>
@@ -29117,7 +29106,7 @@
         <v>52.079999899999997</v>
       </c>
       <c r="P6" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q6" s="13">
@@ -29127,7 +29116,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -29135,7 +29124,7 @@
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="W6" s="6">
@@ -29168,7 +29157,7 @@
     </row>
     <row r="7" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45875</v>
       </c>
       <c r="B7" s="29">
@@ -29178,7 +29167,7 @@
         <v>182.0279999</v>
       </c>
       <c r="D7" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>61</v>
       </c>
       <c r="E7" s="13">
@@ -29191,26 +29180,23 @@
       <c r="G7" s="13">
         <v>0</v>
       </c>
-      <c r="H7" s="13">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="I7" s="13">
-        <v>0</v>
-      </c>
-      <c r="J7" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="13">
-        <v>0</v>
-      </c>
-      <c r="L7" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="13">
-        <v>0</v>
+      <c r="H7" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I7" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J7" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K7" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L7" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M7" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N7" s="29">
         <v>269.03999940999984</v>
@@ -29219,7 +29205,7 @@
         <v>52.05599989000001</v>
       </c>
       <c r="P7" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q7" s="13">
@@ -29229,17 +29215,17 @@
         <v>0</v>
       </c>
       <c r="S7" s="13">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="T7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="U7" s="4"/>
+      <c r="V7" s="14">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="T7" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="U7" s="4"/>
-      <c r="V7" s="14">
-        <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
       <c r="W7" s="6">
         <v>9325</v>
       </c>
@@ -29269,7 +29255,7 @@
     </row>
     <row r="8" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45876</v>
       </c>
       <c r="B8" s="29">
@@ -29279,7 +29265,7 @@
         <v>225.11999994000001</v>
       </c>
       <c r="D8" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="E8" s="13">
@@ -29292,26 +29278,23 @@
       <c r="G8" s="13">
         <v>0</v>
       </c>
-      <c r="H8" s="13">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="I8" s="13">
-        <v>0</v>
-      </c>
-      <c r="J8" s="13">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="K8" s="13">
-        <v>0</v>
-      </c>
-      <c r="L8" s="13">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="M8" s="13">
-        <v>0</v>
+      <c r="H8" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I8" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J8" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K8" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L8" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M8" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N8" s="29">
         <v>260.87999933999964</v>
@@ -29320,7 +29303,7 @@
         <v>60.839999890000001</v>
       </c>
       <c r="P8" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q8" s="13">
@@ -29330,7 +29313,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -29338,7 +29321,7 @@
       </c>
       <c r="U8" s="4"/>
       <c r="V8" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="W8" s="6">
@@ -29374,7 +29357,7 @@
     </row>
     <row r="9" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45877</v>
       </c>
       <c r="B9" s="29">
@@ -29384,7 +29367,7 @@
         <v>202.01999991</v>
       </c>
       <c r="D9" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>69</v>
       </c>
       <c r="E9" s="13">
@@ -29397,26 +29380,23 @@
       <c r="G9" s="13">
         <v>0</v>
       </c>
-      <c r="H9" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="13">
-        <v>0</v>
-      </c>
-      <c r="J9" s="13">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="K9" s="13">
-        <v>0</v>
-      </c>
-      <c r="L9" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="13">
-        <v>0</v>
+      <c r="H9" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I9" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J9" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K9" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L9" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M9" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N9" s="29">
         <v>277.10399936999966</v>
@@ -29425,7 +29405,7 @@
         <v>49.511999879999998</v>
       </c>
       <c r="P9" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q9" s="13">
@@ -29435,7 +29415,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -29443,7 +29423,7 @@
       </c>
       <c r="U9" s="4"/>
       <c r="V9" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="W9" s="6">
@@ -29478,7 +29458,7 @@
     </row>
     <row r="10" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45878</v>
       </c>
       <c r="B10" s="29">
@@ -29488,7 +29468,7 @@
         <v>163.12799993999997</v>
       </c>
       <c r="D10" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>46</v>
       </c>
       <c r="E10" s="13">
@@ -29501,26 +29481,23 @@
       <c r="G10" s="13">
         <v>0</v>
       </c>
-      <c r="H10" s="13">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="I10" s="13">
-        <v>0</v>
-      </c>
-      <c r="J10" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="13">
-        <v>0</v>
-      </c>
-      <c r="L10" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="13">
-        <v>0</v>
+      <c r="H10" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I10" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J10" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K10" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L10" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M10" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N10" s="29">
         <v>251.39999929999985</v>
@@ -29529,7 +29506,7 @@
         <v>45.959999910000001</v>
       </c>
       <c r="P10" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q10" s="13">
@@ -29539,7 +29516,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T10" s="6" t="s">
@@ -29547,7 +29524,7 @@
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="W10" s="6">
@@ -29582,7 +29559,7 @@
     </row>
     <row r="11" spans="1:40" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45879</v>
       </c>
       <c r="B11" s="29">
@@ -29592,7 +29569,7 @@
         <v>143.72399992999999</v>
       </c>
       <c r="D11" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="E11" s="13">
@@ -29605,26 +29582,23 @@
       <c r="G11" s="13">
         <v>0</v>
       </c>
-      <c r="H11" s="13">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="I11" s="13">
-        <v>0</v>
-      </c>
-      <c r="J11" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="13">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="M11" s="13">
-        <v>0</v>
+      <c r="H11" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I11" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J11" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K11" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L11" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M11" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N11" s="29">
         <v>232.34399937999984</v>
@@ -29633,7 +29607,7 @@
         <v>57.167999909999999</v>
       </c>
       <c r="P11" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q11" s="13">
@@ -29643,7 +29617,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="T11" s="6" t="s">
@@ -29651,7 +29625,7 @@
       </c>
       <c r="U11" s="4"/>
       <c r="V11" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="W11" s="6">
@@ -29686,7 +29660,7 @@
     </row>
     <row r="12" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A12" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45880</v>
       </c>
       <c r="B12" s="29">
@@ -29696,7 +29670,7 @@
         <v>190.46999993</v>
       </c>
       <c r="D12" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="E12" s="13">
@@ -29709,26 +29683,23 @@
       <c r="G12" s="13">
         <v>0</v>
       </c>
-      <c r="H12" s="13">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="I12" s="13">
-        <v>0</v>
-      </c>
-      <c r="J12" s="13">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="K12" s="13">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="13">
-        <v>0</v>
+      <c r="H12" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I12" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J12" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K12" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L12" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M12" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N12" s="29">
         <v>227.95199947999987</v>
@@ -29737,7 +29708,7 @@
         <v>55.751999879999985</v>
       </c>
       <c r="P12" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q12" s="13">
@@ -29747,7 +29718,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T12" s="6" t="s">
@@ -29755,7 +29726,7 @@
       </c>
       <c r="U12" s="4"/>
       <c r="V12" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="W12" s="6">
@@ -29790,7 +29761,7 @@
     </row>
     <row r="13" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45881</v>
       </c>
       <c r="B13" s="29">
@@ -29800,7 +29771,7 @@
         <v>234.65399993999998</v>
       </c>
       <c r="D13" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>42</v>
       </c>
       <c r="E13" s="13">
@@ -29813,26 +29784,23 @@
       <c r="G13" s="13">
         <v>0</v>
       </c>
-      <c r="H13" s="13">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="I13" s="13">
-        <v>0</v>
-      </c>
-      <c r="J13" s="13">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="K13" s="13">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="13">
-        <v>0</v>
+      <c r="H13" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I13" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J13" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K13" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L13" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M13" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N13" s="29">
         <v>247.17599935999982</v>
@@ -29841,7 +29809,7 @@
         <v>58.679999909999999</v>
       </c>
       <c r="P13" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q13" s="13">
@@ -29851,7 +29819,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -29859,7 +29827,7 @@
       </c>
       <c r="U13" s="4"/>
       <c r="V13" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="W13" s="15">
@@ -29894,7 +29862,7 @@
     </row>
     <row r="14" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A14" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45882</v>
       </c>
       <c r="B14" s="29">
@@ -29904,7 +29872,7 @@
         <v>232.09199993999999</v>
       </c>
       <c r="D14" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="E14" s="13">
@@ -29917,26 +29885,23 @@
       <c r="G14" s="13">
         <v>0</v>
       </c>
-      <c r="H14" s="13">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="I14" s="13">
-        <v>0</v>
-      </c>
-      <c r="J14" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="13">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="M14" s="13">
-        <v>0</v>
+      <c r="H14" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I14" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J14" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K14" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L14" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M14" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N14" s="29">
         <v>258.83999937000016</v>
@@ -29945,7 +29910,7 @@
         <v>54.287999900000003</v>
       </c>
       <c r="P14" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q14" s="13">
@@ -29955,7 +29920,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T14" s="6" t="s">
@@ -29963,7 +29928,7 @@
       </c>
       <c r="U14" s="4"/>
       <c r="V14" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="W14" s="6">
@@ -29994,7 +29959,7 @@
     </row>
     <row r="15" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A15" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45883</v>
       </c>
       <c r="B15" s="29">
@@ -30004,7 +29969,7 @@
         <v>214.19999989999999</v>
       </c>
       <c r="D15" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>90</v>
       </c>
       <c r="E15" s="13">
@@ -30017,25 +29982,23 @@
       <c r="G15" s="13">
         <v>0</v>
       </c>
-      <c r="H15" s="13">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="I15" s="13">
-        <v>0</v>
-      </c>
-      <c r="J15" s="13">
-        <v>1</v>
-      </c>
-      <c r="K15" s="13">
-        <v>0</v>
-      </c>
-      <c r="L15" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="13">
-        <v>0</v>
+      <c r="H15" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I15" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J15" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K15" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L15" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M15" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N15" s="29">
         <v>299.83199936999978</v>
@@ -30044,7 +30007,7 @@
         <v>60.935999920000015</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q15" s="13">
@@ -30054,7 +30017,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="T15" s="6" t="s">
@@ -30062,7 +30025,7 @@
       </c>
       <c r="U15" s="4"/>
       <c r="V15" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="W15" s="6">
@@ -30093,7 +30056,7 @@
     </row>
     <row r="16" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A16" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45884</v>
       </c>
       <c r="B16" s="29">
@@ -30103,7 +30066,7 @@
         <v>181.60799991000002</v>
       </c>
       <c r="D16" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>53</v>
       </c>
       <c r="E16" s="13">
@@ -30116,26 +30079,23 @@
       <c r="G16" s="13">
         <v>0</v>
       </c>
-      <c r="H16" s="13">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="I16" s="13">
-        <v>0</v>
-      </c>
-      <c r="J16" s="13">
-        <f t="shared" ref="J16:J32" si="9">Z17-Z16</f>
-        <v>1</v>
-      </c>
-      <c r="K16" s="13">
-        <v>0</v>
-      </c>
-      <c r="L16" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="13">
-        <v>0</v>
+      <c r="H16" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I16" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J16" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K16" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L16" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M16" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N16" s="29">
         <v>258.45599932999994</v>
@@ -30144,7 +30104,7 @@
         <v>61.87199992</v>
       </c>
       <c r="P16" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q16" s="13">
@@ -30154,7 +30114,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="T16" s="6" t="s">
@@ -30162,7 +30122,7 @@
       </c>
       <c r="U16" s="4"/>
       <c r="V16" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="W16" s="16">
@@ -30192,7 +30152,7 @@
     </row>
     <row r="17" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45885</v>
       </c>
       <c r="B17" s="29">
@@ -30202,7 +30162,7 @@
         <v>184.84199990999997</v>
       </c>
       <c r="D17" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E17" s="13">
@@ -30215,26 +30175,23 @@
       <c r="G17" s="13">
         <v>0</v>
       </c>
-      <c r="H17" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="13">
-        <v>0</v>
-      </c>
-      <c r="J17" s="13">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="13">
-        <v>0</v>
-      </c>
-      <c r="L17" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="13">
-        <v>0</v>
+      <c r="H17" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I17" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J17" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K17" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L17" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M17" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N17" s="29">
         <v>259.39199942999977</v>
@@ -30243,7 +30200,7 @@
         <v>56.687999900000001</v>
       </c>
       <c r="P17" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q17" s="13">
@@ -30253,7 +30210,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T17" s="6" t="s">
@@ -30261,7 +30218,7 @@
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="W17" s="16">
@@ -30291,7 +30248,7 @@
     </row>
     <row r="18" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45886</v>
       </c>
       <c r="B18" s="29">
@@ -30301,7 +30258,7 @@
         <v>197.60999991</v>
       </c>
       <c r="D18" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>43</v>
       </c>
       <c r="E18" s="13">
@@ -30314,26 +30271,23 @@
       <c r="G18" s="13">
         <v>0</v>
       </c>
-      <c r="H18" s="13">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="I18" s="13">
-        <v>0</v>
-      </c>
-      <c r="J18" s="13">
-        <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="K18" s="13">
-        <v>0</v>
-      </c>
-      <c r="L18" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="13">
-        <v>0</v>
+      <c r="H18" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I18" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J18" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K18" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L18" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M18" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N18" s="29">
         <v>277.94399946999999</v>
@@ -30342,7 +30296,7 @@
         <v>62.567999910000005</v>
       </c>
       <c r="P18" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q18" s="13">
@@ -30352,7 +30306,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="T18" s="6" t="s">
@@ -30360,7 +30314,7 @@
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="W18" s="16">
@@ -30390,7 +30344,7 @@
     </row>
     <row r="19" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A19" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45887</v>
       </c>
       <c r="B19" s="29">
@@ -30400,7 +30354,7 @@
         <v>259.05599991000003</v>
       </c>
       <c r="D19" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="E19" s="13">
@@ -30413,26 +30367,23 @@
       <c r="G19" s="13">
         <v>0</v>
       </c>
-      <c r="H19" s="13">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="I19" s="13">
-        <v>0</v>
-      </c>
-      <c r="J19" s="13">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="K19" s="13">
-        <v>0</v>
-      </c>
-      <c r="L19" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="13">
-        <v>0</v>
+      <c r="H19" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I19" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J19" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K19" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L19" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M19" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N19" s="29">
         <v>281.27999936999993</v>
@@ -30441,7 +30392,7 @@
         <v>61.583999900000009</v>
       </c>
       <c r="P19" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q19" s="13">
@@ -30451,7 +30402,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="T19" s="6" t="s">
@@ -30459,7 +30410,7 @@
       </c>
       <c r="U19" s="17"/>
       <c r="V19" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="W19" s="19">
@@ -30489,7 +30440,7 @@
     </row>
     <row r="20" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45888</v>
       </c>
       <c r="B20" s="29">
@@ -30499,7 +30450,7 @@
         <v>254.05799991000001</v>
       </c>
       <c r="D20" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
       <c r="E20" s="13">
@@ -30512,26 +30463,23 @@
       <c r="G20" s="13">
         <v>0</v>
       </c>
-      <c r="H20" s="13">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="I20" s="13">
-        <v>0</v>
-      </c>
-      <c r="J20" s="13">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="13">
-        <v>0</v>
-      </c>
-      <c r="L20" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="13">
-        <v>0</v>
+      <c r="H20" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I20" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J20" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K20" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L20" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M20" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N20" s="29">
         <v>293.13599932</v>
@@ -30540,7 +30488,7 @@
         <v>69.09599990000001</v>
       </c>
       <c r="P20" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q20" s="13">
@@ -30550,7 +30498,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -30558,7 +30506,7 @@
       </c>
       <c r="U20" s="4"/>
       <c r="V20" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="W20" s="15">
@@ -30588,7 +30536,7 @@
     </row>
     <row r="21" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45889</v>
       </c>
       <c r="B21" s="29">
@@ -30598,7 +30546,7 @@
         <v>249.52199989999997</v>
       </c>
       <c r="D21" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E21" s="13">
@@ -30611,26 +30559,23 @@
       <c r="G21" s="13">
         <v>0</v>
       </c>
-      <c r="H21" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="13">
-        <v>0</v>
-      </c>
-      <c r="J21" s="13">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="13">
-        <v>0</v>
-      </c>
-      <c r="L21" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="13">
-        <v>0</v>
+      <c r="H21" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I21" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J21" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K21" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L21" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M21" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N21" s="29">
         <v>304.48799938000002</v>
@@ -30639,7 +30584,7 @@
         <v>66.38399991</v>
       </c>
       <c r="P21" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q21" s="13">
@@ -30657,7 +30602,7 @@
       </c>
       <c r="U21" s="4"/>
       <c r="V21" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
       <c r="W21" s="15">
@@ -30687,7 +30632,7 @@
     </row>
     <row r="22" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A22" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45890</v>
       </c>
       <c r="B22" s="29">
@@ -30697,7 +30642,7 @@
         <v>297.69599991000001</v>
       </c>
       <c r="D22" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E22" s="13">
@@ -30710,26 +30655,23 @@
       <c r="G22" s="13">
         <v>0</v>
       </c>
-      <c r="H22" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="13">
-        <v>0</v>
-      </c>
-      <c r="J22" s="13">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="13">
-        <v>0</v>
-      </c>
-      <c r="L22" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="13">
-        <v>0</v>
+      <c r="H22" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I22" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J22" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K22" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L22" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M22" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N22" s="29">
         <v>343.60799934999983</v>
@@ -30738,7 +30680,7 @@
         <v>68.543999890000009</v>
       </c>
       <c r="P22" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q22" s="13">
@@ -30748,7 +30690,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
@@ -30756,7 +30698,7 @@
       </c>
       <c r="U22" s="4"/>
       <c r="V22" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="W22" s="15">
@@ -30786,7 +30728,7 @@
     </row>
     <row r="23" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45891</v>
       </c>
       <c r="B23" s="29">
@@ -30796,7 +30738,7 @@
         <v>205.75799993999996</v>
       </c>
       <c r="D23" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E23" s="13">
@@ -30809,26 +30751,23 @@
       <c r="G23" s="13">
         <v>0</v>
       </c>
-      <c r="H23" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="13">
-        <v>0</v>
-      </c>
-      <c r="J23" s="13">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="13">
-        <v>0</v>
-      </c>
-      <c r="L23" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="13">
-        <v>0</v>
+      <c r="H23" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I23" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J23" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K23" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L23" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M23" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N23" s="29">
         <v>341.73599936000016</v>
@@ -30837,7 +30776,7 @@
         <v>62.687999879999992</v>
       </c>
       <c r="P23" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q23" s="13">
@@ -30847,7 +30786,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
@@ -30855,7 +30794,7 @@
       </c>
       <c r="U23" s="4"/>
       <c r="V23" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="W23" s="15">
@@ -30885,7 +30824,7 @@
     </row>
     <row r="24" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45892</v>
       </c>
       <c r="B24" s="29">
@@ -30895,7 +30834,7 @@
         <v>196.26599993999997</v>
       </c>
       <c r="D24" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>223</v>
       </c>
       <c r="E24" s="13">
@@ -30908,26 +30847,23 @@
       <c r="G24" s="13">
         <v>0</v>
       </c>
-      <c r="H24" s="13">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="I24" s="13">
-        <v>0</v>
-      </c>
-      <c r="J24" s="13">
-        <f t="shared" si="9"/>
-        <v>4</v>
-      </c>
-      <c r="K24" s="13">
-        <v>0</v>
-      </c>
-      <c r="L24" s="13">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="M24" s="13">
-        <v>0</v>
+      <c r="H24" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I24" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J24" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K24" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L24" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M24" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N24" s="29">
         <v>306.07199935999989</v>
@@ -30936,7 +30872,7 @@
         <v>70.199999890000001</v>
       </c>
       <c r="P24" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="Q24" s="13">
@@ -30946,7 +30882,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -30954,7 +30890,7 @@
       </c>
       <c r="U24" s="4"/>
       <c r="V24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="W24" s="15">
@@ -30984,7 +30920,7 @@
     </row>
     <row r="25" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45893</v>
       </c>
       <c r="B25" s="29">
@@ -30994,7 +30930,7 @@
         <v>222.72599991999999</v>
       </c>
       <c r="D25" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E25" s="13">
@@ -31007,26 +30943,23 @@
       <c r="G25" s="13">
         <v>0</v>
       </c>
-      <c r="H25" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="13">
-        <v>0</v>
-      </c>
-      <c r="J25" s="13">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="13">
-        <v>0</v>
-      </c>
-      <c r="L25" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="13">
-        <v>0</v>
+      <c r="H25" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I25" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J25" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K25" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L25" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M25" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N25" s="29">
         <v>316.55999934999988</v>
@@ -31035,7 +30968,7 @@
         <v>65.255999880000005</v>
       </c>
       <c r="P25" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q25" s="13">
@@ -31045,7 +30978,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -31053,7 +30986,7 @@
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="W25" s="21">
@@ -31083,7 +31016,7 @@
     </row>
     <row r="26" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45894</v>
       </c>
       <c r="B26" s="29">
@@ -31093,7 +31026,7 @@
         <v>237.38399989999999</v>
       </c>
       <c r="D26" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E26" s="13">
@@ -31106,26 +31039,23 @@
       <c r="G26" s="13">
         <v>0</v>
       </c>
-      <c r="H26" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="13">
-        <v>0</v>
-      </c>
-      <c r="J26" s="13">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="13">
-        <v>0</v>
-      </c>
-      <c r="L26" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="13">
-        <v>0</v>
+      <c r="H26" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I26" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J26" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K26" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L26" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M26" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N26" s="29">
         <v>352.91999938999993</v>
@@ -31134,7 +31064,7 @@
         <v>76.00799988</v>
       </c>
       <c r="P26" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q26" s="13">
@@ -31144,7 +31074,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -31152,7 +31082,7 @@
       </c>
       <c r="U26" s="4"/>
       <c r="V26" s="20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
       <c r="W26" s="21">
@@ -31182,7 +31112,7 @@
     </row>
     <row r="27" spans="1:30" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A27" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45895</v>
       </c>
       <c r="B27" s="29">
@@ -31192,7 +31122,7 @@
         <v>259.85399989999996</v>
       </c>
       <c r="D27" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>55</v>
       </c>
       <c r="E27" s="13">
@@ -31205,26 +31135,23 @@
       <c r="G27" s="13">
         <v>0</v>
       </c>
-      <c r="H27" s="13">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="I27" s="13">
-        <v>0</v>
-      </c>
-      <c r="J27" s="13">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="K27" s="13">
-        <v>0</v>
-      </c>
-      <c r="L27" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M27" s="13">
-        <v>0</v>
+      <c r="H27" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I27" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J27" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K27" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L27" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M27" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N27" s="29">
         <v>345.47999932000005</v>
@@ -31233,7 +31160,7 @@
         <v>71.039999929999993</v>
       </c>
       <c r="P27" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q27" s="13">
@@ -31243,7 +31170,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="T27" s="6" t="s">
@@ -31251,7 +31178,7 @@
       </c>
       <c r="U27" s="4"/>
       <c r="V27" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="W27" s="21">
@@ -31281,7 +31208,7 @@
     </row>
     <row r="28" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A28" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45896</v>
       </c>
       <c r="B28" s="29">
@@ -31291,7 +31218,7 @@
         <v>247.00199992</v>
       </c>
       <c r="D28" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>76</v>
       </c>
       <c r="E28" s="13">
@@ -31304,26 +31231,23 @@
       <c r="G28" s="13">
         <v>0</v>
       </c>
-      <c r="H28" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="13">
-        <v>0</v>
-      </c>
-      <c r="J28" s="13">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="K28" s="13">
-        <v>0</v>
-      </c>
-      <c r="L28" s="13">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="M28" s="13">
-        <v>0</v>
+      <c r="H28" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I28" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J28" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K28" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L28" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M28" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N28" s="29">
         <v>319.17599931999985</v>
@@ -31332,7 +31256,7 @@
         <v>66.527999870000002</v>
       </c>
       <c r="P28" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="Q28" s="13">
@@ -31342,7 +31266,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="T28" s="6" t="s">
@@ -31350,7 +31274,7 @@
       </c>
       <c r="U28" s="4"/>
       <c r="V28" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
       <c r="W28" s="15">
@@ -31380,7 +31304,7 @@
     </row>
     <row r="29" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45897</v>
       </c>
       <c r="B29" s="29">
@@ -31390,7 +31314,7 @@
         <v>236.37599990999999</v>
       </c>
       <c r="D29" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>95</v>
       </c>
       <c r="E29" s="13">
@@ -31403,26 +31327,23 @@
       <c r="G29" s="13">
         <v>0</v>
       </c>
-      <c r="H29" s="13">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="I29" s="13">
-        <v>0</v>
-      </c>
-      <c r="J29" s="13">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="K29" s="13">
-        <v>0</v>
-      </c>
-      <c r="L29" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="13">
-        <v>0</v>
+      <c r="H29" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I29" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J29" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K29" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L29" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M29" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N29" s="29">
         <v>361.05599924000001</v>
@@ -31431,7 +31352,7 @@
         <v>67.127999890000012</v>
       </c>
       <c r="P29" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q29" s="13">
@@ -31441,7 +31362,7 @@
         <v>0</v>
       </c>
       <c r="S29" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="T29" s="6" t="s">
@@ -31449,7 +31370,7 @@
       </c>
       <c r="U29" s="4"/>
       <c r="V29" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="W29" s="15">
@@ -31479,7 +31400,7 @@
     </row>
     <row r="30" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45898</v>
       </c>
       <c r="B30" s="29">
@@ -31489,7 +31410,7 @@
         <v>169.46999990000003</v>
       </c>
       <c r="D30" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="E30" s="13">
@@ -31502,26 +31423,23 @@
       <c r="G30" s="13">
         <v>0</v>
       </c>
-      <c r="H30" s="13">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="I30" s="13">
-        <v>0</v>
-      </c>
-      <c r="J30" s="13">
-        <f t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="K30" s="13">
-        <v>0</v>
-      </c>
-      <c r="L30" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M30" s="13">
-        <v>0</v>
+      <c r="H30" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I30" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J30" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K30" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L30" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M30" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N30" s="29">
         <v>300.50399937000003</v>
@@ -31530,7 +31448,7 @@
         <v>51.695999910000005</v>
       </c>
       <c r="P30" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q30" s="13">
@@ -31540,7 +31458,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T30" s="6" t="s">
@@ -31548,7 +31466,7 @@
       </c>
       <c r="U30" s="4"/>
       <c r="V30" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="W30" s="15">
@@ -31578,7 +31496,7 @@
     </row>
     <row r="31" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45899</v>
       </c>
       <c r="B31" s="29">
@@ -31588,7 +31506,7 @@
         <v>189.37799994000002</v>
       </c>
       <c r="D31" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>136</v>
       </c>
       <c r="E31" s="13">
@@ -31601,26 +31519,23 @@
       <c r="G31" s="13">
         <v>0</v>
       </c>
-      <c r="H31" s="13">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="I31" s="13">
-        <v>0</v>
-      </c>
-      <c r="J31" s="13">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="13">
-        <v>0</v>
-      </c>
-      <c r="L31" s="13">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="M31" s="13">
-        <v>0</v>
+      <c r="H31" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I31" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J31" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K31" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L31" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M31" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N31" s="29">
         <v>308.30399930999977</v>
@@ -31629,7 +31544,7 @@
         <v>57.863999920000005</v>
       </c>
       <c r="P31" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="Q31" s="13">
@@ -31639,7 +31554,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="T31" s="6" t="s">
@@ -31647,7 +31562,7 @@
       </c>
       <c r="U31" s="4"/>
       <c r="V31" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="W31" s="15">
@@ -31677,7 +31592,7 @@
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>45900</v>
       </c>
       <c r="B32" s="29">
@@ -31687,7 +31602,7 @@
         <v>214.91399988000001</v>
       </c>
       <c r="D32" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="E32" s="13">
@@ -31700,26 +31615,23 @@
       <c r="G32" s="13">
         <v>0</v>
       </c>
-      <c r="H32" s="13">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="I32" s="13">
-        <v>0</v>
-      </c>
-      <c r="J32" s="13">
-        <f t="shared" si="9"/>
-        <v>2</v>
-      </c>
-      <c r="K32" s="13">
-        <v>0</v>
-      </c>
-      <c r="L32" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M32" s="13">
-        <v>0</v>
+      <c r="H32" s="29">
+        <v>126.45161290322579</v>
+      </c>
+      <c r="I32" s="29">
+        <v>54.193548387096776</v>
+      </c>
+      <c r="J32" s="29">
+        <v>31.612903225806448</v>
+      </c>
+      <c r="K32" s="29">
+        <v>13.548387096774194</v>
+      </c>
+      <c r="L32" s="29">
+        <v>32.516129032258064</v>
+      </c>
+      <c r="M32" s="29">
+        <v>13.935483870967742</v>
       </c>
       <c r="N32" s="29">
         <v>273.71999938999977</v>
@@ -31728,7 +31640,7 @@
         <v>53.255999909999986</v>
       </c>
       <c r="P32" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q32" s="13">
@@ -31744,7 +31656,7 @@
       <c r="T32" s="6"/>
       <c r="U32" s="4"/>
       <c r="V32" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="W32" s="15">
@@ -31775,7 +31687,7 @@
     <row r="33" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="U33" s="4"/>
       <c r="V33" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>31</v>
       </c>
       <c r="W33" s="15">
@@ -31956,6 +31868,7 @@
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
+      <c r="N48" s="38"/>
     </row>
     <row r="49" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
@@ -32507,6 +32420,7 @@
     <col min="7" max="7" width="13.42578125" customWidth="1"/>
     <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
     <col min="12" max="12" width="13.140625" customWidth="1"/>
     <col min="20" max="20" width="47.28515625" customWidth="1"/>
   </cols>
@@ -32631,25 +32545,23 @@
       <c r="G2" s="13">
         <v>0</v>
       </c>
-      <c r="H2" s="13">
-        <f t="shared" ref="H2:H32" si="1">Y3-Y2</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="13">
-        <v>0</v>
-      </c>
-      <c r="J2" s="13">
-        <f t="shared" ref="J2:J14" si="2">Z3-Z2</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="13">
-        <v>0</v>
-      </c>
-      <c r="L2" s="13">
-        <v>29</v>
-      </c>
-      <c r="M2" s="13">
-        <v>10</v>
+      <c r="H2" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I2" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J2" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K2" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L2" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M2" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N2" s="29">
         <v>273.19199933999994</v>
@@ -32658,7 +32570,7 @@
         <v>58.631999890000003</v>
       </c>
       <c r="P2" s="13">
-        <f t="shared" ref="P2:P32" si="3">AC3-AC2</f>
+        <f t="shared" ref="P2:P32" si="1">AC3-AC2</f>
         <v>0</v>
       </c>
       <c r="Q2" s="13">
@@ -32668,7 +32580,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="13">
-        <f t="shared" ref="S2:S32" si="4">AD3-AD2</f>
+        <f t="shared" ref="S2:S32" si="2">AD3-AD2</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -32712,7 +32624,7 @@
     </row>
     <row r="3" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="28">
-        <f t="shared" ref="A3:A32" si="5">A2+1</f>
+        <f t="shared" ref="A3:A32" si="3">A2+1</f>
         <v>45840</v>
       </c>
       <c r="B3" s="29">
@@ -32722,7 +32634,7 @@
         <v>194.16599989000002</v>
       </c>
       <c r="D3" s="13">
-        <f t="shared" ref="D3:D32" si="6">W4-W3</f>
+        <f t="shared" ref="D3:D32" si="4">W4-W3</f>
         <v>126</v>
       </c>
       <c r="E3" s="13">
@@ -32735,25 +32647,23 @@
       <c r="G3" s="13">
         <v>0</v>
       </c>
-      <c r="H3" s="13">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="I3" s="13">
-        <v>0</v>
-      </c>
-      <c r="J3" s="13">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="K3" s="13">
-        <v>0</v>
-      </c>
-      <c r="L3" s="13">
-        <v>29</v>
-      </c>
-      <c r="M3" s="13">
-        <v>10</v>
+      <c r="H3" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I3" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J3" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K3" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L3" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M3" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N3" s="29">
         <v>244.2479993499999</v>
@@ -32762,7 +32672,7 @@
         <v>53.351999930000005</v>
       </c>
       <c r="P3" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q3" s="13">
@@ -32772,7 +32682,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -32809,7 +32719,7 @@
     </row>
     <row r="4" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A4" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45841</v>
       </c>
       <c r="B4" s="29">
@@ -32819,7 +32729,7 @@
         <v>188.95799991000001</v>
       </c>
       <c r="D4" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E4" s="13">
@@ -32832,25 +32742,23 @@
       <c r="G4" s="13">
         <v>0</v>
       </c>
-      <c r="H4" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I4" s="13">
-        <v>0</v>
-      </c>
-      <c r="J4" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="13">
-        <v>0</v>
-      </c>
-      <c r="L4" s="13">
-        <v>29</v>
-      </c>
-      <c r="M4" s="13">
-        <v>10</v>
+      <c r="H4" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I4" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J4" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K4" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L4" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M4" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N4" s="29">
         <v>238.70399939999993</v>
@@ -32859,7 +32767,7 @@
         <v>47.591999919999992</v>
       </c>
       <c r="P4" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q4" s="13">
@@ -32869,7 +32777,7 @@
         <v>0</v>
       </c>
       <c r="S4" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -32877,7 +32785,7 @@
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="14">
-        <f t="shared" ref="V4:V33" si="7">V3+1</f>
+        <f t="shared" ref="V4:V33" si="5">V3+1</f>
         <v>2</v>
       </c>
       <c r="W4" s="6">
@@ -32907,7 +32815,7 @@
     </row>
     <row r="5" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45842</v>
       </c>
       <c r="B5" s="29">
@@ -32917,7 +32825,7 @@
         <v>146.36999994000001</v>
       </c>
       <c r="D5" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>132</v>
       </c>
       <c r="E5" s="13">
@@ -32930,25 +32838,23 @@
       <c r="G5" s="13">
         <v>0</v>
       </c>
-      <c r="H5" s="13">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="I5" s="13">
-        <v>0</v>
-      </c>
-      <c r="J5" s="13">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="K5" s="13">
-        <v>0</v>
-      </c>
-      <c r="L5" s="13">
-        <v>29</v>
-      </c>
-      <c r="M5" s="13">
-        <v>10</v>
+      <c r="H5" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I5" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J5" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K5" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L5" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M5" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N5" s="29">
         <v>261.69599937999982</v>
@@ -32957,7 +32863,7 @@
         <v>46.919999890000007</v>
       </c>
       <c r="P5" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q5" s="13">
@@ -32967,7 +32873,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -32975,7 +32881,7 @@
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="W5" s="6">
@@ -33005,7 +32911,7 @@
     </row>
     <row r="6" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45843</v>
       </c>
       <c r="B6" s="29">
@@ -33015,7 +32921,7 @@
         <v>149.56199989999999</v>
       </c>
       <c r="D6" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>56</v>
       </c>
       <c r="E6" s="13">
@@ -33028,25 +32934,23 @@
       <c r="G6" s="13">
         <v>0</v>
       </c>
-      <c r="H6" s="13">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="I6" s="13">
-        <v>0</v>
-      </c>
-      <c r="J6" s="13">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="K6" s="13">
-        <v>0</v>
-      </c>
-      <c r="L6" s="13">
-        <v>29</v>
-      </c>
-      <c r="M6" s="13">
-        <v>10</v>
+      <c r="H6" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I6" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J6" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K6" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L6" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M6" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N6" s="29">
         <v>243.26399940999994</v>
@@ -33055,7 +32959,7 @@
         <v>57.911999910000006</v>
       </c>
       <c r="P6" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q6" s="13">
@@ -33065,7 +32969,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -33073,7 +32977,7 @@
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="W6" s="6">
@@ -33103,7 +33007,7 @@
     </row>
     <row r="7" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45844</v>
       </c>
       <c r="B7" s="29">
@@ -33113,7 +33017,7 @@
         <v>156.28199990000002</v>
       </c>
       <c r="D7" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="E7" s="13">
@@ -33126,25 +33030,23 @@
       <c r="G7" s="13">
         <v>0</v>
       </c>
-      <c r="H7" s="13">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="I7" s="13">
-        <v>0</v>
-      </c>
-      <c r="J7" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="13">
-        <v>0</v>
-      </c>
-      <c r="L7" s="13">
-        <v>29</v>
-      </c>
-      <c r="M7" s="13">
-        <v>10</v>
+      <c r="H7" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I7" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J7" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K7" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L7" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M7" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N7" s="29">
         <v>255.88799939000006</v>
@@ -33153,7 +33055,7 @@
         <v>61.943999909999995</v>
       </c>
       <c r="P7" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q7" s="13">
@@ -33163,7 +33065,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -33171,7 +33073,7 @@
       </c>
       <c r="U7" s="4"/>
       <c r="V7" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="W7" s="6">
@@ -33201,7 +33103,7 @@
     </row>
     <row r="8" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45845</v>
       </c>
       <c r="B8" s="29">
@@ -33211,7 +33113,7 @@
         <v>192.14999990999999</v>
       </c>
       <c r="D8" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E8" s="13">
@@ -33224,25 +33126,23 @@
       <c r="G8" s="13">
         <v>0</v>
       </c>
-      <c r="H8" s="13">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="I8" s="13">
-        <v>0</v>
-      </c>
-      <c r="J8" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="13">
-        <v>0</v>
-      </c>
-      <c r="L8" s="13">
-        <v>29</v>
-      </c>
-      <c r="M8" s="13">
-        <v>10</v>
+      <c r="H8" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I8" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J8" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K8" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L8" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M8" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N8" s="29">
         <v>237.64799939999963</v>
@@ -33251,7 +33151,7 @@
         <v>63.479999890000009</v>
       </c>
       <c r="P8" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q8" s="13">
@@ -33261,7 +33161,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -33269,7 +33169,7 @@
       </c>
       <c r="U8" s="4"/>
       <c r="V8" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="W8" s="6">
@@ -33299,7 +33199,7 @@
     </row>
     <row r="9" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45846</v>
       </c>
       <c r="B9" s="29">
@@ -33309,7 +33209,7 @@
         <v>183.20399994000005</v>
       </c>
       <c r="D9" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>69</v>
       </c>
       <c r="E9" s="13">
@@ -33322,25 +33222,23 @@
       <c r="G9" s="13">
         <v>0</v>
       </c>
-      <c r="H9" s="13">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="I9" s="13">
-        <v>0</v>
-      </c>
-      <c r="J9" s="13">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="K9" s="13">
-        <v>0</v>
-      </c>
-      <c r="L9" s="13">
-        <v>29</v>
-      </c>
-      <c r="M9" s="13">
-        <v>10</v>
+      <c r="H9" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I9" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J9" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K9" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L9" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M9" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N9" s="29">
         <v>233.6159993399998</v>
@@ -33349,7 +33247,7 @@
         <v>49.703999919999994</v>
       </c>
       <c r="P9" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q9" s="13">
@@ -33359,7 +33257,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -33367,7 +33265,7 @@
       </c>
       <c r="U9" s="4"/>
       <c r="V9" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="W9" s="6">
@@ -33397,7 +33295,7 @@
     </row>
     <row r="10" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45847</v>
       </c>
       <c r="B10" s="29">
@@ -33407,7 +33305,7 @@
         <v>190.30199987999998</v>
       </c>
       <c r="D10" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>65</v>
       </c>
       <c r="E10" s="13">
@@ -33420,25 +33318,23 @@
       <c r="G10" s="13">
         <v>0</v>
       </c>
-      <c r="H10" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="13">
-        <v>0</v>
-      </c>
-      <c r="J10" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="13">
-        <v>0</v>
-      </c>
-      <c r="L10" s="13">
-        <v>29</v>
-      </c>
-      <c r="M10" s="13">
-        <v>10</v>
+      <c r="H10" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I10" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J10" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K10" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L10" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M10" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N10" s="29">
         <v>221.99999943999987</v>
@@ -33447,7 +33343,7 @@
         <v>63.287999890000002</v>
       </c>
       <c r="P10" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q10" s="13">
@@ -33457,7 +33353,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="T10" s="6" t="s">
@@ -33465,7 +33361,7 @@
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="W10" s="6">
@@ -33495,7 +33391,7 @@
     </row>
     <row r="11" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45848</v>
       </c>
       <c r="B11" s="29">
@@ -33505,7 +33401,7 @@
         <v>177.15599992000003</v>
       </c>
       <c r="D11" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>45</v>
       </c>
       <c r="E11" s="13">
@@ -33518,150 +33414,146 @@
       <c r="G11" s="13">
         <v>0</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I11" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J11" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K11" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L11" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M11" s="29">
+        <v>11.612903225806452</v>
+      </c>
+      <c r="N11" s="29">
+        <v>239.39999935999995</v>
+      </c>
+      <c r="O11" s="29">
+        <v>48.239999900000008</v>
+      </c>
+      <c r="P11" s="13">
         <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="I11" s="13">
-        <v>0</v>
-      </c>
-      <c r="J11" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>0</v>
+      </c>
+      <c r="R11" s="13">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="T11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="U11" s="4"/>
+      <c r="V11" s="14">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="W11" s="6">
+        <v>8171</v>
+      </c>
+      <c r="X11" s="6">
+        <v>10046</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>9414</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>10826</v>
+      </c>
+      <c r="AA11" s="6">
+        <v>1277</v>
+      </c>
+      <c r="AB11" s="6">
+        <v>3847</v>
+      </c>
+      <c r="AC11" s="6">
+        <v>386</v>
+      </c>
+      <c r="AD11" s="6">
+        <v>3461</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="28">
+        <f t="shared" si="3"/>
+        <v>45849</v>
+      </c>
+      <c r="B12" s="29">
+        <v>1060.20599956</v>
+      </c>
+      <c r="C12" s="29">
+        <v>145.10999994000002</v>
+      </c>
+      <c r="D12" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <v>0</v>
+      </c>
+      <c r="H12" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I12" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J12" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K12" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L12" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M12" s="29">
+        <v>11.612903225806452</v>
+      </c>
+      <c r="N12" s="29">
+        <v>272.44799940999985</v>
+      </c>
+      <c r="O12" s="29">
+        <v>54.503999889999996</v>
+      </c>
+      <c r="P12" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>0</v>
+      </c>
+      <c r="R12" s="13">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K11" s="13">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13">
-        <v>29</v>
-      </c>
-      <c r="M11" s="13">
-        <v>10</v>
-      </c>
-      <c r="N11" s="29">
-        <v>239.39999935999995</v>
-      </c>
-      <c r="O11" s="29">
-        <v>48.239999900000008</v>
-      </c>
-      <c r="P11" s="13">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>0</v>
-      </c>
-      <c r="R11" s="13">
-        <v>0</v>
-      </c>
-      <c r="S11" s="13">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="T11" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="U11" s="4"/>
-      <c r="V11" s="14">
-        <f t="shared" si="7"/>
-        <v>9</v>
-      </c>
-      <c r="W11" s="6">
-        <v>8171</v>
-      </c>
-      <c r="X11" s="6">
-        <v>10046</v>
-      </c>
-      <c r="Y11" s="6">
-        <v>9414</v>
-      </c>
-      <c r="Z11" s="6">
-        <v>10826</v>
-      </c>
-      <c r="AA11" s="6">
-        <v>1277</v>
-      </c>
-      <c r="AB11" s="6">
-        <v>3847</v>
-      </c>
-      <c r="AC11" s="6">
-        <v>386</v>
-      </c>
-      <c r="AD11" s="6">
-        <v>3461</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="28">
-        <f t="shared" si="5"/>
-        <v>45849</v>
-      </c>
-      <c r="B12" s="29">
-        <v>1060.20599956</v>
-      </c>
-      <c r="C12" s="29">
-        <v>145.10999994000002</v>
-      </c>
-      <c r="D12" s="13">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="13">
-        <v>0</v>
-      </c>
-      <c r="F12" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="13">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="I12" s="13">
-        <v>0</v>
-      </c>
-      <c r="J12" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="13">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13">
-        <v>29</v>
-      </c>
-      <c r="M12" s="13">
-        <v>10</v>
-      </c>
-      <c r="N12" s="29">
-        <v>272.44799940999985</v>
-      </c>
-      <c r="O12" s="29">
-        <v>54.503999889999996</v>
-      </c>
-      <c r="P12" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>0</v>
-      </c>
-      <c r="R12" s="13">
-        <v>0</v>
-      </c>
-      <c r="S12" s="13">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="T12" s="6" t="s">
         <v>55</v>
       </c>
       <c r="U12" s="4"/>
       <c r="V12" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="W12" s="6">
@@ -33691,7 +33583,7 @@
     </row>
     <row r="13" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45850</v>
       </c>
       <c r="B13" s="29">
@@ -33701,7 +33593,7 @@
         <v>138.13799994999999</v>
       </c>
       <c r="D13" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E13" s="13">
@@ -33714,25 +33606,23 @@
       <c r="G13" s="13">
         <v>0</v>
       </c>
-      <c r="H13" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="13">
-        <v>0</v>
-      </c>
-      <c r="J13" s="13">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="13">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13">
-        <v>29</v>
-      </c>
-      <c r="M13" s="13">
-        <v>10</v>
+      <c r="H13" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I13" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J13" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K13" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L13" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M13" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N13" s="29">
         <v>273.93599928999976</v>
@@ -33741,7 +33631,7 @@
         <v>50.255999900000006</v>
       </c>
       <c r="P13" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q13" s="13">
@@ -33751,7 +33641,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -33759,7 +33649,7 @@
       </c>
       <c r="U13" s="4"/>
       <c r="V13" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="W13" s="15">
@@ -33789,7 +33679,7 @@
     </row>
     <row r="14" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45851</v>
       </c>
       <c r="B14" s="29">
@@ -33799,7 +33689,7 @@
         <v>164.00999991999998</v>
       </c>
       <c r="D14" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>109</v>
       </c>
       <c r="E14" s="13">
@@ -33812,25 +33702,23 @@
       <c r="G14" s="13">
         <v>0</v>
       </c>
-      <c r="H14" s="13">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="I14" s="13">
-        <v>0</v>
-      </c>
-      <c r="J14" s="13">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="K14" s="13">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13">
-        <v>29</v>
-      </c>
-      <c r="M14" s="13">
-        <v>10</v>
+      <c r="H14" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I14" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J14" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K14" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L14" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M14" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N14" s="29">
         <v>266.95199932999975</v>
@@ -33839,7 +33727,7 @@
         <v>59.44799991</v>
       </c>
       <c r="P14" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q14" s="13">
@@ -33849,7 +33737,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="T14" s="6" t="s">
@@ -33857,7 +33745,7 @@
       </c>
       <c r="U14" s="4"/>
       <c r="V14" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="W14" s="15">
@@ -33887,7 +33775,7 @@
     </row>
     <row r="15" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45852</v>
       </c>
       <c r="B15" s="29">
@@ -33897,7 +33785,7 @@
         <v>183.37199992999999</v>
       </c>
       <c r="D15" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E15" s="13">
@@ -33910,24 +33798,23 @@
       <c r="G15" s="13">
         <v>0</v>
       </c>
-      <c r="H15" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="13">
-        <v>0</v>
-      </c>
-      <c r="J15" s="13">
-        <v>1</v>
-      </c>
-      <c r="K15" s="13">
-        <v>0</v>
-      </c>
-      <c r="L15" s="13">
-        <v>29</v>
-      </c>
-      <c r="M15" s="13">
-        <v>10</v>
+      <c r="H15" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I15" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J15" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K15" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L15" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M15" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N15" s="29">
         <v>237.09599936999976</v>
@@ -33936,7 +33823,7 @@
         <v>57.767999929999995</v>
       </c>
       <c r="P15" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q15" s="13">
@@ -33946,7 +33833,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T15" s="6" t="s">
@@ -33954,7 +33841,7 @@
       </c>
       <c r="U15" s="4"/>
       <c r="V15" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="W15" s="6">
@@ -33984,7 +33871,7 @@
     </row>
     <row r="16" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45853</v>
       </c>
       <c r="B16" s="29">
@@ -33994,7 +33881,7 @@
         <v>175.81199992000001</v>
       </c>
       <c r="D16" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
       <c r="E16" s="13">
@@ -34007,25 +33894,23 @@
       <c r="G16" s="13">
         <v>0</v>
       </c>
-      <c r="H16" s="13">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="I16" s="13">
-        <v>0</v>
-      </c>
-      <c r="J16" s="13">
-        <f t="shared" ref="J16:J32" si="8">Z17-Z16</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="13">
-        <v>0</v>
-      </c>
-      <c r="L16" s="13">
-        <v>29</v>
-      </c>
-      <c r="M16" s="13">
-        <v>10</v>
+      <c r="H16" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I16" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J16" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K16" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L16" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M16" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N16" s="29">
         <v>251.08799935999988</v>
@@ -34034,7 +33919,7 @@
         <v>57.599999870000005</v>
       </c>
       <c r="P16" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q16" s="13">
@@ -34044,7 +33929,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="T16" s="6" t="s">
@@ -34052,7 +33937,7 @@
       </c>
       <c r="U16" s="4"/>
       <c r="V16" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="W16" s="6">
@@ -34082,7 +33967,7 @@
     </row>
     <row r="17" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45854</v>
       </c>
       <c r="B17" s="29">
@@ -34092,7 +33977,7 @@
         <v>201.51599995000004</v>
       </c>
       <c r="D17" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E17" s="13">
@@ -34105,25 +33990,23 @@
       <c r="G17" s="13">
         <v>0</v>
       </c>
-      <c r="H17" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="13">
-        <v>0</v>
-      </c>
-      <c r="J17" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="13">
-        <v>0</v>
-      </c>
-      <c r="L17" s="13">
-        <v>29</v>
-      </c>
-      <c r="M17" s="13">
-        <v>10</v>
+      <c r="H17" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I17" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J17" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K17" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L17" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M17" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N17" s="29">
         <v>249.23999939999999</v>
@@ -34132,7 +34015,7 @@
         <v>48.911999910000006</v>
       </c>
       <c r="P17" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q17" s="13">
@@ -34142,7 +34025,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T17" s="6" t="s">
@@ -34150,7 +34033,7 @@
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="W17" s="16">
@@ -34180,7 +34063,7 @@
     </row>
     <row r="18" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45855</v>
       </c>
       <c r="B18" s="29">
@@ -34190,7 +34073,7 @@
         <v>221.17199995000004</v>
       </c>
       <c r="D18" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>106</v>
       </c>
       <c r="E18" s="13">
@@ -34203,25 +34086,23 @@
       <c r="G18" s="13">
         <v>0</v>
       </c>
-      <c r="H18" s="13">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="I18" s="13">
-        <v>0</v>
-      </c>
-      <c r="J18" s="13">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="K18" s="13">
-        <v>0</v>
-      </c>
-      <c r="L18" s="13">
-        <v>29</v>
-      </c>
-      <c r="M18" s="13">
-        <v>10</v>
+      <c r="H18" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I18" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J18" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K18" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L18" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M18" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N18" s="29">
         <v>241.43999937000009</v>
@@ -34230,7 +34111,7 @@
         <v>49.607999879999994</v>
       </c>
       <c r="P18" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q18" s="13">
@@ -34240,7 +34121,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="T18" s="6" t="s">
@@ -34248,7 +34129,7 @@
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="W18" s="16">
@@ -34278,7 +34159,7 @@
     </row>
     <row r="19" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45856</v>
       </c>
       <c r="B19" s="29">
@@ -34288,7 +34169,7 @@
         <v>155.48399988999995</v>
       </c>
       <c r="D19" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>63</v>
       </c>
       <c r="E19" s="13">
@@ -34301,25 +34182,23 @@
       <c r="G19" s="13">
         <v>0</v>
       </c>
-      <c r="H19" s="13">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="I19" s="13">
-        <v>0</v>
-      </c>
-      <c r="J19" s="13">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="K19" s="13">
-        <v>0</v>
-      </c>
-      <c r="L19" s="13">
-        <v>29</v>
-      </c>
-      <c r="M19" s="13">
-        <v>10</v>
+      <c r="H19" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I19" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J19" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K19" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L19" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M19" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N19" s="29">
         <v>232.10399942999979</v>
@@ -34328,7 +34207,7 @@
         <v>43.3439999</v>
       </c>
       <c r="P19" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="Q19" s="13">
@@ -34338,7 +34217,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="T19" s="6" t="s">
@@ -34346,7 +34225,7 @@
       </c>
       <c r="U19" s="17"/>
       <c r="V19" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="W19" s="19">
@@ -34376,7 +34255,7 @@
     </row>
     <row r="20" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45857</v>
       </c>
       <c r="B20" s="29">
@@ -34386,7 +34265,7 @@
         <v>204.45599989000002</v>
       </c>
       <c r="D20" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="E20" s="13">
@@ -34399,25 +34278,23 @@
       <c r="G20" s="13">
         <v>0</v>
       </c>
-      <c r="H20" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="13">
-        <v>0</v>
-      </c>
-      <c r="J20" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="13">
-        <v>0</v>
-      </c>
-      <c r="L20" s="13">
-        <v>29</v>
-      </c>
-      <c r="M20" s="13">
-        <v>10</v>
+      <c r="H20" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I20" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J20" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K20" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L20" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M20" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N20" s="29">
         <v>274.1519993600001</v>
@@ -34426,7 +34303,7 @@
         <v>53.015999870000009</v>
       </c>
       <c r="P20" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q20" s="13">
@@ -34436,7 +34313,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -34444,7 +34321,7 @@
       </c>
       <c r="U20" s="4"/>
       <c r="V20" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="W20" s="15">
@@ -34474,7 +34351,7 @@
     </row>
     <row r="21" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45858</v>
       </c>
       <c r="B21" s="29">
@@ -34484,7 +34361,7 @@
         <v>176.69399991</v>
       </c>
       <c r="D21" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>65</v>
       </c>
       <c r="E21" s="13">
@@ -34497,25 +34374,23 @@
       <c r="G21" s="13">
         <v>0</v>
       </c>
-      <c r="H21" s="13">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="I21" s="13">
-        <v>0</v>
-      </c>
-      <c r="J21" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="13">
-        <v>0</v>
-      </c>
-      <c r="L21" s="13">
-        <v>29</v>
-      </c>
-      <c r="M21" s="13">
-        <v>10</v>
+      <c r="H21" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I21" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J21" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K21" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L21" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M21" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N21" s="29">
         <v>255.64799941999971</v>
@@ -34524,7 +34399,7 @@
         <v>49.031999899999995</v>
       </c>
       <c r="P21" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q21" s="13">
@@ -34534,7 +34409,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -34542,7 +34417,7 @@
       </c>
       <c r="U21" s="4"/>
       <c r="V21" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
       <c r="W21" s="15">
@@ -34572,7 +34447,7 @@
     </row>
     <row r="22" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45859</v>
       </c>
       <c r="B22" s="29">
@@ -34582,7 +34457,7 @@
         <v>191.64599992999999</v>
       </c>
       <c r="D22" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>49</v>
       </c>
       <c r="E22" s="13">
@@ -34595,25 +34470,23 @@
       <c r="G22" s="13">
         <v>0</v>
       </c>
-      <c r="H22" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="13">
-        <v>0</v>
-      </c>
-      <c r="J22" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="13">
-        <v>0</v>
-      </c>
-      <c r="L22" s="13">
-        <v>29</v>
-      </c>
-      <c r="M22" s="13">
-        <v>10</v>
+      <c r="H22" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I22" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J22" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K22" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L22" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M22" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N22" s="29">
         <v>264.26399941999972</v>
@@ -34622,7 +34495,7 @@
         <v>59.85599989</v>
       </c>
       <c r="P22" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q22" s="13">
@@ -34632,7 +34505,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="T22" s="6" t="s">
@@ -34640,7 +34513,7 @@
       </c>
       <c r="U22" s="4"/>
       <c r="V22" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="W22" s="15">
@@ -34670,7 +34543,7 @@
     </row>
     <row r="23" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45860</v>
       </c>
       <c r="B23" s="29">
@@ -34680,7 +34553,7 @@
         <v>213.06599991999997</v>
       </c>
       <c r="D23" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E23" s="13">
@@ -34693,25 +34566,23 @@
       <c r="G23" s="13">
         <v>0</v>
       </c>
-      <c r="H23" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="13">
-        <v>0</v>
-      </c>
-      <c r="J23" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="13">
-        <v>0</v>
-      </c>
-      <c r="L23" s="13">
-        <v>29</v>
-      </c>
-      <c r="M23" s="13">
-        <v>10</v>
+      <c r="H23" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I23" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J23" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K23" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L23" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M23" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N23" s="29">
         <v>280.87199934999984</v>
@@ -34720,7 +34591,7 @@
         <v>56.519999890000001</v>
       </c>
       <c r="P23" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q23" s="13">
@@ -34730,7 +34601,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T23" s="6" t="s">
@@ -34738,7 +34609,7 @@
       </c>
       <c r="U23" s="4"/>
       <c r="V23" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="W23" s="15">
@@ -34768,7 +34639,7 @@
     </row>
     <row r="24" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45861</v>
       </c>
       <c r="B24" s="29">
@@ -34778,7 +34649,7 @@
         <v>238.01399993000001</v>
       </c>
       <c r="D24" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E24" s="13">
@@ -34791,25 +34662,23 @@
       <c r="G24" s="13">
         <v>0</v>
       </c>
-      <c r="H24" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="13">
-        <v>0</v>
-      </c>
-      <c r="J24" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="13">
-        <v>0</v>
-      </c>
-      <c r="L24" s="13">
-        <v>29</v>
-      </c>
-      <c r="M24" s="13">
-        <v>10</v>
+      <c r="H24" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I24" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J24" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K24" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L24" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M24" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N24" s="29">
         <v>270.69599941999996</v>
@@ -34818,7 +34687,7 @@
         <v>63.119999909999997</v>
       </c>
       <c r="P24" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q24" s="13">
@@ -34828,7 +34697,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -34836,7 +34705,7 @@
       </c>
       <c r="U24" s="4"/>
       <c r="V24" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="W24" s="15">
@@ -34866,7 +34735,7 @@
     </row>
     <row r="25" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45862</v>
       </c>
       <c r="B25" s="29">
@@ -34876,7 +34745,7 @@
         <v>238.22399992999996</v>
       </c>
       <c r="D25" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E25" s="13">
@@ -34889,25 +34758,23 @@
       <c r="G25" s="13">
         <v>0</v>
       </c>
-      <c r="H25" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="13">
-        <v>0</v>
-      </c>
-      <c r="J25" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="13">
-        <v>0</v>
-      </c>
-      <c r="L25" s="13">
-        <v>29</v>
-      </c>
-      <c r="M25" s="13">
-        <v>10</v>
+      <c r="H25" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I25" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J25" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K25" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L25" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M25" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N25" s="29">
         <v>294.16799943999979</v>
@@ -34916,7 +34783,7 @@
         <v>55.607999909999997</v>
       </c>
       <c r="P25" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q25" s="13">
@@ -34926,7 +34793,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -34934,7 +34801,7 @@
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="W25" s="15">
@@ -34964,7 +34831,7 @@
     </row>
     <row r="26" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45863</v>
       </c>
       <c r="B26" s="29">
@@ -34974,7 +34841,7 @@
         <v>165.14399989999998</v>
       </c>
       <c r="D26" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>204</v>
       </c>
       <c r="E26" s="13">
@@ -34987,25 +34854,23 @@
       <c r="G26" s="13">
         <v>0</v>
       </c>
-      <c r="H26" s="13">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="I26" s="13">
-        <v>0</v>
-      </c>
-      <c r="J26" s="13">
-        <f t="shared" si="8"/>
-        <v>3</v>
-      </c>
-      <c r="K26" s="13">
-        <v>0</v>
-      </c>
-      <c r="L26" s="13">
-        <v>29</v>
-      </c>
-      <c r="M26" s="13">
-        <v>10</v>
+      <c r="H26" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I26" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J26" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K26" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L26" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M26" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N26" s="29">
         <v>297.31199934999978</v>
@@ -35014,7 +34879,7 @@
         <v>55.487999910000006</v>
       </c>
       <c r="P26" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q26" s="13">
@@ -35024,7 +34889,7 @@
         <v>0</v>
       </c>
       <c r="S26" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -35032,7 +34897,7 @@
       </c>
       <c r="U26" s="4"/>
       <c r="V26" s="20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
       <c r="W26" s="15">
@@ -35062,7 +34927,7 @@
     </row>
     <row r="27" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45864</v>
       </c>
       <c r="B27" s="29">
@@ -35072,7 +34937,7 @@
         <v>158.25599991999997</v>
       </c>
       <c r="D27" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>78</v>
       </c>
       <c r="E27" s="13">
@@ -35085,25 +34950,23 @@
       <c r="G27" s="13">
         <v>0</v>
       </c>
-      <c r="H27" s="13">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="I27" s="13">
-        <v>0</v>
-      </c>
-      <c r="J27" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="13">
-        <v>0</v>
-      </c>
-      <c r="L27" s="13">
-        <v>29</v>
-      </c>
-      <c r="M27" s="13">
-        <v>10</v>
+      <c r="H27" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I27" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J27" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K27" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L27" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M27" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N27" s="29">
         <v>285.45599935999996</v>
@@ -35112,7 +34975,7 @@
         <v>53.327999879999993</v>
       </c>
       <c r="P27" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q27" s="13">
@@ -35122,7 +34985,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="T27" s="6" t="s">
@@ -35130,7 +34993,7 @@
       </c>
       <c r="U27" s="4"/>
       <c r="V27" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="W27" s="15">
@@ -35160,7 +35023,7 @@
     </row>
     <row r="28" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45865</v>
       </c>
       <c r="B28" s="29">
@@ -35170,7 +35033,7 @@
         <v>160.06199992999998</v>
       </c>
       <c r="D28" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E28" s="13">
@@ -35183,25 +35046,23 @@
       <c r="G28" s="13">
         <v>0</v>
       </c>
-      <c r="H28" s="13">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="I28" s="13">
-        <v>0</v>
-      </c>
-      <c r="J28" s="13">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="K28" s="13">
-        <v>0</v>
-      </c>
-      <c r="L28" s="13">
-        <v>29</v>
-      </c>
-      <c r="M28" s="13">
-        <v>10</v>
+      <c r="H28" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I28" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J28" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K28" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L28" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M28" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N28" s="29">
         <v>295.63199934999972</v>
@@ -35210,7 +35071,7 @@
         <v>56.92799990999999</v>
       </c>
       <c r="P28" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q28" s="13">
@@ -35220,7 +35081,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="T28" s="6" t="s">
@@ -35228,7 +35089,7 @@
       </c>
       <c r="U28" s="4"/>
       <c r="V28" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>26</v>
       </c>
       <c r="W28" s="15">
@@ -35258,7 +35119,7 @@
     </row>
     <row r="29" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45866</v>
       </c>
       <c r="B29" s="29">
@@ -35268,7 +35129,7 @@
         <v>187.86599992999999</v>
       </c>
       <c r="D29" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E29" s="13">
@@ -35281,25 +35142,23 @@
       <c r="G29" s="13">
         <v>0</v>
       </c>
-      <c r="H29" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="13">
-        <v>0</v>
-      </c>
-      <c r="J29" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="13">
-        <v>0</v>
-      </c>
-      <c r="L29" s="13">
-        <v>29</v>
-      </c>
-      <c r="M29" s="13">
-        <v>10</v>
+      <c r="H29" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I29" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J29" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K29" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L29" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M29" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N29" s="29">
         <v>274.46399932999992</v>
@@ -35308,7 +35167,7 @@
         <v>54.455999929999997</v>
       </c>
       <c r="P29" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q29" s="13">
@@ -35318,7 +35177,7 @@
         <v>0</v>
       </c>
       <c r="S29" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T29" s="6" t="s">
@@ -35326,7 +35185,7 @@
       </c>
       <c r="U29" s="4"/>
       <c r="V29" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="W29" s="15">
@@ -35356,7 +35215,7 @@
     </row>
     <row r="30" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45867</v>
       </c>
       <c r="B30" s="29">
@@ -35366,7 +35225,7 @@
         <v>213.06599994000004</v>
       </c>
       <c r="D30" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>87</v>
       </c>
       <c r="E30" s="13">
@@ -35379,25 +35238,23 @@
       <c r="G30" s="13">
         <v>0</v>
       </c>
-      <c r="H30" s="13">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="I30" s="13">
-        <v>0</v>
-      </c>
-      <c r="J30" s="13">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="K30" s="13">
-        <v>0</v>
-      </c>
-      <c r="L30" s="13">
-        <v>29</v>
-      </c>
-      <c r="M30" s="13">
-        <v>10</v>
+      <c r="H30" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I30" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J30" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K30" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L30" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M30" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N30" s="29">
         <v>226.48799934999997</v>
@@ -35406,7 +35263,7 @@
         <v>47.639999899999999</v>
       </c>
       <c r="P30" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>-10</v>
       </c>
       <c r="Q30" s="13">
@@ -35416,7 +35273,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="T30" s="6" t="s">
@@ -35424,7 +35281,7 @@
       </c>
       <c r="U30" s="4"/>
       <c r="V30" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="W30" s="15">
@@ -35454,7 +35311,7 @@
     </row>
     <row r="31" spans="1:30" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A31" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45868</v>
       </c>
       <c r="B31" s="29">
@@ -35464,7 +35321,7 @@
         <v>190.80599993999996</v>
       </c>
       <c r="D31" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E31" s="13">
@@ -35477,25 +35334,23 @@
       <c r="G31" s="13">
         <v>0</v>
       </c>
-      <c r="H31" s="13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="13">
-        <v>0</v>
-      </c>
-      <c r="J31" s="13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="13">
-        <v>0</v>
-      </c>
-      <c r="L31" s="13">
-        <v>29</v>
-      </c>
-      <c r="M31" s="13">
-        <v>10</v>
+      <c r="H31" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I31" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J31" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K31" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L31" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M31" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N31" s="29">
         <v>233.9999993399997</v>
@@ -35504,7 +35359,7 @@
         <v>48.023999929999995</v>
       </c>
       <c r="P31" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q31" s="13">
@@ -35514,7 +35369,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="T31" s="6" t="s">
@@ -35522,7 +35377,7 @@
       </c>
       <c r="U31" s="4"/>
       <c r="V31" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>29</v>
       </c>
       <c r="W31" s="15">
@@ -35552,7 +35407,7 @@
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>45869</v>
       </c>
       <c r="B32" s="29">
@@ -35562,7 +35417,7 @@
         <v>200.59199991999998</v>
       </c>
       <c r="D32" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>85</v>
       </c>
       <c r="E32" s="13">
@@ -35575,25 +35430,23 @@
       <c r="G32" s="13">
         <v>0</v>
       </c>
-      <c r="H32" s="13">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="I32" s="13">
-        <v>0</v>
-      </c>
-      <c r="J32" s="13">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="K32" s="13">
-        <v>0</v>
-      </c>
-      <c r="L32" s="13">
-        <v>29</v>
-      </c>
-      <c r="M32" s="13">
-        <v>10</v>
+      <c r="H32" s="29">
+        <v>109.29032258064517</v>
+      </c>
+      <c r="I32" s="29">
+        <v>46.838709677419352</v>
+      </c>
+      <c r="J32" s="29">
+        <v>2.1225806451612903</v>
+      </c>
+      <c r="K32" s="29">
+        <v>0.9096774193548387</v>
+      </c>
+      <c r="L32" s="29">
+        <v>27.096774193548388</v>
+      </c>
+      <c r="M32" s="29">
+        <v>11.612903225806452</v>
       </c>
       <c r="N32" s="29">
         <v>228.04799942999989</v>
@@ -35602,7 +35455,7 @@
         <v>55.175999879999999</v>
       </c>
       <c r="P32" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q32" s="13">
@@ -35612,7 +35465,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="T32" s="6" t="s">
@@ -35620,7 +35473,7 @@
       </c>
       <c r="U32" s="4"/>
       <c r="V32" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="W32" s="15">
@@ -35651,7 +35504,7 @@
     <row r="33" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="U33" s="4"/>
       <c r="V33" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>31</v>
       </c>
       <c r="W33" s="15">
@@ -35689,6 +35542,8 @@
       <c r="G36" s="50"/>
       <c r="H36" s="50"/>
       <c r="I36" s="50"/>
+      <c r="Q36" s="55"/>
+      <c r="R36" s="55"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37061773-AB62-4D0F-B3FB-9300CA33FBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9AAC2D-1EE8-4D90-99B7-0C5009C33E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -536,7 +536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -665,6 +665,7 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -678,8 +679,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1730,7 +1729,7 @@
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="D16" s="56"/>
+      <c r="D16" s="44"/>
       <c r="E16" s="44"/>
       <c r="F16" s="47"/>
     </row>
@@ -4897,15 +4896,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="50"/>
-      <c r="B69" s="50"/>
-      <c r="C69" s="50"/>
-      <c r="D69" s="50"/>
-      <c r="E69" s="50"/>
-      <c r="F69" s="50"/>
-      <c r="G69" s="50"/>
-      <c r="H69" s="50"/>
-      <c r="I69" s="50"/>
+      <c r="A69" s="51"/>
+      <c r="B69" s="51"/>
+      <c r="C69" s="51"/>
+      <c r="D69" s="51"/>
+      <c r="E69" s="51"/>
+      <c r="F69" s="51"/>
+      <c r="G69" s="51"/>
+      <c r="H69" s="51"/>
+      <c r="I69" s="51"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -4930,15 +4929,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="51"/>
-      <c r="B74" s="51"/>
-      <c r="C74" s="51"/>
-      <c r="D74" s="51"/>
-      <c r="E74" s="51"/>
-      <c r="F74" s="51"/>
-      <c r="G74" s="51"/>
-      <c r="H74" s="51"/>
-      <c r="I74" s="51"/>
+      <c r="A74" s="52"/>
+      <c r="B74" s="52"/>
+      <c r="C74" s="52"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="52"/>
+      <c r="F74" s="52"/>
+      <c r="G74" s="52"/>
+      <c r="H74" s="52"/>
+      <c r="I74" s="52"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -4974,15 +4973,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="52"/>
-      <c r="B78" s="52"/>
-      <c r="C78" s="52"/>
-      <c r="D78" s="52"/>
-      <c r="E78" s="52"/>
-      <c r="F78" s="52"/>
-      <c r="G78" s="52"/>
-      <c r="H78" s="52"/>
-      <c r="I78" s="52"/>
+      <c r="A78" s="53"/>
+      <c r="B78" s="53"/>
+      <c r="C78" s="53"/>
+      <c r="D78" s="53"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53"/>
+      <c r="H78" s="53"/>
+      <c r="I78" s="53"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -5018,15 +5017,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="51"/>
-      <c r="B86" s="51"/>
-      <c r="C86" s="51"/>
-      <c r="D86" s="51"/>
-      <c r="E86" s="51"/>
-      <c r="F86" s="51"/>
-      <c r="G86" s="51"/>
-      <c r="H86" s="51"/>
-      <c r="I86" s="51"/>
+      <c r="A86" s="52"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="52"/>
+      <c r="D86" s="52"/>
+      <c r="E86" s="52"/>
+      <c r="F86" s="52"/>
+      <c r="G86" s="52"/>
+      <c r="H86" s="52"/>
+      <c r="I86" s="52"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -5129,15 +5128,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="50"/>
-      <c r="B99" s="50"/>
-      <c r="C99" s="50"/>
-      <c r="D99" s="50"/>
-      <c r="E99" s="50"/>
-      <c r="F99" s="50"/>
-      <c r="G99" s="50"/>
-      <c r="H99" s="50"/>
-      <c r="I99" s="50"/>
+      <c r="A99" s="51"/>
+      <c r="B99" s="51"/>
+      <c r="C99" s="51"/>
+      <c r="D99" s="51"/>
+      <c r="E99" s="51"/>
+      <c r="F99" s="51"/>
+      <c r="G99" s="51"/>
+      <c r="H99" s="51"/>
+      <c r="I99" s="51"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -8337,14 +8336,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -8721,15 +8720,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="50"/>
-      <c r="B71" s="50"/>
-      <c r="C71" s="50"/>
-      <c r="D71" s="50"/>
-      <c r="E71" s="50"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="50"/>
-      <c r="H71" s="50"/>
-      <c r="I71" s="50"/>
+      <c r="A71" s="51"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="51"/>
+      <c r="D71" s="51"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="51"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="51"/>
+      <c r="I71" s="51"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -8754,15 +8753,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="51"/>
-      <c r="B76" s="51"/>
-      <c r="C76" s="51"/>
-      <c r="D76" s="51"/>
-      <c r="E76" s="51"/>
-      <c r="F76" s="51"/>
-      <c r="G76" s="51"/>
-      <c r="H76" s="51"/>
-      <c r="I76" s="51"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -8798,15 +8797,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="52"/>
-      <c r="B80" s="52"/>
-      <c r="C80" s="52"/>
-      <c r="D80" s="52"/>
-      <c r="E80" s="52"/>
-      <c r="F80" s="52"/>
-      <c r="G80" s="52"/>
-      <c r="H80" s="52"/>
-      <c r="I80" s="52"/>
+      <c r="A80" s="53"/>
+      <c r="B80" s="53"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -8842,15 +8841,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="51"/>
-      <c r="B88" s="51"/>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="51"/>
-      <c r="G88" s="51"/>
-      <c r="H88" s="51"/>
-      <c r="I88" s="51"/>
+      <c r="A88" s="52"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="52"/>
+      <c r="G88" s="52"/>
+      <c r="H88" s="52"/>
+      <c r="I88" s="52"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -8953,15 +8952,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="50"/>
-      <c r="B101" s="50"/>
-      <c r="C101" s="50"/>
-      <c r="D101" s="50"/>
-      <c r="E101" s="50"/>
-      <c r="F101" s="50"/>
-      <c r="G101" s="50"/>
-      <c r="H101" s="50"/>
-      <c r="I101" s="50"/>
+      <c r="A101" s="51"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="51"/>
+      <c r="G101" s="51"/>
+      <c r="H101" s="51"/>
+      <c r="I101" s="51"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -11335,14 +11334,14 @@
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="50"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="51"/>
       <c r="T32" s="27"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
@@ -11720,15 +11719,15 @@
       <c r="I66" s="1"/>
     </row>
     <row r="67" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="50"/>
-      <c r="B67" s="50"/>
-      <c r="C67" s="50"/>
-      <c r="D67" s="50"/>
-      <c r="E67" s="50"/>
-      <c r="F67" s="50"/>
-      <c r="G67" s="50"/>
-      <c r="H67" s="50"/>
-      <c r="I67" s="50"/>
+      <c r="A67" s="51"/>
+      <c r="B67" s="51"/>
+      <c r="C67" s="51"/>
+      <c r="D67" s="51"/>
+      <c r="E67" s="51"/>
+      <c r="F67" s="51"/>
+      <c r="G67" s="51"/>
+      <c r="H67" s="51"/>
+      <c r="I67" s="51"/>
     </row>
     <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
@@ -11753,15 +11752,15 @@
       <c r="I69" s="23"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="51"/>
-      <c r="B72" s="51"/>
-      <c r="C72" s="51"/>
-      <c r="D72" s="51"/>
-      <c r="E72" s="51"/>
-      <c r="F72" s="51"/>
-      <c r="G72" s="51"/>
-      <c r="H72" s="51"/>
-      <c r="I72" s="51"/>
+      <c r="A72" s="52"/>
+      <c r="B72" s="52"/>
+      <c r="C72" s="52"/>
+      <c r="D72" s="52"/>
+      <c r="E72" s="52"/>
+      <c r="F72" s="52"/>
+      <c r="G72" s="52"/>
+      <c r="H72" s="52"/>
+      <c r="I72" s="52"/>
     </row>
     <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
@@ -11797,15 +11796,15 @@
       <c r="I75" s="25"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="52"/>
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
+      <c r="A76" s="53"/>
+      <c r="B76" s="53"/>
+      <c r="C76" s="53"/>
+      <c r="D76" s="53"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
+      <c r="H76" s="53"/>
+      <c r="I76" s="53"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -11841,15 +11840,15 @@
       <c r="B82" s="23"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="51"/>
-      <c r="B84" s="51"/>
-      <c r="C84" s="51"/>
-      <c r="D84" s="51"/>
-      <c r="E84" s="51"/>
-      <c r="F84" s="51"/>
-      <c r="G84" s="51"/>
-      <c r="H84" s="51"/>
-      <c r="I84" s="51"/>
+      <c r="A84" s="52"/>
+      <c r="B84" s="52"/>
+      <c r="C84" s="52"/>
+      <c r="D84" s="52"/>
+      <c r="E84" s="52"/>
+      <c r="F84" s="52"/>
+      <c r="G84" s="52"/>
+      <c r="H84" s="52"/>
+      <c r="I84" s="52"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
@@ -11952,15 +11951,15 @@
       <c r="B95" s="26"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="50"/>
-      <c r="B97" s="50"/>
-      <c r="C97" s="50"/>
-      <c r="D97" s="50"/>
-      <c r="E97" s="50"/>
-      <c r="F97" s="50"/>
-      <c r="G97" s="50"/>
-      <c r="H97" s="50"/>
-      <c r="I97" s="50"/>
+      <c r="A97" s="51"/>
+      <c r="B97" s="51"/>
+      <c r="C97" s="51"/>
+      <c r="D97" s="51"/>
+      <c r="E97" s="51"/>
+      <c r="F97" s="51"/>
+      <c r="G97" s="51"/>
+      <c r="H97" s="51"/>
+      <c r="I97" s="51"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
@@ -14510,14 +14509,14 @@
     <row r="34" spans="1:21" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
     </row>
     <row r="37" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -14894,15 +14893,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="50"/>
-      <c r="B71" s="50"/>
-      <c r="C71" s="50"/>
-      <c r="D71" s="50"/>
-      <c r="E71" s="50"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="50"/>
-      <c r="H71" s="50"/>
-      <c r="I71" s="50"/>
+      <c r="A71" s="51"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="51"/>
+      <c r="D71" s="51"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="51"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="51"/>
+      <c r="I71" s="51"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -14927,15 +14926,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="51"/>
-      <c r="B76" s="51"/>
-      <c r="C76" s="51"/>
-      <c r="D76" s="51"/>
-      <c r="E76" s="51"/>
-      <c r="F76" s="51"/>
-      <c r="G76" s="51"/>
-      <c r="H76" s="51"/>
-      <c r="I76" s="51"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -14971,15 +14970,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="52"/>
-      <c r="B80" s="52"/>
-      <c r="C80" s="52"/>
-      <c r="D80" s="52"/>
-      <c r="E80" s="52"/>
-      <c r="F80" s="52"/>
-      <c r="G80" s="52"/>
-      <c r="H80" s="52"/>
-      <c r="I80" s="52"/>
+      <c r="A80" s="53"/>
+      <c r="B80" s="53"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -15015,15 +15014,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="51"/>
-      <c r="B88" s="51"/>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="51"/>
-      <c r="G88" s="51"/>
-      <c r="H88" s="51"/>
-      <c r="I88" s="51"/>
+      <c r="A88" s="52"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="52"/>
+      <c r="G88" s="52"/>
+      <c r="H88" s="52"/>
+      <c r="I88" s="52"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -15126,15 +15125,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="50"/>
-      <c r="B101" s="50"/>
-      <c r="C101" s="50"/>
-      <c r="D101" s="50"/>
-      <c r="E101" s="50"/>
-      <c r="F101" s="50"/>
-      <c r="G101" s="50"/>
-      <c r="H101" s="50"/>
-      <c r="I101" s="50"/>
+      <c r="A101" s="51"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="51"/>
+      <c r="G101" s="51"/>
+      <c r="H101" s="51"/>
+      <c r="I101" s="51"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -17869,14 +17868,14 @@
     </row>
     <row r="35" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="50"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
     </row>
     <row r="36" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -18254,15 +18253,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="50"/>
-      <c r="B70" s="50"/>
-      <c r="C70" s="50"/>
-      <c r="D70" s="50"/>
-      <c r="E70" s="50"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="50"/>
-      <c r="H70" s="50"/>
-      <c r="I70" s="50"/>
+      <c r="A70" s="51"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="51"/>
+      <c r="I70" s="51"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -18287,15 +18286,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="51"/>
-      <c r="B75" s="51"/>
-      <c r="C75" s="51"/>
-      <c r="D75" s="51"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="51"/>
-      <c r="G75" s="51"/>
-      <c r="H75" s="51"/>
-      <c r="I75" s="51"/>
+      <c r="A75" s="52"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="F75" s="52"/>
+      <c r="G75" s="52"/>
+      <c r="H75" s="52"/>
+      <c r="I75" s="52"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -18331,15 +18330,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="52"/>
-      <c r="B79" s="52"/>
-      <c r="C79" s="52"/>
-      <c r="D79" s="52"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="52"/>
-      <c r="G79" s="52"/>
-      <c r="H79" s="52"/>
-      <c r="I79" s="52"/>
+      <c r="A79" s="53"/>
+      <c r="B79" s="53"/>
+      <c r="C79" s="53"/>
+      <c r="D79" s="53"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
+      <c r="H79" s="53"/>
+      <c r="I79" s="53"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -18375,15 +18374,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="51"/>
-      <c r="B87" s="51"/>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="51"/>
-      <c r="G87" s="51"/>
-      <c r="H87" s="51"/>
-      <c r="I87" s="51"/>
+      <c r="A87" s="52"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="52"/>
+      <c r="E87" s="52"/>
+      <c r="F87" s="52"/>
+      <c r="G87" s="52"/>
+      <c r="H87" s="52"/>
+      <c r="I87" s="52"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -18486,15 +18485,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="50"/>
-      <c r="B100" s="50"/>
-      <c r="C100" s="50"/>
-      <c r="D100" s="50"/>
-      <c r="E100" s="50"/>
-      <c r="F100" s="50"/>
-      <c r="G100" s="50"/>
-      <c r="H100" s="50"/>
-      <c r="I100" s="50"/>
+      <c r="A100" s="51"/>
+      <c r="B100" s="51"/>
+      <c r="C100" s="51"/>
+      <c r="D100" s="51"/>
+      <c r="E100" s="51"/>
+      <c r="F100" s="51"/>
+      <c r="G100" s="51"/>
+      <c r="H100" s="51"/>
+      <c r="I100" s="51"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -21121,14 +21120,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="50"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -21506,15 +21505,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="50"/>
-      <c r="B70" s="50"/>
-      <c r="C70" s="50"/>
-      <c r="D70" s="50"/>
-      <c r="E70" s="50"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="50"/>
-      <c r="H70" s="50"/>
-      <c r="I70" s="50"/>
+      <c r="A70" s="51"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="51"/>
+      <c r="I70" s="51"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -21539,15 +21538,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="51"/>
-      <c r="B75" s="51"/>
-      <c r="C75" s="51"/>
-      <c r="D75" s="51"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="51"/>
-      <c r="G75" s="51"/>
-      <c r="H75" s="51"/>
-      <c r="I75" s="51"/>
+      <c r="A75" s="52"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="F75" s="52"/>
+      <c r="G75" s="52"/>
+      <c r="H75" s="52"/>
+      <c r="I75" s="52"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -21583,15 +21582,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="52"/>
-      <c r="B79" s="52"/>
-      <c r="C79" s="52"/>
-      <c r="D79" s="52"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="52"/>
-      <c r="G79" s="52"/>
-      <c r="H79" s="52"/>
-      <c r="I79" s="52"/>
+      <c r="A79" s="53"/>
+      <c r="B79" s="53"/>
+      <c r="C79" s="53"/>
+      <c r="D79" s="53"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
+      <c r="H79" s="53"/>
+      <c r="I79" s="53"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -21627,15 +21626,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="51"/>
-      <c r="B87" s="51"/>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="51"/>
-      <c r="G87" s="51"/>
-      <c r="H87" s="51"/>
-      <c r="I87" s="51"/>
+      <c r="A87" s="52"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="52"/>
+      <c r="E87" s="52"/>
+      <c r="F87" s="52"/>
+      <c r="G87" s="52"/>
+      <c r="H87" s="52"/>
+      <c r="I87" s="52"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -21738,15 +21737,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="50"/>
-      <c r="B100" s="50"/>
-      <c r="C100" s="50"/>
-      <c r="D100" s="50"/>
-      <c r="E100" s="50"/>
-      <c r="F100" s="50"/>
-      <c r="G100" s="50"/>
-      <c r="H100" s="50"/>
-      <c r="I100" s="50"/>
+      <c r="A100" s="51"/>
+      <c r="B100" s="51"/>
+      <c r="C100" s="51"/>
+      <c r="D100" s="51"/>
+      <c r="E100" s="51"/>
+      <c r="F100" s="51"/>
+      <c r="G100" s="51"/>
+      <c r="H100" s="51"/>
+      <c r="I100" s="51"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -24449,14 +24448,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -24834,15 +24833,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="50"/>
-      <c r="B71" s="50"/>
-      <c r="C71" s="50"/>
-      <c r="D71" s="50"/>
-      <c r="E71" s="50"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="50"/>
-      <c r="H71" s="50"/>
-      <c r="I71" s="50"/>
+      <c r="A71" s="51"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="51"/>
+      <c r="D71" s="51"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="51"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="51"/>
+      <c r="I71" s="51"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -24867,15 +24866,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="51"/>
-      <c r="B76" s="51"/>
-      <c r="C76" s="51"/>
-      <c r="D76" s="51"/>
-      <c r="E76" s="51"/>
-      <c r="F76" s="51"/>
-      <c r="G76" s="51"/>
-      <c r="H76" s="51"/>
-      <c r="I76" s="51"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -24911,15 +24910,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="52"/>
-      <c r="B80" s="52"/>
-      <c r="C80" s="52"/>
-      <c r="D80" s="52"/>
-      <c r="E80" s="52"/>
-      <c r="F80" s="52"/>
-      <c r="G80" s="52"/>
-      <c r="H80" s="52"/>
-      <c r="I80" s="52"/>
+      <c r="A80" s="53"/>
+      <c r="B80" s="53"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -24955,15 +24954,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="51"/>
-      <c r="B88" s="51"/>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="51"/>
-      <c r="G88" s="51"/>
-      <c r="H88" s="51"/>
-      <c r="I88" s="51"/>
+      <c r="A88" s="52"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="52"/>
+      <c r="G88" s="52"/>
+      <c r="H88" s="52"/>
+      <c r="I88" s="52"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -25066,15 +25065,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="50"/>
-      <c r="B101" s="50"/>
-      <c r="C101" s="50"/>
-      <c r="D101" s="50"/>
-      <c r="E101" s="50"/>
-      <c r="F101" s="50"/>
-      <c r="G101" s="50"/>
-      <c r="H101" s="50"/>
-      <c r="I101" s="50"/>
+      <c r="A101" s="51"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="51"/>
+      <c r="G101" s="51"/>
+      <c r="H101" s="51"/>
+      <c r="I101" s="51"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -25344,11 +25343,11 @@
         <v>3660</v>
       </c>
       <c r="AF2" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AG2" s="11">
         <f t="array" ref="AG2">_xlfn.IFS(AF2="Verde",0,AF2="Amarela",1.885,AF2="Vermelha P1",4.463,AF2="Vermelha P2",7.877)</f>
-        <v>4.4630000000000001</v>
+        <v>7.8769999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
@@ -26041,49 +26040,49 @@
       </c>
       <c r="D10" s="6">
         <f t="shared" si="0"/>
-        <v>-10940</v>
+        <v>95</v>
       </c>
       <c r="E10" s="6">
         <v>0</v>
       </c>
       <c r="F10" s="6">
         <f t="shared" si="1"/>
-        <v>-13446</v>
+        <v>148</v>
       </c>
       <c r="G10" s="6">
         <v>0</v>
       </c>
       <c r="H10" s="6">
         <f t="shared" si="2"/>
-        <v>-9682</v>
+        <v>4</v>
       </c>
       <c r="I10" s="6">
         <v>0</v>
       </c>
       <c r="J10" s="6">
         <f t="shared" si="3"/>
-        <v>-10867</v>
+        <v>0</v>
       </c>
       <c r="K10" s="6">
         <v>0</v>
       </c>
       <c r="L10" s="6">
         <f t="shared" si="4"/>
-        <v>-1289</v>
+        <v>0</v>
       </c>
       <c r="M10" s="6">
         <v>0</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="5"/>
-        <v>-4102</v>
+        <v>5</v>
       </c>
       <c r="O10" s="6">
         <v>0</v>
       </c>
       <c r="P10" s="6">
         <f t="shared" si="6"/>
-        <v>-415</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="6">
         <v>0</v>
@@ -26093,7 +26092,7 @@
       </c>
       <c r="S10" s="6">
         <f t="shared" si="7"/>
-        <v>-3686</v>
+        <v>5</v>
       </c>
       <c r="T10" s="6"/>
       <c r="U10" s="4"/>
@@ -26138,49 +26137,49 @@
       </c>
       <c r="D11" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="E11" s="6">
         <v>0</v>
       </c>
       <c r="F11" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="G11" s="6">
         <v>0</v>
       </c>
       <c r="H11" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" s="6">
         <v>0</v>
       </c>
       <c r="J11" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="6">
         <v>0</v>
       </c>
       <c r="L11" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="6">
         <v>0</v>
       </c>
       <c r="N11" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O11" s="6">
         <v>0</v>
       </c>
       <c r="P11" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="6">
         <v>0</v>
@@ -26190,7 +26189,7 @@
       </c>
       <c r="S11" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T11" s="6"/>
       <c r="U11" s="4"/>
@@ -26198,14 +26197,30 @@
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="6"/>
-      <c r="AB11" s="6"/>
-      <c r="AC11" s="6"/>
-      <c r="AD11" s="6"/>
+      <c r="W11" s="15">
+        <v>11035</v>
+      </c>
+      <c r="X11" s="15">
+        <v>13594</v>
+      </c>
+      <c r="Y11" s="15">
+        <v>9686</v>
+      </c>
+      <c r="Z11" s="15">
+        <v>10867</v>
+      </c>
+      <c r="AA11" s="15">
+        <v>1289</v>
+      </c>
+      <c r="AB11" s="15">
+        <v>4107</v>
+      </c>
+      <c r="AC11" s="15">
+        <v>416</v>
+      </c>
+      <c r="AD11" s="15">
+        <v>3691</v>
+      </c>
     </row>
     <row r="12" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
@@ -26219,28 +26234,28 @@
       </c>
       <c r="D12" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="E12" s="6">
         <v>0</v>
       </c>
       <c r="F12" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G12" s="6">
         <v>0</v>
       </c>
       <c r="H12" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" s="6">
         <v>0</v>
       </c>
       <c r="J12" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="K12" s="6">
         <v>0</v>
@@ -26254,14 +26269,14 @@
       </c>
       <c r="N12" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" s="6">
         <v>0</v>
       </c>
       <c r="P12" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="6">
         <v>0</v>
@@ -26271,7 +26286,7 @@
       </c>
       <c r="S12" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12" s="6"/>
       <c r="U12" s="4"/>
@@ -26279,14 +26294,30 @@
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="6"/>
-      <c r="AA12" s="6"/>
-      <c r="AB12" s="6"/>
-      <c r="AC12" s="6"/>
-      <c r="AD12" s="6"/>
+      <c r="W12" s="6">
+        <v>11123</v>
+      </c>
+      <c r="X12" s="6">
+        <v>13701</v>
+      </c>
+      <c r="Y12" s="6">
+        <v>9689</v>
+      </c>
+      <c r="Z12" s="6">
+        <v>10868</v>
+      </c>
+      <c r="AA12" s="6">
+        <v>1290</v>
+      </c>
+      <c r="AB12" s="6">
+        <v>4114</v>
+      </c>
+      <c r="AC12" s="6">
+        <v>417</v>
+      </c>
+      <c r="AD12" s="6">
+        <v>3696</v>
+      </c>
     </row>
     <row r="13" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
@@ -26300,28 +26331,28 @@
       </c>
       <c r="D13" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13" s="6">
         <v>0</v>
       </c>
       <c r="F13" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="G13" s="6">
         <v>0</v>
       </c>
       <c r="H13" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" s="6">
         <v>0</v>
       </c>
       <c r="J13" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K13" s="6">
         <v>0</v>
@@ -26335,14 +26366,14 @@
       </c>
       <c r="N13" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O13" s="6">
         <v>0</v>
       </c>
       <c r="P13" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="6">
         <v>0</v>
@@ -26352,7 +26383,7 @@
       </c>
       <c r="S13" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T13" s="6"/>
       <c r="U13" s="4"/>
@@ -26360,14 +26391,30 @@
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="W13" s="15"/>
-      <c r="X13" s="15"/>
-      <c r="Y13" s="15"/>
-      <c r="Z13" s="15"/>
-      <c r="AA13" s="15"/>
-      <c r="AB13" s="15"/>
-      <c r="AC13" s="15"/>
-      <c r="AD13" s="15"/>
+      <c r="W13" s="15">
+        <v>11253</v>
+      </c>
+      <c r="X13" s="15">
+        <v>13788</v>
+      </c>
+      <c r="Y13" s="15">
+        <v>9692</v>
+      </c>
+      <c r="Z13" s="15">
+        <v>10860</v>
+      </c>
+      <c r="AA13" s="15">
+        <v>1290</v>
+      </c>
+      <c r="AB13" s="15">
+        <v>4117</v>
+      </c>
+      <c r="AC13" s="15">
+        <v>418</v>
+      </c>
+      <c r="AD13" s="15">
+        <v>3699</v>
+      </c>
     </row>
     <row r="14" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
@@ -26381,28 +26428,28 @@
       </c>
       <c r="D14" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="E14" s="6">
         <v>0</v>
       </c>
       <c r="F14" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G14" s="6">
         <v>0</v>
       </c>
       <c r="H14" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="6">
         <v>0</v>
       </c>
       <c r="J14" s="6">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="6">
         <v>0</v>
@@ -26416,7 +26463,7 @@
       </c>
       <c r="N14" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O14" s="6">
         <v>0</v>
@@ -26433,7 +26480,7 @@
       </c>
       <c r="S14" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="4"/>
@@ -26441,14 +26488,30 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="6"/>
-      <c r="AB14" s="6"/>
-      <c r="AC14" s="6"/>
-      <c r="AD14" s="6"/>
+      <c r="W14" s="6">
+        <v>11353</v>
+      </c>
+      <c r="X14" s="6">
+        <v>13895</v>
+      </c>
+      <c r="Y14" s="6">
+        <v>9695</v>
+      </c>
+      <c r="Z14" s="6">
+        <v>10870</v>
+      </c>
+      <c r="AA14" s="6">
+        <v>1290</v>
+      </c>
+      <c r="AB14" s="6">
+        <v>4124</v>
+      </c>
+      <c r="AC14" s="6">
+        <v>419</v>
+      </c>
+      <c r="AD14" s="6">
+        <v>3705</v>
+      </c>
     </row>
     <row r="15" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
@@ -26462,21 +26525,21 @@
       </c>
       <c r="D15" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="E15" s="6">
         <v>0</v>
       </c>
       <c r="F15" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="G15" s="6">
         <v>0</v>
       </c>
       <c r="H15" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I15" s="6">
         <v>0</v>
@@ -26496,7 +26559,7 @@
       </c>
       <c r="N15" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O15" s="6">
         <v>0</v>
@@ -26513,7 +26576,7 @@
       </c>
       <c r="S15" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T15" s="6"/>
       <c r="U15" s="4"/>
@@ -26521,14 +26584,30 @@
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="6"/>
-      <c r="AB15" s="6"/>
-      <c r="AC15" s="6"/>
-      <c r="AD15" s="6"/>
+      <c r="W15" s="6">
+        <v>11440</v>
+      </c>
+      <c r="X15" s="6">
+        <v>13929</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>9697</v>
+      </c>
+      <c r="Z15" s="6">
+        <v>10871</v>
+      </c>
+      <c r="AA15" s="6">
+        <v>1290</v>
+      </c>
+      <c r="AB15" s="6">
+        <v>4129</v>
+      </c>
+      <c r="AC15" s="6">
+        <v>419</v>
+      </c>
+      <c r="AD15" s="6">
+        <v>3710</v>
+      </c>
     </row>
     <row r="16" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
@@ -26542,28 +26621,28 @@
       </c>
       <c r="D16" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E16" s="6">
         <v>0</v>
       </c>
       <c r="F16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G16" s="6">
         <v>0</v>
       </c>
       <c r="H16" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I16" s="6">
         <v>0</v>
       </c>
       <c r="J16" s="6">
         <f t="shared" ref="J16:J31" si="9">Z17-Z16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="6">
         <v>0</v>
@@ -26577,7 +26656,7 @@
       </c>
       <c r="N16" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O16" s="6">
         <v>0</v>
@@ -26594,7 +26673,7 @@
       </c>
       <c r="S16" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="4"/>
@@ -26602,14 +26681,30 @@
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="16"/>
-      <c r="Z16" s="16"/>
-      <c r="AA16" s="16"/>
-      <c r="AB16" s="16"/>
-      <c r="AC16" s="16"/>
-      <c r="AD16" s="16"/>
+      <c r="W16" s="16">
+        <v>11509</v>
+      </c>
+      <c r="X16" s="16">
+        <v>14008</v>
+      </c>
+      <c r="Y16" s="16">
+        <v>9702</v>
+      </c>
+      <c r="Z16" s="16">
+        <v>10871</v>
+      </c>
+      <c r="AA16" s="16">
+        <v>1290</v>
+      </c>
+      <c r="AB16" s="16">
+        <v>4135</v>
+      </c>
+      <c r="AC16" s="16">
+        <v>419</v>
+      </c>
+      <c r="AD16" s="16">
+        <v>3715</v>
+      </c>
     </row>
     <row r="17" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
@@ -26623,21 +26718,21 @@
       </c>
       <c r="D17" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17" s="6">
         <v>0</v>
       </c>
       <c r="F17" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G17" s="6">
         <v>0</v>
       </c>
       <c r="H17" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="6">
         <v>0</v>
@@ -26651,21 +26746,21 @@
       </c>
       <c r="L17" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="6">
         <v>0</v>
       </c>
       <c r="N17" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O17" s="6">
         <v>0</v>
       </c>
       <c r="P17" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="6">
         <v>0</v>
@@ -26675,7 +26770,7 @@
       </c>
       <c r="S17" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T17" s="6"/>
       <c r="U17" s="4"/>
@@ -26683,14 +26778,30 @@
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="16"/>
-      <c r="AB17" s="16"/>
-      <c r="AC17" s="16"/>
-      <c r="AD17" s="16"/>
+      <c r="W17" s="16">
+        <v>11536</v>
+      </c>
+      <c r="X17" s="16">
+        <v>14046</v>
+      </c>
+      <c r="Y17" s="16">
+        <v>9709</v>
+      </c>
+      <c r="Z17" s="16">
+        <v>10872</v>
+      </c>
+      <c r="AA17" s="16">
+        <v>1290</v>
+      </c>
+      <c r="AB17" s="16">
+        <v>4141</v>
+      </c>
+      <c r="AC17" s="16">
+        <v>419</v>
+      </c>
+      <c r="AD17" s="16">
+        <v>3721</v>
+      </c>
     </row>
     <row r="18" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
@@ -26704,49 +26815,49 @@
       </c>
       <c r="D18" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-11636</v>
       </c>
       <c r="E18" s="6">
         <v>0</v>
       </c>
       <c r="F18" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-14127</v>
       </c>
       <c r="G18" s="6">
         <v>0</v>
       </c>
       <c r="H18" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9710</v>
       </c>
       <c r="I18" s="6">
         <v>0</v>
       </c>
       <c r="J18" s="6">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-10872</v>
       </c>
       <c r="K18" s="6">
         <v>0</v>
       </c>
       <c r="L18" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1291</v>
       </c>
       <c r="M18" s="6">
         <v>0</v>
       </c>
       <c r="N18" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4148</v>
       </c>
       <c r="O18" s="6">
         <v>0</v>
       </c>
       <c r="P18" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-420</v>
       </c>
       <c r="Q18" s="6">
         <v>0</v>
@@ -26756,7 +26867,7 @@
       </c>
       <c r="S18" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3727</v>
       </c>
       <c r="T18" s="6"/>
       <c r="U18" s="4"/>
@@ -26764,14 +26875,30 @@
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
-      <c r="Y18" s="16"/>
-      <c r="Z18" s="16"/>
-      <c r="AA18" s="16"/>
-      <c r="AB18" s="16"/>
-      <c r="AC18" s="16"/>
-      <c r="AD18" s="16"/>
+      <c r="W18" s="16">
+        <v>11636</v>
+      </c>
+      <c r="X18" s="16">
+        <v>14127</v>
+      </c>
+      <c r="Y18" s="16">
+        <v>9710</v>
+      </c>
+      <c r="Z18" s="16">
+        <v>10872</v>
+      </c>
+      <c r="AA18" s="16">
+        <v>1291</v>
+      </c>
+      <c r="AB18" s="16">
+        <v>4148</v>
+      </c>
+      <c r="AC18" s="16">
+        <v>420</v>
+      </c>
+      <c r="AD18" s="16">
+        <v>3727</v>
+      </c>
     </row>
     <row r="19" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
@@ -27854,14 +27981,14 @@
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="50"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="50"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="51"/>
+      <c r="I34" s="51"/>
     </row>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
@@ -28239,15 +28366,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="50"/>
-      <c r="B69" s="50"/>
-      <c r="C69" s="50"/>
-      <c r="D69" s="50"/>
-      <c r="E69" s="50"/>
-      <c r="F69" s="50"/>
-      <c r="G69" s="50"/>
-      <c r="H69" s="50"/>
-      <c r="I69" s="50"/>
+      <c r="A69" s="51"/>
+      <c r="B69" s="51"/>
+      <c r="C69" s="51"/>
+      <c r="D69" s="51"/>
+      <c r="E69" s="51"/>
+      <c r="F69" s="51"/>
+      <c r="G69" s="51"/>
+      <c r="H69" s="51"/>
+      <c r="I69" s="51"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -28272,15 +28399,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="51"/>
-      <c r="B74" s="51"/>
-      <c r="C74" s="51"/>
-      <c r="D74" s="51"/>
-      <c r="E74" s="51"/>
-      <c r="F74" s="51"/>
-      <c r="G74" s="51"/>
-      <c r="H74" s="51"/>
-      <c r="I74" s="51"/>
+      <c r="A74" s="52"/>
+      <c r="B74" s="52"/>
+      <c r="C74" s="52"/>
+      <c r="D74" s="52"/>
+      <c r="E74" s="52"/>
+      <c r="F74" s="52"/>
+      <c r="G74" s="52"/>
+      <c r="H74" s="52"/>
+      <c r="I74" s="52"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -28316,15 +28443,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="52"/>
-      <c r="B78" s="52"/>
-      <c r="C78" s="52"/>
-      <c r="D78" s="52"/>
-      <c r="E78" s="52"/>
-      <c r="F78" s="52"/>
-      <c r="G78" s="52"/>
-      <c r="H78" s="52"/>
-      <c r="I78" s="52"/>
+      <c r="A78" s="53"/>
+      <c r="B78" s="53"/>
+      <c r="C78" s="53"/>
+      <c r="D78" s="53"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="53"/>
+      <c r="H78" s="53"/>
+      <c r="I78" s="53"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -28360,15 +28487,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="51"/>
-      <c r="B86" s="51"/>
-      <c r="C86" s="51"/>
-      <c r="D86" s="51"/>
-      <c r="E86" s="51"/>
-      <c r="F86" s="51"/>
-      <c r="G86" s="51"/>
-      <c r="H86" s="51"/>
-      <c r="I86" s="51"/>
+      <c r="A86" s="52"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="52"/>
+      <c r="D86" s="52"/>
+      <c r="E86" s="52"/>
+      <c r="F86" s="52"/>
+      <c r="G86" s="52"/>
+      <c r="H86" s="52"/>
+      <c r="I86" s="52"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -28471,15 +28598,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="50"/>
-      <c r="B99" s="50"/>
-      <c r="C99" s="50"/>
-      <c r="D99" s="50"/>
-      <c r="E99" s="50"/>
-      <c r="F99" s="50"/>
-      <c r="G99" s="50"/>
-      <c r="H99" s="50"/>
-      <c r="I99" s="50"/>
+      <c r="A99" s="51"/>
+      <c r="B99" s="51"/>
+      <c r="C99" s="51"/>
+      <c r="D99" s="51"/>
+      <c r="E99" s="51"/>
+      <c r="F99" s="51"/>
+      <c r="G99" s="51"/>
+      <c r="H99" s="51"/>
+      <c r="I99" s="51"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -29348,12 +29475,12 @@
       <c r="AD8" s="6">
         <v>3558</v>
       </c>
-      <c r="AH8" s="53"/>
-      <c r="AI8" s="53"/>
-      <c r="AJ8" s="53"/>
-      <c r="AK8" s="54"/>
-      <c r="AL8" s="54"/>
-      <c r="AM8" s="54"/>
+      <c r="AH8" s="54"/>
+      <c r="AI8" s="54"/>
+      <c r="AJ8" s="54"/>
+      <c r="AK8" s="55"/>
+      <c r="AL8" s="55"/>
+      <c r="AM8" s="55"/>
     </row>
     <row r="9" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="28">
@@ -31717,14 +31844,14 @@
     </row>
     <row r="35" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="50"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -32103,15 +32230,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="50"/>
-      <c r="B70" s="50"/>
-      <c r="C70" s="50"/>
-      <c r="D70" s="50"/>
-      <c r="E70" s="50"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="50"/>
-      <c r="H70" s="50"/>
-      <c r="I70" s="50"/>
+      <c r="A70" s="51"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="51"/>
+      <c r="I70" s="51"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -32136,15 +32263,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="51"/>
-      <c r="B75" s="51"/>
-      <c r="C75" s="51"/>
-      <c r="D75" s="51"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="51"/>
-      <c r="G75" s="51"/>
-      <c r="H75" s="51"/>
-      <c r="I75" s="51"/>
+      <c r="A75" s="52"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="F75" s="52"/>
+      <c r="G75" s="52"/>
+      <c r="H75" s="52"/>
+      <c r="I75" s="52"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -32180,15 +32307,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="52"/>
-      <c r="B79" s="52"/>
-      <c r="C79" s="52"/>
-      <c r="D79" s="52"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="52"/>
-      <c r="G79" s="52"/>
-      <c r="H79" s="52"/>
-      <c r="I79" s="52"/>
+      <c r="A79" s="53"/>
+      <c r="B79" s="53"/>
+      <c r="C79" s="53"/>
+      <c r="D79" s="53"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
+      <c r="H79" s="53"/>
+      <c r="I79" s="53"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -32224,15 +32351,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="51"/>
-      <c r="B87" s="51"/>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="51"/>
-      <c r="G87" s="51"/>
-      <c r="H87" s="51"/>
-      <c r="I87" s="51"/>
+      <c r="A87" s="52"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="52"/>
+      <c r="E87" s="52"/>
+      <c r="F87" s="52"/>
+      <c r="G87" s="52"/>
+      <c r="H87" s="52"/>
+      <c r="I87" s="52"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -32335,15 +32462,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="50"/>
-      <c r="B100" s="50"/>
-      <c r="C100" s="50"/>
-      <c r="D100" s="50"/>
-      <c r="E100" s="50"/>
-      <c r="F100" s="50"/>
-      <c r="G100" s="50"/>
-      <c r="H100" s="50"/>
-      <c r="I100" s="50"/>
+      <c r="A100" s="51"/>
+      <c r="B100" s="51"/>
+      <c r="C100" s="51"/>
+      <c r="D100" s="51"/>
+      <c r="E100" s="51"/>
+      <c r="F100" s="51"/>
+      <c r="G100" s="51"/>
+      <c r="H100" s="51"/>
+      <c r="I100" s="51"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -35534,16 +35661,16 @@
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="55"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
+      <c r="Q36" s="50"/>
+      <c r="R36" s="50"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -35921,15 +36048,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="50"/>
-      <c r="B71" s="50"/>
-      <c r="C71" s="50"/>
-      <c r="D71" s="50"/>
-      <c r="E71" s="50"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="50"/>
-      <c r="H71" s="50"/>
-      <c r="I71" s="50"/>
+      <c r="A71" s="51"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="51"/>
+      <c r="D71" s="51"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="51"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="51"/>
+      <c r="I71" s="51"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -35954,15 +36081,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="51"/>
-      <c r="B76" s="51"/>
-      <c r="C76" s="51"/>
-      <c r="D76" s="51"/>
-      <c r="E76" s="51"/>
-      <c r="F76" s="51"/>
-      <c r="G76" s="51"/>
-      <c r="H76" s="51"/>
-      <c r="I76" s="51"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -35998,15 +36125,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="52"/>
-      <c r="B80" s="52"/>
-      <c r="C80" s="52"/>
-      <c r="D80" s="52"/>
-      <c r="E80" s="52"/>
-      <c r="F80" s="52"/>
-      <c r="G80" s="52"/>
-      <c r="H80" s="52"/>
-      <c r="I80" s="52"/>
+      <c r="A80" s="53"/>
+      <c r="B80" s="53"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -36042,15 +36169,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="51"/>
-      <c r="B88" s="51"/>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="51"/>
-      <c r="G88" s="51"/>
-      <c r="H88" s="51"/>
-      <c r="I88" s="51"/>
+      <c r="A88" s="52"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="52"/>
+      <c r="G88" s="52"/>
+      <c r="H88" s="52"/>
+      <c r="I88" s="52"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -36153,15 +36280,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="50"/>
-      <c r="B101" s="50"/>
-      <c r="C101" s="50"/>
-      <c r="D101" s="50"/>
-      <c r="E101" s="50"/>
-      <c r="F101" s="50"/>
-      <c r="G101" s="50"/>
-      <c r="H101" s="50"/>
-      <c r="I101" s="50"/>
+      <c r="A101" s="51"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="51"/>
+      <c r="G101" s="51"/>
+      <c r="H101" s="51"/>
+      <c r="I101" s="51"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -39213,22 +39340,22 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="50"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="50"/>
-      <c r="P35" s="50"/>
-      <c r="Q35" s="50"/>
-      <c r="R35" s="50"/>
-      <c r="S35" s="50"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
+      <c r="J35" s="51"/>
+      <c r="K35" s="51"/>
+      <c r="L35" s="51"/>
+      <c r="M35" s="51"/>
+      <c r="N35" s="51"/>
+      <c r="O35" s="51"/>
+      <c r="P35" s="51"/>
+      <c r="Q35" s="51"/>
+      <c r="R35" s="51"/>
+      <c r="S35" s="51"/>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -39946,25 +40073,25 @@
       <c r="S69" s="1"/>
     </row>
     <row r="70" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="50"/>
-      <c r="B70" s="50"/>
-      <c r="C70" s="50"/>
-      <c r="D70" s="50"/>
-      <c r="E70" s="50"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="50"/>
-      <c r="H70" s="50"/>
-      <c r="I70" s="50"/>
-      <c r="J70" s="50"/>
-      <c r="K70" s="50"/>
-      <c r="L70" s="50"/>
-      <c r="M70" s="50"/>
-      <c r="N70" s="50"/>
-      <c r="O70" s="50"/>
-      <c r="P70" s="50"/>
-      <c r="Q70" s="50"/>
-      <c r="R70" s="50"/>
-      <c r="S70" s="50"/>
+      <c r="A70" s="51"/>
+      <c r="B70" s="51"/>
+      <c r="C70" s="51"/>
+      <c r="D70" s="51"/>
+      <c r="E70" s="51"/>
+      <c r="F70" s="51"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="51"/>
+      <c r="I70" s="51"/>
+      <c r="J70" s="51"/>
+      <c r="K70" s="51"/>
+      <c r="L70" s="51"/>
+      <c r="M70" s="51"/>
+      <c r="N70" s="51"/>
+      <c r="O70" s="51"/>
+      <c r="P70" s="51"/>
+      <c r="Q70" s="51"/>
+      <c r="R70" s="51"/>
+      <c r="S70" s="51"/>
     </row>
     <row r="71" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -40009,25 +40136,25 @@
       <c r="S72" s="23"/>
     </row>
     <row r="75" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="51"/>
-      <c r="B75" s="51"/>
-      <c r="C75" s="51"/>
-      <c r="D75" s="51"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="51"/>
-      <c r="G75" s="51"/>
-      <c r="H75" s="51"/>
-      <c r="I75" s="51"/>
-      <c r="J75" s="51"/>
-      <c r="K75" s="51"/>
-      <c r="L75" s="51"/>
-      <c r="M75" s="51"/>
-      <c r="N75" s="51"/>
-      <c r="O75" s="51"/>
-      <c r="P75" s="51"/>
-      <c r="Q75" s="51"/>
-      <c r="R75" s="51"/>
-      <c r="S75" s="51"/>
+      <c r="A75" s="52"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="F75" s="52"/>
+      <c r="G75" s="52"/>
+      <c r="H75" s="52"/>
+      <c r="I75" s="52"/>
+      <c r="J75" s="52"/>
+      <c r="K75" s="52"/>
+      <c r="L75" s="52"/>
+      <c r="M75" s="52"/>
+      <c r="N75" s="52"/>
+      <c r="O75" s="52"/>
+      <c r="P75" s="52"/>
+      <c r="Q75" s="52"/>
+      <c r="R75" s="52"/>
+      <c r="S75" s="52"/>
     </row>
     <row r="76" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -40093,25 +40220,25 @@
       <c r="S78" s="25"/>
     </row>
     <row r="79" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="52"/>
-      <c r="B79" s="52"/>
-      <c r="C79" s="52"/>
-      <c r="D79" s="52"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="52"/>
-      <c r="G79" s="52"/>
-      <c r="H79" s="52"/>
-      <c r="I79" s="52"/>
-      <c r="J79" s="52"/>
-      <c r="K79" s="52"/>
-      <c r="L79" s="52"/>
-      <c r="M79" s="52"/>
-      <c r="N79" s="52"/>
-      <c r="O79" s="52"/>
-      <c r="P79" s="52"/>
-      <c r="Q79" s="52"/>
-      <c r="R79" s="52"/>
-      <c r="S79" s="52"/>
+      <c r="A79" s="53"/>
+      <c r="B79" s="53"/>
+      <c r="C79" s="53"/>
+      <c r="D79" s="53"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="53"/>
+      <c r="H79" s="53"/>
+      <c r="I79" s="53"/>
+      <c r="J79" s="53"/>
+      <c r="K79" s="53"/>
+      <c r="L79" s="53"/>
+      <c r="M79" s="53"/>
+      <c r="N79" s="53"/>
+      <c r="O79" s="53"/>
+      <c r="P79" s="53"/>
+      <c r="Q79" s="53"/>
+      <c r="R79" s="53"/>
+      <c r="S79" s="53"/>
     </row>
     <row r="80" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -40175,25 +40302,25 @@
       <c r="E85" s="23"/>
     </row>
     <row r="87" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="51"/>
-      <c r="B87" s="51"/>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="51"/>
-      <c r="G87" s="51"/>
-      <c r="H87" s="51"/>
-      <c r="I87" s="51"/>
-      <c r="J87" s="51"/>
-      <c r="K87" s="51"/>
-      <c r="L87" s="51"/>
-      <c r="M87" s="51"/>
-      <c r="N87" s="51"/>
-      <c r="O87" s="51"/>
-      <c r="P87" s="51"/>
-      <c r="Q87" s="51"/>
-      <c r="R87" s="51"/>
-      <c r="S87" s="51"/>
+      <c r="A87" s="52"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="52"/>
+      <c r="E87" s="52"/>
+      <c r="F87" s="52"/>
+      <c r="G87" s="52"/>
+      <c r="H87" s="52"/>
+      <c r="I87" s="52"/>
+      <c r="J87" s="52"/>
+      <c r="K87" s="52"/>
+      <c r="L87" s="52"/>
+      <c r="M87" s="52"/>
+      <c r="N87" s="52"/>
+      <c r="O87" s="52"/>
+      <c r="P87" s="52"/>
+      <c r="Q87" s="52"/>
+      <c r="R87" s="52"/>
+      <c r="S87" s="52"/>
     </row>
     <row r="88" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -40385,25 +40512,25 @@
       <c r="E98" s="26"/>
     </row>
     <row r="100" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="50"/>
-      <c r="B100" s="50"/>
-      <c r="C100" s="50"/>
-      <c r="D100" s="50"/>
-      <c r="E100" s="50"/>
-      <c r="F100" s="50"/>
-      <c r="G100" s="50"/>
-      <c r="H100" s="50"/>
-      <c r="I100" s="50"/>
-      <c r="J100" s="50"/>
-      <c r="K100" s="50"/>
-      <c r="L100" s="50"/>
-      <c r="M100" s="50"/>
-      <c r="N100" s="50"/>
-      <c r="O100" s="50"/>
-      <c r="P100" s="50"/>
-      <c r="Q100" s="50"/>
-      <c r="R100" s="50"/>
-      <c r="S100" s="50"/>
+      <c r="A100" s="51"/>
+      <c r="B100" s="51"/>
+      <c r="C100" s="51"/>
+      <c r="D100" s="51"/>
+      <c r="E100" s="51"/>
+      <c r="F100" s="51"/>
+      <c r="G100" s="51"/>
+      <c r="H100" s="51"/>
+      <c r="I100" s="51"/>
+      <c r="J100" s="51"/>
+      <c r="K100" s="51"/>
+      <c r="L100" s="51"/>
+      <c r="M100" s="51"/>
+      <c r="N100" s="51"/>
+      <c r="O100" s="51"/>
+      <c r="P100" s="51"/>
+      <c r="Q100" s="51"/>
+      <c r="R100" s="51"/>
+      <c r="S100" s="51"/>
     </row>
     <row r="101" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -43646,14 +43773,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -44031,15 +44158,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="50"/>
-      <c r="B71" s="50"/>
-      <c r="C71" s="50"/>
-      <c r="D71" s="50"/>
-      <c r="E71" s="50"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="50"/>
-      <c r="H71" s="50"/>
-      <c r="I71" s="50"/>
+      <c r="A71" s="51"/>
+      <c r="B71" s="51"/>
+      <c r="C71" s="51"/>
+      <c r="D71" s="51"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="51"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="51"/>
+      <c r="I71" s="51"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -44064,15 +44191,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="51"/>
-      <c r="B76" s="51"/>
-      <c r="C76" s="51"/>
-      <c r="D76" s="51"/>
-      <c r="E76" s="51"/>
-      <c r="F76" s="51"/>
-      <c r="G76" s="51"/>
-      <c r="H76" s="51"/>
-      <c r="I76" s="51"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
+      <c r="D76" s="52"/>
+      <c r="E76" s="52"/>
+      <c r="F76" s="52"/>
+      <c r="G76" s="52"/>
+      <c r="H76" s="52"/>
+      <c r="I76" s="52"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -44108,15 +44235,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="52"/>
-      <c r="B80" s="52"/>
-      <c r="C80" s="52"/>
-      <c r="D80" s="52"/>
-      <c r="E80" s="52"/>
-      <c r="F80" s="52"/>
-      <c r="G80" s="52"/>
-      <c r="H80" s="52"/>
-      <c r="I80" s="52"/>
+      <c r="A80" s="53"/>
+      <c r="B80" s="53"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -44152,15 +44279,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="51"/>
-      <c r="B88" s="51"/>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="51"/>
-      <c r="G88" s="51"/>
-      <c r="H88" s="51"/>
-      <c r="I88" s="51"/>
+      <c r="A88" s="52"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="52"/>
+      <c r="E88" s="52"/>
+      <c r="F88" s="52"/>
+      <c r="G88" s="52"/>
+      <c r="H88" s="52"/>
+      <c r="I88" s="52"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -44263,15 +44390,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="50"/>
-      <c r="B101" s="50"/>
-      <c r="C101" s="50"/>
-      <c r="D101" s="50"/>
-      <c r="E101" s="50"/>
-      <c r="F101" s="50"/>
-      <c r="G101" s="50"/>
-      <c r="H101" s="50"/>
-      <c r="I101" s="50"/>
+      <c r="A101" s="51"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="51"/>
+      <c r="G101" s="51"/>
+      <c r="H101" s="51"/>
+      <c r="I101" s="51"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9AAC2D-1EE8-4D90-99B7-0C5009C33E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241A61C7-30A2-4136-BAC1-BCC7A70E7D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="99">
   <si>
     <t>Data</t>
   </si>
@@ -314,6 +314,36 @@
   </si>
   <si>
     <t>APOIO LOG - OP ATLAS</t>
+  </si>
+  <si>
+    <t>CAPACITAÇÃO DFPC</t>
+  </si>
+  <si>
+    <t>DESFILE 7 SET</t>
+  </si>
+  <si>
+    <t>2ª CH TAT</t>
+  </si>
+  <si>
+    <t>2ª CH TAT, PCI ESA</t>
+  </si>
+  <si>
+    <t>CULTOS, 2ª CH TAT, PCI ESA</t>
+  </si>
+  <si>
+    <t>PCI ESA</t>
+  </si>
+  <si>
+    <t>PCI CIAVEX</t>
+  </si>
+  <si>
+    <t>PCI CIAVEX, FORM GERAL</t>
+  </si>
+  <si>
+    <t>CHEGADA MEIO OP AZUL TURQUESA</t>
+  </si>
+  <si>
+    <t>TRNSP OP AZUL TURQUESA</t>
   </si>
 </sst>
 </file>
@@ -25149,6 +25179,7 @@
     <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
     <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
@@ -25313,7 +25344,9 @@
         <f t="shared" ref="S2:S31" si="7">AD3-AD2</f>
         <v>0</v>
       </c>
-      <c r="T2" s="6"/>
+      <c r="T2" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="U2" s="4"/>
       <c r="V2" s="8">
         <v>0</v>
@@ -25416,7 +25449,9 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="T3" s="6"/>
+      <c r="T3" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="U3" s="4"/>
       <c r="V3" s="12">
         <v>1</v>
@@ -25512,7 +25547,9 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="T4" s="6"/>
+      <c r="T4" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U4" s="4"/>
       <c r="V4" s="14">
         <f t="shared" ref="V4:V32" si="8">V3+1</f>
@@ -25609,7 +25646,9 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="T5" s="6"/>
+      <c r="T5" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="U5" s="4"/>
       <c r="V5" s="14">
         <f t="shared" si="8"/>
@@ -25706,7 +25745,9 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="T6" s="6"/>
+      <c r="T6" s="6" t="s">
+        <v>89</v>
+      </c>
       <c r="U6" s="4"/>
       <c r="V6" s="14">
         <f t="shared" si="8"/>
@@ -25803,7 +25844,9 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="T7" s="6"/>
+      <c r="T7" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U7" s="4"/>
       <c r="V7" s="14">
         <f t="shared" si="8"/>
@@ -25900,7 +25943,9 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="T8" s="6"/>
+      <c r="T8" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="U8" s="4"/>
       <c r="V8" s="14">
         <f t="shared" si="8"/>
@@ -25997,7 +26042,9 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="T9" s="6"/>
+      <c r="T9" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="U9" s="4"/>
       <c r="V9" s="14">
         <f t="shared" si="8"/>
@@ -26094,7 +26141,9 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="T10" s="6"/>
+      <c r="T10" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="U10" s="4"/>
       <c r="V10" s="14">
         <f t="shared" si="8"/>
@@ -26125,7 +26174,7 @@
         <v>3686</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>45910</v>
       </c>
@@ -26191,7 +26240,9 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="T11" s="6"/>
+      <c r="T11" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="U11" s="4"/>
       <c r="V11" s="14">
         <f t="shared" si="8"/>
@@ -26288,7 +26339,9 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="T12" s="6"/>
+      <c r="T12" s="6" t="s">
+        <v>92</v>
+      </c>
       <c r="U12" s="4"/>
       <c r="V12" s="14">
         <f t="shared" si="8"/>
@@ -26385,7 +26438,9 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="T13" s="6"/>
+      <c r="T13" s="6" t="s">
+        <v>94</v>
+      </c>
       <c r="U13" s="4"/>
       <c r="V13" s="14">
         <f t="shared" si="8"/>
@@ -26482,7 +26537,9 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="T14" s="6"/>
+      <c r="T14" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U14" s="4"/>
       <c r="V14" s="14">
         <f t="shared" si="8"/>
@@ -26578,7 +26635,9 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="T15" s="6"/>
+      <c r="T15" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U15" s="4"/>
       <c r="V15" s="14">
         <f t="shared" si="8"/>
@@ -26675,7 +26734,9 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="T16" s="6"/>
+      <c r="T16" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U16" s="4"/>
       <c r="V16" s="14">
         <f t="shared" si="8"/>
@@ -26772,7 +26833,9 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="T17" s="6"/>
+      <c r="T17" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U17" s="4"/>
       <c r="V17" s="14">
         <f t="shared" si="8"/>
@@ -26815,49 +26878,49 @@
       </c>
       <c r="D18" s="6">
         <f t="shared" si="0"/>
-        <v>-11636</v>
+        <v>0</v>
       </c>
       <c r="E18" s="6">
         <v>0</v>
       </c>
       <c r="F18" s="6">
         <f t="shared" si="1"/>
-        <v>-14127</v>
+        <v>0</v>
       </c>
       <c r="G18" s="6">
         <v>0</v>
       </c>
       <c r="H18" s="6">
         <f t="shared" si="2"/>
-        <v>-9710</v>
+        <v>0</v>
       </c>
       <c r="I18" s="6">
         <v>0</v>
       </c>
       <c r="J18" s="6">
         <f t="shared" si="9"/>
-        <v>-10872</v>
+        <v>0</v>
       </c>
       <c r="K18" s="6">
         <v>0</v>
       </c>
       <c r="L18" s="6">
         <f t="shared" si="4"/>
-        <v>-1291</v>
+        <v>0</v>
       </c>
       <c r="M18" s="6">
         <v>0</v>
       </c>
       <c r="N18" s="6">
         <f t="shared" si="5"/>
-        <v>-4148</v>
+        <v>0</v>
       </c>
       <c r="O18" s="6">
         <v>0</v>
       </c>
       <c r="P18" s="6">
         <f t="shared" si="6"/>
-        <v>-420</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="6">
         <v>0</v>
@@ -26867,9 +26930,11 @@
       </c>
       <c r="S18" s="6">
         <f t="shared" si="7"/>
-        <v>-3727</v>
-      </c>
-      <c r="T18" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U18" s="4"/>
       <c r="V18" s="14">
         <f t="shared" si="8"/>
@@ -26912,21 +26977,21 @@
       </c>
       <c r="D19" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="E19" s="6">
         <v>0</v>
       </c>
       <c r="F19" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="G19" s="6">
         <v>0</v>
       </c>
       <c r="H19" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I19" s="6">
         <v>0</v>
@@ -26947,14 +27012,14 @@
       </c>
       <c r="N19" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O19" s="6">
         <v>0</v>
       </c>
       <c r="P19" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="6">
         <v>0</v>
@@ -26964,22 +27029,40 @@
       </c>
       <c r="S19" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T19" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="T19" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U19" s="17"/>
       <c r="V19" s="18">
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19"/>
-      <c r="Y19" s="19"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="19"/>
-      <c r="AB19" s="19"/>
-      <c r="AC19" s="19"/>
-      <c r="AD19" s="19"/>
+      <c r="W19" s="16">
+        <v>11636</v>
+      </c>
+      <c r="X19" s="16">
+        <v>14127</v>
+      </c>
+      <c r="Y19" s="16">
+        <v>9710</v>
+      </c>
+      <c r="Z19" s="16">
+        <v>10872</v>
+      </c>
+      <c r="AA19" s="16">
+        <v>1291</v>
+      </c>
+      <c r="AB19" s="16">
+        <v>4148</v>
+      </c>
+      <c r="AC19" s="16">
+        <v>420</v>
+      </c>
+      <c r="AD19" s="16">
+        <v>3727</v>
+      </c>
     </row>
     <row r="20" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
@@ -27047,20 +27130,38 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T20" s="6"/>
+      <c r="T20" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U20" s="4"/>
       <c r="V20" s="18">
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
-      <c r="Y20" s="15"/>
-      <c r="Z20" s="15"/>
-      <c r="AA20" s="15"/>
-      <c r="AB20" s="15"/>
-      <c r="AC20" s="15"/>
-      <c r="AD20" s="15"/>
+      <c r="W20" s="15">
+        <v>11849</v>
+      </c>
+      <c r="X20" s="15">
+        <v>14310</v>
+      </c>
+      <c r="Y20" s="15">
+        <v>9722</v>
+      </c>
+      <c r="Z20" s="15">
+        <v>10872</v>
+      </c>
+      <c r="AA20" s="15">
+        <v>1291</v>
+      </c>
+      <c r="AB20" s="15">
+        <v>4154</v>
+      </c>
+      <c r="AC20" s="15">
+        <v>421</v>
+      </c>
+      <c r="AD20" s="15">
+        <v>3732</v>
+      </c>
     </row>
     <row r="21" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
@@ -27074,49 +27175,49 @@
       </c>
       <c r="D21" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="E21" s="6">
         <v>0</v>
       </c>
       <c r="F21" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="G21" s="6">
         <v>0</v>
       </c>
       <c r="H21" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I21" s="6">
         <v>0</v>
       </c>
       <c r="J21" s="6">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K21" s="6">
         <v>0</v>
       </c>
       <c r="L21" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="6">
         <v>0</v>
       </c>
       <c r="N21" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O21" s="6">
         <v>0</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="6">
         <v>0</v>
@@ -27126,22 +27227,40 @@
       </c>
       <c r="S21" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T21" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="T21" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U21" s="4"/>
       <c r="V21" s="18">
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="W21" s="15"/>
-      <c r="X21" s="15"/>
-      <c r="Y21" s="15"/>
-      <c r="Z21" s="15"/>
-      <c r="AA21" s="15"/>
-      <c r="AB21" s="15"/>
-      <c r="AC21" s="15"/>
-      <c r="AD21" s="15"/>
+      <c r="W21" s="15">
+        <v>11849</v>
+      </c>
+      <c r="X21" s="15">
+        <v>14310</v>
+      </c>
+      <c r="Y21" s="15">
+        <v>9722</v>
+      </c>
+      <c r="Z21" s="15">
+        <v>10872</v>
+      </c>
+      <c r="AA21" s="15">
+        <v>1291</v>
+      </c>
+      <c r="AB21" s="15">
+        <v>4154</v>
+      </c>
+      <c r="AC21" s="15">
+        <v>421</v>
+      </c>
+      <c r="AD21" s="15">
+        <v>3732</v>
+      </c>
     </row>
     <row r="22" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
@@ -27209,20 +27328,38 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T22" s="6"/>
+      <c r="T22" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U22" s="4"/>
       <c r="V22" s="18">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="W22" s="15"/>
-      <c r="X22" s="15"/>
-      <c r="Y22" s="15"/>
-      <c r="Z22" s="15"/>
-      <c r="AA22" s="15"/>
-      <c r="AB22" s="15"/>
-      <c r="AC22" s="15"/>
-      <c r="AD22" s="15"/>
+      <c r="W22" s="15">
+        <v>11996</v>
+      </c>
+      <c r="X22" s="15">
+        <v>14442</v>
+      </c>
+      <c r="Y22" s="15">
+        <v>9731</v>
+      </c>
+      <c r="Z22" s="15">
+        <v>10878</v>
+      </c>
+      <c r="AA22" s="15">
+        <v>1292</v>
+      </c>
+      <c r="AB22" s="15">
+        <v>4171</v>
+      </c>
+      <c r="AC22" s="15">
+        <v>424</v>
+      </c>
+      <c r="AD22" s="15">
+        <v>3747</v>
+      </c>
     </row>
     <row r="23" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
@@ -27236,21 +27373,21 @@
       </c>
       <c r="D23" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="E23" s="6">
         <v>0</v>
       </c>
       <c r="F23" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="G23" s="6">
         <v>0</v>
       </c>
       <c r="H23" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I23" s="6">
         <v>0</v>
@@ -27271,7 +27408,7 @@
       </c>
       <c r="N23" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O23" s="6">
         <v>0</v>
@@ -27288,22 +27425,40 @@
       </c>
       <c r="S23" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T23" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="T23" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="U23" s="4"/>
       <c r="V23" s="18">
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="W23" s="15"/>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="15"/>
-      <c r="Z23" s="15"/>
-      <c r="AA23" s="15"/>
-      <c r="AB23" s="15"/>
-      <c r="AC23" s="15"/>
-      <c r="AD23" s="15"/>
+      <c r="W23" s="15">
+        <v>11996</v>
+      </c>
+      <c r="X23" s="15">
+        <v>14442</v>
+      </c>
+      <c r="Y23" s="15">
+        <v>9731</v>
+      </c>
+      <c r="Z23" s="15">
+        <v>10878</v>
+      </c>
+      <c r="AA23" s="15">
+        <v>1292</v>
+      </c>
+      <c r="AB23" s="15">
+        <v>4171</v>
+      </c>
+      <c r="AC23" s="15">
+        <v>424</v>
+      </c>
+      <c r="AD23" s="15">
+        <v>3747</v>
+      </c>
     </row>
     <row r="24" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
@@ -27317,21 +27472,21 @@
       </c>
       <c r="D24" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E24" s="6">
         <v>0</v>
       </c>
       <c r="F24" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="G24" s="6">
         <v>0</v>
       </c>
       <c r="H24" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" s="6">
         <v>0</v>
@@ -27352,7 +27507,7 @@
       </c>
       <c r="N24" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O24" s="6">
         <v>0</v>
@@ -27369,22 +27524,40 @@
       </c>
       <c r="S24" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T24" s="6"/>
+        <v>7</v>
+      </c>
+      <c r="T24" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="U24" s="4"/>
       <c r="V24" s="18">
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="W24" s="15"/>
-      <c r="X24" s="15"/>
-      <c r="Y24" s="15"/>
-      <c r="Z24" s="15"/>
-      <c r="AA24" s="15"/>
-      <c r="AB24" s="15"/>
-      <c r="AC24" s="15"/>
-      <c r="AD24" s="15"/>
+      <c r="W24" s="15">
+        <v>12048</v>
+      </c>
+      <c r="X24" s="15">
+        <v>14533</v>
+      </c>
+      <c r="Y24" s="15">
+        <v>9742</v>
+      </c>
+      <c r="Z24" s="15">
+        <v>10878</v>
+      </c>
+      <c r="AA24" s="15">
+        <v>1292</v>
+      </c>
+      <c r="AB24" s="15">
+        <v>4179</v>
+      </c>
+      <c r="AC24" s="15">
+        <v>424</v>
+      </c>
+      <c r="AD24" s="15">
+        <v>3755</v>
+      </c>
     </row>
     <row r="25" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
@@ -27398,21 +27571,21 @@
       </c>
       <c r="D25" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="E25" s="6">
         <v>0</v>
       </c>
       <c r="F25" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G25" s="6">
         <v>0</v>
       </c>
       <c r="H25" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I25" s="6">
         <v>0</v>
@@ -27433,7 +27606,7 @@
       </c>
       <c r="N25" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O25" s="6">
         <v>0</v>
@@ -27450,22 +27623,40 @@
       </c>
       <c r="S25" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T25" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="T25" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="U25" s="4"/>
       <c r="V25" s="18">
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15"/>
-      <c r="AA25" s="15"/>
-      <c r="AB25" s="15"/>
-      <c r="AC25" s="15"/>
-      <c r="AD25" s="15"/>
+      <c r="W25" s="15">
+        <v>12112</v>
+      </c>
+      <c r="X25" s="15">
+        <v>14590</v>
+      </c>
+      <c r="Y25" s="15">
+        <v>9745</v>
+      </c>
+      <c r="Z25" s="15">
+        <v>10878</v>
+      </c>
+      <c r="AA25" s="15">
+        <v>1292</v>
+      </c>
+      <c r="AB25" s="15">
+        <v>4187</v>
+      </c>
+      <c r="AC25" s="15">
+        <v>424</v>
+      </c>
+      <c r="AD25" s="15">
+        <v>3762</v>
+      </c>
     </row>
     <row r="26" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
@@ -27479,28 +27670,28 @@
       </c>
       <c r="D26" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="E26" s="6">
         <v>0</v>
       </c>
       <c r="F26" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G26" s="6">
         <v>0</v>
       </c>
       <c r="H26" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I26" s="6">
         <v>0</v>
       </c>
       <c r="J26" s="6">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K26" s="6">
         <v>0</v>
@@ -27514,14 +27705,14 @@
       </c>
       <c r="N26" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O26" s="6">
         <v>0</v>
       </c>
       <c r="P26" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="6">
         <v>0</v>
@@ -27531,22 +27722,40 @@
       </c>
       <c r="S26" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T26" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="T26" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="U26" s="4"/>
       <c r="V26" s="20">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="W26" s="21"/>
-      <c r="X26" s="21"/>
-      <c r="Y26" s="21"/>
-      <c r="Z26" s="21"/>
-      <c r="AA26" s="21"/>
-      <c r="AB26" s="21"/>
-      <c r="AC26" s="21"/>
-      <c r="AD26" s="21"/>
+      <c r="W26" s="21">
+        <v>12211</v>
+      </c>
+      <c r="X26" s="21">
+        <v>14729</v>
+      </c>
+      <c r="Y26" s="21">
+        <v>9749</v>
+      </c>
+      <c r="Z26" s="21">
+        <v>10878</v>
+      </c>
+      <c r="AA26" s="21">
+        <v>1292</v>
+      </c>
+      <c r="AB26" s="21">
+        <v>4193</v>
+      </c>
+      <c r="AC26" s="21">
+        <v>424</v>
+      </c>
+      <c r="AD26" s="21">
+        <v>3767</v>
+      </c>
     </row>
     <row r="27" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
@@ -27560,49 +27769,49 @@
       </c>
       <c r="D27" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-12288</v>
       </c>
       <c r="E27" s="6">
         <v>0</v>
       </c>
       <c r="F27" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-14831</v>
       </c>
       <c r="G27" s="6">
         <v>0</v>
       </c>
       <c r="H27" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9754</v>
       </c>
       <c r="I27" s="6">
         <v>0</v>
       </c>
       <c r="J27" s="6">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-10899</v>
       </c>
       <c r="K27" s="6">
         <v>0</v>
       </c>
       <c r="L27" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1292</v>
       </c>
       <c r="M27" s="6">
         <v>0</v>
       </c>
       <c r="N27" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4198</v>
       </c>
       <c r="O27" s="6">
         <v>0</v>
       </c>
       <c r="P27" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-426</v>
       </c>
       <c r="Q27" s="6">
         <v>0</v>
@@ -27612,22 +27821,40 @@
       </c>
       <c r="S27" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T27" s="6"/>
+        <v>-3771</v>
+      </c>
+      <c r="T27" s="6" t="s">
+        <v>95</v>
+      </c>
       <c r="U27" s="4"/>
       <c r="V27" s="18">
         <f t="shared" si="8"/>
         <v>25</v>
       </c>
-      <c r="W27" s="15"/>
-      <c r="X27" s="15"/>
-      <c r="Y27" s="15"/>
-      <c r="Z27" s="15"/>
-      <c r="AA27" s="15"/>
-      <c r="AB27" s="15"/>
-      <c r="AC27" s="15"/>
-      <c r="AD27" s="15"/>
+      <c r="W27" s="15">
+        <v>12288</v>
+      </c>
+      <c r="X27" s="15">
+        <v>14831</v>
+      </c>
+      <c r="Y27" s="15">
+        <v>9754</v>
+      </c>
+      <c r="Z27" s="15">
+        <v>10899</v>
+      </c>
+      <c r="AA27" s="15">
+        <v>1292</v>
+      </c>
+      <c r="AB27" s="15">
+        <v>4198</v>
+      </c>
+      <c r="AC27" s="15">
+        <v>426</v>
+      </c>
+      <c r="AD27" s="15">
+        <v>3771</v>
+      </c>
     </row>
     <row r="28" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
@@ -27695,7 +27922,9 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T28" s="6"/>
+      <c r="T28" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U28" s="4"/>
       <c r="V28" s="18">
         <f t="shared" si="8"/>
@@ -27710,7 +27939,7 @@
       <c r="AC28" s="15"/>
       <c r="AD28" s="15"/>
     </row>
-    <row r="29" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>45928</v>
       </c>
@@ -27776,7 +28005,9 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T29" s="6"/>
+      <c r="T29" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="U29" s="4"/>
       <c r="V29" s="18">
         <f t="shared" si="8"/>
@@ -27791,7 +28022,7 @@
       <c r="AC29" s="15"/>
       <c r="AD29" s="15"/>
     </row>
-    <row r="30" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>45929</v>
       </c>
@@ -27857,7 +28088,9 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T30" s="6"/>
+      <c r="T30" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="U30" s="4"/>
       <c r="V30" s="18">
         <f t="shared" si="8"/>
@@ -27872,7 +28105,7 @@
       <c r="AC30" s="15"/>
       <c r="AD30" s="15"/>
     </row>
-    <row r="31" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>45930</v>
       </c>
@@ -27938,7 +28171,9 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T31" s="6"/>
+      <c r="T31" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="U31" s="4"/>
       <c r="V31" s="18">
         <f t="shared" si="8"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241A61C7-30A2-4136-BAC1-BCC7A70E7D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE22020-18C8-41A5-B1E7-91201C284B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -1527,10 +1527,10 @@
         <v>41</v>
       </c>
       <c r="B10" s="41">
-        <v>0</v>
+        <v>43496.36</v>
       </c>
       <c r="C10" s="41">
-        <v>0</v>
+        <v>16134.03</v>
       </c>
       <c r="D10" s="41">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="N10" s="41">
-        <v>0</v>
+        <v>9005.64</v>
       </c>
       <c r="O10" s="41">
-        <v>0</v>
+        <v>4227.58</v>
       </c>
       <c r="P10" s="41">
         <v>0</v>
@@ -21961,21 +21961,21 @@
       </c>
       <c r="D2" s="13">
         <f t="shared" ref="D2:D32" si="0">W3-W2</f>
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="E2" s="6">
         <v>0</v>
       </c>
       <c r="F2" s="13">
         <f t="shared" ref="F2:F32" si="1">X3-X2</f>
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="G2" s="6">
         <v>0</v>
       </c>
       <c r="H2" s="13">
         <f t="shared" ref="H2:H32" si="2">Y3-Y2</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I2" s="6">
         <v>0</v>
@@ -21996,14 +21996,14 @@
       </c>
       <c r="N2" s="13">
         <f t="shared" ref="N2:N32" si="5">AB3-AB2</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O2" s="6">
         <v>0</v>
       </c>
       <c r="P2" s="13">
         <f t="shared" ref="P2:P32" si="6">AC3-AC2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="6">
         <v>0</v>
@@ -22013,21 +22013,37 @@
       </c>
       <c r="S2" s="13">
         <f t="shared" ref="S2:S32" si="7">AD3-AD2</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T2" s="6"/>
       <c r="U2" s="4"/>
       <c r="V2" s="8">
         <v>0</v>
       </c>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
+      <c r="W2" s="15">
+        <v>12443</v>
+      </c>
+      <c r="X2" s="15">
+        <v>15123</v>
+      </c>
+      <c r="Y2" s="15">
+        <v>9765</v>
+      </c>
+      <c r="Z2" s="15">
+        <v>10882</v>
+      </c>
+      <c r="AA2" s="15">
+        <v>1293</v>
+      </c>
+      <c r="AB2" s="15">
+        <v>4211</v>
+      </c>
+      <c r="AC2" s="15">
+        <v>427</v>
+      </c>
+      <c r="AD2" s="15">
+        <v>3783</v>
+      </c>
       <c r="AF2" s="10" t="s">
         <v>29</v>
       </c>
@@ -22048,49 +22064,49 @@
       </c>
       <c r="D3" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="E3" s="6">
         <v>0</v>
       </c>
       <c r="F3" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G3" s="6">
         <v>0</v>
       </c>
       <c r="H3" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I3" s="6">
         <v>0</v>
       </c>
       <c r="J3" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="6">
         <v>0</v>
       </c>
       <c r="L3" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="6">
         <v>0</v>
       </c>
       <c r="N3" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" s="6">
         <v>0</v>
       </c>
       <c r="P3" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="6">
         <v>0</v>
@@ -22100,21 +22116,37 @@
       </c>
       <c r="S3" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" s="6"/>
       <c r="U3" s="4"/>
       <c r="V3" s="12">
         <v>1</v>
       </c>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="13"/>
+      <c r="W3" s="13">
+        <v>12650</v>
+      </c>
+      <c r="X3" s="13">
+        <v>15396</v>
+      </c>
+      <c r="Y3" s="13">
+        <v>9775</v>
+      </c>
+      <c r="Z3" s="13">
+        <v>10882</v>
+      </c>
+      <c r="AA3" s="13">
+        <v>1293</v>
+      </c>
+      <c r="AB3" s="13">
+        <v>4227</v>
+      </c>
+      <c r="AC3" s="13">
+        <v>429</v>
+      </c>
+      <c r="AD3" s="13">
+        <v>3798</v>
+      </c>
     </row>
     <row r="4" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
@@ -22128,28 +22160,28 @@
       </c>
       <c r="D4" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="E4" s="6">
         <v>0</v>
       </c>
       <c r="F4" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
       </c>
       <c r="H4" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="6">
         <v>0</v>
       </c>
       <c r="J4" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="6">
         <v>0</v>
@@ -22163,7 +22195,7 @@
       </c>
       <c r="N4" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O4" s="6">
         <v>0</v>
@@ -22180,7 +22212,7 @@
       </c>
       <c r="S4" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T4" s="6"/>
       <c r="U4" s="4"/>
@@ -22188,14 +22220,30 @@
         <f t="shared" ref="V4:V32" si="8">V3+1</f>
         <v>2</v>
       </c>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
+      <c r="W4" s="6">
+        <v>12746</v>
+      </c>
+      <c r="X4" s="6">
+        <v>15464</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>9783</v>
+      </c>
+      <c r="Z4" s="6">
+        <v>10883</v>
+      </c>
+      <c r="AA4" s="6">
+        <v>1294</v>
+      </c>
+      <c r="AB4" s="6">
+        <v>4229</v>
+      </c>
+      <c r="AC4" s="6">
+        <v>431</v>
+      </c>
+      <c r="AD4" s="6">
+        <v>3799</v>
+      </c>
     </row>
     <row r="5" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
@@ -22209,49 +22257,49 @@
       </c>
       <c r="D5" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-12838</v>
       </c>
       <c r="E5" s="6">
         <v>0</v>
       </c>
       <c r="F5" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-15591</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
       </c>
       <c r="H5" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9784</v>
       </c>
       <c r="I5" s="6">
         <v>0</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-10884</v>
       </c>
       <c r="K5" s="6">
         <v>0</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1294</v>
       </c>
       <c r="M5" s="6">
         <v>0</v>
       </c>
       <c r="N5" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4299</v>
       </c>
       <c r="O5" s="6">
         <v>0</v>
       </c>
       <c r="P5" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-431</v>
       </c>
       <c r="Q5" s="6">
         <v>0</v>
@@ -22261,7 +22309,7 @@
       </c>
       <c r="S5" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3807</v>
       </c>
       <c r="T5" s="6"/>
       <c r="U5" s="4"/>
@@ -22269,14 +22317,30 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
+      <c r="W5" s="6">
+        <v>12838</v>
+      </c>
+      <c r="X5" s="6">
+        <v>15591</v>
+      </c>
+      <c r="Y5" s="6">
+        <v>9784</v>
+      </c>
+      <c r="Z5" s="6">
+        <v>10884</v>
+      </c>
+      <c r="AA5" s="6">
+        <v>1294</v>
+      </c>
+      <c r="AB5" s="6">
+        <v>4299</v>
+      </c>
+      <c r="AC5" s="6">
+        <v>431</v>
+      </c>
+      <c r="AD5" s="6">
+        <v>3807</v>
+      </c>
     </row>
     <row r="6" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
@@ -27691,7 +27755,7 @@
       </c>
       <c r="J26" s="6">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K26" s="6">
         <v>0</v>
@@ -27769,49 +27833,49 @@
       </c>
       <c r="D27" s="6">
         <f t="shared" si="0"/>
-        <v>-12288</v>
+        <v>89</v>
       </c>
       <c r="E27" s="6">
         <v>0</v>
       </c>
       <c r="F27" s="6">
         <f t="shared" si="1"/>
-        <v>-14831</v>
+        <v>119</v>
       </c>
       <c r="G27" s="6">
         <v>0</v>
       </c>
       <c r="H27" s="6">
         <f t="shared" si="2"/>
-        <v>-9754</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6">
         <v>0</v>
       </c>
       <c r="J27" s="6">
         <f t="shared" si="9"/>
-        <v>-10899</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6">
         <v>0</v>
       </c>
       <c r="L27" s="6">
         <f t="shared" si="4"/>
-        <v>-1292</v>
+        <v>1</v>
       </c>
       <c r="M27" s="6">
         <v>0</v>
       </c>
       <c r="N27" s="6">
         <f t="shared" si="5"/>
-        <v>-4198</v>
+        <v>2</v>
       </c>
       <c r="O27" s="6">
         <v>0</v>
       </c>
       <c r="P27" s="6">
         <f t="shared" si="6"/>
-        <v>-426</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="6">
         <v>0</v>
@@ -27821,7 +27885,7 @@
       </c>
       <c r="S27" s="6">
         <f t="shared" si="7"/>
-        <v>-3771</v>
+        <v>2</v>
       </c>
       <c r="T27" s="6" t="s">
         <v>95</v>
@@ -27841,7 +27905,7 @@
         <v>9754</v>
       </c>
       <c r="Z27" s="15">
-        <v>10899</v>
+        <v>10882</v>
       </c>
       <c r="AA27" s="15">
         <v>1292</v>
@@ -27930,14 +27994,30 @@
         <f t="shared" si="8"/>
         <v>26</v>
       </c>
-      <c r="W28" s="15"/>
-      <c r="X28" s="15"/>
-      <c r="Y28" s="15"/>
-      <c r="Z28" s="15"/>
-      <c r="AA28" s="15"/>
-      <c r="AB28" s="15"/>
-      <c r="AC28" s="15"/>
-      <c r="AD28" s="15"/>
+      <c r="W28" s="15">
+        <v>12377</v>
+      </c>
+      <c r="X28" s="15">
+        <v>14950</v>
+      </c>
+      <c r="Y28" s="15">
+        <v>9754</v>
+      </c>
+      <c r="Z28" s="15">
+        <v>10882</v>
+      </c>
+      <c r="AA28" s="15">
+        <v>1293</v>
+      </c>
+      <c r="AB28" s="15">
+        <v>4200</v>
+      </c>
+      <c r="AC28" s="15">
+        <v>427</v>
+      </c>
+      <c r="AD28" s="15">
+        <v>3773</v>
+      </c>
     </row>
     <row r="29" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
@@ -27951,21 +28031,21 @@
       </c>
       <c r="D29" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="E29" s="6">
         <v>0</v>
       </c>
       <c r="F29" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="G29" s="6">
         <v>0</v>
       </c>
       <c r="H29" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I29" s="6">
         <v>0</v>
@@ -27986,7 +28066,7 @@
       </c>
       <c r="N29" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O29" s="6">
         <v>0</v>
@@ -28003,7 +28083,7 @@
       </c>
       <c r="S29" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T29" s="6" t="s">
         <v>97</v>
@@ -28013,14 +28093,30 @@
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
-      <c r="W29" s="15"/>
-      <c r="X29" s="15"/>
-      <c r="Y29" s="15"/>
-      <c r="Z29" s="15"/>
-      <c r="AA29" s="15"/>
-      <c r="AB29" s="15"/>
-      <c r="AC29" s="15"/>
-      <c r="AD29" s="15"/>
+      <c r="W29" s="15">
+        <v>12377</v>
+      </c>
+      <c r="X29" s="15">
+        <v>14950</v>
+      </c>
+      <c r="Y29" s="15">
+        <v>9754</v>
+      </c>
+      <c r="Z29" s="15">
+        <v>10882</v>
+      </c>
+      <c r="AA29" s="15">
+        <v>1293</v>
+      </c>
+      <c r="AB29" s="15">
+        <v>4200</v>
+      </c>
+      <c r="AC29" s="15">
+        <v>427</v>
+      </c>
+      <c r="AD29" s="15">
+        <v>3773</v>
+      </c>
     </row>
     <row r="30" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
@@ -28096,14 +28192,30 @@
         <f t="shared" si="8"/>
         <v>28</v>
       </c>
-      <c r="W30" s="15"/>
-      <c r="X30" s="15"/>
-      <c r="Y30" s="15"/>
-      <c r="Z30" s="15"/>
-      <c r="AA30" s="15"/>
-      <c r="AB30" s="15"/>
-      <c r="AC30" s="15"/>
-      <c r="AD30" s="15"/>
+      <c r="W30" s="15">
+        <v>12443</v>
+      </c>
+      <c r="X30" s="15">
+        <v>15123</v>
+      </c>
+      <c r="Y30" s="15">
+        <v>9765</v>
+      </c>
+      <c r="Z30" s="15">
+        <v>10882</v>
+      </c>
+      <c r="AA30" s="15">
+        <v>1293</v>
+      </c>
+      <c r="AB30" s="15">
+        <v>4211</v>
+      </c>
+      <c r="AC30" s="15">
+        <v>427</v>
+      </c>
+      <c r="AD30" s="15">
+        <v>3783</v>
+      </c>
     </row>
     <row r="31" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
@@ -28179,14 +28291,30 @@
         <f t="shared" si="8"/>
         <v>29</v>
       </c>
-      <c r="W31" s="15"/>
-      <c r="X31" s="15"/>
-      <c r="Y31" s="15"/>
-      <c r="Z31" s="15"/>
-      <c r="AA31" s="15"/>
-      <c r="AB31" s="15"/>
-      <c r="AC31" s="15"/>
-      <c r="AD31" s="15"/>
+      <c r="W31" s="15">
+        <v>12443</v>
+      </c>
+      <c r="X31" s="15">
+        <v>15123</v>
+      </c>
+      <c r="Y31" s="15">
+        <v>9765</v>
+      </c>
+      <c r="Z31" s="15">
+        <v>10882</v>
+      </c>
+      <c r="AA31" s="15">
+        <v>1293</v>
+      </c>
+      <c r="AB31" s="15">
+        <v>4211</v>
+      </c>
+      <c r="AC31" s="15">
+        <v>427</v>
+      </c>
+      <c r="AD31" s="15">
+        <v>3783</v>
+      </c>
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B32" s="27"/>
@@ -28205,14 +28333,30 @@
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-      <c r="W32" s="15"/>
-      <c r="X32" s="15"/>
-      <c r="Y32" s="15"/>
-      <c r="Z32" s="15"/>
-      <c r="AA32" s="15"/>
-      <c r="AB32" s="15"/>
-      <c r="AC32" s="15"/>
-      <c r="AD32" s="15"/>
+      <c r="W32" s="15">
+        <v>12443</v>
+      </c>
+      <c r="X32" s="15">
+        <v>15123</v>
+      </c>
+      <c r="Y32" s="15">
+        <v>9765</v>
+      </c>
+      <c r="Z32" s="15">
+        <v>10882</v>
+      </c>
+      <c r="AA32" s="15">
+        <v>1293</v>
+      </c>
+      <c r="AB32" s="15">
+        <v>4211</v>
+      </c>
+      <c r="AC32" s="15">
+        <v>427</v>
+      </c>
+      <c r="AD32" s="15">
+        <v>3783</v>
+      </c>
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE22020-18C8-41A5-B1E7-91201C284B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4A23A3-1BA8-4DD9-90B2-F1369A8CE8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -22195,7 +22195,7 @@
       </c>
       <c r="N4" s="13">
         <f t="shared" si="5"/>
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="O4" s="6">
         <v>0</v>
@@ -22257,49 +22257,49 @@
       </c>
       <c r="D5" s="13">
         <f t="shared" si="0"/>
-        <v>-12838</v>
+        <v>44</v>
       </c>
       <c r="E5" s="6">
         <v>0</v>
       </c>
       <c r="F5" s="13">
         <f t="shared" si="1"/>
-        <v>-15591</v>
+        <v>36</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
       </c>
       <c r="H5" s="13">
         <f t="shared" si="2"/>
-        <v>-9784</v>
+        <v>6</v>
       </c>
       <c r="I5" s="6">
         <v>0</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" si="3"/>
-        <v>-10884</v>
+        <v>0</v>
       </c>
       <c r="K5" s="6">
         <v>0</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="4"/>
-        <v>-1294</v>
+        <v>0</v>
       </c>
       <c r="M5" s="6">
         <v>0</v>
       </c>
       <c r="N5" s="13">
         <f t="shared" si="5"/>
-        <v>-4299</v>
+        <v>15</v>
       </c>
       <c r="O5" s="6">
         <v>0</v>
       </c>
       <c r="P5" s="13">
         <f t="shared" si="6"/>
-        <v>-431</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="6">
         <v>0</v>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="S5" s="13">
         <f t="shared" si="7"/>
-        <v>-3807</v>
+        <v>5</v>
       </c>
       <c r="T5" s="6"/>
       <c r="U5" s="4"/>
@@ -22333,7 +22333,7 @@
         <v>1294</v>
       </c>
       <c r="AB5" s="6">
-        <v>4299</v>
+        <v>4229</v>
       </c>
       <c r="AC5" s="6">
         <v>431</v>
@@ -22354,28 +22354,28 @@
       </c>
       <c r="D6" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E6" s="6">
         <v>0</v>
       </c>
       <c r="F6" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
       </c>
       <c r="H6" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I6" s="6">
         <v>0</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" s="6">
         <v>0</v>
@@ -22389,7 +22389,7 @@
       </c>
       <c r="N6" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O6" s="6">
         <v>0</v>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="S6" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" s="6"/>
       <c r="U6" s="4"/>
@@ -22414,14 +22414,30 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
-      <c r="AB6" s="6"/>
-      <c r="AC6" s="6"/>
-      <c r="AD6" s="6"/>
+      <c r="W6" s="6">
+        <v>12882</v>
+      </c>
+      <c r="X6" s="6">
+        <v>15627</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>9790</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>10884</v>
+      </c>
+      <c r="AA6" s="6">
+        <v>1294</v>
+      </c>
+      <c r="AB6" s="6">
+        <v>4244</v>
+      </c>
+      <c r="AC6" s="6">
+        <v>431</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>3812</v>
+      </c>
     </row>
     <row r="7" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
@@ -22435,21 +22451,21 @@
       </c>
       <c r="D7" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E7" s="6">
         <v>0</v>
       </c>
       <c r="F7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G7" s="6">
         <v>0</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I7" s="6">
         <v>0</v>
@@ -22495,14 +22511,30 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="6"/>
+      <c r="W7" s="6">
+        <v>12912</v>
+      </c>
+      <c r="X7" s="6">
+        <v>15725</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>9796</v>
+      </c>
+      <c r="Z7" s="6">
+        <v>10886</v>
+      </c>
+      <c r="AA7" s="6">
+        <v>1294</v>
+      </c>
+      <c r="AB7" s="6">
+        <v>4247</v>
+      </c>
+      <c r="AC7" s="6">
+        <v>431</v>
+      </c>
+      <c r="AD7" s="6">
+        <v>3815</v>
+      </c>
     </row>
     <row r="8" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
@@ -22516,49 +22548,49 @@
       </c>
       <c r="D8" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-12945</v>
       </c>
       <c r="E8" s="6">
         <v>0</v>
       </c>
       <c r="F8" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-15795</v>
       </c>
       <c r="G8" s="6">
         <v>0</v>
       </c>
       <c r="H8" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9801</v>
       </c>
       <c r="I8" s="6">
         <v>0</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-10886</v>
       </c>
       <c r="K8" s="6">
         <v>0</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1294</v>
       </c>
       <c r="M8" s="6">
         <v>0</v>
       </c>
       <c r="N8" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4247</v>
       </c>
       <c r="O8" s="6">
         <v>0</v>
       </c>
       <c r="P8" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-431</v>
       </c>
       <c r="Q8" s="6">
         <v>0</v>
@@ -22568,7 +22600,7 @@
       </c>
       <c r="S8" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3815</v>
       </c>
       <c r="T8" s="6"/>
       <c r="U8" s="4"/>
@@ -22576,14 +22608,30 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
+      <c r="W8" s="6">
+        <v>12945</v>
+      </c>
+      <c r="X8" s="6">
+        <v>15795</v>
+      </c>
+      <c r="Y8" s="6">
+        <v>9801</v>
+      </c>
+      <c r="Z8" s="6">
+        <v>10886</v>
+      </c>
+      <c r="AA8" s="6">
+        <v>1294</v>
+      </c>
+      <c r="AB8" s="6">
+        <v>4247</v>
+      </c>
+      <c r="AC8" s="6">
+        <v>431</v>
+      </c>
+      <c r="AD8" s="6">
+        <v>3815</v>
+      </c>
     </row>
     <row r="9" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
@@ -25200,7 +25248,7 @@
     <mergeCell ref="A80:I80"/>
     <mergeCell ref="A88:I88"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A89" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Bandeira,Verde,Amarela,Vermelha p1,Vermelha p2"</formula1>
       <formula2>0</formula2>
@@ -25210,7 +25258,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000000000000}">
           <x14:formula1>
             <xm:f>Planilha1!$A$2:$A$5</xm:f>
@@ -28031,21 +28079,21 @@
       </c>
       <c r="D29" s="6">
         <f t="shared" si="0"/>
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="E29" s="6">
         <v>0</v>
       </c>
       <c r="F29" s="6">
         <f t="shared" si="1"/>
-        <v>173</v>
+        <v>128</v>
       </c>
       <c r="G29" s="6">
         <v>0</v>
       </c>
       <c r="H29" s="6">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I29" s="6">
         <v>0</v>
@@ -28066,7 +28114,7 @@
       </c>
       <c r="N29" s="6">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O29" s="6">
         <v>0</v>
@@ -28083,7 +28131,7 @@
       </c>
       <c r="S29" s="6">
         <f t="shared" si="7"/>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T29" s="6" t="s">
         <v>97</v>
@@ -28130,21 +28178,21 @@
       </c>
       <c r="D30" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E30" s="6">
         <v>0</v>
       </c>
       <c r="F30" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="G30" s="6">
         <v>0</v>
       </c>
       <c r="H30" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I30" s="6">
         <v>0</v>
@@ -28165,7 +28213,7 @@
       </c>
       <c r="N30" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O30" s="6">
         <v>0</v>
@@ -28182,7 +28230,7 @@
       </c>
       <c r="S30" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T30" s="6" t="s">
         <v>98</v>
@@ -28193,13 +28241,13 @@
         <v>28</v>
       </c>
       <c r="W30" s="15">
-        <v>12443</v>
+        <v>12421</v>
       </c>
       <c r="X30" s="15">
-        <v>15123</v>
+        <v>15078</v>
       </c>
       <c r="Y30" s="15">
-        <v>9765</v>
+        <v>9763</v>
       </c>
       <c r="Z30" s="15">
         <v>10882</v>
@@ -28208,13 +28256,13 @@
         <v>1293</v>
       </c>
       <c r="AB30" s="15">
-        <v>4211</v>
+        <v>4204</v>
       </c>
       <c r="AC30" s="15">
         <v>427</v>
       </c>
       <c r="AD30" s="15">
-        <v>3783</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
@@ -28229,21 +28277,21 @@
       </c>
       <c r="D31" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="E31" s="6">
         <v>0</v>
       </c>
       <c r="F31" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="G31" s="6">
         <v>0</v>
       </c>
       <c r="H31" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I31" s="6">
         <v>0</v>
@@ -28264,14 +28312,14 @@
       </c>
       <c r="N31" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O31" s="6">
         <v>0</v>
       </c>
       <c r="P31" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="6">
         <v>0</v>
@@ -28281,7 +28329,7 @@
       </c>
       <c r="S31" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>98</v>
@@ -28292,13 +28340,13 @@
         <v>29</v>
       </c>
       <c r="W31" s="15">
-        <v>12443</v>
+        <v>12469</v>
       </c>
       <c r="X31" s="15">
-        <v>15123</v>
+        <v>15201</v>
       </c>
       <c r="Y31" s="15">
-        <v>9765</v>
+        <v>9772</v>
       </c>
       <c r="Z31" s="15">
         <v>10882</v>
@@ -28307,13 +28355,13 @@
         <v>1293</v>
       </c>
       <c r="AB31" s="15">
-        <v>4211</v>
+        <v>4216</v>
       </c>
       <c r="AC31" s="15">
         <v>427</v>
       </c>
       <c r="AD31" s="15">
-        <v>3783</v>
+        <v>3788</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
@@ -28334,13 +28382,13 @@
         <v>30</v>
       </c>
       <c r="W32" s="15">
-        <v>12443</v>
+        <v>12571</v>
       </c>
       <c r="X32" s="15">
-        <v>15123</v>
+        <v>15310</v>
       </c>
       <c r="Y32" s="15">
-        <v>9765</v>
+        <v>9775</v>
       </c>
       <c r="Z32" s="15">
         <v>10882</v>
@@ -28349,13 +28397,13 @@
         <v>1293</v>
       </c>
       <c r="AB32" s="15">
-        <v>4211</v>
+        <v>4222</v>
       </c>
       <c r="AC32" s="15">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AD32" s="15">
-        <v>3783</v>
+        <v>3793</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4A23A3-1BA8-4DD9-90B2-F1369A8CE8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6ECDF6-0948-47E9-8D0E-C1A225C1DB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -25394,11 +25394,11 @@
       <c r="A2" s="5">
         <v>45901</v>
       </c>
-      <c r="B2" s="6">
-        <v>0</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0</v>
+      <c r="B2" s="7">
+        <v>1593.8579995099997</v>
+      </c>
+      <c r="C2" s="7">
+        <v>249.64799989000002</v>
       </c>
       <c r="D2" s="6">
         <f t="shared" ref="D2:D31" si="0">W3-W2</f>
@@ -25435,15 +25435,14 @@
       <c r="M2" s="6">
         <v>0</v>
       </c>
-      <c r="N2" s="6">
-        <f t="shared" ref="N2:N31" si="5">AB3-AB2</f>
-        <v>5</v>
-      </c>
-      <c r="O2" s="6">
-        <v>0</v>
+      <c r="N2" s="7">
+        <v>264.67199936999987</v>
+      </c>
+      <c r="O2" s="7">
+        <v>59.903999919999997</v>
       </c>
       <c r="P2" s="6">
-        <f t="shared" ref="P2:P31" si="6">AC3-AC2</f>
+        <f t="shared" ref="P2:P31" si="5">AC3-AC2</f>
         <v>0</v>
       </c>
       <c r="Q2" s="6">
@@ -25453,7 +25452,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="6">
-        <f t="shared" ref="S2:S31" si="7">AD3-AD2</f>
+        <f t="shared" ref="S2:S31" si="6">AD3-AD2</f>
         <v>0</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -25499,11 +25498,11 @@
       <c r="A3" s="5">
         <v>45902</v>
       </c>
-      <c r="B3" s="6">
-        <v>0</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0</v>
+      <c r="B3" s="7">
+        <v>1671.3899995100005</v>
+      </c>
+      <c r="C3" s="7">
+        <v>242.50799992</v>
       </c>
       <c r="D3" s="6">
         <f t="shared" si="0"/>
@@ -25540,25 +25539,24 @@
       <c r="M3" s="6">
         <v>0</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="7">
+        <v>273.28799932000004</v>
+      </c>
+      <c r="O3" s="7">
+        <v>57.191999889999998</v>
+      </c>
+      <c r="P3" s="6">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
-      </c>
-      <c r="P3" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>0</v>
+      </c>
+      <c r="R3" s="6">
+        <v>0</v>
+      </c>
+      <c r="S3" s="6">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>0</v>
-      </c>
-      <c r="R3" s="6">
-        <v>0</v>
-      </c>
-      <c r="S3" s="6">
-        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -25597,11 +25595,11 @@
       <c r="A4" s="5">
         <v>45903</v>
       </c>
-      <c r="B4" s="6">
-        <v>0</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0</v>
+      <c r="B4" s="7">
+        <v>1606.1639995499993</v>
+      </c>
+      <c r="C4" s="7">
+        <v>218.35799990000001</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" si="0"/>
@@ -25638,25 +25636,24 @@
       <c r="M4" s="6">
         <v>0</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="7">
+        <v>253.77599939999993</v>
+      </c>
+      <c r="O4" s="7">
+        <v>51.263999930000004</v>
+      </c>
+      <c r="P4" s="6">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6">
-        <v>0</v>
-      </c>
-      <c r="S4" s="6">
-        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -25664,7 +25661,7 @@
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="14">
-        <f t="shared" ref="V4:V32" si="8">V3+1</f>
+        <f t="shared" ref="V4:V32" si="7">V3+1</f>
         <v>2</v>
       </c>
       <c r="W4" s="6">
@@ -25696,11 +25693,11 @@
       <c r="A5" s="5">
         <v>45904</v>
       </c>
-      <c r="B5" s="6">
-        <v>0</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0</v>
+      <c r="B5" s="7">
+        <v>1491.0839995099998</v>
+      </c>
+      <c r="C5" s="7">
+        <v>224.90999993</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="0"/>
@@ -25737,25 +25734,24 @@
       <c r="M5" s="6">
         <v>0</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="7">
+        <v>287.20799941000007</v>
+      </c>
+      <c r="O5" s="7">
+        <v>59.927999880000002</v>
+      </c>
+      <c r="P5" s="6">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6">
+        <v>0</v>
+      </c>
+      <c r="S5" s="6">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6">
-        <v>0</v>
-      </c>
-      <c r="S5" s="6">
-        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -25763,7 +25759,7 @@
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="W5" s="6">
@@ -25795,11 +25791,11 @@
       <c r="A6" s="5">
         <v>45905</v>
       </c>
-      <c r="B6" s="6">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0</v>
+      <c r="B6" s="7">
+        <v>1345.0079994299995</v>
+      </c>
+      <c r="C6" s="7">
+        <v>223.81799995</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" si="0"/>
@@ -25836,25 +25832,24 @@
       <c r="M6" s="6">
         <v>0</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="7">
+        <v>299.56799928999999</v>
+      </c>
+      <c r="O6" s="7">
+        <v>68.375999889999989</v>
+      </c>
+      <c r="P6" s="6">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6">
-        <v>0</v>
-      </c>
-      <c r="S6" s="6">
-        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -25862,7 +25857,7 @@
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="W6" s="6">
@@ -25894,11 +25889,11 @@
       <c r="A7" s="5">
         <v>45906</v>
       </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
+      <c r="B7" s="7">
+        <v>1190.3219994899998</v>
+      </c>
+      <c r="C7" s="7">
+        <v>206.59799988999998</v>
       </c>
       <c r="D7" s="6">
         <f t="shared" si="0"/>
@@ -25935,25 +25930,24 @@
       <c r="M7" s="6">
         <v>0</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="7">
+        <v>345.6239993099997</v>
+      </c>
+      <c r="O7" s="7">
+        <v>74.303999909999987</v>
+      </c>
+      <c r="P7" s="6">
         <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>0</v>
+      </c>
+      <c r="R7" s="6">
+        <v>0</v>
+      </c>
+      <c r="S7" s="6">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6">
-        <v>0</v>
-      </c>
-      <c r="S7" s="6">
-        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -25961,7 +25955,7 @@
       </c>
       <c r="U7" s="4"/>
       <c r="V7" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="W7" s="6">
@@ -25993,11 +25987,11 @@
       <c r="A8" s="5">
         <v>45907</v>
       </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0</v>
+      <c r="B8" s="7">
+        <v>1284.4859995599995</v>
+      </c>
+      <c r="C8" s="7">
+        <v>230.15999994999999</v>
       </c>
       <c r="D8" s="6">
         <f t="shared" si="0"/>
@@ -26034,25 +26028,24 @@
       <c r="M8" s="6">
         <v>0</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="7">
+        <v>368.15999933999984</v>
+      </c>
+      <c r="O8" s="7">
+        <v>63.815999930000011</v>
+      </c>
+      <c r="P8" s="6">
         <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>0</v>
+      </c>
+      <c r="R8" s="6">
+        <v>0</v>
+      </c>
+      <c r="S8" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6">
-        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -26060,7 +26053,7 @@
       </c>
       <c r="U8" s="4"/>
       <c r="V8" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="W8" s="6">
@@ -26092,11 +26085,11 @@
       <c r="A9" s="5">
         <v>45908</v>
       </c>
-      <c r="B9" s="6">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0</v>
+      <c r="B9" s="7">
+        <v>1645.8539995100002</v>
+      </c>
+      <c r="C9" s="7">
+        <v>242.92799993</v>
       </c>
       <c r="D9" s="6">
         <f t="shared" si="0"/>
@@ -26133,25 +26126,24 @@
       <c r="M9" s="6">
         <v>0</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="7">
+        <v>341.30399937000004</v>
+      </c>
+      <c r="O9" s="7">
+        <v>63.215999880000005</v>
+      </c>
+      <c r="P9" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>0</v>
+      </c>
+      <c r="R9" s="6">
+        <v>0</v>
+      </c>
+      <c r="S9" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>0</v>
-      </c>
-      <c r="R9" s="6">
-        <v>0</v>
-      </c>
-      <c r="S9" s="6">
-        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -26159,7 +26151,7 @@
       </c>
       <c r="U9" s="4"/>
       <c r="V9" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="W9" s="6">
@@ -26191,11 +26183,11 @@
       <c r="A10" s="5">
         <v>45909</v>
       </c>
-      <c r="B10" s="6">
-        <v>0</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0</v>
+      <c r="B10" s="7">
+        <v>2031.665999439999</v>
+      </c>
+      <c r="C10" s="7">
+        <v>319.91399990999997</v>
       </c>
       <c r="D10" s="6">
         <f t="shared" si="0"/>
@@ -26232,25 +26224,24 @@
       <c r="M10" s="6">
         <v>0</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="7">
+        <v>331.72799933999988</v>
+      </c>
+      <c r="O10" s="7">
+        <v>68.399999919999985</v>
+      </c>
+      <c r="P10" s="6">
         <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="O10" s="6">
-        <v>0</v>
-      </c>
-      <c r="P10" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>0</v>
+      </c>
+      <c r="R10" s="6">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>0</v>
-      </c>
-      <c r="R10" s="6">
-        <v>0</v>
-      </c>
-      <c r="S10" s="6">
-        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="T10" s="6" t="s">
@@ -26258,7 +26249,7 @@
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="W10" s="6">
@@ -26290,11 +26281,11 @@
       <c r="A11" s="5">
         <v>45910</v>
       </c>
-      <c r="B11" s="6">
-        <v>0</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0</v>
+      <c r="B11" s="7">
+        <v>2039.5199995099993</v>
+      </c>
+      <c r="C11" s="7">
+        <v>273.16799993000001</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" si="0"/>
@@ -26331,25 +26322,24 @@
       <c r="M11" s="6">
         <v>0</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="7">
+        <v>304.91999933000005</v>
+      </c>
+      <c r="O11" s="7">
+        <v>64.463999880000003</v>
+      </c>
+      <c r="P11" s="6">
         <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="O11" s="6">
-        <v>0</v>
-      </c>
-      <c r="P11" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>0</v>
+      </c>
+      <c r="R11" s="6">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>0</v>
-      </c>
-      <c r="R11" s="6">
-        <v>0</v>
-      </c>
-      <c r="S11" s="6">
-        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="T11" s="6" t="s">
@@ -26357,7 +26347,7 @@
       </c>
       <c r="U11" s="4"/>
       <c r="V11" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="W11" s="15">
@@ -26389,11 +26379,11 @@
       <c r="A12" s="5">
         <v>45911</v>
       </c>
-      <c r="B12" s="6">
-        <v>0</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0</v>
+      <c r="B12" s="7">
+        <v>2072.6999994100011</v>
+      </c>
+      <c r="C12" s="7">
+        <v>308.19599991000001</v>
       </c>
       <c r="D12" s="6">
         <f t="shared" si="0"/>
@@ -26430,25 +26420,24 @@
       <c r="M12" s="6">
         <v>0</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="7">
+        <v>337.75199938999981</v>
+      </c>
+      <c r="O12" s="7">
+        <v>71.423999910000006</v>
+      </c>
+      <c r="P12" s="6">
         <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6">
+        <v>0</v>
+      </c>
+      <c r="S12" s="6">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>0</v>
-      </c>
-      <c r="R12" s="6">
-        <v>0</v>
-      </c>
-      <c r="S12" s="6">
-        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="T12" s="6" t="s">
@@ -26456,7 +26445,7 @@
       </c>
       <c r="U12" s="4"/>
       <c r="V12" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="W12" s="6">
@@ -26488,11 +26477,11 @@
       <c r="A13" s="5">
         <v>45912</v>
       </c>
-      <c r="B13" s="6">
-        <v>0</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0</v>
+      <c r="B13" s="7">
+        <v>1604.3159994499999</v>
+      </c>
+      <c r="C13" s="7">
+        <v>236.20799994999999</v>
       </c>
       <c r="D13" s="6">
         <f t="shared" si="0"/>
@@ -26529,25 +26518,24 @@
       <c r="M13" s="6">
         <v>0</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="7">
+        <v>385.96799933000017</v>
+      </c>
+      <c r="O13" s="7">
+        <v>81.479999890000002</v>
+      </c>
+      <c r="P13" s="6">
         <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="O13" s="6">
-        <v>0</v>
-      </c>
-      <c r="P13" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6">
+        <v>0</v>
+      </c>
+      <c r="S13" s="6">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>0</v>
-      </c>
-      <c r="R13" s="6">
-        <v>0</v>
-      </c>
-      <c r="S13" s="6">
-        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -26555,7 +26543,7 @@
       </c>
       <c r="U13" s="4"/>
       <c r="V13" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="W13" s="15">
@@ -26587,11 +26575,11 @@
       <c r="A14" s="5">
         <v>45913</v>
       </c>
-      <c r="B14" s="6">
-        <v>0</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0</v>
+      <c r="B14" s="7">
+        <v>1223.7539994899998</v>
+      </c>
+      <c r="C14" s="7">
+        <v>202.43999993</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" si="0"/>
@@ -26628,25 +26616,24 @@
       <c r="M14" s="6">
         <v>0</v>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="7">
+        <v>367.96799933000028</v>
+      </c>
+      <c r="O14" s="7">
+        <v>73.631999899999997</v>
+      </c>
+      <c r="P14" s="6">
         <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="O14" s="6">
-        <v>0</v>
-      </c>
-      <c r="P14" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>0</v>
+      </c>
+      <c r="R14" s="6">
+        <v>0</v>
+      </c>
+      <c r="S14" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>0</v>
-      </c>
-      <c r="R14" s="6">
-        <v>0</v>
-      </c>
-      <c r="S14" s="6">
-        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="T14" s="6" t="s">
@@ -26654,7 +26641,7 @@
       </c>
       <c r="U14" s="4"/>
       <c r="V14" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="W14" s="6">
@@ -26686,11 +26673,11 @@
       <c r="A15" s="5">
         <v>45914</v>
       </c>
-      <c r="B15" s="6">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0</v>
+      <c r="B15" s="7">
+        <v>1271.9699995100004</v>
+      </c>
+      <c r="C15" s="7">
+        <v>223.60799988000005</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="0"/>
@@ -26726,25 +26713,24 @@
       <c r="M15" s="6">
         <v>0</v>
       </c>
-      <c r="N15" s="6">
+      <c r="N15" s="7">
+        <v>400.39199936999995</v>
+      </c>
+      <c r="O15" s="7">
+        <v>87.527999910000005</v>
+      </c>
+      <c r="P15" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="O15" s="6">
-        <v>0</v>
-      </c>
-      <c r="P15" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6">
+        <v>0</v>
+      </c>
+      <c r="S15" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6">
-        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="T15" s="6" t="s">
@@ -26752,7 +26738,7 @@
       </c>
       <c r="U15" s="4"/>
       <c r="V15" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="W15" s="6">
@@ -26784,11 +26770,11 @@
       <c r="A16" s="5">
         <v>45915</v>
       </c>
-      <c r="B16" s="6">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0</v>
+      <c r="B16" s="7">
+        <v>1955.8559994400002</v>
+      </c>
+      <c r="C16" s="7">
+        <v>270.10199994999999</v>
       </c>
       <c r="D16" s="6">
         <f t="shared" si="0"/>
@@ -26812,7 +26798,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="6">
-        <f t="shared" ref="J16:J31" si="9">Z17-Z16</f>
+        <f t="shared" ref="J16:J31" si="8">Z17-Z16</f>
         <v>1</v>
       </c>
       <c r="K16" s="6">
@@ -26825,25 +26811,24 @@
       <c r="M16" s="6">
         <v>0</v>
       </c>
-      <c r="N16" s="6">
+      <c r="N16" s="7">
+        <v>406.27199932000008</v>
+      </c>
+      <c r="O16" s="7">
+        <v>77.615999909999999</v>
+      </c>
+      <c r="P16" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="O16" s="6">
-        <v>0</v>
-      </c>
-      <c r="P16" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6">
+        <v>0</v>
+      </c>
+      <c r="S16" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6">
-        <v>0</v>
-      </c>
-      <c r="S16" s="6">
-        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="T16" s="6" t="s">
@@ -26851,7 +26836,7 @@
       </c>
       <c r="U16" s="4"/>
       <c r="V16" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="W16" s="16">
@@ -26883,11 +26868,11 @@
       <c r="A17" s="5">
         <v>45916</v>
       </c>
-      <c r="B17" s="6">
-        <v>0</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0</v>
+      <c r="B17" s="7">
+        <v>2078.3699994699996</v>
+      </c>
+      <c r="C17" s="7">
+        <v>285.47399987999995</v>
       </c>
       <c r="D17" s="6">
         <f t="shared" si="0"/>
@@ -26911,7 +26896,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K17" s="6">
@@ -26924,25 +26909,24 @@
       <c r="M17" s="6">
         <v>0</v>
       </c>
-      <c r="N17" s="6">
+      <c r="N17" s="7">
+        <v>405.19199943000001</v>
+      </c>
+      <c r="O17" s="7">
+        <v>81.239999889999993</v>
+      </c>
+      <c r="P17" s="6">
         <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="O17" s="6">
-        <v>0</v>
-      </c>
-      <c r="P17" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6">
+        <v>0</v>
+      </c>
+      <c r="S17" s="6">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q17" s="6">
-        <v>0</v>
-      </c>
-      <c r="R17" s="6">
-        <v>0</v>
-      </c>
-      <c r="S17" s="6">
-        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="T17" s="6" t="s">
@@ -26950,7 +26934,7 @@
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="W17" s="16">
@@ -26982,11 +26966,11 @@
       <c r="A18" s="5">
         <v>45917</v>
       </c>
-      <c r="B18" s="6">
-        <v>0</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0</v>
+      <c r="B18" s="7">
+        <v>2110.3319994599983</v>
+      </c>
+      <c r="C18" s="7">
+        <v>284.63399989999999</v>
       </c>
       <c r="D18" s="6">
         <f t="shared" si="0"/>
@@ -27010,7 +26994,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K18" s="6">
@@ -27023,25 +27007,24 @@
       <c r="M18" s="6">
         <v>0</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N18" s="7">
+        <v>423.69599936999987</v>
+      </c>
+      <c r="O18" s="7">
+        <v>76.799999909999997</v>
+      </c>
+      <c r="P18" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O18" s="6">
-        <v>0</v>
-      </c>
-      <c r="P18" s="6">
+      <c r="Q18" s="6">
+        <v>0</v>
+      </c>
+      <c r="R18" s="6">
+        <v>0</v>
+      </c>
+      <c r="S18" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6">
-        <v>0</v>
-      </c>
-      <c r="R18" s="6">
-        <v>0</v>
-      </c>
-      <c r="S18" s="6">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T18" s="6" t="s">
@@ -27049,7 +27032,7 @@
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="W18" s="16">
@@ -27081,11 +27064,11 @@
       <c r="A19" s="5">
         <v>45918</v>
       </c>
-      <c r="B19" s="6">
-        <v>0</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0</v>
+      <c r="B19" s="7">
+        <v>2201.1779994800008</v>
+      </c>
+      <c r="C19" s="7">
+        <v>305.33999990999996</v>
       </c>
       <c r="D19" s="6">
         <f t="shared" si="0"/>
@@ -27109,7 +27092,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K19" s="6">
@@ -27122,25 +27105,24 @@
       <c r="M19" s="6">
         <v>0</v>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="7">
+        <v>403.96799934999984</v>
+      </c>
+      <c r="O19" s="7">
+        <v>72.023999910000001</v>
+      </c>
+      <c r="P19" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="O19" s="6">
-        <v>0</v>
-      </c>
-      <c r="P19" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6">
-        <v>0</v>
-      </c>
-      <c r="S19" s="6">
-        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="T19" s="6" t="s">
@@ -27148,7 +27130,7 @@
       </c>
       <c r="U19" s="17"/>
       <c r="V19" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="W19" s="16">
@@ -27180,11 +27162,11 @@
       <c r="A20" s="5">
         <v>45919</v>
       </c>
-      <c r="B20" s="6">
-        <v>0</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0</v>
+      <c r="B20" s="7">
+        <v>1709.8619994600003</v>
+      </c>
+      <c r="C20" s="7">
+        <v>238.34999991000001</v>
       </c>
       <c r="D20" s="6">
         <f t="shared" si="0"/>
@@ -27208,7 +27190,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K20" s="6">
@@ -27221,25 +27203,24 @@
       <c r="M20" s="6">
         <v>0</v>
       </c>
-      <c r="N20" s="6">
+      <c r="N20" s="7">
+        <v>389.75999933999992</v>
+      </c>
+      <c r="O20" s="7">
+        <v>51.623999920000003</v>
+      </c>
+      <c r="P20" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O20" s="6">
-        <v>0</v>
-      </c>
-      <c r="P20" s="6">
+      <c r="Q20" s="6">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6">
+        <v>0</v>
+      </c>
+      <c r="S20" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="6">
-        <v>0</v>
-      </c>
-      <c r="R20" s="6">
-        <v>0</v>
-      </c>
-      <c r="S20" s="6">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -27247,7 +27228,7 @@
       </c>
       <c r="U20" s="4"/>
       <c r="V20" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="W20" s="15">
@@ -27279,11 +27260,11 @@
       <c r="A21" s="5">
         <v>45920</v>
       </c>
-      <c r="B21" s="6">
-        <v>0</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0</v>
+      <c r="B21" s="7">
+        <v>1339.2119994400002</v>
+      </c>
+      <c r="C21" s="7">
+        <v>219.91199994000002</v>
       </c>
       <c r="D21" s="6">
         <f t="shared" si="0"/>
@@ -27307,7 +27288,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="K21" s="6">
@@ -27320,25 +27301,24 @@
       <c r="M21" s="6">
         <v>0</v>
       </c>
-      <c r="N21" s="6">
+      <c r="N21" s="7">
+        <v>343.05599934999992</v>
+      </c>
+      <c r="O21" s="7">
+        <v>68.111999879999985</v>
+      </c>
+      <c r="P21" s="6">
         <f t="shared" si="5"/>
-        <v>17</v>
-      </c>
-      <c r="O21" s="6">
-        <v>0</v>
-      </c>
-      <c r="P21" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>0</v>
+      </c>
+      <c r="R21" s="6">
+        <v>0</v>
+      </c>
+      <c r="S21" s="6">
         <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="Q21" s="6">
-        <v>0</v>
-      </c>
-      <c r="R21" s="6">
-        <v>0</v>
-      </c>
-      <c r="S21" s="6">
-        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -27346,7 +27326,7 @@
       </c>
       <c r="U21" s="4"/>
       <c r="V21" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="W21" s="15">
@@ -27378,11 +27358,11 @@
       <c r="A22" s="5">
         <v>45921</v>
       </c>
-      <c r="B22" s="6">
-        <v>0</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0</v>
+      <c r="B22" s="7">
+        <v>1350.2579995199997</v>
+      </c>
+      <c r="C22" s="7">
+        <v>211.00799993999999</v>
       </c>
       <c r="D22" s="6">
         <f t="shared" si="0"/>
@@ -27406,7 +27386,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K22" s="6">
@@ -27419,25 +27399,24 @@
       <c r="M22" s="6">
         <v>0</v>
       </c>
-      <c r="N22" s="6">
+      <c r="N22" s="7">
+        <v>426.88799933000007</v>
+      </c>
+      <c r="O22" s="7">
+        <v>85.679999879999997</v>
+      </c>
+      <c r="P22" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O22" s="6">
-        <v>0</v>
-      </c>
-      <c r="P22" s="6">
+      <c r="Q22" s="6">
+        <v>0</v>
+      </c>
+      <c r="R22" s="6">
+        <v>0</v>
+      </c>
+      <c r="S22" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="6">
-        <v>0</v>
-      </c>
-      <c r="R22" s="6">
-        <v>0</v>
-      </c>
-      <c r="S22" s="6">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
@@ -27445,7 +27424,7 @@
       </c>
       <c r="U22" s="4"/>
       <c r="V22" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="W22" s="15">
@@ -27477,11 +27456,11 @@
       <c r="A23" s="5">
         <v>45922</v>
       </c>
-      <c r="B23" s="6">
-        <v>0</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0</v>
+      <c r="B23" s="7">
+        <v>1615.6139994699993</v>
+      </c>
+      <c r="C23" s="7">
+        <v>222.72599990999998</v>
       </c>
       <c r="D23" s="6">
         <f t="shared" si="0"/>
@@ -27505,7 +27484,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K23" s="6">
@@ -27518,25 +27497,24 @@
       <c r="M23" s="6">
         <v>0</v>
       </c>
-      <c r="N23" s="6">
+      <c r="N23" s="7">
+        <v>318.64799941000012</v>
+      </c>
+      <c r="O23" s="7">
+        <v>49.055999909999997</v>
+      </c>
+      <c r="P23" s="6">
         <f t="shared" si="5"/>
-        <v>8</v>
-      </c>
-      <c r="O23" s="6">
-        <v>0</v>
-      </c>
-      <c r="P23" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>0</v>
+      </c>
+      <c r="R23" s="6">
+        <v>0</v>
+      </c>
+      <c r="S23" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="6">
-        <v>0</v>
-      </c>
-      <c r="R23" s="6">
-        <v>0</v>
-      </c>
-      <c r="S23" s="6">
-        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="T23" s="6" t="s">
@@ -27544,7 +27522,7 @@
       </c>
       <c r="U23" s="4"/>
       <c r="V23" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>21</v>
       </c>
       <c r="W23" s="15">
@@ -27576,11 +27554,11 @@
       <c r="A24" s="5">
         <v>45923</v>
       </c>
-      <c r="B24" s="6">
-        <v>0</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0</v>
+      <c r="B24" s="7">
+        <v>1767.9479994699986</v>
+      </c>
+      <c r="C24" s="7">
+        <v>251.57999993999999</v>
       </c>
       <c r="D24" s="6">
         <f t="shared" si="0"/>
@@ -27604,7 +27582,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K24" s="6">
@@ -27617,25 +27595,24 @@
       <c r="M24" s="6">
         <v>0</v>
       </c>
-      <c r="N24" s="6">
+      <c r="N24" s="7">
+        <v>332.99999931000008</v>
+      </c>
+      <c r="O24" s="7">
+        <v>70.559999899999994</v>
+      </c>
+      <c r="P24" s="6">
         <f t="shared" si="5"/>
-        <v>8</v>
-      </c>
-      <c r="O24" s="6">
-        <v>0</v>
-      </c>
-      <c r="P24" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0</v>
+      </c>
+      <c r="R24" s="6">
+        <v>0</v>
+      </c>
+      <c r="S24" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="6">
-        <v>0</v>
-      </c>
-      <c r="R24" s="6">
-        <v>0</v>
-      </c>
-      <c r="S24" s="6">
-        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -27643,7 +27620,7 @@
       </c>
       <c r="U24" s="4"/>
       <c r="V24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="W24" s="15">
@@ -27675,11 +27652,11 @@
       <c r="A25" s="5">
         <v>45924</v>
       </c>
-      <c r="B25" s="6">
-        <v>0</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0</v>
+      <c r="B25" s="7">
+        <v>1889.5379994700004</v>
+      </c>
+      <c r="C25" s="7">
+        <v>245.19599993999995</v>
       </c>
       <c r="D25" s="6">
         <f t="shared" si="0"/>
@@ -27703,7 +27680,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K25" s="6">
@@ -27716,25 +27693,24 @@
       <c r="M25" s="6">
         <v>0</v>
       </c>
-      <c r="N25" s="6">
+      <c r="N25" s="7">
+        <v>366.23999934000011</v>
+      </c>
+      <c r="O25" s="7">
+        <v>78.095999899999981</v>
+      </c>
+      <c r="P25" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="O25" s="6">
-        <v>0</v>
-      </c>
-      <c r="P25" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>0</v>
+      </c>
+      <c r="R25" s="6">
+        <v>0</v>
+      </c>
+      <c r="S25" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>0</v>
-      </c>
-      <c r="R25" s="6">
-        <v>0</v>
-      </c>
-      <c r="S25" s="6">
-        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -27742,7 +27718,7 @@
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>23</v>
       </c>
       <c r="W25" s="15">
@@ -27774,11 +27750,11 @@
       <c r="A26" s="5">
         <v>45925</v>
       </c>
-      <c r="B26" s="6">
-        <v>0</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0</v>
+      <c r="B26" s="7">
+        <v>1703.6459995599998</v>
+      </c>
+      <c r="C26" s="7">
+        <v>270.85799993000001</v>
       </c>
       <c r="D26" s="6">
         <f t="shared" si="0"/>
@@ -27802,7 +27778,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="K26" s="6">
@@ -27815,25 +27791,24 @@
       <c r="M26" s="6">
         <v>0</v>
       </c>
-      <c r="N26" s="6">
+      <c r="N26" s="7">
+        <v>313.89599937000008</v>
+      </c>
+      <c r="O26" s="7">
+        <v>70.655999910000006</v>
+      </c>
+      <c r="P26" s="6">
         <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="O26" s="6">
-        <v>0</v>
-      </c>
-      <c r="P26" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>0</v>
+      </c>
+      <c r="R26" s="6">
+        <v>0</v>
+      </c>
+      <c r="S26" s="6">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="Q26" s="6">
-        <v>0</v>
-      </c>
-      <c r="R26" s="6">
-        <v>0</v>
-      </c>
-      <c r="S26" s="6">
-        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -27841,7 +27816,7 @@
       </c>
       <c r="U26" s="4"/>
       <c r="V26" s="20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
       <c r="W26" s="21">
@@ -27873,11 +27848,11 @@
       <c r="A27" s="5">
         <v>45926</v>
       </c>
-      <c r="B27" s="6">
-        <v>0</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0</v>
+      <c r="B27" s="7">
+        <v>1400.0279994900002</v>
+      </c>
+      <c r="C27" s="7">
+        <v>202.43999991999999</v>
       </c>
       <c r="D27" s="6">
         <f t="shared" si="0"/>
@@ -27901,7 +27876,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K27" s="6">
@@ -27914,25 +27889,24 @@
       <c r="M27" s="6">
         <v>0</v>
       </c>
-      <c r="N27" s="6">
+      <c r="N27" s="7">
+        <v>294.14399926999988</v>
+      </c>
+      <c r="O27" s="7">
+        <v>51.311999899999996</v>
+      </c>
+      <c r="P27" s="6">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="O27" s="6">
-        <v>0</v>
-      </c>
-      <c r="P27" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>0</v>
+      </c>
+      <c r="R27" s="6">
+        <v>0</v>
+      </c>
+      <c r="S27" s="6">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q27" s="6">
-        <v>0</v>
-      </c>
-      <c r="R27" s="6">
-        <v>0</v>
-      </c>
-      <c r="S27" s="6">
-        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T27" s="6" t="s">
@@ -27940,7 +27914,7 @@
       </c>
       <c r="U27" s="4"/>
       <c r="V27" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="W27" s="15">
@@ -27972,11 +27946,11 @@
       <c r="A28" s="5">
         <v>45927</v>
       </c>
-      <c r="B28" s="6">
-        <v>0</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0</v>
+      <c r="B28" s="7">
+        <v>1167.1379994699994</v>
+      </c>
+      <c r="C28" s="7">
+        <v>200.80199991999999</v>
       </c>
       <c r="D28" s="6">
         <f t="shared" si="0"/>
@@ -28000,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K28" s="6">
@@ -28013,25 +27987,24 @@
       <c r="M28" s="6">
         <v>0</v>
       </c>
-      <c r="N28" s="6">
+      <c r="N28" s="7">
+        <v>308.3279993700001</v>
+      </c>
+      <c r="O28" s="7">
+        <v>59.975999919999992</v>
+      </c>
+      <c r="P28" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O28" s="6">
-        <v>0</v>
-      </c>
-      <c r="P28" s="6">
+      <c r="Q28" s="6">
+        <v>0</v>
+      </c>
+      <c r="R28" s="6">
+        <v>0</v>
+      </c>
+      <c r="S28" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="6">
-        <v>0</v>
-      </c>
-      <c r="R28" s="6">
-        <v>0</v>
-      </c>
-      <c r="S28" s="6">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T28" s="6" t="s">
@@ -28039,7 +28012,7 @@
       </c>
       <c r="U28" s="4"/>
       <c r="V28" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="W28" s="15">
@@ -28071,11 +28044,11 @@
       <c r="A29" s="5">
         <v>45928</v>
       </c>
-      <c r="B29" s="6">
-        <v>0</v>
-      </c>
-      <c r="C29" s="6">
-        <v>0</v>
+      <c r="B29" s="7">
+        <v>1118.9219995199992</v>
+      </c>
+      <c r="C29" s="7">
+        <v>193.91399992000004</v>
       </c>
       <c r="D29" s="6">
         <f t="shared" si="0"/>
@@ -28099,7 +28072,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K29" s="6">
@@ -28112,25 +28085,24 @@
       <c r="M29" s="6">
         <v>0</v>
       </c>
-      <c r="N29" s="6">
+      <c r="N29" s="7">
+        <v>302.78399932999992</v>
+      </c>
+      <c r="O29" s="7">
+        <v>69.263999890000008</v>
+      </c>
+      <c r="P29" s="6">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="O29" s="6">
-        <v>0</v>
-      </c>
-      <c r="P29" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="6">
+        <v>0</v>
+      </c>
+      <c r="R29" s="6">
+        <v>0</v>
+      </c>
+      <c r="S29" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="6">
-        <v>0</v>
-      </c>
-      <c r="R29" s="6">
-        <v>0</v>
-      </c>
-      <c r="S29" s="6">
-        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="T29" s="6" t="s">
@@ -28138,7 +28110,7 @@
       </c>
       <c r="U29" s="4"/>
       <c r="V29" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>27</v>
       </c>
       <c r="W29" s="15">
@@ -28170,11 +28142,11 @@
       <c r="A30" s="5">
         <v>45929</v>
       </c>
-      <c r="B30" s="6">
-        <v>0</v>
-      </c>
-      <c r="C30" s="6">
-        <v>0</v>
+      <c r="B30" s="7">
+        <v>1829.8979994399999</v>
+      </c>
+      <c r="C30" s="7">
+        <v>268.50599996</v>
       </c>
       <c r="D30" s="6">
         <f t="shared" si="0"/>
@@ -28198,7 +28170,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K30" s="6">
@@ -28211,25 +28183,24 @@
       <c r="M30" s="6">
         <v>0</v>
       </c>
-      <c r="N30" s="6">
+      <c r="N30" s="7">
+        <v>338.44799930999977</v>
+      </c>
+      <c r="O30" s="7">
+        <v>70.559999919999996</v>
+      </c>
+      <c r="P30" s="6">
         <f t="shared" si="5"/>
-        <v>12</v>
-      </c>
-      <c r="O30" s="6">
-        <v>0</v>
-      </c>
-      <c r="P30" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>0</v>
+      </c>
+      <c r="R30" s="6">
+        <v>0</v>
+      </c>
+      <c r="S30" s="6">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="6">
-        <v>0</v>
-      </c>
-      <c r="R30" s="6">
-        <v>0</v>
-      </c>
-      <c r="S30" s="6">
-        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="T30" s="6" t="s">
@@ -28237,7 +28208,7 @@
       </c>
       <c r="U30" s="4"/>
       <c r="V30" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="W30" s="15">
@@ -28269,11 +28240,11 @@
       <c r="A31" s="5">
         <v>45930</v>
       </c>
-      <c r="B31" s="6">
-        <v>0</v>
-      </c>
-      <c r="C31" s="6">
-        <v>0</v>
+      <c r="B31" s="7">
+        <v>2025.8279995000016</v>
+      </c>
+      <c r="C31" s="7">
+        <v>274.13399992999996</v>
       </c>
       <c r="D31" s="6">
         <f t="shared" si="0"/>
@@ -28297,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K31" s="6">
@@ -28310,25 +28281,24 @@
       <c r="M31" s="6">
         <v>0</v>
       </c>
-      <c r="N31" s="6">
+      <c r="N31" s="7">
+        <v>363.47999940999978</v>
+      </c>
+      <c r="O31" s="7">
+        <v>71.927999900000003</v>
+      </c>
+      <c r="P31" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="O31" s="6">
-        <v>0</v>
-      </c>
-      <c r="P31" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>0</v>
+      </c>
+      <c r="R31" s="6">
+        <v>0</v>
+      </c>
+      <c r="S31" s="6">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>0</v>
-      </c>
-      <c r="R31" s="6">
-        <v>0</v>
-      </c>
-      <c r="S31" s="6">
-        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="T31" s="6" t="s">
@@ -28336,7 +28306,7 @@
       </c>
       <c r="U31" s="4"/>
       <c r="V31" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>29</v>
       </c>
       <c r="W31" s="15">
@@ -28378,7 +28348,7 @@
       <c r="T32" s="27"/>
       <c r="U32" s="4"/>
       <c r="V32" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="W32" s="15">

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6ECDF6-0948-47E9-8D0E-C1A225C1DB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AA3E77-A4C4-46D1-BF7D-53798102A457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="99">
   <si>
     <t>Data</t>
   </si>
@@ -566,7 +566,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -709,6 +709,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -971,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{343B5D31-DB35-40E5-8AAC-64B51E6DA6BC}">
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -981,8 +982,7 @@
     <col min="6" max="9" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -1533,34 +1533,34 @@
         <v>16134.03</v>
       </c>
       <c r="D10" s="41">
-        <v>0</v>
+        <v>1372.826</v>
       </c>
       <c r="E10" s="41">
-        <v>0</v>
+        <v>588.35400000000004</v>
       </c>
       <c r="F10" s="41">
-        <v>0</v>
+        <v>1747.9979999999998</v>
       </c>
       <c r="G10" s="41">
-        <v>0</v>
+        <v>749.14199999999994</v>
       </c>
       <c r="H10" s="41">
-        <v>0</v>
+        <v>4365.6409999999996</v>
       </c>
       <c r="I10" s="41">
-        <v>0</v>
+        <v>1870.989</v>
       </c>
       <c r="J10" s="41">
-        <v>0</v>
+        <v>1071.9589999999998</v>
       </c>
       <c r="K10" s="41">
-        <v>0</v>
+        <v>459.41099999999994</v>
       </c>
       <c r="L10" s="41">
-        <v>0</v>
+        <v>1181.2919999999999</v>
       </c>
       <c r="M10" s="41">
-        <v>0</v>
+        <v>506.26799999999997</v>
       </c>
       <c r="N10" s="41">
         <v>9005.64</v>
@@ -1763,9 +1763,23 @@
       <c r="E16" s="44"/>
       <c r="F16" s="47"/>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D17" s="45"/>
       <c r="E17" s="45"/>
+      <c r="L17" s="56">
+        <v>1531.37</v>
+      </c>
+      <c r="M17" s="56">
+        <f>L17*0.7</f>
+        <v>1071.9589999999998</v>
+      </c>
+      <c r="N17" s="56">
+        <f>L17*0.3</f>
+        <v>459.41099999999994</v>
+      </c>
+    </row>
+    <row r="22" spans="4:14" x14ac:dyDescent="0.2">
+      <c r="J22" s="56"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -25279,118 +25293,121 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AG101"/>
+  <dimension ref="A1:AH101"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="25.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="39" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="U1" s="4"/>
-      <c r="V1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="W1" s="3" t="s">
+      <c r="V1" s="4"/>
+      <c r="W1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>45901</v>
       </c>
@@ -25401,100 +25418,99 @@
         <v>249.64799989000002</v>
       </c>
       <c r="D2" s="6">
-        <f t="shared" ref="D2:D31" si="0">W3-W2</f>
+        <f t="shared" ref="D2:D31" si="0">X3-X2</f>
         <v>21</v>
       </c>
-      <c r="E2" s="6">
-        <v>0</v>
-      </c>
-      <c r="F2" s="6">
-        <f t="shared" ref="F2:F31" si="1">X3-X2</f>
-        <v>30</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0</v>
-      </c>
-      <c r="H2" s="6">
-        <f t="shared" ref="H2:H31" si="2">Y3-Y2</f>
-        <v>5</v>
-      </c>
-      <c r="I2" s="6">
-        <v>0</v>
-      </c>
-      <c r="J2" s="6">
-        <f t="shared" ref="J2:J14" si="3">Z3-Z2</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="6">
-        <v>0</v>
-      </c>
-      <c r="L2" s="6">
-        <f t="shared" ref="L2:L31" si="4">AA3-AA2</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="6">
-        <v>0</v>
+      <c r="E2" s="7">
+        <v>14.7</v>
+      </c>
+      <c r="F2" s="7">
+        <v>6.3</v>
+      </c>
+      <c r="G2" s="7">
+        <v>42.857142857142861</v>
+      </c>
+      <c r="H2" s="7">
+        <v>9</v>
+      </c>
+      <c r="I2" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J2" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K2" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L2" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M2" s="7">
+        <v>33.599999999999994</v>
       </c>
       <c r="N2" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O2" s="7">
         <v>264.67199936999987</v>
       </c>
-      <c r="O2" s="7">
+      <c r="P2" s="7">
         <v>59.903999919999997</v>
       </c>
-      <c r="P2" s="6">
-        <f t="shared" ref="P2:P31" si="5">AC3-AC2</f>
-        <v>0</v>
-      </c>
       <c r="Q2" s="6">
+        <f t="shared" ref="Q2:Q31" si="1">AD3-AD2</f>
         <v>0</v>
       </c>
       <c r="R2" s="6">
         <v>0</v>
       </c>
       <c r="S2" s="6">
-        <f t="shared" ref="S2:S31" si="6">AD3-AD2</f>
-        <v>0</v>
-      </c>
-      <c r="T2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" s="6">
+        <f t="shared" ref="T2:T31" si="2">AE3-AE2</f>
+        <v>0</v>
+      </c>
+      <c r="U2" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="U2" s="4"/>
-      <c r="V2" s="8">
-        <v>0</v>
-      </c>
-      <c r="W2" s="15">
+      <c r="V2" s="4"/>
+      <c r="W2" s="8">
+        <v>0</v>
+      </c>
+      <c r="X2" s="15">
         <v>10491</v>
       </c>
-      <c r="X2" s="15">
+      <c r="Y2" s="15">
         <v>13042</v>
       </c>
-      <c r="Y2" s="15">
+      <c r="Z2" s="15">
         <v>9644</v>
       </c>
-      <c r="Z2" s="15">
+      <c r="AA2" s="15">
         <v>10861</v>
       </c>
-      <c r="AA2" s="15">
+      <c r="AB2" s="15">
         <v>1288</v>
       </c>
-      <c r="AB2" s="15">
+      <c r="AC2" s="15">
         <v>4067</v>
       </c>
-      <c r="AC2" s="15">
+      <c r="AD2" s="15">
         <v>412</v>
       </c>
-      <c r="AD2" s="15">
+      <c r="AE2" s="15">
         <v>3660</v>
       </c>
-      <c r="AF2" s="10" t="s">
+      <c r="AG2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AG2" s="11">
-        <f t="array" ref="AG2">_xlfn.IFS(AF2="Verde",0,AF2="Amarela",1.885,AF2="Vermelha P1",4.463,AF2="Vermelha P2",7.877)</f>
+      <c r="AH2" s="11">
+        <f t="array" ref="AH2">_xlfn.IFS(AG2="Verde",0,AG2="Amarela",1.885,AG2="Vermelha P1",4.463,AG2="Vermelha P2",7.877)</f>
         <v>7.8769999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>45902</v>
       </c>
@@ -25508,90 +25524,89 @@
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="E3" s="6">
-        <v>0</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="E3" s="7">
+        <v>58.8</v>
+      </c>
+      <c r="F3" s="7">
+        <v>25.2</v>
+      </c>
+      <c r="G3" s="7">
+        <v>57.142857142857146</v>
+      </c>
+      <c r="H3" s="7">
+        <v>12</v>
+      </c>
+      <c r="I3" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J3" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K3" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L3" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M3" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N3" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O3" s="7">
+        <v>273.28799932000004</v>
+      </c>
+      <c r="P3" s="7">
+        <v>57.191999889999998</v>
+      </c>
+      <c r="Q3" s="6">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="R3" s="6">
+        <v>0</v>
+      </c>
+      <c r="S3" s="6">
+        <v>0</v>
+      </c>
+      <c r="T3" s="6">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6">
-        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="V3" s="4"/>
+      <c r="W3" s="12">
         <v>1</v>
       </c>
-      <c r="K3" s="6">
-        <v>0</v>
-      </c>
-      <c r="L3" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M3" s="6">
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <v>273.28799932000004</v>
-      </c>
-      <c r="O3" s="7">
-        <v>57.191999889999998</v>
-      </c>
-      <c r="P3" s="6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>0</v>
-      </c>
-      <c r="R3" s="6">
-        <v>0</v>
-      </c>
-      <c r="S3" s="6">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="U3" s="4"/>
-      <c r="V3" s="12">
-        <v>1</v>
-      </c>
-      <c r="W3" s="13">
+      <c r="X3" s="13">
         <v>10512</v>
       </c>
-      <c r="X3" s="13">
+      <c r="Y3" s="13">
         <v>13072</v>
       </c>
-      <c r="Y3" s="13">
+      <c r="Z3" s="13">
         <v>9649</v>
       </c>
-      <c r="Z3" s="13">
+      <c r="AA3" s="13">
         <v>10861</v>
       </c>
-      <c r="AA3" s="13">
+      <c r="AB3" s="13">
         <v>1288</v>
       </c>
-      <c r="AB3" s="13">
+      <c r="AC3" s="13">
         <v>4072</v>
       </c>
-      <c r="AC3" s="13">
+      <c r="AD3" s="13">
         <v>412</v>
       </c>
-      <c r="AD3" s="13">
+      <c r="AE3" s="13">
         <v>3660</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>45903</v>
       </c>
@@ -25605,91 +25620,90 @@
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="E4" s="6">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="E4" s="7">
+        <v>58.099999999999994</v>
+      </c>
+      <c r="F4" s="7">
+        <v>24.9</v>
+      </c>
+      <c r="G4" s="7">
+        <v>75.714285714285722</v>
+      </c>
+      <c r="H4" s="7">
+        <v>15.899999999999999</v>
+      </c>
+      <c r="I4" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J4" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K4" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L4" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M4" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N4" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O4" s="7">
+        <v>253.77599939999993</v>
+      </c>
+      <c r="P4" s="7">
+        <v>51.263999930000004</v>
+      </c>
+      <c r="Q4" s="6">
         <f t="shared" si="1"/>
-        <v>53</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6">
+        <v>0</v>
+      </c>
+      <c r="T4" s="6">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="I4" s="6">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K4" s="6">
-        <v>0</v>
-      </c>
-      <c r="L4" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M4" s="6">
-        <v>0</v>
-      </c>
-      <c r="N4" s="7">
-        <v>253.77599939999993</v>
-      </c>
-      <c r="O4" s="7">
-        <v>51.263999930000004</v>
-      </c>
-      <c r="P4" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6">
-        <v>0</v>
-      </c>
-      <c r="S4" s="6">
-        <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="U4" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U4" s="4"/>
-      <c r="V4" s="14">
-        <f t="shared" ref="V4:V32" si="7">V3+1</f>
+      <c r="V4" s="4"/>
+      <c r="W4" s="14">
+        <f t="shared" ref="W4:W32" si="3">W3+1</f>
         <v>2</v>
       </c>
-      <c r="W4" s="6">
+      <c r="X4" s="6">
         <v>10596</v>
       </c>
-      <c r="X4" s="6">
+      <c r="Y4" s="6">
         <v>13112</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Z4" s="6">
         <v>9654</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="AA4" s="6">
         <v>10862</v>
       </c>
-      <c r="AA4" s="6">
+      <c r="AB4" s="6">
         <v>1288</v>
       </c>
-      <c r="AB4" s="6">
+      <c r="AC4" s="6">
         <v>4076</v>
       </c>
-      <c r="AC4" s="6">
+      <c r="AD4" s="6">
         <v>413</v>
       </c>
-      <c r="AD4" s="6">
+      <c r="AE4" s="6">
         <v>3663</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>45904</v>
       </c>
@@ -25703,91 +25717,90 @@
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="E5" s="6">
-        <v>0</v>
-      </c>
-      <c r="F5" s="6">
+      <c r="E5" s="7">
+        <v>60.9</v>
+      </c>
+      <c r="F5" s="7">
+        <v>26.099999999999998</v>
+      </c>
+      <c r="G5" s="7">
+        <v>110</v>
+      </c>
+      <c r="H5" s="7">
+        <v>23.099999999999998</v>
+      </c>
+      <c r="I5" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J5" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K5" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L5" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M5" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N5" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O5" s="7">
+        <v>287.20799941000007</v>
+      </c>
+      <c r="P5" s="7">
+        <v>59.927999880000002</v>
+      </c>
+      <c r="Q5" s="6">
         <f t="shared" si="1"/>
-        <v>77</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
+        <v>1</v>
+      </c>
+      <c r="R5" s="6">
+        <v>0</v>
+      </c>
+      <c r="S5" s="6">
+        <v>0</v>
+      </c>
+      <c r="T5" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I5" s="6">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6">
+      <c r="U5" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="V5" s="4"/>
+      <c r="W5" s="14">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K5" s="6">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="6">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7">
-        <v>287.20799941000007</v>
-      </c>
-      <c r="O5" s="7">
-        <v>59.927999880000002</v>
-      </c>
-      <c r="P5" s="6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6">
-        <v>0</v>
-      </c>
-      <c r="S5" s="6">
-        <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="T5" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="U5" s="4"/>
-      <c r="V5" s="14">
-        <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="W5" s="6">
+      <c r="X5" s="6">
         <v>10679</v>
       </c>
-      <c r="X5" s="6">
+      <c r="Y5" s="6">
         <v>13165</v>
       </c>
-      <c r="Y5" s="6">
+      <c r="Z5" s="6">
         <v>9658</v>
       </c>
-      <c r="Z5" s="6">
+      <c r="AA5" s="6">
         <v>10863</v>
       </c>
-      <c r="AA5" s="6">
+      <c r="AB5" s="6">
         <v>1288</v>
       </c>
-      <c r="AB5" s="6">
+      <c r="AC5" s="6">
         <v>4080</v>
       </c>
-      <c r="AC5" s="6">
+      <c r="AD5" s="6">
         <v>413</v>
       </c>
-      <c r="AD5" s="6">
+      <c r="AE5" s="6">
         <v>3666</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>45905</v>
       </c>
@@ -25801,91 +25814,90 @@
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="E6" s="7">
+        <v>45.5</v>
+      </c>
+      <c r="F6" s="7">
+        <v>19.5</v>
+      </c>
+      <c r="G6" s="7">
+        <v>170</v>
+      </c>
+      <c r="H6" s="7">
+        <v>35.699999999999996</v>
+      </c>
+      <c r="I6" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J6" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K6" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L6" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M6" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N6" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O6" s="7">
+        <v>299.56799928999999</v>
+      </c>
+      <c r="P6" s="7">
+        <v>68.375999889999989</v>
+      </c>
+      <c r="Q6" s="6">
         <f t="shared" si="1"/>
-        <v>119</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0</v>
+      </c>
+      <c r="T6" s="6">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
+        <v>2</v>
+      </c>
+      <c r="U6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="V6" s="4"/>
+      <c r="W6" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M6" s="6">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
-        <v>299.56799928999999</v>
-      </c>
-      <c r="O6" s="7">
-        <v>68.375999889999989</v>
-      </c>
-      <c r="P6" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6">
-        <v>0</v>
-      </c>
-      <c r="S6" s="6">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="T6" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="U6" s="4"/>
-      <c r="V6" s="14">
-        <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="W6" s="6">
+      <c r="X6" s="6">
         <v>10766</v>
       </c>
-      <c r="X6" s="6">
+      <c r="Y6" s="6">
         <v>13242</v>
       </c>
-      <c r="Y6" s="6">
+      <c r="Z6" s="6">
         <v>9661</v>
       </c>
-      <c r="Z6" s="6">
+      <c r="AA6" s="6">
         <v>10864</v>
       </c>
-      <c r="AA6" s="6">
+      <c r="AB6" s="6">
         <v>1288</v>
       </c>
-      <c r="AB6" s="6">
+      <c r="AC6" s="6">
         <v>4084</v>
       </c>
-      <c r="AC6" s="6">
+      <c r="AD6" s="6">
         <v>414</v>
       </c>
-      <c r="AD6" s="6">
+      <c r="AE6" s="6">
         <v>3669</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>45906</v>
       </c>
@@ -25899,91 +25911,90 @@
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="E7" s="7">
+        <v>42.699999999999996</v>
+      </c>
+      <c r="F7" s="7">
+        <v>18.3</v>
+      </c>
+      <c r="G7" s="7">
+        <v>47.142857142857146</v>
+      </c>
+      <c r="H7" s="7">
+        <v>9.9</v>
+      </c>
+      <c r="I7" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J7" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K7" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L7" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M7" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N7" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O7" s="7">
+        <v>345.6239993099997</v>
+      </c>
+      <c r="P7" s="7">
+        <v>74.303999909999987</v>
+      </c>
+      <c r="Q7" s="6">
         <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
+        <v>1</v>
+      </c>
+      <c r="R7" s="6">
+        <v>0</v>
+      </c>
+      <c r="S7" s="6">
+        <v>0</v>
+      </c>
+      <c r="T7" s="6">
         <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="U7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="V7" s="4"/>
+      <c r="W7" s="14">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
-      <c r="N7" s="7">
-        <v>345.6239993099997</v>
-      </c>
-      <c r="O7" s="7">
-        <v>74.303999909999987</v>
-      </c>
-      <c r="P7" s="6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6">
-        <v>0</v>
-      </c>
-      <c r="S7" s="6">
-        <f t="shared" si="6"/>
-        <v>6</v>
-      </c>
-      <c r="T7" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="U7" s="4"/>
-      <c r="V7" s="14">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="W7" s="6">
+      <c r="X7" s="6">
         <v>10831</v>
       </c>
-      <c r="X7" s="6">
+      <c r="Y7" s="6">
         <v>13361</v>
       </c>
-      <c r="Y7" s="6">
+      <c r="Z7" s="6">
         <v>9666</v>
       </c>
-      <c r="Z7" s="6">
+      <c r="AA7" s="6">
         <v>10864</v>
       </c>
-      <c r="AA7" s="6">
+      <c r="AB7" s="6">
         <v>1289</v>
       </c>
-      <c r="AB7" s="6">
+      <c r="AC7" s="6">
         <v>4086</v>
       </c>
-      <c r="AC7" s="6">
+      <c r="AD7" s="6">
         <v>414</v>
       </c>
-      <c r="AD7" s="6">
+      <c r="AE7" s="6">
         <v>3671</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>45907</v>
       </c>
@@ -25997,91 +26008,90 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="E8" s="7">
+        <v>9.1</v>
+      </c>
+      <c r="F8" s="7">
+        <v>3.9</v>
+      </c>
+      <c r="G8" s="7">
+        <v>74.285714285714292</v>
+      </c>
+      <c r="H8" s="7">
+        <v>15.6</v>
+      </c>
+      <c r="I8" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J8" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K8" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L8" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M8" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N8" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O8" s="7">
+        <v>368.15999933999984</v>
+      </c>
+      <c r="P8" s="7">
+        <v>63.815999930000011</v>
+      </c>
+      <c r="Q8" s="6">
         <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="R8" s="6">
+        <v>0</v>
+      </c>
+      <c r="S8" s="6">
+        <v>0</v>
+      </c>
+      <c r="T8" s="6">
         <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="U8" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="V8" s="4"/>
+      <c r="W8" s="14">
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="6">
-        <v>0</v>
-      </c>
-      <c r="N8" s="7">
-        <v>368.15999933999984</v>
-      </c>
-      <c r="O8" s="7">
-        <v>63.815999930000011</v>
-      </c>
-      <c r="P8" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="T8" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="U8" s="4"/>
-      <c r="V8" s="14">
-        <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="W8" s="6">
+      <c r="X8" s="6">
         <v>10892</v>
       </c>
-      <c r="X8" s="6">
+      <c r="Y8" s="6">
         <v>13394</v>
       </c>
-      <c r="Y8" s="6">
+      <c r="Z8" s="6">
         <v>9671</v>
       </c>
-      <c r="Z8" s="6">
+      <c r="AA8" s="6">
         <v>10865</v>
       </c>
-      <c r="AA8" s="6">
+      <c r="AB8" s="6">
         <v>1289</v>
       </c>
-      <c r="AB8" s="6">
+      <c r="AC8" s="6">
         <v>4093</v>
       </c>
-      <c r="AC8" s="6">
+      <c r="AD8" s="6">
         <v>415</v>
       </c>
-      <c r="AD8" s="6">
+      <c r="AE8" s="6">
         <v>3677</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>45908</v>
       </c>
@@ -26095,91 +26105,90 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="E9" s="6">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="E9" s="7">
+        <v>24.5</v>
+      </c>
+      <c r="F9" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J9" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K9" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L9" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M9" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N9" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O9" s="7">
+        <v>341.30399937000004</v>
+      </c>
+      <c r="P9" s="7">
+        <v>63.215999880000005</v>
+      </c>
+      <c r="Q9" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
+      <c r="R9" s="6">
+        <v>0</v>
+      </c>
+      <c r="S9" s="6">
+        <v>0</v>
+      </c>
+      <c r="T9" s="6">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="I9" s="6">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6">
+        <v>6</v>
+      </c>
+      <c r="U9" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="V9" s="4"/>
+      <c r="W9" s="14">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="6">
-        <v>0</v>
-      </c>
-      <c r="N9" s="7">
-        <v>341.30399937000004</v>
-      </c>
-      <c r="O9" s="7">
-        <v>63.215999880000005</v>
-      </c>
-      <c r="P9" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>0</v>
-      </c>
-      <c r="R9" s="6">
-        <v>0</v>
-      </c>
-      <c r="S9" s="6">
-        <f t="shared" si="6"/>
-        <v>6</v>
-      </c>
-      <c r="T9" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="U9" s="4"/>
-      <c r="V9" s="14">
-        <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="W9" s="6">
+      <c r="X9" s="6">
         <v>10905</v>
       </c>
-      <c r="X9" s="6">
+      <c r="Y9" s="6">
         <v>13446</v>
       </c>
-      <c r="Y9" s="6">
+      <c r="Z9" s="6">
         <v>9677</v>
       </c>
-      <c r="Z9" s="6">
+      <c r="AA9" s="6">
         <v>10866</v>
       </c>
-      <c r="AA9" s="6">
+      <c r="AB9" s="6">
         <v>1289</v>
       </c>
-      <c r="AB9" s="6">
+      <c r="AC9" s="6">
         <v>4096</v>
       </c>
-      <c r="AC9" s="6">
+      <c r="AD9" s="6">
         <v>415</v>
       </c>
-      <c r="AD9" s="6">
+      <c r="AE9" s="6">
         <v>3680</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>45909</v>
       </c>
@@ -26193,91 +26202,90 @@
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="E10" s="6">
-        <v>0</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="E10" s="7">
+        <v>66.5</v>
+      </c>
+      <c r="F10" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="G10" s="7">
+        <v>211.42857142857144</v>
+      </c>
+      <c r="H10" s="7">
+        <v>44.4</v>
+      </c>
+      <c r="I10" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J10" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K10" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L10" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M10" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N10" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O10" s="7">
+        <v>331.72799933999988</v>
+      </c>
+      <c r="P10" s="7">
+        <v>68.399999919999985</v>
+      </c>
+      <c r="Q10" s="6">
         <f t="shared" si="1"/>
-        <v>148</v>
-      </c>
-      <c r="G10" s="6">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6">
+        <v>1</v>
+      </c>
+      <c r="R10" s="6">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6">
+        <v>0</v>
+      </c>
+      <c r="T10" s="6">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="I10" s="6">
-        <v>0</v>
-      </c>
-      <c r="J10" s="6">
+        <v>5</v>
+      </c>
+      <c r="U10" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="V10" s="4"/>
+      <c r="W10" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="6">
-        <v>0</v>
-      </c>
-      <c r="N10" s="7">
-        <v>331.72799933999988</v>
-      </c>
-      <c r="O10" s="7">
-        <v>68.399999919999985</v>
-      </c>
-      <c r="P10" s="6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>0</v>
-      </c>
-      <c r="R10" s="6">
-        <v>0</v>
-      </c>
-      <c r="S10" s="6">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="T10" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="U10" s="4"/>
-      <c r="V10" s="14">
-        <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="W10" s="6">
+      <c r="X10" s="6">
         <v>10940</v>
       </c>
-      <c r="X10" s="6">
+      <c r="Y10" s="6">
         <v>13446</v>
       </c>
-      <c r="Y10" s="6">
+      <c r="Z10" s="6">
         <v>9682</v>
       </c>
-      <c r="Z10" s="6">
+      <c r="AA10" s="6">
         <v>10867</v>
       </c>
-      <c r="AA10" s="6">
+      <c r="AB10" s="6">
         <v>1289</v>
       </c>
-      <c r="AB10" s="6">
+      <c r="AC10" s="6">
         <v>4102</v>
       </c>
-      <c r="AC10" s="6">
+      <c r="AD10" s="6">
         <v>415</v>
       </c>
-      <c r="AD10" s="6">
+      <c r="AE10" s="6">
         <v>3686</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>45910</v>
       </c>
@@ -26291,91 +26299,90 @@
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="E11" s="6">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="E11" s="7">
+        <v>61.599999999999994</v>
+      </c>
+      <c r="F11" s="7">
+        <v>26.4</v>
+      </c>
+      <c r="G11" s="7">
+        <v>152.85714285714286</v>
+      </c>
+      <c r="H11" s="7">
+        <v>32.1</v>
+      </c>
+      <c r="I11" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J11" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K11" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L11" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M11" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N11" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O11" s="7">
+        <v>304.91999933000005</v>
+      </c>
+      <c r="P11" s="7">
+        <v>64.463999880000003</v>
+      </c>
+      <c r="Q11" s="6">
         <f t="shared" si="1"/>
-        <v>107</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6">
+        <v>1</v>
+      </c>
+      <c r="R11" s="6">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6">
+        <v>0</v>
+      </c>
+      <c r="T11" s="6">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="I11" s="6">
-        <v>0</v>
-      </c>
-      <c r="J11" s="6">
+        <v>5</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="V11" s="4"/>
+      <c r="W11" s="14">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K11" s="6">
-        <v>0</v>
-      </c>
-      <c r="L11" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M11" s="6">
-        <v>0</v>
-      </c>
-      <c r="N11" s="7">
-        <v>304.91999933000005</v>
-      </c>
-      <c r="O11" s="7">
-        <v>64.463999880000003</v>
-      </c>
-      <c r="P11" s="6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>0</v>
-      </c>
-      <c r="R11" s="6">
-        <v>0</v>
-      </c>
-      <c r="S11" s="6">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="T11" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="U11" s="4"/>
-      <c r="V11" s="14">
-        <f t="shared" si="7"/>
         <v>9</v>
       </c>
-      <c r="W11" s="15">
+      <c r="X11" s="15">
         <v>11035</v>
       </c>
-      <c r="X11" s="15">
+      <c r="Y11" s="15">
         <v>13594</v>
       </c>
-      <c r="Y11" s="15">
+      <c r="Z11" s="15">
         <v>9686</v>
       </c>
-      <c r="Z11" s="15">
+      <c r="AA11" s="15">
         <v>10867</v>
       </c>
-      <c r="AA11" s="15">
+      <c r="AB11" s="15">
         <v>1289</v>
       </c>
-      <c r="AB11" s="15">
+      <c r="AC11" s="15">
         <v>4107</v>
       </c>
-      <c r="AC11" s="15">
+      <c r="AD11" s="15">
         <v>416</v>
       </c>
-      <c r="AD11" s="15">
+      <c r="AE11" s="15">
         <v>3691</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>45911</v>
       </c>
@@ -26389,91 +26396,90 @@
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="E12" s="6">
-        <v>0</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="E12" s="7">
+        <v>91</v>
+      </c>
+      <c r="F12" s="7">
+        <v>39</v>
+      </c>
+      <c r="G12" s="7">
+        <v>124.28571428571429</v>
+      </c>
+      <c r="H12" s="7">
+        <v>26.099999999999998</v>
+      </c>
+      <c r="I12" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J12" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K12" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L12" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M12" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N12" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O12" s="7">
+        <v>337.75199938999981</v>
+      </c>
+      <c r="P12" s="7">
+        <v>71.423999910000006</v>
+      </c>
+      <c r="Q12" s="6">
         <f t="shared" si="1"/>
-        <v>87</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6">
+        <v>1</v>
+      </c>
+      <c r="R12" s="6">
+        <v>0</v>
+      </c>
+      <c r="S12" s="6">
+        <v>0</v>
+      </c>
+      <c r="T12" s="6">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I12" s="6">
-        <v>0</v>
-      </c>
-      <c r="J12" s="6">
+      <c r="U12" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="V12" s="4"/>
+      <c r="W12" s="14">
         <f t="shared" si="3"/>
-        <v>-8</v>
-      </c>
-      <c r="K12" s="6">
-        <v>0</v>
-      </c>
-      <c r="L12" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="6">
-        <v>0</v>
-      </c>
-      <c r="N12" s="7">
-        <v>337.75199938999981</v>
-      </c>
-      <c r="O12" s="7">
-        <v>71.423999910000006</v>
-      </c>
-      <c r="P12" s="6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>0</v>
-      </c>
-      <c r="R12" s="6">
-        <v>0</v>
-      </c>
-      <c r="S12" s="6">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="T12" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="U12" s="4"/>
-      <c r="V12" s="14">
-        <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="W12" s="6">
+      <c r="X12" s="6">
         <v>11123</v>
       </c>
-      <c r="X12" s="6">
+      <c r="Y12" s="6">
         <v>13701</v>
       </c>
-      <c r="Y12" s="6">
+      <c r="Z12" s="6">
         <v>9689</v>
       </c>
-      <c r="Z12" s="6">
+      <c r="AA12" s="6">
         <v>10868</v>
       </c>
-      <c r="AA12" s="6">
+      <c r="AB12" s="6">
         <v>1290</v>
       </c>
-      <c r="AB12" s="6">
+      <c r="AC12" s="6">
         <v>4114</v>
       </c>
-      <c r="AC12" s="6">
+      <c r="AD12" s="6">
         <v>417</v>
       </c>
-      <c r="AD12" s="6">
+      <c r="AE12" s="6">
         <v>3696</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>45912</v>
       </c>
@@ -26487,91 +26493,90 @@
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="E13" s="6">
-        <v>0</v>
-      </c>
-      <c r="F13" s="6">
+      <c r="E13" s="7">
+        <v>70</v>
+      </c>
+      <c r="F13" s="7">
+        <v>30</v>
+      </c>
+      <c r="G13" s="7">
+        <v>152.85714285714286</v>
+      </c>
+      <c r="H13" s="7">
+        <v>32.1</v>
+      </c>
+      <c r="I13" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J13" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K13" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L13" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M13" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N13" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O13" s="7">
+        <v>385.96799933000017</v>
+      </c>
+      <c r="P13" s="7">
+        <v>81.479999890000002</v>
+      </c>
+      <c r="Q13" s="6">
         <f t="shared" si="1"/>
-        <v>107</v>
-      </c>
-      <c r="G13" s="6">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6">
+        <v>1</v>
+      </c>
+      <c r="R13" s="6">
+        <v>0</v>
+      </c>
+      <c r="S13" s="6">
+        <v>0</v>
+      </c>
+      <c r="T13" s="6">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="I13" s="6">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6">
+        <v>6</v>
+      </c>
+      <c r="U13" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V13" s="4"/>
+      <c r="W13" s="14">
         <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="K13" s="6">
-        <v>0</v>
-      </c>
-      <c r="L13" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="6">
-        <v>0</v>
-      </c>
-      <c r="N13" s="7">
-        <v>385.96799933000017</v>
-      </c>
-      <c r="O13" s="7">
-        <v>81.479999890000002</v>
-      </c>
-      <c r="P13" s="6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>0</v>
-      </c>
-      <c r="R13" s="6">
-        <v>0</v>
-      </c>
-      <c r="S13" s="6">
-        <f t="shared" si="6"/>
-        <v>6</v>
-      </c>
-      <c r="T13" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U13" s="4"/>
-      <c r="V13" s="14">
-        <f t="shared" si="7"/>
         <v>11</v>
       </c>
-      <c r="W13" s="15">
+      <c r="X13" s="15">
         <v>11253</v>
       </c>
-      <c r="X13" s="15">
+      <c r="Y13" s="15">
         <v>13788</v>
       </c>
-      <c r="Y13" s="15">
+      <c r="Z13" s="15">
         <v>9692</v>
       </c>
-      <c r="Z13" s="15">
+      <c r="AA13" s="15">
         <v>10860</v>
       </c>
-      <c r="AA13" s="15">
+      <c r="AB13" s="15">
         <v>1290</v>
       </c>
-      <c r="AB13" s="15">
+      <c r="AC13" s="15">
         <v>4117</v>
       </c>
-      <c r="AC13" s="15">
+      <c r="AD13" s="15">
         <v>418</v>
       </c>
-      <c r="AD13" s="15">
+      <c r="AE13" s="15">
         <v>3699</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>45913</v>
       </c>
@@ -26585,91 +26590,90 @@
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="E14" s="6">
-        <v>0</v>
-      </c>
-      <c r="F14" s="6">
+      <c r="E14" s="7">
+        <v>60.9</v>
+      </c>
+      <c r="F14" s="7">
+        <v>26.099999999999998</v>
+      </c>
+      <c r="G14" s="7">
+        <v>48.571428571428577</v>
+      </c>
+      <c r="H14" s="7">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="I14" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J14" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K14" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L14" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M14" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N14" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O14" s="7">
+        <v>367.96799933000028</v>
+      </c>
+      <c r="P14" s="7">
+        <v>73.631999899999997</v>
+      </c>
+      <c r="Q14" s="6">
         <f t="shared" si="1"/>
-        <v>34</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6">
+        <v>0</v>
+      </c>
+      <c r="R14" s="6">
+        <v>0</v>
+      </c>
+      <c r="S14" s="6">
+        <v>0</v>
+      </c>
+      <c r="T14" s="6">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="I14" s="6">
-        <v>0</v>
-      </c>
-      <c r="J14" s="6">
+        <v>5</v>
+      </c>
+      <c r="U14" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="V14" s="4"/>
+      <c r="W14" s="14">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K14" s="6">
-        <v>0</v>
-      </c>
-      <c r="L14" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="6">
-        <v>0</v>
-      </c>
-      <c r="N14" s="7">
-        <v>367.96799933000028</v>
-      </c>
-      <c r="O14" s="7">
-        <v>73.631999899999997</v>
-      </c>
-      <c r="P14" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>0</v>
-      </c>
-      <c r="R14" s="6">
-        <v>0</v>
-      </c>
-      <c r="S14" s="6">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="T14" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="U14" s="4"/>
-      <c r="V14" s="14">
-        <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="W14" s="6">
+      <c r="X14" s="6">
         <v>11353</v>
       </c>
-      <c r="X14" s="6">
+      <c r="Y14" s="6">
         <v>13895</v>
       </c>
-      <c r="Y14" s="6">
+      <c r="Z14" s="6">
         <v>9695</v>
       </c>
-      <c r="Z14" s="6">
+      <c r="AA14" s="6">
         <v>10870</v>
       </c>
-      <c r="AA14" s="6">
+      <c r="AB14" s="6">
         <v>1290</v>
       </c>
-      <c r="AB14" s="6">
+      <c r="AC14" s="6">
         <v>4124</v>
       </c>
-      <c r="AC14" s="6">
+      <c r="AD14" s="6">
         <v>419</v>
       </c>
-      <c r="AD14" s="6">
+      <c r="AE14" s="6">
         <v>3705</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>45914</v>
       </c>
@@ -26683,90 +26687,90 @@
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="E15" s="6">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6">
+      <c r="E15" s="7">
+        <v>48.3</v>
+      </c>
+      <c r="F15" s="7">
+        <v>20.7</v>
+      </c>
+      <c r="G15" s="7">
+        <v>112.85714285714286</v>
+      </c>
+      <c r="H15" s="7">
+        <v>23.7</v>
+      </c>
+      <c r="I15" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J15" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K15" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L15" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M15" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N15" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O15" s="7">
+        <v>400.39199936999995</v>
+      </c>
+      <c r="P15" s="7">
+        <v>87.527999910000005</v>
+      </c>
+      <c r="Q15" s="6">
         <f t="shared" si="1"/>
-        <v>79</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6">
+        <v>0</v>
+      </c>
+      <c r="S15" s="6">
+        <v>0</v>
+      </c>
+      <c r="T15" s="6">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="I15" s="6">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6">
-        <v>1</v>
-      </c>
-      <c r="K15" s="6">
-        <v>0</v>
-      </c>
-      <c r="L15" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="6">
-        <v>0</v>
-      </c>
-      <c r="N15" s="7">
-        <v>400.39199936999995</v>
-      </c>
-      <c r="O15" s="7">
-        <v>87.527999910000005</v>
-      </c>
-      <c r="P15" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="T15" s="6" t="s">
+      <c r="U15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U15" s="4"/>
-      <c r="V15" s="14">
-        <f t="shared" si="7"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="14">
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
-      <c r="W15" s="6">
+      <c r="X15" s="6">
         <v>11440</v>
       </c>
-      <c r="X15" s="6">
+      <c r="Y15" s="6">
         <v>13929</v>
       </c>
-      <c r="Y15" s="6">
+      <c r="Z15" s="6">
         <v>9697</v>
       </c>
-      <c r="Z15" s="6">
+      <c r="AA15" s="6">
         <v>10871</v>
       </c>
-      <c r="AA15" s="6">
+      <c r="AB15" s="6">
         <v>1290</v>
       </c>
-      <c r="AB15" s="6">
+      <c r="AC15" s="6">
         <v>4129</v>
       </c>
-      <c r="AC15" s="6">
+      <c r="AD15" s="6">
         <v>419</v>
       </c>
-      <c r="AD15" s="6">
+      <c r="AE15" s="6">
         <v>3710</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>45915</v>
       </c>
@@ -26780,91 +26784,90 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="E16" s="6">
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
+      <c r="E16" s="7">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="F16" s="7">
+        <v>8.1</v>
+      </c>
+      <c r="G16" s="7">
+        <v>54.285714285714292</v>
+      </c>
+      <c r="H16" s="7">
+        <v>11.4</v>
+      </c>
+      <c r="I16" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J16" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K16" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L16" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M16" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N16" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O16" s="7">
+        <v>406.27199932000008</v>
+      </c>
+      <c r="P16" s="7">
+        <v>77.615999909999999</v>
+      </c>
+      <c r="Q16" s="6">
         <f t="shared" si="1"/>
-        <v>38</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6">
+        <v>0</v>
+      </c>
+      <c r="S16" s="6">
+        <v>0</v>
+      </c>
+      <c r="T16" s="6">
         <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="I16" s="6">
-        <v>0</v>
-      </c>
-      <c r="J16" s="6">
-        <f t="shared" ref="J16:J31" si="8">Z17-Z16</f>
-        <v>1</v>
-      </c>
-      <c r="K16" s="6">
-        <v>0</v>
-      </c>
-      <c r="L16" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="6">
-        <v>0</v>
-      </c>
-      <c r="N16" s="7">
-        <v>406.27199932000008</v>
-      </c>
-      <c r="O16" s="7">
-        <v>77.615999909999999</v>
-      </c>
-      <c r="P16" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6">
-        <v>0</v>
-      </c>
-      <c r="S16" s="6">
-        <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="T16" s="6" t="s">
+      <c r="U16" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U16" s="4"/>
-      <c r="V16" s="14">
-        <f t="shared" si="7"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="14">
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="W16" s="16">
+      <c r="X16" s="16">
         <v>11509</v>
       </c>
-      <c r="X16" s="16">
+      <c r="Y16" s="16">
         <v>14008</v>
       </c>
-      <c r="Y16" s="16">
+      <c r="Z16" s="16">
         <v>9702</v>
       </c>
-      <c r="Z16" s="16">
+      <c r="AA16" s="16">
         <v>10871</v>
       </c>
-      <c r="AA16" s="16">
+      <c r="AB16" s="16">
         <v>1290</v>
       </c>
-      <c r="AB16" s="16">
+      <c r="AC16" s="16">
         <v>4135</v>
       </c>
-      <c r="AC16" s="16">
+      <c r="AD16" s="16">
         <v>419</v>
       </c>
-      <c r="AD16" s="16">
+      <c r="AE16" s="16">
         <v>3715</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>45916</v>
       </c>
@@ -26878,91 +26881,90 @@
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="E17" s="6">
-        <v>0</v>
-      </c>
-      <c r="F17" s="6">
+      <c r="E17" s="7">
+        <v>70</v>
+      </c>
+      <c r="F17" s="7">
+        <v>30</v>
+      </c>
+      <c r="G17" s="7">
+        <v>115.71428571428572</v>
+      </c>
+      <c r="H17" s="7">
+        <v>24.3</v>
+      </c>
+      <c r="I17" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J17" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K17" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L17" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M17" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N17" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O17" s="7">
+        <v>405.19199943000001</v>
+      </c>
+      <c r="P17" s="7">
+        <v>81.239999889999993</v>
+      </c>
+      <c r="Q17" s="6">
         <f t="shared" si="1"/>
-        <v>81</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6">
+        <v>1</v>
+      </c>
+      <c r="R17" s="6">
+        <v>0</v>
+      </c>
+      <c r="S17" s="6">
+        <v>0</v>
+      </c>
+      <c r="T17" s="6">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="I17" s="6">
-        <v>0</v>
-      </c>
-      <c r="J17" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="6">
-        <v>0</v>
-      </c>
-      <c r="L17" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M17" s="6">
-        <v>0</v>
-      </c>
-      <c r="N17" s="7">
-        <v>405.19199943000001</v>
-      </c>
-      <c r="O17" s="7">
-        <v>81.239999889999993</v>
-      </c>
-      <c r="P17" s="6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q17" s="6">
-        <v>0</v>
-      </c>
-      <c r="R17" s="6">
-        <v>0</v>
-      </c>
-      <c r="S17" s="6">
-        <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="T17" s="6" t="s">
+      <c r="U17" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U17" s="4"/>
-      <c r="V17" s="14">
-        <f t="shared" si="7"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="14">
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="W17" s="16">
+      <c r="X17" s="16">
         <v>11536</v>
       </c>
-      <c r="X17" s="16">
+      <c r="Y17" s="16">
         <v>14046</v>
       </c>
-      <c r="Y17" s="16">
+      <c r="Z17" s="16">
         <v>9709</v>
       </c>
-      <c r="Z17" s="16">
+      <c r="AA17" s="16">
         <v>10872</v>
       </c>
-      <c r="AA17" s="16">
+      <c r="AB17" s="16">
         <v>1290</v>
       </c>
-      <c r="AB17" s="16">
+      <c r="AC17" s="16">
         <v>4141</v>
       </c>
-      <c r="AC17" s="16">
+      <c r="AD17" s="16">
         <v>419</v>
       </c>
-      <c r="AD17" s="16">
+      <c r="AE17" s="16">
         <v>3721</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>45917</v>
       </c>
@@ -26976,91 +26978,90 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E18" s="6">
-        <v>0</v>
-      </c>
-      <c r="F18" s="6">
+      <c r="E18" s="7">
+        <v>0</v>
+      </c>
+      <c r="F18" s="7">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0</v>
+      </c>
+      <c r="I18" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J18" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K18" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L18" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M18" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N18" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O18" s="7">
+        <v>423.69599936999987</v>
+      </c>
+      <c r="P18" s="7">
+        <v>76.799999909999997</v>
+      </c>
+      <c r="Q18" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G18" s="6">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6">
+      <c r="R18" s="6">
+        <v>0</v>
+      </c>
+      <c r="S18" s="6">
+        <v>0</v>
+      </c>
+      <c r="T18" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I18" s="6">
-        <v>0</v>
-      </c>
-      <c r="J18" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="6">
-        <v>0</v>
-      </c>
-      <c r="L18" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="6">
-        <v>0</v>
-      </c>
-      <c r="N18" s="7">
-        <v>423.69599936999987</v>
-      </c>
-      <c r="O18" s="7">
-        <v>76.799999909999997</v>
-      </c>
-      <c r="P18" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6">
-        <v>0</v>
-      </c>
-      <c r="R18" s="6">
-        <v>0</v>
-      </c>
-      <c r="S18" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="6" t="s">
+      <c r="U18" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U18" s="4"/>
-      <c r="V18" s="14">
-        <f t="shared" si="7"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="14">
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="W18" s="16">
+      <c r="X18" s="16">
         <v>11636</v>
       </c>
-      <c r="X18" s="16">
+      <c r="Y18" s="16">
         <v>14127</v>
       </c>
-      <c r="Y18" s="16">
+      <c r="Z18" s="16">
         <v>9710</v>
       </c>
-      <c r="Z18" s="16">
+      <c r="AA18" s="16">
         <v>10872</v>
       </c>
-      <c r="AA18" s="16">
+      <c r="AB18" s="16">
         <v>1291</v>
       </c>
-      <c r="AB18" s="16">
+      <c r="AC18" s="16">
         <v>4148</v>
       </c>
-      <c r="AC18" s="16">
+      <c r="AD18" s="16">
         <v>420</v>
       </c>
-      <c r="AD18" s="16">
+      <c r="AE18" s="16">
         <v>3727</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>45918</v>
       </c>
@@ -27074,91 +27075,90 @@
         <f t="shared" si="0"/>
         <v>213</v>
       </c>
-      <c r="E19" s="6">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6">
+      <c r="E19" s="7">
+        <v>149.1</v>
+      </c>
+      <c r="F19" s="7">
+        <v>63.9</v>
+      </c>
+      <c r="G19" s="7">
+        <v>261.42857142857144</v>
+      </c>
+      <c r="H19" s="7">
+        <v>54.9</v>
+      </c>
+      <c r="I19" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J19" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K19" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L19" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M19" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N19" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O19" s="7">
+        <v>403.96799934999984</v>
+      </c>
+      <c r="P19" s="7">
+        <v>72.023999910000001</v>
+      </c>
+      <c r="Q19" s="6">
         <f t="shared" si="1"/>
-        <v>183</v>
-      </c>
-      <c r="G19" s="6">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6">
+        <v>1</v>
+      </c>
+      <c r="R19" s="6">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6">
         <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="I19" s="6">
-        <v>0</v>
-      </c>
-      <c r="J19" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="6">
-        <v>0</v>
-      </c>
-      <c r="L19" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="6">
-        <v>0</v>
-      </c>
-      <c r="N19" s="7">
-        <v>403.96799934999984</v>
-      </c>
-      <c r="O19" s="7">
-        <v>72.023999910000001</v>
-      </c>
-      <c r="P19" s="6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6">
-        <v>0</v>
-      </c>
-      <c r="S19" s="6">
-        <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="T19" s="6" t="s">
+      <c r="U19" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U19" s="17"/>
-      <c r="V19" s="18">
-        <f t="shared" si="7"/>
+      <c r="V19" s="17"/>
+      <c r="W19" s="18">
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="W19" s="16">
+      <c r="X19" s="16">
         <v>11636</v>
       </c>
-      <c r="X19" s="16">
+      <c r="Y19" s="16">
         <v>14127</v>
       </c>
-      <c r="Y19" s="16">
+      <c r="Z19" s="16">
         <v>9710</v>
       </c>
-      <c r="Z19" s="16">
+      <c r="AA19" s="16">
         <v>10872</v>
       </c>
-      <c r="AA19" s="16">
+      <c r="AB19" s="16">
         <v>1291</v>
       </c>
-      <c r="AB19" s="16">
+      <c r="AC19" s="16">
         <v>4148</v>
       </c>
-      <c r="AC19" s="16">
+      <c r="AD19" s="16">
         <v>420</v>
       </c>
-      <c r="AD19" s="16">
+      <c r="AE19" s="16">
         <v>3727</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>45919</v>
       </c>
@@ -27172,91 +27172,90 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E20" s="6">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
+      <c r="E20" s="7">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7">
+        <v>0</v>
+      </c>
+      <c r="I20" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J20" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K20" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L20" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M20" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N20" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O20" s="7">
+        <v>389.75999933999992</v>
+      </c>
+      <c r="P20" s="7">
+        <v>51.623999920000003</v>
+      </c>
+      <c r="Q20" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G20" s="6">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6">
+      <c r="R20" s="6">
+        <v>0</v>
+      </c>
+      <c r="S20" s="6">
+        <v>0</v>
+      </c>
+      <c r="T20" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I20" s="6">
-        <v>0</v>
-      </c>
-      <c r="J20" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="6">
-        <v>0</v>
-      </c>
-      <c r="L20" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="6">
-        <v>0</v>
-      </c>
-      <c r="N20" s="7">
-        <v>389.75999933999992</v>
-      </c>
-      <c r="O20" s="7">
-        <v>51.623999920000003</v>
-      </c>
-      <c r="P20" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="6">
-        <v>0</v>
-      </c>
-      <c r="R20" s="6">
-        <v>0</v>
-      </c>
-      <c r="S20" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T20" s="6" t="s">
+      <c r="U20" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U20" s="4"/>
-      <c r="V20" s="18">
-        <f t="shared" si="7"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="18">
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="W20" s="15">
+      <c r="X20" s="15">
         <v>11849</v>
       </c>
-      <c r="X20" s="15">
+      <c r="Y20" s="15">
         <v>14310</v>
       </c>
-      <c r="Y20" s="15">
+      <c r="Z20" s="15">
         <v>9722</v>
       </c>
-      <c r="Z20" s="15">
+      <c r="AA20" s="15">
         <v>10872</v>
       </c>
-      <c r="AA20" s="15">
+      <c r="AB20" s="15">
         <v>1291</v>
       </c>
-      <c r="AB20" s="15">
+      <c r="AC20" s="15">
         <v>4154</v>
       </c>
-      <c r="AC20" s="15">
+      <c r="AD20" s="15">
         <v>421</v>
       </c>
-      <c r="AD20" s="15">
+      <c r="AE20" s="15">
         <v>3732</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>45920</v>
       </c>
@@ -27270,91 +27269,90 @@
         <f t="shared" si="0"/>
         <v>147</v>
       </c>
-      <c r="E21" s="6">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6">
+      <c r="E21" s="7">
+        <v>102.89999999999999</v>
+      </c>
+      <c r="F21" s="7">
+        <v>44.1</v>
+      </c>
+      <c r="G21" s="7">
+        <v>188.57142857142858</v>
+      </c>
+      <c r="H21" s="7">
+        <v>39.6</v>
+      </c>
+      <c r="I21" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J21" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K21" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L21" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M21" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N21" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O21" s="7">
+        <v>343.05599934999992</v>
+      </c>
+      <c r="P21" s="7">
+        <v>68.111999879999985</v>
+      </c>
+      <c r="Q21" s="6">
         <f t="shared" si="1"/>
-        <v>132</v>
-      </c>
-      <c r="G21" s="6">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6">
+        <v>3</v>
+      </c>
+      <c r="R21" s="6">
+        <v>0</v>
+      </c>
+      <c r="S21" s="6">
+        <v>0</v>
+      </c>
+      <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="I21" s="6">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6">
-        <f t="shared" si="8"/>
-        <v>6</v>
-      </c>
-      <c r="K21" s="6">
-        <v>0</v>
-      </c>
-      <c r="L21" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M21" s="6">
-        <v>0</v>
-      </c>
-      <c r="N21" s="7">
-        <v>343.05599934999992</v>
-      </c>
-      <c r="O21" s="7">
-        <v>68.111999879999985</v>
-      </c>
-      <c r="P21" s="6">
-        <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="Q21" s="6">
-        <v>0</v>
-      </c>
-      <c r="R21" s="6">
-        <v>0</v>
-      </c>
-      <c r="S21" s="6">
-        <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="T21" s="6" t="s">
+      <c r="U21" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U21" s="4"/>
-      <c r="V21" s="18">
-        <f t="shared" si="7"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="18">
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="W21" s="15">
+      <c r="X21" s="15">
         <v>11849</v>
       </c>
-      <c r="X21" s="15">
+      <c r="Y21" s="15">
         <v>14310</v>
       </c>
-      <c r="Y21" s="15">
+      <c r="Z21" s="15">
         <v>9722</v>
       </c>
-      <c r="Z21" s="15">
+      <c r="AA21" s="15">
         <v>10872</v>
       </c>
-      <c r="AA21" s="15">
+      <c r="AB21" s="15">
         <v>1291</v>
       </c>
-      <c r="AB21" s="15">
+      <c r="AC21" s="15">
         <v>4154</v>
       </c>
-      <c r="AC21" s="15">
+      <c r="AD21" s="15">
         <v>421</v>
       </c>
-      <c r="AD21" s="15">
+      <c r="AE21" s="15">
         <v>3732</v>
       </c>
     </row>
-    <row r="22" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>45921</v>
       </c>
@@ -27368,91 +27366,90 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E22" s="6">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
+      <c r="E22" s="7">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7">
+        <v>0</v>
+      </c>
+      <c r="I22" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J22" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K22" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L22" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M22" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N22" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O22" s="7">
+        <v>426.88799933000007</v>
+      </c>
+      <c r="P22" s="7">
+        <v>85.679999879999997</v>
+      </c>
+      <c r="Q22" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G22" s="6">
-        <v>0</v>
-      </c>
-      <c r="H22" s="6">
+      <c r="R22" s="6">
+        <v>0</v>
+      </c>
+      <c r="S22" s="6">
+        <v>0</v>
+      </c>
+      <c r="T22" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I22" s="6">
-        <v>0</v>
-      </c>
-      <c r="J22" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="6">
-        <v>0</v>
-      </c>
-      <c r="L22" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="6">
-        <v>0</v>
-      </c>
-      <c r="N22" s="7">
-        <v>426.88799933000007</v>
-      </c>
-      <c r="O22" s="7">
-        <v>85.679999879999997</v>
-      </c>
-      <c r="P22" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="6">
-        <v>0</v>
-      </c>
-      <c r="R22" s="6">
-        <v>0</v>
-      </c>
-      <c r="S22" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T22" s="6" t="s">
+      <c r="U22" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U22" s="4"/>
-      <c r="V22" s="18">
-        <f t="shared" si="7"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="18">
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="W22" s="15">
+      <c r="X22" s="15">
         <v>11996</v>
       </c>
-      <c r="X22" s="15">
+      <c r="Y22" s="15">
         <v>14442</v>
       </c>
-      <c r="Y22" s="15">
+      <c r="Z22" s="15">
         <v>9731</v>
       </c>
-      <c r="Z22" s="15">
+      <c r="AA22" s="15">
         <v>10878</v>
       </c>
-      <c r="AA22" s="15">
+      <c r="AB22" s="15">
         <v>1292</v>
       </c>
-      <c r="AB22" s="15">
+      <c r="AC22" s="15">
         <v>4171</v>
       </c>
-      <c r="AC22" s="15">
+      <c r="AD22" s="15">
         <v>424</v>
       </c>
-      <c r="AD22" s="15">
+      <c r="AE22" s="15">
         <v>3747</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>45922</v>
       </c>
@@ -27466,91 +27463,90 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="E23" s="6">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6">
+      <c r="E23" s="7">
+        <v>36.4</v>
+      </c>
+      <c r="F23" s="7">
+        <v>15.6</v>
+      </c>
+      <c r="G23" s="7">
+        <v>130</v>
+      </c>
+      <c r="H23" s="7">
+        <v>27.3</v>
+      </c>
+      <c r="I23" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J23" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K23" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L23" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M23" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N23" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O23" s="7">
+        <v>318.64799941000012</v>
+      </c>
+      <c r="P23" s="7">
+        <v>49.055999909999997</v>
+      </c>
+      <c r="Q23" s="6">
         <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
-      <c r="G23" s="6">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6">
+        <v>0</v>
+      </c>
+      <c r="R23" s="6">
+        <v>0</v>
+      </c>
+      <c r="S23" s="6">
+        <v>0</v>
+      </c>
+      <c r="T23" s="6">
         <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="I23" s="6">
-        <v>0</v>
-      </c>
-      <c r="J23" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="6">
-        <v>0</v>
-      </c>
-      <c r="L23" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="6">
-        <v>0</v>
-      </c>
-      <c r="N23" s="7">
-        <v>318.64799941000012</v>
-      </c>
-      <c r="O23" s="7">
-        <v>49.055999909999997</v>
-      </c>
-      <c r="P23" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="6">
-        <v>0</v>
-      </c>
-      <c r="R23" s="6">
-        <v>0</v>
-      </c>
-      <c r="S23" s="6">
-        <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="T23" s="6" t="s">
+      <c r="U23" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="U23" s="4"/>
-      <c r="V23" s="18">
-        <f t="shared" si="7"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="18">
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="W23" s="15">
+      <c r="X23" s="15">
         <v>11996</v>
       </c>
-      <c r="X23" s="15">
+      <c r="Y23" s="15">
         <v>14442</v>
       </c>
-      <c r="Y23" s="15">
+      <c r="Z23" s="15">
         <v>9731</v>
       </c>
-      <c r="Z23" s="15">
+      <c r="AA23" s="15">
         <v>10878</v>
       </c>
-      <c r="AA23" s="15">
+      <c r="AB23" s="15">
         <v>1292</v>
       </c>
-      <c r="AB23" s="15">
+      <c r="AC23" s="15">
         <v>4171</v>
       </c>
-      <c r="AC23" s="15">
+      <c r="AD23" s="15">
         <v>424</v>
       </c>
-      <c r="AD23" s="15">
+      <c r="AE23" s="15">
         <v>3747</v>
       </c>
     </row>
-    <row r="24" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>45923</v>
       </c>
@@ -27564,91 +27560,90 @@
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="E24" s="6">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
+      <c r="E24" s="7">
+        <v>44.8</v>
+      </c>
+      <c r="F24" s="7">
+        <v>19.2</v>
+      </c>
+      <c r="G24" s="7">
+        <v>81.428571428571431</v>
+      </c>
+      <c r="H24" s="7">
+        <v>17.099999999999998</v>
+      </c>
+      <c r="I24" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J24" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K24" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L24" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M24" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N24" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O24" s="7">
+        <v>332.99999931000008</v>
+      </c>
+      <c r="P24" s="7">
+        <v>70.559999899999994</v>
+      </c>
+      <c r="Q24" s="6">
         <f t="shared" si="1"/>
-        <v>57</v>
-      </c>
-      <c r="G24" s="6">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6">
+        <v>0</v>
+      </c>
+      <c r="R24" s="6">
+        <v>0</v>
+      </c>
+      <c r="S24" s="6">
+        <v>0</v>
+      </c>
+      <c r="T24" s="6">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="I24" s="6">
-        <v>0</v>
-      </c>
-      <c r="J24" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="6">
-        <v>0</v>
-      </c>
-      <c r="L24" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="6">
-        <v>0</v>
-      </c>
-      <c r="N24" s="7">
-        <v>332.99999931000008</v>
-      </c>
-      <c r="O24" s="7">
-        <v>70.559999899999994</v>
-      </c>
-      <c r="P24" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="6">
-        <v>0</v>
-      </c>
-      <c r="R24" s="6">
-        <v>0</v>
-      </c>
-      <c r="S24" s="6">
-        <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="T24" s="6" t="s">
+      <c r="U24" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="U24" s="4"/>
-      <c r="V24" s="18">
-        <f t="shared" si="7"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="18">
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="W24" s="15">
+      <c r="X24" s="15">
         <v>12048</v>
       </c>
-      <c r="X24" s="15">
+      <c r="Y24" s="15">
         <v>14533</v>
       </c>
-      <c r="Y24" s="15">
+      <c r="Z24" s="15">
         <v>9742</v>
       </c>
-      <c r="Z24" s="15">
+      <c r="AA24" s="15">
         <v>10878</v>
       </c>
-      <c r="AA24" s="15">
+      <c r="AB24" s="15">
         <v>1292</v>
       </c>
-      <c r="AB24" s="15">
+      <c r="AC24" s="15">
         <v>4179</v>
       </c>
-      <c r="AC24" s="15">
+      <c r="AD24" s="15">
         <v>424</v>
       </c>
-      <c r="AD24" s="15">
+      <c r="AE24" s="15">
         <v>3755</v>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>45924</v>
       </c>
@@ -27662,91 +27657,90 @@
         <f t="shared" si="0"/>
         <v>99</v>
       </c>
-      <c r="E25" s="6">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6">
+      <c r="E25" s="7">
+        <v>69.3</v>
+      </c>
+      <c r="F25" s="7">
+        <v>29.7</v>
+      </c>
+      <c r="G25" s="7">
+        <v>198.57142857142858</v>
+      </c>
+      <c r="H25" s="7">
+        <v>41.699999999999996</v>
+      </c>
+      <c r="I25" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J25" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K25" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L25" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M25" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N25" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O25" s="7">
+        <v>366.23999934000011</v>
+      </c>
+      <c r="P25" s="7">
+        <v>78.095999899999981</v>
+      </c>
+      <c r="Q25" s="6">
         <f t="shared" si="1"/>
-        <v>139</v>
-      </c>
-      <c r="G25" s="6">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6">
+        <v>0</v>
+      </c>
+      <c r="R25" s="6">
+        <v>0</v>
+      </c>
+      <c r="S25" s="6">
+        <v>0</v>
+      </c>
+      <c r="T25" s="6">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="I25" s="6">
-        <v>0</v>
-      </c>
-      <c r="J25" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="6">
-        <v>0</v>
-      </c>
-      <c r="L25" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="6">
-        <v>0</v>
-      </c>
-      <c r="N25" s="7">
-        <v>366.23999934000011</v>
-      </c>
-      <c r="O25" s="7">
-        <v>78.095999899999981</v>
-      </c>
-      <c r="P25" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>0</v>
-      </c>
-      <c r="R25" s="6">
-        <v>0</v>
-      </c>
-      <c r="S25" s="6">
-        <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="T25" s="6" t="s">
+      <c r="U25" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="U25" s="4"/>
-      <c r="V25" s="18">
-        <f t="shared" si="7"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="18">
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
-      <c r="W25" s="15">
+      <c r="X25" s="15">
         <v>12112</v>
       </c>
-      <c r="X25" s="15">
+      <c r="Y25" s="15">
         <v>14590</v>
       </c>
-      <c r="Y25" s="15">
+      <c r="Z25" s="15">
         <v>9745</v>
       </c>
-      <c r="Z25" s="15">
+      <c r="AA25" s="15">
         <v>10878</v>
       </c>
-      <c r="AA25" s="15">
+      <c r="AB25" s="15">
         <v>1292</v>
       </c>
-      <c r="AB25" s="15">
+      <c r="AC25" s="15">
         <v>4187</v>
       </c>
-      <c r="AC25" s="15">
+      <c r="AD25" s="15">
         <v>424</v>
       </c>
-      <c r="AD25" s="15">
+      <c r="AE25" s="15">
         <v>3762</v>
       </c>
     </row>
-    <row r="26" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>45925</v>
       </c>
@@ -27760,91 +27754,90 @@
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="E26" s="6">
-        <v>0</v>
-      </c>
-      <c r="F26" s="6">
+      <c r="E26" s="7">
+        <v>53.9</v>
+      </c>
+      <c r="F26" s="7">
+        <v>23.099999999999998</v>
+      </c>
+      <c r="G26" s="7">
+        <v>145.71428571428572</v>
+      </c>
+      <c r="H26" s="7">
+        <v>30.599999999999998</v>
+      </c>
+      <c r="I26" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J26" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K26" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L26" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M26" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N26" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O26" s="7">
+        <v>313.89599937000008</v>
+      </c>
+      <c r="P26" s="7">
+        <v>70.655999910000006</v>
+      </c>
+      <c r="Q26" s="6">
         <f t="shared" si="1"/>
-        <v>102</v>
-      </c>
-      <c r="G26" s="6">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6">
+        <v>2</v>
+      </c>
+      <c r="R26" s="6">
+        <v>0</v>
+      </c>
+      <c r="S26" s="6">
+        <v>0</v>
+      </c>
+      <c r="T26" s="6">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="I26" s="6">
-        <v>0</v>
-      </c>
-      <c r="J26" s="6">
-        <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="K26" s="6">
-        <v>0</v>
-      </c>
-      <c r="L26" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="6">
-        <v>0</v>
-      </c>
-      <c r="N26" s="7">
-        <v>313.89599937000008</v>
-      </c>
-      <c r="O26" s="7">
-        <v>70.655999910000006</v>
-      </c>
-      <c r="P26" s="6">
-        <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="Q26" s="6">
-        <v>0</v>
-      </c>
-      <c r="R26" s="6">
-        <v>0</v>
-      </c>
-      <c r="S26" s="6">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="T26" s="6" t="s">
+      <c r="U26" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="U26" s="4"/>
-      <c r="V26" s="20">
-        <f t="shared" si="7"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="20">
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="W26" s="21">
+      <c r="X26" s="21">
         <v>12211</v>
       </c>
-      <c r="X26" s="21">
+      <c r="Y26" s="21">
         <v>14729</v>
       </c>
-      <c r="Y26" s="21">
+      <c r="Z26" s="21">
         <v>9749</v>
       </c>
-      <c r="Z26" s="21">
+      <c r="AA26" s="21">
         <v>10878</v>
       </c>
-      <c r="AA26" s="21">
+      <c r="AB26" s="21">
         <v>1292</v>
       </c>
-      <c r="AB26" s="21">
+      <c r="AC26" s="21">
         <v>4193</v>
       </c>
-      <c r="AC26" s="21">
+      <c r="AD26" s="21">
         <v>424</v>
       </c>
-      <c r="AD26" s="21">
+      <c r="AE26" s="21">
         <v>3767</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>45926</v>
       </c>
@@ -27858,91 +27851,90 @@
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="E27" s="6">
-        <v>0</v>
-      </c>
-      <c r="F27" s="6">
+      <c r="E27" s="7">
+        <v>62.3</v>
+      </c>
+      <c r="F27" s="7">
+        <v>26.7</v>
+      </c>
+      <c r="G27" s="7">
+        <v>170</v>
+      </c>
+      <c r="H27" s="7">
+        <v>35.699999999999996</v>
+      </c>
+      <c r="I27" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J27" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K27" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L27" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M27" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N27" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O27" s="7">
+        <v>294.14399926999988</v>
+      </c>
+      <c r="P27" s="7">
+        <v>51.311999899999996</v>
+      </c>
+      <c r="Q27" s="6">
         <f t="shared" si="1"/>
-        <v>119</v>
-      </c>
-      <c r="G27" s="6">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6">
+        <v>1</v>
+      </c>
+      <c r="R27" s="6">
+        <v>0</v>
+      </c>
+      <c r="S27" s="6">
+        <v>0</v>
+      </c>
+      <c r="T27" s="6">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="6">
-        <v>0</v>
-      </c>
-      <c r="J27" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="6">
-        <v>0</v>
-      </c>
-      <c r="L27" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="M27" s="6">
-        <v>0</v>
-      </c>
-      <c r="N27" s="7">
-        <v>294.14399926999988</v>
-      </c>
-      <c r="O27" s="7">
-        <v>51.311999899999996</v>
-      </c>
-      <c r="P27" s="6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q27" s="6">
-        <v>0</v>
-      </c>
-      <c r="R27" s="6">
-        <v>0</v>
-      </c>
-      <c r="S27" s="6">
-        <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="T27" s="6" t="s">
+      <c r="U27" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="U27" s="4"/>
-      <c r="V27" s="18">
-        <f t="shared" si="7"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="18">
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="W27" s="15">
+      <c r="X27" s="15">
         <v>12288</v>
       </c>
-      <c r="X27" s="15">
+      <c r="Y27" s="15">
         <v>14831</v>
       </c>
-      <c r="Y27" s="15">
+      <c r="Z27" s="15">
         <v>9754</v>
       </c>
-      <c r="Z27" s="15">
+      <c r="AA27" s="15">
         <v>10882</v>
       </c>
-      <c r="AA27" s="15">
+      <c r="AB27" s="15">
         <v>1292</v>
       </c>
-      <c r="AB27" s="15">
+      <c r="AC27" s="15">
         <v>4198</v>
       </c>
-      <c r="AC27" s="15">
+      <c r="AD27" s="15">
         <v>426</v>
       </c>
-      <c r="AD27" s="15">
+      <c r="AE27" s="15">
         <v>3771</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>45927</v>
       </c>
@@ -27956,91 +27948,90 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="6">
-        <v>0</v>
-      </c>
-      <c r="F28" s="6">
+      <c r="E28" s="7">
+        <v>0</v>
+      </c>
+      <c r="F28" s="7">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7">
+        <v>0</v>
+      </c>
+      <c r="I28" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J28" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K28" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L28" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M28" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N28" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O28" s="7">
+        <v>308.3279993700001</v>
+      </c>
+      <c r="P28" s="7">
+        <v>59.975999919999992</v>
+      </c>
+      <c r="Q28" s="6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G28" s="6">
-        <v>0</v>
-      </c>
-      <c r="H28" s="6">
+      <c r="R28" s="6">
+        <v>0</v>
+      </c>
+      <c r="S28" s="6">
+        <v>0</v>
+      </c>
+      <c r="T28" s="6">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I28" s="6">
-        <v>0</v>
-      </c>
-      <c r="J28" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="6">
-        <v>0</v>
-      </c>
-      <c r="L28" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M28" s="6">
-        <v>0</v>
-      </c>
-      <c r="N28" s="7">
-        <v>308.3279993700001</v>
-      </c>
-      <c r="O28" s="7">
-        <v>59.975999919999992</v>
-      </c>
-      <c r="P28" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="6">
-        <v>0</v>
-      </c>
-      <c r="R28" s="6">
-        <v>0</v>
-      </c>
-      <c r="S28" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T28" s="6" t="s">
+      <c r="U28" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U28" s="4"/>
-      <c r="V28" s="18">
-        <f t="shared" si="7"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="18">
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="W28" s="15">
+      <c r="X28" s="15">
         <v>12377</v>
       </c>
-      <c r="X28" s="15">
+      <c r="Y28" s="15">
         <v>14950</v>
       </c>
-      <c r="Y28" s="15">
+      <c r="Z28" s="15">
         <v>9754</v>
       </c>
-      <c r="Z28" s="15">
+      <c r="AA28" s="15">
         <v>10882</v>
       </c>
-      <c r="AA28" s="15">
+      <c r="AB28" s="15">
         <v>1293</v>
       </c>
-      <c r="AB28" s="15">
+      <c r="AC28" s="15">
         <v>4200</v>
       </c>
-      <c r="AC28" s="15">
+      <c r="AD28" s="15">
         <v>427</v>
       </c>
-      <c r="AD28" s="15">
+      <c r="AE28" s="15">
         <v>3773</v>
       </c>
     </row>
-    <row r="29" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:31" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>45928</v>
       </c>
@@ -28054,91 +28045,90 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="E29" s="6">
-        <v>0</v>
-      </c>
-      <c r="F29" s="6">
+      <c r="E29" s="7">
+        <v>30.799999999999997</v>
+      </c>
+      <c r="F29" s="7">
+        <v>13.2</v>
+      </c>
+      <c r="G29" s="7">
+        <v>182.85714285714286</v>
+      </c>
+      <c r="H29" s="7">
+        <v>38.4</v>
+      </c>
+      <c r="I29" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J29" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K29" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L29" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M29" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N29" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O29" s="7">
+        <v>302.78399932999992</v>
+      </c>
+      <c r="P29" s="7">
+        <v>69.263999890000008</v>
+      </c>
+      <c r="Q29" s="6">
         <f t="shared" si="1"/>
-        <v>128</v>
-      </c>
-      <c r="G29" s="6">
-        <v>0</v>
-      </c>
-      <c r="H29" s="6">
+        <v>0</v>
+      </c>
+      <c r="R29" s="6">
+        <v>0</v>
+      </c>
+      <c r="S29" s="6">
+        <v>0</v>
+      </c>
+      <c r="T29" s="6">
         <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="I29" s="6">
-        <v>0</v>
-      </c>
-      <c r="J29" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="6">
-        <v>0</v>
-      </c>
-      <c r="L29" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="6">
-        <v>0</v>
-      </c>
-      <c r="N29" s="7">
-        <v>302.78399932999992</v>
-      </c>
-      <c r="O29" s="7">
-        <v>69.263999890000008</v>
-      </c>
-      <c r="P29" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="6">
-        <v>0</v>
-      </c>
-      <c r="R29" s="6">
-        <v>0</v>
-      </c>
-      <c r="S29" s="6">
-        <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="T29" s="6" t="s">
+      <c r="U29" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="U29" s="4"/>
-      <c r="V29" s="18">
-        <f t="shared" si="7"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="18">
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
-      <c r="W29" s="15">
+      <c r="X29" s="15">
         <v>12377</v>
       </c>
-      <c r="X29" s="15">
+      <c r="Y29" s="15">
         <v>14950</v>
       </c>
-      <c r="Y29" s="15">
+      <c r="Z29" s="15">
         <v>9754</v>
       </c>
-      <c r="Z29" s="15">
+      <c r="AA29" s="15">
         <v>10882</v>
       </c>
-      <c r="AA29" s="15">
+      <c r="AB29" s="15">
         <v>1293</v>
       </c>
-      <c r="AB29" s="15">
+      <c r="AC29" s="15">
         <v>4200</v>
       </c>
-      <c r="AC29" s="15">
+      <c r="AD29" s="15">
         <v>427</v>
       </c>
-      <c r="AD29" s="15">
+      <c r="AE29" s="15">
         <v>3773</v>
       </c>
     </row>
-    <row r="30" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:31" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>45929</v>
       </c>
@@ -28152,91 +28142,90 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="E30" s="6">
-        <v>0</v>
-      </c>
-      <c r="F30" s="6">
+      <c r="E30" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="F30" s="7">
+        <v>14.399999999999999</v>
+      </c>
+      <c r="G30" s="7">
+        <v>175.71428571428572</v>
+      </c>
+      <c r="H30" s="7">
+        <v>36.9</v>
+      </c>
+      <c r="I30" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J30" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K30" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L30" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M30" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N30" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O30" s="7">
+        <v>338.44799930999977</v>
+      </c>
+      <c r="P30" s="7">
+        <v>70.559999919999996</v>
+      </c>
+      <c r="Q30" s="6">
         <f t="shared" si="1"/>
-        <v>123</v>
-      </c>
-      <c r="G30" s="6">
-        <v>0</v>
-      </c>
-      <c r="H30" s="6">
+        <v>0</v>
+      </c>
+      <c r="R30" s="6">
+        <v>0</v>
+      </c>
+      <c r="S30" s="6">
+        <v>0</v>
+      </c>
+      <c r="T30" s="6">
         <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="I30" s="6">
-        <v>0</v>
-      </c>
-      <c r="J30" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="6">
-        <v>0</v>
-      </c>
-      <c r="L30" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M30" s="6">
-        <v>0</v>
-      </c>
-      <c r="N30" s="7">
-        <v>338.44799930999977</v>
-      </c>
-      <c r="O30" s="7">
-        <v>70.559999919999996</v>
-      </c>
-      <c r="P30" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="6">
-        <v>0</v>
-      </c>
-      <c r="R30" s="6">
-        <v>0</v>
-      </c>
-      <c r="S30" s="6">
-        <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="T30" s="6" t="s">
+      <c r="U30" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="U30" s="4"/>
-      <c r="V30" s="18">
-        <f t="shared" si="7"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="18">
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="W30" s="15">
+      <c r="X30" s="15">
         <v>12421</v>
       </c>
-      <c r="X30" s="15">
+      <c r="Y30" s="15">
         <v>15078</v>
       </c>
-      <c r="Y30" s="15">
+      <c r="Z30" s="15">
         <v>9763</v>
       </c>
-      <c r="Z30" s="15">
+      <c r="AA30" s="15">
         <v>10882</v>
       </c>
-      <c r="AA30" s="15">
+      <c r="AB30" s="15">
         <v>1293</v>
       </c>
-      <c r="AB30" s="15">
+      <c r="AC30" s="15">
         <v>4204</v>
       </c>
-      <c r="AC30" s="15">
+      <c r="AD30" s="15">
         <v>427</v>
       </c>
-      <c r="AD30" s="15">
+      <c r="AE30" s="15">
         <v>3777</v>
       </c>
     </row>
-    <row r="31" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:31" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>45930</v>
       </c>
@@ -28250,133 +28239,132 @@
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
-      <c r="E31" s="6">
-        <v>0</v>
-      </c>
-      <c r="F31" s="6">
+      <c r="E31" s="7">
+        <v>71.399999999999991</v>
+      </c>
+      <c r="F31" s="7">
+        <v>30.599999999999998</v>
+      </c>
+      <c r="G31" s="7">
+        <v>155.71428571428572</v>
+      </c>
+      <c r="H31" s="7">
+        <v>32.699999999999996</v>
+      </c>
+      <c r="I31" s="7">
+        <v>127.86666666666665</v>
+      </c>
+      <c r="J31" s="7">
+        <v>54.8</v>
+      </c>
+      <c r="K31" s="7">
+        <v>31.733333333333331</v>
+      </c>
+      <c r="L31" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="M31" s="7">
+        <v>33.599999999999994</v>
+      </c>
+      <c r="N31" s="7">
+        <v>14.4</v>
+      </c>
+      <c r="O31" s="7">
+        <v>363.47999940999978</v>
+      </c>
+      <c r="P31" s="7">
+        <v>71.927999900000003</v>
+      </c>
+      <c r="Q31" s="6">
         <f t="shared" si="1"/>
-        <v>109</v>
-      </c>
-      <c r="G31" s="6">
-        <v>0</v>
-      </c>
-      <c r="H31" s="6">
+        <v>1</v>
+      </c>
+      <c r="R31" s="6">
+        <v>0</v>
+      </c>
+      <c r="S31" s="6">
+        <v>0</v>
+      </c>
+      <c r="T31" s="6">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="I31" s="6">
-        <v>0</v>
-      </c>
-      <c r="J31" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="6">
-        <v>0</v>
-      </c>
-      <c r="L31" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M31" s="6">
-        <v>0</v>
-      </c>
-      <c r="N31" s="7">
-        <v>363.47999940999978</v>
-      </c>
-      <c r="O31" s="7">
-        <v>71.927999900000003</v>
-      </c>
-      <c r="P31" s="6">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>0</v>
-      </c>
-      <c r="R31" s="6">
-        <v>0</v>
-      </c>
-      <c r="S31" s="6">
-        <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="T31" s="6" t="s">
+      <c r="U31" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="U31" s="4"/>
-      <c r="V31" s="18">
-        <f t="shared" si="7"/>
+      <c r="V31" s="4"/>
+      <c r="W31" s="18">
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
-      <c r="W31" s="15">
+      <c r="X31" s="15">
         <v>12469</v>
       </c>
-      <c r="X31" s="15">
+      <c r="Y31" s="15">
         <v>15201</v>
       </c>
-      <c r="Y31" s="15">
+      <c r="Z31" s="15">
         <v>9772</v>
       </c>
-      <c r="Z31" s="15">
+      <c r="AA31" s="15">
         <v>10882</v>
       </c>
-      <c r="AA31" s="15">
+      <c r="AB31" s="15">
         <v>1293</v>
       </c>
-      <c r="AB31" s="15">
+      <c r="AC31" s="15">
         <v>4216</v>
       </c>
-      <c r="AC31" s="15">
+      <c r="AD31" s="15">
         <v>427</v>
       </c>
-      <c r="AD31" s="15">
+      <c r="AE31" s="15">
         <v>3788</v>
       </c>
     </row>
-    <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:31" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B32" s="27"/>
       <c r="C32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="Q32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="J32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="N32" s="27"/>
+      <c r="P32" s="27"/>
       <c r="R32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="18">
-        <f t="shared" si="7"/>
+      <c r="S32" s="27"/>
+      <c r="U32" s="27"/>
+      <c r="V32" s="4"/>
+      <c r="W32" s="18">
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="W32" s="15">
+      <c r="X32" s="15">
         <v>12571</v>
       </c>
-      <c r="X32" s="15">
+      <c r="Y32" s="15">
         <v>15310</v>
       </c>
-      <c r="Y32" s="15">
+      <c r="Z32" s="15">
         <v>9775</v>
       </c>
-      <c r="Z32" s="15">
+      <c r="AA32" s="15">
         <v>10882</v>
       </c>
-      <c r="AA32" s="15">
+      <c r="AB32" s="15">
         <v>1293</v>
       </c>
-      <c r="AB32" s="15">
+      <c r="AC32" s="15">
         <v>4222</v>
       </c>
-      <c r="AC32" s="15">
+      <c r="AD32" s="15">
         <v>428</v>
       </c>
-      <c r="AD32" s="15">
+      <c r="AE32" s="15">
         <v>3793</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="51"/>
       <c r="C34" s="51"/>
@@ -28386,8 +28374,9 @@
       <c r="G34" s="51"/>
       <c r="H34" s="51"/>
       <c r="I34" s="51"/>
-    </row>
-    <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J34" s="51"/>
+    </row>
+    <row r="35" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -28397,8 +28386,9 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
-    </row>
-    <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -28408,8 +28398,9 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
-    </row>
-    <row r="37" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -28419,8 +28410,11 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
-    </row>
-    <row r="38" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J37" s="1"/>
+      <c r="N37" s="50"/>
+      <c r="O37" s="50"/>
+    </row>
+    <row r="38" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -28430,8 +28424,9 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -28441,8 +28436,9 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -28452,8 +28448,9 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -28463,8 +28460,9 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -28474,8 +28472,9 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -28485,8 +28484,9 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -28496,8 +28496,9 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-    </row>
-    <row r="45" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -28507,8 +28508,9 @@
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
-    </row>
-    <row r="46" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J45" s="1"/>
+    </row>
+    <row r="46" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -28518,8 +28520,9 @@
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
-    </row>
-    <row r="47" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -28529,8 +28532,9 @@
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
-    </row>
-    <row r="48" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -28540,8 +28544,9 @@
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
-    </row>
-    <row r="49" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J48" s="1"/>
+    </row>
+    <row r="49" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -28551,8 +28556,9 @@
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
-    </row>
-    <row r="50" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J49" s="1"/>
+    </row>
+    <row r="50" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -28562,8 +28568,9 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-    </row>
-    <row r="51" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J50" s="1"/>
+    </row>
+    <row r="51" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -28573,9 +28580,10 @@
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
-      <c r="K51" s="22"/>
-    </row>
-    <row r="52" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J51" s="1"/>
+      <c r="L51" s="22"/>
+    </row>
+    <row r="52" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -28585,8 +28593,9 @@
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
-    </row>
-    <row r="53" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -28596,8 +28605,9 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-    </row>
-    <row r="54" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -28607,8 +28617,9 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-    </row>
-    <row r="55" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -28618,8 +28629,9 @@
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
-    </row>
-    <row r="56" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -28629,8 +28641,9 @@
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
-    </row>
-    <row r="57" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -28640,8 +28653,9 @@
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
-    </row>
-    <row r="58" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -28651,8 +28665,9 @@
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
-    </row>
-    <row r="59" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -28662,8 +28677,9 @@
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
-    </row>
-    <row r="60" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J59" s="1"/>
+    </row>
+    <row r="60" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -28673,8 +28689,9 @@
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-    </row>
-    <row r="61" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J60" s="1"/>
+    </row>
+    <row r="61" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -28684,8 +28701,9 @@
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-    </row>
-    <row r="62" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J61" s="1"/>
+    </row>
+    <row r="62" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -28695,8 +28713,9 @@
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
-    </row>
-    <row r="63" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J62" s="1"/>
+    </row>
+    <row r="63" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -28706,8 +28725,9 @@
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
-    </row>
-    <row r="64" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J63" s="1"/>
+    </row>
+    <row r="64" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -28717,8 +28737,9 @@
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
-    </row>
-    <row r="65" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J64" s="1"/>
+    </row>
+    <row r="65" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -28728,8 +28749,9 @@
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
-    </row>
-    <row r="66" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J65" s="1"/>
+    </row>
+    <row r="66" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -28739,8 +28761,9 @@
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
-    </row>
-    <row r="67" spans="1:9" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="J66" s="1"/>
+    </row>
+    <row r="67" spans="1:10" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -28750,8 +28773,9 @@
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
-    </row>
-    <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J67" s="1"/>
+    </row>
+    <row r="68" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -28761,8 +28785,9 @@
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
-    </row>
-    <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J68" s="1"/>
+    </row>
+    <row r="69" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="51"/>
       <c r="B69" s="51"/>
       <c r="C69" s="51"/>
@@ -28772,8 +28797,9 @@
       <c r="G69" s="51"/>
       <c r="H69" s="51"/>
       <c r="I69" s="51"/>
-    </row>
-    <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J69" s="51"/>
+    </row>
+    <row r="70" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="23"/>
       <c r="C70" s="23"/>
@@ -28783,8 +28809,9 @@
       <c r="G70" s="23"/>
       <c r="H70" s="23"/>
       <c r="I70" s="23"/>
-    </row>
-    <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J70" s="23"/>
+    </row>
+    <row r="71" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="23"/>
       <c r="B71" s="23"/>
       <c r="C71" s="23"/>
@@ -28794,8 +28821,9 @@
       <c r="G71" s="23"/>
       <c r="H71" s="23"/>
       <c r="I71" s="23"/>
-    </row>
-    <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J71" s="23"/>
+    </row>
+    <row r="74" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="52"/>
       <c r="B74" s="52"/>
       <c r="C74" s="52"/>
@@ -28805,8 +28833,9 @@
       <c r="G74" s="52"/>
       <c r="H74" s="52"/>
       <c r="I74" s="52"/>
-    </row>
-    <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J74" s="52"/>
+    </row>
+    <row r="75" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="24"/>
       <c r="C75" s="24"/>
@@ -28816,8 +28845,9 @@
       <c r="G75" s="24"/>
       <c r="H75" s="24"/>
       <c r="I75" s="24"/>
-    </row>
-    <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J75" s="24"/>
+    </row>
+    <row r="76" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="25"/>
       <c r="C76" s="25"/>
@@ -28827,8 +28857,9 @@
       <c r="G76" s="25"/>
       <c r="H76" s="25"/>
       <c r="I76" s="25"/>
-    </row>
-    <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J76" s="25"/>
+    </row>
+    <row r="77" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="25"/>
       <c r="C77" s="25"/>
@@ -28838,8 +28869,9 @@
       <c r="G77" s="25"/>
       <c r="H77" s="25"/>
       <c r="I77" s="25"/>
-    </row>
-    <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J77" s="25"/>
+    </row>
+    <row r="78" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="53"/>
       <c r="B78" s="53"/>
       <c r="C78" s="53"/>
@@ -28849,8 +28881,9 @@
       <c r="G78" s="53"/>
       <c r="H78" s="53"/>
       <c r="I78" s="53"/>
-    </row>
-    <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J78" s="53"/>
+    </row>
+    <row r="79" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -28860,8 +28893,9 @@
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
-    </row>
-    <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J79" s="1"/>
+    </row>
+    <row r="80" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -28871,19 +28905,20 @@
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
-    </row>
-    <row r="82" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J80" s="1"/>
+    </row>
+    <row r="82" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
     </row>
-    <row r="83" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
     </row>
-    <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="23"/>
     </row>
-    <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="52"/>
       <c r="B86" s="52"/>
       <c r="C86" s="52"/>
@@ -28893,8 +28928,9 @@
       <c r="G86" s="52"/>
       <c r="H86" s="52"/>
       <c r="I86" s="52"/>
-    </row>
-    <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J86" s="52"/>
+    </row>
+    <row r="87" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="26"/>
       <c r="C87" s="26"/>
@@ -28904,8 +28940,9 @@
       <c r="G87" s="26"/>
       <c r="H87" s="26"/>
       <c r="I87" s="26"/>
-    </row>
-    <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J87" s="26"/>
+    </row>
+    <row r="88" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="26"/>
       <c r="C88" s="26"/>
@@ -28915,8 +28952,9 @@
       <c r="G88" s="26"/>
       <c r="H88" s="26"/>
       <c r="I88" s="26"/>
-    </row>
-    <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J88" s="26"/>
+    </row>
+    <row r="89" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="26"/>
       <c r="C89" s="26"/>
@@ -28926,8 +28964,9 @@
       <c r="G89" s="26"/>
       <c r="H89" s="26"/>
       <c r="I89" s="26"/>
-    </row>
-    <row r="90" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J89" s="26"/>
+    </row>
+    <row r="90" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="26"/>
       <c r="C90" s="26"/>
@@ -28937,8 +28976,9 @@
       <c r="G90" s="26"/>
       <c r="H90" s="26"/>
       <c r="I90" s="26"/>
-    </row>
-    <row r="91" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J90" s="26"/>
+    </row>
+    <row r="91" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="26"/>
       <c r="C91" s="26"/>
@@ -28948,8 +28988,9 @@
       <c r="G91" s="26"/>
       <c r="H91" s="26"/>
       <c r="I91" s="26"/>
-    </row>
-    <row r="92" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J91" s="26"/>
+    </row>
+    <row r="92" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="26"/>
       <c r="C92" s="26"/>
@@ -28959,8 +29000,9 @@
       <c r="G92" s="26"/>
       <c r="H92" s="26"/>
       <c r="I92" s="26"/>
-    </row>
-    <row r="93" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J92" s="26"/>
+    </row>
+    <row r="93" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="26"/>
       <c r="C93" s="26"/>
@@ -28970,8 +29012,9 @@
       <c r="G93" s="26"/>
       <c r="H93" s="26"/>
       <c r="I93" s="26"/>
-    </row>
-    <row r="94" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J93" s="26"/>
+    </row>
+    <row r="94" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -28981,20 +29024,21 @@
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
-    </row>
-    <row r="95" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J94" s="1"/>
+    </row>
+    <row r="95" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="26"/>
     </row>
-    <row r="96" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
     </row>
-    <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="26"/>
     </row>
-    <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="51"/>
       <c r="B99" s="51"/>
       <c r="C99" s="51"/>
@@ -29004,8 +29048,9 @@
       <c r="G99" s="51"/>
       <c r="H99" s="51"/>
       <c r="I99" s="51"/>
-    </row>
-    <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J99" s="51"/>
+    </row>
+    <row r="100" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="23"/>
       <c r="C100" s="23"/>
@@ -29015,8 +29060,9 @@
       <c r="G100" s="23"/>
       <c r="H100" s="23"/>
       <c r="I100" s="23"/>
-    </row>
-    <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="J100" s="23"/>
+    </row>
+    <row r="101" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="23"/>
       <c r="B101" s="23"/>
       <c r="C101" s="23"/>
@@ -29026,15 +29072,16 @@
       <c r="G101" s="23"/>
       <c r="H101" s="23"/>
       <c r="I101" s="23"/>
+      <c r="J101" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A99:I99"/>
-    <mergeCell ref="B34:I34"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A74:I74"/>
-    <mergeCell ref="A78:I78"/>
-    <mergeCell ref="A86:I86"/>
+    <mergeCell ref="A99:J99"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="A69:J69"/>
+    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A86:J86"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A87" xr:uid="{00000000-0002-0000-0300-000001000000}">
@@ -29054,7 +29101,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>AF2</xm:sqref>
+          <xm:sqref>AG2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -32249,6 +32296,9 @@
       <c r="G35" s="51"/>
       <c r="H35" s="51"/>
       <c r="I35" s="51"/>
+      <c r="N35" s="50"/>
+      <c r="O35" s="45"/>
+      <c r="P35" s="45"/>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -32260,6 +32310,9 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
+      <c r="N36" s="50"/>
+      <c r="O36" s="45"/>
+      <c r="P36" s="45"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -32271,6 +32324,9 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
+      <c r="N37" s="50"/>
+      <c r="O37" s="45"/>
+      <c r="P37" s="45"/>
     </row>
     <row r="38" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
@@ -32282,6 +32338,9 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
+      <c r="N38" s="50"/>
+      <c r="O38" s="45"/>
+      <c r="P38" s="45"/>
     </row>
     <row r="39" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
@@ -32293,6 +32352,9 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
+      <c r="N39" s="50"/>
+      <c r="O39" s="45"/>
+      <c r="P39" s="45"/>
     </row>
     <row r="40" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
@@ -32304,6 +32366,9 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
+      <c r="N40" s="50"/>
+      <c r="O40" s="45"/>
+      <c r="P40" s="45"/>
     </row>
     <row r="41" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AA3E77-A4C4-46D1-BF7D-53798102A457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDF4456-0C1A-4430-B94F-7B6CCA0C7CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -696,6 +696,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -709,7 +710,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1766,20 +1766,20 @@
     <row r="17" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D17" s="45"/>
       <c r="E17" s="45"/>
-      <c r="L17" s="56">
+      <c r="L17" s="51">
         <v>1531.37</v>
       </c>
-      <c r="M17" s="56">
+      <c r="M17" s="51">
         <f>L17*0.7</f>
         <v>1071.9589999999998</v>
       </c>
-      <c r="N17" s="56">
+      <c r="N17" s="51">
         <f>L17*0.3</f>
         <v>459.41099999999994</v>
       </c>
     </row>
     <row r="22" spans="4:14" x14ac:dyDescent="0.2">
-      <c r="J22" s="56"/>
+      <c r="J22" s="51"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -4940,15 +4940,15 @@
       <c r="I68" s="1"/>
     </row>
     <row r="69" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="51"/>
-      <c r="B69" s="51"/>
-      <c r="C69" s="51"/>
-      <c r="D69" s="51"/>
-      <c r="E69" s="51"/>
-      <c r="F69" s="51"/>
-      <c r="G69" s="51"/>
-      <c r="H69" s="51"/>
-      <c r="I69" s="51"/>
+      <c r="A69" s="52"/>
+      <c r="B69" s="52"/>
+      <c r="C69" s="52"/>
+      <c r="D69" s="52"/>
+      <c r="E69" s="52"/>
+      <c r="F69" s="52"/>
+      <c r="G69" s="52"/>
+      <c r="H69" s="52"/>
+      <c r="I69" s="52"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -4973,15 +4973,15 @@
       <c r="I71" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="52"/>
-      <c r="B74" s="52"/>
-      <c r="C74" s="52"/>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="52"/>
-      <c r="G74" s="52"/>
-      <c r="H74" s="52"/>
-      <c r="I74" s="52"/>
+      <c r="A74" s="53"/>
+      <c r="B74" s="53"/>
+      <c r="C74" s="53"/>
+      <c r="D74" s="53"/>
+      <c r="E74" s="53"/>
+      <c r="F74" s="53"/>
+      <c r="G74" s="53"/>
+      <c r="H74" s="53"/>
+      <c r="I74" s="53"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -5017,15 +5017,15 @@
       <c r="I77" s="25"/>
     </row>
     <row r="78" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="53"/>
-      <c r="B78" s="53"/>
-      <c r="C78" s="53"/>
-      <c r="D78" s="53"/>
-      <c r="E78" s="53"/>
-      <c r="F78" s="53"/>
-      <c r="G78" s="53"/>
-      <c r="H78" s="53"/>
-      <c r="I78" s="53"/>
+      <c r="A78" s="54"/>
+      <c r="B78" s="54"/>
+      <c r="C78" s="54"/>
+      <c r="D78" s="54"/>
+      <c r="E78" s="54"/>
+      <c r="F78" s="54"/>
+      <c r="G78" s="54"/>
+      <c r="H78" s="54"/>
+      <c r="I78" s="54"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -5061,15 +5061,15 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="52"/>
-      <c r="B86" s="52"/>
-      <c r="C86" s="52"/>
-      <c r="D86" s="52"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="52"/>
-      <c r="G86" s="52"/>
-      <c r="H86" s="52"/>
-      <c r="I86" s="52"/>
+      <c r="A86" s="53"/>
+      <c r="B86" s="53"/>
+      <c r="C86" s="53"/>
+      <c r="D86" s="53"/>
+      <c r="E86" s="53"/>
+      <c r="F86" s="53"/>
+      <c r="G86" s="53"/>
+      <c r="H86" s="53"/>
+      <c r="I86" s="53"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -5172,15 +5172,15 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="51"/>
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
-      <c r="D99" s="51"/>
-      <c r="E99" s="51"/>
-      <c r="F99" s="51"/>
-      <c r="G99" s="51"/>
-      <c r="H99" s="51"/>
-      <c r="I99" s="51"/>
+      <c r="A99" s="52"/>
+      <c r="B99" s="52"/>
+      <c r="C99" s="52"/>
+      <c r="D99" s="52"/>
+      <c r="E99" s="52"/>
+      <c r="F99" s="52"/>
+      <c r="G99" s="52"/>
+      <c r="H99" s="52"/>
+      <c r="I99" s="52"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -8380,14 +8380,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -8764,15 +8764,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="51"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="51"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="51"/>
-      <c r="I71" s="51"/>
+      <c r="A71" s="52"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="52"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="52"/>
+      <c r="F71" s="52"/>
+      <c r="G71" s="52"/>
+      <c r="H71" s="52"/>
+      <c r="I71" s="52"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -8797,15 +8797,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="52"/>
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
+      <c r="A76" s="53"/>
+      <c r="B76" s="53"/>
+      <c r="C76" s="53"/>
+      <c r="D76" s="53"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
+      <c r="H76" s="53"/>
+      <c r="I76" s="53"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -8841,15 +8841,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="53"/>
-      <c r="B80" s="53"/>
-      <c r="C80" s="53"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53"/>
-      <c r="H80" s="53"/>
-      <c r="I80" s="53"/>
+      <c r="A80" s="54"/>
+      <c r="B80" s="54"/>
+      <c r="C80" s="54"/>
+      <c r="D80" s="54"/>
+      <c r="E80" s="54"/>
+      <c r="F80" s="54"/>
+      <c r="G80" s="54"/>
+      <c r="H80" s="54"/>
+      <c r="I80" s="54"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -8885,15 +8885,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="52"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="52"/>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
-      <c r="G88" s="52"/>
-      <c r="H88" s="52"/>
-      <c r="I88" s="52"/>
+      <c r="A88" s="53"/>
+      <c r="B88" s="53"/>
+      <c r="C88" s="53"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="53"/>
+      <c r="G88" s="53"/>
+      <c r="H88" s="53"/>
+      <c r="I88" s="53"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -8996,15 +8996,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="51"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
-      <c r="F101" s="51"/>
-      <c r="G101" s="51"/>
-      <c r="H101" s="51"/>
-      <c r="I101" s="51"/>
+      <c r="A101" s="52"/>
+      <c r="B101" s="52"/>
+      <c r="C101" s="52"/>
+      <c r="D101" s="52"/>
+      <c r="E101" s="52"/>
+      <c r="F101" s="52"/>
+      <c r="G101" s="52"/>
+      <c r="H101" s="52"/>
+      <c r="I101" s="52"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -11378,14 +11378,14 @@
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="51"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
       <c r="T32" s="27"/>
     </row>
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
@@ -11763,15 +11763,15 @@
       <c r="I66" s="1"/>
     </row>
     <row r="67" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="51"/>
-      <c r="B67" s="51"/>
-      <c r="C67" s="51"/>
-      <c r="D67" s="51"/>
-      <c r="E67" s="51"/>
-      <c r="F67" s="51"/>
-      <c r="G67" s="51"/>
-      <c r="H67" s="51"/>
-      <c r="I67" s="51"/>
+      <c r="A67" s="52"/>
+      <c r="B67" s="52"/>
+      <c r="C67" s="52"/>
+      <c r="D67" s="52"/>
+      <c r="E67" s="52"/>
+      <c r="F67" s="52"/>
+      <c r="G67" s="52"/>
+      <c r="H67" s="52"/>
+      <c r="I67" s="52"/>
     </row>
     <row r="68" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
@@ -11796,15 +11796,15 @@
       <c r="I69" s="23"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="52"/>
-      <c r="B72" s="52"/>
-      <c r="C72" s="52"/>
-      <c r="D72" s="52"/>
-      <c r="E72" s="52"/>
-      <c r="F72" s="52"/>
-      <c r="G72" s="52"/>
-      <c r="H72" s="52"/>
-      <c r="I72" s="52"/>
+      <c r="A72" s="53"/>
+      <c r="B72" s="53"/>
+      <c r="C72" s="53"/>
+      <c r="D72" s="53"/>
+      <c r="E72" s="53"/>
+      <c r="F72" s="53"/>
+      <c r="G72" s="53"/>
+      <c r="H72" s="53"/>
+      <c r="I72" s="53"/>
     </row>
     <row r="73" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
@@ -11840,15 +11840,15 @@
       <c r="I75" s="25"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="53"/>
-      <c r="B76" s="53"/>
-      <c r="C76" s="53"/>
-      <c r="D76" s="53"/>
-      <c r="E76" s="53"/>
-      <c r="F76" s="53"/>
-      <c r="G76" s="53"/>
-      <c r="H76" s="53"/>
-      <c r="I76" s="53"/>
+      <c r="A76" s="54"/>
+      <c r="B76" s="54"/>
+      <c r="C76" s="54"/>
+      <c r="D76" s="54"/>
+      <c r="E76" s="54"/>
+      <c r="F76" s="54"/>
+      <c r="G76" s="54"/>
+      <c r="H76" s="54"/>
+      <c r="I76" s="54"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -11884,15 +11884,15 @@
       <c r="B82" s="23"/>
     </row>
     <row r="84" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="52"/>
-      <c r="B84" s="52"/>
-      <c r="C84" s="52"/>
-      <c r="D84" s="52"/>
-      <c r="E84" s="52"/>
-      <c r="F84" s="52"/>
-      <c r="G84" s="52"/>
-      <c r="H84" s="52"/>
-      <c r="I84" s="52"/>
+      <c r="A84" s="53"/>
+      <c r="B84" s="53"/>
+      <c r="C84" s="53"/>
+      <c r="D84" s="53"/>
+      <c r="E84" s="53"/>
+      <c r="F84" s="53"/>
+      <c r="G84" s="53"/>
+      <c r="H84" s="53"/>
+      <c r="I84" s="53"/>
     </row>
     <row r="85" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
@@ -11995,15 +11995,15 @@
       <c r="B95" s="26"/>
     </row>
     <row r="97" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="51"/>
-      <c r="B97" s="51"/>
-      <c r="C97" s="51"/>
-      <c r="D97" s="51"/>
-      <c r="E97" s="51"/>
-      <c r="F97" s="51"/>
-      <c r="G97" s="51"/>
-      <c r="H97" s="51"/>
-      <c r="I97" s="51"/>
+      <c r="A97" s="52"/>
+      <c r="B97" s="52"/>
+      <c r="C97" s="52"/>
+      <c r="D97" s="52"/>
+      <c r="E97" s="52"/>
+      <c r="F97" s="52"/>
+      <c r="G97" s="52"/>
+      <c r="H97" s="52"/>
+      <c r="I97" s="52"/>
     </row>
     <row r="98" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
@@ -14553,14 +14553,14 @@
     <row r="34" spans="1:21" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
     </row>
     <row r="37" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -14937,15 +14937,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="51"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="51"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="51"/>
-      <c r="I71" s="51"/>
+      <c r="A71" s="52"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="52"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="52"/>
+      <c r="F71" s="52"/>
+      <c r="G71" s="52"/>
+      <c r="H71" s="52"/>
+      <c r="I71" s="52"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -14970,15 +14970,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="52"/>
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
+      <c r="A76" s="53"/>
+      <c r="B76" s="53"/>
+      <c r="C76" s="53"/>
+      <c r="D76" s="53"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
+      <c r="H76" s="53"/>
+      <c r="I76" s="53"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -15014,15 +15014,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="53"/>
-      <c r="B80" s="53"/>
-      <c r="C80" s="53"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53"/>
-      <c r="H80" s="53"/>
-      <c r="I80" s="53"/>
+      <c r="A80" s="54"/>
+      <c r="B80" s="54"/>
+      <c r="C80" s="54"/>
+      <c r="D80" s="54"/>
+      <c r="E80" s="54"/>
+      <c r="F80" s="54"/>
+      <c r="G80" s="54"/>
+      <c r="H80" s="54"/>
+      <c r="I80" s="54"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -15058,15 +15058,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="52"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="52"/>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
-      <c r="G88" s="52"/>
-      <c r="H88" s="52"/>
-      <c r="I88" s="52"/>
+      <c r="A88" s="53"/>
+      <c r="B88" s="53"/>
+      <c r="C88" s="53"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="53"/>
+      <c r="G88" s="53"/>
+      <c r="H88" s="53"/>
+      <c r="I88" s="53"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -15169,15 +15169,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="51"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
-      <c r="F101" s="51"/>
-      <c r="G101" s="51"/>
-      <c r="H101" s="51"/>
-      <c r="I101" s="51"/>
+      <c r="A101" s="52"/>
+      <c r="B101" s="52"/>
+      <c r="C101" s="52"/>
+      <c r="D101" s="52"/>
+      <c r="E101" s="52"/>
+      <c r="F101" s="52"/>
+      <c r="G101" s="52"/>
+      <c r="H101" s="52"/>
+      <c r="I101" s="52"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -17912,14 +17912,14 @@
     </row>
     <row r="35" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
     </row>
     <row r="36" spans="1:21" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -18297,15 +18297,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="51"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="51"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="51"/>
-      <c r="I70" s="51"/>
+      <c r="A70" s="52"/>
+      <c r="B70" s="52"/>
+      <c r="C70" s="52"/>
+      <c r="D70" s="52"/>
+      <c r="E70" s="52"/>
+      <c r="F70" s="52"/>
+      <c r="G70" s="52"/>
+      <c r="H70" s="52"/>
+      <c r="I70" s="52"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -18330,15 +18330,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="52"/>
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="52"/>
+      <c r="A75" s="53"/>
+      <c r="B75" s="53"/>
+      <c r="C75" s="53"/>
+      <c r="D75" s="53"/>
+      <c r="E75" s="53"/>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53"/>
+      <c r="H75" s="53"/>
+      <c r="I75" s="53"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -18374,15 +18374,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="53"/>
-      <c r="B79" s="53"/>
-      <c r="C79" s="53"/>
-      <c r="D79" s="53"/>
-      <c r="E79" s="53"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53"/>
-      <c r="H79" s="53"/>
-      <c r="I79" s="53"/>
+      <c r="A79" s="54"/>
+      <c r="B79" s="54"/>
+      <c r="C79" s="54"/>
+      <c r="D79" s="54"/>
+      <c r="E79" s="54"/>
+      <c r="F79" s="54"/>
+      <c r="G79" s="54"/>
+      <c r="H79" s="54"/>
+      <c r="I79" s="54"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -18418,15 +18418,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="52"/>
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
-      <c r="I87" s="52"/>
+      <c r="A87" s="53"/>
+      <c r="B87" s="53"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="53"/>
+      <c r="G87" s="53"/>
+      <c r="H87" s="53"/>
+      <c r="I87" s="53"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -18529,15 +18529,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="51"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
-      <c r="F100" s="51"/>
-      <c r="G100" s="51"/>
-      <c r="H100" s="51"/>
-      <c r="I100" s="51"/>
+      <c r="A100" s="52"/>
+      <c r="B100" s="52"/>
+      <c r="C100" s="52"/>
+      <c r="D100" s="52"/>
+      <c r="E100" s="52"/>
+      <c r="F100" s="52"/>
+      <c r="G100" s="52"/>
+      <c r="H100" s="52"/>
+      <c r="I100" s="52"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -21164,14 +21164,14 @@
     <row r="33" spans="1:9" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="35" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
     </row>
     <row r="36" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -21549,15 +21549,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="51"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="51"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="51"/>
-      <c r="I70" s="51"/>
+      <c r="A70" s="52"/>
+      <c r="B70" s="52"/>
+      <c r="C70" s="52"/>
+      <c r="D70" s="52"/>
+      <c r="E70" s="52"/>
+      <c r="F70" s="52"/>
+      <c r="G70" s="52"/>
+      <c r="H70" s="52"/>
+      <c r="I70" s="52"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -21582,15 +21582,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="52"/>
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="52"/>
+      <c r="A75" s="53"/>
+      <c r="B75" s="53"/>
+      <c r="C75" s="53"/>
+      <c r="D75" s="53"/>
+      <c r="E75" s="53"/>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53"/>
+      <c r="H75" s="53"/>
+      <c r="I75" s="53"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -21626,15 +21626,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="53"/>
-      <c r="B79" s="53"/>
-      <c r="C79" s="53"/>
-      <c r="D79" s="53"/>
-      <c r="E79" s="53"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53"/>
-      <c r="H79" s="53"/>
-      <c r="I79" s="53"/>
+      <c r="A79" s="54"/>
+      <c r="B79" s="54"/>
+      <c r="C79" s="54"/>
+      <c r="D79" s="54"/>
+      <c r="E79" s="54"/>
+      <c r="F79" s="54"/>
+      <c r="G79" s="54"/>
+      <c r="H79" s="54"/>
+      <c r="I79" s="54"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -21670,15 +21670,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="52"/>
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
-      <c r="I87" s="52"/>
+      <c r="A87" s="53"/>
+      <c r="B87" s="53"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="53"/>
+      <c r="G87" s="53"/>
+      <c r="H87" s="53"/>
+      <c r="I87" s="53"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -21781,15 +21781,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="51"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
-      <c r="F100" s="51"/>
-      <c r="G100" s="51"/>
-      <c r="H100" s="51"/>
-      <c r="I100" s="51"/>
+      <c r="A100" s="52"/>
+      <c r="B100" s="52"/>
+      <c r="C100" s="52"/>
+      <c r="D100" s="52"/>
+      <c r="E100" s="52"/>
+      <c r="F100" s="52"/>
+      <c r="G100" s="52"/>
+      <c r="H100" s="52"/>
+      <c r="I100" s="52"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -22562,49 +22562,49 @@
       </c>
       <c r="D8" s="13">
         <f t="shared" si="0"/>
-        <v>-12945</v>
+        <v>104</v>
       </c>
       <c r="E8" s="6">
         <v>0</v>
       </c>
       <c r="F8" s="13">
         <f t="shared" si="1"/>
-        <v>-15795</v>
+        <v>77</v>
       </c>
       <c r="G8" s="6">
         <v>0</v>
       </c>
       <c r="H8" s="13">
         <f t="shared" si="2"/>
-        <v>-9801</v>
+        <v>2</v>
       </c>
       <c r="I8" s="6">
         <v>0</v>
       </c>
       <c r="J8" s="13">
         <f t="shared" si="3"/>
-        <v>-10886</v>
+        <v>1</v>
       </c>
       <c r="K8" s="6">
         <v>0</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="4"/>
-        <v>-1294</v>
+        <v>1</v>
       </c>
       <c r="M8" s="6">
         <v>0</v>
       </c>
       <c r="N8" s="13">
         <f t="shared" si="5"/>
-        <v>-4247</v>
+        <v>14</v>
       </c>
       <c r="O8" s="6">
         <v>0</v>
       </c>
       <c r="P8" s="13">
         <f t="shared" si="6"/>
-        <v>-431</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="6">
         <v>0</v>
@@ -22614,7 +22614,7 @@
       </c>
       <c r="S8" s="13">
         <f t="shared" si="7"/>
-        <v>-3815</v>
+        <v>13</v>
       </c>
       <c r="T8" s="6"/>
       <c r="U8" s="4"/>
@@ -22659,28 +22659,28 @@
       </c>
       <c r="D9" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="E9" s="6">
         <v>0</v>
       </c>
       <c r="F9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="G9" s="6">
         <v>0</v>
       </c>
       <c r="H9" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I9" s="6">
         <v>0</v>
       </c>
       <c r="J9" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="6">
         <v>0</v>
@@ -22694,7 +22694,7 @@
       </c>
       <c r="N9" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O9" s="6">
         <v>0</v>
@@ -22711,7 +22711,7 @@
       </c>
       <c r="S9" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T9" s="6"/>
       <c r="U9" s="4"/>
@@ -22719,14 +22719,30 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="6"/>
-      <c r="AB9" s="6"/>
-      <c r="AC9" s="6"/>
-      <c r="AD9" s="6"/>
+      <c r="W9" s="6">
+        <v>13049</v>
+      </c>
+      <c r="X9" s="6">
+        <v>15872</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>9803</v>
+      </c>
+      <c r="Z9" s="6">
+        <v>10887</v>
+      </c>
+      <c r="AA9" s="6">
+        <v>1295</v>
+      </c>
+      <c r="AB9" s="6">
+        <v>4261</v>
+      </c>
+      <c r="AC9" s="6">
+        <v>433</v>
+      </c>
+      <c r="AD9" s="6">
+        <v>3828</v>
+      </c>
     </row>
     <row r="10" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
@@ -22740,21 +22756,21 @@
       </c>
       <c r="D10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="E10" s="6">
         <v>0</v>
       </c>
       <c r="F10" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="G10" s="6">
         <v>0</v>
       </c>
       <c r="H10" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10" s="6">
         <v>0</v>
@@ -22775,14 +22791,14 @@
       </c>
       <c r="N10" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O10" s="6">
         <v>0</v>
       </c>
       <c r="P10" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="6">
         <v>0</v>
@@ -22792,7 +22808,7 @@
       </c>
       <c r="S10" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T10" s="6"/>
       <c r="U10" s="4"/>
@@ -22800,14 +22816,30 @@
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="6"/>
-      <c r="AB10" s="6"/>
-      <c r="AC10" s="6"/>
-      <c r="AD10" s="6"/>
+      <c r="W10" s="6">
+        <v>13168</v>
+      </c>
+      <c r="X10" s="6">
+        <v>16015</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>9807</v>
+      </c>
+      <c r="Z10" s="6">
+        <v>10888</v>
+      </c>
+      <c r="AA10" s="6">
+        <v>1295</v>
+      </c>
+      <c r="AB10" s="6">
+        <v>4264</v>
+      </c>
+      <c r="AC10" s="6">
+        <v>433</v>
+      </c>
+      <c r="AD10" s="6">
+        <v>3831</v>
+      </c>
     </row>
     <row r="11" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
@@ -22881,14 +22913,30 @@
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="6"/>
-      <c r="AB11" s="6"/>
-      <c r="AC11" s="6"/>
-      <c r="AD11" s="6"/>
+      <c r="W11" s="6">
+        <v>13269</v>
+      </c>
+      <c r="X11" s="6">
+        <v>16196</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>9811</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>10888</v>
+      </c>
+      <c r="AA11" s="6">
+        <v>1295</v>
+      </c>
+      <c r="AB11" s="6">
+        <v>4275</v>
+      </c>
+      <c r="AC11" s="6">
+        <v>435</v>
+      </c>
+      <c r="AD11" s="6">
+        <v>3840</v>
+      </c>
     </row>
     <row r="12" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
@@ -22962,14 +23010,30 @@
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="6"/>
-      <c r="AA12" s="6"/>
-      <c r="AB12" s="6"/>
-      <c r="AC12" s="6"/>
-      <c r="AD12" s="6"/>
+      <c r="W12" s="6">
+        <v>13269</v>
+      </c>
+      <c r="X12" s="6">
+        <v>16196</v>
+      </c>
+      <c r="Y12" s="6">
+        <v>9811</v>
+      </c>
+      <c r="Z12" s="6">
+        <v>10888</v>
+      </c>
+      <c r="AA12" s="6">
+        <v>1295</v>
+      </c>
+      <c r="AB12" s="6">
+        <v>4275</v>
+      </c>
+      <c r="AC12" s="6">
+        <v>435</v>
+      </c>
+      <c r="AD12" s="6">
+        <v>3840</v>
+      </c>
     </row>
     <row r="13" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
@@ -22983,49 +23047,49 @@
       </c>
       <c r="D13" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="E13" s="6">
         <v>0</v>
       </c>
       <c r="F13" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="G13" s="6">
         <v>0</v>
       </c>
       <c r="H13" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I13" s="6">
         <v>0</v>
       </c>
       <c r="J13" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13" s="6">
         <v>0</v>
       </c>
       <c r="L13" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="6">
         <v>0</v>
       </c>
       <c r="N13" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O13" s="6">
         <v>0</v>
       </c>
       <c r="P13" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="6">
         <v>0</v>
@@ -23035,7 +23099,7 @@
       </c>
       <c r="S13" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T13" s="6"/>
       <c r="U13" s="4"/>
@@ -23043,14 +23107,30 @@
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="W13" s="15"/>
-      <c r="X13" s="15"/>
-      <c r="Y13" s="15"/>
-      <c r="Z13" s="15"/>
-      <c r="AA13" s="15"/>
-      <c r="AB13" s="15"/>
-      <c r="AC13" s="15"/>
-      <c r="AD13" s="15"/>
+      <c r="W13" s="6">
+        <v>13269</v>
+      </c>
+      <c r="X13" s="6">
+        <v>16196</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>9811</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>10888</v>
+      </c>
+      <c r="AA13" s="6">
+        <v>1295</v>
+      </c>
+      <c r="AB13" s="6">
+        <v>4275</v>
+      </c>
+      <c r="AC13" s="6">
+        <v>435</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>3840</v>
+      </c>
     </row>
     <row r="14" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
@@ -23064,21 +23144,21 @@
       </c>
       <c r="D14" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E14" s="6">
         <v>0</v>
       </c>
       <c r="F14" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G14" s="6">
         <v>0</v>
       </c>
       <c r="H14" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I14" s="6">
         <v>0</v>
@@ -23099,7 +23179,7 @@
       </c>
       <c r="N14" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O14" s="6">
         <v>0</v>
@@ -23116,7 +23196,7 @@
       </c>
       <c r="S14" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="4"/>
@@ -23124,14 +23204,30 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="6"/>
-      <c r="AB14" s="6"/>
-      <c r="AC14" s="6"/>
-      <c r="AD14" s="6"/>
+      <c r="W14" s="6">
+        <v>13434</v>
+      </c>
+      <c r="X14" s="6">
+        <v>16489</v>
+      </c>
+      <c r="Y14" s="6">
+        <v>9830</v>
+      </c>
+      <c r="Z14" s="6">
+        <v>10891</v>
+      </c>
+      <c r="AA14" s="6">
+        <v>1296</v>
+      </c>
+      <c r="AB14" s="6">
+        <v>4288</v>
+      </c>
+      <c r="AC14" s="6">
+        <v>436</v>
+      </c>
+      <c r="AD14" s="6">
+        <v>3851</v>
+      </c>
     </row>
     <row r="15" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
@@ -23145,21 +23241,21 @@
       </c>
       <c r="D15" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-13465</v>
       </c>
       <c r="E15" s="6">
         <v>0</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-16628</v>
       </c>
       <c r="G15" s="6">
         <v>0</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9834</v>
       </c>
       <c r="I15" s="6">
         <v>0</v>
@@ -23172,21 +23268,21 @@
       </c>
       <c r="L15" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1296</v>
       </c>
       <c r="M15" s="6">
         <v>0</v>
       </c>
       <c r="N15" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4295</v>
       </c>
       <c r="O15" s="6">
         <v>0</v>
       </c>
       <c r="P15" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-436</v>
       </c>
       <c r="Q15" s="6">
         <v>0</v>
@@ -23196,7 +23292,7 @@
       </c>
       <c r="S15" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3859</v>
       </c>
       <c r="T15" s="6"/>
       <c r="U15" s="4"/>
@@ -23204,14 +23300,30 @@
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="6"/>
-      <c r="AB15" s="6"/>
-      <c r="AC15" s="6"/>
-      <c r="AD15" s="6"/>
+      <c r="W15" s="6">
+        <v>13465</v>
+      </c>
+      <c r="X15" s="6">
+        <v>16628</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>9834</v>
+      </c>
+      <c r="Z15" s="6">
+        <v>10891</v>
+      </c>
+      <c r="AA15" s="6">
+        <v>1296</v>
+      </c>
+      <c r="AB15" s="6">
+        <v>4295</v>
+      </c>
+      <c r="AC15" s="6">
+        <v>436</v>
+      </c>
+      <c r="AD15" s="6">
+        <v>3859</v>
+      </c>
     </row>
     <row r="16" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
@@ -24604,14 +24716,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -24989,15 +25101,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="51"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="51"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="51"/>
-      <c r="I71" s="51"/>
+      <c r="A71" s="52"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="52"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="52"/>
+      <c r="F71" s="52"/>
+      <c r="G71" s="52"/>
+      <c r="H71" s="52"/>
+      <c r="I71" s="52"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -25022,15 +25134,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="52"/>
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
+      <c r="A76" s="53"/>
+      <c r="B76" s="53"/>
+      <c r="C76" s="53"/>
+      <c r="D76" s="53"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
+      <c r="H76" s="53"/>
+      <c r="I76" s="53"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -25066,15 +25178,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="53"/>
-      <c r="B80" s="53"/>
-      <c r="C80" s="53"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53"/>
-      <c r="H80" s="53"/>
-      <c r="I80" s="53"/>
+      <c r="A80" s="54"/>
+      <c r="B80" s="54"/>
+      <c r="C80" s="54"/>
+      <c r="D80" s="54"/>
+      <c r="E80" s="54"/>
+      <c r="F80" s="54"/>
+      <c r="G80" s="54"/>
+      <c r="H80" s="54"/>
+      <c r="I80" s="54"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -25110,15 +25222,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="52"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="52"/>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
-      <c r="G88" s="52"/>
-      <c r="H88" s="52"/>
-      <c r="I88" s="52"/>
+      <c r="A88" s="53"/>
+      <c r="B88" s="53"/>
+      <c r="C88" s="53"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="53"/>
+      <c r="G88" s="53"/>
+      <c r="H88" s="53"/>
+      <c r="I88" s="53"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -25221,15 +25333,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="51"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
-      <c r="F101" s="51"/>
-      <c r="G101" s="51"/>
-      <c r="H101" s="51"/>
-      <c r="I101" s="51"/>
+      <c r="A101" s="52"/>
+      <c r="B101" s="52"/>
+      <c r="C101" s="52"/>
+      <c r="D101" s="52"/>
+      <c r="E101" s="52"/>
+      <c r="F101" s="52"/>
+      <c r="G101" s="52"/>
+      <c r="H101" s="52"/>
+      <c r="I101" s="52"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -28366,15 +28478,15 @@
     </row>
     <row r="34" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="51"/>
-      <c r="I34" s="51"/>
-      <c r="J34" s="51"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
     </row>
     <row r="35" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
@@ -28788,16 +28900,16 @@
       <c r="J68" s="1"/>
     </row>
     <row r="69" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="51"/>
-      <c r="B69" s="51"/>
-      <c r="C69" s="51"/>
-      <c r="D69" s="51"/>
-      <c r="E69" s="51"/>
-      <c r="F69" s="51"/>
-      <c r="G69" s="51"/>
-      <c r="H69" s="51"/>
-      <c r="I69" s="51"/>
-      <c r="J69" s="51"/>
+      <c r="A69" s="52"/>
+      <c r="B69" s="52"/>
+      <c r="C69" s="52"/>
+      <c r="D69" s="52"/>
+      <c r="E69" s="52"/>
+      <c r="F69" s="52"/>
+      <c r="G69" s="52"/>
+      <c r="H69" s="52"/>
+      <c r="I69" s="52"/>
+      <c r="J69" s="52"/>
     </row>
     <row r="70" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
@@ -28824,16 +28936,16 @@
       <c r="J71" s="23"/>
     </row>
     <row r="74" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A74" s="52"/>
-      <c r="B74" s="52"/>
-      <c r="C74" s="52"/>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="52"/>
-      <c r="G74" s="52"/>
-      <c r="H74" s="52"/>
-      <c r="I74" s="52"/>
-      <c r="J74" s="52"/>
+      <c r="A74" s="53"/>
+      <c r="B74" s="53"/>
+      <c r="C74" s="53"/>
+      <c r="D74" s="53"/>
+      <c r="E74" s="53"/>
+      <c r="F74" s="53"/>
+      <c r="G74" s="53"/>
+      <c r="H74" s="53"/>
+      <c r="I74" s="53"/>
+      <c r="J74" s="53"/>
     </row>
     <row r="75" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
@@ -28872,16 +28984,16 @@
       <c r="J77" s="25"/>
     </row>
     <row r="78" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="53"/>
-      <c r="B78" s="53"/>
-      <c r="C78" s="53"/>
-      <c r="D78" s="53"/>
-      <c r="E78" s="53"/>
-      <c r="F78" s="53"/>
-      <c r="G78" s="53"/>
-      <c r="H78" s="53"/>
-      <c r="I78" s="53"/>
-      <c r="J78" s="53"/>
+      <c r="A78" s="54"/>
+      <c r="B78" s="54"/>
+      <c r="C78" s="54"/>
+      <c r="D78" s="54"/>
+      <c r="E78" s="54"/>
+      <c r="F78" s="54"/>
+      <c r="G78" s="54"/>
+      <c r="H78" s="54"/>
+      <c r="I78" s="54"/>
+      <c r="J78" s="54"/>
     </row>
     <row r="79" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
@@ -28919,16 +29031,16 @@
       <c r="B84" s="23"/>
     </row>
     <row r="86" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="52"/>
-      <c r="B86" s="52"/>
-      <c r="C86" s="52"/>
-      <c r="D86" s="52"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="52"/>
-      <c r="G86" s="52"/>
-      <c r="H86" s="52"/>
-      <c r="I86" s="52"/>
-      <c r="J86" s="52"/>
+      <c r="A86" s="53"/>
+      <c r="B86" s="53"/>
+      <c r="C86" s="53"/>
+      <c r="D86" s="53"/>
+      <c r="E86" s="53"/>
+      <c r="F86" s="53"/>
+      <c r="G86" s="53"/>
+      <c r="H86" s="53"/>
+      <c r="I86" s="53"/>
+      <c r="J86" s="53"/>
     </row>
     <row r="87" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
@@ -29039,16 +29151,16 @@
       <c r="B97" s="26"/>
     </row>
     <row r="99" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A99" s="51"/>
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
-      <c r="D99" s="51"/>
-      <c r="E99" s="51"/>
-      <c r="F99" s="51"/>
-      <c r="G99" s="51"/>
-      <c r="H99" s="51"/>
-      <c r="I99" s="51"/>
-      <c r="J99" s="51"/>
+      <c r="A99" s="52"/>
+      <c r="B99" s="52"/>
+      <c r="C99" s="52"/>
+      <c r="D99" s="52"/>
+      <c r="E99" s="52"/>
+      <c r="F99" s="52"/>
+      <c r="G99" s="52"/>
+      <c r="H99" s="52"/>
+      <c r="I99" s="52"/>
+      <c r="J99" s="52"/>
     </row>
     <row r="100" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
@@ -29919,12 +30031,12 @@
       <c r="AD8" s="6">
         <v>3558</v>
       </c>
-      <c r="AH8" s="54"/>
-      <c r="AI8" s="54"/>
-      <c r="AJ8" s="54"/>
-      <c r="AK8" s="55"/>
-      <c r="AL8" s="55"/>
-      <c r="AM8" s="55"/>
+      <c r="AH8" s="55"/>
+      <c r="AI8" s="55"/>
+      <c r="AJ8" s="55"/>
+      <c r="AK8" s="56"/>
+      <c r="AL8" s="56"/>
+      <c r="AM8" s="56"/>
     </row>
     <row r="9" spans="1:40" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="28">
@@ -32288,14 +32400,14 @@
     </row>
     <row r="35" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
       <c r="N35" s="50"/>
       <c r="O35" s="45"/>
       <c r="P35" s="45"/>
@@ -32692,15 +32804,15 @@
       <c r="I69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="51"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="51"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="51"/>
-      <c r="I70" s="51"/>
+      <c r="A70" s="52"/>
+      <c r="B70" s="52"/>
+      <c r="C70" s="52"/>
+      <c r="D70" s="52"/>
+      <c r="E70" s="52"/>
+      <c r="F70" s="52"/>
+      <c r="G70" s="52"/>
+      <c r="H70" s="52"/>
+      <c r="I70" s="52"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -32725,15 +32837,15 @@
       <c r="I72" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="52"/>
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="52"/>
+      <c r="A75" s="53"/>
+      <c r="B75" s="53"/>
+      <c r="C75" s="53"/>
+      <c r="D75" s="53"/>
+      <c r="E75" s="53"/>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53"/>
+      <c r="H75" s="53"/>
+      <c r="I75" s="53"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -32769,15 +32881,15 @@
       <c r="I78" s="25"/>
     </row>
     <row r="79" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="53"/>
-      <c r="B79" s="53"/>
-      <c r="C79" s="53"/>
-      <c r="D79" s="53"/>
-      <c r="E79" s="53"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53"/>
-      <c r="H79" s="53"/>
-      <c r="I79" s="53"/>
+      <c r="A79" s="54"/>
+      <c r="B79" s="54"/>
+      <c r="C79" s="54"/>
+      <c r="D79" s="54"/>
+      <c r="E79" s="54"/>
+      <c r="F79" s="54"/>
+      <c r="G79" s="54"/>
+      <c r="H79" s="54"/>
+      <c r="I79" s="54"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -32813,15 +32925,15 @@
       <c r="B85" s="23"/>
     </row>
     <row r="87" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="52"/>
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
-      <c r="I87" s="52"/>
+      <c r="A87" s="53"/>
+      <c r="B87" s="53"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="53"/>
+      <c r="G87" s="53"/>
+      <c r="H87" s="53"/>
+      <c r="I87" s="53"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -32924,15 +33036,15 @@
       <c r="B98" s="26"/>
     </row>
     <row r="100" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="51"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
-      <c r="F100" s="51"/>
-      <c r="G100" s="51"/>
-      <c r="H100" s="51"/>
-      <c r="I100" s="51"/>
+      <c r="A100" s="52"/>
+      <c r="B100" s="52"/>
+      <c r="C100" s="52"/>
+      <c r="D100" s="52"/>
+      <c r="E100" s="52"/>
+      <c r="F100" s="52"/>
+      <c r="G100" s="52"/>
+      <c r="H100" s="52"/>
+      <c r="I100" s="52"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -36123,14 +36235,14 @@
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
       <c r="Q36" s="50"/>
       <c r="R36" s="50"/>
     </row>
@@ -36510,15 +36622,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="51"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="51"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="51"/>
-      <c r="I71" s="51"/>
+      <c r="A71" s="52"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="52"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="52"/>
+      <c r="F71" s="52"/>
+      <c r="G71" s="52"/>
+      <c r="H71" s="52"/>
+      <c r="I71" s="52"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -36543,15 +36655,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="52"/>
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
+      <c r="A76" s="53"/>
+      <c r="B76" s="53"/>
+      <c r="C76" s="53"/>
+      <c r="D76" s="53"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
+      <c r="H76" s="53"/>
+      <c r="I76" s="53"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -36587,15 +36699,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="53"/>
-      <c r="B80" s="53"/>
-      <c r="C80" s="53"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53"/>
-      <c r="H80" s="53"/>
-      <c r="I80" s="53"/>
+      <c r="A80" s="54"/>
+      <c r="B80" s="54"/>
+      <c r="C80" s="54"/>
+      <c r="D80" s="54"/>
+      <c r="E80" s="54"/>
+      <c r="F80" s="54"/>
+      <c r="G80" s="54"/>
+      <c r="H80" s="54"/>
+      <c r="I80" s="54"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -36631,15 +36743,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="52"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="52"/>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
-      <c r="G88" s="52"/>
-      <c r="H88" s="52"/>
-      <c r="I88" s="52"/>
+      <c r="A88" s="53"/>
+      <c r="B88" s="53"/>
+      <c r="C88" s="53"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="53"/>
+      <c r="G88" s="53"/>
+      <c r="H88" s="53"/>
+      <c r="I88" s="53"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -36742,15 +36854,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="51"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
-      <c r="F101" s="51"/>
-      <c r="G101" s="51"/>
-      <c r="H101" s="51"/>
-      <c r="I101" s="51"/>
+      <c r="A101" s="52"/>
+      <c r="B101" s="52"/>
+      <c r="C101" s="52"/>
+      <c r="D101" s="52"/>
+      <c r="E101" s="52"/>
+      <c r="F101" s="52"/>
+      <c r="G101" s="52"/>
+      <c r="H101" s="52"/>
+      <c r="I101" s="52"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
@@ -39802,22 +39914,22 @@
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
-      <c r="J35" s="51"/>
-      <c r="K35" s="51"/>
-      <c r="L35" s="51"/>
-      <c r="M35" s="51"/>
-      <c r="N35" s="51"/>
-      <c r="O35" s="51"/>
-      <c r="P35" s="51"/>
-      <c r="Q35" s="51"/>
-      <c r="R35" s="51"/>
-      <c r="S35" s="51"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="52"/>
     </row>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -40535,25 +40647,25 @@
       <c r="S69" s="1"/>
     </row>
     <row r="70" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="51"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="51"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="51"/>
-      <c r="I70" s="51"/>
-      <c r="J70" s="51"/>
-      <c r="K70" s="51"/>
-      <c r="L70" s="51"/>
-      <c r="M70" s="51"/>
-      <c r="N70" s="51"/>
-      <c r="O70" s="51"/>
-      <c r="P70" s="51"/>
-      <c r="Q70" s="51"/>
-      <c r="R70" s="51"/>
-      <c r="S70" s="51"/>
+      <c r="A70" s="52"/>
+      <c r="B70" s="52"/>
+      <c r="C70" s="52"/>
+      <c r="D70" s="52"/>
+      <c r="E70" s="52"/>
+      <c r="F70" s="52"/>
+      <c r="G70" s="52"/>
+      <c r="H70" s="52"/>
+      <c r="I70" s="52"/>
+      <c r="J70" s="52"/>
+      <c r="K70" s="52"/>
+      <c r="L70" s="52"/>
+      <c r="M70" s="52"/>
+      <c r="N70" s="52"/>
+      <c r="O70" s="52"/>
+      <c r="P70" s="52"/>
+      <c r="Q70" s="52"/>
+      <c r="R70" s="52"/>
+      <c r="S70" s="52"/>
     </row>
     <row r="71" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
@@ -40598,25 +40710,25 @@
       <c r="S72" s="23"/>
     </row>
     <row r="75" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="52"/>
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="52"/>
-      <c r="J75" s="52"/>
-      <c r="K75" s="52"/>
-      <c r="L75" s="52"/>
-      <c r="M75" s="52"/>
-      <c r="N75" s="52"/>
-      <c r="O75" s="52"/>
-      <c r="P75" s="52"/>
-      <c r="Q75" s="52"/>
-      <c r="R75" s="52"/>
-      <c r="S75" s="52"/>
+      <c r="A75" s="53"/>
+      <c r="B75" s="53"/>
+      <c r="C75" s="53"/>
+      <c r="D75" s="53"/>
+      <c r="E75" s="53"/>
+      <c r="F75" s="53"/>
+      <c r="G75" s="53"/>
+      <c r="H75" s="53"/>
+      <c r="I75" s="53"/>
+      <c r="J75" s="53"/>
+      <c r="K75" s="53"/>
+      <c r="L75" s="53"/>
+      <c r="M75" s="53"/>
+      <c r="N75" s="53"/>
+      <c r="O75" s="53"/>
+      <c r="P75" s="53"/>
+      <c r="Q75" s="53"/>
+      <c r="R75" s="53"/>
+      <c r="S75" s="53"/>
     </row>
     <row r="76" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
@@ -40682,25 +40794,25 @@
       <c r="S78" s="25"/>
     </row>
     <row r="79" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="53"/>
-      <c r="B79" s="53"/>
-      <c r="C79" s="53"/>
-      <c r="D79" s="53"/>
-      <c r="E79" s="53"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53"/>
-      <c r="H79" s="53"/>
-      <c r="I79" s="53"/>
-      <c r="J79" s="53"/>
-      <c r="K79" s="53"/>
-      <c r="L79" s="53"/>
-      <c r="M79" s="53"/>
-      <c r="N79" s="53"/>
-      <c r="O79" s="53"/>
-      <c r="P79" s="53"/>
-      <c r="Q79" s="53"/>
-      <c r="R79" s="53"/>
-      <c r="S79" s="53"/>
+      <c r="A79" s="54"/>
+      <c r="B79" s="54"/>
+      <c r="C79" s="54"/>
+      <c r="D79" s="54"/>
+      <c r="E79" s="54"/>
+      <c r="F79" s="54"/>
+      <c r="G79" s="54"/>
+      <c r="H79" s="54"/>
+      <c r="I79" s="54"/>
+      <c r="J79" s="54"/>
+      <c r="K79" s="54"/>
+      <c r="L79" s="54"/>
+      <c r="M79" s="54"/>
+      <c r="N79" s="54"/>
+      <c r="O79" s="54"/>
+      <c r="P79" s="54"/>
+      <c r="Q79" s="54"/>
+      <c r="R79" s="54"/>
+      <c r="S79" s="54"/>
     </row>
     <row r="80" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
@@ -40764,25 +40876,25 @@
       <c r="E85" s="23"/>
     </row>
     <row r="87" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="52"/>
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="52"/>
-      <c r="I87" s="52"/>
-      <c r="J87" s="52"/>
-      <c r="K87" s="52"/>
-      <c r="L87" s="52"/>
-      <c r="M87" s="52"/>
-      <c r="N87" s="52"/>
-      <c r="O87" s="52"/>
-      <c r="P87" s="52"/>
-      <c r="Q87" s="52"/>
-      <c r="R87" s="52"/>
-      <c r="S87" s="52"/>
+      <c r="A87" s="53"/>
+      <c r="B87" s="53"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="53"/>
+      <c r="G87" s="53"/>
+      <c r="H87" s="53"/>
+      <c r="I87" s="53"/>
+      <c r="J87" s="53"/>
+      <c r="K87" s="53"/>
+      <c r="L87" s="53"/>
+      <c r="M87" s="53"/>
+      <c r="N87" s="53"/>
+      <c r="O87" s="53"/>
+      <c r="P87" s="53"/>
+      <c r="Q87" s="53"/>
+      <c r="R87" s="53"/>
+      <c r="S87" s="53"/>
     </row>
     <row r="88" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
@@ -40974,25 +41086,25 @@
       <c r="E98" s="26"/>
     </row>
     <row r="100" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A100" s="51"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
-      <c r="F100" s="51"/>
-      <c r="G100" s="51"/>
-      <c r="H100" s="51"/>
-      <c r="I100" s="51"/>
-      <c r="J100" s="51"/>
-      <c r="K100" s="51"/>
-      <c r="L100" s="51"/>
-      <c r="M100" s="51"/>
-      <c r="N100" s="51"/>
-      <c r="O100" s="51"/>
-      <c r="P100" s="51"/>
-      <c r="Q100" s="51"/>
-      <c r="R100" s="51"/>
-      <c r="S100" s="51"/>
+      <c r="A100" s="52"/>
+      <c r="B100" s="52"/>
+      <c r="C100" s="52"/>
+      <c r="D100" s="52"/>
+      <c r="E100" s="52"/>
+      <c r="F100" s="52"/>
+      <c r="G100" s="52"/>
+      <c r="H100" s="52"/>
+      <c r="I100" s="52"/>
+      <c r="J100" s="52"/>
+      <c r="K100" s="52"/>
+      <c r="L100" s="52"/>
+      <c r="M100" s="52"/>
+      <c r="N100" s="52"/>
+      <c r="O100" s="52"/>
+      <c r="P100" s="52"/>
+      <c r="Q100" s="52"/>
+      <c r="R100" s="52"/>
+      <c r="S100" s="52"/>
     </row>
     <row r="101" spans="1:19" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
@@ -44235,14 +44347,14 @@
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
     </row>
     <row r="37" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
@@ -44620,15 +44732,15 @@
       <c r="I70" s="1"/>
     </row>
     <row r="71" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="51"/>
-      <c r="B71" s="51"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="51"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="51"/>
-      <c r="I71" s="51"/>
+      <c r="A71" s="52"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="52"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="52"/>
+      <c r="F71" s="52"/>
+      <c r="G71" s="52"/>
+      <c r="H71" s="52"/>
+      <c r="I71" s="52"/>
     </row>
     <row r="72" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
@@ -44653,15 +44765,15 @@
       <c r="I73" s="23"/>
     </row>
     <row r="76" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="52"/>
-      <c r="B76" s="52"/>
-      <c r="C76" s="52"/>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="52"/>
-      <c r="H76" s="52"/>
-      <c r="I76" s="52"/>
+      <c r="A76" s="53"/>
+      <c r="B76" s="53"/>
+      <c r="C76" s="53"/>
+      <c r="D76" s="53"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="53"/>
+      <c r="H76" s="53"/>
+      <c r="I76" s="53"/>
     </row>
     <row r="77" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
@@ -44697,15 +44809,15 @@
       <c r="I79" s="25"/>
     </row>
     <row r="80" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="53"/>
-      <c r="B80" s="53"/>
-      <c r="C80" s="53"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53"/>
-      <c r="H80" s="53"/>
-      <c r="I80" s="53"/>
+      <c r="A80" s="54"/>
+      <c r="B80" s="54"/>
+      <c r="C80" s="54"/>
+      <c r="D80" s="54"/>
+      <c r="E80" s="54"/>
+      <c r="F80" s="54"/>
+      <c r="G80" s="54"/>
+      <c r="H80" s="54"/>
+      <c r="I80" s="54"/>
     </row>
     <row r="81" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
@@ -44741,15 +44853,15 @@
       <c r="B86" s="23"/>
     </row>
     <row r="88" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="52"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="52"/>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
-      <c r="G88" s="52"/>
-      <c r="H88" s="52"/>
-      <c r="I88" s="52"/>
+      <c r="A88" s="53"/>
+      <c r="B88" s="53"/>
+      <c r="C88" s="53"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="53"/>
+      <c r="G88" s="53"/>
+      <c r="H88" s="53"/>
+      <c r="I88" s="53"/>
     </row>
     <row r="89" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
@@ -44852,15 +44964,15 @@
       <c r="B99" s="26"/>
     </row>
     <row r="101" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A101" s="51"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
-      <c r="F101" s="51"/>
-      <c r="G101" s="51"/>
-      <c r="H101" s="51"/>
-      <c r="I101" s="51"/>
+      <c r="A101" s="52"/>
+      <c r="B101" s="52"/>
+      <c r="C101" s="52"/>
+      <c r="D101" s="52"/>
+      <c r="E101" s="52"/>
+      <c r="F101" s="52"/>
+      <c r="G101" s="52"/>
+      <c r="H101" s="52"/>
+      <c r="I101" s="52"/>
     </row>
     <row r="102" spans="1:9" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDF4456-0C1A-4430-B94F-7B6CCA0C7CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE2298F-DB35-467B-B1D7-5B3AAB1FE494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23241,21 +23241,21 @@
       </c>
       <c r="D15" s="13">
         <f t="shared" si="0"/>
-        <v>-13465</v>
+        <v>0</v>
       </c>
       <c r="E15" s="6">
         <v>0</v>
       </c>
       <c r="F15" s="13">
         <f t="shared" si="1"/>
-        <v>-16628</v>
+        <v>0</v>
       </c>
       <c r="G15" s="6">
         <v>0</v>
       </c>
       <c r="H15" s="13">
         <f t="shared" si="2"/>
-        <v>-9834</v>
+        <v>3</v>
       </c>
       <c r="I15" s="6">
         <v>0</v>
@@ -23268,21 +23268,21 @@
       </c>
       <c r="L15" s="13">
         <f t="shared" si="4"/>
-        <v>-1296</v>
+        <v>1</v>
       </c>
       <c r="M15" s="6">
         <v>0</v>
       </c>
       <c r="N15" s="13">
         <f t="shared" si="5"/>
-        <v>-4295</v>
+        <v>5</v>
       </c>
       <c r="O15" s="6">
         <v>0</v>
       </c>
       <c r="P15" s="13">
         <f t="shared" si="6"/>
-        <v>-436</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="6">
         <v>0</v>
@@ -23292,7 +23292,7 @@
       </c>
       <c r="S15" s="13">
         <f t="shared" si="7"/>
-        <v>-3859</v>
+        <v>3</v>
       </c>
       <c r="T15" s="6"/>
       <c r="U15" s="4"/>
@@ -23337,21 +23337,21 @@
       </c>
       <c r="D16" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="E16" s="6">
         <v>0</v>
       </c>
       <c r="F16" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="G16" s="6">
         <v>0</v>
       </c>
       <c r="H16" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I16" s="6">
         <v>0</v>
@@ -23372,14 +23372,14 @@
       </c>
       <c r="N16" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O16" s="6">
         <v>0</v>
       </c>
       <c r="P16" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="6">
         <v>0</v>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="S16" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="4"/>
@@ -23397,14 +23397,30 @@
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="16"/>
-      <c r="Z16" s="16"/>
-      <c r="AA16" s="16"/>
-      <c r="AB16" s="16"/>
-      <c r="AC16" s="16"/>
-      <c r="AD16" s="16"/>
+      <c r="W16" s="6">
+        <v>13465</v>
+      </c>
+      <c r="X16" s="6">
+        <v>16628</v>
+      </c>
+      <c r="Y16" s="6">
+        <v>9837</v>
+      </c>
+      <c r="Z16" s="6">
+        <v>10892</v>
+      </c>
+      <c r="AA16" s="6">
+        <v>1297</v>
+      </c>
+      <c r="AB16" s="6">
+        <v>4300</v>
+      </c>
+      <c r="AC16" s="6">
+        <v>437</v>
+      </c>
+      <c r="AD16" s="6">
+        <v>3862</v>
+      </c>
     </row>
     <row r="17" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
@@ -23418,14 +23434,14 @@
       </c>
       <c r="D17" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="E17" s="6">
         <v>0</v>
       </c>
       <c r="F17" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G17" s="6">
         <v>0</v>
@@ -23453,14 +23469,14 @@
       </c>
       <c r="N17" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O17" s="6">
         <v>0</v>
       </c>
       <c r="P17" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="6">
         <v>0</v>
@@ -23470,7 +23486,7 @@
       </c>
       <c r="S17" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T17" s="6"/>
       <c r="U17" s="4"/>
@@ -23478,14 +23494,30 @@
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="16"/>
-      <c r="AB17" s="16"/>
-      <c r="AC17" s="16"/>
-      <c r="AD17" s="16"/>
+      <c r="W17" s="16">
+        <v>13643</v>
+      </c>
+      <c r="X17" s="16">
+        <v>16910</v>
+      </c>
+      <c r="Y17" s="16">
+        <v>9844</v>
+      </c>
+      <c r="Z17" s="16">
+        <v>10892</v>
+      </c>
+      <c r="AA17" s="16">
+        <v>1297</v>
+      </c>
+      <c r="AB17" s="16">
+        <v>4305</v>
+      </c>
+      <c r="AC17" s="16">
+        <v>438</v>
+      </c>
+      <c r="AD17" s="16">
+        <v>3866</v>
+      </c>
     </row>
     <row r="18" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
@@ -23499,28 +23531,28 @@
       </c>
       <c r="D18" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="E18" s="6">
         <v>0</v>
       </c>
       <c r="F18" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G18" s="6">
         <v>0</v>
       </c>
       <c r="H18" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I18" s="6">
         <v>0</v>
       </c>
       <c r="J18" s="13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" s="6">
         <v>0</v>
@@ -23534,14 +23566,14 @@
       </c>
       <c r="N18" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O18" s="6">
         <v>0</v>
       </c>
       <c r="P18" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="6">
         <v>0</v>
@@ -23551,7 +23583,7 @@
       </c>
       <c r="S18" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T18" s="6"/>
       <c r="U18" s="4"/>
@@ -23559,14 +23591,30 @@
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
-      <c r="Y18" s="16"/>
-      <c r="Z18" s="16"/>
-      <c r="AA18" s="16"/>
-      <c r="AB18" s="16"/>
-      <c r="AC18" s="16"/>
-      <c r="AD18" s="16"/>
+      <c r="W18" s="16">
+        <v>13722</v>
+      </c>
+      <c r="X18" s="16">
+        <v>16960</v>
+      </c>
+      <c r="Y18" s="16">
+        <v>9844</v>
+      </c>
+      <c r="Z18" s="16">
+        <v>10892</v>
+      </c>
+      <c r="AA18" s="16">
+        <v>1297</v>
+      </c>
+      <c r="AB18" s="16">
+        <v>4309</v>
+      </c>
+      <c r="AC18" s="16">
+        <v>439</v>
+      </c>
+      <c r="AD18" s="16">
+        <v>3872</v>
+      </c>
     </row>
     <row r="19" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
@@ -23640,14 +23688,30 @@
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19"/>
-      <c r="Y19" s="19"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="19"/>
-      <c r="AB19" s="19"/>
-      <c r="AC19" s="19"/>
-      <c r="AD19" s="19"/>
+      <c r="W19" s="19">
+        <v>13931</v>
+      </c>
+      <c r="X19" s="19">
+        <v>17120</v>
+      </c>
+      <c r="Y19" s="19">
+        <v>9853</v>
+      </c>
+      <c r="Z19" s="19">
+        <v>10894</v>
+      </c>
+      <c r="AA19" s="19">
+        <v>1297</v>
+      </c>
+      <c r="AB19" s="19">
+        <v>4314</v>
+      </c>
+      <c r="AC19" s="19">
+        <v>440</v>
+      </c>
+      <c r="AD19" s="19">
+        <v>3874</v>
+      </c>
     </row>
     <row r="20" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
@@ -23721,14 +23785,30 @@
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
-      <c r="Y20" s="15"/>
-      <c r="Z20" s="15"/>
-      <c r="AA20" s="15"/>
-      <c r="AB20" s="15"/>
-      <c r="AC20" s="15"/>
-      <c r="AD20" s="15"/>
+      <c r="W20" s="19">
+        <v>13931</v>
+      </c>
+      <c r="X20" s="19">
+        <v>17120</v>
+      </c>
+      <c r="Y20" s="19">
+        <v>9853</v>
+      </c>
+      <c r="Z20" s="19">
+        <v>10894</v>
+      </c>
+      <c r="AA20" s="19">
+        <v>1297</v>
+      </c>
+      <c r="AB20" s="19">
+        <v>4314</v>
+      </c>
+      <c r="AC20" s="19">
+        <v>440</v>
+      </c>
+      <c r="AD20" s="19">
+        <v>3874</v>
+      </c>
     </row>
     <row r="21" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
@@ -23802,14 +23882,30 @@
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="W21" s="15"/>
-      <c r="X21" s="15"/>
-      <c r="Y21" s="15"/>
-      <c r="Z21" s="15"/>
-      <c r="AA21" s="15"/>
-      <c r="AB21" s="15"/>
-      <c r="AC21" s="15"/>
-      <c r="AD21" s="15"/>
+      <c r="W21" s="19">
+        <v>13931</v>
+      </c>
+      <c r="X21" s="19">
+        <v>17120</v>
+      </c>
+      <c r="Y21" s="19">
+        <v>9853</v>
+      </c>
+      <c r="Z21" s="19">
+        <v>10894</v>
+      </c>
+      <c r="AA21" s="19">
+        <v>1297</v>
+      </c>
+      <c r="AB21" s="19">
+        <v>4314</v>
+      </c>
+      <c r="AC21" s="19">
+        <v>440</v>
+      </c>
+      <c r="AD21" s="19">
+        <v>3874</v>
+      </c>
     </row>
     <row r="22" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
@@ -23883,14 +23979,30 @@
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="W22" s="15"/>
-      <c r="X22" s="15"/>
-      <c r="Y22" s="15"/>
-      <c r="Z22" s="15"/>
-      <c r="AA22" s="15"/>
-      <c r="AB22" s="15"/>
-      <c r="AC22" s="15"/>
-      <c r="AD22" s="15"/>
+      <c r="W22" s="19">
+        <v>13931</v>
+      </c>
+      <c r="X22" s="19">
+        <v>17120</v>
+      </c>
+      <c r="Y22" s="19">
+        <v>9853</v>
+      </c>
+      <c r="Z22" s="19">
+        <v>10894</v>
+      </c>
+      <c r="AA22" s="19">
+        <v>1297</v>
+      </c>
+      <c r="AB22" s="19">
+        <v>4314</v>
+      </c>
+      <c r="AC22" s="19">
+        <v>440</v>
+      </c>
+      <c r="AD22" s="19">
+        <v>3874</v>
+      </c>
     </row>
     <row r="23" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
@@ -23904,49 +24016,49 @@
       </c>
       <c r="D23" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E23" s="6">
         <v>0</v>
       </c>
       <c r="F23" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="G23" s="6">
         <v>0</v>
       </c>
       <c r="H23" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I23" s="6">
         <v>0</v>
       </c>
       <c r="J23" s="13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K23" s="6">
         <v>0</v>
       </c>
       <c r="L23" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="6">
         <v>0</v>
       </c>
       <c r="N23" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O23" s="6">
         <v>0</v>
       </c>
       <c r="P23" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="6">
         <v>0</v>
@@ -23956,7 +24068,7 @@
       </c>
       <c r="S23" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T23" s="6"/>
       <c r="U23" s="4"/>
@@ -23964,14 +24076,30 @@
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="W23" s="15"/>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="15"/>
-      <c r="Z23" s="15"/>
-      <c r="AA23" s="15"/>
-      <c r="AB23" s="15"/>
-      <c r="AC23" s="15"/>
-      <c r="AD23" s="15"/>
+      <c r="W23" s="19">
+        <v>13931</v>
+      </c>
+      <c r="X23" s="19">
+        <v>17120</v>
+      </c>
+      <c r="Y23" s="19">
+        <v>9853</v>
+      </c>
+      <c r="Z23" s="19">
+        <v>10894</v>
+      </c>
+      <c r="AA23" s="19">
+        <v>1297</v>
+      </c>
+      <c r="AB23" s="19">
+        <v>4314</v>
+      </c>
+      <c r="AC23" s="19">
+        <v>440</v>
+      </c>
+      <c r="AD23" s="19">
+        <v>3874</v>
+      </c>
     </row>
     <row r="24" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
@@ -23985,14 +24113,14 @@
       </c>
       <c r="D24" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E24" s="6">
         <v>0</v>
       </c>
       <c r="F24" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G24" s="6">
         <v>0</v>
@@ -24006,7 +24134,7 @@
       </c>
       <c r="J24" s="13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="6">
         <v>0</v>
@@ -24020,7 +24148,7 @@
       </c>
       <c r="N24" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O24" s="6">
         <v>0</v>
@@ -24037,7 +24165,7 @@
       </c>
       <c r="S24" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T24" s="6"/>
       <c r="U24" s="4"/>
@@ -24045,14 +24173,30 @@
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="W24" s="15"/>
-      <c r="X24" s="15"/>
-      <c r="Y24" s="15"/>
-      <c r="Z24" s="15"/>
-      <c r="AA24" s="15"/>
-      <c r="AB24" s="15"/>
-      <c r="AC24" s="15"/>
-      <c r="AD24" s="15"/>
+      <c r="W24" s="15">
+        <v>14091</v>
+      </c>
+      <c r="X24" s="15">
+        <v>17567</v>
+      </c>
+      <c r="Y24" s="15">
+        <v>9874</v>
+      </c>
+      <c r="Z24" s="15">
+        <v>10897</v>
+      </c>
+      <c r="AA24" s="15">
+        <v>1298</v>
+      </c>
+      <c r="AB24" s="15">
+        <v>4341</v>
+      </c>
+      <c r="AC24" s="15">
+        <v>442</v>
+      </c>
+      <c r="AD24" s="15">
+        <v>3898</v>
+      </c>
     </row>
     <row r="25" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
@@ -24066,49 +24210,49 @@
       </c>
       <c r="D25" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-14167</v>
       </c>
       <c r="E25" s="6">
         <v>0</v>
       </c>
       <c r="F25" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-17603</v>
       </c>
       <c r="G25" s="6">
         <v>0</v>
       </c>
       <c r="H25" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9874</v>
       </c>
       <c r="I25" s="6">
         <v>0</v>
       </c>
       <c r="J25" s="13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-10898</v>
       </c>
       <c r="K25" s="6">
         <v>0</v>
       </c>
       <c r="L25" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1298</v>
       </c>
       <c r="M25" s="6">
         <v>0</v>
       </c>
       <c r="N25" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4343</v>
       </c>
       <c r="O25" s="6">
         <v>0</v>
       </c>
       <c r="P25" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-442</v>
       </c>
       <c r="Q25" s="6">
         <v>0</v>
@@ -24118,7 +24262,7 @@
       </c>
       <c r="S25" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3900</v>
       </c>
       <c r="T25" s="6"/>
       <c r="U25" s="4"/>
@@ -24126,14 +24270,30 @@
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15"/>
-      <c r="AA25" s="15"/>
-      <c r="AB25" s="15"/>
-      <c r="AC25" s="15"/>
-      <c r="AD25" s="15"/>
+      <c r="W25" s="15">
+        <v>14167</v>
+      </c>
+      <c r="X25" s="15">
+        <v>17603</v>
+      </c>
+      <c r="Y25" s="15">
+        <v>9874</v>
+      </c>
+      <c r="Z25" s="15">
+        <v>10898</v>
+      </c>
+      <c r="AA25" s="15">
+        <v>1298</v>
+      </c>
+      <c r="AB25" s="15">
+        <v>4343</v>
+      </c>
+      <c r="AC25" s="15">
+        <v>442</v>
+      </c>
+      <c r="AD25" s="15">
+        <v>3900</v>
+      </c>
     </row>
     <row r="26" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="5">

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE2298F-DB35-467B-B1D7-5B3AAB1FE494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20A9130-763A-4D0C-8310-38D5763C9D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="105">
   <si>
     <t>Data</t>
   </si>
@@ -344,6 +344,24 @@
   </si>
   <si>
     <t>TRNSP OP AZUL TURQUESA</t>
+  </si>
+  <si>
+    <t>COMITIVA MD - CIENG, FIT NPOR</t>
+  </si>
+  <si>
+    <t>FIT NPOR</t>
+  </si>
+  <si>
+    <t>CULTOS RELIGIOSOS, FIT NPOR</t>
+  </si>
+  <si>
+    <t>3º TAF, VOT 7º CTA</t>
+  </si>
+  <si>
+    <t>3º TAF</t>
+  </si>
+  <si>
+    <t>VOT 11 RM, PASA</t>
   </si>
 </sst>
 </file>
@@ -21864,7 +21882,8 @@
     <col min="7" max="7" width="13.42578125" customWidth="1"/>
     <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="12" max="12" width="3.42578125" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
@@ -21963,7 +21982,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>45931</v>
       </c>
@@ -22029,7 +22048,9 @@
         <f t="shared" ref="S2:S32" si="7">AD3-AD2</f>
         <v>15</v>
       </c>
-      <c r="T2" s="6"/>
+      <c r="T2" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="U2" s="4"/>
       <c r="V2" s="8">
         <v>0</v>
@@ -22066,7 +22087,7 @@
         <v>4.4630000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>45932</v>
       </c>
@@ -22132,7 +22153,9 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="T3" s="6"/>
+      <c r="T3" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="U3" s="4"/>
       <c r="V3" s="12">
         <v>1</v>
@@ -22228,10 +22251,12 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="T4" s="6"/>
+      <c r="T4" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U4" s="4"/>
       <c r="V4" s="14">
-        <f t="shared" ref="V4:V32" si="8">V3+1</f>
+        <f t="shared" ref="V4:V33" si="8">V3+1</f>
         <v>2</v>
       </c>
       <c r="W4" s="6">
@@ -22325,7 +22350,9 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="T5" s="6"/>
+      <c r="T5" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U5" s="4"/>
       <c r="V5" s="14">
         <f t="shared" si="8"/>
@@ -22422,7 +22449,9 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="T6" s="6"/>
+      <c r="T6" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U6" s="4"/>
       <c r="V6" s="14">
         <f t="shared" si="8"/>
@@ -22519,7 +22548,9 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T7" s="6"/>
+      <c r="T7" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U7" s="4"/>
       <c r="V7" s="14">
         <f t="shared" si="8"/>
@@ -22616,7 +22647,9 @@
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
-      <c r="T8" s="6"/>
+      <c r="T8" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U8" s="4"/>
       <c r="V8" s="14">
         <f t="shared" si="8"/>
@@ -22713,7 +22746,9 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="T9" s="6"/>
+      <c r="T9" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U9" s="4"/>
       <c r="V9" s="14">
         <f t="shared" si="8"/>
@@ -22810,7 +22845,9 @@
         <f t="shared" si="7"/>
         <v>9</v>
       </c>
-      <c r="T10" s="6"/>
+      <c r="T10" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U10" s="4"/>
       <c r="V10" s="14">
         <f t="shared" si="8"/>
@@ -22907,7 +22944,9 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T11" s="6"/>
+      <c r="T11" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U11" s="4"/>
       <c r="V11" s="14">
         <f t="shared" si="8"/>
@@ -23004,7 +23043,9 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T12" s="6"/>
+      <c r="T12" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U12" s="4"/>
       <c r="V12" s="14">
         <f t="shared" si="8"/>
@@ -23101,7 +23142,9 @@
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
-      <c r="T13" s="6"/>
+      <c r="T13" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U13" s="4"/>
       <c r="V13" s="14">
         <f t="shared" si="8"/>
@@ -23198,7 +23241,9 @@
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="T14" s="6"/>
+      <c r="T14" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U14" s="4"/>
       <c r="V14" s="14">
         <f t="shared" si="8"/>
@@ -23229,7 +23274,7 @@
         <v>3851</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>45944</v>
       </c>
@@ -23294,7 +23339,9 @@
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="T15" s="6"/>
+      <c r="T15" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="U15" s="4"/>
       <c r="V15" s="14">
         <f t="shared" si="8"/>
@@ -23391,7 +23438,9 @@
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="T16" s="6"/>
+      <c r="T16" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="U16" s="4"/>
       <c r="V16" s="14">
         <f t="shared" si="8"/>
@@ -23422,7 +23471,7 @@
         <v>3862</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>45946</v>
       </c>
@@ -23488,7 +23537,9 @@
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="T17" s="6"/>
+      <c r="T17" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="U17" s="4"/>
       <c r="V17" s="14">
         <f t="shared" si="8"/>
@@ -23585,7 +23636,9 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="T18" s="6"/>
+      <c r="T18" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U18" s="4"/>
       <c r="V18" s="14">
         <f t="shared" si="8"/>
@@ -23682,7 +23735,9 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T19" s="6"/>
+      <c r="T19" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U19" s="17"/>
       <c r="V19" s="18">
         <f t="shared" si="8"/>
@@ -23779,7 +23834,9 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T20" s="6"/>
+      <c r="T20" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U20" s="4"/>
       <c r="V20" s="18">
         <f t="shared" si="8"/>
@@ -23876,7 +23933,9 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T21" s="6"/>
+      <c r="T21" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U21" s="4"/>
       <c r="V21" s="18">
         <f t="shared" si="8"/>
@@ -23973,7 +24032,9 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T22" s="6"/>
+      <c r="T22" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="U22" s="4"/>
       <c r="V22" s="18">
         <f t="shared" si="8"/>
@@ -24070,7 +24131,9 @@
         <f t="shared" si="7"/>
         <v>24</v>
       </c>
-      <c r="T23" s="6"/>
+      <c r="T23" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U23" s="4"/>
       <c r="V23" s="18">
         <f t="shared" si="8"/>
@@ -24167,7 +24230,9 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="T24" s="6"/>
+      <c r="T24" s="6" t="s">
+        <v>103</v>
+      </c>
       <c r="U24" s="4"/>
       <c r="V24" s="18">
         <f t="shared" si="8"/>
@@ -24210,49 +24275,49 @@
       </c>
       <c r="D25" s="13">
         <f t="shared" si="0"/>
-        <v>-14167</v>
+        <v>80</v>
       </c>
       <c r="E25" s="6">
         <v>0</v>
       </c>
       <c r="F25" s="13">
         <f t="shared" si="1"/>
-        <v>-17603</v>
+        <v>37</v>
       </c>
       <c r="G25" s="6">
         <v>0</v>
       </c>
       <c r="H25" s="13">
         <f t="shared" si="2"/>
-        <v>-9874</v>
+        <v>11</v>
       </c>
       <c r="I25" s="6">
         <v>0</v>
       </c>
       <c r="J25" s="13">
         <f t="shared" si="9"/>
-        <v>-10898</v>
+        <v>0</v>
       </c>
       <c r="K25" s="6">
         <v>0</v>
       </c>
       <c r="L25" s="13">
         <f t="shared" si="4"/>
-        <v>-1298</v>
+        <v>0</v>
       </c>
       <c r="M25" s="6">
         <v>0</v>
       </c>
       <c r="N25" s="13">
         <f t="shared" si="5"/>
-        <v>-4343</v>
+        <v>4</v>
       </c>
       <c r="O25" s="6">
         <v>0</v>
       </c>
       <c r="P25" s="13">
         <f t="shared" si="6"/>
-        <v>-442</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="6">
         <v>0</v>
@@ -24262,9 +24327,11 @@
       </c>
       <c r="S25" s="13">
         <f t="shared" si="7"/>
-        <v>-3900</v>
-      </c>
-      <c r="T25" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="T25" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U25" s="4"/>
       <c r="V25" s="18">
         <f t="shared" si="8"/>
@@ -24307,28 +24374,28 @@
       </c>
       <c r="D26" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E26" s="6">
         <v>0</v>
       </c>
       <c r="F26" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G26" s="6">
         <v>0</v>
       </c>
       <c r="H26" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" s="6">
         <v>0</v>
       </c>
       <c r="J26" s="13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="6">
         <v>0</v>
@@ -24342,14 +24409,14 @@
       </c>
       <c r="N26" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O26" s="6">
         <v>0</v>
       </c>
       <c r="P26" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="6">
         <v>0</v>
@@ -24359,22 +24426,40 @@
       </c>
       <c r="S26" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T26" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="T26" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U26" s="4"/>
       <c r="V26" s="20">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="W26" s="21"/>
-      <c r="X26" s="21"/>
-      <c r="Y26" s="21"/>
-      <c r="Z26" s="21"/>
-      <c r="AA26" s="21"/>
-      <c r="AB26" s="21"/>
-      <c r="AC26" s="21"/>
-      <c r="AD26" s="21"/>
+      <c r="W26" s="21">
+        <v>14247</v>
+      </c>
+      <c r="X26" s="21">
+        <v>17640</v>
+      </c>
+      <c r="Y26" s="21">
+        <v>9885</v>
+      </c>
+      <c r="Z26" s="21">
+        <v>10898</v>
+      </c>
+      <c r="AA26" s="21">
+        <v>1298</v>
+      </c>
+      <c r="AB26" s="21">
+        <v>4347</v>
+      </c>
+      <c r="AC26" s="21">
+        <v>443</v>
+      </c>
+      <c r="AD26" s="21">
+        <v>3903</v>
+      </c>
     </row>
     <row r="27" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
@@ -24388,42 +24473,42 @@
       </c>
       <c r="D27" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E27" s="6">
         <v>0</v>
       </c>
       <c r="F27" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G27" s="6">
         <v>0</v>
       </c>
       <c r="H27" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I27" s="6">
         <v>0</v>
       </c>
       <c r="J27" s="13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="6">
         <v>0</v>
       </c>
       <c r="L27" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="6">
         <v>0</v>
       </c>
       <c r="N27" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O27" s="6">
         <v>0</v>
@@ -24440,22 +24525,40 @@
       </c>
       <c r="S27" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T27" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="T27" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="U27" s="4"/>
       <c r="V27" s="18">
         <f t="shared" si="8"/>
         <v>25</v>
       </c>
-      <c r="W27" s="15"/>
-      <c r="X27" s="15"/>
-      <c r="Y27" s="15"/>
-      <c r="Z27" s="15"/>
-      <c r="AA27" s="15"/>
-      <c r="AB27" s="15"/>
-      <c r="AC27" s="15"/>
-      <c r="AD27" s="15"/>
+      <c r="W27" s="15">
+        <v>14302</v>
+      </c>
+      <c r="X27" s="15">
+        <v>17718</v>
+      </c>
+      <c r="Y27" s="15">
+        <v>9888</v>
+      </c>
+      <c r="Z27" s="15">
+        <v>10899</v>
+      </c>
+      <c r="AA27" s="15">
+        <v>1298</v>
+      </c>
+      <c r="AB27" s="15">
+        <v>4354</v>
+      </c>
+      <c r="AC27" s="15">
+        <v>444</v>
+      </c>
+      <c r="AD27" s="15">
+        <v>3909</v>
+      </c>
     </row>
     <row r="28" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
@@ -24469,21 +24572,21 @@
       </c>
       <c r="D28" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E28" s="6">
         <v>0</v>
       </c>
       <c r="F28" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G28" s="6">
         <v>0</v>
       </c>
       <c r="H28" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I28" s="6">
         <v>0</v>
@@ -24504,7 +24607,7 @@
       </c>
       <c r="N28" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O28" s="6">
         <v>0</v>
@@ -24521,22 +24624,40 @@
       </c>
       <c r="S28" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T28" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="T28" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="U28" s="4"/>
       <c r="V28" s="18">
         <f t="shared" si="8"/>
         <v>26</v>
       </c>
-      <c r="W28" s="15"/>
-      <c r="X28" s="15"/>
-      <c r="Y28" s="15"/>
-      <c r="Z28" s="15"/>
-      <c r="AA28" s="15"/>
-      <c r="AB28" s="15"/>
-      <c r="AC28" s="15"/>
-      <c r="AD28" s="15"/>
+      <c r="W28" s="15">
+        <v>14350</v>
+      </c>
+      <c r="X28" s="15">
+        <v>17800</v>
+      </c>
+      <c r="Y28" s="15">
+        <v>9892</v>
+      </c>
+      <c r="Z28" s="15">
+        <v>10900</v>
+      </c>
+      <c r="AA28" s="15">
+        <v>1299</v>
+      </c>
+      <c r="AB28" s="15">
+        <v>4356</v>
+      </c>
+      <c r="AC28" s="15">
+        <v>444</v>
+      </c>
+      <c r="AD28" s="15">
+        <v>3912</v>
+      </c>
     </row>
     <row r="29" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
@@ -24550,49 +24671,49 @@
       </c>
       <c r="D29" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E29" s="6">
         <v>0</v>
       </c>
       <c r="F29" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="G29" s="6">
         <v>0</v>
       </c>
       <c r="H29" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I29" s="6">
         <v>0</v>
       </c>
       <c r="J29" s="13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" s="6">
         <v>0</v>
       </c>
       <c r="L29" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="6">
         <v>0</v>
       </c>
       <c r="N29" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O29" s="6">
         <v>0</v>
       </c>
       <c r="P29" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="6">
         <v>0</v>
@@ -24602,22 +24723,40 @@
       </c>
       <c r="S29" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T29" s="6"/>
+        <v>7</v>
+      </c>
+      <c r="T29" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="U29" s="4"/>
       <c r="V29" s="18">
         <f t="shared" si="8"/>
         <v>27</v>
       </c>
-      <c r="W29" s="15"/>
-      <c r="X29" s="15"/>
-      <c r="Y29" s="15"/>
-      <c r="Z29" s="15"/>
-      <c r="AA29" s="15"/>
-      <c r="AB29" s="15"/>
-      <c r="AC29" s="15"/>
-      <c r="AD29" s="15"/>
+      <c r="W29" s="15">
+        <v>14361</v>
+      </c>
+      <c r="X29" s="15">
+        <v>17862</v>
+      </c>
+      <c r="Y29" s="15">
+        <v>9899</v>
+      </c>
+      <c r="Z29" s="15">
+        <v>10900</v>
+      </c>
+      <c r="AA29" s="15">
+        <v>1299</v>
+      </c>
+      <c r="AB29" s="15">
+        <v>4362</v>
+      </c>
+      <c r="AC29" s="15">
+        <v>444</v>
+      </c>
+      <c r="AD29" s="15">
+        <v>3917</v>
+      </c>
     </row>
     <row r="30" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
@@ -24631,21 +24770,21 @@
       </c>
       <c r="D30" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="E30" s="6">
         <v>0</v>
       </c>
       <c r="F30" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="G30" s="6">
         <v>0</v>
       </c>
       <c r="H30" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" s="6">
         <v>0</v>
@@ -24666,14 +24805,14 @@
       </c>
       <c r="N30" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O30" s="6">
         <v>0</v>
       </c>
       <c r="P30" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="6">
         <v>0</v>
@@ -24683,22 +24822,40 @@
       </c>
       <c r="S30" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T30" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="T30" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="U30" s="4"/>
       <c r="V30" s="18">
         <f t="shared" si="8"/>
         <v>28</v>
       </c>
-      <c r="W30" s="15"/>
-      <c r="X30" s="15"/>
-      <c r="Y30" s="15"/>
-      <c r="Z30" s="15"/>
-      <c r="AA30" s="15"/>
-      <c r="AB30" s="15"/>
-      <c r="AC30" s="15"/>
-      <c r="AD30" s="15"/>
+      <c r="W30" s="15">
+        <v>14446</v>
+      </c>
+      <c r="X30" s="15">
+        <v>18135</v>
+      </c>
+      <c r="Y30" s="15">
+        <v>9903</v>
+      </c>
+      <c r="Z30" s="15">
+        <v>10902</v>
+      </c>
+      <c r="AA30" s="15">
+        <v>1300</v>
+      </c>
+      <c r="AB30" s="15">
+        <v>4369</v>
+      </c>
+      <c r="AC30" s="15">
+        <v>445</v>
+      </c>
+      <c r="AD30" s="15">
+        <v>3924</v>
+      </c>
     </row>
     <row r="31" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
@@ -24712,21 +24869,21 @@
       </c>
       <c r="D31" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E31" s="6">
         <v>0</v>
       </c>
       <c r="F31" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="G31" s="6">
         <v>0</v>
       </c>
       <c r="H31" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I31" s="6">
         <v>0</v>
@@ -24747,7 +24904,7 @@
       </c>
       <c r="N31" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O31" s="6">
         <v>0</v>
@@ -24764,22 +24921,40 @@
       </c>
       <c r="S31" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T31" s="6"/>
+        <v>5</v>
+      </c>
+      <c r="T31" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="U31" s="4"/>
       <c r="V31" s="18">
         <f t="shared" si="8"/>
         <v>29</v>
       </c>
-      <c r="W31" s="15"/>
-      <c r="X31" s="15"/>
-      <c r="Y31" s="15"/>
-      <c r="Z31" s="15"/>
-      <c r="AA31" s="15"/>
-      <c r="AB31" s="15"/>
-      <c r="AC31" s="15"/>
-      <c r="AD31" s="15"/>
+      <c r="W31" s="15">
+        <v>14559</v>
+      </c>
+      <c r="X31" s="15">
+        <v>18249</v>
+      </c>
+      <c r="Y31" s="15">
+        <v>9905</v>
+      </c>
+      <c r="Z31" s="15">
+        <v>10902</v>
+      </c>
+      <c r="AA31" s="15">
+        <v>1300</v>
+      </c>
+      <c r="AB31" s="15">
+        <v>4374</v>
+      </c>
+      <c r="AC31" s="15">
+        <v>446</v>
+      </c>
+      <c r="AD31" s="15">
+        <v>3928</v>
+      </c>
     </row>
     <row r="32" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
@@ -24792,50 +24967,50 @@
         <v>0</v>
       </c>
       <c r="D32" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>W33-W32</f>
+        <v>-14669</v>
       </c>
       <c r="E32" s="6">
         <v>0</v>
       </c>
       <c r="F32" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-18387</v>
       </c>
       <c r="G32" s="6">
         <v>0</v>
       </c>
       <c r="H32" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9911</v>
       </c>
       <c r="I32" s="6">
         <v>0</v>
       </c>
       <c r="J32" s="13">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-10902</v>
       </c>
       <c r="K32" s="6">
         <v>0</v>
       </c>
       <c r="L32" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="M32" s="6">
         <v>0</v>
       </c>
       <c r="N32" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4380</v>
       </c>
       <c r="O32" s="6">
         <v>0</v>
       </c>
       <c r="P32" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-446</v>
       </c>
       <c r="Q32" s="6">
         <v>0</v>
@@ -24845,25 +25020,47 @@
       </c>
       <c r="S32" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T32" s="6"/>
+        <v>-3933</v>
+      </c>
+      <c r="T32" s="6" t="s">
+        <v>104</v>
+      </c>
       <c r="U32" s="4"/>
       <c r="V32" s="18">
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-      <c r="W32" s="15"/>
-      <c r="X32" s="15"/>
-      <c r="Y32" s="15"/>
-      <c r="Z32" s="15"/>
-      <c r="AA32" s="15"/>
-      <c r="AB32" s="15"/>
-      <c r="AC32" s="15"/>
-      <c r="AD32" s="15"/>
+      <c r="W32" s="15">
+        <v>14669</v>
+      </c>
+      <c r="X32" s="15">
+        <v>18387</v>
+      </c>
+      <c r="Y32" s="15">
+        <v>9911</v>
+      </c>
+      <c r="Z32" s="15">
+        <v>10902</v>
+      </c>
+      <c r="AA32" s="15">
+        <v>1300</v>
+      </c>
+      <c r="AB32" s="15">
+        <v>4380</v>
+      </c>
+      <c r="AC32" s="15">
+        <v>446</v>
+      </c>
+      <c r="AD32" s="15">
+        <v>3933</v>
+      </c>
     </row>
     <row r="33" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="U33" s="4"/>
+      <c r="V33" s="18">
+        <f t="shared" si="8"/>
+        <v>31</v>
+      </c>
       <c r="W33" s="15"/>
       <c r="X33" s="15"/>
       <c r="Y33" s="15"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20A9130-763A-4D0C-8310-38D5763C9D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4317855-62CF-49A6-A9A8-8B6F9D708B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -44,6 +44,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1784,17 +1806,9 @@
     <row r="17" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D17" s="45"/>
       <c r="E17" s="45"/>
-      <c r="L17" s="51">
-        <v>1531.37</v>
-      </c>
-      <c r="M17" s="51">
-        <f>L17*0.7</f>
-        <v>1071.9589999999998</v>
-      </c>
-      <c r="N17" s="51">
-        <f>L17*0.3</f>
-        <v>459.41099999999994</v>
-      </c>
+      <c r="L17" s="51"/>
+      <c r="M17" s="51"/>
+      <c r="N17" s="51"/>
     </row>
     <row r="22" spans="4:14" x14ac:dyDescent="0.2">
       <c r="J22" s="51"/>
@@ -18741,28 +18755,28 @@
       </c>
       <c r="D2" s="13">
         <f t="shared" ref="D2:D31" si="0">W3-W2</f>
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="E2" s="6">
         <v>0</v>
       </c>
       <c r="F2" s="13">
         <f t="shared" ref="F2:F31" si="1">X3-X2</f>
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="G2" s="6">
         <v>0</v>
       </c>
       <c r="H2" s="13">
         <f t="shared" ref="H2:H31" si="2">Y3-Y2</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I2" s="6">
         <v>0</v>
       </c>
       <c r="J2" s="13">
         <f t="shared" ref="J2:J14" si="3">Z3-Z2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" s="6">
         <v>0</v>
@@ -18776,14 +18790,14 @@
       </c>
       <c r="N2" s="13">
         <f t="shared" ref="N2:N31" si="5">AB3-AB2</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O2" s="6">
         <v>0</v>
       </c>
       <c r="P2" s="13">
         <f t="shared" ref="P2:P31" si="6">AC3-AC2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="6">
         <v>0</v>
@@ -18793,21 +18807,37 @@
       </c>
       <c r="S2" s="13">
         <f t="shared" ref="S2:S31" si="7">AD3-AD2</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T2" s="6"/>
       <c r="U2" s="4"/>
       <c r="V2" s="8">
         <v>0</v>
       </c>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
+      <c r="W2" s="15">
+        <v>14669</v>
+      </c>
+      <c r="X2" s="15">
+        <v>18387</v>
+      </c>
+      <c r="Y2" s="15">
+        <v>9911</v>
+      </c>
+      <c r="Z2" s="15">
+        <v>10902</v>
+      </c>
+      <c r="AA2" s="15">
+        <v>1300</v>
+      </c>
+      <c r="AB2" s="15">
+        <v>4380</v>
+      </c>
+      <c r="AC2" s="15">
+        <v>446</v>
+      </c>
+      <c r="AD2" s="15">
+        <v>3933</v>
+      </c>
       <c r="AF2" s="10" t="s">
         <v>29</v>
       </c>
@@ -18828,21 +18858,21 @@
       </c>
       <c r="D3" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E3" s="6">
         <v>0</v>
       </c>
       <c r="F3" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G3" s="6">
         <v>0</v>
       </c>
       <c r="H3" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I3" s="6">
         <v>0</v>
@@ -18863,14 +18893,14 @@
       </c>
       <c r="N3" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" s="6">
         <v>0</v>
       </c>
       <c r="P3" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="6">
         <v>0</v>
@@ -18880,21 +18910,37 @@
       </c>
       <c r="S3" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T3" s="6"/>
       <c r="U3" s="4"/>
       <c r="V3" s="12">
         <v>1</v>
       </c>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="13"/>
+      <c r="W3" s="13">
+        <v>14778</v>
+      </c>
+      <c r="X3" s="13">
+        <v>18694</v>
+      </c>
+      <c r="Y3" s="13">
+        <v>9923</v>
+      </c>
+      <c r="Z3" s="13">
+        <v>10904</v>
+      </c>
+      <c r="AA3" s="13">
+        <v>1300</v>
+      </c>
+      <c r="AB3" s="13">
+        <v>4390</v>
+      </c>
+      <c r="AC3" s="13">
+        <v>448</v>
+      </c>
+      <c r="AD3" s="13">
+        <v>3942</v>
+      </c>
     </row>
     <row r="4" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
@@ -18908,28 +18954,28 @@
       </c>
       <c r="D4" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E4" s="6">
         <v>0</v>
       </c>
       <c r="F4" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
       </c>
       <c r="H4" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>977</v>
       </c>
       <c r="I4" s="6">
         <v>0</v>
       </c>
       <c r="J4" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="6">
         <v>0</v>
@@ -18943,7 +18989,7 @@
       </c>
       <c r="N4" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O4" s="6">
         <v>0</v>
@@ -18960,7 +19006,7 @@
       </c>
       <c r="S4" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T4" s="6"/>
       <c r="U4" s="4"/>
@@ -18968,14 +19014,30 @@
         <f t="shared" ref="V4:V32" si="8">V3+1</f>
         <v>2</v>
       </c>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
+      <c r="W4" s="6">
+        <v>14804</v>
+      </c>
+      <c r="X4" s="6">
+        <v>18760</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>9928</v>
+      </c>
+      <c r="Z4" s="6">
+        <v>10904</v>
+      </c>
+      <c r="AA4" s="6">
+        <v>1300</v>
+      </c>
+      <c r="AB4" s="6">
+        <v>4393</v>
+      </c>
+      <c r="AC4" s="6">
+        <v>449</v>
+      </c>
+      <c r="AD4" s="6">
+        <v>3944</v>
+      </c>
     </row>
     <row r="5" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
@@ -18989,49 +19051,49 @@
       </c>
       <c r="D5" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-14815</v>
       </c>
       <c r="E5" s="6">
         <v>0</v>
       </c>
       <c r="F5" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-18879</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
       </c>
       <c r="H5" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-10905</v>
       </c>
       <c r="I5" s="6">
         <v>0</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-10905</v>
       </c>
       <c r="K5" s="6">
         <v>0</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="M5" s="6">
         <v>0</v>
       </c>
       <c r="N5" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4401</v>
       </c>
       <c r="O5" s="6">
         <v>0</v>
       </c>
       <c r="P5" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-449</v>
       </c>
       <c r="Q5" s="6">
         <v>0</v>
@@ -19041,7 +19103,7 @@
       </c>
       <c r="S5" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3953</v>
       </c>
       <c r="T5" s="6"/>
       <c r="U5" s="4"/>
@@ -19049,14 +19111,30 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
+      <c r="W5" s="6">
+        <v>14815</v>
+      </c>
+      <c r="X5" s="6">
+        <v>18879</v>
+      </c>
+      <c r="Y5" s="6">
+        <v>10905</v>
+      </c>
+      <c r="Z5" s="6">
+        <v>10905</v>
+      </c>
+      <c r="AA5" s="6">
+        <v>1300</v>
+      </c>
+      <c r="AB5" s="6">
+        <v>4401</v>
+      </c>
+      <c r="AC5" s="6">
+        <v>449</v>
+      </c>
+      <c r="AD5" s="6">
+        <v>3953</v>
+      </c>
     </row>
     <row r="6" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
@@ -21982,7 +22060,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>45931</v>
       </c>
@@ -21993,7 +22071,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="13">
-        <f t="shared" ref="D2:D32" si="0">W3-W2</f>
+        <f t="shared" ref="D2:D31" si="0">W3-W2</f>
         <v>207</v>
       </c>
       <c r="E2" s="6">
@@ -22080,11 +22158,11 @@
         <v>3783</v>
       </c>
       <c r="AF2" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="AG2" s="11">
+        <v>31</v>
+      </c>
+      <c r="AG2" s="11" cm="1">
         <f t="array" ref="AG2">_xlfn.IFS(AF2="Verde",0,AF2="Amarela",1.885,AF2="Vermelha P1",4.463,AF2="Vermelha P2",7.877)</f>
-        <v>4.4630000000000001</v>
+        <v>1.885</v>
       </c>
     </row>
     <row r="3" spans="1:33" ht="25.5" x14ac:dyDescent="0.2">
@@ -24968,49 +25046,49 @@
       </c>
       <c r="D32" s="13">
         <f>W33-W32</f>
-        <v>-14669</v>
+        <v>0</v>
       </c>
       <c r="E32" s="6">
         <v>0</v>
       </c>
       <c r="F32" s="13">
         <f t="shared" si="1"/>
-        <v>-18387</v>
+        <v>0</v>
       </c>
       <c r="G32" s="6">
         <v>0</v>
       </c>
       <c r="H32" s="13">
         <f t="shared" si="2"/>
-        <v>-9911</v>
+        <v>0</v>
       </c>
       <c r="I32" s="6">
         <v>0</v>
       </c>
       <c r="J32" s="13">
         <f t="shared" si="9"/>
-        <v>-10902</v>
+        <v>0</v>
       </c>
       <c r="K32" s="6">
         <v>0</v>
       </c>
       <c r="L32" s="13">
         <f t="shared" si="4"/>
-        <v>-1300</v>
+        <v>0</v>
       </c>
       <c r="M32" s="6">
         <v>0</v>
       </c>
       <c r="N32" s="13">
         <f t="shared" si="5"/>
-        <v>-4380</v>
+        <v>0</v>
       </c>
       <c r="O32" s="6">
         <v>0</v>
       </c>
       <c r="P32" s="13">
         <f t="shared" si="6"/>
-        <v>-446</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="6">
         <v>0</v>
@@ -25020,7 +25098,7 @@
       </c>
       <c r="S32" s="13">
         <f t="shared" si="7"/>
-        <v>-3933</v>
+        <v>0</v>
       </c>
       <c r="T32" s="6" t="s">
         <v>104</v>
@@ -25061,14 +25139,30 @@
         <f t="shared" si="8"/>
         <v>31</v>
       </c>
-      <c r="W33" s="15"/>
-      <c r="X33" s="15"/>
-      <c r="Y33" s="15"/>
-      <c r="Z33" s="15"/>
-      <c r="AA33" s="15"/>
-      <c r="AB33" s="15"/>
-      <c r="AC33" s="15"/>
-      <c r="AD33" s="15"/>
+      <c r="W33" s="15">
+        <v>14669</v>
+      </c>
+      <c r="X33" s="15">
+        <v>18387</v>
+      </c>
+      <c r="Y33" s="15">
+        <v>9911</v>
+      </c>
+      <c r="Z33" s="15">
+        <v>10902</v>
+      </c>
+      <c r="AA33" s="15">
+        <v>1300</v>
+      </c>
+      <c r="AB33" s="15">
+        <v>4380</v>
+      </c>
+      <c r="AC33" s="15">
+        <v>446</v>
+      </c>
+      <c r="AD33" s="15">
+        <v>3933</v>
+      </c>
     </row>
     <row r="34" spans="1:30" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="36" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
@@ -25731,7 +25825,7 @@
     <mergeCell ref="A80:I80"/>
     <mergeCell ref="A88:I88"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A89" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Bandeira,Verde,Amarela,Vermelha p1,Vermelha p2"</formula1>
       <formula2>0</formula2>
@@ -25741,7 +25835,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000000000000}">
           <x14:formula1>
             <xm:f>Planilha1!$A$2:$A$5</xm:f>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4317855-62CF-49A6-A9A8-8B6F9D708B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C395132-E934-4817-BA0C-745F3ED138BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -1626,10 +1626,10 @@
         <v>42</v>
       </c>
       <c r="B11" s="41">
-        <v>0</v>
+        <v>44891.299999999996</v>
       </c>
       <c r="C11" s="41">
-        <v>0</v>
+        <v>17165.38</v>
       </c>
       <c r="D11" s="41">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="N11" s="41">
-        <v>0</v>
+        <v>6086.84</v>
       </c>
       <c r="O11" s="41">
-        <v>0</v>
+        <v>4659.17</v>
       </c>
       <c r="P11" s="41">
         <v>0</v>
@@ -18839,11 +18839,11 @@
         <v>3933</v>
       </c>
       <c r="AF2" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AG2" s="11">
         <f t="array" ref="AG2">_xlfn.IFS(AF2="Verde",0,AF2="Amarela",1.885,AF2="Vermelha P1",4.463,AF2="Vermelha P2",7.877)</f>
-        <v>4.4630000000000001</v>
+        <v>7.8769999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="H4" s="13">
         <f t="shared" si="2"/>
-        <v>977</v>
+        <v>0</v>
       </c>
       <c r="I4" s="6">
         <v>0</v>
@@ -19051,49 +19051,49 @@
       </c>
       <c r="D5" s="13">
         <f t="shared" si="0"/>
-        <v>-14815</v>
+        <v>74</v>
       </c>
       <c r="E5" s="6">
         <v>0</v>
       </c>
       <c r="F5" s="13">
         <f t="shared" si="1"/>
-        <v>-18879</v>
+        <v>126</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
       </c>
       <c r="H5" s="13">
         <f t="shared" si="2"/>
-        <v>-10905</v>
+        <v>9</v>
       </c>
       <c r="I5" s="6">
         <v>0</v>
       </c>
       <c r="J5" s="13">
         <f t="shared" si="3"/>
-        <v>-10905</v>
+        <v>1</v>
       </c>
       <c r="K5" s="6">
         <v>0</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="4"/>
-        <v>-1300</v>
+        <v>0</v>
       </c>
       <c r="M5" s="6">
         <v>0</v>
       </c>
       <c r="N5" s="13">
         <f t="shared" si="5"/>
-        <v>-4401</v>
+        <v>4</v>
       </c>
       <c r="O5" s="6">
         <v>0</v>
       </c>
       <c r="P5" s="13">
         <f t="shared" si="6"/>
-        <v>-449</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="6">
         <v>0</v>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="S5" s="13">
         <f t="shared" si="7"/>
-        <v>-3953</v>
+        <v>3</v>
       </c>
       <c r="T5" s="6"/>
       <c r="U5" s="4"/>
@@ -19118,7 +19118,7 @@
         <v>18879</v>
       </c>
       <c r="Y5" s="6">
-        <v>10905</v>
+        <v>9928</v>
       </c>
       <c r="Z5" s="6">
         <v>10905</v>
@@ -19148,49 +19148,49 @@
       </c>
       <c r="D6" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-14889</v>
       </c>
       <c r="E6" s="6">
         <v>0</v>
       </c>
       <c r="F6" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-19005</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
       </c>
       <c r="H6" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-9937</v>
       </c>
       <c r="I6" s="6">
         <v>0</v>
       </c>
       <c r="J6" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-10906</v>
       </c>
       <c r="K6" s="6">
         <v>0</v>
       </c>
       <c r="L6" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="M6" s="6">
         <v>0</v>
       </c>
       <c r="N6" s="13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-4405</v>
       </c>
       <c r="O6" s="6">
         <v>0</v>
       </c>
       <c r="P6" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-449</v>
       </c>
       <c r="Q6" s="6">
         <v>0</v>
@@ -19200,7 +19200,7 @@
       </c>
       <c r="S6" s="13">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-3956</v>
       </c>
       <c r="T6" s="6"/>
       <c r="U6" s="4"/>
@@ -19208,14 +19208,30 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
-      <c r="AB6" s="6"/>
-      <c r="AC6" s="6"/>
-      <c r="AD6" s="6"/>
+      <c r="W6" s="6">
+        <v>14889</v>
+      </c>
+      <c r="X6" s="6">
+        <v>19005</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>9937</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>10906</v>
+      </c>
+      <c r="AA6" s="6">
+        <v>1300</v>
+      </c>
+      <c r="AB6" s="6">
+        <v>4405</v>
+      </c>
+      <c r="AC6" s="6">
+        <v>449</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>3956</v>
+      </c>
     </row>
     <row r="7" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="5">

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C395132-E934-4817-BA0C-745F3ED138BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1ED74D1-3C62-4303-946A-7CC25252364F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -19148,7 +19148,7 @@
       </c>
       <c r="D6" s="13">
         <f t="shared" si="0"/>
-        <v>-14889</v>
+        <v>-14888</v>
       </c>
       <c r="E6" s="6">
         <v>0</v>
@@ -19245,7 +19245,7 @@
       </c>
       <c r="D7" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E7" s="6">
         <v>0</v>
@@ -19305,7 +19305,9 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="W7" s="6"/>
+      <c r="W7" s="6">
+        <v>1</v>
+      </c>
       <c r="X7" s="6"/>
       <c r="Y7" s="6"/>
       <c r="Z7" s="6"/>

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgt.marquezzini\Documents\GitHub\Dashboardenergia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1ED74D1-3C62-4303-946A-7CC25252364F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890251D2-8DA6-4E55-8DD9-37CC54630EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="14" r:id="rId1"/>
@@ -18754,49 +18754,49 @@
         <v>0</v>
       </c>
       <c r="D2" s="13">
-        <f t="shared" ref="D2:D31" si="0">W3-W2</f>
+        <f>W3-W2</f>
         <v>109</v>
       </c>
       <c r="E2" s="6">
         <v>0</v>
       </c>
       <c r="F2" s="13">
-        <f t="shared" ref="F2:F31" si="1">X3-X2</f>
+        <f t="shared" ref="F2:F31" si="0">X3-X2</f>
         <v>307</v>
       </c>
       <c r="G2" s="6">
         <v>0</v>
       </c>
       <c r="H2" s="13">
-        <f t="shared" ref="H2:H31" si="2">Y3-Y2</f>
+        <f t="shared" ref="H2:H31" si="1">Y3-Y2</f>
         <v>12</v>
       </c>
       <c r="I2" s="6">
         <v>0</v>
       </c>
       <c r="J2" s="13">
-        <f t="shared" ref="J2:J14" si="3">Z3-Z2</f>
+        <f t="shared" ref="J2:J14" si="2">Z3-Z2</f>
         <v>2</v>
       </c>
       <c r="K2" s="6">
         <v>0</v>
       </c>
       <c r="L2" s="13">
-        <f t="shared" ref="L2:L31" si="4">AA3-AA2</f>
+        <f t="shared" ref="L2:L31" si="3">AA3-AA2</f>
         <v>0</v>
       </c>
       <c r="M2" s="6">
         <v>0</v>
       </c>
       <c r="N2" s="13">
-        <f t="shared" ref="N2:N31" si="5">AB3-AB2</f>
+        <f t="shared" ref="N2:N31" si="4">AB3-AB2</f>
         <v>10</v>
       </c>
       <c r="O2" s="6">
         <v>0</v>
       </c>
       <c r="P2" s="13">
-        <f t="shared" ref="P2:P31" si="6">AC3-AC2</f>
+        <f t="shared" ref="P2:P31" si="5">AC3-AC2</f>
         <v>2</v>
       </c>
       <c r="Q2" s="6">
@@ -18806,7 +18806,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="13">
-        <f t="shared" ref="S2:S31" si="7">AD3-AD2</f>
+        <f t="shared" ref="S2:S31" si="6">AD3-AD2</f>
         <v>9</v>
       </c>
       <c r="T2" s="6"/>
@@ -18857,59 +18857,59 @@
         <v>0</v>
       </c>
       <c r="D3" s="13">
+        <f t="shared" ref="D2:D31" si="7">W4-W3</f>
+        <v>26</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="13">
         <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="E3" s="6">
-        <v>0</v>
-      </c>
-      <c r="F3" s="13">
+        <v>66</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="13">
         <f t="shared" si="1"/>
-        <v>66</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0</v>
-      </c>
-      <c r="H3" s="13">
+        <v>5</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0</v>
+      </c>
+      <c r="J3" s="13">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0</v>
-      </c>
-      <c r="J3" s="13">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0</v>
+      </c>
+      <c r="L3" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K3" s="6">
-        <v>0</v>
-      </c>
-      <c r="L3" s="13">
+      <c r="M3" s="6">
+        <v>0</v>
+      </c>
+      <c r="N3" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M3" s="6">
-        <v>0</v>
-      </c>
-      <c r="N3" s="13">
+        <v>3</v>
+      </c>
+      <c r="O3" s="6">
+        <v>0</v>
+      </c>
+      <c r="P3" s="13">
         <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="O3" s="6">
-        <v>0</v>
-      </c>
-      <c r="P3" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>0</v>
+      </c>
+      <c r="R3" s="6">
+        <v>0</v>
+      </c>
+      <c r="S3" s="13">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>0</v>
-      </c>
-      <c r="R3" s="6">
-        <v>0</v>
-      </c>
-      <c r="S3" s="13">
-        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T3" s="6"/>
@@ -18953,59 +18953,59 @@
         <v>0</v>
       </c>
       <c r="D4" s="13">
+        <f t="shared" si="7"/>
+        <v>11</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="13">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0</v>
-      </c>
-      <c r="F4" s="13">
+        <v>119</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="13">
         <f t="shared" si="1"/>
-        <v>119</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0</v>
-      </c>
-      <c r="H4" s="13">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
-        <v>0</v>
-      </c>
-      <c r="J4" s="13">
+        <v>1</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0</v>
+      </c>
+      <c r="L4" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K4" s="6">
-        <v>0</v>
-      </c>
-      <c r="L4" s="13">
+        <v>0</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0</v>
+      </c>
+      <c r="N4" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M4" s="6">
-        <v>0</v>
-      </c>
-      <c r="N4" s="13">
+        <v>8</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0</v>
+      </c>
+      <c r="P4" s="13">
         <f t="shared" si="5"/>
-        <v>8</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
-      <c r="P4" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0</v>
+      </c>
+      <c r="S4" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6">
-        <v>0</v>
-      </c>
-      <c r="S4" s="13">
-        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="T4" s="6"/>
@@ -19050,59 +19050,59 @@
         <v>0</v>
       </c>
       <c r="D5" s="13">
+        <f t="shared" si="7"/>
+        <v>74</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+      <c r="F5" s="13">
         <f t="shared" si="0"/>
-        <v>74</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0</v>
-      </c>
-      <c r="F5" s="13">
+        <v>126</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0</v>
+      </c>
+      <c r="H5" s="13">
         <f t="shared" si="1"/>
-        <v>126</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13">
+        <v>9</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0</v>
+      </c>
+      <c r="J5" s="13">
         <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="I5" s="6">
-        <v>0</v>
-      </c>
-      <c r="J5" s="13">
+        <v>1</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="L5" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="K5" s="6">
-        <v>0</v>
-      </c>
-      <c r="L5" s="13">
+        <v>0</v>
+      </c>
+      <c r="M5" s="6">
+        <v>0</v>
+      </c>
+      <c r="N5" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="6">
-        <v>0</v>
-      </c>
-      <c r="N5" s="13">
+        <v>4</v>
+      </c>
+      <c r="O5" s="6">
+        <v>0</v>
+      </c>
+      <c r="P5" s="13">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6">
+        <v>0</v>
+      </c>
+      <c r="S5" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6">
-        <v>0</v>
-      </c>
-      <c r="S5" s="13">
-        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="T5" s="6"/>
@@ -19147,59 +19147,59 @@
         <v>0</v>
       </c>
       <c r="D6" s="13">
+        <f t="shared" si="7"/>
+        <v>-14888</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="13">
         <f t="shared" si="0"/>
-        <v>-14888</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="13">
+        <v>-19005</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="13">
         <f t="shared" si="1"/>
-        <v>-19005</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13">
+        <v>-9937</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="13">
         <f t="shared" si="2"/>
-        <v>-9937</v>
-      </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="13">
+        <v>-10906</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0</v>
+      </c>
+      <c r="L6" s="13">
         <f t="shared" si="3"/>
-        <v>-10906</v>
-      </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="13">
+        <v>-1300</v>
+      </c>
+      <c r="M6" s="6">
+        <v>0</v>
+      </c>
+      <c r="N6" s="13">
         <f t="shared" si="4"/>
-        <v>-1300</v>
-      </c>
-      <c r="M6" s="6">
-        <v>0</v>
-      </c>
-      <c r="N6" s="13">
+        <v>-4405</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
+      </c>
+      <c r="P6" s="13">
         <f t="shared" si="5"/>
-        <v>-4405</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="13">
+        <v>-449</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13">
         <f t="shared" si="6"/>
-        <v>-449</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6">
-        <v>0</v>
-      </c>
-      <c r="S6" s="13">
-        <f t="shared" si="7"/>
         <v>-3956</v>
       </c>
       <c r="T6" s="6"/>
@@ -19244,59 +19244,59 @@
         <v>0</v>
       </c>
       <c r="D7" s="13">
+        <f t="shared" si="7"/>
+        <v>-1</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13">
         <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="13">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="13">
+      <c r="I7" s="6">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-      <c r="J7" s="13">
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+      <c r="L7" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="13">
+      <c r="M7" s="6">
+        <v>0</v>
+      </c>
+      <c r="N7" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
-      <c r="N7" s="13">
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+      <c r="P7" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="13">
+      <c r="Q7" s="6">
+        <v>0</v>
+      </c>
+      <c r="R7" s="6">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6">
-        <v>0</v>
-      </c>
-      <c r="S7" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T7" s="6"/>
@@ -19327,59 +19327,59 @@
         <v>0</v>
       </c>
       <c r="D8" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="13">
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" s="6">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13">
+      <c r="I8" s="6">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-      <c r="J8" s="13">
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="13">
+      <c r="M8" s="6">
+        <v>0</v>
+      </c>
+      <c r="N8" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M8" s="6">
-        <v>0</v>
-      </c>
-      <c r="N8" s="13">
+      <c r="O8" s="6">
+        <v>0</v>
+      </c>
+      <c r="P8" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="13">
+      <c r="Q8" s="6">
+        <v>0</v>
+      </c>
+      <c r="R8" s="6">
+        <v>0</v>
+      </c>
+      <c r="S8" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T8" s="6"/>
@@ -19408,59 +19408,59 @@
         <v>0</v>
       </c>
       <c r="D9" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E9" s="6">
-        <v>0</v>
-      </c>
-      <c r="F9" s="13">
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-      <c r="H9" s="13">
+      <c r="I9" s="6">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I9" s="6">
-        <v>0</v>
-      </c>
-      <c r="J9" s="13">
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="L9" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="13">
+      <c r="M9" s="6">
+        <v>0</v>
+      </c>
+      <c r="N9" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M9" s="6">
-        <v>0</v>
-      </c>
-      <c r="N9" s="13">
+      <c r="O9" s="6">
+        <v>0</v>
+      </c>
+      <c r="P9" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="13">
+      <c r="Q9" s="6">
+        <v>0</v>
+      </c>
+      <c r="R9" s="6">
+        <v>0</v>
+      </c>
+      <c r="S9" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>0</v>
-      </c>
-      <c r="R9" s="6">
-        <v>0</v>
-      </c>
-      <c r="S9" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T9" s="6"/>
@@ -19489,59 +19489,59 @@
         <v>0</v>
       </c>
       <c r="D10" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10" s="6">
-        <v>0</v>
-      </c>
-      <c r="F10" s="13">
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G10" s="6">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13">
+      <c r="I10" s="6">
+        <v>0</v>
+      </c>
+      <c r="J10" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I10" s="6">
-        <v>0</v>
-      </c>
-      <c r="J10" s="13">
+      <c r="K10" s="6">
+        <v>0</v>
+      </c>
+      <c r="L10" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="13">
+      <c r="M10" s="6">
+        <v>0</v>
+      </c>
+      <c r="N10" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M10" s="6">
-        <v>0</v>
-      </c>
-      <c r="N10" s="13">
+      <c r="O10" s="6">
+        <v>0</v>
+      </c>
+      <c r="P10" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O10" s="6">
-        <v>0</v>
-      </c>
-      <c r="P10" s="13">
+      <c r="Q10" s="6">
+        <v>0</v>
+      </c>
+      <c r="R10" s="6">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>0</v>
-      </c>
-      <c r="R10" s="6">
-        <v>0</v>
-      </c>
-      <c r="S10" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T10" s="6"/>
@@ -19570,59 +19570,59 @@
         <v>0</v>
       </c>
       <c r="D11" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E11" s="6">
-        <v>0</v>
-      </c>
-      <c r="F11" s="13">
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G11" s="6">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13">
+      <c r="I11" s="6">
+        <v>0</v>
+      </c>
+      <c r="J11" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I11" s="6">
-        <v>0</v>
-      </c>
-      <c r="J11" s="13">
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="L11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K11" s="6">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13">
+      <c r="M11" s="6">
+        <v>0</v>
+      </c>
+      <c r="N11" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M11" s="6">
-        <v>0</v>
-      </c>
-      <c r="N11" s="13">
+      <c r="O11" s="6">
+        <v>0</v>
+      </c>
+      <c r="P11" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="6">
-        <v>0</v>
-      </c>
-      <c r="P11" s="13">
+      <c r="Q11" s="6">
+        <v>0</v>
+      </c>
+      <c r="R11" s="6">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>0</v>
-      </c>
-      <c r="R11" s="6">
-        <v>0</v>
-      </c>
-      <c r="S11" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T11" s="6"/>
@@ -19651,59 +19651,59 @@
         <v>0</v>
       </c>
       <c r="D12" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E12" s="6">
-        <v>0</v>
-      </c>
-      <c r="F12" s="13">
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G12" s="6">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13">
+      <c r="I12" s="6">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I12" s="6">
-        <v>0</v>
-      </c>
-      <c r="J12" s="13">
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+      <c r="L12" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K12" s="6">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13">
+      <c r="M12" s="6">
+        <v>0</v>
+      </c>
+      <c r="N12" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M12" s="6">
-        <v>0</v>
-      </c>
-      <c r="N12" s="13">
+      <c r="O12" s="6">
+        <v>0</v>
+      </c>
+      <c r="P12" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="13">
+      <c r="Q12" s="6">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>0</v>
-      </c>
-      <c r="R12" s="6">
-        <v>0</v>
-      </c>
-      <c r="S12" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T12" s="6"/>
@@ -19732,59 +19732,59 @@
         <v>0</v>
       </c>
       <c r="D13" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E13" s="6">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13">
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G13" s="6">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13">
+      <c r="I13" s="6">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I13" s="6">
-        <v>0</v>
-      </c>
-      <c r="J13" s="13">
+      <c r="K13" s="6">
+        <v>0</v>
+      </c>
+      <c r="L13" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K13" s="6">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13">
+      <c r="M13" s="6">
+        <v>0</v>
+      </c>
+      <c r="N13" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M13" s="6">
-        <v>0</v>
-      </c>
-      <c r="N13" s="13">
+      <c r="O13" s="6">
+        <v>0</v>
+      </c>
+      <c r="P13" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O13" s="6">
-        <v>0</v>
-      </c>
-      <c r="P13" s="13">
+      <c r="Q13" s="6">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>0</v>
-      </c>
-      <c r="R13" s="6">
-        <v>0</v>
-      </c>
-      <c r="S13" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T13" s="6"/>
@@ -19813,59 +19813,59 @@
         <v>0</v>
       </c>
       <c r="D14" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E14" s="6">
-        <v>0</v>
-      </c>
-      <c r="F14" s="13">
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G14" s="6">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13">
+      <c r="I14" s="6">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I14" s="6">
-        <v>0</v>
-      </c>
-      <c r="J14" s="13">
+      <c r="K14" s="6">
+        <v>0</v>
+      </c>
+      <c r="L14" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K14" s="6">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13">
+      <c r="M14" s="6">
+        <v>0</v>
+      </c>
+      <c r="N14" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M14" s="6">
-        <v>0</v>
-      </c>
-      <c r="N14" s="13">
+      <c r="O14" s="6">
+        <v>0</v>
+      </c>
+      <c r="P14" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O14" s="6">
-        <v>0</v>
-      </c>
-      <c r="P14" s="13">
+      <c r="Q14" s="6">
+        <v>0</v>
+      </c>
+      <c r="R14" s="6">
+        <v>0</v>
+      </c>
+      <c r="S14" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>0</v>
-      </c>
-      <c r="R14" s="6">
-        <v>0</v>
-      </c>
-      <c r="S14" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T14" s="6"/>
@@ -19894,21 +19894,21 @@
         <v>0</v>
       </c>
       <c r="D15" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0</v>
+      </c>
+      <c r="F15" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E15" s="6">
-        <v>0</v>
-      </c>
-      <c r="F15" s="13">
+      <c r="G15" s="6">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I15" s="6">
@@ -19921,31 +19921,31 @@
         <v>0</v>
       </c>
       <c r="L15" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="6">
+        <v>0</v>
+      </c>
+      <c r="N15" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M15" s="6">
-        <v>0</v>
-      </c>
-      <c r="N15" s="13">
+      <c r="O15" s="6">
+        <v>0</v>
+      </c>
+      <c r="P15" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O15" s="6">
-        <v>0</v>
-      </c>
-      <c r="P15" s="13">
+      <c r="Q15" s="6">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6">
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6">
-        <v>0</v>
-      </c>
-      <c r="S15" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T15" s="6"/>
@@ -19974,21 +19974,21 @@
         <v>0</v>
       </c>
       <c r="D16" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E16" s="6">
-        <v>0</v>
-      </c>
-      <c r="F16" s="13">
+      <c r="G16" s="6">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I16" s="6">
@@ -20002,31 +20002,31 @@
         <v>0</v>
       </c>
       <c r="L16" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="6">
+        <v>0</v>
+      </c>
+      <c r="N16" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M16" s="6">
-        <v>0</v>
-      </c>
-      <c r="N16" s="13">
+      <c r="O16" s="6">
+        <v>0</v>
+      </c>
+      <c r="P16" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O16" s="6">
-        <v>0</v>
-      </c>
-      <c r="P16" s="13">
+      <c r="Q16" s="6">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6">
+        <v>0</v>
+      </c>
+      <c r="S16" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6">
-        <v>0</v>
-      </c>
-      <c r="S16" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T16" s="6"/>
@@ -20055,21 +20055,21 @@
         <v>0</v>
       </c>
       <c r="D17" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0</v>
+      </c>
+      <c r="F17" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E17" s="6">
-        <v>0</v>
-      </c>
-      <c r="F17" s="13">
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I17" s="6">
@@ -20083,31 +20083,31 @@
         <v>0</v>
       </c>
       <c r="L17" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="6">
+        <v>0</v>
+      </c>
+      <c r="N17" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M17" s="6">
-        <v>0</v>
-      </c>
-      <c r="N17" s="13">
+      <c r="O17" s="6">
+        <v>0</v>
+      </c>
+      <c r="P17" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O17" s="6">
-        <v>0</v>
-      </c>
-      <c r="P17" s="13">
+      <c r="Q17" s="6">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6">
+        <v>0</v>
+      </c>
+      <c r="S17" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="6">
-        <v>0</v>
-      </c>
-      <c r="R17" s="6">
-        <v>0</v>
-      </c>
-      <c r="S17" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T17" s="6"/>
@@ -20136,21 +20136,21 @@
         <v>0</v>
       </c>
       <c r="D18" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0</v>
+      </c>
+      <c r="F18" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E18" s="6">
-        <v>0</v>
-      </c>
-      <c r="F18" s="13">
+      <c r="G18" s="6">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="6">
-        <v>0</v>
-      </c>
-      <c r="H18" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I18" s="6">
@@ -20164,31 +20164,31 @@
         <v>0</v>
       </c>
       <c r="L18" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="6">
+        <v>0</v>
+      </c>
+      <c r="N18" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M18" s="6">
-        <v>0</v>
-      </c>
-      <c r="N18" s="13">
+      <c r="O18" s="6">
+        <v>0</v>
+      </c>
+      <c r="P18" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O18" s="6">
-        <v>0</v>
-      </c>
-      <c r="P18" s="13">
+      <c r="Q18" s="6">
+        <v>0</v>
+      </c>
+      <c r="R18" s="6">
+        <v>0</v>
+      </c>
+      <c r="S18" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6">
-        <v>0</v>
-      </c>
-      <c r="R18" s="6">
-        <v>0</v>
-      </c>
-      <c r="S18" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T18" s="6"/>
@@ -20217,21 +20217,21 @@
         <v>0</v>
       </c>
       <c r="D19" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0</v>
+      </c>
+      <c r="F19" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E19" s="6">
-        <v>0</v>
-      </c>
-      <c r="F19" s="13">
+      <c r="G19" s="6">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="6">
-        <v>0</v>
-      </c>
-      <c r="H19" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I19" s="6">
@@ -20245,31 +20245,31 @@
         <v>0</v>
       </c>
       <c r="L19" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="6">
+        <v>0</v>
+      </c>
+      <c r="N19" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M19" s="6">
-        <v>0</v>
-      </c>
-      <c r="N19" s="13">
+      <c r="O19" s="6">
+        <v>0</v>
+      </c>
+      <c r="P19" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O19" s="6">
-        <v>0</v>
-      </c>
-      <c r="P19" s="13">
+      <c r="Q19" s="6">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6">
+        <v>0</v>
+      </c>
+      <c r="S19" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6">
-        <v>0</v>
-      </c>
-      <c r="S19" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T19" s="6"/>
@@ -20298,21 +20298,21 @@
         <v>0</v>
       </c>
       <c r="D20" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E20" s="6">
-        <v>0</v>
-      </c>
-      <c r="F20" s="13">
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="6">
-        <v>0</v>
-      </c>
-      <c r="H20" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I20" s="6">
@@ -20326,31 +20326,31 @@
         <v>0</v>
       </c>
       <c r="L20" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="6">
+        <v>0</v>
+      </c>
+      <c r="N20" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M20" s="6">
-        <v>0</v>
-      </c>
-      <c r="N20" s="13">
+      <c r="O20" s="6">
+        <v>0</v>
+      </c>
+      <c r="P20" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O20" s="6">
-        <v>0</v>
-      </c>
-      <c r="P20" s="13">
+      <c r="Q20" s="6">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6">
+        <v>0</v>
+      </c>
+      <c r="S20" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="6">
-        <v>0</v>
-      </c>
-      <c r="R20" s="6">
-        <v>0</v>
-      </c>
-      <c r="S20" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T20" s="6"/>
@@ -20379,21 +20379,21 @@
         <v>0</v>
       </c>
       <c r="D21" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E21" s="6">
-        <v>0</v>
-      </c>
-      <c r="F21" s="13">
+      <c r="G21" s="6">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="6">
-        <v>0</v>
-      </c>
-      <c r="H21" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I21" s="6">
@@ -20407,31 +20407,31 @@
         <v>0</v>
       </c>
       <c r="L21" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="6">
+        <v>0</v>
+      </c>
+      <c r="N21" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M21" s="6">
-        <v>0</v>
-      </c>
-      <c r="N21" s="13">
+      <c r="O21" s="6">
+        <v>0</v>
+      </c>
+      <c r="P21" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O21" s="6">
-        <v>0</v>
-      </c>
-      <c r="P21" s="13">
+      <c r="Q21" s="6">
+        <v>0</v>
+      </c>
+      <c r="R21" s="6">
+        <v>0</v>
+      </c>
+      <c r="S21" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="6">
-        <v>0</v>
-      </c>
-      <c r="R21" s="6">
-        <v>0</v>
-      </c>
-      <c r="S21" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T21" s="6"/>
@@ -20460,21 +20460,21 @@
         <v>0</v>
       </c>
       <c r="D22" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0</v>
+      </c>
+      <c r="F22" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E22" s="6">
-        <v>0</v>
-      </c>
-      <c r="F22" s="13">
+      <c r="G22" s="6">
+        <v>0</v>
+      </c>
+      <c r="H22" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="6">
-        <v>0</v>
-      </c>
-      <c r="H22" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I22" s="6">
@@ -20488,31 +20488,31 @@
         <v>0</v>
       </c>
       <c r="L22" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="6">
+        <v>0</v>
+      </c>
+      <c r="N22" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M22" s="6">
-        <v>0</v>
-      </c>
-      <c r="N22" s="13">
+      <c r="O22" s="6">
+        <v>0</v>
+      </c>
+      <c r="P22" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O22" s="6">
-        <v>0</v>
-      </c>
-      <c r="P22" s="13">
+      <c r="Q22" s="6">
+        <v>0</v>
+      </c>
+      <c r="R22" s="6">
+        <v>0</v>
+      </c>
+      <c r="S22" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="6">
-        <v>0</v>
-      </c>
-      <c r="R22" s="6">
-        <v>0</v>
-      </c>
-      <c r="S22" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T22" s="6"/>
@@ -20541,21 +20541,21 @@
         <v>0</v>
       </c>
       <c r="D23" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0</v>
+      </c>
+      <c r="F23" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E23" s="6">
-        <v>0</v>
-      </c>
-      <c r="F23" s="13">
+      <c r="G23" s="6">
+        <v>0</v>
+      </c>
+      <c r="H23" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="6">
-        <v>0</v>
-      </c>
-      <c r="H23" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I23" s="6">
@@ -20569,31 +20569,31 @@
         <v>0</v>
       </c>
       <c r="L23" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="6">
+        <v>0</v>
+      </c>
+      <c r="N23" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M23" s="6">
-        <v>0</v>
-      </c>
-      <c r="N23" s="13">
+      <c r="O23" s="6">
+        <v>0</v>
+      </c>
+      <c r="P23" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O23" s="6">
-        <v>0</v>
-      </c>
-      <c r="P23" s="13">
+      <c r="Q23" s="6">
+        <v>0</v>
+      </c>
+      <c r="R23" s="6">
+        <v>0</v>
+      </c>
+      <c r="S23" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="6">
-        <v>0</v>
-      </c>
-      <c r="R23" s="6">
-        <v>0</v>
-      </c>
-      <c r="S23" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T23" s="6"/>
@@ -20622,21 +20622,21 @@
         <v>0</v>
       </c>
       <c r="D24" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0</v>
+      </c>
+      <c r="F24" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E24" s="6">
-        <v>0</v>
-      </c>
-      <c r="F24" s="13">
+      <c r="G24" s="6">
+        <v>0</v>
+      </c>
+      <c r="H24" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="6">
-        <v>0</v>
-      </c>
-      <c r="H24" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I24" s="6">
@@ -20650,31 +20650,31 @@
         <v>0</v>
       </c>
       <c r="L24" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="6">
+        <v>0</v>
+      </c>
+      <c r="N24" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M24" s="6">
-        <v>0</v>
-      </c>
-      <c r="N24" s="13">
+      <c r="O24" s="6">
+        <v>0</v>
+      </c>
+      <c r="P24" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O24" s="6">
-        <v>0</v>
-      </c>
-      <c r="P24" s="13">
+      <c r="Q24" s="6">
+        <v>0</v>
+      </c>
+      <c r="R24" s="6">
+        <v>0</v>
+      </c>
+      <c r="S24" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="6">
-        <v>0</v>
-      </c>
-      <c r="R24" s="6">
-        <v>0</v>
-      </c>
-      <c r="S24" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T24" s="6"/>
@@ -20703,21 +20703,21 @@
         <v>0</v>
       </c>
       <c r="D25" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0</v>
+      </c>
+      <c r="F25" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E25" s="6">
-        <v>0</v>
-      </c>
-      <c r="F25" s="13">
+      <c r="G25" s="6">
+        <v>0</v>
+      </c>
+      <c r="H25" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="6">
-        <v>0</v>
-      </c>
-      <c r="H25" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I25" s="6">
@@ -20731,31 +20731,31 @@
         <v>0</v>
       </c>
       <c r="L25" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="6">
+        <v>0</v>
+      </c>
+      <c r="N25" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M25" s="6">
-        <v>0</v>
-      </c>
-      <c r="N25" s="13">
+      <c r="O25" s="6">
+        <v>0</v>
+      </c>
+      <c r="P25" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O25" s="6">
-        <v>0</v>
-      </c>
-      <c r="P25" s="13">
+      <c r="Q25" s="6">
+        <v>0</v>
+      </c>
+      <c r="R25" s="6">
+        <v>0</v>
+      </c>
+      <c r="S25" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>0</v>
-      </c>
-      <c r="R25" s="6">
-        <v>0</v>
-      </c>
-      <c r="S25" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T25" s="6"/>
@@ -20784,21 +20784,21 @@
         <v>0</v>
       </c>
       <c r="D26" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0</v>
+      </c>
+      <c r="F26" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="6">
-        <v>0</v>
-      </c>
-      <c r="F26" s="13">
+      <c r="G26" s="6">
+        <v>0</v>
+      </c>
+      <c r="H26" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="6">
-        <v>0</v>
-      </c>
-      <c r="H26" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I26" s="6">
@@ -20812,31 +20812,31 @@
         <v>0</v>
       </c>
       <c r="L26" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="6">
+        <v>0</v>
+      </c>
+      <c r="N26" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M26" s="6">
-        <v>0</v>
-      </c>
-      <c r="N26" s="13">
+      <c r="O26" s="6">
+        <v>0</v>
+      </c>
+      <c r="P26" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O26" s="6">
-        <v>0</v>
-      </c>
-      <c r="P26" s="13">
+      <c r="Q26" s="6">
+        <v>0</v>
+      </c>
+      <c r="R26" s="6">
+        <v>0</v>
+      </c>
+      <c r="S26" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="6">
-        <v>0</v>
-      </c>
-      <c r="R26" s="6">
-        <v>0</v>
-      </c>
-      <c r="S26" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T26" s="6"/>
@@ -20865,21 +20865,21 @@
         <v>0</v>
       </c>
       <c r="D27" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0</v>
+      </c>
+      <c r="F27" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E27" s="6">
-        <v>0</v>
-      </c>
-      <c r="F27" s="13">
+      <c r="G27" s="6">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="6">
-        <v>0</v>
-      </c>
-      <c r="H27" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I27" s="6">
@@ -20893,31 +20893,31 @@
         <v>0</v>
       </c>
       <c r="L27" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="6">
+        <v>0</v>
+      </c>
+      <c r="N27" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M27" s="6">
-        <v>0</v>
-      </c>
-      <c r="N27" s="13">
+      <c r="O27" s="6">
+        <v>0</v>
+      </c>
+      <c r="P27" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O27" s="6">
-        <v>0</v>
-      </c>
-      <c r="P27" s="13">
+      <c r="Q27" s="6">
+        <v>0</v>
+      </c>
+      <c r="R27" s="6">
+        <v>0</v>
+      </c>
+      <c r="S27" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="6">
-        <v>0</v>
-      </c>
-      <c r="R27" s="6">
-        <v>0</v>
-      </c>
-      <c r="S27" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T27" s="6"/>
@@ -20946,21 +20946,21 @@
         <v>0</v>
       </c>
       <c r="D28" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0</v>
+      </c>
+      <c r="F28" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="6">
-        <v>0</v>
-      </c>
-      <c r="F28" s="13">
+      <c r="G28" s="6">
+        <v>0</v>
+      </c>
+      <c r="H28" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G28" s="6">
-        <v>0</v>
-      </c>
-      <c r="H28" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I28" s="6">
@@ -20974,31 +20974,31 @@
         <v>0</v>
       </c>
       <c r="L28" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="6">
+        <v>0</v>
+      </c>
+      <c r="N28" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M28" s="6">
-        <v>0</v>
-      </c>
-      <c r="N28" s="13">
+      <c r="O28" s="6">
+        <v>0</v>
+      </c>
+      <c r="P28" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O28" s="6">
-        <v>0</v>
-      </c>
-      <c r="P28" s="13">
+      <c r="Q28" s="6">
+        <v>0</v>
+      </c>
+      <c r="R28" s="6">
+        <v>0</v>
+      </c>
+      <c r="S28" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="6">
-        <v>0</v>
-      </c>
-      <c r="R28" s="6">
-        <v>0</v>
-      </c>
-      <c r="S28" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T28" s="6"/>
@@ -21027,21 +21027,21 @@
         <v>0</v>
       </c>
       <c r="D29" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+      <c r="F29" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E29" s="6">
-        <v>0</v>
-      </c>
-      <c r="F29" s="13">
+      <c r="G29" s="6">
+        <v>0</v>
+      </c>
+      <c r="H29" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="6">
-        <v>0</v>
-      </c>
-      <c r="H29" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I29" s="6">
@@ -21055,31 +21055,31 @@
         <v>0</v>
       </c>
       <c r="L29" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="6">
+        <v>0</v>
+      </c>
+      <c r="N29" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M29" s="6">
-        <v>0</v>
-      </c>
-      <c r="N29" s="13">
+      <c r="O29" s="6">
+        <v>0</v>
+      </c>
+      <c r="P29" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O29" s="6">
-        <v>0</v>
-      </c>
-      <c r="P29" s="13">
+      <c r="Q29" s="6">
+        <v>0</v>
+      </c>
+      <c r="R29" s="6">
+        <v>0</v>
+      </c>
+      <c r="S29" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="6">
-        <v>0</v>
-      </c>
-      <c r="R29" s="6">
-        <v>0</v>
-      </c>
-      <c r="S29" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T29" s="6"/>
@@ -21108,21 +21108,21 @@
         <v>0</v>
       </c>
       <c r="D30" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0</v>
+      </c>
+      <c r="F30" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E30" s="6">
-        <v>0</v>
-      </c>
-      <c r="F30" s="13">
+      <c r="G30" s="6">
+        <v>0</v>
+      </c>
+      <c r="H30" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="6">
-        <v>0</v>
-      </c>
-      <c r="H30" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I30" s="6">
@@ -21136,31 +21136,31 @@
         <v>0</v>
       </c>
       <c r="L30" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="6">
+        <v>0</v>
+      </c>
+      <c r="N30" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M30" s="6">
-        <v>0</v>
-      </c>
-      <c r="N30" s="13">
+      <c r="O30" s="6">
+        <v>0</v>
+      </c>
+      <c r="P30" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O30" s="6">
-        <v>0</v>
-      </c>
-      <c r="P30" s="13">
+      <c r="Q30" s="6">
+        <v>0</v>
+      </c>
+      <c r="R30" s="6">
+        <v>0</v>
+      </c>
+      <c r="S30" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="6">
-        <v>0</v>
-      </c>
-      <c r="R30" s="6">
-        <v>0</v>
-      </c>
-      <c r="S30" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T30" s="6"/>
@@ -21189,21 +21189,21 @@
         <v>0</v>
       </c>
       <c r="D31" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0</v>
+      </c>
+      <c r="F31" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E31" s="6">
-        <v>0</v>
-      </c>
-      <c r="F31" s="13">
+      <c r="G31" s="6">
+        <v>0</v>
+      </c>
+      <c r="H31" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="6">
-        <v>0</v>
-      </c>
-      <c r="H31" s="13">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I31" s="6">
@@ -21217,31 +21217,31 @@
         <v>0</v>
       </c>
       <c r="L31" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="6">
+        <v>0</v>
+      </c>
+      <c r="N31" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M31" s="6">
-        <v>0</v>
-      </c>
-      <c r="N31" s="13">
+      <c r="O31" s="6">
+        <v>0</v>
+      </c>
+      <c r="P31" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O31" s="6">
-        <v>0</v>
-      </c>
-      <c r="P31" s="13">
+      <c r="Q31" s="6">
+        <v>0</v>
+      </c>
+      <c r="R31" s="6">
+        <v>0</v>
+      </c>
+      <c r="S31" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>0</v>
-      </c>
-      <c r="R31" s="6">
-        <v>0</v>
-      </c>
-      <c r="S31" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T31" s="6"/>
@@ -22082,11 +22082,11 @@
       <c r="A2" s="5">
         <v>45931</v>
       </c>
-      <c r="B2" s="6">
-        <v>0</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0</v>
+      <c r="B2" s="7">
+        <v>1974.0419995399998</v>
+      </c>
+      <c r="C2" s="7">
+        <v>274.13399992000001</v>
       </c>
       <c r="D2" s="13">
         <f t="shared" ref="D2:D31" si="0">W3-W2</f>
@@ -22123,15 +22123,14 @@
       <c r="M2" s="6">
         <v>0</v>
       </c>
-      <c r="N2" s="13">
-        <f t="shared" ref="N2:N32" si="5">AB3-AB2</f>
-        <v>16</v>
-      </c>
-      <c r="O2" s="6">
-        <v>0</v>
+      <c r="N2" s="29">
+        <v>391.82399937000008</v>
+      </c>
+      <c r="O2" s="7">
+        <v>71.903999920000004</v>
       </c>
       <c r="P2" s="13">
-        <f t="shared" ref="P2:P32" si="6">AC3-AC2</f>
+        <f t="shared" ref="P2:P32" si="5">AC3-AC2</f>
         <v>2</v>
       </c>
       <c r="Q2" s="6">
@@ -22141,7 +22140,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="13">
-        <f t="shared" ref="S2:S32" si="7">AD3-AD2</f>
+        <f t="shared" ref="S2:S32" si="6">AD3-AD2</f>
         <v>15</v>
       </c>
       <c r="T2" s="6" t="s">
@@ -22187,11 +22186,11 @@
       <c r="A3" s="5">
         <v>45932</v>
       </c>
-      <c r="B3" s="6">
-        <v>0</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0</v>
+      <c r="B3" s="7">
+        <v>1972.8239995699996</v>
+      </c>
+      <c r="C3" s="7">
+        <v>259.68599991999997</v>
       </c>
       <c r="D3" s="13">
         <f t="shared" si="0"/>
@@ -22228,25 +22227,24 @@
       <c r="M3" s="6">
         <v>0</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="29">
+        <v>371.68799940000002</v>
+      </c>
+      <c r="O3" s="7">
+        <v>70.007999880000014</v>
+      </c>
+      <c r="P3" s="13">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="O3" s="6">
-        <v>0</v>
-      </c>
-      <c r="P3" s="13">
+      <c r="Q3" s="6">
+        <v>0</v>
+      </c>
+      <c r="R3" s="6">
+        <v>0</v>
+      </c>
+      <c r="S3" s="13">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>0</v>
-      </c>
-      <c r="R3" s="6">
-        <v>0</v>
-      </c>
-      <c r="S3" s="13">
-        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T3" s="6" t="s">
@@ -22285,11 +22283,11 @@
       <c r="A4" s="5">
         <v>45933</v>
       </c>
-      <c r="B4" s="6">
-        <v>0</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0</v>
+      <c r="B4" s="7">
+        <v>1478.0639995100003</v>
+      </c>
+      <c r="C4" s="7">
+        <v>228.98399992999995</v>
       </c>
       <c r="D4" s="13">
         <f t="shared" si="0"/>
@@ -22326,25 +22324,24 @@
       <c r="M4" s="6">
         <v>0</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="29">
+        <v>363.59999933000017</v>
+      </c>
+      <c r="O4" s="7">
+        <v>68.975999879999989</v>
+      </c>
+      <c r="P4" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O4" s="6">
-        <v>0</v>
-      </c>
-      <c r="P4" s="13">
+      <c r="Q4" s="6">
+        <v>0</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0</v>
+      </c>
+      <c r="S4" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>0</v>
-      </c>
-      <c r="R4" s="6">
-        <v>0</v>
-      </c>
-      <c r="S4" s="13">
-        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="T4" s="6" t="s">
@@ -22352,7 +22349,7 @@
       </c>
       <c r="U4" s="4"/>
       <c r="V4" s="14">
-        <f t="shared" ref="V4:V33" si="8">V3+1</f>
+        <f t="shared" ref="V4:V33" si="7">V3+1</f>
         <v>2</v>
       </c>
       <c r="W4" s="6">
@@ -22384,11 +22381,11 @@
       <c r="A5" s="5">
         <v>45934</v>
       </c>
-      <c r="B5" s="6">
-        <v>0</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0</v>
+      <c r="B5" s="7">
+        <v>1104.5159994799997</v>
+      </c>
+      <c r="C5" s="7">
+        <v>196.26599991999996</v>
       </c>
       <c r="D5" s="13">
         <f t="shared" si="0"/>
@@ -22425,25 +22422,24 @@
       <c r="M5" s="6">
         <v>0</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="29">
+        <v>332.85599936999978</v>
+      </c>
+      <c r="O5" s="7">
+        <v>80.495999900000001</v>
+      </c>
+      <c r="P5" s="13">
         <f t="shared" si="5"/>
-        <v>15</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0</v>
-      </c>
-      <c r="P5" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6">
+        <v>0</v>
+      </c>
+      <c r="S5" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>0</v>
-      </c>
-      <c r="R5" s="6">
-        <v>0</v>
-      </c>
-      <c r="S5" s="13">
-        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="T5" s="6" t="s">
@@ -22451,7 +22447,7 @@
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="W5" s="6">
@@ -22483,11 +22479,11 @@
       <c r="A6" s="5">
         <v>45935</v>
       </c>
-      <c r="B6" s="6">
-        <v>0</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0</v>
+      <c r="B6" s="7">
+        <v>1267.3919994599996</v>
+      </c>
+      <c r="C6" s="7">
+        <v>228.47999994000003</v>
       </c>
       <c r="D6" s="13">
         <f t="shared" si="0"/>
@@ -22524,25 +22520,24 @@
       <c r="M6" s="6">
         <v>0</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="29">
+        <v>342.91199941999969</v>
+      </c>
+      <c r="O6" s="7">
+        <v>66.671999900000003</v>
+      </c>
+      <c r="P6" s="13">
         <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0</v>
-      </c>
-      <c r="P6" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>0</v>
-      </c>
-      <c r="R6" s="6">
-        <v>0</v>
-      </c>
-      <c r="S6" s="13">
-        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="T6" s="6" t="s">
@@ -22550,7 +22545,7 @@
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="W6" s="6">
@@ -22582,11 +22577,11 @@
       <c r="A7" s="5">
         <v>45936</v>
       </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
+      <c r="B7" s="7">
+        <v>2014.86599959</v>
+      </c>
+      <c r="C7" s="7">
+        <v>286.22999989999994</v>
       </c>
       <c r="D7" s="13">
         <f t="shared" si="0"/>
@@ -22623,25 +22618,24 @@
       <c r="M7" s="6">
         <v>0</v>
       </c>
-      <c r="N7" s="13">
+      <c r="N7" s="29">
+        <v>423.86399934999997</v>
+      </c>
+      <c r="O7" s="7">
+        <v>89.231999879999989</v>
+      </c>
+      <c r="P7" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O7" s="6">
-        <v>0</v>
-      </c>
-      <c r="P7" s="13">
+      <c r="Q7" s="6">
+        <v>0</v>
+      </c>
+      <c r="R7" s="6">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>0</v>
-      </c>
-      <c r="R7" s="6">
-        <v>0</v>
-      </c>
-      <c r="S7" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T7" s="6" t="s">
@@ -22649,7 +22643,7 @@
       </c>
       <c r="U7" s="4"/>
       <c r="V7" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="W7" s="6">
@@ -22681,11 +22675,11 @@
       <c r="A8" s="5">
         <v>45937</v>
       </c>
-      <c r="B8" s="6">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0</v>
+      <c r="B8" s="7">
+        <v>2256.0719994599995</v>
+      </c>
+      <c r="C8" s="7">
+        <v>305.67599992999999</v>
       </c>
       <c r="D8" s="13">
         <f t="shared" si="0"/>
@@ -22722,25 +22716,24 @@
       <c r="M8" s="6">
         <v>0</v>
       </c>
-      <c r="N8" s="13">
+      <c r="N8" s="29">
+        <v>464.32799941000007</v>
+      </c>
+      <c r="O8" s="7">
+        <v>98.663999889999999</v>
+      </c>
+      <c r="P8" s="13">
         <f t="shared" si="5"/>
-        <v>14</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>0</v>
+      </c>
+      <c r="R8" s="6">
+        <v>0</v>
+      </c>
+      <c r="S8" s="13">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="13">
-        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="T8" s="6" t="s">
@@ -22748,7 +22741,7 @@
       </c>
       <c r="U8" s="4"/>
       <c r="V8" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="W8" s="6">
@@ -22780,11 +22773,11 @@
       <c r="A9" s="5">
         <v>45938</v>
       </c>
-      <c r="B9" s="6">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0</v>
+      <c r="B9" s="7">
+        <v>2261.1539994999989</v>
+      </c>
+      <c r="C9" s="7">
+        <v>319.57799992999998</v>
       </c>
       <c r="D9" s="13">
         <f t="shared" si="0"/>
@@ -22821,25 +22814,24 @@
       <c r="M9" s="6">
         <v>0</v>
       </c>
-      <c r="N9" s="13">
+      <c r="N9" s="29">
+        <v>469.39199939999986</v>
+      </c>
+      <c r="O9" s="7">
+        <v>94.703999880000012</v>
+      </c>
+      <c r="P9" s="13">
         <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0</v>
-      </c>
-      <c r="P9" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>0</v>
+      </c>
+      <c r="R9" s="6">
+        <v>0</v>
+      </c>
+      <c r="S9" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>0</v>
-      </c>
-      <c r="R9" s="6">
-        <v>0</v>
-      </c>
-      <c r="S9" s="13">
-        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="T9" s="6" t="s">
@@ -22847,7 +22839,7 @@
       </c>
       <c r="U9" s="4"/>
       <c r="V9" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="W9" s="6">
@@ -22879,11 +22871,11 @@
       <c r="A10" s="5">
         <v>45939</v>
       </c>
-      <c r="B10" s="6">
-        <v>0</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0</v>
+      <c r="B10" s="7">
+        <v>2287.5719994599995</v>
+      </c>
+      <c r="C10" s="7">
+        <v>309.49799994</v>
       </c>
       <c r="D10" s="13">
         <f t="shared" si="0"/>
@@ -22920,25 +22912,24 @@
       <c r="M10" s="6">
         <v>0</v>
       </c>
-      <c r="N10" s="13">
+      <c r="N10" s="29">
+        <v>432.35999932000004</v>
+      </c>
+      <c r="O10" s="7">
+        <v>76.943999890000001</v>
+      </c>
+      <c r="P10" s="13">
         <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="O10" s="6">
-        <v>0</v>
-      </c>
-      <c r="P10" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>0</v>
+      </c>
+      <c r="R10" s="6">
+        <v>0</v>
+      </c>
+      <c r="S10" s="13">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>0</v>
-      </c>
-      <c r="R10" s="6">
-        <v>0</v>
-      </c>
-      <c r="S10" s="13">
-        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="T10" s="6" t="s">
@@ -22946,7 +22937,7 @@
       </c>
       <c r="U10" s="4"/>
       <c r="V10" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="W10" s="6">
@@ -22978,11 +22969,11 @@
       <c r="A11" s="5">
         <v>45940</v>
       </c>
-      <c r="B11" s="6">
-        <v>0</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0</v>
+      <c r="B11" s="7">
+        <v>1645.3919995300002</v>
+      </c>
+      <c r="C11" s="7">
+        <v>273.29399991999998</v>
       </c>
       <c r="D11" s="13">
         <f t="shared" si="0"/>
@@ -23019,25 +23010,24 @@
       <c r="M11" s="6">
         <v>0</v>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="29">
+        <v>361.91999931000021</v>
+      </c>
+      <c r="O11" s="7">
+        <v>55.751999900000008</v>
+      </c>
+      <c r="P11" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="6">
-        <v>0</v>
-      </c>
-      <c r="P11" s="13">
+      <c r="Q11" s="6">
+        <v>0</v>
+      </c>
+      <c r="R11" s="6">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>0</v>
-      </c>
-      <c r="R11" s="6">
-        <v>0</v>
-      </c>
-      <c r="S11" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T11" s="6" t="s">
@@ -23045,7 +23035,7 @@
       </c>
       <c r="U11" s="4"/>
       <c r="V11" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="W11" s="6">
@@ -23077,11 +23067,11 @@
       <c r="A12" s="5">
         <v>45941</v>
       </c>
-      <c r="B12" s="6">
-        <v>0</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0</v>
+      <c r="B12" s="7">
+        <v>1321.9919994899997</v>
+      </c>
+      <c r="C12" s="7">
+        <v>213.48599991</v>
       </c>
       <c r="D12" s="13">
         <f t="shared" si="0"/>
@@ -23118,25 +23108,24 @@
       <c r="M12" s="6">
         <v>0</v>
       </c>
-      <c r="N12" s="13">
+      <c r="N12" s="29">
+        <v>309.23999933000005</v>
+      </c>
+      <c r="O12" s="7">
+        <v>47.063999870000004</v>
+      </c>
+      <c r="P12" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="13">
+      <c r="Q12" s="6">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6">
+        <v>0</v>
+      </c>
+      <c r="S12" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>0</v>
-      </c>
-      <c r="R12" s="6">
-        <v>0</v>
-      </c>
-      <c r="S12" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T12" s="6" t="s">
@@ -23144,7 +23133,7 @@
       </c>
       <c r="U12" s="4"/>
       <c r="V12" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="W12" s="6">
@@ -23176,11 +23165,11 @@
       <c r="A13" s="5">
         <v>45942</v>
       </c>
-      <c r="B13" s="6">
-        <v>0</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0</v>
+      <c r="B13" s="7">
+        <v>1269.0719994499996</v>
+      </c>
+      <c r="C13" s="7">
+        <v>197.39999994999999</v>
       </c>
       <c r="D13" s="13">
         <f t="shared" si="0"/>
@@ -23217,25 +23206,24 @@
       <c r="M13" s="6">
         <v>0</v>
       </c>
-      <c r="N13" s="13">
+      <c r="N13" s="29">
+        <v>323.85599941999976</v>
+      </c>
+      <c r="O13" s="7">
+        <v>74.327999879999993</v>
+      </c>
+      <c r="P13" s="13">
         <f t="shared" si="5"/>
-        <v>13</v>
-      </c>
-      <c r="O13" s="6">
-        <v>0</v>
-      </c>
-      <c r="P13" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>0</v>
-      </c>
-      <c r="R13" s="6">
-        <v>0</v>
-      </c>
-      <c r="S13" s="13">
-        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="T13" s="6" t="s">
@@ -23243,7 +23231,7 @@
       </c>
       <c r="U13" s="4"/>
       <c r="V13" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="W13" s="6">
@@ -23275,11 +23263,11 @@
       <c r="A14" s="5">
         <v>45943</v>
       </c>
-      <c r="B14" s="6">
-        <v>0</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0</v>
+      <c r="B14" s="7">
+        <v>1736.1959994599993</v>
+      </c>
+      <c r="C14" s="7">
+        <v>283.49999989000003</v>
       </c>
       <c r="D14" s="13">
         <f t="shared" si="0"/>
@@ -23316,25 +23304,24 @@
       <c r="M14" s="6">
         <v>0</v>
       </c>
-      <c r="N14" s="13">
+      <c r="N14" s="29">
+        <v>289.05599934999987</v>
+      </c>
+      <c r="O14" s="7">
+        <v>56.471999899999993</v>
+      </c>
+      <c r="P14" s="13">
         <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="O14" s="6">
-        <v>0</v>
-      </c>
-      <c r="P14" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>0</v>
+      </c>
+      <c r="R14" s="6">
+        <v>0</v>
+      </c>
+      <c r="S14" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>0</v>
-      </c>
-      <c r="R14" s="6">
-        <v>0</v>
-      </c>
-      <c r="S14" s="13">
-        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="T14" s="6" t="s">
@@ -23342,7 +23329,7 @@
       </c>
       <c r="U14" s="4"/>
       <c r="V14" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="W14" s="6">
@@ -23374,11 +23361,11 @@
       <c r="A15" s="5">
         <v>45944</v>
       </c>
-      <c r="B15" s="6">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0</v>
+      <c r="B15" s="7">
+        <v>2011.6739994899995</v>
+      </c>
+      <c r="C15" s="7">
+        <v>269.34599992</v>
       </c>
       <c r="D15" s="13">
         <f t="shared" si="0"/>
@@ -23414,25 +23401,24 @@
       <c r="M15" s="6">
         <v>0</v>
       </c>
-      <c r="N15" s="13">
+      <c r="N15" s="29">
+        <v>299.37599936000015</v>
+      </c>
+      <c r="O15" s="7">
+        <v>66.143999910000005</v>
+      </c>
+      <c r="P15" s="13">
         <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="O15" s="6">
-        <v>0</v>
-      </c>
-      <c r="P15" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>0</v>
+      </c>
+      <c r="R15" s="6">
+        <v>0</v>
+      </c>
+      <c r="S15" s="13">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6">
-        <v>0</v>
-      </c>
-      <c r="S15" s="13">
-        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="T15" s="6" t="s">
@@ -23440,7 +23426,7 @@
       </c>
       <c r="U15" s="4"/>
       <c r="V15" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="W15" s="6">
@@ -23472,11 +23458,11 @@
       <c r="A16" s="5">
         <v>45945</v>
       </c>
-      <c r="B16" s="6">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0</v>
+      <c r="B16" s="7">
+        <v>2204.7899994199988</v>
+      </c>
+      <c r="C16" s="7">
+        <v>365.77799989999994</v>
       </c>
       <c r="D16" s="13">
         <f t="shared" si="0"/>
@@ -23500,7 +23486,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="13">
-        <f t="shared" ref="J16:J32" si="9">Z17-Z16</f>
+        <f t="shared" ref="J16:J32" si="8">Z17-Z16</f>
         <v>0</v>
       </c>
       <c r="K16" s="6">
@@ -23513,25 +23499,24 @@
       <c r="M16" s="6">
         <v>0</v>
       </c>
-      <c r="N16" s="13">
+      <c r="N16" s="29">
+        <v>383.92799930000001</v>
+      </c>
+      <c r="O16" s="7">
+        <v>80.903999909999996</v>
+      </c>
+      <c r="P16" s="13">
         <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="O16" s="6">
-        <v>0</v>
-      </c>
-      <c r="P16" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6">
+        <v>0</v>
+      </c>
+      <c r="S16" s="13">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q16" s="6">
-        <v>0</v>
-      </c>
-      <c r="R16" s="6">
-        <v>0</v>
-      </c>
-      <c r="S16" s="13">
-        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="T16" s="6" t="s">
@@ -23539,7 +23524,7 @@
       </c>
       <c r="U16" s="4"/>
       <c r="V16" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="W16" s="6">
@@ -23571,11 +23556,11 @@
       <c r="A17" s="5">
         <v>45946</v>
       </c>
-      <c r="B17" s="6">
-        <v>0</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0</v>
+      <c r="B17" s="7">
+        <v>2037.1679994899994</v>
+      </c>
+      <c r="C17" s="7">
+        <v>278.9219999</v>
       </c>
       <c r="D17" s="13">
         <f t="shared" si="0"/>
@@ -23599,7 +23584,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K17" s="6">
@@ -23612,25 +23597,24 @@
       <c r="M17" s="6">
         <v>0</v>
       </c>
-      <c r="N17" s="13">
+      <c r="N17" s="29">
+        <v>461.90399937000012</v>
+      </c>
+      <c r="O17" s="7">
+        <v>91.055999880000002</v>
+      </c>
+      <c r="P17" s="13">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="O17" s="6">
-        <v>0</v>
-      </c>
-      <c r="P17" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6">
+        <v>0</v>
+      </c>
+      <c r="S17" s="13">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q17" s="6">
-        <v>0</v>
-      </c>
-      <c r="R17" s="6">
-        <v>0</v>
-      </c>
-      <c r="S17" s="13">
-        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="T17" s="6" t="s">
@@ -23638,7 +23622,7 @@
       </c>
       <c r="U17" s="4"/>
       <c r="V17" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="W17" s="16">
@@ -23670,11 +23654,11 @@
       <c r="A18" s="5">
         <v>45947</v>
       </c>
-      <c r="B18" s="6">
-        <v>0</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0</v>
+      <c r="B18" s="7">
+        <v>1163.2739994400004</v>
+      </c>
+      <c r="C18" s="7">
+        <v>259.68599992000003</v>
       </c>
       <c r="D18" s="13">
         <f t="shared" si="0"/>
@@ -23698,7 +23682,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="K18" s="6">
@@ -23711,25 +23695,24 @@
       <c r="M18" s="6">
         <v>0</v>
       </c>
-      <c r="N18" s="13">
+      <c r="N18" s="29">
+        <v>450.26399930000014</v>
+      </c>
+      <c r="O18" s="7">
+        <v>83.687999889999986</v>
+      </c>
+      <c r="P18" s="13">
         <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="O18" s="6">
-        <v>0</v>
-      </c>
-      <c r="P18" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>0</v>
+      </c>
+      <c r="R18" s="6">
+        <v>0</v>
+      </c>
+      <c r="S18" s="13">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q18" s="6">
-        <v>0</v>
-      </c>
-      <c r="R18" s="6">
-        <v>0</v>
-      </c>
-      <c r="S18" s="13">
-        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T18" s="6" t="s">
@@ -23737,7 +23720,7 @@
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="W18" s="16">
@@ -23769,11 +23752,11 @@
       <c r="A19" s="5">
         <v>45948</v>
       </c>
-      <c r="B19" s="6">
-        <v>0</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0</v>
+      <c r="B19" s="7">
+        <v>1258.823999499999</v>
+      </c>
+      <c r="C19" s="7">
+        <v>191.89799992000002</v>
       </c>
       <c r="D19" s="13">
         <f t="shared" si="0"/>
@@ -23797,7 +23780,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K19" s="6">
@@ -23810,25 +23793,24 @@
       <c r="M19" s="6">
         <v>0</v>
       </c>
-      <c r="N19" s="13">
+      <c r="N19" s="29">
+        <v>378.52799936999975</v>
+      </c>
+      <c r="O19" s="7">
+        <v>65.903999900000002</v>
+      </c>
+      <c r="P19" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O19" s="6">
-        <v>0</v>
-      </c>
-      <c r="P19" s="13">
+      <c r="Q19" s="6">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6">
+        <v>0</v>
+      </c>
+      <c r="S19" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>0</v>
-      </c>
-      <c r="R19" s="6">
-        <v>0</v>
-      </c>
-      <c r="S19" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T19" s="6" t="s">
@@ -23836,7 +23818,7 @@
       </c>
       <c r="U19" s="17"/>
       <c r="V19" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="W19" s="19">
@@ -23868,11 +23850,11 @@
       <c r="A20" s="5">
         <v>45949</v>
       </c>
-      <c r="B20" s="6">
-        <v>0</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0</v>
+      <c r="B20" s="7">
+        <v>1154.7479994600003</v>
+      </c>
+      <c r="C20" s="7">
+        <v>190.30199994999995</v>
       </c>
       <c r="D20" s="13">
         <f t="shared" si="0"/>
@@ -23896,7 +23878,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K20" s="6">
@@ -23909,25 +23891,24 @@
       <c r="M20" s="6">
         <v>0</v>
       </c>
-      <c r="N20" s="13">
+      <c r="N20" s="29">
+        <v>280.51199933999993</v>
+      </c>
+      <c r="O20" s="7">
+        <v>50.927999919999991</v>
+      </c>
+      <c r="P20" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O20" s="6">
-        <v>0</v>
-      </c>
-      <c r="P20" s="13">
+      <c r="Q20" s="6">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6">
+        <v>0</v>
+      </c>
+      <c r="S20" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="6">
-        <v>0</v>
-      </c>
-      <c r="R20" s="6">
-        <v>0</v>
-      </c>
-      <c r="S20" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T20" s="6" t="s">
@@ -23935,7 +23916,7 @@
       </c>
       <c r="U20" s="4"/>
       <c r="V20" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="W20" s="19">
@@ -23967,11 +23948,11 @@
       <c r="A21" s="5">
         <v>45950</v>
       </c>
-      <c r="B21" s="6">
-        <v>0</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0</v>
+      <c r="B21" s="7">
+        <v>1641.4019995399999</v>
+      </c>
+      <c r="C21" s="7">
+        <v>236.87999991999999</v>
       </c>
       <c r="D21" s="13">
         <f t="shared" si="0"/>
@@ -23995,7 +23976,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K21" s="6">
@@ -24008,25 +23989,24 @@
       <c r="M21" s="6">
         <v>0</v>
       </c>
-      <c r="N21" s="13">
+      <c r="N21" s="29">
+        <v>260.13599938999988</v>
+      </c>
+      <c r="O21" s="7">
+        <v>59.255999899999999</v>
+      </c>
+      <c r="P21" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O21" s="6">
-        <v>0</v>
-      </c>
-      <c r="P21" s="13">
+      <c r="Q21" s="6">
+        <v>0</v>
+      </c>
+      <c r="R21" s="6">
+        <v>0</v>
+      </c>
+      <c r="S21" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="6">
-        <v>0</v>
-      </c>
-      <c r="R21" s="6">
-        <v>0</v>
-      </c>
-      <c r="S21" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T21" s="6" t="s">
@@ -24034,7 +24014,7 @@
       </c>
       <c r="U21" s="4"/>
       <c r="V21" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="W21" s="19">
@@ -24066,11 +24046,11 @@
       <c r="A22" s="5">
         <v>45951</v>
       </c>
-      <c r="B22" s="6">
-        <v>0</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0</v>
+      <c r="B22" s="7">
+        <v>1585.6259995699991</v>
+      </c>
+      <c r="C22" s="7">
+        <v>230.36999992999998</v>
       </c>
       <c r="D22" s="13">
         <f t="shared" si="0"/>
@@ -24094,7 +24074,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K22" s="6">
@@ -24107,25 +24087,24 @@
       <c r="M22" s="6">
         <v>0</v>
       </c>
-      <c r="N22" s="13">
+      <c r="N22" s="29">
+        <v>248.73599941999996</v>
+      </c>
+      <c r="O22" s="7">
+        <v>61.439999889999989</v>
+      </c>
+      <c r="P22" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O22" s="6">
-        <v>0</v>
-      </c>
-      <c r="P22" s="13">
+      <c r="Q22" s="6">
+        <v>0</v>
+      </c>
+      <c r="R22" s="6">
+        <v>0</v>
+      </c>
+      <c r="S22" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="6">
-        <v>0</v>
-      </c>
-      <c r="R22" s="6">
-        <v>0</v>
-      </c>
-      <c r="S22" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T22" s="6" t="s">
@@ -24133,7 +24112,7 @@
       </c>
       <c r="U22" s="4"/>
       <c r="V22" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="W22" s="19">
@@ -24165,11 +24144,11 @@
       <c r="A23" s="5">
         <v>45952</v>
       </c>
-      <c r="B23" s="6">
-        <v>0</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0</v>
+      <c r="B23" s="7">
+        <v>1632.9599995199994</v>
+      </c>
+      <c r="C23" s="7">
+        <v>272.70599993000002</v>
       </c>
       <c r="D23" s="13">
         <f t="shared" si="0"/>
@@ -24193,7 +24172,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="K23" s="6">
@@ -24206,25 +24185,24 @@
       <c r="M23" s="6">
         <v>0</v>
       </c>
-      <c r="N23" s="13">
+      <c r="N23" s="29">
+        <v>251.32799935999972</v>
+      </c>
+      <c r="O23" s="7">
+        <v>62.639999920000001</v>
+      </c>
+      <c r="P23" s="13">
         <f t="shared" si="5"/>
-        <v>27</v>
-      </c>
-      <c r="O23" s="6">
-        <v>0</v>
-      </c>
-      <c r="P23" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>0</v>
+      </c>
+      <c r="R23" s="6">
+        <v>0</v>
+      </c>
+      <c r="S23" s="13">
         <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="Q23" s="6">
-        <v>0</v>
-      </c>
-      <c r="R23" s="6">
-        <v>0</v>
-      </c>
-      <c r="S23" s="13">
-        <f t="shared" si="7"/>
         <v>24</v>
       </c>
       <c r="T23" s="6" t="s">
@@ -24232,7 +24210,7 @@
       </c>
       <c r="U23" s="4"/>
       <c r="V23" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>21</v>
       </c>
       <c r="W23" s="19">
@@ -24264,11 +24242,11 @@
       <c r="A24" s="5">
         <v>45953</v>
       </c>
-      <c r="B24" s="6">
-        <v>0</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0</v>
+      <c r="B24" s="7">
+        <v>1804.90799947</v>
+      </c>
+      <c r="C24" s="7">
+        <v>256.03199992999998</v>
       </c>
       <c r="D24" s="13">
         <f t="shared" si="0"/>
@@ -24292,7 +24270,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K24" s="6">
@@ -24305,25 +24283,24 @@
       <c r="M24" s="6">
         <v>0</v>
       </c>
-      <c r="N24" s="13">
+      <c r="N24" s="29">
+        <v>260.20799942999986</v>
+      </c>
+      <c r="O24" s="7">
+        <v>57.52799989999999</v>
+      </c>
+      <c r="P24" s="13">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="O24" s="6">
-        <v>0</v>
-      </c>
-      <c r="P24" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0</v>
+      </c>
+      <c r="R24" s="6">
+        <v>0</v>
+      </c>
+      <c r="S24" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="6">
-        <v>0</v>
-      </c>
-      <c r="R24" s="6">
-        <v>0</v>
-      </c>
-      <c r="S24" s="13">
-        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T24" s="6" t="s">
@@ -24331,7 +24308,7 @@
       </c>
       <c r="U24" s="4"/>
       <c r="V24" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="W24" s="15">
@@ -24363,11 +24340,11 @@
       <c r="A25" s="5">
         <v>45954</v>
       </c>
-      <c r="B25" s="6">
-        <v>0</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0</v>
+      <c r="B25" s="7">
+        <v>1398.3479995799994</v>
+      </c>
+      <c r="C25" s="7">
+        <v>219.40799992000001</v>
       </c>
       <c r="D25" s="13">
         <f t="shared" si="0"/>
@@ -24391,7 +24368,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K25" s="6">
@@ -24404,25 +24381,24 @@
       <c r="M25" s="6">
         <v>0</v>
       </c>
-      <c r="N25" s="13">
+      <c r="N25" s="29">
+        <v>301.03199926999997</v>
+      </c>
+      <c r="O25" s="7">
+        <v>54.431999900000001</v>
+      </c>
+      <c r="P25" s="13">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="O25" s="6">
-        <v>0</v>
-      </c>
-      <c r="P25" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>0</v>
+      </c>
+      <c r="R25" s="6">
+        <v>0</v>
+      </c>
+      <c r="S25" s="13">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>0</v>
-      </c>
-      <c r="R25" s="6">
-        <v>0</v>
-      </c>
-      <c r="S25" s="13">
-        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="T25" s="6" t="s">
@@ -24430,7 +24406,7 @@
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>23</v>
       </c>
       <c r="W25" s="15">
@@ -24462,11 +24438,11 @@
       <c r="A26" s="5">
         <v>45955</v>
       </c>
-      <c r="B26" s="6">
-        <v>0</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0</v>
+      <c r="B26" s="7">
+        <v>1327.7879995399994</v>
+      </c>
+      <c r="C26" s="7">
+        <v>228.94199995000002</v>
       </c>
       <c r="D26" s="13">
         <f t="shared" si="0"/>
@@ -24490,7 +24466,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K26" s="6">
@@ -24503,25 +24479,24 @@
       <c r="M26" s="6">
         <v>0</v>
       </c>
-      <c r="N26" s="13">
+      <c r="N26" s="29">
+        <v>342.31199933999994</v>
+      </c>
+      <c r="O26" s="7">
+        <v>63.863999929999991</v>
+      </c>
+      <c r="P26" s="13">
         <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="O26" s="6">
-        <v>0</v>
-      </c>
-      <c r="P26" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>0</v>
+      </c>
+      <c r="R26" s="6">
+        <v>0</v>
+      </c>
+      <c r="S26" s="13">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q26" s="6">
-        <v>0</v>
-      </c>
-      <c r="R26" s="6">
-        <v>0</v>
-      </c>
-      <c r="S26" s="13">
-        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="T26" s="6" t="s">
@@ -24529,7 +24504,7 @@
       </c>
       <c r="U26" s="4"/>
       <c r="V26" s="20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
       <c r="W26" s="21">
@@ -24561,11 +24536,11 @@
       <c r="A27" s="5">
         <v>45956</v>
       </c>
-      <c r="B27" s="6">
-        <v>0</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0</v>
+      <c r="B27" s="7">
+        <v>1327.9139995199998</v>
+      </c>
+      <c r="C27" s="7">
+        <v>249.56399994</v>
       </c>
       <c r="D27" s="13">
         <f t="shared" si="0"/>
@@ -24589,7 +24564,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K27" s="6">
@@ -24602,25 +24577,24 @@
       <c r="M27" s="6">
         <v>0</v>
       </c>
-      <c r="N27" s="13">
+      <c r="N27" s="29">
+        <v>369.47999936999986</v>
+      </c>
+      <c r="O27" s="7">
+        <v>76.439999910000012</v>
+      </c>
+      <c r="P27" s="13">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="O27" s="6">
-        <v>0</v>
-      </c>
-      <c r="P27" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>0</v>
+      </c>
+      <c r="R27" s="6">
+        <v>0</v>
+      </c>
+      <c r="S27" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="6">
-        <v>0</v>
-      </c>
-      <c r="R27" s="6">
-        <v>0</v>
-      </c>
-      <c r="S27" s="13">
-        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="T27" s="6" t="s">
@@ -24628,7 +24602,7 @@
       </c>
       <c r="U27" s="4"/>
       <c r="V27" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="W27" s="15">
@@ -24660,11 +24634,11 @@
       <c r="A28" s="5">
         <v>45957</v>
       </c>
-      <c r="B28" s="6">
-        <v>0</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0</v>
+      <c r="B28" s="7">
+        <v>1937.3339994699995</v>
+      </c>
+      <c r="C28" s="7">
+        <v>285.47399992000004</v>
       </c>
       <c r="D28" s="13">
         <f t="shared" si="0"/>
@@ -24688,7 +24662,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K28" s="6">
@@ -24701,25 +24675,24 @@
       <c r="M28" s="6">
         <v>0</v>
       </c>
-      <c r="N28" s="13">
+      <c r="N28" s="29">
+        <v>332.37599937999994</v>
+      </c>
+      <c r="O28" s="7">
+        <v>59.807999889999991</v>
+      </c>
+      <c r="P28" s="13">
         <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="O28" s="6">
-        <v>0</v>
-      </c>
-      <c r="P28" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0</v>
+      </c>
+      <c r="R28" s="6">
+        <v>0</v>
+      </c>
+      <c r="S28" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="6">
-        <v>0</v>
-      </c>
-      <c r="R28" s="6">
-        <v>0</v>
-      </c>
-      <c r="S28" s="13">
-        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="T28" s="6" t="s">
@@ -24727,7 +24700,7 @@
       </c>
       <c r="U28" s="4"/>
       <c r="V28" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="W28" s="15">
@@ -24759,11 +24732,11 @@
       <c r="A29" s="5">
         <v>45958</v>
       </c>
-      <c r="B29" s="6">
-        <v>0</v>
-      </c>
-      <c r="C29" s="6">
-        <v>0</v>
+      <c r="B29" s="7">
+        <v>2172.5759995200006</v>
+      </c>
+      <c r="C29" s="7">
+        <v>295.25999992999999</v>
       </c>
       <c r="D29" s="13">
         <f t="shared" si="0"/>
@@ -24787,7 +24760,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="K29" s="6">
@@ -24800,25 +24773,24 @@
       <c r="M29" s="6">
         <v>0</v>
       </c>
-      <c r="N29" s="13">
+      <c r="N29" s="29">
+        <v>324.50399940999995</v>
+      </c>
+      <c r="O29" s="7">
+        <v>60.551999910000006</v>
+      </c>
+      <c r="P29" s="13">
         <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="O29" s="6">
-        <v>0</v>
-      </c>
-      <c r="P29" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="6">
+        <v>0</v>
+      </c>
+      <c r="R29" s="6">
+        <v>0</v>
+      </c>
+      <c r="S29" s="13">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q29" s="6">
-        <v>0</v>
-      </c>
-      <c r="R29" s="6">
-        <v>0</v>
-      </c>
-      <c r="S29" s="13">
-        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="T29" s="6" t="s">
@@ -24826,7 +24798,7 @@
       </c>
       <c r="U29" s="4"/>
       <c r="V29" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>27</v>
       </c>
       <c r="W29" s="15">
@@ -24858,11 +24830,11 @@
       <c r="A30" s="5">
         <v>45959</v>
       </c>
-      <c r="B30" s="6">
-        <v>0</v>
-      </c>
-      <c r="C30" s="6">
-        <v>0</v>
+      <c r="B30" s="7">
+        <v>2328.2279994999994</v>
+      </c>
+      <c r="C30" s="7">
+        <v>352.63199993000001</v>
       </c>
       <c r="D30" s="13">
         <f t="shared" si="0"/>
@@ -24886,7 +24858,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K30" s="6">
@@ -24899,25 +24871,24 @@
       <c r="M30" s="6">
         <v>0</v>
       </c>
-      <c r="N30" s="13">
+      <c r="N30" s="29">
+        <v>402.88799941999997</v>
+      </c>
+      <c r="O30" s="7">
+        <v>76.751999889999993</v>
+      </c>
+      <c r="P30" s="13">
         <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="O30" s="6">
-        <v>0</v>
-      </c>
-      <c r="P30" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>0</v>
+      </c>
+      <c r="R30" s="6">
+        <v>0</v>
+      </c>
+      <c r="S30" s="13">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q30" s="6">
-        <v>0</v>
-      </c>
-      <c r="R30" s="6">
-        <v>0</v>
-      </c>
-      <c r="S30" s="13">
-        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="T30" s="6" t="s">
@@ -24925,7 +24896,7 @@
       </c>
       <c r="U30" s="4"/>
       <c r="V30" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="W30" s="15">
@@ -24957,11 +24928,11 @@
       <c r="A31" s="5">
         <v>45960</v>
       </c>
-      <c r="B31" s="6">
-        <v>0</v>
-      </c>
-      <c r="C31" s="6">
-        <v>0</v>
+      <c r="B31" s="7">
+        <v>1901.2559995199997</v>
+      </c>
+      <c r="C31" s="7">
+        <v>237.21599992</v>
       </c>
       <c r="D31" s="13">
         <f t="shared" si="0"/>
@@ -24985,7 +24956,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K31" s="6">
@@ -24998,25 +24969,24 @@
       <c r="M31" s="6">
         <v>0</v>
       </c>
-      <c r="N31" s="13">
+      <c r="N31" s="29">
+        <v>325.15199937000017</v>
+      </c>
+      <c r="O31" s="7">
+        <v>63.839999890000001</v>
+      </c>
+      <c r="P31" s="13">
         <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="O31" s="6">
-        <v>0</v>
-      </c>
-      <c r="P31" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>0</v>
+      </c>
+      <c r="R31" s="6">
+        <v>0</v>
+      </c>
+      <c r="S31" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>0</v>
-      </c>
-      <c r="R31" s="6">
-        <v>0</v>
-      </c>
-      <c r="S31" s="13">
-        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="T31" s="6" t="s">
@@ -25024,7 +24994,7 @@
       </c>
       <c r="U31" s="4"/>
       <c r="V31" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>29</v>
       </c>
       <c r="W31" s="15">
@@ -25056,11 +25026,11 @@
       <c r="A32" s="5">
         <v>45961</v>
       </c>
-      <c r="B32" s="6">
-        <v>0</v>
-      </c>
-      <c r="C32" s="6">
-        <v>0</v>
+      <c r="B32" s="7">
+        <v>1520.2739994599997</v>
+      </c>
+      <c r="C32" s="7">
+        <v>234.14999992</v>
       </c>
       <c r="D32" s="13">
         <f>W33-W32</f>
@@ -25084,7 +25054,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="13">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K32" s="6">
@@ -25097,25 +25067,24 @@
       <c r="M32" s="6">
         <v>0</v>
       </c>
-      <c r="N32" s="13">
+      <c r="N32" s="29">
+        <v>309.26399934000005</v>
+      </c>
+      <c r="O32" s="7">
+        <v>59.18399994</v>
+      </c>
+      <c r="P32" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O32" s="6">
-        <v>0</v>
-      </c>
-      <c r="P32" s="13">
+      <c r="Q32" s="6">
+        <v>0</v>
+      </c>
+      <c r="R32" s="6">
+        <v>0</v>
+      </c>
+      <c r="S32" s="13">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="6">
-        <v>0</v>
-      </c>
-      <c r="R32" s="6">
-        <v>0</v>
-      </c>
-      <c r="S32" s="13">
-        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T32" s="6" t="s">
@@ -25123,7 +25092,7 @@
       </c>
       <c r="U32" s="4"/>
       <c r="V32" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="W32" s="15">
@@ -25154,7 +25123,7 @@
     <row r="33" spans="1:30" ht="12.75" x14ac:dyDescent="0.2">
       <c r="U33" s="4"/>
       <c r="V33" s="18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>31</v>
       </c>
       <c r="W33" s="15">

--- a/medicao_energia_2025.xlsx
+++ b/medicao_energia_2025.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="GASTOMENSAL" sheetId="1" state="visible" r:id="rId3"/>
@@ -354,17 +354,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="_-&quot;R$ &quot;* #,##0.00_-;&quot;-R$ &quot;* #,##0.00_-;_-&quot;R$ &quot;* \-??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;R$ &quot;* #,##0.00_-;&quot;-R$ &quot;* #,##0.00_-;_-&quot;R$ &quot;* \-??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.00"/>
-    <numFmt numFmtId="169" formatCode="0"/>
-    <numFmt numFmtId="170" formatCode="_-&quot;R$ &quot;* #,##0.000_-;&quot;-R$ &quot;* #,##0.000_-;_-&quot;R$ &quot;* \-??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="[$R$ -416]#,##0.00"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* \-???_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="0.00"/>
+    <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;R$ &quot;* #,##0.000_-;&quot;-R$ &quot;* #,##0.000_-;_-&quot;R$ &quot;* \-??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="[$R$ -416]#,##0.00"/>
+    <numFmt numFmtId="171" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* \-???_-;_-@_-"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -574,231 +573,231 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="17" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="17" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="17" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1054,792 +1053,792 @@
   <dimension ref="A1:S22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="0" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="13.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="13.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="13.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="13.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="12.15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="5" t="n">
         <v>33257.08</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>11421.12</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>1005.039</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>430.731</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>2233.763</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="5" t="n">
         <v>957.327</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="5" t="n">
         <v>3425.681</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>1468.149</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J2" s="5" t="n">
         <v>905.954</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="K2" s="5" t="n">
         <v>388.266</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="5" t="n">
         <v>679.469</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="M2" s="5" t="n">
         <v>291.201</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N2" s="5" t="n">
         <v>7546.52</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="O2" s="5" t="n">
         <v>3690.74</v>
       </c>
-      <c r="P2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="4" t="n">
+      <c r="P2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>34662.64</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>12923.27</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>1301.972</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>557.988</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>2088.422</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>895.038</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>2921.079</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>1251.891</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J3" s="5" t="n">
         <v>1145.515</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K3" s="5" t="n">
         <v>490.935</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="5" t="n">
         <v>687.302</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="M3" s="5" t="n">
         <v>294.558</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" s="5" t="n">
         <v>7279.59</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="5" t="n">
         <v>3440.58</v>
       </c>
-      <c r="P3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4" t="n">
+      <c r="P3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>38732.56</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>15148.14</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>1557.675</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>667.575</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>2790.004</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>1195.716</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="5" t="n">
         <v>3189.403</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>1366.887</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J4" s="5" t="n">
         <v>1139.068</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K4" s="5" t="n">
         <v>488.172</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="5" t="n">
         <v>854.287</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="M4" s="5" t="n">
         <v>366.123</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" s="5" t="n">
         <v>8302.77</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="O4" s="5" t="n">
         <v>4094.98</v>
       </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4" t="n">
+      <c r="P4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>32733.99</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>13320.42</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>1614.851</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>692.079</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>2178.323</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <v>933.567</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <v>3332.798</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>1428.342</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="5" t="n">
         <v>57.883</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="5" t="n">
         <v>24.807</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="5" t="n">
         <v>847.308</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="M5" s="5" t="n">
         <v>363.132</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="N5" s="5" t="n">
         <v>7360.23</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="O5" s="5" t="n">
         <v>3442.02</v>
       </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
+      <c r="P5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>29658.6</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>11856.09</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>1413.552</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>605.808</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="5" t="n">
         <v>1600.977</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="5" t="n">
         <v>686.133</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="5" t="n">
         <v>3361.092</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>1440.468</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="5" t="n">
         <v>1038.478</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" s="5" t="n">
         <v>445.062</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="5" t="n">
         <v>1036.861</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M6" s="5" t="n">
         <v>444.369</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="5" t="n">
         <v>6618.68</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="O6" s="5" t="n">
         <v>3472.13</v>
       </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4" t="n">
+      <c r="P6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>29014.23</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>11147.95</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>1093.8501</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <v>491.4399</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="5" t="n">
         <v>964.2957</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="5" t="n">
         <v>433.2343</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="5" t="n">
         <v>3648.3405</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="5" t="n">
         <v>1639.1095</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="5" t="n">
         <v>1095.6717</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="5" t="n">
         <v>492.2583</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="5" t="n">
         <v>906.2391</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="M7" s="5" t="n">
         <v>407.1509</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="5" t="n">
         <v>6962.7</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="O7" s="5" t="n">
         <v>3143.83</v>
       </c>
-      <c r="P7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4" t="n">
+      <c r="P7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>30377.2</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>12141.35</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="5" t="n">
         <v>1056.74</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <v>474.77</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="5" t="n">
         <v>1111.7</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="5" t="n">
         <v>499.45</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="5" t="n">
         <v>3638.02</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="5" t="n">
         <v>1634.475</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="5" t="n">
         <v>60.92</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="K8" s="5" t="n">
         <v>27.36</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="5" t="n">
         <v>934.1772</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="M8" s="5" t="n">
         <v>419.7</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="5" t="n">
         <v>6888.16</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="O8" s="5" t="n">
         <v>3678.28</v>
       </c>
-      <c r="P8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4" t="n">
+      <c r="P8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>34465.15</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>12666.75</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="5" t="n">
         <v>1057.021</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="5" t="n">
         <v>453.009</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="5" t="n">
         <v>1199.492</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="5" t="n">
         <v>514.068</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="5" t="n">
         <v>4666.942</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="5" t="n">
         <v>2000.118</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="5" t="n">
         <v>1162.273</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="K9" s="5" t="n">
         <v>498.117</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="5" t="n">
         <v>1192.8</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="M9" s="5" t="n">
         <v>511.2</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="N9" s="5" t="n">
         <v>8025.69</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="O9" s="5" t="n">
         <v>3709.53</v>
       </c>
-      <c r="P9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="4" t="n">
+      <c r="P9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="n">
         <v>43496.36</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
         <v>16134.03</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="5" t="n">
         <v>1372.826</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="5" t="n">
         <v>588.354</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="5" t="n">
         <v>1747.998</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="5" t="n">
         <v>749.142</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="5" t="n">
         <v>4365.641</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="5" t="n">
         <v>1870.989</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J10" s="5" t="n">
         <v>1071.959</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="K10" s="5" t="n">
         <v>459.411</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="5" t="n">
         <v>1181.292</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="M10" s="5" t="n">
         <v>506.268</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="N10" s="5" t="n">
         <v>9005.64</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="O10" s="5" t="n">
         <v>4227.58</v>
       </c>
-      <c r="P10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4" t="n">
+      <c r="P10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="5" t="n">
         <v>44891.3</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="5" t="n">
         <v>17165.38</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="5" t="n">
         <v>1806</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="5" t="n">
         <v>774</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="5" t="n">
         <v>2170.707</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="5" t="n">
         <v>930.303</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="5" t="n">
         <v>4353.552</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="5" t="n">
         <v>1865.808</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="5" t="n">
         <v>67.368</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="K11" s="5" t="n">
         <v>28.872</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="L11" s="5" t="n">
         <v>1187.2</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="M11" s="5" t="n">
         <v>508.8</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="N11" s="5" t="n">
         <v>6086.84</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="O11" s="5" t="n">
         <v>4659.17</v>
       </c>
-      <c r="P11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="4" t="n">
+      <c r="P11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="4" t="n">
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="4" t="n">
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1879,22 +1878,22 @@
   <dimension ref="A1:AG101"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="19.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="11.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="7.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="17" style="0" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="19.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="11.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="7.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="17" style="1" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1907,94 +1906,94 @@
       <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U1" s="11"/>
       <c r="V1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45748</v>
       </c>
       <c r="B2" s="38" t="n">
@@ -5324,8 +5323,8 @@
   <dimension ref="A1:AG103"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="7.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5338,94 +5337,94 @@
       <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U1" s="11"/>
       <c r="V1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45717</v>
       </c>
       <c r="B2" s="55" t="n">
@@ -9141,8 +9140,8 @@
   <dimension ref="A1:AG99"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="7.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9155,94 +9154,94 @@
       <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U1" s="11"/>
       <c r="V1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45689</v>
       </c>
       <c r="B2" s="13" t="n">
@@ -12132,8 +12131,8 @@
   <dimension ref="A1:AG103"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="8.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="14.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12146,94 +12145,94 @@
       <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U1" s="11"/>
       <c r="V1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45658</v>
       </c>
       <c r="B2" s="13" t="n">
@@ -15300,15 +15299,15 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -15364,15 +15363,15 @@
   <dimension ref="A1:AG102"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15385,94 +15384,94 @@
       <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U1" s="11"/>
       <c r="V1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45992</v>
       </c>
       <c r="B2" s="12" t="n">
@@ -15558,7 +15557,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45993</v>
       </c>
       <c r="B3" s="12" t="n">
@@ -15637,7 +15636,7 @@
       <c r="AD3" s="19"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45994</v>
       </c>
       <c r="B4" s="12" t="n">
@@ -15717,7 +15716,7 @@
       <c r="AD4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45995</v>
       </c>
       <c r="B5" s="12" t="n">
@@ -15797,7 +15796,7 @@
       <c r="AD5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45996</v>
       </c>
       <c r="B6" s="12" t="n">
@@ -15877,7 +15876,7 @@
       <c r="AD6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45997</v>
       </c>
       <c r="B7" s="12" t="n">
@@ -15957,7 +15956,7 @@
       <c r="AD7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45998</v>
       </c>
       <c r="B8" s="12" t="n">
@@ -16037,7 +16036,7 @@
       <c r="AD8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45999</v>
       </c>
       <c r="B9" s="12" t="n">
@@ -16117,7 +16116,7 @@
       <c r="AD9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>46000</v>
       </c>
       <c r="B10" s="12" t="n">
@@ -16197,7 +16196,7 @@
       <c r="AD10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>46001</v>
       </c>
       <c r="B11" s="12" t="n">
@@ -16277,7 +16276,7 @@
       <c r="AD11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>46002</v>
       </c>
       <c r="B12" s="12" t="n">
@@ -16357,7 +16356,7 @@
       <c r="AD12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>46003</v>
       </c>
       <c r="B13" s="12" t="n">
@@ -16437,7 +16436,7 @@
       <c r="AD13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>46004</v>
       </c>
       <c r="B14" s="12" t="n">
@@ -16517,7 +16516,7 @@
       <c r="AD14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>46005</v>
       </c>
       <c r="B15" s="12" t="n">
@@ -16596,7 +16595,7 @@
       <c r="AD15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>46006</v>
       </c>
       <c r="B16" s="12" t="n">
@@ -16676,7 +16675,7 @@
       <c r="AD16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>46007</v>
       </c>
       <c r="B17" s="12" t="n">
@@ -16756,7 +16755,7 @@
       <c r="AD17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>46008</v>
       </c>
       <c r="B18" s="12" t="n">
@@ -16836,7 +16835,7 @@
       <c r="AD18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>46009</v>
       </c>
       <c r="B19" s="12" t="n">
@@ -16916,7 +16915,7 @@
       <c r="AD19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>46010</v>
       </c>
       <c r="B20" s="12" t="n">
@@ -16996,7 +16995,7 @@
       <c r="AD20" s="21"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>46011</v>
       </c>
       <c r="B21" s="12" t="n">
@@ -17076,7 +17075,7 @@
       <c r="AD21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>46012</v>
       </c>
       <c r="B22" s="12" t="n">
@@ -17156,7 +17155,7 @@
       <c r="AD22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>46013</v>
       </c>
       <c r="B23" s="12" t="n">
@@ -17236,7 +17235,7 @@
       <c r="AD23" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>46014</v>
       </c>
       <c r="B24" s="12" t="n">
@@ -17316,7 +17315,7 @@
       <c r="AD24" s="21"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>46015</v>
       </c>
       <c r="B25" s="12" t="n">
@@ -17396,7 +17395,7 @@
       <c r="AD25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="4" t="n">
         <v>46016</v>
       </c>
       <c r="B26" s="12" t="n">
@@ -17476,7 +17475,7 @@
       <c r="AD26" s="27"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="4" t="n">
         <v>46017</v>
       </c>
       <c r="B27" s="12" t="n">
@@ -17556,7 +17555,7 @@
       <c r="AD27" s="21"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="4" t="n">
         <v>46018</v>
       </c>
       <c r="B28" s="12" t="n">
@@ -17636,7 +17635,7 @@
       <c r="AD28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="4" t="n">
         <v>46019</v>
       </c>
       <c r="B29" s="12" t="n">
@@ -17716,7 +17715,7 @@
       <c r="AD29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="4" t="n">
         <v>46020</v>
       </c>
       <c r="B30" s="12" t="n">
@@ -17796,7 +17795,7 @@
       <c r="AD30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="4" t="n">
         <v>46021</v>
       </c>
       <c r="B31" s="12" t="n">
@@ -17876,7 +17875,7 @@
       <c r="AD31" s="21"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="4" t="n">
         <v>46022</v>
       </c>
       <c r="B32" s="12" t="n">
@@ -18664,15 +18663,16 @@
   <dimension ref="A1:AG102"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="3.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="15.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18685,94 +18685,94 @@
       <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U1" s="11"/>
       <c r="V1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45962</v>
       </c>
       <c r="B2" s="12" t="n">
@@ -18875,7 +18875,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45963</v>
       </c>
       <c r="B3" s="12" t="n">
@@ -18971,7 +18971,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45964</v>
       </c>
       <c r="B4" s="12" t="n">
@@ -19068,7 +19068,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45965</v>
       </c>
       <c r="B5" s="12" t="n">
@@ -19165,7 +19165,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45966</v>
       </c>
       <c r="B6" s="12" t="n">
@@ -19176,49 +19176,49 @@
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">W7-W6</f>
-        <v>-14888</v>
+        <v>98</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="19" t="n">
         <f aca="false">X7-X6</f>
-        <v>-19005</v>
+        <v>149</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="19" t="n">
         <f aca="false">Y7-Y6</f>
-        <v>-9937</v>
+        <v>3</v>
       </c>
       <c r="I6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="19" t="n">
         <f aca="false">Z7-Z6</f>
-        <v>-10906</v>
+        <v>1</v>
       </c>
       <c r="K6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="19" t="n">
         <f aca="false">AA7-AA6</f>
-        <v>-1300</v>
+        <v>0</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="19" t="n">
         <f aca="false">AB7-AB6</f>
-        <v>-4405</v>
+        <v>2</v>
       </c>
       <c r="O6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="19" t="n">
         <f aca="false">AC7-AC6</f>
-        <v>-449</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="12" t="n">
         <v>0</v>
@@ -19228,7 +19228,7 @@
       </c>
       <c r="S6" s="19" t="n">
         <f aca="false">AD7-AD6</f>
-        <v>-3956</v>
+        <v>5</v>
       </c>
       <c r="T6" s="12"/>
       <c r="U6" s="11"/>
@@ -19262,7 +19262,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45967</v>
       </c>
       <c r="B7" s="12" t="n">
@@ -19273,28 +19273,28 @@
       </c>
       <c r="D7" s="19" t="n">
         <f aca="false">W8-W7</f>
-        <v>-1</v>
+        <v>123</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="19" t="n">
         <f aca="false">X8-X7</f>
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="G7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="19" t="n">
         <f aca="false">Y8-Y7</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="19" t="n">
         <f aca="false">Z8-Z7</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K7" s="12" t="n">
         <v>0</v>
@@ -19308,7 +19308,7 @@
       </c>
       <c r="N7" s="19" t="n">
         <f aca="false">AB8-AB7</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O7" s="12" t="n">
         <v>0</v>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="S7" s="19" t="n">
         <f aca="false">AD8-AD7</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T7" s="12"/>
       <c r="U7" s="11"/>
@@ -19334,18 +19334,32 @@
         <v>5</v>
       </c>
       <c r="W7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X7" s="12"/>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="12"/>
-      <c r="AA7" s="12"/>
-      <c r="AB7" s="12"/>
-      <c r="AC7" s="12"/>
-      <c r="AD7" s="12"/>
+        <v>14987</v>
+      </c>
+      <c r="X7" s="12" t="n">
+        <v>19154</v>
+      </c>
+      <c r="Y7" s="12" t="n">
+        <v>9940</v>
+      </c>
+      <c r="Z7" s="12" t="n">
+        <v>10907</v>
+      </c>
+      <c r="AA7" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="AB7" s="12" t="n">
+        <v>4407</v>
+      </c>
+      <c r="AC7" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="AD7" s="12" t="n">
+        <v>3961</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45968</v>
       </c>
       <c r="B8" s="12" t="n">
@@ -19356,49 +19370,49 @@
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">W9-W8</f>
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">X9-X8</f>
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="19" t="n">
         <f aca="false">Y9-Y8</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="19" t="n">
         <f aca="false">Z9-Z8</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="19" t="n">
         <f aca="false">AA9-AA8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="19" t="n">
         <f aca="false">AB9-AB8</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="19" t="n">
         <f aca="false">AC9-AC8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="12" t="n">
         <v>0</v>
@@ -19408,7 +19422,7 @@
       </c>
       <c r="S8" s="19" t="n">
         <f aca="false">AD9-AD8</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T8" s="12"/>
       <c r="U8" s="11"/>
@@ -19416,17 +19430,33 @@
         <f aca="false">V7+1</f>
         <v>6</v>
       </c>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="12"/>
-      <c r="AA8" s="12"/>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="12"/>
+      <c r="W8" s="12" t="n">
+        <v>15110</v>
+      </c>
+      <c r="X8" s="12" t="n">
+        <v>19325</v>
+      </c>
+      <c r="Y8" s="12" t="n">
+        <v>9943</v>
+      </c>
+      <c r="Z8" s="12" t="n">
+        <v>10906</v>
+      </c>
+      <c r="AA8" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="AB8" s="12" t="n">
+        <v>4416</v>
+      </c>
+      <c r="AC8" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="AD8" s="12" t="n">
+        <v>3966</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45969</v>
       </c>
       <c r="B9" s="12" t="n">
@@ -19497,17 +19527,33 @@
         <f aca="false">V8+1</f>
         <v>7</v>
       </c>
-      <c r="W9" s="12"/>
-      <c r="X9" s="12"/>
-      <c r="Y9" s="12"/>
-      <c r="Z9" s="12"/>
-      <c r="AA9" s="12"/>
-      <c r="AB9" s="12"/>
-      <c r="AC9" s="12"/>
-      <c r="AD9" s="12"/>
+      <c r="W9" s="12" t="n">
+        <v>15275</v>
+      </c>
+      <c r="X9" s="12" t="n">
+        <v>19512</v>
+      </c>
+      <c r="Y9" s="12" t="n">
+        <v>9951</v>
+      </c>
+      <c r="Z9" s="12" t="n">
+        <v>10919</v>
+      </c>
+      <c r="AA9" s="12" t="n">
+        <v>1301</v>
+      </c>
+      <c r="AB9" s="12" t="n">
+        <v>4423</v>
+      </c>
+      <c r="AC9" s="12" t="n">
+        <v>451</v>
+      </c>
+      <c r="AD9" s="12" t="n">
+        <v>3972</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45970</v>
       </c>
       <c r="B10" s="12" t="n">
@@ -19518,21 +19564,21 @@
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">W11-W10</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">X11-X10</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="19" t="n">
         <f aca="false">Y11-Y10</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" s="12" t="n">
         <v>0</v>
@@ -19553,14 +19599,14 @@
       </c>
       <c r="N10" s="19" t="n">
         <f aca="false">AB11-AB10</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="19" t="n">
         <f aca="false">AC11-AC10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="12" t="n">
         <v>0</v>
@@ -19570,7 +19616,7 @@
       </c>
       <c r="S10" s="19" t="n">
         <f aca="false">AD11-AD10</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T10" s="12"/>
       <c r="U10" s="11"/>
@@ -19578,17 +19624,33 @@
         <f aca="false">V9+1</f>
         <v>8</v>
       </c>
-      <c r="W10" s="12"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="12"/>
-      <c r="Z10" s="12"/>
-      <c r="AA10" s="12"/>
-      <c r="AB10" s="12"/>
-      <c r="AC10" s="12"/>
-      <c r="AD10" s="12"/>
+      <c r="W10" s="12" t="n">
+        <v>15275</v>
+      </c>
+      <c r="X10" s="12" t="n">
+        <v>19512</v>
+      </c>
+      <c r="Y10" s="12" t="n">
+        <v>9951</v>
+      </c>
+      <c r="Z10" s="12" t="n">
+        <v>10919</v>
+      </c>
+      <c r="AA10" s="12" t="n">
+        <v>1301</v>
+      </c>
+      <c r="AB10" s="12" t="n">
+        <v>4423</v>
+      </c>
+      <c r="AC10" s="12" t="n">
+        <v>451</v>
+      </c>
+      <c r="AD10" s="12" t="n">
+        <v>3972</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>45971</v>
       </c>
       <c r="B11" s="12" t="n">
@@ -19613,14 +19675,14 @@
       </c>
       <c r="H11" s="19" t="n">
         <f aca="false">Y12-Y11</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="19" t="n">
         <f aca="false">Z12-Z11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>0</v>
@@ -19634,7 +19696,7 @@
       </c>
       <c r="N11" s="19" t="n">
         <f aca="false">AB12-AB11</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O11" s="12" t="n">
         <v>0</v>
@@ -19651,7 +19713,7 @@
       </c>
       <c r="S11" s="19" t="n">
         <f aca="false">AD12-AD11</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T11" s="12"/>
       <c r="U11" s="11"/>
@@ -19659,17 +19721,33 @@
         <f aca="false">V10+1</f>
         <v>9</v>
       </c>
-      <c r="W11" s="12"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="12"/>
-      <c r="Z11" s="12"/>
-      <c r="AA11" s="12"/>
-      <c r="AB11" s="12"/>
-      <c r="AC11" s="12"/>
-      <c r="AD11" s="12"/>
+      <c r="W11" s="12" t="n">
+        <v>15304</v>
+      </c>
+      <c r="X11" s="12" t="n">
+        <v>19596</v>
+      </c>
+      <c r="Y11" s="12" t="n">
+        <v>9954</v>
+      </c>
+      <c r="Z11" s="12" t="n">
+        <v>10919</v>
+      </c>
+      <c r="AA11" s="12" t="n">
+        <v>1301</v>
+      </c>
+      <c r="AB11" s="12" t="n">
+        <v>4432</v>
+      </c>
+      <c r="AC11" s="12" t="n">
+        <v>452</v>
+      </c>
+      <c r="AD11" s="12" t="n">
+        <v>3980</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>45972</v>
       </c>
       <c r="B12" s="12" t="n">
@@ -19680,28 +19758,28 @@
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">W13-W12</f>
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="19" t="n">
         <f aca="false">X13-X12</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="19" t="n">
         <f aca="false">Y13-Y12</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="19" t="n">
         <f aca="false">Z13-Z12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>0</v>
@@ -19715,14 +19793,14 @@
       </c>
       <c r="N12" s="19" t="n">
         <f aca="false">AB13-AB12</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P12" s="19" t="n">
         <f aca="false">AC13-AC12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="12" t="n">
         <v>0</v>
@@ -19732,7 +19810,7 @@
       </c>
       <c r="S12" s="19" t="n">
         <f aca="false">AD13-AD12</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12" s="12"/>
       <c r="U12" s="11"/>
@@ -19740,17 +19818,33 @@
         <f aca="false">V11+1</f>
         <v>10</v>
       </c>
-      <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="12"/>
-      <c r="Z12" s="12"/>
-      <c r="AA12" s="12"/>
-      <c r="AB12" s="12"/>
-      <c r="AC12" s="12"/>
-      <c r="AD12" s="12"/>
+      <c r="W12" s="12" t="n">
+        <v>15304</v>
+      </c>
+      <c r="X12" s="12" t="n">
+        <v>19596</v>
+      </c>
+      <c r="Y12" s="12" t="n">
+        <v>9959</v>
+      </c>
+      <c r="Z12" s="12" t="n">
+        <v>10920</v>
+      </c>
+      <c r="AA12" s="12" t="n">
+        <v>1301</v>
+      </c>
+      <c r="AB12" s="12" t="n">
+        <v>4437</v>
+      </c>
+      <c r="AC12" s="12" t="n">
+        <v>452</v>
+      </c>
+      <c r="AD12" s="12" t="n">
+        <v>3984</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>45973</v>
       </c>
       <c r="B13" s="12" t="n">
@@ -19761,42 +19855,42 @@
       </c>
       <c r="D13" s="19" t="n">
         <f aca="false">W14-W13</f>
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="19" t="n">
         <f aca="false">X14-X13</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="19" t="n">
         <f aca="false">Y14-Y13</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="19" t="n">
         <f aca="false">Z14-Z13</f>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="19" t="n">
         <f aca="false">AA14-AA13</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="19" t="n">
         <f aca="false">AB14-AB13</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O13" s="12" t="n">
         <v>0</v>
@@ -19821,17 +19915,33 @@
         <f aca="false">V12+1</f>
         <v>11</v>
       </c>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
+      <c r="W13" s="21" t="n">
+        <v>15415</v>
+      </c>
+      <c r="X13" s="21" t="n">
+        <v>19796</v>
+      </c>
+      <c r="Y13" s="21" t="n">
+        <v>9966</v>
+      </c>
+      <c r="Z13" s="21" t="n">
+        <v>10921</v>
+      </c>
+      <c r="AA13" s="21" t="n">
+        <v>1301</v>
+      </c>
+      <c r="AB13" s="21" t="n">
+        <v>4440</v>
+      </c>
+      <c r="AC13" s="21" t="n">
+        <v>453</v>
+      </c>
+      <c r="AD13" s="21" t="n">
+        <v>3987</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>45974</v>
       </c>
       <c r="B14" s="12" t="n">
@@ -19842,49 +19952,49 @@
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">W15-W14</f>
-        <v>0</v>
+        <v>-15539</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false">X15-X14</f>
-        <v>0</v>
+        <v>-19832</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="19" t="n">
         <f aca="false">Y15-Y14</f>
-        <v>0</v>
+        <v>-9971</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="19" t="n">
         <f aca="false">Z15-Z14</f>
-        <v>0</v>
+        <v>-10913</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="19" t="n">
         <f aca="false">AA15-AA14</f>
-        <v>0</v>
+        <v>-1302</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="19" t="n">
         <f aca="false">AB15-AB14</f>
-        <v>0</v>
+        <v>-4447</v>
       </c>
       <c r="O14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="19" t="n">
         <f aca="false">AC15-AC14</f>
-        <v>0</v>
+        <v>-453</v>
       </c>
       <c r="Q14" s="12" t="n">
         <v>0</v>
@@ -19894,7 +20004,7 @@
       </c>
       <c r="S14" s="19" t="n">
         <f aca="false">AD15-AD14</f>
-        <v>0</v>
+        <v>-3987</v>
       </c>
       <c r="T14" s="12"/>
       <c r="U14" s="11"/>
@@ -19902,17 +20012,33 @@
         <f aca="false">V13+1</f>
         <v>12</v>
       </c>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12"/>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="12"/>
-      <c r="AB14" s="12"/>
-      <c r="AC14" s="12"/>
-      <c r="AD14" s="12"/>
+      <c r="W14" s="12" t="n">
+        <v>15539</v>
+      </c>
+      <c r="X14" s="12" t="n">
+        <v>19832</v>
+      </c>
+      <c r="Y14" s="12" t="n">
+        <v>9971</v>
+      </c>
+      <c r="Z14" s="12" t="n">
+        <v>10913</v>
+      </c>
+      <c r="AA14" s="12" t="n">
+        <v>1302</v>
+      </c>
+      <c r="AB14" s="12" t="n">
+        <v>4447</v>
+      </c>
+      <c r="AC14" s="12" t="n">
+        <v>453</v>
+      </c>
+      <c r="AD14" s="12" t="n">
+        <v>3987</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>45975</v>
       </c>
       <c r="B15" s="12" t="n">
@@ -19992,7 +20118,7 @@
       <c r="AD15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>45976</v>
       </c>
       <c r="B16" s="12" t="n">
@@ -20073,7 +20199,7 @@
       <c r="AD16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>45977</v>
       </c>
       <c r="B17" s="12" t="n">
@@ -20154,7 +20280,7 @@
       <c r="AD17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>45978</v>
       </c>
       <c r="B18" s="12" t="n">
@@ -20235,7 +20361,7 @@
       <c r="AD18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>45979</v>
       </c>
       <c r="B19" s="12" t="n">
@@ -20316,7 +20442,7 @@
       <c r="AD19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>45980</v>
       </c>
       <c r="B20" s="12" t="n">
@@ -20397,7 +20523,7 @@
       <c r="AD20" s="21"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>45981</v>
       </c>
       <c r="B21" s="12" t="n">
@@ -20478,7 +20604,7 @@
       <c r="AD21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>45982</v>
       </c>
       <c r="B22" s="12" t="n">
@@ -20559,7 +20685,7 @@
       <c r="AD22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>45983</v>
       </c>
       <c r="B23" s="12" t="n">
@@ -20640,7 +20766,7 @@
       <c r="AD23" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>45984</v>
       </c>
       <c r="B24" s="12" t="n">
@@ -20721,7 +20847,7 @@
       <c r="AD24" s="21"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>45985</v>
       </c>
       <c r="B25" s="12" t="n">
@@ -20802,7 +20928,7 @@
       <c r="AD25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="4" t="n">
         <v>45986</v>
       </c>
       <c r="B26" s="12" t="n">
@@ -20883,7 +21009,7 @@
       <c r="AD26" s="27"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="4" t="n">
         <v>45987</v>
       </c>
       <c r="B27" s="12" t="n">
@@ -20964,7 +21090,7 @@
       <c r="AD27" s="21"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="4" t="n">
         <v>45988</v>
       </c>
       <c r="B28" s="12" t="n">
@@ -21045,7 +21171,7 @@
       <c r="AD28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="4" t="n">
         <v>45989</v>
       </c>
       <c r="B29" s="12" t="n">
@@ -21126,7 +21252,7 @@
       <c r="AD29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="4" t="n">
         <v>45990</v>
       </c>
       <c r="B30" s="12" t="n">
@@ -21207,7 +21333,7 @@
       <c r="AD30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="4" t="n">
         <v>45991</v>
       </c>
       <c r="B31" s="12" t="n">
@@ -21993,16 +22119,16 @@
   <dimension ref="A1:AG103"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="26.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="17.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="26.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22015,94 +22141,94 @@
       <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U1" s="11"/>
       <c r="V1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45931</v>
       </c>
       <c r="B2" s="13" t="n">
@@ -22204,7 +22330,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45932</v>
       </c>
       <c r="B3" s="13" t="n">
@@ -22299,7 +22425,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45933</v>
       </c>
       <c r="B4" s="13" t="n">
@@ -22395,7 +22521,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45934</v>
       </c>
       <c r="B5" s="13" t="n">
@@ -22491,7 +22617,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45935</v>
       </c>
       <c r="B6" s="13" t="n">
@@ -22587,7 +22713,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45936</v>
       </c>
       <c r="B7" s="13" t="n">
@@ -22683,7 +22809,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45937</v>
       </c>
       <c r="B8" s="13" t="n">
@@ -22779,7 +22905,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45938</v>
       </c>
       <c r="B9" s="13" t="n">
@@ -22875,7 +23001,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45939</v>
       </c>
       <c r="B10" s="13" t="n">
@@ -22971,7 +23097,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>45940</v>
       </c>
       <c r="B11" s="13" t="n">
@@ -23067,7 +23193,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>45941</v>
       </c>
       <c r="B12" s="13" t="n">
@@ -23163,7 +23289,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>45942</v>
       </c>
       <c r="B13" s="13" t="n">
@@ -23259,7 +23385,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>45943</v>
       </c>
       <c r="B14" s="13" t="n">
@@ -23355,7 +23481,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>45944</v>
       </c>
       <c r="B15" s="13" t="n">
@@ -23450,7 +23576,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>45945</v>
       </c>
       <c r="B16" s="13" t="n">
@@ -23546,7 +23672,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>45946</v>
       </c>
       <c r="B17" s="13" t="n">
@@ -23642,7 +23768,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>45947</v>
       </c>
       <c r="B18" s="13" t="n">
@@ -23738,7 +23864,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>45948</v>
       </c>
       <c r="B19" s="13" t="n">
@@ -23834,7 +23960,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>45949</v>
       </c>
       <c r="B20" s="13" t="n">
@@ -23930,7 +24056,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>45950</v>
       </c>
       <c r="B21" s="13" t="n">
@@ -24026,7 +24152,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>45951</v>
       </c>
       <c r="B22" s="13" t="n">
@@ -24122,7 +24248,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>45952</v>
       </c>
       <c r="B23" s="13" t="n">
@@ -24218,7 +24344,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>45953</v>
       </c>
       <c r="B24" s="13" t="n">
@@ -24314,7 +24440,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>45954</v>
       </c>
       <c r="B25" s="13" t="n">
@@ -24410,7 +24536,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="4" t="n">
         <v>45955</v>
       </c>
       <c r="B26" s="13" t="n">
@@ -24506,7 +24632,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="4" t="n">
         <v>45956</v>
       </c>
       <c r="B27" s="13" t="n">
@@ -24602,7 +24728,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="4" t="n">
         <v>45957</v>
       </c>
       <c r="B28" s="13" t="n">
@@ -24698,7 +24824,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="4" t="n">
         <v>45958</v>
       </c>
       <c r="B29" s="13" t="n">
@@ -24794,7 +24920,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="4" t="n">
         <v>45959</v>
       </c>
       <c r="B30" s="13" t="n">
@@ -24890,7 +25016,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="4" t="n">
         <v>45960</v>
       </c>
       <c r="B31" s="13" t="n">
@@ -24986,7 +25112,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="4" t="n">
         <v>45961</v>
       </c>
       <c r="B32" s="13" t="n">
@@ -25804,119 +25930,119 @@
   <dimension ref="A1:AH101"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="25.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="25.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="V1" s="11"/>
       <c r="W1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45901</v>
       </c>
       <c r="B2" s="13" t="n">
@@ -26019,7 +26145,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>45902</v>
       </c>
       <c r="B3" s="13" t="n">
@@ -26115,7 +26241,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>45903</v>
       </c>
       <c r="B4" s="13" t="n">
@@ -26212,7 +26338,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>45904</v>
       </c>
       <c r="B5" s="13" t="n">
@@ -26309,7 +26435,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>45905</v>
       </c>
       <c r="B6" s="13" t="n">
@@ -26406,7 +26532,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>45906</v>
       </c>
       <c r="B7" s="13" t="n">
@@ -26503,7 +26629,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>45907</v>
       </c>
       <c r="B8" s="13" t="n">
@@ -26600,7 +26726,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>45908</v>
       </c>
       <c r="B9" s="13" t="n">
@@ -26697,7 +26823,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>45909</v>
       </c>
       <c r="B10" s="13" t="n">
@@ -26794,7 +26920,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>45910</v>
       </c>
       <c r="B11" s="13" t="n">
@@ -26891,7 +27017,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>45911</v>
       </c>
       <c r="B12" s="13" t="n">
@@ -26988,7 +27114,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>45912</v>
       </c>
       <c r="B13" s="13" t="n">
@@ -27085,7 +27211,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>45913</v>
       </c>
       <c r="B14" s="13" t="n">
@@ -27182,7 +27308,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>45914</v>
       </c>
       <c r="B15" s="13" t="n">
@@ -27279,7 +27405,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>45915</v>
       </c>
       <c r="B16" s="13" t="n">
@@ -27376,7 +27502,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>45916</v>
       </c>
       <c r="B17" s="13" t="n">
@@ -27473,7 +27599,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>45917</v>
       </c>
       <c r="B18" s="13" t="n">
@@ -27570,7 +27696,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>45918</v>
       </c>
       <c r="B19" s="13" t="n">
@@ -27667,7 +27793,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>45919</v>
       </c>
       <c r="B20" s="13" t="n">
@@ -27764,7 +27890,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>45920</v>
       </c>
       <c r="B21" s="13" t="n">
@@ -27861,7 +27987,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>45921</v>
       </c>
       <c r="B22" s="13" t="n">
@@ -27958,7 +28084,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>45922</v>
       </c>
       <c r="B23" s="13" t="n">
@@ -28055,7 +28181,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>45923</v>
       </c>
       <c r="B24" s="13" t="n">
@@ -28152,7 +28278,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>45924</v>
       </c>
       <c r="B25" s="13" t="n">
@@ -28249,7 +28375,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="4" t="n">
         <v>45925</v>
       </c>
       <c r="B26" s="13" t="n">
@@ -28346,7 +28472,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="4" t="n">
         <v>45926</v>
       </c>
       <c r="B27" s="13" t="n">
@@ -28443,7 +28569,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="4" t="n">
         <v>45927</v>
       </c>
       <c r="B28" s="13" t="n">
@@ -28540,7 +28666,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="4" t="n">
         <v>45928</v>
       </c>
       <c r="B29" s="13" t="n">
@@ -28637,7 +28763,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="4" t="n">
         <v>45929</v>
       </c>
       <c r="B30" s="13" t="n">
@@ -28734,7 +28860,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="4" t="n">
         <v>45930</v>
       </c>
       <c r="B31" s="13" t="n">
@@ -29620,18 +29746,18 @@
   <dimension ref="A1:AN102"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="12.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="13.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="18.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="13.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29644,94 +29770,94 @@
       <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U1" s="11"/>
       <c r="V1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45870</v>
       </c>
       <c r="B2" s="38" t="n">
@@ -33499,17 +33625,17 @@
   <dimension ref="A1:AG103"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="47.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="47.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33522,94 +33648,94 @@
       <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U1" s="11"/>
       <c r="V1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>45839</v>
       </c>
       <c r="B2" s="38" t="n">
@@ -37282,12 +37408,12 @@
     <mergeCell ref="A101:I101"/>
   </mergeCells>
   <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="AF2" type="list">
+      <formula1>Planilha1!$A$2:$A$5</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A89" type="list">
       <formula1>"Bandeira,Verde,Amarela,Vermelha p1,Vermelha p2"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="AF2" type="list">
-      <formula1>Planilha1!$A$2:$A$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -37310,18 +37436,18 @@
   <dimension ref="A1:AG102"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="14.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="13.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="47.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="14.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="13.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="47.29"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="21" min="21" style="11" width="12.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="11.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37334,93 +37460,93 @@
       <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="V1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>35</v>
  